--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -9,8 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -23,11 +23,11 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0)"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.0x"/>
-    <numFmt numFmtId="168" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +138,29 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="10"/>
     </font>
@@ -149,6 +172,12 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00F2F2F2"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <color rgb="000000CC"/>
       <sz val="10"/>
     </font>
@@ -178,31 +207,8 @@
     </font>
     <font>
       <name val="Garamond"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
       <color rgb="00006100"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="001F2A44"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="7">
@@ -229,12 +235,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00006100"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00006100"/>
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -263,7 +269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -304,22 +310,58 @@
     <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,92 +370,59 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="29" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="17" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -422,7 +431,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1090,7 +1099,515 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>SCENARIO ANALYSIS</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+    </row>
+    <row r="2">
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>Key assumptions (5-yr forecast)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E revenue growth</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="D4" s="15" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>FY2027–FY2030E revenue growth (avg)</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>FY2026E EBIT margin</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Terminal (FY2030E) EBIT margin</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Terminal growth</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>5-year forecast paths (by scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue – year 1</t>
+        </is>
+      </c>
+      <c r="C12" s="26">
+        <f>11102600*(1+C4)</f>
+        <v/>
+      </c>
+      <c r="D12" s="26">
+        <f>11102600*(1+D4)</f>
+        <v/>
+      </c>
+      <c r="E12" s="26">
+        <f>11102600*(1+E4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue – year 2</t>
+        </is>
+      </c>
+      <c r="C13" s="26">
+        <f>C12*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D13" s="26">
+        <f>D12*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E13" s="26">
+        <f>E12*(1+E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue – year 3</t>
+        </is>
+      </c>
+      <c r="C14" s="26">
+        <f>C13*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D14" s="26">
+        <f>D13*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E14" s="26">
+        <f>E13*(1+E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue – year 4</t>
+        </is>
+      </c>
+      <c r="C15" s="26">
+        <f>C14*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D15" s="26">
+        <f>D14*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E15" s="26">
+        <f>E14*(1+E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue – year 5</t>
+        </is>
+      </c>
+      <c r="C16" s="26">
+        <f>C15*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D16" s="26">
+        <f>D15*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E16" s="26">
+        <f>E15*(1+E5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin – year 1</t>
+        </is>
+      </c>
+      <c r="C17" s="27">
+        <f>C6+(C7-C6)*0/4</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>D6+(D7-D6)*0/4</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>E6+(E7-E6)*0/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin – year 2</t>
+        </is>
+      </c>
+      <c r="C18" s="27">
+        <f>C6+(C7-C6)*1/4</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>D6+(D7-D6)*1/4</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>E6+(E7-E6)*1/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin – year 3</t>
+        </is>
+      </c>
+      <c r="C19" s="27">
+        <f>C6+(C7-C6)*2/4</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>D6+(D7-D6)*2/4</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>E6+(E7-E6)*2/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin – year 4</t>
+        </is>
+      </c>
+      <c r="C20" s="27">
+        <f>C6+(C7-C6)*3/4</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>D6+(D7-D6)*3/4</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>E6+(E7-E6)*3/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT margin – year 5</t>
+        </is>
+      </c>
+      <c r="C21" s="27">
+        <f>C6+(C7-C6)*4/4</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>D6+(D7-D6)*4/4</f>
+        <v/>
+      </c>
+      <c r="E21" s="27">
+        <f>E6+(E7-E6)*4/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 1</t>
+        </is>
+      </c>
+      <c r="C22" s="26">
+        <f>(C12*C17)*(1-0.27)+C12*0.045-C12*0.05-0.075*(C12-11102600)</f>
+        <v/>
+      </c>
+      <c r="D22" s="26">
+        <f>(D12*D17)*(1-0.27)+D12*0.045-D12*0.05-0.075*(D12-11102600)</f>
+        <v/>
+      </c>
+      <c r="E22" s="26">
+        <f>(E12*E17)*(1-0.27)+E12*0.045-E12*0.05-0.075*(E12-11102600)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 2</t>
+        </is>
+      </c>
+      <c r="C23" s="26">
+        <f>(C13*C18)*(1-0.27)+C13*0.045-C13*0.05-0.075*(C13-C12)</f>
+        <v/>
+      </c>
+      <c r="D23" s="26">
+        <f>(D13*D18)*(1-0.27)+D13*0.045-D13*0.05-0.075*(D13-D12)</f>
+        <v/>
+      </c>
+      <c r="E23" s="26">
+        <f>(E13*E18)*(1-0.27)+E13*0.045-E13*0.05-0.075*(E13-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 3</t>
+        </is>
+      </c>
+      <c r="C24" s="26">
+        <f>(C14*C19)*(1-0.27)+C14*0.045-C14*0.05-0.075*(C14-C13)</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>(D14*D19)*(1-0.27)+D14*0.045-D14*0.05-0.075*(D14-D13)</f>
+        <v/>
+      </c>
+      <c r="E24" s="26">
+        <f>(E14*E19)*(1-0.27)+E14*0.045-E14*0.05-0.075*(E14-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 4</t>
+        </is>
+      </c>
+      <c r="C25" s="26">
+        <f>(C15*C20)*(1-0.27)+C15*0.045-C15*0.05-0.075*(C15-C14)</f>
+        <v/>
+      </c>
+      <c r="D25" s="26">
+        <f>(D15*D20)*(1-0.27)+D15*0.045-D15*0.05-0.075*(D15-D14)</f>
+        <v/>
+      </c>
+      <c r="E25" s="26">
+        <f>(E15*E20)*(1-0.27)+E15*0.045-E15*0.05-0.075*(E15-E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 5</t>
+        </is>
+      </c>
+      <c r="C26" s="26">
+        <f>(C16*C21)*(1-0.27)+C16*0.045-C16*0.05-0.075*(C16-C15)</f>
+        <v/>
+      </c>
+      <c r="D26" s="26">
+        <f>(D16*D21)*(1-0.27)+D16*0.045-D16*0.05-0.075*(D16-D15)</f>
+        <v/>
+      </c>
+      <c r="E26" s="26">
+        <f>(E16*E21)*(1-0.27)+E16*0.045-E16*0.05-0.075*(E16-E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Enterprise value (DCF)</t>
+        </is>
+      </c>
+      <c r="C28" s="28">
+        <f>NPV(C8,C22,C23,C24,C25,C26)+(C26*(1+C9)/(C8-C9))/(1+C8)^5</f>
+        <v/>
+      </c>
+      <c r="D28" s="28">
+        <f>NPV(D8,D22,D23,D24,D25,D26)+(D26*(1+D9)/(D8-D9))/(1+D8)^5</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>NPV(E8,E22,E23,E24,E25,E26)+(E26*(1+E9)/(E8-E9))/(1+E8)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="C29" s="30">
+        <f>(C28+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="D29" s="31">
+        <f>(D28+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="E29" s="30">
+        <f>(E28+1807202-0)/111380</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs current</t>
+        </is>
+      </c>
+      <c r="C30" s="32">
+        <f>C29/100.0-1</f>
+        <v/>
+      </c>
+      <c r="D30" s="32">
+        <f>D29/100.0-1</f>
+        <v/>
+      </c>
+      <c r="E30" s="32">
+        <f>E29/100.0-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1118,57 +1635,42 @@
       <c r="H1" s="12" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="33" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="34" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="34" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="34" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="34" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="34" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Revenue growth %</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>0.03</v>
+    <row r="3">
+      <c r="A3" s="35" t="inlineStr">
+        <is>
+          <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1177,1285 +1679,810 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="36" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="25">
-        <f>C5*(1+D4)</f>
-        <v/>
-      </c>
-      <c r="E5" s="25">
-        <f>D5*(1+E4)</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>E5*(1+F4)</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>F5*(1+G4)</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>G5*(1+H4)</f>
+      <c r="D5" s="37">
+        <f>Scenarios!D12</f>
+        <v/>
+      </c>
+      <c r="E5" s="37">
+        <f>Scenarios!D13</f>
+        <v/>
+      </c>
+      <c r="F5" s="37">
+        <f>Scenarios!D14</f>
+        <v/>
+      </c>
+      <c r="G5" s="37">
+        <f>Scenarios!D15</f>
+        <v/>
+      </c>
+      <c r="H5" s="37">
+        <f>Scenarios!D16</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
+          <t>Revenue growth %</t>
+        </is>
+      </c>
+      <c r="D6" s="38">
+        <f>D5/C5-1</f>
+        <v/>
+      </c>
+      <c r="E6" s="38">
+        <f>E5/D5-1</f>
+        <v/>
+      </c>
+      <c r="F6" s="38">
+        <f>F5/E5-1</f>
+        <v/>
+      </c>
+      <c r="G6" s="38">
+        <f>G5/F5-1</f>
+        <v/>
+      </c>
+      <c r="H6" s="38">
+        <f>H5/G5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.155</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="D7" s="38">
+        <f>Scenarios!D17</f>
+        <v/>
+      </c>
+      <c r="E7" s="38">
+        <f>Scenarios!D18</f>
+        <v/>
+      </c>
+      <c r="F7" s="38">
+        <f>Scenarios!D19</f>
+        <v/>
+      </c>
+      <c r="G7" s="38">
+        <f>Scenarios!D20</f>
+        <v/>
+      </c>
+      <c r="H7" s="38">
+        <f>Scenarios!D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C8" s="39" t="n">
         <v>2210615</v>
       </c>
-      <c r="D7" s="27">
-        <f>D5*D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="27">
-        <f>E5*E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="27">
-        <f>F5*F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>G5*G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="27">
-        <f>H5*H6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="D8" s="28">
+        <f>D5*D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>E5*E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="28">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="28">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D8" s="25">
-        <f>-D7*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>-E7*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>-F7*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>-G7*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>-H7*WACC!C10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="D9" s="37">
+        <f>-D8*WACC!C10</f>
+        <v/>
+      </c>
+      <c r="E9" s="37">
+        <f>-E8*WACC!C10</f>
+        <v/>
+      </c>
+      <c r="F9" s="37">
+        <f>-F8*WACC!C10</f>
+        <v/>
+      </c>
+      <c r="G9" s="37">
+        <f>-G8*WACC!C10</f>
+        <v/>
+      </c>
+      <c r="H9" s="37">
+        <f>-H8*WACC!C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D9" s="27">
-        <f>D7+D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="27">
-        <f>E7+E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="27">
-        <f>F7+F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="27">
-        <f>G7+G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="27">
-        <f>H7+H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>0.045</v>
+      <c r="D10" s="28">
+        <f>D8+D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>E8+E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>F8+F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="28">
+        <f>G8+G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="28">
+        <f>H8+H9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Plus: depreciation &amp; amortization</t>
-        </is>
-      </c>
-      <c r="D11" s="25">
-        <f>D5*D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="25">
-        <f>E5*E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>F5*F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>G5*G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="25">
-        <f>H5*H10</f>
-        <v/>
+          <t xml:space="preserve">  D&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0.045</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex % of revenue</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.05</v>
+          <t>Plus: depreciation &amp; amortization</t>
+        </is>
+      </c>
+      <c r="D12" s="37">
+        <f>D5*D11</f>
+        <v/>
+      </c>
+      <c r="E12" s="37">
+        <f>E5*E11</f>
+        <v/>
+      </c>
+      <c r="F12" s="37">
+        <f>F5*F11</f>
+        <v/>
+      </c>
+      <c r="G12" s="37">
+        <f>G5*G11</f>
+        <v/>
+      </c>
+      <c r="H12" s="37">
+        <f>H5*H11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Less: capital expenditures</t>
-        </is>
-      </c>
-      <c r="D13" s="25">
-        <f>-D5*D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>-E5*E12</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>-F5*F12</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>-G5*G12</f>
-        <v/>
-      </c>
-      <c r="H13" s="25">
-        <f>-H5*H12</f>
-        <v/>
+          <t xml:space="preserve">  Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NWC % of revenue</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F14" s="15" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G14" s="15" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H14" s="15" t="n">
-        <v>0.075</v>
+          <t>Less: capital expenditures</t>
+        </is>
+      </c>
+      <c r="D14" s="37">
+        <f>-D5*D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="37">
+        <f>-E5*E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="37">
+        <f>-F5*F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="37">
+        <f>-G5*G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="37">
+        <f>-H5*H13</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t xml:space="preserve">  NWC % of revenue</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
           <t>Less: increase in net working capital</t>
         </is>
       </c>
-      <c r="D15" s="25">
-        <f>-D14*(D5-C5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="25">
-        <f>-E14*(E5-D5)</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>-F14*(F5-E5)</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>-G14*(G5-F5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="25">
-        <f>-H14*(H5-G5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="D16" s="37">
+        <f>-D15*(D5-C5)</f>
+        <v/>
+      </c>
+      <c r="E16" s="37">
+        <f>-E15*(E5-D5)</f>
+        <v/>
+      </c>
+      <c r="F16" s="37">
+        <f>-F15*(F5-E5)</f>
+        <v/>
+      </c>
+      <c r="G16" s="37">
+        <f>-G15*(G5-F5)</f>
+        <v/>
+      </c>
+      <c r="H16" s="37">
+        <f>-H15*(H5-G5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D16" s="28">
-        <f>D9+D11+D13+D15</f>
-        <v/>
-      </c>
-      <c r="E16" s="28">
-        <f>E9+E11+E13+E15</f>
-        <v/>
-      </c>
-      <c r="F16" s="28">
-        <f>F9+F11+F13+F15</f>
-        <v/>
-      </c>
-      <c r="G16" s="28">
-        <f>G9+G11+G13+G15</f>
-        <v/>
-      </c>
-      <c r="H16" s="28">
-        <f>H9+H11+H13+H15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Discount period (years)</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>2</v>
-      </c>
-      <c r="F17" s="29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" s="29" t="n">
-        <v>4</v>
-      </c>
-      <c r="H17" s="29" t="n">
-        <v>5</v>
+      <c r="D17" s="40">
+        <f>D10+D12+D14+D16</f>
+        <v/>
+      </c>
+      <c r="E17" s="40">
+        <f>E10+E12+E14+E16</f>
+        <v/>
+      </c>
+      <c r="F17" s="40">
+        <f>F10+F12+F14+F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="40">
+        <f>G10+G12+G14+G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="40">
+        <f>H10+H12+H14+H16</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="D18" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" s="41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D18" s="30">
-        <f>1/(1+WACC!C16)^D17</f>
-        <v/>
-      </c>
-      <c r="E18" s="30">
-        <f>1/(1+WACC!C16)^E17</f>
-        <v/>
-      </c>
-      <c r="F18" s="30">
-        <f>1/(1+WACC!C16)^F17</f>
-        <v/>
-      </c>
-      <c r="G18" s="30">
-        <f>1/(1+WACC!C16)^G17</f>
-        <v/>
-      </c>
-      <c r="H18" s="30">
-        <f>1/(1+WACC!C16)^H17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="D19" s="42">
+        <f>1/(1+Scenarios!$D$8)^D18</f>
+        <v/>
+      </c>
+      <c r="E19" s="42">
+        <f>1/(1+Scenarios!$D$8)^E18</f>
+        <v/>
+      </c>
+      <c r="F19" s="42">
+        <f>1/(1+Scenarios!$D$8)^F18</f>
+        <v/>
+      </c>
+      <c r="G19" s="42">
+        <f>1/(1+Scenarios!$D$8)^G18</f>
+        <v/>
+      </c>
+      <c r="H19" s="42">
+        <f>1/(1+Scenarios!$D$8)^H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D19" s="27">
-        <f>D16*D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="27">
-        <f>E16*E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="27">
-        <f>F16*F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="27">
-        <f>G16*G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="27">
-        <f>H16*H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="D20" s="28">
+        <f>D17*D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E17*E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>F17*F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="28">
+        <f>G17*G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="28">
+        <f>H17*H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C22" s="32">
-        <f>SUM(D19:H19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>Terminal growth rate (g)</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>0.0225</v>
+      <c r="C23" s="44">
+        <f>SUM(D20:H20)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="C24" s="25">
-        <f>H16*(1+C23)/(WACC!C16-C23)</f>
+          <t>Terminal growth rate (g)</t>
+        </is>
+      </c>
+      <c r="C24" s="38">
+        <f>Scenarios!$D$9</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
         <is>
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="C25" s="37">
+        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Implied terminal EV/EBITDA (sanity check)</t>
         </is>
       </c>
-      <c r="C25" s="33">
-        <f>C24/(H7+H11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="C26" s="32">
-        <f>C24/(1+WACC!C16)^H17</f>
+      <c r="C26" s="45">
+        <f>C25/(H8+H12)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C27" s="44">
+        <f>C25/(1+Scenarios!$D$8)^H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C27" s="27">
-        <f>C22+C26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="n">
-        <v>1807202</v>
+      <c r="C28" s="28">
+        <f>C23+C27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>1807202</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C29" s="24" t="n">
+      <c r="C30" s="36" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C30" s="27">
-        <f>C27+C28+C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="C31" s="28">
+        <f>C28+C29+C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n">
+      <c r="C32" s="36" t="n">
         <v>111380</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C32" s="34">
-        <f>C30/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="C33" s="46">
+        <f>C31/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C34" s="47" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C34" s="36">
-        <f>C32/C33-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="C35" s="48">
+        <f>C33/C34-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C35" s="37">
-        <f>C26/C27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="C36" s="38">
+        <f>C27/C28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C38" s="32">
-        <f>H7+H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>Exit EV/EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="C39" s="38" t="n">
-        <v>8</v>
+      <c r="C39" s="44">
+        <f>H8+H12</f>
+        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Terminal value (exit multiple)</t>
-        </is>
-      </c>
-      <c r="C40" s="25">
-        <f>C38*C39</f>
-        <v/>
+          <t>Exit EV/EBITDA multiple</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
+          <t>Terminal value (exit multiple)</t>
+        </is>
+      </c>
+      <c r="C41" s="37">
+        <f>C39*C40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C41" s="25">
-        <f>C40/(1+WACC!C16)^H17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="C42" s="27">
-        <f>C22+C41</f>
+      <c r="C42" s="37">
+        <f>C41/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="C43" s="28">
+        <f>C23+C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C43" s="39">
-        <f>(C42+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="C44" s="50">
+        <f>(C43+C29+C30)/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B46" s="12" t="n"/>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="12" t="n"/>
-      <c r="G46" s="12" t="n"/>
-      <c r="H46" s="12" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="40" t="inlineStr">
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="12" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="12" t="n"/>
+      <c r="G47" s="12" t="n"/>
+      <c r="H47" s="12" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D47" s="41" t="n">
+      <c r="D48" s="52" t="n">
         <v>0.015</v>
       </c>
-      <c r="E47" s="41" t="n">
+      <c r="E48" s="52" t="n">
         <v>0.02</v>
       </c>
-      <c r="F47" s="41" t="n">
+      <c r="F48" s="52" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G47" s="41" t="n">
+      <c r="G48" s="52" t="n">
         <v>0.025</v>
       </c>
-      <c r="H47" s="41" t="n">
+      <c r="H48" s="52" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="41" t="n">
+    <row r="49">
+      <c r="A49" s="52" t="n">
         <v>0.09</v>
       </c>
-      <c r="D48" s="42">
-        <f>(NPV(0.09,D16:H16)+(H16*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="E48" s="42">
-        <f>(NPV(0.09,D16:H16)+(H16*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="F48" s="42">
-        <f>(NPV(0.09,D16:H16)+(H16*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="G48" s="42">
-        <f>(NPV(0.09,D16:H16)+(H16*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="H48" s="42">
-        <f>(NPV(0.09,D16:H16)+(H16*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="41" t="n">
+      <c r="D49" s="53">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="E49" s="53">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="F49" s="53">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="G49" s="53">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="H49" s="53">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="52" t="n">
         <v>0.095</v>
       </c>
-      <c r="D49" s="42">
-        <f>(NPV(0.095,D16:H16)+(H16*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="E49" s="42">
-        <f>(NPV(0.095,D16:H16)+(H16*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="F49" s="42">
-        <f>(NPV(0.095,D16:H16)+(H16*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="G49" s="42">
-        <f>(NPV(0.095,D16:H16)+(H16*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="H49" s="42">
-        <f>(NPV(0.095,D16:H16)+(H16*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="41" t="n">
+      <c r="D50" s="53">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="E50" s="53">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="F50" s="53">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="G50" s="53">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="H50" s="53">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="52" t="n">
         <v>0.1</v>
       </c>
-      <c r="D50" s="42">
-        <f>(NPV(0.1,D16:H16)+(H16*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="E50" s="42">
-        <f>(NPV(0.1,D16:H16)+(H16*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="F50" s="43">
-        <f>(NPV(0.1,D16:H16)+(H16*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="G50" s="42">
-        <f>(NPV(0.1,D16:H16)+(H16*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="H50" s="42">
-        <f>(NPV(0.1,D16:H16)+(H16*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="41" t="n">
+      <c r="D51" s="53">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="E51" s="53">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="F51" s="54">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="G51" s="53">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="H51" s="53">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="52" t="n">
         <v>0.105</v>
       </c>
-      <c r="D51" s="42">
-        <f>(NPV(0.105,D16:H16)+(H16*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="E51" s="42">
-        <f>(NPV(0.105,D16:H16)+(H16*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="F51" s="42">
-        <f>(NPV(0.105,D16:H16)+(H16*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="G51" s="42">
-        <f>(NPV(0.105,D16:H16)+(H16*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="H51" s="42">
-        <f>(NPV(0.105,D16:H16)+(H16*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="41" t="n">
+      <c r="D52" s="53">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="E52" s="53">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="F52" s="53">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="G52" s="53">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="H52" s="53">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="52" t="n">
         <v>0.11</v>
       </c>
-      <c r="D52" s="42">
-        <f>(NPV(0.11,D16:H16)+(H16*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="E52" s="42">
-        <f>(NPV(0.11,D16:H16)+(H16*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="F52" s="42">
-        <f>(NPV(0.11,D16:H16)+(H16*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="G52" s="42">
-        <f>(NPV(0.11,D16:H16)+(H16*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-      <c r="H52" s="42">
-        <f>(NPV(0.11,D16:H16)+(H16*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C28+C29)/C31</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
-        <is>
-          <t>SCENARIO ANALYSIS</t>
-        </is>
-      </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="44" t="inlineStr">
-        <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="D2" s="45" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="E2" s="46" t="inlineStr">
-        <is>
-          <t>Bull</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>Key assumptions (5-yr forecast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>FY2026E revenue growth</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="D4" s="15" t="n">
-        <v>-0.061</v>
-      </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>FY2028–FY2030E revenue growth (avg)</t>
-        </is>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="D5" s="15" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>FY2026E EBIT margin</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D6" s="15" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Terminal (FY2030E) EBIT margin</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>WACC</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D8" s="15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Terminal growth</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Illustrative unlevered FCF &amp; valuation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 1</t>
-        </is>
-      </c>
-      <c r="C12" s="48">
-        <f>11102600*(1+C4)</f>
-        <v/>
-      </c>
-      <c r="D12" s="48">
-        <f>11102600*(1+D4)</f>
-        <v/>
-      </c>
-      <c r="E12" s="48">
-        <f>11102600*(1+E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 2</t>
-        </is>
-      </c>
-      <c r="C13" s="48">
-        <f>C12*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="48">
-        <f>D12*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="48">
-        <f>E12*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 3</t>
-        </is>
-      </c>
-      <c r="C14" s="48">
-        <f>C13*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="48">
-        <f>D13*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="48">
-        <f>E13*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 4</t>
-        </is>
-      </c>
-      <c r="C15" s="48">
-        <f>C14*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="48">
-        <f>D14*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="48">
-        <f>E14*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 5</t>
-        </is>
-      </c>
-      <c r="C16" s="48">
-        <f>C15*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D16" s="48">
-        <f>D15*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="48">
-        <f>E15*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 1</t>
-        </is>
-      </c>
-      <c r="C17" s="49">
-        <f>C6+(C7-C6)*0/4</f>
-        <v/>
-      </c>
-      <c r="D17" s="49">
-        <f>D6+(D7-D6)*0/4</f>
-        <v/>
-      </c>
-      <c r="E17" s="49">
-        <f>E6+(E7-E6)*0/4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 2</t>
-        </is>
-      </c>
-      <c r="C18" s="49">
-        <f>C6+(C7-C6)*1/4</f>
-        <v/>
-      </c>
-      <c r="D18" s="49">
-        <f>D6+(D7-D6)*1/4</f>
-        <v/>
-      </c>
-      <c r="E18" s="49">
-        <f>E6+(E7-E6)*1/4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 3</t>
-        </is>
-      </c>
-      <c r="C19" s="49">
-        <f>C6+(C7-C6)*2/4</f>
-        <v/>
-      </c>
-      <c r="D19" s="49">
-        <f>D6+(D7-D6)*2/4</f>
-        <v/>
-      </c>
-      <c r="E19" s="49">
-        <f>E6+(E7-E6)*2/4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 4</t>
-        </is>
-      </c>
-      <c r="C20" s="49">
-        <f>C6+(C7-C6)*3/4</f>
-        <v/>
-      </c>
-      <c r="D20" s="49">
-        <f>D6+(D7-D6)*3/4</f>
-        <v/>
-      </c>
-      <c r="E20" s="49">
-        <f>E6+(E7-E6)*3/4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 5</t>
-        </is>
-      </c>
-      <c r="C21" s="49">
-        <f>C6+(C7-C6)*4/4</f>
-        <v/>
-      </c>
-      <c r="D21" s="49">
-        <f>D6+(D7-D6)*4/4</f>
-        <v/>
-      </c>
-      <c r="E21" s="49">
-        <f>E6+(E7-E6)*4/4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 1</t>
-        </is>
-      </c>
-      <c r="C22" s="48">
-        <f>(C12*C17)*(1-0.27)+C12*0.045-C12*0.05-0.075*(C12-11102600)</f>
-        <v/>
-      </c>
-      <c r="D22" s="48">
-        <f>(D12*D17)*(1-0.27)+D12*0.045-D12*0.05-0.075*(D12-11102600)</f>
-        <v/>
-      </c>
-      <c r="E22" s="48">
-        <f>(E12*E17)*(1-0.27)+E12*0.045-E12*0.05-0.075*(E12-11102600)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 2</t>
-        </is>
-      </c>
-      <c r="C23" s="48">
-        <f>(C13*C18)*(1-0.27)+C13*0.045-C13*0.05-0.075*(C13-C12)</f>
-        <v/>
-      </c>
-      <c r="D23" s="48">
-        <f>(D13*D18)*(1-0.27)+D13*0.045-D13*0.05-0.075*(D13-D12)</f>
-        <v/>
-      </c>
-      <c r="E23" s="48">
-        <f>(E13*E18)*(1-0.27)+E13*0.045-E13*0.05-0.075*(E13-E12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 3</t>
-        </is>
-      </c>
-      <c r="C24" s="48">
-        <f>(C14*C19)*(1-0.27)+C14*0.045-C14*0.05-0.075*(C14-C13)</f>
-        <v/>
-      </c>
-      <c r="D24" s="48">
-        <f>(D14*D19)*(1-0.27)+D14*0.045-D14*0.05-0.075*(D14-D13)</f>
-        <v/>
-      </c>
-      <c r="E24" s="48">
-        <f>(E14*E19)*(1-0.27)+E14*0.045-E14*0.05-0.075*(E14-E13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 4</t>
-        </is>
-      </c>
-      <c r="C25" s="48">
-        <f>(C15*C20)*(1-0.27)+C15*0.045-C15*0.05-0.075*(C15-C14)</f>
-        <v/>
-      </c>
-      <c r="D25" s="48">
-        <f>(D15*D20)*(1-0.27)+D15*0.045-D15*0.05-0.075*(D15-D14)</f>
-        <v/>
-      </c>
-      <c r="E25" s="48">
-        <f>(E15*E20)*(1-0.27)+E15*0.045-E15*0.05-0.075*(E15-E14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 5</t>
-        </is>
-      </c>
-      <c r="C26" s="48">
-        <f>(C16*C21)*(1-0.27)+C16*0.045-C16*0.05-0.075*(C16-C15)</f>
-        <v/>
-      </c>
-      <c r="D26" s="48">
-        <f>(D16*D21)*(1-0.27)+D16*0.045-D16*0.05-0.075*(D16-D15)</f>
-        <v/>
-      </c>
-      <c r="E26" s="48">
-        <f>(E16*E21)*(1-0.27)+E16*0.045-E16*0.05-0.075*(E16-E15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>Enterprise value (DCF)</t>
-        </is>
-      </c>
-      <c r="C28" s="27">
-        <f>NPV(C8,C22,C23,C24,C25,C26)+(C26*(1+C9)/(C8-C9))/(1+C8)^5</f>
-        <v/>
-      </c>
-      <c r="D28" s="27">
-        <f>NPV(D8,D22,D23,D24,D25,D26)+(D26*(1+D9)/(D8-D9))/(1+D8)^5</f>
-        <v/>
-      </c>
-      <c r="E28" s="27">
-        <f>NPV(E8,E22,E23,E24,E25,E26)+(E26*(1+E9)/(E8-E9))/(1+E8)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="50" t="inlineStr">
-        <is>
-          <t>Implied share price</t>
-        </is>
-      </c>
-      <c r="C29" s="51">
-        <f>(C28+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="D29" s="52">
-        <f>(D28+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="E29" s="51">
-        <f>(E28+1807202-0)/111380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>Upside / (downside) vs current</t>
-        </is>
-      </c>
-      <c r="C30" s="53">
-        <f>C29/100.0-1</f>
-        <v/>
-      </c>
-      <c r="D30" s="53">
-        <f>D29/100.0-1</f>
-        <v/>
-      </c>
-      <c r="E30" s="53">
-        <f>E29/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
-        </is>
+      <c r="D53" s="53">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="E53" s="53">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="F53" s="53">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="G53" s="53">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C29+C30)/C32</f>
+        <v/>
+      </c>
+      <c r="H53" s="53">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C29+C30)/C32</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2532,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="36" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -2515,7 +2542,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="37">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -2526,7 +2553,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="47" t="n">
         <v>9.609999999999999</v>
       </c>
     </row>
@@ -2536,7 +2563,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="36" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -2546,7 +2573,7 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="36" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -2556,28 +2583,28 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="47" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="inlineStr">
+      <c r="A10" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="56">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="56">
         <f>C9/C6</f>
         <v/>
       </c>
@@ -2590,27 +2617,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="56" t="inlineStr">
+      <c r="A14" s="57" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D14" s="57" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E14" s="57" t="inlineStr">
+      <c r="E14" s="58" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F14" s="57" t="inlineStr">
+      <c r="F14" s="58" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -2622,17 +2649,17 @@
           <t>EV / EBITDA (FY2025A)</t>
         </is>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="59" t="n">
         <v>4.5</v>
       </c>
-      <c r="D15" s="58" t="n">
+      <c r="D15" s="59" t="n">
         <v>7.5</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="60">
         <f>(C5*C15+C7)/C8</f>
         <v/>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="60">
         <f>(C5*D15+C7)/C8</f>
         <v/>
       </c>
@@ -2643,17 +2670,17 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C16" s="58" t="n">
+      <c r="C16" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="58" t="n">
+      <c r="D16" s="59" t="n">
         <v>18</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="60">
         <f>C6*C16</f>
         <v/>
       </c>
-      <c r="F16" s="59">
+      <c r="F16" s="60">
         <f>C6*D16</f>
         <v/>
       </c>
@@ -2664,32 +2691,32 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C17" s="60" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="59">
+      <c r="E17" s="60">
         <f>Scenarios!C29</f>
         <v/>
       </c>
-      <c r="F17" s="59">
+      <c r="F17" s="60">
         <f>Scenarios!E29</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="61" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C19" s="62" t="n">
+      <c r="C19" s="63" t="n">
         <v>100</v>
       </c>
     </row>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,6 +192,18 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -269,7 +281,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -389,26 +401,45 @@
     <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -417,6 +448,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1607,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2123,365 +2157,495 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="C25" s="37">
-        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C25" s="28">
+        <f>H8+H12</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Implied terminal EV/EBITDA (sanity check)</t>
-        </is>
-      </c>
-      <c r="C26" s="45">
-        <f>C25/(H8+H12)</f>
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="C26" s="37">
+        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="C27" s="44">
-        <f>C25/(1+Scenarios!$D$8)^H18</f>
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
+        </is>
+      </c>
+      <c r="C27" s="45">
+        <f>C26/C25</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C28" s="44">
+        <f>C26/(1+Scenarios!$D$8)^H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C28" s="28">
-        <f>C23+C27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>1807202</v>
+      <c r="C29" s="28">
+        <f>C23+C28</f>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>1807202</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n">
+      <c r="C31" s="36" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C31" s="28">
-        <f>C28+C29+C30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="C32" s="28">
+        <f>C29+C30+C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n">
+      <c r="C33" s="36" t="n">
         <v>111380</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C33" s="46">
-        <f>C31/C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="C34" s="46">
+        <f>C32/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C34" s="47" t="n">
+      <c r="C35" s="47" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C35" s="48">
-        <f>C33/C34-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="C36" s="48">
+        <f>C34/C35-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C36" s="38">
-        <f>C27/C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43" t="inlineStr">
+      <c r="C37" s="38">
+        <f>C28/C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="18" t="inlineStr">
-        <is>
-          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C39" s="44">
-        <f>H8+H12</f>
-        <v/>
-      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>Exit EV/EBITDA multiple</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="n">
-        <v>8</v>
+      <c r="A40" s="49" t="inlineStr">
+        <is>
+          <t>Exit multiple selection (see Comps tab for peer build)</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
         <is>
-          <t>Terminal value (exit multiple)</t>
-        </is>
-      </c>
-      <c r="C41" s="37">
-        <f>C39*C40</f>
-        <v/>
+          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
+        </is>
+      </c>
+      <c r="C41" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>Base-case terminal multiple; see Comps → Exit Multiple Build</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
+          <t>Terminal value = Terminal EBITDA × exit multiple</t>
+        </is>
+      </c>
+      <c r="C42" s="37">
+        <f>C25*C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C42" s="37">
-        <f>C41/(1+Scenarios!$D$8)^H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="18" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="C43" s="28">
-        <f>C23+C42</f>
+      <c r="C43" s="37">
+        <f>C42/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="C44" s="28">
+        <f>C23+C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C44" s="50">
-        <f>(C43+C29+C30)/C32</f>
+      <c r="C45" s="51">
+        <f>(C44+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
+          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
       <c r="B47" s="12" t="n"/>
       <c r="C47" s="12" t="n"/>
       <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
-      <c r="H47" s="12" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="A48" s="52" t="inlineStr"/>
+      <c r="B48" s="53" t="inlineStr">
+        <is>
+          <t>Gordon Growth</t>
+        </is>
+      </c>
+      <c r="C48" s="53" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D48" s="53" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Terminal value ($)</t>
+        </is>
+      </c>
+      <c r="B49" s="44">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="C49" s="44">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D49" s="44">
+        <f>B49-C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA (implied vs selected)</t>
+        </is>
+      </c>
+      <c r="B50" s="54">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="C50" s="54">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="D50" s="54">
+        <f>B50-C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Terminal value variance (%)</t>
+        </is>
+      </c>
+      <c r="B51" s="38" t="inlineStr"/>
+      <c r="C51" s="38" t="inlineStr"/>
+      <c r="D51" s="38">
+        <f>(B49-C49)/B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="inlineStr">
+        <is>
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="B52" s="55">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="C52" s="55">
+        <f>C45</f>
+        <v/>
+      </c>
+      <c r="D52" s="55">
+        <f>B52-C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="56" t="inlineStr">
+        <is>
+          <t>Sanity check: multiples within ±1.5 turns?</t>
+        </is>
+      </c>
+      <c r="B53" s="57">
+        <f>IF(ABS(D50)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C53" s="58">
+        <f>TEXT(D50,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Gordon implied should bracket exit assumption</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
+        </is>
+      </c>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="12" t="n"/>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="12" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="59" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D48" s="52" t="n">
+      <c r="D57" s="60" t="n">
         <v>0.015</v>
       </c>
-      <c r="E48" s="52" t="n">
+      <c r="E57" s="60" t="n">
         <v>0.02</v>
       </c>
-      <c r="F48" s="52" t="n">
+      <c r="F57" s="60" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G48" s="52" t="n">
+      <c r="G57" s="60" t="n">
         <v>0.025</v>
       </c>
-      <c r="H48" s="52" t="n">
+      <c r="H57" s="60" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="52" t="n">
+    <row r="58">
+      <c r="A58" s="60" t="n">
         <v>0.09</v>
       </c>
-      <c r="D49" s="53">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="E49" s="53">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="F49" s="53">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="G49" s="53">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="H49" s="53">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="52" t="n">
+      <c r="D58" s="61">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="E58" s="61">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="F58" s="61">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="G58" s="61">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="H58" s="61">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="60" t="n">
         <v>0.095</v>
       </c>
-      <c r="D50" s="53">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="E50" s="53">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="F50" s="53">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="G50" s="53">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="H50" s="53">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="52" t="n">
+      <c r="D59" s="61">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="E59" s="61">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="F59" s="61">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="G59" s="61">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="H59" s="61">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="60" t="n">
         <v>0.1</v>
       </c>
-      <c r="D51" s="53">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="E51" s="53">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="F51" s="54">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="G51" s="53">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="H51" s="53">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="52" t="n">
+      <c r="D60" s="61">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="E60" s="61">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="F60" s="62">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="G60" s="61">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="H60" s="61">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="60" t="n">
         <v>0.105</v>
       </c>
-      <c r="D52" s="53">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="E52" s="53">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="F52" s="53">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="G52" s="53">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="H52" s="53">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="52" t="n">
+      <c r="D61" s="61">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="E61" s="61">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="F61" s="61">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="G61" s="61">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="H61" s="61">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="60" t="n">
         <v>0.11</v>
       </c>
-      <c r="D53" s="53">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="E53" s="53">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="F53" s="53">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="G53" s="53">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C29+C30)/C32</f>
-        <v/>
-      </c>
-      <c r="H53" s="53">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C29+C30)/C32</f>
+      <c r="D62" s="61">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="E62" s="61">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="F62" s="61">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="G62" s="61">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C30+C31)/C33</f>
+        <v/>
+      </c>
+      <c r="H62" s="61">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
@@ -2496,7 +2660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2588,23 +2752,23 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="55" t="inlineStr">
+      <c r="A10" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="63">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="inlineStr">
+      <c r="A11" s="58" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="63">
         <f>C9/C6</f>
         <v/>
       </c>
@@ -2612,116 +2776,320 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Methodology / multiple ranges</t>
+          <t>EXIT MULTIPLE BUILD — FY2030E TERMINAL YEAR</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="57" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="C14" s="58" t="inlineStr">
-        <is>
-          <t>Low mult.</t>
-        </is>
-      </c>
-      <c r="D14" s="58" t="inlineStr">
-        <is>
-          <t>High mult.</t>
-        </is>
-      </c>
-      <c r="E14" s="58" t="inlineStr">
-        <is>
-          <t>Implied px (low)</t>
-        </is>
-      </c>
-      <c r="F14" s="58" t="inlineStr">
-        <is>
-          <t>Implied px (high)</t>
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>EV / EBITDA (FY2025A)</t>
-        </is>
-      </c>
-      <c r="C15" s="59" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E15" s="60">
-        <f>(C5*C15+C7)/C8</f>
-        <v/>
-      </c>
-      <c r="F15" s="60">
-        <f>(C5*D15+C7)/C8</f>
-        <v/>
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C15" s="65" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>P / E (FY2026E EPS)</t>
-        </is>
-      </c>
-      <c r="C16" s="59" t="n">
-        <v>10</v>
-      </c>
-      <c r="D16" s="59" t="n">
-        <v>18</v>
-      </c>
-      <c r="E16" s="60">
-        <f>C6*C16</f>
-        <v/>
-      </c>
-      <c r="F16" s="60">
-        <f>C6*D16</f>
-        <v/>
+          <t>lululemon (LULU) — current</t>
+        </is>
+      </c>
+      <c r="C16" s="66">
+        <f>(C9*C8-C7)/C5</f>
+        <v/>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>Distressed trough; FY2025A EBITDA</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
+          <t>Nike (NKE)</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="n">
+        <v>18</v>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>Mature global brand; lower growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Deckers (DECK)</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Premium footwear peer; HOKA/UGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>On Holding (ONON)</t>
+        </is>
+      </c>
+      <c r="C19" s="67" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>High-growth athletic peer</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>adidas (ADS)</t>
+        </is>
+      </c>
+      <c r="C20" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>Global incumbent; restructuring</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>V.F. Corp (VFC)</t>
+        </is>
+      </c>
+      <c r="C21" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Multi-brand apparel; challenged</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Terminal multiple selection (DCF exit method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Gordon Growth implied exit EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="C24" s="45">
+        <f>DCF!C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>Selected exit multiple (base case)</t>
+        </is>
+      </c>
+      <c r="C25" s="54">
+        <f>DCF!C41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Spread (selected − Gordon implied)</t>
+        </is>
+      </c>
+      <c r="C26" s="45">
+        <f>C25-C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="56" t="inlineStr">
+        <is>
+          <t>Rationale for 8.0x</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>•  Above current LULU (~3.5x) — assumes partial recovery from trough, not full re-rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>•  Above comps football-field high (7.5x on FY2025A) — terminal year has higher EBITDA &amp; normalized margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>•  ~1 turn above Gordon-implied exit multiple — conservative buffer vs perpetuity math</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>•  Well below historical LULU peak multiples (20–30x) — avoids heroic assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Methodology / multiple ranges (FY2025A — football field)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="64" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C35" s="65" t="inlineStr">
+        <is>
+          <t>Low mult.</t>
+        </is>
+      </c>
+      <c r="D35" s="65" t="inlineStr">
+        <is>
+          <t>High mult.</t>
+        </is>
+      </c>
+      <c r="E35" s="65" t="inlineStr">
+        <is>
+          <t>Implied px (low)</t>
+        </is>
+      </c>
+      <c r="F35" s="65" t="inlineStr">
+        <is>
+          <t>Implied px (high)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>EV / EBITDA (FY2025A)</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D36" s="67" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E36" s="68">
+        <f>(C5*C36+C7)/C8</f>
+        <v/>
+      </c>
+      <c r="F36" s="68">
+        <f>(C5*D36+C7)/C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>P / E (FY2026E EPS)</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="D37" s="67" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="68">
+        <f>C6*C37</f>
+        <v/>
+      </c>
+      <c r="F37" s="68">
+        <f>C6*D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C38" s="69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="61" t="inlineStr">
+      <c r="D38" s="69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="60">
+      <c r="E38" s="68">
         <f>Scenarios!C29</f>
         <v/>
       </c>
-      <c r="F17" s="60">
+      <c r="F38" s="68">
         <f>Scenarios!E29</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="62" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="70" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C19" s="63" t="n">
+      <c r="C40" s="71" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -90,6 +90,17 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
@@ -166,6 +177,19 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
@@ -178,8 +202,10 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -221,6 +247,13 @@
       <name val="Garamond"/>
       <color rgb="00006100"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="7">
@@ -281,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -294,77 +327,81 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="23" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="17" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="19" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -373,10 +410,10 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -385,75 +422,78 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="35" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -465,8 +505,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -833,7 +873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B21"/>
+  <dimension ref="B2:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -878,7 +918,7 @@
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Blue font  =  figures reported by the company (release, filing, or call)</t>
+          <t>Blue font  =  figures reported by the company (click value or source link)</t>
         </is>
       </c>
     </row>
@@ -918,27 +958,47 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>SEC EDGAR XBRL company facts, CIK 0001397187 (Form 10-K, FY2025 ended Feb 1, 2026).</t>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>SEC EDGAR XBRL company facts, CIK 0001397187 (Form 10-K, FY2025)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Market data &amp; Q2 FY2026 results per company release dated Sep 3, 2026.</t>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 Form 10-K (ended Feb 1, 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="10" t="inlineStr">
         <is>
+          <t>Current share price (NASDAQ: LULU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="11" t="inlineStr">
+        <is>
           <t>Built from scratch for the GIS IR selection assignment.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -959,165 +1019,165 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>WEIGHTED AVERAGE COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Risk-free rate (10-yr UST)</t>
         </is>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="16" t="n">
         <v>0.043</v>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="17" t="inlineStr">
         <is>
           <t>analyst input</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>0.06</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="17" t="inlineStr">
         <is>
           <t>analyst input</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>~0.86 market beta; 0.95 used for near-term uncertainty</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>C3+C5*C4</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Cost of debt</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>illustrative; LULU has no funded debt</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>0.27</v>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>normalized marginal rate</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="21">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Capital structure (market values)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>net-cash balance sheet → ~100% equity</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <f>C14*C6+C15*C11</f>
         <v/>
       </c>
@@ -1144,487 +1204,487 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>SCENARIO ANALYSIS</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E2" s="24" t="inlineStr">
+      <c r="E2" s="25" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>-0.09</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="16" t="n">
         <v>-0.061</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="16" t="n">
         <v>-0.04</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>0.028</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="16" t="n">
         <v>0.06</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>FY2026E EBIT margin</t>
         </is>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>0.125</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="16" t="n">
         <v>0.139</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>0.12</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="16" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>0.19</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>0.11</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="16" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>0.09</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>0.015</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.0225</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>5-year forecast paths (by scenario)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>11102600*(1+C4)</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>11102600*(1+D4)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <f>C12*(1+C5)</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <f>D12*(1+D5)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>E12*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>C13*(1+C5)</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>D13*(1+D5)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>E13*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>C14*(1+C5)</f>
         <v/>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>D14*(1+D5)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>E14*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="27">
         <f>C15*(1+C5)</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="27">
         <f>D15*(1+D5)</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <f>E15*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>C6+(C7-C6)*1/4</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>D6+(D7-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>C6+(C7-C6)*2/4</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>D6+(D7-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>C6+(C7-C6)*3/4</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>D6+(D7-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <f>C6+(C7-C6)*4/4</f>
         <v/>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <f>D6+(D7-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>(C12*C17)*(1-0.27)+C12*0.045-C12*0.05-0.075*(C12-11102600)</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>(D12*D17)*(1-0.27)+D12*0.045-D12*0.05-0.075*(D12-11102600)</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>(E12*E17)*(1-0.27)+E12*0.045-E12*0.05-0.075*(E12-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <f>(C13*C18)*(1-0.27)+C13*0.045-C13*0.05-0.075*(C13-C12)</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="27">
         <f>(D13*D18)*(1-0.27)+D13*0.045-D13*0.05-0.075*(D13-D12)</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <f>(E13*E18)*(1-0.27)+E13*0.045-E13*0.05-0.075*(E13-E12)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="27">
         <f>(C14*C19)*(1-0.27)+C14*0.045-C14*0.05-0.075*(C14-C13)</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="27">
         <f>(D14*D19)*(1-0.27)+D14*0.045-D14*0.05-0.075*(D14-D13)</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <f>(E14*E19)*(1-0.27)+E14*0.045-E14*0.05-0.075*(E14-E13)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>(C15*C20)*(1-0.27)+C15*0.045-C15*0.05-0.075*(C15-C14)</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="27">
         <f>(D15*D20)*(1-0.27)+D15*0.045-D15*0.05-0.075*(D15-D14)</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f>(E15*E20)*(1-0.27)+E15*0.045-E15*0.05-0.075*(E15-E14)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="27">
         <f>(C16*C21)*(1-0.27)+C16*0.045-C16*0.05-0.075*(C16-C15)</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="27">
         <f>(D16*D21)*(1-0.27)+D16*0.045-D16*0.05-0.075*(D16-D15)</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <f>(E16*E21)*(1-0.27)+E16*0.045-E16*0.05-0.075*(E16-E15)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="29">
         <f>NPV(C8,C22,C23,C24,C25,C26)+(C26*(1+C9)/(C8-C9))/(1+C8)^5</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="29">
         <f>NPV(D8,D22,D23,D24,D25,D26)+(D26*(1+D9)/(D8-D9))/(1+D8)^5</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="29">
         <f>NPV(E8,E22,E23,E24,E25,E26)+(E26*(1+E9)/(E8-E9))/(1+E8)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <f>(C28+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="32">
         <f>(D28+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <f>(E28+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <f>C29/100.0-1</f>
         <v/>
       </c>
-      <c r="D30" s="32">
+      <c r="D30" s="33">
         <f>D29/100.0-1</f>
         <v/>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="33">
         <f>E29/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -1647,7 +1707,7 @@
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -1655,1001 +1715,1039 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>DISCOUNTED CASH FLOW — BASE CASE  (US$ thousands)</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-      <c r="F1" s="12" t="n"/>
-      <c r="G1" s="12" t="n"/>
-      <c r="H1" s="12" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="33" t="inlineStr">
+      <c r="C2" s="34" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="34" t="inlineStr">
+      <c r="D2" s="35" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="34" t="inlineStr">
+      <c r="E2" s="35" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="34" t="inlineStr">
+      <c r="F2" s="35" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="34" t="inlineStr">
+      <c r="G2" s="35" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="34" t="inlineStr">
+      <c r="H2" s="35" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
+      <c r="C3" s="37" t="inlineStr">
+        <is>
+          <t>10-K source</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="38" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="37">
+      <c r="D5" s="39">
         <f>Scenarios!D12</f>
         <v/>
       </c>
-      <c r="E5" s="37">
+      <c r="E5" s="39">
         <f>Scenarios!D13</f>
         <v/>
       </c>
-      <c r="F5" s="37">
+      <c r="F5" s="39">
         <f>Scenarios!D14</f>
         <v/>
       </c>
-      <c r="G5" s="37">
+      <c r="G5" s="39">
         <f>Scenarios!D15</f>
         <v/>
       </c>
-      <c r="H5" s="37">
+      <c r="H5" s="39">
         <f>Scenarios!D16</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="38">
+      <c r="D6" s="40">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="40">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="40">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="38">
+      <c r="G6" s="40">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="40">
         <f>H5/G5-1</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="38">
+      <c r="D7" s="40">
         <f>Scenarios!D17</f>
         <v/>
       </c>
-      <c r="E7" s="38">
+      <c r="E7" s="40">
         <f>Scenarios!D18</f>
         <v/>
       </c>
-      <c r="F7" s="38">
+      <c r="F7" s="40">
         <f>Scenarios!D19</f>
         <v/>
       </c>
-      <c r="G7" s="38">
+      <c r="G7" s="40">
         <f>Scenarios!D20</f>
         <v/>
       </c>
-      <c r="H7" s="38">
+      <c r="H7" s="40">
         <f>Scenarios!D21</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="41" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <f>H5*H7</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="39">
         <f>-D8*WACC!C10</f>
         <v/>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="39">
         <f>-E8*WACC!C10</f>
         <v/>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="39">
         <f>-F8*WACC!C10</f>
         <v/>
       </c>
-      <c r="G9" s="37">
+      <c r="G9" s="39">
         <f>-G8*WACC!C10</f>
         <v/>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="39">
         <f>-H8*WACC!C10</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>G8+G9</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>H8+H9</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="16" t="n">
         <v>0.045</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <v>0.045</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="16" t="n">
         <v>0.045</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="16" t="n">
         <v>0.045</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="16" t="n">
         <v>0.045</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="37">
+      <c r="D12" s="39">
         <f>D5*D11</f>
         <v/>
       </c>
-      <c r="E12" s="37">
+      <c r="E12" s="39">
         <f>E5*E11</f>
         <v/>
       </c>
-      <c r="F12" s="37">
+      <c r="F12" s="39">
         <f>F5*F11</f>
         <v/>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="39">
         <f>G5*G11</f>
         <v/>
       </c>
-      <c r="H12" s="37">
+      <c r="H12" s="39">
         <f>H5*H11</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="16" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="39">
         <f>-D5*D13</f>
         <v/>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="39">
         <f>-E5*E13</f>
         <v/>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="39">
         <f>-F5*F13</f>
         <v/>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="39">
         <f>-G5*G13</f>
         <v/>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="39">
         <f>-H5*H13</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC % of revenue</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="16" t="n">
         <v>0.075</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="16" t="n">
         <v>0.075</v>
       </c>
-      <c r="F15" s="15" t="n">
+      <c r="F15" s="16" t="n">
         <v>0.075</v>
       </c>
-      <c r="G15" s="15" t="n">
+      <c r="G15" s="16" t="n">
         <v>0.075</v>
       </c>
-      <c r="H15" s="15" t="n">
+      <c r="H15" s="16" t="n">
         <v>0.075</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Less: increase in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="37">
+      <c r="D16" s="39">
         <f>-D15*(D5-C5)</f>
         <v/>
       </c>
-      <c r="E16" s="37">
+      <c r="E16" s="39">
         <f>-E15*(E5-D5)</f>
         <v/>
       </c>
-      <c r="F16" s="37">
+      <c r="F16" s="39">
         <f>-F15*(F5-E5)</f>
         <v/>
       </c>
-      <c r="G16" s="37">
+      <c r="G16" s="39">
         <f>-G15*(G5-F5)</f>
         <v/>
       </c>
-      <c r="H16" s="37">
+      <c r="H16" s="39">
         <f>-H15*(H5-G5)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="42">
         <f>D10+D12+D14+D16</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="42">
         <f>E10+E12+E14+E16</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="42">
         <f>F10+F12+F14+F16</f>
         <v/>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="42">
         <f>G10+G12+G14+G16</f>
         <v/>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="42">
         <f>H10+H12+H14+H16</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D18" s="41" t="n">
+      <c r="D18" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="41" t="n">
+      <c r="E18" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="41" t="n">
+      <c r="F18" s="43" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="41" t="n">
+      <c r="G18" s="43" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="41" t="n">
+      <c r="H18" s="43" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D19" s="42">
+      <c r="D19" s="44">
         <f>1/(1+Scenarios!$D$8)^D18</f>
         <v/>
       </c>
-      <c r="E19" s="42">
+      <c r="E19" s="44">
         <f>1/(1+Scenarios!$D$8)^E18</f>
         <v/>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="44">
         <f>1/(1+Scenarios!$D$8)^F18</f>
         <v/>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="44">
         <f>1/(1+Scenarios!$D$8)^G18</f>
         <v/>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="44">
         <f>1/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="29">
         <f>D17*D19</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="29">
         <f>E17*E19</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="29">
         <f>F17*F19</f>
         <v/>
       </c>
-      <c r="G20" s="28">
+      <c r="G20" s="29">
         <f>G17*G19</f>
         <v/>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="29">
         <f>H17*H19</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="45" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
+      <c r="B22" s="13" t="n"/>
+      <c r="C22" s="13" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C23" s="44">
+      <c r="C23" s="46">
         <f>SUM(D20:H20)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C24" s="38">
+      <c r="C24" s="40">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>H8+H12</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="39">
         <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C27" s="45">
+      <c r="C27" s="47">
         <f>C26/C25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C28" s="44">
+      <c r="C28" s="46">
         <f>C26/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>C23+C28</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n">
+      <c r="C30" s="38" t="n">
         <v>1807202</v>
       </c>
+      <c r="D30" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n">
+      <c r="C31" s="38" t="n">
         <v>0</v>
       </c>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>C29+C30+C31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C33" s="36" t="n">
+      <c r="C33" s="38" t="n">
         <v>111380</v>
       </c>
+      <c r="D33" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C34" s="46">
+      <c r="C34" s="49">
         <f>C32/C33</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C35" s="47" t="n">
+      <c r="C35" s="50" t="n">
         <v>100</v>
       </c>
+      <c r="D35" s="48" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C36" s="48">
+      <c r="C36" s="51">
         <f>C34/C35-1</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C37" s="38">
+      <c r="C37" s="40">
         <f>C28/C29</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="43" t="inlineStr">
+      <c r="A39" s="45" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
+      <c r="B39" s="13" t="n"/>
+      <c r="C39" s="13" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="49" t="inlineStr">
+      <c r="A40" s="52" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C41" s="50" t="n">
+      <c r="C41" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="D41" s="16" t="inlineStr">
+      <c r="D41" s="17" t="inlineStr">
         <is>
           <t>Base-case terminal multiple; see Comps → Exit Multiple Build</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="39">
         <f>C25*C41</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="39">
         <f>C42/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="29">
         <f>C23+C43</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="54">
         <f>(C44+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="43" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="52" t="inlineStr"/>
-      <c r="B48" s="53" t="inlineStr">
+      <c r="A48" s="55" t="inlineStr"/>
+      <c r="B48" s="56" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C48" s="53" t="inlineStr">
+      <c r="C48" s="56" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D48" s="53" t="inlineStr">
+      <c r="D48" s="56" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B49" s="44">
+      <c r="B49" s="46">
         <f>C26</f>
         <v/>
       </c>
-      <c r="C49" s="44">
+      <c r="C49" s="46">
         <f>C42</f>
         <v/>
       </c>
-      <c r="D49" s="44">
+      <c r="D49" s="46">
         <f>B49-C49</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B50" s="54">
+      <c r="B50" s="57">
         <f>C27</f>
         <v/>
       </c>
-      <c r="C50" s="54">
+      <c r="C50" s="57">
         <f>C41</f>
         <v/>
       </c>
-      <c r="D50" s="54">
+      <c r="D50" s="57">
         <f>B50-C50</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="14" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B51" s="38" t="inlineStr"/>
-      <c r="C51" s="38" t="inlineStr"/>
-      <c r="D51" s="38">
+      <c r="B51" s="40" t="inlineStr"/>
+      <c r="C51" s="40" t="inlineStr"/>
+      <c r="D51" s="40">
         <f>(B49-C49)/B49</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B52" s="55">
+      <c r="B52" s="58">
         <f>C34</f>
         <v/>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="58">
         <f>C45</f>
         <v/>
       </c>
-      <c r="D52" s="55">
+      <c r="D52" s="58">
         <f>B52-C52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="56" t="inlineStr">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B53" s="57">
+      <c r="B53" s="60">
         <f>IF(ABS(D50)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C53" s="58">
+      <c r="C53" s="61">
         <f>TEXT(D50,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D53" s="16" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="43" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="12" t="n"/>
-      <c r="H56" s="12" t="n"/>
+      <c r="B56" s="13" t="n"/>
+      <c r="C56" s="13" t="n"/>
+      <c r="D56" s="13" t="n"/>
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="13" t="n"/>
+      <c r="G56" s="13" t="n"/>
+      <c r="H56" s="13" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="59" t="inlineStr">
+      <c r="A57" s="62" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D57" s="60" t="n">
+      <c r="D57" s="63" t="n">
         <v>0.015</v>
       </c>
-      <c r="E57" s="60" t="n">
+      <c r="E57" s="63" t="n">
         <v>0.02</v>
       </c>
-      <c r="F57" s="60" t="n">
+      <c r="F57" s="63" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G57" s="60" t="n">
+      <c r="G57" s="63" t="n">
         <v>0.025</v>
       </c>
-      <c r="H57" s="60" t="n">
+      <c r="H57" s="63" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="60" t="n">
+      <c r="A58" s="63" t="n">
         <v>0.09</v>
       </c>
-      <c r="D58" s="61">
+      <c r="D58" s="64">
         <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="E58" s="61">
+      <c r="E58" s="64">
         <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="F58" s="61">
+      <c r="F58" s="64">
         <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="G58" s="61">
+      <c r="G58" s="64">
         <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="H58" s="61">
+      <c r="H58" s="64">
         <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="60" t="n">
+      <c r="A59" s="63" t="n">
         <v>0.095</v>
       </c>
-      <c r="D59" s="61">
+      <c r="D59" s="64">
         <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="E59" s="61">
+      <c r="E59" s="64">
         <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="F59" s="61">
+      <c r="F59" s="64">
         <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="G59" s="61">
+      <c r="G59" s="64">
         <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="H59" s="61">
+      <c r="H59" s="64">
         <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="60" t="n">
+      <c r="A60" s="63" t="n">
         <v>0.1</v>
       </c>
-      <c r="D60" s="61">
+      <c r="D60" s="64">
         <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="E60" s="61">
+      <c r="E60" s="64">
         <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="F60" s="62">
+      <c r="F60" s="65">
         <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="G60" s="61">
+      <c r="G60" s="64">
         <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="H60" s="61">
+      <c r="H60" s="64">
         <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="60" t="n">
+      <c r="A61" s="63" t="n">
         <v>0.105</v>
       </c>
-      <c r="D61" s="61">
+      <c r="D61" s="64">
         <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="E61" s="61">
+      <c r="E61" s="64">
         <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="F61" s="61">
+      <c r="F61" s="64">
         <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="G61" s="61">
+      <c r="G61" s="64">
         <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="H61" s="61">
+      <c r="H61" s="64">
         <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="60" t="n">
+      <c r="A62" s="63" t="n">
         <v>0.11</v>
       </c>
-      <c r="D62" s="61">
+      <c r="D62" s="64">
         <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="E62" s="61">
+      <c r="E62" s="64">
         <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="F62" s="61">
+      <c r="F62" s="64">
         <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="G62" s="61">
+      <c r="G62" s="64">
         <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
-      <c r="H62" s="61">
+      <c r="H62" s="64">
         <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C30+C31)/C33</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2672,430 +2770,474 @@
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>RELATIVE VALUATION — IMPLIED PRICE RANGES (FOOTBALL FIELD)</t>
         </is>
       </c>
-      <c r="B1" s="12" t="n"/>
-      <c r="C1" s="12" t="n"/>
-      <c r="D1" s="12" t="n"/>
-      <c r="E1" s="12" t="n"/>
-      <c r="F1" s="12" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>LULU operating metrics (FY2025A / FY2026E)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="36" t="n">
+      <c r="C4" s="38" t="n">
         <v>11102600</v>
       </c>
+      <c r="D4" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="37">
+      <c r="C5" s="39">
         <f>2210615+496228</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="47" t="n">
+      <c r="C6" s="50" t="n">
         <v>9.609999999999999</v>
       </c>
+      <c r="D6" s="48" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="38" t="n">
         <v>1807202</v>
       </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="38" t="n">
         <v>111380</v>
       </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="47" t="n">
+      <c r="C9" s="50" t="n">
         <v>100</v>
       </c>
+      <c r="D9" s="48" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="58" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="63">
+      <c r="C10" s="66">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="58" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="63">
+      <c r="C11" s="66">
         <f>C9/C6</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>EXIT MULTIPLE BUILD — FY2030E TERMINAL YEAR</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="58" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="64" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C15" s="65" t="inlineStr">
+      <c r="C15" s="68" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="64" t="inlineStr">
+      <c r="D15" s="67" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C16" s="66">
+      <c r="C16" s="69">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
         <is>
           <t>Distressed trough; FY2025A EBITDA</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C17" s="67" t="n">
+      <c r="C17" s="70" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Mature global brand; lower growth</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C18" s="67" t="n">
+      <c r="C18" s="70" t="n">
         <v>15</v>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Premium footwear peer; HOKA/UGG</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C19" s="67" t="n">
+      <c r="C19" s="70" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
         <is>
           <t>High-growth athletic peer</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C20" s="67" t="n">
+      <c r="C20" s="70" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Global incumbent; restructuring</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C21" s="67" t="n">
+      <c r="C21" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="17" t="inlineStr">
         <is>
           <t>Multi-brand apparel; challenged</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Terminal multiple selection (DCF exit method)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="45">
+      <c r="C24" s="47">
         <f>DCF!C27</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="56" t="inlineStr">
+      <c r="A25" s="59" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="57">
         <f>DCF!C41</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="47">
         <f>C25-C24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="56" t="inlineStr">
+      <c r="A27" s="59" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x) — assumes partial recovery from trough, not full re-rating</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>•  Above comps football-field high (7.5x on FY2025A) — terminal year has higher EBITDA &amp; normalized margins</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>•  ~1 turn above Gordon-implied exit multiple — conservative buffer vs perpetuity math</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>•  Well below historical LULU peak multiples (20–30x) — avoids heroic assumptions</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>Methodology / multiple ranges (FY2025A — football field)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="64" t="inlineStr">
+      <c r="A35" s="67" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C35" s="65" t="inlineStr">
+      <c r="C35" s="68" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D35" s="65" t="inlineStr">
+      <c r="D35" s="68" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E35" s="65" t="inlineStr">
+      <c r="E35" s="68" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F35" s="65" t="inlineStr">
+      <c r="F35" s="68" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2025A)</t>
         </is>
       </c>
-      <c r="C36" s="67" t="n">
+      <c r="C36" s="70" t="n">
         <v>4.5</v>
       </c>
-      <c r="D36" s="67" t="n">
+      <c r="D36" s="70" t="n">
         <v>7.5</v>
       </c>
-      <c r="E36" s="68">
+      <c r="E36" s="71">
         <f>(C5*C36+C7)/C8</f>
         <v/>
       </c>
-      <c r="F36" s="68">
+      <c r="F36" s="71">
         <f>(C5*D36+C7)/C8</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C37" s="67" t="n">
+      <c r="C37" s="70" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="67" t="n">
+      <c r="D37" s="70" t="n">
         <v>18</v>
       </c>
-      <c r="E37" s="68">
+      <c r="E37" s="71">
         <f>C6*C37</f>
         <v/>
       </c>
-      <c r="F37" s="68">
+      <c r="F37" s="71">
         <f>C6*D37</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="69" t="inlineStr">
+      <c r="C38" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="69" t="inlineStr">
+      <c r="D38" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="68">
+      <c r="E38" s="71">
         <f>Scenarios!C29</f>
         <v/>
       </c>
-      <c r="F38" s="68">
+      <c r="F38" s="71">
         <f>Scenarios!E29</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="70" t="inlineStr">
+      <c r="A40" s="73" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="71" t="n">
+      <c r="C40" s="74" t="n">
         <v>100</v>
       </c>
+      <c r="D40" s="48" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -203,6 +203,23 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00F2F2F2"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="10"/>
       <u val="single"/>
@@ -210,6 +227,24 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="13"/>
     </font>
@@ -218,12 +253,6 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00C8102E"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -314,7 +343,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -395,23 +424,35 @@
     <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -421,6 +462,12 @@
     </xf>
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -432,26 +479,23 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="36" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -463,22 +507,22 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="40" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -505,7 +549,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1193,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1334,357 +1378,896 @@
         <v>0.03</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Cash tax rate</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>D&amp;A % of revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>NWC build % of Δrevenue</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>5-year forecast paths (by scenario)</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 1</t>
-        </is>
-      </c>
-      <c r="C12" s="27">
-        <f>11102600*(1+C4)</f>
-        <v/>
-      </c>
-      <c r="D12" s="27">
-        <f>11102600*(1+D4)</f>
-        <v/>
-      </c>
-      <c r="E12" s="27">
-        <f>11102600*(1+E4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 2</t>
-        </is>
-      </c>
-      <c r="C13" s="27">
-        <f>C12*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D13" s="27">
-        <f>D12*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E13" s="27">
-        <f>E12*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 3</t>
-        </is>
-      </c>
-      <c r="C14" s="27">
-        <f>C13*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D14" s="27">
-        <f>D13*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E14" s="27">
-        <f>E13*(1+E5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 4</t>
-        </is>
-      </c>
-      <c r="C15" s="27">
-        <f>C14*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D15" s="27">
-        <f>D14*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E15" s="27">
-        <f>E14*(1+E5)</f>
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue – year 5</t>
+          <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
       <c r="C16" s="27">
-        <f>C15*(1+C5)</f>
+        <f>11102600*(1+C4)</f>
         <v/>
       </c>
       <c r="D16" s="27">
-        <f>D15*(1+D5)</f>
+        <f>11102600*(1+D4)</f>
         <v/>
       </c>
       <c r="E16" s="27">
-        <f>E15*(1+E5)</f>
+        <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT margin – year 1</t>
-        </is>
-      </c>
-      <c r="C17" s="28">
-        <f>C6+(C7-C6)*0/4</f>
-        <v/>
-      </c>
-      <c r="D17" s="28">
-        <f>D6+(D7-D6)*0/4</f>
-        <v/>
-      </c>
-      <c r="E17" s="28">
-        <f>E6+(E7-E6)*0/4</f>
+          <t xml:space="preserve">  Revenue – year 2</t>
+        </is>
+      </c>
+      <c r="C17" s="27">
+        <f>C16*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>D16*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E17" s="27">
+        <f>E16*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT margin – year 2</t>
-        </is>
-      </c>
-      <c r="C18" s="28">
-        <f>C6+(C7-C6)*1/4</f>
-        <v/>
-      </c>
-      <c r="D18" s="28">
-        <f>D6+(D7-D6)*1/4</f>
-        <v/>
-      </c>
-      <c r="E18" s="28">
-        <f>E6+(E7-E6)*1/4</f>
+          <t xml:space="preserve">  Revenue – year 3</t>
+        </is>
+      </c>
+      <c r="C18" s="27">
+        <f>C17*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>D17*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E18" s="27">
+        <f>E17*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT margin – year 3</t>
-        </is>
-      </c>
-      <c r="C19" s="28">
-        <f>C6+(C7-C6)*2/4</f>
-        <v/>
-      </c>
-      <c r="D19" s="28">
-        <f>D6+(D7-D6)*2/4</f>
-        <v/>
-      </c>
-      <c r="E19" s="28">
-        <f>E6+(E7-E6)*2/4</f>
+          <t xml:space="preserve">  Revenue – year 4</t>
+        </is>
+      </c>
+      <c r="C19" s="27">
+        <f>C18*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>D18*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E19" s="27">
+        <f>E18*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT margin – year 4</t>
-        </is>
-      </c>
-      <c r="C20" s="28">
-        <f>C6+(C7-C6)*3/4</f>
-        <v/>
-      </c>
-      <c r="D20" s="28">
-        <f>D6+(D7-D6)*3/4</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>E6+(E7-E6)*3/4</f>
+          <t xml:space="preserve">  Revenue – year 5</t>
+        </is>
+      </c>
+      <c r="C20" s="27">
+        <f>C19*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>D19*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E20" s="27">
+        <f>E19*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT margin – year 5</t>
+          <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
       <c r="C21" s="28">
-        <f>C6+(C7-C6)*4/4</f>
+        <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>D6+(D7-D6)*4/4</f>
+        <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
       <c r="E21" s="28">
-        <f>E6+(E7-E6)*4/4</f>
+        <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 1</t>
-        </is>
-      </c>
-      <c r="C22" s="27">
-        <f>(C12*C17)*(1-0.27)+C12*0.045-C12*0.05-0.075*(C12-11102600)</f>
-        <v/>
-      </c>
-      <c r="D22" s="27">
-        <f>(D12*D17)*(1-0.27)+D12*0.045-D12*0.05-0.075*(D12-11102600)</f>
-        <v/>
-      </c>
-      <c r="E22" s="27">
-        <f>(E12*E17)*(1-0.27)+E12*0.045-E12*0.05-0.075*(E12-11102600)</f>
+          <t xml:space="preserve">  EBIT margin – year 2</t>
+        </is>
+      </c>
+      <c r="C22" s="28">
+        <f>C6+(C7-C6)*1/4</f>
+        <v/>
+      </c>
+      <c r="D22" s="28">
+        <f>D6+(D7-D6)*1/4</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 2</t>
-        </is>
-      </c>
-      <c r="C23" s="27">
-        <f>(C13*C18)*(1-0.27)+C13*0.045-C13*0.05-0.075*(C13-C12)</f>
-        <v/>
-      </c>
-      <c r="D23" s="27">
-        <f>(D13*D18)*(1-0.27)+D13*0.045-D13*0.05-0.075*(D13-D12)</f>
-        <v/>
-      </c>
-      <c r="E23" s="27">
-        <f>(E13*E18)*(1-0.27)+E13*0.045-E13*0.05-0.075*(E13-E12)</f>
+          <t xml:space="preserve">  EBIT margin – year 3</t>
+        </is>
+      </c>
+      <c r="C23" s="28">
+        <f>C6+(C7-C6)*2/4</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>D6+(D7-D6)*2/4</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 3</t>
-        </is>
-      </c>
-      <c r="C24" s="27">
-        <f>(C14*C19)*(1-0.27)+C14*0.045-C14*0.05-0.075*(C14-C13)</f>
-        <v/>
-      </c>
-      <c r="D24" s="27">
-        <f>(D14*D19)*(1-0.27)+D14*0.045-D14*0.05-0.075*(D14-D13)</f>
-        <v/>
-      </c>
-      <c r="E24" s="27">
-        <f>(E14*E19)*(1-0.27)+E14*0.045-E14*0.05-0.075*(E14-E13)</f>
+          <t xml:space="preserve">  EBIT margin – year 4</t>
+        </is>
+      </c>
+      <c r="C24" s="28">
+        <f>C6+(C7-C6)*3/4</f>
+        <v/>
+      </c>
+      <c r="D24" s="28">
+        <f>D6+(D7-D6)*3/4</f>
+        <v/>
+      </c>
+      <c r="E24" s="28">
+        <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 4</t>
-        </is>
-      </c>
-      <c r="C25" s="27">
-        <f>(C15*C20)*(1-0.27)+C15*0.045-C15*0.05-0.075*(C15-C14)</f>
-        <v/>
-      </c>
-      <c r="D25" s="27">
-        <f>(D15*D20)*(1-0.27)+D15*0.045-D15*0.05-0.075*(D15-D14)</f>
-        <v/>
-      </c>
-      <c r="E25" s="27">
-        <f>(E15*E20)*(1-0.27)+E15*0.045-E15*0.05-0.075*(E15-E14)</f>
+          <t xml:space="preserve">  EBIT margin – year 5</t>
+        </is>
+      </c>
+      <c r="C25" s="28">
+        <f>C6+(C7-C6)*4/4</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>D6+(D7-D6)*4/4</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="26" t="inlineStr">
         <is>
+          <t xml:space="preserve">  EBIT – year 1</t>
+        </is>
+      </c>
+      <c r="C26" s="27">
+        <f>C16*C21</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>D16*D21</f>
+        <v/>
+      </c>
+      <c r="E26" s="27">
+        <f>E16*E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT – year 2</t>
+        </is>
+      </c>
+      <c r="C27" s="27">
+        <f>C17*C22</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>D17*D22</f>
+        <v/>
+      </c>
+      <c r="E27" s="27">
+        <f>E17*E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT – year 3</t>
+        </is>
+      </c>
+      <c r="C28" s="27">
+        <f>C18*C23</f>
+        <v/>
+      </c>
+      <c r="D28" s="27">
+        <f>D18*D23</f>
+        <v/>
+      </c>
+      <c r="E28" s="27">
+        <f>E18*E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT – year 4</t>
+        </is>
+      </c>
+      <c r="C29" s="27">
+        <f>C19*C24</f>
+        <v/>
+      </c>
+      <c r="D29" s="27">
+        <f>D19*D24</f>
+        <v/>
+      </c>
+      <c r="E29" s="27">
+        <f>E19*E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBIT – year 5</t>
+        </is>
+      </c>
+      <c r="C30" s="27">
+        <f>C20*C25</f>
+        <v/>
+      </c>
+      <c r="D30" s="27">
+        <f>D20*D25</f>
+        <v/>
+      </c>
+      <c r="E30" s="27">
+        <f>E20*E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOPAT – year 1</t>
+        </is>
+      </c>
+      <c r="C31" s="27">
+        <f>C26*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>D26*(1-D10)</f>
+        <v/>
+      </c>
+      <c r="E31" s="27">
+        <f>E26*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOPAT – year 2</t>
+        </is>
+      </c>
+      <c r="C32" s="27">
+        <f>C27*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>D27*(1-D10)</f>
+        <v/>
+      </c>
+      <c r="E32" s="27">
+        <f>E27*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOPAT – year 3</t>
+        </is>
+      </c>
+      <c r="C33" s="27">
+        <f>C28*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>D28*(1-D10)</f>
+        <v/>
+      </c>
+      <c r="E33" s="27">
+        <f>E28*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOPAT – year 4</t>
+        </is>
+      </c>
+      <c r="C34" s="27">
+        <f>C29*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>D29*(1-D10)</f>
+        <v/>
+      </c>
+      <c r="E34" s="27">
+        <f>E29*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOPAT – year 5</t>
+        </is>
+      </c>
+      <c r="C35" s="27">
+        <f>C30*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="D35" s="27">
+        <f>D30*(1-D10)</f>
+        <v/>
+      </c>
+      <c r="E35" s="27">
+        <f>E30*(1-E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A – year 1</t>
+        </is>
+      </c>
+      <c r="C36" s="27">
+        <f>C16*C11</f>
+        <v/>
+      </c>
+      <c r="D36" s="27">
+        <f>D16*D11</f>
+        <v/>
+      </c>
+      <c r="E36" s="27">
+        <f>E16*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A – year 2</t>
+        </is>
+      </c>
+      <c r="C37" s="27">
+        <f>C17*C11</f>
+        <v/>
+      </c>
+      <c r="D37" s="27">
+        <f>D17*D11</f>
+        <v/>
+      </c>
+      <c r="E37" s="27">
+        <f>E17*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A – year 3</t>
+        </is>
+      </c>
+      <c r="C38" s="27">
+        <f>C18*C11</f>
+        <v/>
+      </c>
+      <c r="D38" s="27">
+        <f>D18*D11</f>
+        <v/>
+      </c>
+      <c r="E38" s="27">
+        <f>E18*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A – year 4</t>
+        </is>
+      </c>
+      <c r="C39" s="27">
+        <f>C19*C11</f>
+        <v/>
+      </c>
+      <c r="D39" s="27">
+        <f>D19*D11</f>
+        <v/>
+      </c>
+      <c r="E39" s="27">
+        <f>E19*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A – year 5</t>
+        </is>
+      </c>
+      <c r="C40" s="27">
+        <f>C20*C11</f>
+        <v/>
+      </c>
+      <c r="D40" s="27">
+        <f>D20*D11</f>
+        <v/>
+      </c>
+      <c r="E40" s="27">
+        <f>E20*E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex – year 1</t>
+        </is>
+      </c>
+      <c r="C41" s="27">
+        <f>C16*C12</f>
+        <v/>
+      </c>
+      <c r="D41" s="27">
+        <f>D16*D12</f>
+        <v/>
+      </c>
+      <c r="E41" s="27">
+        <f>E16*E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex – year 2</t>
+        </is>
+      </c>
+      <c r="C42" s="27">
+        <f>C17*C12</f>
+        <v/>
+      </c>
+      <c r="D42" s="27">
+        <f>D17*D12</f>
+        <v/>
+      </c>
+      <c r="E42" s="27">
+        <f>E17*E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex – year 3</t>
+        </is>
+      </c>
+      <c r="C43" s="27">
+        <f>C18*C12</f>
+        <v/>
+      </c>
+      <c r="D43" s="27">
+        <f>D18*D12</f>
+        <v/>
+      </c>
+      <c r="E43" s="27">
+        <f>E18*E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex – year 4</t>
+        </is>
+      </c>
+      <c r="C44" s="27">
+        <f>C19*C12</f>
+        <v/>
+      </c>
+      <c r="D44" s="27">
+        <f>D19*D12</f>
+        <v/>
+      </c>
+      <c r="E44" s="27">
+        <f>E19*E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex – year 5</t>
+        </is>
+      </c>
+      <c r="C45" s="27">
+        <f>C20*C12</f>
+        <v/>
+      </c>
+      <c r="D45" s="27">
+        <f>D20*D12</f>
+        <v/>
+      </c>
+      <c r="E45" s="27">
+        <f>E20*E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 1</t>
+        </is>
+      </c>
+      <c r="C46" s="27">
+        <f>C13*(C16-11102600)</f>
+        <v/>
+      </c>
+      <c r="D46" s="27">
+        <f>D13*(D16-11102600)</f>
+        <v/>
+      </c>
+      <c r="E46" s="27">
+        <f>E13*(E16-11102600)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 2</t>
+        </is>
+      </c>
+      <c r="C47" s="27">
+        <f>C13*(C17-C16)</f>
+        <v/>
+      </c>
+      <c r="D47" s="27">
+        <f>D13*(D17-D16)</f>
+        <v/>
+      </c>
+      <c r="E47" s="27">
+        <f>E13*(E17-E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 3</t>
+        </is>
+      </c>
+      <c r="C48" s="27">
+        <f>C13*(C18-C17)</f>
+        <v/>
+      </c>
+      <c r="D48" s="27">
+        <f>D13*(D18-D17)</f>
+        <v/>
+      </c>
+      <c r="E48" s="27">
+        <f>E13*(E18-E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 4</t>
+        </is>
+      </c>
+      <c r="C49" s="27">
+        <f>C13*(C19-C18)</f>
+        <v/>
+      </c>
+      <c r="D49" s="27">
+        <f>D13*(D19-D18)</f>
+        <v/>
+      </c>
+      <c r="E49" s="27">
+        <f>E13*(E19-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 5</t>
+        </is>
+      </c>
+      <c r="C50" s="27">
+        <f>C13*(C20-C19)</f>
+        <v/>
+      </c>
+      <c r="D50" s="27">
+        <f>D13*(D20-D19)</f>
+        <v/>
+      </c>
+      <c r="E50" s="27">
+        <f>E13*(E20-E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 1</t>
+        </is>
+      </c>
+      <c r="C51" s="27">
+        <f>C31+C36-C41-C46</f>
+        <v/>
+      </c>
+      <c r="D51" s="27">
+        <f>D31+D36-D41-D46</f>
+        <v/>
+      </c>
+      <c r="E51" s="27">
+        <f>E31+E36-E41-E46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 2</t>
+        </is>
+      </c>
+      <c r="C52" s="27">
+        <f>C32+C37-C42-C47</f>
+        <v/>
+      </c>
+      <c r="D52" s="27">
+        <f>D32+D37-D42-D47</f>
+        <v/>
+      </c>
+      <c r="E52" s="27">
+        <f>E32+E37-E42-E47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 3</t>
+        </is>
+      </c>
+      <c r="C53" s="27">
+        <f>C33+C38-C43-C48</f>
+        <v/>
+      </c>
+      <c r="D53" s="27">
+        <f>D33+D38-D43-D48</f>
+        <v/>
+      </c>
+      <c r="E53" s="27">
+        <f>E33+E38-E43-E48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 4</t>
+        </is>
+      </c>
+      <c r="C54" s="27">
+        <f>C34+C39-C44-C49</f>
+        <v/>
+      </c>
+      <c r="D54" s="27">
+        <f>D34+D39-D44-D49</f>
+        <v/>
+      </c>
+      <c r="E54" s="27">
+        <f>E34+E39-E44-E49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="26" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C26" s="27">
-        <f>(C16*C21)*(1-0.27)+C16*0.045-C16*0.05-0.075*(C16-C15)</f>
-        <v/>
-      </c>
-      <c r="D26" s="27">
-        <f>(D16*D21)*(1-0.27)+D16*0.045-D16*0.05-0.075*(D16-D15)</f>
-        <v/>
-      </c>
-      <c r="E26" s="27">
-        <f>(E16*E21)*(1-0.27)+E16*0.045-E16*0.05-0.075*(E16-E15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="C55" s="27">
+        <f>C35+C40-C45-C50</f>
+        <v/>
+      </c>
+      <c r="D55" s="27">
+        <f>D35+D40-D45-D50</f>
+        <v/>
+      </c>
+      <c r="E55" s="27">
+        <f>E35+E40-E45-E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C28" s="29">
-        <f>NPV(C8,C22,C23,C24,C25,C26)+(C26*(1+C9)/(C8-C9))/(1+C8)^5</f>
-        <v/>
-      </c>
-      <c r="D28" s="29">
-        <f>NPV(D8,D22,D23,D24,D25,D26)+(D26*(1+D9)/(D8-D9))/(1+D8)^5</f>
-        <v/>
-      </c>
-      <c r="E28" s="29">
-        <f>NPV(E8,E22,E23,E24,E25,E26)+(E26*(1+E9)/(E8-E9))/(1+E8)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="C57" s="29">
+        <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
+        <v/>
+      </c>
+      <c r="D57" s="29">
+        <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
+        <v/>
+      </c>
+      <c r="E57" s="29">
+        <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C29" s="31">
-        <f>(C28+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="D29" s="32">
-        <f>(D28+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="E29" s="31">
-        <f>(E28+1807202-0)/111380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="C58" s="31">
+        <f>(C57+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="D58" s="32">
+        <f>(D57+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="E58" s="31">
+        <f>(E57+1807202-0)/111380</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C30" s="33">
-        <f>C29/100.0-1</f>
-        <v/>
-      </c>
-      <c r="D30" s="33">
-        <f>D29/100.0-1</f>
-        <v/>
-      </c>
-      <c r="E30" s="33">
-        <f>E29/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="C59" s="33">
+        <f>C58/100.0-1</f>
+        <v/>
+      </c>
+      <c r="D59" s="33">
+        <f>D58/100.0-1</f>
+        <v/>
+      </c>
+      <c r="E59" s="33">
+        <f>E58/100.0-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -1701,7 +2284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1712,6 +2295,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1759,16 +2343,26 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="I2" s="36" t="inlineStr">
+        <is>
+          <t>Δ vs Scenarios</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
-      <c r="C3" s="37" t="inlineStr">
+      <c r="C3" s="38" t="inlineStr">
         <is>
           <t>10-K source</t>
+        </is>
+      </c>
+      <c r="I3" s="39" t="inlineStr">
+        <is>
+          <t>(should be 0)</t>
         </is>
       </c>
     </row>
@@ -1778,27 +2372,31 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="38" t="n">
+      <c r="C5" s="40" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="39">
-        <f>Scenarios!D12</f>
-        <v/>
-      </c>
-      <c r="E5" s="39">
-        <f>Scenarios!D13</f>
-        <v/>
-      </c>
-      <c r="F5" s="39">
-        <f>Scenarios!D14</f>
-        <v/>
-      </c>
-      <c r="G5" s="39">
-        <f>Scenarios!D15</f>
-        <v/>
-      </c>
-      <c r="H5" s="39">
+      <c r="D5" s="41">
         <f>Scenarios!D16</f>
+        <v/>
+      </c>
+      <c r="E5" s="41">
+        <f>Scenarios!D17</f>
+        <v/>
+      </c>
+      <c r="F5" s="41">
+        <f>Scenarios!D18</f>
+        <v/>
+      </c>
+      <c r="G5" s="41">
+        <f>Scenarios!D19</f>
+        <v/>
+      </c>
+      <c r="H5" s="41">
+        <f>Scenarios!D20</f>
+        <v/>
+      </c>
+      <c r="I5" s="42">
+        <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -1808,23 +2406,23 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="43">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="43">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="43">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="43">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="40">
+      <c r="H6" s="43">
         <f>H5/G5-1</f>
         <v/>
       </c>
@@ -1835,24 +2433,28 @@
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="40">
-        <f>Scenarios!D17</f>
-        <v/>
-      </c>
-      <c r="E7" s="40">
-        <f>Scenarios!D18</f>
-        <v/>
-      </c>
-      <c r="F7" s="40">
-        <f>Scenarios!D19</f>
-        <v/>
-      </c>
-      <c r="G7" s="40">
-        <f>Scenarios!D20</f>
-        <v/>
-      </c>
-      <c r="H7" s="40">
+      <c r="D7" s="43">
         <f>Scenarios!D21</f>
+        <v/>
+      </c>
+      <c r="E7" s="43">
+        <f>Scenarios!D22</f>
+        <v/>
+      </c>
+      <c r="F7" s="43">
+        <f>Scenarios!D23</f>
+        <v/>
+      </c>
+      <c r="G7" s="43">
+        <f>Scenarios!D24</f>
+        <v/>
+      </c>
+      <c r="H7" s="43">
+        <f>Scenarios!D25</f>
+        <v/>
+      </c>
+      <c r="I7" s="42">
+        <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -1862,27 +2464,31 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="44" t="n">
         <v>2210615</v>
       </c>
       <c r="D8" s="29">
-        <f>D5*D7</f>
+        <f>Scenarios!D26</f>
         <v/>
       </c>
       <c r="E8" s="29">
-        <f>E5*E7</f>
+        <f>Scenarios!D27</f>
         <v/>
       </c>
       <c r="F8" s="29">
-        <f>F5*F7</f>
+        <f>Scenarios!D28</f>
         <v/>
       </c>
       <c r="G8" s="29">
-        <f>G5*G7</f>
+        <f>Scenarios!D29</f>
         <v/>
       </c>
       <c r="H8" s="29">
-        <f>H5*H7</f>
+        <f>Scenarios!D30</f>
+        <v/>
+      </c>
+      <c r="I8" s="45">
+        <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -1892,24 +2498,24 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="39">
-        <f>-D8*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="E9" s="39">
-        <f>-E8*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="F9" s="39">
-        <f>-F8*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="G9" s="39">
-        <f>-G8*WACC!C10</f>
-        <v/>
-      </c>
-      <c r="H9" s="39">
-        <f>-H8*WACC!C10</f>
+      <c r="D9" s="41">
+        <f>-Scenarios!D26*Scenarios!$D$10</f>
+        <v/>
+      </c>
+      <c r="E9" s="41">
+        <f>-Scenarios!D27*Scenarios!$D$10</f>
+        <v/>
+      </c>
+      <c r="F9" s="41">
+        <f>-Scenarios!D28*Scenarios!$D$10</f>
+        <v/>
+      </c>
+      <c r="G9" s="41">
+        <f>-Scenarios!D29*Scenarios!$D$10</f>
+        <v/>
+      </c>
+      <c r="H9" s="41">
+        <f>-Scenarios!D30*Scenarios!$D$10</f>
         <v/>
       </c>
     </row>
@@ -1920,23 +2526,27 @@
         </is>
       </c>
       <c r="D10" s="29">
-        <f>D8+D9</f>
+        <f>Scenarios!D31</f>
         <v/>
       </c>
       <c r="E10" s="29">
-        <f>E8+E9</f>
+        <f>Scenarios!D32</f>
         <v/>
       </c>
       <c r="F10" s="29">
-        <f>F8+F9</f>
+        <f>Scenarios!D33</f>
         <v/>
       </c>
       <c r="G10" s="29">
-        <f>G8+G9</f>
+        <f>Scenarios!D34</f>
         <v/>
       </c>
       <c r="H10" s="29">
-        <f>H8+H9</f>
+        <f>Scenarios!D35</f>
+        <v/>
+      </c>
+      <c r="I10" s="45">
+        <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -1946,20 +2556,25 @@
           <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.045</v>
+      <c r="D11" s="16">
+        <f>Scenarios!$D$11</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>Scenarios!$D$11</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>Scenarios!$D$11</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>Scenarios!$D$11</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>Scenarios!$D$11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -1968,24 +2583,28 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="39">
-        <f>D5*D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="39">
-        <f>E5*E11</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
-        <f>F5*F11</f>
-        <v/>
-      </c>
-      <c r="G12" s="39">
-        <f>G5*G11</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>H5*H11</f>
+      <c r="D12" s="41">
+        <f>Scenarios!D36</f>
+        <v/>
+      </c>
+      <c r="E12" s="41">
+        <f>Scenarios!D37</f>
+        <v/>
+      </c>
+      <c r="F12" s="41">
+        <f>Scenarios!D38</f>
+        <v/>
+      </c>
+      <c r="G12" s="41">
+        <f>Scenarios!D39</f>
+        <v/>
+      </c>
+      <c r="H12" s="41">
+        <f>Scenarios!D40</f>
+        <v/>
+      </c>
+      <c r="I12" s="42">
+        <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -1995,20 +2614,25 @@
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.05</v>
+      <c r="D13" s="16">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>Scenarios!$D$12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2017,47 +2641,56 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="39">
-        <f>-D5*D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="39">
-        <f>-E5*E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="39">
-        <f>-F5*F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="39">
-        <f>-G5*G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="39">
-        <f>-H5*H13</f>
+      <c r="D14" s="41">
+        <f>-Scenarios!D41</f>
+        <v/>
+      </c>
+      <c r="E14" s="41">
+        <f>-Scenarios!D42</f>
+        <v/>
+      </c>
+      <c r="F14" s="41">
+        <f>-Scenarios!D43</f>
+        <v/>
+      </c>
+      <c r="G14" s="41">
+        <f>-Scenarios!D44</f>
+        <v/>
+      </c>
+      <c r="H14" s="41">
+        <f>-Scenarios!D45</f>
+        <v/>
+      </c>
+      <c r="I14" s="42">
+        <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NWC % of revenue</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H15" s="16" t="n">
-        <v>0.075</v>
+          <t xml:space="preserve">  NWC build % of Δrevenue</t>
+        </is>
+      </c>
+      <c r="D15" s="16">
+        <f>Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>Scenarios!$D$13</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2066,24 +2699,28 @@
           <t>Less: increase in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="39">
-        <f>-D15*(D5-C5)</f>
-        <v/>
-      </c>
-      <c r="E16" s="39">
-        <f>-E15*(E5-D5)</f>
-        <v/>
-      </c>
-      <c r="F16" s="39">
-        <f>-F15*(F5-E5)</f>
-        <v/>
-      </c>
-      <c r="G16" s="39">
-        <f>-G15*(G5-F5)</f>
-        <v/>
-      </c>
-      <c r="H16" s="39">
-        <f>-H15*(H5-G5)</f>
+      <c r="D16" s="41">
+        <f>-Scenarios!D46</f>
+        <v/>
+      </c>
+      <c r="E16" s="41">
+        <f>-Scenarios!D47</f>
+        <v/>
+      </c>
+      <c r="F16" s="41">
+        <f>-Scenarios!D48</f>
+        <v/>
+      </c>
+      <c r="G16" s="41">
+        <f>-Scenarios!D49</f>
+        <v/>
+      </c>
+      <c r="H16" s="41">
+        <f>-Scenarios!D50</f>
+        <v/>
+      </c>
+      <c r="I16" s="42">
+        <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2093,24 +2730,28 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D17" s="42">
-        <f>D10+D12+D14+D16</f>
-        <v/>
-      </c>
-      <c r="E17" s="42">
-        <f>E10+E12+E14+E16</f>
-        <v/>
-      </c>
-      <c r="F17" s="42">
-        <f>F10+F12+F14+F16</f>
-        <v/>
-      </c>
-      <c r="G17" s="42">
-        <f>G10+G12+G14+G16</f>
-        <v/>
-      </c>
-      <c r="H17" s="42">
-        <f>H10+H12+H14+H16</f>
+      <c r="D17" s="46">
+        <f>Scenarios!D51</f>
+        <v/>
+      </c>
+      <c r="E17" s="46">
+        <f>Scenarios!D52</f>
+        <v/>
+      </c>
+      <c r="F17" s="46">
+        <f>Scenarios!D53</f>
+        <v/>
+      </c>
+      <c r="G17" s="46">
+        <f>Scenarios!D54</f>
+        <v/>
+      </c>
+      <c r="H17" s="46">
+        <f>Scenarios!D55</f>
+        <v/>
+      </c>
+      <c r="I17" s="45">
+        <f>IF(MAX(ABS(D17-Scenarios!$D$51),ABS(E17-Scenarios!$D$52),ABS(F17-Scenarios!$D$53),ABS(G17-Scenarios!$D$54),ABS(H17-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2120,19 +2761,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="43" t="n">
+      <c r="E18" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="43" t="n">
+      <c r="F18" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="43" t="n">
+      <c r="G18" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="H18" s="43" t="n">
+      <c r="H18" s="47" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2142,23 +2783,23 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="48">
         <f>1/(1+Scenarios!$D$8)^D18</f>
         <v/>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="48">
         <f>1/(1+Scenarios!$D$8)^E18</f>
         <v/>
       </c>
-      <c r="F19" s="44">
+      <c r="F19" s="48">
         <f>1/(1+Scenarios!$D$8)^F18</f>
         <v/>
       </c>
-      <c r="G19" s="44">
+      <c r="G19" s="48">
         <f>1/(1+Scenarios!$D$8)^G18</f>
         <v/>
       </c>
-      <c r="H19" s="44">
+      <c r="H19" s="48">
         <f>1/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
@@ -2191,546 +2832,561 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="45" t="inlineStr">
+      <c r="A22" s="49" t="inlineStr">
+        <is>
+          <t>Scenarios linkage summary (column I should all read OK)</t>
+        </is>
+      </c>
+      <c r="I22" s="50">
+        <f>IF(COUNTIF(I5:I17,"CHECK")=0,"ALL OK","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C23" s="46">
+      <c r="C24" s="52">
         <f>SUM(D20:H20)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C24" s="40">
+      <c r="C25" s="43">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f>H8+H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="C26" s="39">
-        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="15" t="inlineStr">
         <is>
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="C27" s="41">
+        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C27" s="47">
-        <f>C26/C25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="C28" s="46">
-        <f>C26/(1+Scenarios!$D$8)^H18</f>
+      <c r="C28" s="53">
+        <f>C27/C26</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C29" s="52">
+        <f>C27/(1+Scenarios!$D$8)^H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C29" s="29">
-        <f>C23+C28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C30" s="38" t="n">
-        <v>1807202</v>
-      </c>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
+      <c r="C30" s="29">
+        <f>C24+C29</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C31" s="40" t="n">
+        <v>1807202</v>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C31" s="38" t="n">
+      <c r="C32" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D31" s="48" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C32" s="29">
-        <f>C29+C30+C31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="C33" s="29">
+        <f>C30+C31+C32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C33" s="38" t="n">
+      <c r="C34" s="40" t="n">
         <v>111380</v>
       </c>
-      <c r="D33" s="48" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C34" s="49">
-        <f>C32/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="C35" s="55">
+        <f>C33/C34</f>
+        <v/>
+      </c>
+      <c r="I35" s="45">
+        <f>IF(ABS(C35-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C35" s="50" t="n">
+      <c r="C36" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="D35" s="48" t="inlineStr">
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C36" s="51">
-        <f>C34/C35-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="C37" s="57">
+        <f>C35/C36-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C37" s="40">
-        <f>C28/C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="45" t="inlineStr">
+      <c r="C38" s="43">
+        <f>C29/C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="51" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="52" t="inlineStr">
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="49" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
-        </is>
-      </c>
-      <c r="C41" s="53" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
-        <is>
-          <t>Base-case terminal multiple; see Comps → Exit Multiple Build</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>Terminal value = Terminal EBITDA × exit multiple</t>
-        </is>
-      </c>
-      <c r="C42" s="39">
-        <f>C25*C41</f>
-        <v/>
+          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
+        </is>
+      </c>
+      <c r="C42" s="58" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>Base-case terminal multiple; see Comps → Exit Multiple Build</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
+          <t>Terminal value = Terminal EBITDA × exit multiple</t>
+        </is>
+      </c>
+      <c r="C43" s="41">
+        <f>C26*C42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C43" s="39">
-        <f>C42/(1+Scenarios!$D$8)^H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="19" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="C44" s="29">
-        <f>C23+C43</f>
+      <c r="C44" s="41">
+        <f>C43/(1+Scenarios!$D$8)^H18</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="C45" s="29">
+        <f>C24+C44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C45" s="54">
-        <f>(C44+C30+C31)/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="45" t="inlineStr">
+      <c r="C46" s="59">
+        <f>(C45+C31+C32)/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
-      <c r="D47" s="13" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="55" t="inlineStr"/>
-      <c r="B48" s="56" t="inlineStr">
+      <c r="B48" s="13" t="n"/>
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="60" t="inlineStr"/>
+      <c r="B49" s="61" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C48" s="56" t="inlineStr">
+      <c r="C49" s="61" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D48" s="56" t="inlineStr">
+      <c r="D49" s="61" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="inlineStr">
-        <is>
-          <t>Terminal value ($)</t>
-        </is>
-      </c>
-      <c r="B49" s="46">
-        <f>C26</f>
-        <v/>
-      </c>
-      <c r="C49" s="46">
-        <f>C42</f>
-        <v/>
-      </c>
-      <c r="D49" s="46">
-        <f>B49-C49</f>
-        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
+          <t>Terminal value ($)</t>
+        </is>
+      </c>
+      <c r="B50" s="52">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="C50" s="52">
+        <f>C43</f>
+        <v/>
+      </c>
+      <c r="D50" s="52">
+        <f>B50-C50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B50" s="57">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="C50" s="57">
-        <f>C41</f>
-        <v/>
-      </c>
-      <c r="D50" s="57">
-        <f>B50-C50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="B51" s="62">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="C51" s="62">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="D51" s="62">
+        <f>B51-C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B51" s="40" t="inlineStr"/>
-      <c r="C51" s="40" t="inlineStr"/>
-      <c r="D51" s="40">
-        <f>(B49-C49)/B49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr"/>
+      <c r="C52" s="43" t="inlineStr"/>
+      <c r="D52" s="43">
+        <f>(B50-C50)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B52" s="58">
-        <f>C34</f>
-        <v/>
-      </c>
-      <c r="C52" s="58">
-        <f>C45</f>
-        <v/>
-      </c>
-      <c r="D52" s="58">
-        <f>B52-C52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="59" t="inlineStr">
+      <c r="B53" s="63">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="C53" s="63">
+        <f>C46</f>
+        <v/>
+      </c>
+      <c r="D53" s="63">
+        <f>B53-C53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="64" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B53" s="60">
-        <f>IF(ABS(D50)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C53" s="61">
-        <f>TEXT(D50,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D53" s="17" t="inlineStr">
+      <c r="B54" s="65">
+        <f>IF(ABS(D51)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C54" s="66">
+        <f>TEXT(D51,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D54" s="17" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="45" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="51" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n"/>
-      <c r="C56" s="13" t="n"/>
-      <c r="D56" s="13" t="n"/>
-      <c r="E56" s="13" t="n"/>
-      <c r="F56" s="13" t="n"/>
-      <c r="G56" s="13" t="n"/>
-      <c r="H56" s="13" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="62" t="inlineStr">
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="67" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D57" s="63" t="n">
+      <c r="D58" s="68" t="n">
         <v>0.015</v>
       </c>
-      <c r="E57" s="63" t="n">
+      <c r="E58" s="68" t="n">
         <v>0.02</v>
       </c>
-      <c r="F57" s="63" t="n">
+      <c r="F58" s="68" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G57" s="63" t="n">
+      <c r="G58" s="68" t="n">
         <v>0.025</v>
       </c>
-      <c r="H57" s="63" t="n">
+      <c r="H58" s="68" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="63" t="n">
+    <row r="59">
+      <c r="A59" s="68" t="n">
         <v>0.09</v>
       </c>
-      <c r="D58" s="64">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="E58" s="64">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="F58" s="64">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="G58" s="64">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="H58" s="64">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="63" t="n">
+      <c r="D59" s="69">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="E59" s="69">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="F59" s="69">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="G59" s="69">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="H59" s="69">
+        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="68" t="n">
         <v>0.095</v>
       </c>
-      <c r="D59" s="64">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="E59" s="64">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="F59" s="64">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="G59" s="64">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="H59" s="64">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="63" t="n">
+      <c r="D60" s="69">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="E60" s="69">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="F60" s="69">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="G60" s="69">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="H60" s="69">
+        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="68" t="n">
         <v>0.1</v>
       </c>
-      <c r="D60" s="64">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="E60" s="64">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="F60" s="65">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="G60" s="64">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="H60" s="64">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="63" t="n">
+      <c r="D61" s="69">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="E61" s="69">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="F61" s="70">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="G61" s="69">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="H61" s="69">
+        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="68" t="n">
         <v>0.105</v>
       </c>
-      <c r="D61" s="64">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="E61" s="64">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="F61" s="64">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="G61" s="64">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="H61" s="64">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="63" t="n">
+      <c r="D62" s="69">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="E62" s="69">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="F62" s="69">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="G62" s="69">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="H62" s="69">
+        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="68" t="n">
         <v>0.11</v>
       </c>
-      <c r="D62" s="64">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="E62" s="64">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="F62" s="64">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="G62" s="64">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C30+C31)/C33</f>
-        <v/>
-      </c>
-      <c r="H62" s="64">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C30+C31)/C33</f>
+      <c r="D63" s="69">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="E63" s="69">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="F63" s="69">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="G63" s="69">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C31+C32)/C34</f>
+        <v/>
+      </c>
+      <c r="H63" s="69">
+        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C31+C32)/C34</f>
         <v/>
       </c>
     </row>
@@ -2739,14 +3395,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D30" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2794,10 +3450,10 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="38" t="n">
+      <c r="C4" s="40" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="D4" s="54" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -2809,7 +3465,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="39">
+      <c r="C5" s="41">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -2820,10 +3476,10 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="56" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D6" s="48" t="inlineStr">
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -2835,10 +3491,10 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="38" t="n">
+      <c r="C7" s="40" t="n">
         <v>1807202</v>
       </c>
-      <c r="D7" s="48" t="inlineStr">
+      <c r="D7" s="54" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -2850,10 +3506,10 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="38" t="n">
+      <c r="C8" s="40" t="n">
         <v>111380</v>
       </c>
-      <c r="D8" s="48" t="inlineStr">
+      <c r="D8" s="54" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -2865,33 +3521,33 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="50" t="n">
+      <c r="C9" s="56" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="48" t="inlineStr">
+      <c r="D9" s="54" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="66">
+      <c r="C10" s="71">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="66">
+      <c r="C11" s="71">
         <f>C9/C6</f>
         <v/>
       </c>
@@ -2904,24 +3560,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="66" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="67" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C15" s="68" t="inlineStr">
+      <c r="C15" s="73" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="67" t="inlineStr">
+      <c r="D15" s="72" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -2933,7 +3589,7 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C16" s="69">
+      <c r="C16" s="74">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
@@ -2949,7 +3605,7 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C17" s="70" t="n">
+      <c r="C17" s="75" t="n">
         <v>18</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -2964,7 +3620,7 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C18" s="70" t="n">
+      <c r="C18" s="75" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -2979,7 +3635,7 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C19" s="70" t="n">
+      <c r="C19" s="75" t="n">
         <v>25</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
@@ -2994,7 +3650,7 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C20" s="70" t="n">
+      <c r="C20" s="75" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -3009,7 +3665,7 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C21" s="70" t="n">
+      <c r="C21" s="75" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
@@ -3031,19 +3687,19 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="47">
-        <f>DCF!C27</f>
+      <c r="C24" s="53">
+        <f>DCF!C28</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="59" t="inlineStr">
+      <c r="A25" s="64" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C25" s="57">
-        <f>DCF!C41</f>
+      <c r="C25" s="62">
+        <f>DCF!C42</f>
         <v/>
       </c>
     </row>
@@ -3053,13 +3709,13 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="53">
         <f>C25-C24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="59" t="inlineStr">
+      <c r="A27" s="64" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
@@ -3108,27 +3764,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="67" t="inlineStr">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C35" s="68" t="inlineStr">
+      <c r="C35" s="73" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D35" s="68" t="inlineStr">
+      <c r="D35" s="73" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E35" s="68" t="inlineStr">
+      <c r="E35" s="73" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F35" s="68" t="inlineStr">
+      <c r="F35" s="73" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -3140,17 +3796,17 @@
           <t>EV / EBITDA (FY2025A)</t>
         </is>
       </c>
-      <c r="C36" s="70" t="n">
+      <c r="C36" s="75" t="n">
         <v>4.5</v>
       </c>
-      <c r="D36" s="70" t="n">
+      <c r="D36" s="75" t="n">
         <v>7.5</v>
       </c>
-      <c r="E36" s="71">
+      <c r="E36" s="76">
         <f>(C5*C36+C7)/C8</f>
         <v/>
       </c>
-      <c r="F36" s="71">
+      <c r="F36" s="76">
         <f>(C5*D36+C7)/C8</f>
         <v/>
       </c>
@@ -3161,17 +3817,17 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C37" s="70" t="n">
+      <c r="C37" s="75" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="70" t="n">
+      <c r="D37" s="75" t="n">
         <v>18</v>
       </c>
-      <c r="E37" s="71">
+      <c r="E37" s="76">
         <f>C6*C37</f>
         <v/>
       </c>
-      <c r="F37" s="71">
+      <c r="F37" s="76">
         <f>C6*D37</f>
         <v/>
       </c>
@@ -3182,35 +3838,35 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="72" t="inlineStr">
+      <c r="C38" s="77" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="72" t="inlineStr">
+      <c r="D38" s="77" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="71">
-        <f>Scenarios!C29</f>
-        <v/>
-      </c>
-      <c r="F38" s="71">
-        <f>Scenarios!E29</f>
+      <c r="E38" s="76">
+        <f>Scenarios!C58</f>
+        <v/>
+      </c>
+      <c r="F38" s="76">
+        <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="73" t="inlineStr">
+      <c r="A40" s="78" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="74" t="n">
+      <c r="C40" s="79" t="n">
         <v>100</v>
       </c>
-      <c r="D40" s="48" t="inlineStr">
+      <c r="D40" s="54" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -154,6 +154,12 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <color rgb="00000000"/>
       <sz val="9"/>
     </font>
@@ -233,12 +239,6 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
-      <color rgb="00C8102E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="9"/>
     </font>
@@ -276,6 +276,12 @@
       <name val="Garamond"/>
       <color rgb="00006100"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="7"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -343,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -397,19 +403,22 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="23" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="24" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -418,41 +427,47 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -463,20 +478,17 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="166" fontId="36" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -494,7 +506,7 @@
     <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -519,7 +531,7 @@
     <xf numFmtId="164" fontId="40" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -528,10 +540,10 @@
     <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -543,13 +555,16 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1059,7 +1074,7 @@
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1090,7 +1105,7 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>analyst input</t>
+          <t>10-year UST ~4.3% as of Sep 2026; standard risk-free anchor for US equity DCF discount-rate build.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1120,7 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>analyst input</t>
+          <t>6.0% long-run US equity risk premium; conventional CAPM input for mature, liquid large-cap consumer brands.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1135,7 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>~0.86 market beta; 0.95 used for near-term uncertainty</t>
+          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1168,7 @@
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>illustrative; LULU has no funded debt</t>
+          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1183,7 @@
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>normalized marginal rate</t>
+          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1216,7 @@
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>net-cash balance sheet → ~100% equity</t>
+          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
         </is>
       </c>
     </row>
@@ -1213,6 +1228,11 @@
       </c>
       <c r="C15" s="16" t="n">
         <v>0</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1237,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1245,6 +1265,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1281,6 +1302,11 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
+      <c r="F3" s="26" t="inlineStr">
+        <is>
+          <t>Justification (base case, ~20 words)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
@@ -1297,6 +1323,11 @@
       <c r="E4" s="16" t="n">
         <v>-0.04</v>
       </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1313,6 +1344,11 @@
       <c r="E5" s="16" t="n">
         <v>0.06</v>
       </c>
+      <c r="F5" s="17" t="inlineStr">
+        <is>
+          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1329,6 +1365,11 @@
       <c r="E6" s="16" t="n">
         <v>0.15</v>
       </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1345,6 +1386,11 @@
       <c r="E7" s="16" t="n">
         <v>0.19</v>
       </c>
+      <c r="F7" s="17" t="inlineStr">
+        <is>
+          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1361,6 +1407,11 @@
       <c r="E8" s="16" t="n">
         <v>0.09</v>
       </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1377,6 +1428,11 @@
       <c r="E9" s="16" t="n">
         <v>0.03</v>
       </c>
+      <c r="F9" s="17" t="inlineStr">
+        <is>
+          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1393,6 +1449,11 @@
       <c r="E10" s="16" t="n">
         <v>0.25</v>
       </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1409,6 +1470,11 @@
       <c r="E11" s="16" t="n">
         <v>0.045</v>
       </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -1425,6 +1491,11 @@
       <c r="E12" s="16" t="n">
         <v>0.045</v>
       </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -1441,6 +1512,11 @@
       <c r="E13" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1450,761 +1526,761 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="28">
         <f>11102600*(1+C4)</f>
         <v/>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="28">
         <f>11102600*(1+D4)</f>
         <v/>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="28">
         <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C16*(1+C5)</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D16*(1+D5)</f>
         <v/>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E16*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>C17*(1+C5)</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>D17*(1+D5)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>E17*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f>C18*(1+C5)</f>
         <v/>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="28">
         <f>D18*(1+D5)</f>
         <v/>
       </c>
-      <c r="E19" s="27">
+      <c r="E19" s="28">
         <f>E18*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>C19*(1+C5)</f>
         <v/>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>D19*(1+D5)</f>
         <v/>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>E19*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="29">
         <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="29">
         <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="29">
         <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="29">
         <f>C6+(C7-C6)*1/4</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="29">
         <f>D6+(D7-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="29">
         <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="29">
         <f>C6+(C7-C6)*2/4</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="29">
         <f>D6+(D7-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="29">
         <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="29">
         <f>C6+(C7-C6)*3/4</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="29">
         <f>D6+(D7-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="29">
         <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="29">
         <f>C6+(C7-C6)*4/4</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="29">
         <f>D6+(D7-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="29">
         <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>C16*C21</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>D16*D21</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>E16*E21</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>C17*C22</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>D17*D22</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>E17*E22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="C28" s="27">
+      <c r="C28" s="28">
         <f>C18*C23</f>
         <v/>
       </c>
-      <c r="D28" s="27">
+      <c r="D28" s="28">
         <f>D18*D23</f>
         <v/>
       </c>
-      <c r="E28" s="27">
+      <c r="E28" s="28">
         <f>E18*E23</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f>C19*C24</f>
         <v/>
       </c>
-      <c r="D29" s="27">
+      <c r="D29" s="28">
         <f>D19*D24</f>
         <v/>
       </c>
-      <c r="E29" s="27">
+      <c r="E29" s="28">
         <f>E19*E24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="C30" s="27">
+      <c r="C30" s="28">
         <f>C20*C25</f>
         <v/>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="28">
         <f>D20*D25</f>
         <v/>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="28">
         <f>E20*E25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>C26*(1-C10)</f>
         <v/>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <f>D26*(1-D10)</f>
         <v/>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <f>E26*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="C32" s="27">
+      <c r="C32" s="28">
         <f>C27*(1-C10)</f>
         <v/>
       </c>
-      <c r="D32" s="27">
+      <c r="D32" s="28">
         <f>D27*(1-D10)</f>
         <v/>
       </c>
-      <c r="E32" s="27">
+      <c r="E32" s="28">
         <f>E27*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="C33" s="27">
+      <c r="C33" s="28">
         <f>C28*(1-C10)</f>
         <v/>
       </c>
-      <c r="D33" s="27">
+      <c r="D33" s="28">
         <f>D28*(1-D10)</f>
         <v/>
       </c>
-      <c r="E33" s="27">
+      <c r="E33" s="28">
         <f>E28*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>C29*(1-C10)</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>D29*(1-D10)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>E29*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
+      <c r="A35" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="28">
         <f>C30*(1-C10)</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="28">
         <f>D30*(1-D10)</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="28">
         <f>E30*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="C36" s="27">
+      <c r="C36" s="28">
         <f>C16*C11</f>
         <v/>
       </c>
-      <c r="D36" s="27">
+      <c r="D36" s="28">
         <f>D16*D11</f>
         <v/>
       </c>
-      <c r="E36" s="27">
+      <c r="E36" s="28">
         <f>E16*E11</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="26" t="inlineStr">
+      <c r="A37" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="C37" s="27">
+      <c r="C37" s="28">
         <f>C17*C11</f>
         <v/>
       </c>
-      <c r="D37" s="27">
+      <c r="D37" s="28">
         <f>D17*D11</f>
         <v/>
       </c>
-      <c r="E37" s="27">
+      <c r="E37" s="28">
         <f>E17*E11</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="C38" s="27">
+      <c r="C38" s="28">
         <f>C18*C11</f>
         <v/>
       </c>
-      <c r="D38" s="27">
+      <c r="D38" s="28">
         <f>D18*D11</f>
         <v/>
       </c>
-      <c r="E38" s="27">
+      <c r="E38" s="28">
         <f>E18*E11</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="26" t="inlineStr">
+      <c r="A39" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="C39" s="27">
+      <c r="C39" s="28">
         <f>C19*C11</f>
         <v/>
       </c>
-      <c r="D39" s="27">
+      <c r="D39" s="28">
         <f>D19*D11</f>
         <v/>
       </c>
-      <c r="E39" s="27">
+      <c r="E39" s="28">
         <f>E19*E11</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="C40" s="27">
+      <c r="C40" s="28">
         <f>C20*C11</f>
         <v/>
       </c>
-      <c r="D40" s="27">
+      <c r="D40" s="28">
         <f>D20*D11</f>
         <v/>
       </c>
-      <c r="E40" s="27">
+      <c r="E40" s="28">
         <f>E20*E11</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="C41" s="27">
+      <c r="C41" s="28">
         <f>C16*C12</f>
         <v/>
       </c>
-      <c r="D41" s="27">
+      <c r="D41" s="28">
         <f>D16*D12</f>
         <v/>
       </c>
-      <c r="E41" s="27">
+      <c r="E41" s="28">
         <f>E16*E12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>C17*C12</f>
         <v/>
       </c>
-      <c r="D42" s="27">
+      <c r="D42" s="28">
         <f>D17*D12</f>
         <v/>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="28">
         <f>E17*E12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="C43" s="27">
+      <c r="C43" s="28">
         <f>C18*C12</f>
         <v/>
       </c>
-      <c r="D43" s="27">
+      <c r="D43" s="28">
         <f>D18*D12</f>
         <v/>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="28">
         <f>E18*E12</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f>C19*C12</f>
         <v/>
       </c>
-      <c r="D44" s="27">
+      <c r="D44" s="28">
         <f>D19*D12</f>
         <v/>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="28">
         <f>E19*E12</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="C45" s="27">
+      <c r="C45" s="28">
         <f>C20*C12</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="28">
         <f>D20*D12</f>
         <v/>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="28">
         <f>E20*E12</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="C46" s="27">
+      <c r="C46" s="28">
         <f>C13*(C16-11102600)</f>
         <v/>
       </c>
-      <c r="D46" s="27">
+      <c r="D46" s="28">
         <f>D13*(D16-11102600)</f>
         <v/>
       </c>
-      <c r="E46" s="27">
+      <c r="E46" s="28">
         <f>E13*(E16-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="C47" s="27">
+      <c r="C47" s="28">
         <f>C13*(C17-C16)</f>
         <v/>
       </c>
-      <c r="D47" s="27">
+      <c r="D47" s="28">
         <f>D13*(D17-D16)</f>
         <v/>
       </c>
-      <c r="E47" s="27">
+      <c r="E47" s="28">
         <f>E13*(E17-E16)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="28">
         <f>C13*(C18-C17)</f>
         <v/>
       </c>
-      <c r="D48" s="27">
+      <c r="D48" s="28">
         <f>D13*(D18-D17)</f>
         <v/>
       </c>
-      <c r="E48" s="27">
+      <c r="E48" s="28">
         <f>E13*(E18-E17)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="C49" s="27">
+      <c r="C49" s="28">
         <f>C13*(C19-C18)</f>
         <v/>
       </c>
-      <c r="D49" s="27">
+      <c r="D49" s="28">
         <f>D13*(D19-D18)</f>
         <v/>
       </c>
-      <c r="E49" s="27">
+      <c r="E49" s="28">
         <f>E13*(E19-E18)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="C50" s="27">
+      <c r="C50" s="28">
         <f>C13*(C20-C19)</f>
         <v/>
       </c>
-      <c r="D50" s="27">
+      <c r="D50" s="28">
         <f>D13*(D20-D19)</f>
         <v/>
       </c>
-      <c r="E50" s="27">
+      <c r="E50" s="28">
         <f>E13*(E20-E19)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
+      <c r="A51" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C51" s="27">
+      <c r="C51" s="28">
         <f>C31+C36-C41-C46</f>
         <v/>
       </c>
-      <c r="D51" s="27">
+      <c r="D51" s="28">
         <f>D31+D36-D41-D46</f>
         <v/>
       </c>
-      <c r="E51" s="27">
+      <c r="E51" s="28">
         <f>E31+E36-E41-E46</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C52" s="27">
+      <c r="C52" s="28">
         <f>C32+C37-C42-C47</f>
         <v/>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="28">
         <f>D32+D37-D42-D47</f>
         <v/>
       </c>
-      <c r="E52" s="27">
+      <c r="E52" s="28">
         <f>E32+E37-E42-E47</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C53" s="27">
+      <c r="C53" s="28">
         <f>C33+C38-C43-C48</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="28">
         <f>D33+D38-D43-D48</f>
         <v/>
       </c>
-      <c r="E53" s="27">
+      <c r="E53" s="28">
         <f>E33+E38-E43-E48</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C54" s="27">
+      <c r="C54" s="28">
         <f>C34+C39-C44-C49</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>D34+D39-D44-D49</f>
         <v/>
       </c>
-      <c r="E54" s="27">
+      <c r="E54" s="28">
         <f>E34+E39-E44-E49</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C55" s="27">
+      <c r="C55" s="28">
         <f>C35+C40-C45-C50</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>D35+D40-D45-D50</f>
         <v/>
       </c>
-      <c r="E55" s="27">
+      <c r="E55" s="28">
         <f>E35+E40-E45-E50</f>
         <v/>
       </c>
@@ -2215,34 +2291,34 @@
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="30">
         <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
         <v/>
       </c>
-      <c r="D57" s="29">
+      <c r="D57" s="30">
         <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
         <v/>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="30">
         <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+      <c r="A58" s="31" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="32">
         <f>(C57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="33">
         <f>(D57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="32">
         <f>(E57+1807202-0)/111380</f>
         <v/>
       </c>
@@ -2253,15 +2329,15 @@
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <f>C58/100.0-1</f>
         <v/>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <f>D58/100.0-1</f>
         <v/>
       </c>
-      <c r="E59" s="33">
+      <c r="E59" s="34">
         <f>E58/100.0-1</f>
         <v/>
       </c>
@@ -2284,7 +2360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2296,6 +2372,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2313,54 +2390,59 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="34" t="inlineStr">
+      <c r="C2" s="35" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="35" t="inlineStr">
+      <c r="D2" s="36" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="35" t="inlineStr">
+      <c r="E2" s="36" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="35" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="35" t="inlineStr">
+      <c r="G2" s="36" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="35" t="inlineStr">
+      <c r="H2" s="36" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="I2" s="36" t="inlineStr">
+      <c r="I2" s="37" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
+      <c r="J2" s="38" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
-      <c r="C3" s="38" t="inlineStr">
+      <c r="C3" s="40" t="inlineStr">
         <is>
           <t>10-K source</t>
         </is>
       </c>
-      <c r="I3" s="39" t="inlineStr">
+      <c r="I3" s="41" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2372,30 +2454,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="C5" s="42" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="43">
         <f>Scenarios!D16</f>
         <v/>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="43">
         <f>Scenarios!D17</f>
         <v/>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="43">
         <f>Scenarios!D18</f>
         <v/>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="43">
         <f>Scenarios!D19</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="43">
         <f>Scenarios!D20</f>
         <v/>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="44">
         <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2406,23 +2488,23 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="45">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="45">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="45">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="45">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="45">
         <f>H5/G5-1</f>
         <v/>
       </c>
@@ -2433,27 +2515,27 @@
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="45">
         <f>Scenarios!D21</f>
         <v/>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="45">
         <f>Scenarios!D22</f>
         <v/>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="45">
         <f>Scenarios!D23</f>
         <v/>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="45">
         <f>Scenarios!D24</f>
         <v/>
       </c>
-      <c r="H7" s="43">
+      <c r="H7" s="45">
         <f>Scenarios!D25</f>
         <v/>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="44">
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2464,30 +2546,30 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="46" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="30">
         <f>Scenarios!D26</f>
         <v/>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <f>Scenarios!D27</f>
         <v/>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>Scenarios!D28</f>
         <v/>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="30">
         <f>Scenarios!D29</f>
         <v/>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <f>Scenarios!D30</f>
         <v/>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="47">
         <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2498,23 +2580,23 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="43">
         <f>-Scenarios!D26*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="43">
         <f>-Scenarios!D27*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="43">
         <f>-Scenarios!D28*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="43">
         <f>-Scenarios!D29*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="43">
         <f>-Scenarios!D30*Scenarios!$D$10</f>
         <v/>
       </c>
@@ -2525,27 +2607,27 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>Scenarios!D31</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>Scenarios!D32</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>Scenarios!D33</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>Scenarios!D34</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>Scenarios!D35</f>
         <v/>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="47">
         <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2576,6 +2658,11 @@
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
+      <c r="J11" s="48" t="inlineStr">
+        <is>
+          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -2583,27 +2670,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="43">
         <f>Scenarios!D36</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="43">
         <f>Scenarios!D37</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="43">
         <f>Scenarios!D38</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="43">
         <f>Scenarios!D39</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="43">
         <f>Scenarios!D40</f>
         <v/>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="44">
         <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2634,6 +2721,11 @@
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
+      <c r="J13" s="48" t="inlineStr">
+        <is>
+          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
@@ -2641,27 +2733,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="43">
         <f>-Scenarios!D41</f>
         <v/>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="43">
         <f>-Scenarios!D42</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="43">
         <f>-Scenarios!D43</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="43">
         <f>-Scenarios!D44</f>
         <v/>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="43">
         <f>-Scenarios!D45</f>
         <v/>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="44">
         <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2692,702 +2784,721 @@
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
+      <c r="J15" s="48" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Less: increase in net working capital</t>
-        </is>
-      </c>
-      <c r="D16" s="41">
+          <t>(Increase)/decrease in net working capital</t>
+        </is>
+      </c>
+      <c r="D16" s="43">
         <f>-Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="43">
         <f>-Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="43">
         <f>-Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="43">
         <f>-Scenarios!D49</f>
         <v/>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="43">
         <f>-Scenarios!D50</f>
         <v/>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="44">
         <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D17" s="46">
+      <c r="D18" s="49">
         <f>Scenarios!D51</f>
         <v/>
       </c>
-      <c r="E17" s="46">
+      <c r="E18" s="49">
         <f>Scenarios!D52</f>
         <v/>
       </c>
-      <c r="F17" s="46">
+      <c r="F18" s="49">
         <f>Scenarios!D53</f>
         <v/>
       </c>
-      <c r="G17" s="46">
+      <c r="G18" s="49">
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H17" s="46">
+      <c r="H18" s="49">
         <f>Scenarios!D55</f>
         <v/>
       </c>
-      <c r="I17" s="45">
-        <f>IF(MAX(ABS(D17-Scenarios!$D$51),ABS(E17-Scenarios!$D$52),ABS(F17-Scenarios!$D$53),ABS(G17-Scenarios!$D$54),ABS(H17-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Discount period (years)</t>
-        </is>
-      </c>
-      <c r="D18" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G18" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="H18" s="47" t="n">
-        <v>5</v>
+      <c r="I18" s="47">
+        <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="D19" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" s="50" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D19" s="48">
-        <f>1/(1+Scenarios!$D$8)^D18</f>
-        <v/>
-      </c>
-      <c r="E19" s="48">
-        <f>1/(1+Scenarios!$D$8)^E18</f>
-        <v/>
-      </c>
-      <c r="F19" s="48">
-        <f>1/(1+Scenarios!$D$8)^F18</f>
-        <v/>
-      </c>
-      <c r="G19" s="48">
-        <f>1/(1+Scenarios!$D$8)^G18</f>
-        <v/>
-      </c>
-      <c r="H19" s="48">
-        <f>1/(1+Scenarios!$D$8)^H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="D20" s="51">
+        <f>1/(1+Scenarios!$D$8)^D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="51">
+        <f>1/(1+Scenarios!$D$8)^E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="51">
+        <f>1/(1+Scenarios!$D$8)^F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="51">
+        <f>1/(1+Scenarios!$D$8)^G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="51">
+        <f>1/(1+Scenarios!$D$8)^H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D20" s="29">
-        <f>D17*D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="29">
-        <f>E17*E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="29">
-        <f>F17*F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="29">
-        <f>G17*G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="29">
-        <f>H17*H19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="D21" s="30">
+        <f>D18*D20</f>
+        <v/>
+      </c>
+      <c r="E21" s="30">
+        <f>E18*E20</f>
+        <v/>
+      </c>
+      <c r="F21" s="30">
+        <f>F18*F20</f>
+        <v/>
+      </c>
+      <c r="G21" s="30">
+        <f>G18*G20</f>
+        <v/>
+      </c>
+      <c r="H21" s="30">
+        <f>H18*H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
         <is>
           <t>Scenarios linkage summary (column I should all read OK)</t>
         </is>
       </c>
-      <c r="I22" s="50">
-        <f>IF(COUNTIF(I5:I17,"CHECK")=0,"ALL OK","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="51" t="inlineStr">
+      <c r="I23" s="52">
+        <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="53" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C24" s="52">
-        <f>SUM(D20:H20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="C25" s="54">
+        <f>SUM(D21:H21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C25" s="43">
+      <c r="C26" s="45">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="30">
         <f>H8+H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="C27" s="41">
-        <f>H17*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
         <is>
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="C28" s="43">
+        <f>H18*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C28" s="53">
-        <f>C27/C26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="C29" s="52">
-        <f>C27/(1+Scenarios!$D$8)^H18</f>
+      <c r="C29" s="55">
+        <f>C28/C27</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="C30" s="54">
+        <f>C28/(1+Scenarios!$D$8)^H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C30" s="29">
-        <f>C24+C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C31" s="40" t="n">
-        <v>1807202</v>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
+      <c r="C31" s="30">
+        <f>C25+C30</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="15" t="inlineStr">
         <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="n">
+        <v>1807202</v>
+      </c>
+      <c r="D32" s="56" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C32" s="40" t="n">
+      <c r="C33" s="42" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="54" t="inlineStr">
+      <c r="D33" s="56" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C33" s="29">
-        <f>C30+C31+C32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="C34" s="30">
+        <f>C31+C32+C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C34" s="40" t="n">
+      <c r="C35" s="42" t="n">
         <v>111380</v>
       </c>
-      <c r="D34" s="54" t="inlineStr">
+      <c r="D35" s="56" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="19" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C35" s="55">
-        <f>C33/C34</f>
-        <v/>
-      </c>
-      <c r="I35" s="45">
-        <f>IF(ABS(C35-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="C36" s="57">
+        <f>C34/C35</f>
+        <v/>
+      </c>
+      <c r="I36" s="47">
+        <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C36" s="56" t="n">
+      <c r="C37" s="58" t="n">
         <v>100</v>
       </c>
-      <c r="D36" s="54" t="inlineStr">
+      <c r="D37" s="56" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="19" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C37" s="57">
-        <f>C35/C36-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="C38" s="59">
+        <f>C36/C37-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C38" s="43">
-        <f>C29/C30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="51" t="inlineStr">
+      <c r="C39" s="45">
+        <f>C30/C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="53" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="49" t="inlineStr">
+      <c r="B41" s="13" t="n"/>
+      <c r="C41" s="13" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
-        </is>
-      </c>
-      <c r="C42" s="58" t="n">
-        <v>8</v>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>Base-case terminal multiple; see Comps → Exit Multiple Build</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>Terminal value = Terminal EBITDA × exit multiple</t>
-        </is>
-      </c>
-      <c r="C43" s="41">
-        <f>C26*C42</f>
-        <v/>
+          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; above trough, below premium peers, roughly one turn above Gordon-implied multiple.</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
+          <t>Terminal value = Terminal EBITDA × exit multiple</t>
+        </is>
+      </c>
+      <c r="C44" s="43">
+        <f>C27*C43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C44" s="41">
-        <f>C43/(1+Scenarios!$D$8)^H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="19" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="C45" s="29">
-        <f>C24+C44</f>
+      <c r="C45" s="43">
+        <f>C44/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="C46" s="30">
+        <f>C25+C45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C46" s="59">
-        <f>(C45+C31+C32)/C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="51" t="inlineStr">
+      <c r="C47" s="61">
+        <f>(C46+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="53" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="60" t="inlineStr"/>
-      <c r="B49" s="61" t="inlineStr">
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="inlineStr"/>
+      <c r="B50" s="63" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C49" s="61" t="inlineStr">
+      <c r="C50" s="63" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D49" s="61" t="inlineStr">
+      <c r="D50" s="63" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="19" t="inlineStr">
-        <is>
-          <t>Terminal value ($)</t>
-        </is>
-      </c>
-      <c r="B50" s="52">
-        <f>C27</f>
-        <v/>
-      </c>
-      <c r="C50" s="52">
-        <f>C43</f>
-        <v/>
-      </c>
-      <c r="D50" s="52">
-        <f>B50-C50</f>
-        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
+          <t>Terminal value ($)</t>
+        </is>
+      </c>
+      <c r="B51" s="54">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="C51" s="54">
+        <f>C44</f>
+        <v/>
+      </c>
+      <c r="D51" s="54">
+        <f>B51-C51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="19" t="inlineStr">
+        <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B51" s="62">
-        <f>C28</f>
-        <v/>
-      </c>
-      <c r="C51" s="62">
-        <f>C42</f>
-        <v/>
-      </c>
-      <c r="D51" s="62">
-        <f>B51-C51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="B52" s="64">
+        <f>C29</f>
+        <v/>
+      </c>
+      <c r="C52" s="64">
+        <f>C43</f>
+        <v/>
+      </c>
+      <c r="D52" s="64">
+        <f>B52-C52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B52" s="43" t="inlineStr"/>
-      <c r="C52" s="43" t="inlineStr"/>
-      <c r="D52" s="43">
-        <f>(B50-C50)/B50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="19" t="inlineStr">
+      <c r="B53" s="45" t="inlineStr"/>
+      <c r="C53" s="45" t="inlineStr"/>
+      <c r="D53" s="45">
+        <f>(B51-C51)/B51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B53" s="63">
-        <f>C35</f>
-        <v/>
-      </c>
-      <c r="C53" s="63">
-        <f>C46</f>
-        <v/>
-      </c>
-      <c r="D53" s="63">
-        <f>B53-C53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="64" t="inlineStr">
+      <c r="B54" s="65">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="C54" s="65">
+        <f>C47</f>
+        <v/>
+      </c>
+      <c r="D54" s="65">
+        <f>B54-C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B54" s="65">
-        <f>IF(ABS(D51)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C54" s="66">
-        <f>TEXT(D51,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D54" s="17" t="inlineStr">
+      <c r="B55" s="67">
+        <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C55" s="68">
+        <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D55" s="17" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="51" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="53" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n"/>
-      <c r="C57" s="13" t="n"/>
-      <c r="D57" s="13" t="n"/>
-      <c r="E57" s="13" t="n"/>
-      <c r="F57" s="13" t="n"/>
-      <c r="G57" s="13" t="n"/>
-      <c r="H57" s="13" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="67" t="inlineStr">
+      <c r="B58" s="13" t="n"/>
+      <c r="C58" s="13" t="n"/>
+      <c r="D58" s="13" t="n"/>
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="13" t="n"/>
+      <c r="G58" s="13" t="n"/>
+      <c r="H58" s="13" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="69" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D58" s="68" t="n">
+      <c r="D59" s="70" t="n">
         <v>0.015</v>
       </c>
-      <c r="E58" s="68" t="n">
+      <c r="E59" s="70" t="n">
         <v>0.02</v>
       </c>
-      <c r="F58" s="68" t="n">
+      <c r="F59" s="70" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G58" s="68" t="n">
+      <c r="G59" s="70" t="n">
         <v>0.025</v>
       </c>
-      <c r="H58" s="68" t="n">
+      <c r="H59" s="70" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="68" t="n">
+    <row r="60">
+      <c r="A60" s="70" t="n">
         <v>0.09</v>
       </c>
-      <c r="D59" s="69">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="E59" s="69">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="F59" s="69">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="G59" s="69">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="H59" s="69">
-        <f>(NPV(0.09,D17:H17)+(H17*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="68" t="n">
+      <c r="D60" s="71">
+        <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="E60" s="71">
+        <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="F60" s="71">
+        <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="G60" s="71">
+        <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="H60" s="71">
+        <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="70" t="n">
         <v>0.095</v>
       </c>
-      <c r="D60" s="69">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="E60" s="69">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="F60" s="69">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="G60" s="69">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="H60" s="69">
-        <f>(NPV(0.095,D17:H17)+(H17*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="68" t="n">
+      <c r="D61" s="71">
+        <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="E61" s="71">
+        <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="F61" s="71">
+        <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="G61" s="71">
+        <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="H61" s="71">
+        <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="70" t="n">
         <v>0.1</v>
       </c>
-      <c r="D61" s="69">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="E61" s="69">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="F61" s="70">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="G61" s="69">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="H61" s="69">
-        <f>(NPV(0.1,D17:H17)+(H17*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="68" t="n">
+      <c r="D62" s="71">
+        <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="E62" s="71">
+        <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="F62" s="72">
+        <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="G62" s="71">
+        <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="H62" s="71">
+        <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="70" t="n">
         <v>0.105</v>
       </c>
-      <c r="D62" s="69">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="E62" s="69">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="F62" s="69">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="G62" s="69">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="H62" s="69">
-        <f>(NPV(0.105,D17:H17)+(H17*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="68" t="n">
+      <c r="D63" s="71">
+        <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="E63" s="71">
+        <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="F63" s="71">
+        <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="G63" s="71">
+        <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="H63" s="71">
+        <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="70" t="n">
         <v>0.11</v>
       </c>
-      <c r="D63" s="69">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="E63" s="69">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="F63" s="69">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="G63" s="69">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C31+C32)/C34</f>
-        <v/>
-      </c>
-      <c r="H63" s="69">
-        <f>(NPV(0.11,D17:H17)+(H17*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C31+C32)/C34</f>
-        <v/>
+      <c r="D64" s="71">
+        <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="E64" s="71">
+        <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="F64" s="71">
+        <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="G64" s="71">
+        <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+      <c r="H64" s="71">
+        <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3395,14 +3506,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D34" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D36" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3414,7 +3525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3423,6 +3534,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -3450,10 +3562,10 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="40" t="n">
+      <c r="C4" s="42" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="54" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3465,7 +3577,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="43">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -3476,10 +3588,10 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="56" t="n">
+      <c r="C6" s="58" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="56" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -3491,10 +3603,10 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="40" t="n">
+      <c r="C7" s="42" t="n">
         <v>1807202</v>
       </c>
-      <c r="D7" s="54" t="inlineStr">
+      <c r="D7" s="56" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3506,10 +3618,10 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="40" t="n">
+      <c r="C8" s="42" t="n">
         <v>111380</v>
       </c>
-      <c r="D8" s="54" t="inlineStr">
+      <c r="D8" s="56" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3521,33 +3633,33 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="56" t="n">
+      <c r="C9" s="58" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="54" t="inlineStr">
+      <c r="D9" s="56" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="71">
+      <c r="C10" s="73">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="66" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="71">
+      <c r="C11" s="73">
         <f>C9/C6</f>
         <v/>
       </c>
@@ -3560,24 +3672,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="66" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C15" s="73" t="inlineStr">
+      <c r="C15" s="75" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="72" t="inlineStr">
+      <c r="D15" s="74" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -3589,7 +3701,7 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C16" s="74">
+      <c r="C16" s="76">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
@@ -3605,12 +3717,12 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C17" s="75" t="n">
+      <c r="C17" s="77" t="n">
         <v>18</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>Mature global brand; lower growth</t>
+          <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
         </is>
       </c>
     </row>
@@ -3620,12 +3732,12 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C18" s="75" t="n">
+      <c r="C18" s="77" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>Premium footwear peer; HOKA/UGG</t>
+          <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3747,12 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C19" s="75" t="n">
+      <c r="C19" s="77" t="n">
         <v>25</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>High-growth athletic peer</t>
+          <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
         </is>
       </c>
     </row>
@@ -3650,12 +3762,12 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C20" s="75" t="n">
+      <c r="C20" s="77" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
-          <t>Global incumbent; restructuring</t>
+          <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3777,12 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C21" s="75" t="n">
+      <c r="C21" s="77" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>Multi-brand apparel; challenged</t>
+          <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
         </is>
       </c>
     </row>
@@ -3687,19 +3799,19 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="53">
-        <f>DCF!C28</f>
+      <c r="C24" s="55">
+        <f>DCF!C29</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="inlineStr">
+      <c r="A25" s="66" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C25" s="62">
-        <f>DCF!C42</f>
+      <c r="C25" s="64">
+        <f>DCF!C43</f>
         <v/>
       </c>
     </row>
@@ -3709,48 +3821,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="55">
         <f>C25-C24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="inlineStr">
+      <c r="A27" s="66" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="27" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x) — assumes partial recovery from trough, not full re-rating</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>•  Above comps football-field high (7.5x on FY2025A) — terminal year has higher EBITDA &amp; normalized margins</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="26" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>•  ~1 turn above Gordon-implied exit multiple — conservative buffer vs perpetuity math</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>•  Well below historical LULU peak multiples (20–30x) — avoids heroic assumptions</t>
         </is>
@@ -3764,27 +3876,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="72" t="inlineStr">
+      <c r="A35" s="74" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C35" s="73" t="inlineStr">
+      <c r="C35" s="75" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D35" s="73" t="inlineStr">
+      <c r="D35" s="75" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E35" s="73" t="inlineStr">
+      <c r="E35" s="75" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F35" s="73" t="inlineStr">
+      <c r="F35" s="75" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -3796,19 +3908,24 @@
           <t>EV / EBITDA (FY2025A)</t>
         </is>
       </c>
-      <c r="C36" s="75" t="n">
+      <c r="C36" s="77" t="n">
         <v>4.5</v>
       </c>
-      <c r="D36" s="75" t="n">
+      <c r="D36" s="77" t="n">
         <v>7.5</v>
       </c>
-      <c r="E36" s="76">
+      <c r="E36" s="78">
         <f>(C5*C36+C7)/C8</f>
         <v/>
       </c>
-      <c r="F36" s="76">
+      <c r="F36" s="78">
         <f>(C5*D36+C7)/C8</f>
         <v/>
+      </c>
+      <c r="G36" s="79" t="inlineStr">
+        <is>
+          <t>Lo: 4.5x EV/EBITDA low case on FY2025A; distressed trough pricing near current market de-rating. Hi: 7.5x EV/EBITDA high case on FY2025A; partial recovery before terminal year, below historical peaks.</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -3817,19 +3934,24 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C37" s="75" t="n">
+      <c r="C37" s="77" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="75" t="n">
+      <c r="D37" s="77" t="n">
         <v>18</v>
       </c>
-      <c r="E37" s="76">
+      <c r="E37" s="78">
         <f>C6*C37</f>
         <v/>
       </c>
-      <c r="F37" s="76">
+      <c r="F37" s="78">
         <f>C6*D37</f>
         <v/>
+      </c>
+      <c r="G37" s="79" t="inlineStr">
+        <is>
+          <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating. Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3838,35 +3960,35 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="77" t="inlineStr">
+      <c r="C38" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="77" t="inlineStr">
+      <c r="D38" s="80" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="76">
+      <c r="E38" s="78">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F38" s="76">
+      <c r="F38" s="78">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="78" t="inlineStr">
+      <c r="A40" s="81" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="79" t="n">
+      <c r="C40" s="82" t="n">
         <v>100</v>
       </c>
-      <c r="D40" s="54" t="inlineStr">
+      <c r="D40" s="56" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -130,59 +130,6 @@
     </font>
     <font>
       <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="001F2A44"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00C8102E"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="001F2A44"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="000000CC"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="8"/>
@@ -193,6 +140,59 @@
       <color rgb="000000CC"/>
       <sz val="8"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -349,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -374,60 +374,67 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="24" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -442,7 +449,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,10 +473,7 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -482,13 +486,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="166" fontId="36" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -506,17 +510,17 @@
     <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -531,7 +535,7 @@
     <xf numFmtId="164" fontId="40" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -991,7 +995,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions / inputs</t>
+          <t>Red font  =  analyst assumptions / inputs (justification + clickable source link)</t>
         </is>
       </c>
     </row>
@@ -1068,13 +1072,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1105,7 +1110,12 @@
       </c>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>10-year UST ~4.3% as of Sep 2026; standard risk-free anchor for US equity DCF discount-rate build.</t>
+          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>FRED: 10Y Treasury (DGS10)</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1130,12 @@
       </c>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t>6.0% long-run US equity risk premium; conventional CAPM input for mature, liquid large-cap consumer brands.</t>
+          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1145,7 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="19" t="n">
         <v>0.95</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
@@ -1138,14 +1153,19 @@
           <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
         </is>
       </c>
+      <c r="E5" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU Beta</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <f>C3+C5*C4</f>
         <v/>
       </c>
@@ -1171,6 +1191,11 @@
           <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
         </is>
       </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K (no funded debt)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1186,6 +1211,11 @@
           <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
         </is>
       </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1193,7 +1223,7 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
@@ -1219,6 +1249,11 @@
           <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
         </is>
       </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
@@ -1234,19 +1269,33 @@
           <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
         </is>
       </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="22">
+      <c r="C16" s="23">
         <f>C14*C6+C15*C11</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1257,7 +1306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1265,7 +1314,8 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1280,17 +1330,17 @@
       <c r="E1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="D2" s="24" t="inlineStr">
+      <c r="D2" s="25" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E2" s="25" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1302,9 +1352,14 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="F3" s="26" t="inlineStr">
-        <is>
-          <t>Justification (base case, ~20 words)</t>
+      <c r="F3" s="27" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
+      <c r="G3" s="27" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -1328,6 +1383,11 @@
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
         </is>
       </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
@@ -1349,6 +1409,11 @@
           <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
         </is>
       </c>
+      <c r="G5" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical revenue (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
@@ -1370,6 +1435,11 @@
           <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
         </is>
       </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -1391,6 +1461,11 @@
           <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
         </is>
       </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
@@ -1412,6 +1487,11 @@
           <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
         </is>
       </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab CAPM build (this model)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
@@ -1433,6 +1513,11 @@
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
       </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>BEA: Real GDP (FRED GDPC1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
@@ -1454,6 +1539,11 @@
           <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
         </is>
       </c>
+      <c r="G10" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
@@ -1475,6 +1565,11 @@
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
       </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
@@ -1496,6 +1591,11 @@
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
       </c>
+      <c r="G12" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -1517,6 +1617,11 @@
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
       </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1526,830 +1631,841 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="30">
         <f>11102600*(1+C4)</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="30">
         <f>11102600*(1+D4)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="30">
         <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="30">
         <f>C16*(1+C5)</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="30">
         <f>D16*(1+D5)</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="30">
         <f>E16*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="30">
         <f>C17*(1+C5)</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="30">
         <f>D17*(1+D5)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="30">
         <f>E17*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="30">
         <f>C18*(1+C5)</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="30">
         <f>D18*(1+D5)</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="30">
         <f>E18*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="30">
         <f>C19*(1+C5)</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="30">
         <f>D19*(1+D5)</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="30">
         <f>E19*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="31">
         <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="31">
         <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="31">
         <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="31">
         <f>C6+(C7-C6)*1/4</f>
         <v/>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="31">
         <f>D6+(D7-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="31">
         <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C23" s="29">
+      <c r="C23" s="31">
         <f>C6+(C7-C6)*2/4</f>
         <v/>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="31">
         <f>D6+(D7-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="31">
         <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="31">
         <f>C6+(C7-C6)*3/4</f>
         <v/>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="31">
         <f>D6+(D7-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="31">
         <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="31">
         <f>C6+(C7-C6)*4/4</f>
         <v/>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="31">
         <f>D6+(D7-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="31">
         <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="30">
         <f>C16*C21</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="30">
         <f>D16*D21</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="30">
         <f>E16*E21</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="30">
         <f>C17*C22</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="30">
         <f>D17*D22</f>
         <v/>
       </c>
-      <c r="E27" s="28">
+      <c r="E27" s="30">
         <f>E17*E22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="30">
         <f>C18*C23</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="30">
         <f>D18*D23</f>
         <v/>
       </c>
-      <c r="E28" s="28">
+      <c r="E28" s="30">
         <f>E18*E23</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="30">
         <f>C19*C24</f>
         <v/>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="30">
         <f>D19*D24</f>
         <v/>
       </c>
-      <c r="E29" s="28">
+      <c r="E29" s="30">
         <f>E19*E24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="30">
         <f>C20*C25</f>
         <v/>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="30">
         <f>D20*D25</f>
         <v/>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="30">
         <f>E20*E25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="30">
         <f>C26*(1-C10)</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="30">
         <f>D26*(1-D10)</f>
         <v/>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="30">
         <f>E26*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="30">
         <f>C27*(1-C10)</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="30">
         <f>D27*(1-D10)</f>
         <v/>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="30">
         <f>E27*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="30">
         <f>C28*(1-C10)</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="30">
         <f>D28*(1-D10)</f>
         <v/>
       </c>
-      <c r="E33" s="28">
+      <c r="E33" s="30">
         <f>E28*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="30">
         <f>C29*(1-C10)</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="30">
         <f>D29*(1-D10)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="30">
         <f>E29*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="27" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="30">
         <f>C30*(1-C10)</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="30">
         <f>D30*(1-D10)</f>
         <v/>
       </c>
-      <c r="E35" s="28">
+      <c r="E35" s="30">
         <f>E30*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="30">
         <f>C16*C11</f>
         <v/>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="30">
         <f>D16*D11</f>
         <v/>
       </c>
-      <c r="E36" s="28">
+      <c r="E36" s="30">
         <f>E16*E11</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="30">
         <f>C17*C11</f>
         <v/>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="30">
         <f>D17*D11</f>
         <v/>
       </c>
-      <c r="E37" s="28">
+      <c r="E37" s="30">
         <f>E17*E11</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="30">
         <f>C18*C11</f>
         <v/>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="30">
         <f>D18*D11</f>
         <v/>
       </c>
-      <c r="E38" s="28">
+      <c r="E38" s="30">
         <f>E18*E11</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="30">
         <f>C19*C11</f>
         <v/>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="30">
         <f>D19*D11</f>
         <v/>
       </c>
-      <c r="E39" s="28">
+      <c r="E39" s="30">
         <f>E19*E11</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="30">
         <f>C20*C11</f>
         <v/>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="30">
         <f>D20*D11</f>
         <v/>
       </c>
-      <c r="E40" s="28">
+      <c r="E40" s="30">
         <f>E20*E11</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="30">
         <f>C16*C12</f>
         <v/>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="30">
         <f>D16*D12</f>
         <v/>
       </c>
-      <c r="E41" s="28">
+      <c r="E41" s="30">
         <f>E16*E12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="30">
         <f>C17*C12</f>
         <v/>
       </c>
-      <c r="D42" s="28">
+      <c r="D42" s="30">
         <f>D17*D12</f>
         <v/>
       </c>
-      <c r="E42" s="28">
+      <c r="E42" s="30">
         <f>E17*E12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="30">
         <f>C18*C12</f>
         <v/>
       </c>
-      <c r="D43" s="28">
+      <c r="D43" s="30">
         <f>D18*D12</f>
         <v/>
       </c>
-      <c r="E43" s="28">
+      <c r="E43" s="30">
         <f>E18*E12</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="27" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="30">
         <f>C19*C12</f>
         <v/>
       </c>
-      <c r="D44" s="28">
+      <c r="D44" s="30">
         <f>D19*D12</f>
         <v/>
       </c>
-      <c r="E44" s="28">
+      <c r="E44" s="30">
         <f>E19*E12</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="27" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="30">
         <f>C20*C12</f>
         <v/>
       </c>
-      <c r="D45" s="28">
+      <c r="D45" s="30">
         <f>D20*D12</f>
         <v/>
       </c>
-      <c r="E45" s="28">
+      <c r="E45" s="30">
         <f>E20*E12</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="27" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="30">
         <f>C13*(C16-11102600)</f>
         <v/>
       </c>
-      <c r="D46" s="28">
+      <c r="D46" s="30">
         <f>D13*(D16-11102600)</f>
         <v/>
       </c>
-      <c r="E46" s="28">
+      <c r="E46" s="30">
         <f>E13*(E16-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="27" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="30">
         <f>C13*(C17-C16)</f>
         <v/>
       </c>
-      <c r="D47" s="28">
+      <c r="D47" s="30">
         <f>D13*(D17-D16)</f>
         <v/>
       </c>
-      <c r="E47" s="28">
+      <c r="E47" s="30">
         <f>E13*(E17-E16)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="30">
         <f>C13*(C18-C17)</f>
         <v/>
       </c>
-      <c r="D48" s="28">
+      <c r="D48" s="30">
         <f>D13*(D18-D17)</f>
         <v/>
       </c>
-      <c r="E48" s="28">
+      <c r="E48" s="30">
         <f>E13*(E18-E17)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="30">
         <f>C13*(C19-C18)</f>
         <v/>
       </c>
-      <c r="D49" s="28">
+      <c r="D49" s="30">
         <f>D13*(D19-D18)</f>
         <v/>
       </c>
-      <c r="E49" s="28">
+      <c r="E49" s="30">
         <f>E13*(E19-E18)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="C50" s="28">
+      <c r="C50" s="30">
         <f>C13*(C20-C19)</f>
         <v/>
       </c>
-      <c r="D50" s="28">
+      <c r="D50" s="30">
         <f>D13*(D20-D19)</f>
         <v/>
       </c>
-      <c r="E50" s="28">
+      <c r="E50" s="30">
         <f>E13*(E20-E19)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C51" s="28">
+      <c r="C51" s="30">
         <f>C31+C36-C41-C46</f>
         <v/>
       </c>
-      <c r="D51" s="28">
+      <c r="D51" s="30">
         <f>D31+D36-D41-D46</f>
         <v/>
       </c>
-      <c r="E51" s="28">
+      <c r="E51" s="30">
         <f>E31+E36-E41-E46</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C52" s="28">
+      <c r="C52" s="30">
         <f>C32+C37-C42-C47</f>
         <v/>
       </c>
-      <c r="D52" s="28">
+      <c r="D52" s="30">
         <f>D32+D37-D42-D47</f>
         <v/>
       </c>
-      <c r="E52" s="28">
+      <c r="E52" s="30">
         <f>E32+E37-E42-E47</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="27" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C53" s="28">
+      <c r="C53" s="30">
         <f>C33+C38-C43-C48</f>
         <v/>
       </c>
-      <c r="D53" s="28">
+      <c r="D53" s="30">
         <f>D33+D38-D43-D48</f>
         <v/>
       </c>
-      <c r="E53" s="28">
+      <c r="E53" s="30">
         <f>E33+E38-E43-E48</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="27" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C54" s="28">
+      <c r="C54" s="30">
         <f>C34+C39-C44-C49</f>
         <v/>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="30">
         <f>D34+D39-D44-D49</f>
         <v/>
       </c>
-      <c r="E54" s="28">
+      <c r="E54" s="30">
         <f>E34+E39-E44-E49</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="27" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C55" s="28">
+      <c r="C55" s="30">
         <f>C35+C40-C45-C50</f>
         <v/>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="30">
         <f>D35+D40-D45-D50</f>
         <v/>
       </c>
-      <c r="E55" s="28">
+      <c r="E55" s="30">
         <f>E35+E40-E45-E50</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="19" t="inlineStr">
+      <c r="A57" s="20" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C57" s="30">
+      <c r="C57" s="32">
         <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
         <v/>
       </c>
-      <c r="D57" s="30">
+      <c r="D57" s="32">
         <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
         <v/>
       </c>
-      <c r="E57" s="30">
+      <c r="E57" s="32">
         <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="33" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="34">
         <f>(C57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D58" s="33">
+      <c r="D58" s="35">
         <f>(D57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="34">
         <f>(E57+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="19" t="inlineStr">
+      <c r="A59" s="20" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="34">
+      <c r="C59" s="36">
         <f>C58/100.0-1</f>
         <v/>
       </c>
-      <c r="D59" s="34">
+      <c r="D59" s="36">
         <f>D58/100.0-1</f>
         <v/>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="36">
         <f>E58/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2360,7 +2476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2372,7 +2488,8 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2390,59 +2507,64 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="35" t="inlineStr">
+      <c r="C2" s="38" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="36" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="36" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="36" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="36" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="36" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="I2" s="37" t="inlineStr">
+      <c r="I2" s="40" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="J2" s="38" t="inlineStr">
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
+      <c r="K2" s="41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
-      <c r="C3" s="40" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>10-K source</t>
         </is>
       </c>
-      <c r="I3" s="41" t="inlineStr">
+      <c r="I3" s="44" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2454,30 +2576,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="45" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="46">
         <f>Scenarios!D16</f>
         <v/>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="46">
         <f>Scenarios!D17</f>
         <v/>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="46">
         <f>Scenarios!D18</f>
         <v/>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="46">
         <f>Scenarios!D19</f>
         <v/>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="46">
         <f>Scenarios!D20</f>
         <v/>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="47">
         <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2488,23 +2610,23 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="45">
+      <c r="D6" s="48">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="45">
+      <c r="E6" s="48">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="48">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="48">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="48">
         <f>H5/G5-1</f>
         <v/>
       </c>
@@ -2515,61 +2637,61 @@
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="45">
+      <c r="D7" s="48">
         <f>Scenarios!D21</f>
         <v/>
       </c>
-      <c r="E7" s="45">
+      <c r="E7" s="48">
         <f>Scenarios!D22</f>
         <v/>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="48">
         <f>Scenarios!D23</f>
         <v/>
       </c>
-      <c r="G7" s="45">
+      <c r="G7" s="48">
         <f>Scenarios!D24</f>
         <v/>
       </c>
-      <c r="H7" s="45">
+      <c r="H7" s="48">
         <f>Scenarios!D25</f>
         <v/>
       </c>
-      <c r="I7" s="44">
+      <c r="I7" s="47">
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="49" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="32">
         <f>Scenarios!D26</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="32">
         <f>Scenarios!D27</f>
         <v/>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="32">
         <f>Scenarios!D28</f>
         <v/>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="32">
         <f>Scenarios!D29</f>
         <v/>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="32">
         <f>Scenarios!D30</f>
         <v/>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="50">
         <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2580,54 +2702,54 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="46">
         <f>-Scenarios!D26*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="46">
         <f>-Scenarios!D27*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="46">
         <f>-Scenarios!D28*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="46">
         <f>-Scenarios!D29*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="H9" s="43">
+      <c r="H9" s="46">
         <f>-Scenarios!D30*Scenarios!$D$10</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="32">
         <f>Scenarios!D31</f>
         <v/>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="32">
         <f>Scenarios!D32</f>
         <v/>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="32">
         <f>Scenarios!D33</f>
         <v/>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="32">
         <f>Scenarios!D34</f>
         <v/>
       </c>
-      <c r="H10" s="30">
+      <c r="H10" s="32">
         <f>Scenarios!D35</f>
         <v/>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="50">
         <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2658,9 +2780,14 @@
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="48" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
+      </c>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -2670,27 +2797,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="46">
         <f>Scenarios!D36</f>
         <v/>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="46">
         <f>Scenarios!D37</f>
         <v/>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="46">
         <f>Scenarios!D38</f>
         <v/>
       </c>
-      <c r="G12" s="43">
+      <c r="G12" s="46">
         <f>Scenarios!D39</f>
         <v/>
       </c>
-      <c r="H12" s="43">
+      <c r="H12" s="46">
         <f>Scenarios!D40</f>
         <v/>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="47">
         <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2721,9 +2848,14 @@
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="J13" s="48" t="inlineStr">
+      <c r="J13" s="17" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
+      </c>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -2733,27 +2865,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="46">
         <f>-Scenarios!D41</f>
         <v/>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="46">
         <f>-Scenarios!D42</f>
         <v/>
       </c>
-      <c r="F14" s="43">
+      <c r="F14" s="46">
         <f>-Scenarios!D43</f>
         <v/>
       </c>
-      <c r="G14" s="43">
+      <c r="G14" s="46">
         <f>-Scenarios!D44</f>
         <v/>
       </c>
-      <c r="H14" s="43">
+      <c r="H14" s="46">
         <f>-Scenarios!D45</f>
         <v/>
       </c>
-      <c r="I14" s="44">
+      <c r="I14" s="47">
         <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2784,9 +2916,14 @@
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="J15" s="48" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
+      </c>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
     </row>
@@ -2796,65 +2933,65 @@
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="46">
         <f>-Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="46">
         <f>-Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F16" s="43">
+      <c r="F16" s="46">
         <f>-Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G16" s="43">
+      <c r="G16" s="46">
         <f>-Scenarios!D49</f>
         <v/>
       </c>
-      <c r="H16" s="43">
+      <c r="H16" s="46">
         <f>-Scenarios!D50</f>
         <v/>
       </c>
-      <c r="I16" s="44">
+      <c r="I16" s="47">
         <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D18" s="49">
+      <c r="D18" s="51">
         <f>Scenarios!D51</f>
         <v/>
       </c>
-      <c r="E18" s="49">
+      <c r="E18" s="51">
         <f>Scenarios!D52</f>
         <v/>
       </c>
-      <c r="F18" s="49">
+      <c r="F18" s="51">
         <f>Scenarios!D53</f>
         <v/>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="51">
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H18" s="49">
+      <c r="H18" s="51">
         <f>Scenarios!D55</f>
         <v/>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="50">
         <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2865,19 +3002,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D19" s="50" t="n">
+      <c r="D19" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="50" t="n">
+      <c r="E19" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="50" t="n">
+      <c r="F19" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="50" t="n">
+      <c r="G19" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="50" t="n">
+      <c r="H19" s="52" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2887,67 +3024,67 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="53">
         <f>1/(1+Scenarios!$D$8)^D19</f>
         <v/>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="53">
         <f>1/(1+Scenarios!$D$8)^E19</f>
         <v/>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="53">
         <f>1/(1+Scenarios!$D$8)^F19</f>
         <v/>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="53">
         <f>1/(1+Scenarios!$D$8)^G19</f>
         <v/>
       </c>
-      <c r="H20" s="51">
+      <c r="H20" s="53">
         <f>1/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="32">
         <f>D18*D20</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="32">
         <f>E18*E20</f>
         <v/>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="32">
         <f>F18*F20</f>
         <v/>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="32">
         <f>G18*G20</f>
         <v/>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="32">
         <f>H18*H20</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Scenarios linkage summary (column I should all read OK)</t>
         </is>
       </c>
-      <c r="I23" s="52">
+      <c r="I23" s="54">
         <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -2956,12 +3093,12 @@
       <c r="C24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C25" s="54">
+      <c r="C25" s="56">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
@@ -2972,18 +3109,18 @@
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C26" s="45">
+      <c r="C26" s="48">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="32">
         <f>H8+H12</f>
         <v/>
       </c>
@@ -2994,7 +3131,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="C28" s="43">
+      <c r="C28" s="46">
         <f>H18*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
@@ -3005,29 +3142,29 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="57">
         <f>C28/C27</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C30" s="54">
+      <c r="C30" s="56">
         <f>C28/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="32">
         <f>C25+C30</f>
         <v/>
       </c>
@@ -3038,10 +3175,10 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n">
+      <c r="C32" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D32" s="56" t="inlineStr">
+      <c r="D32" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3053,22 +3190,22 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n">
+      <c r="C33" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="56" t="inlineStr">
+      <c r="D33" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="32">
         <f>C31+C32+C33</f>
         <v/>
       </c>
@@ -3079,26 +3216,26 @@
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C35" s="42" t="n">
+      <c r="C35" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D35" s="56" t="inlineStr">
+      <c r="D35" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C36" s="57">
+      <c r="C36" s="59">
         <f>C34/C35</f>
         <v/>
       </c>
-      <c r="I36" s="47">
+      <c r="I36" s="50">
         <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3109,22 +3246,22 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C37" s="58" t="n">
+      <c r="C37" s="60" t="n">
         <v>100</v>
       </c>
-      <c r="D37" s="56" t="inlineStr">
+      <c r="D37" s="58" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="19" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="61">
         <f>C36/C37-1</f>
         <v/>
       </c>
@@ -3135,13 +3272,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C39" s="45">
+      <c r="C39" s="48">
         <f>C30/C31</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="53" t="inlineStr">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3150,7 +3287,7 @@
       <c r="C41" s="13" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
         </is>
@@ -3162,12 +3299,17 @@
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C43" s="60" t="n">
+      <c r="C43" s="62" t="n">
         <v>8</v>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
           <t>8.0x FY2030E exit EV/EBITDA; above trough, below premium peers, roughly one turn above Gordon-implied multiple.</t>
+        </is>
+      </c>
+      <c r="E43" s="28" t="inlineStr">
+        <is>
+          <t>DCF Comps tab: Exit Multiple Build</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3319,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="C44" s="43">
+      <c r="C44" s="46">
         <f>C27*C43</f>
         <v/>
       </c>
@@ -3188,35 +3330,35 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C45" s="43">
+      <c r="C45" s="46">
         <f>C44/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="19" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="32">
         <f>C25+C45</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="19" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="61">
+      <c r="C47" s="63">
         <f>(C46+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="53" t="inlineStr">
+      <c r="A49" s="55" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3226,57 +3368,57 @@
       <c r="D49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="62" t="inlineStr"/>
-      <c r="B50" s="63" t="inlineStr">
+      <c r="A50" s="64" t="inlineStr"/>
+      <c r="B50" s="65" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="63" t="inlineStr">
+      <c r="C50" s="65" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="63" t="inlineStr">
+      <c r="D50" s="65" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="19" t="inlineStr">
+      <c r="A51" s="20" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="54">
+      <c r="B51" s="56">
         <f>C28</f>
         <v/>
       </c>
-      <c r="C51" s="54">
+      <c r="C51" s="56">
         <f>C44</f>
         <v/>
       </c>
-      <c r="D51" s="54">
+      <c r="D51" s="56">
         <f>B51-C51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="19" t="inlineStr">
+      <c r="A52" s="20" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B52" s="64">
+      <c r="B52" s="66">
         <f>C29</f>
         <v/>
       </c>
-      <c r="C52" s="64">
+      <c r="C52" s="66">
         <f>C43</f>
         <v/>
       </c>
-      <c r="D52" s="64">
+      <c r="D52" s="66">
         <f>B52-C52</f>
         <v/>
       </c>
@@ -3287,54 +3429,54 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B53" s="45" t="inlineStr"/>
-      <c r="C53" s="45" t="inlineStr"/>
-      <c r="D53" s="45">
+      <c r="B53" s="48" t="inlineStr"/>
+      <c r="C53" s="48" t="inlineStr"/>
+      <c r="D53" s="48">
         <f>(B51-C51)/B51</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="19" t="inlineStr">
+      <c r="A54" s="20" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="65">
+      <c r="B54" s="67">
         <f>C36</f>
         <v/>
       </c>
-      <c r="C54" s="65">
+      <c r="C54" s="67">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D54" s="65">
+      <c r="D54" s="67">
         <f>B54-C54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="66" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="67">
+      <c r="B55" s="69">
         <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C55" s="68">
+      <c r="C55" s="70">
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D55" s="17" t="inlineStr">
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="53" t="inlineStr">
+      <c r="A58" s="55" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -3348,156 +3490,161 @@
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="69" t="inlineStr">
+      <c r="A59" s="71" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="70" t="n">
+      <c r="D59" s="72" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="70" t="n">
+      <c r="E59" s="72" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="70" t="n">
+      <c r="F59" s="72" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="70" t="n">
+      <c r="G59" s="72" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="70" t="n">
+      <c r="H59" s="72" t="n">
         <v>0.03</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="70" t="n">
+      <c r="A60" s="72" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="71">
+      <c r="D60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E60" s="71">
+      <c r="E60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F60" s="71">
+      <c r="F60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G60" s="71">
+      <c r="G60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H60" s="71">
+      <c r="H60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="70" t="n">
+      <c r="A61" s="72" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="71">
+      <c r="D61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E61" s="71">
+      <c r="E61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F61" s="71">
+      <c r="F61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G61" s="71">
+      <c r="G61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H61" s="71">
+      <c r="H61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="70" t="n">
+      <c r="A62" s="72" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="71">
+      <c r="D62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E62" s="71">
+      <c r="E62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F62" s="72">
+      <c r="F62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G62" s="71">
+      <c r="G62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H62" s="71">
+      <c r="H62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="70" t="n">
+      <c r="A63" s="72" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="71">
+      <c r="D63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E63" s="71">
+      <c r="E63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F63" s="71">
+      <c r="F63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G63" s="71">
+      <c r="G63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H63" s="71">
+      <c r="H63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="70" t="n">
+      <c r="A64" s="72" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="71">
+      <c r="D64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E64" s="71">
+      <c r="E64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F64" s="71">
+      <c r="F64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G64" s="71">
+      <c r="G64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H64" s="71">
+      <c r="H64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="J65" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
+        </is>
+      </c>
+      <c r="K65" s="28" t="inlineStr">
+        <is>
+          <t>Base WACC/g from Scenarios tab</t>
         </is>
       </c>
     </row>
@@ -3506,14 +3653,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3525,16 +3675,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -3562,10 +3714,10 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C4" s="45" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3577,7 +3729,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="46">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -3588,10 +3740,10 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="58" t="n">
+      <c r="C6" s="60" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D6" s="56" t="inlineStr">
+      <c r="D6" s="58" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -3603,10 +3755,10 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D7" s="56" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3618,10 +3770,10 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D8" s="56" t="inlineStr">
+      <c r="D8" s="58" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3633,33 +3785,33 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="58" t="n">
+      <c r="C9" s="60" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="56" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="68" t="inlineStr">
+      <c r="A10" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="75">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="68" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="75">
         <f>C9/C6</f>
         <v/>
       </c>
@@ -3672,26 +3824,31 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="68" t="inlineStr">
+      <c r="A14" s="70" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="74" t="inlineStr">
+      <c r="A15" s="76" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C15" s="75" t="inlineStr">
+      <c r="C15" s="77" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="74" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="D15" s="76" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="E15" s="76" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -3701,13 +3858,18 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C16" s="76">
+      <c r="C16" s="78">
         <f>(C9*C8-C7)/C5</f>
         <v/>
       </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>Distressed trough; FY2025A EBITDA</t>
+      <c r="D16" s="37" t="inlineStr">
+        <is>
+          <t>Distressed trough multiple on FY2025A EBITDA</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K</t>
         </is>
       </c>
     </row>
@@ -3717,12 +3879,17 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C17" s="77" t="n">
+      <c r="C17" s="79" t="n">
         <v>18</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
+        </is>
+      </c>
+      <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE statistics</t>
         </is>
       </c>
     </row>
@@ -3732,12 +3899,17 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C18" s="77" t="n">
+      <c r="C18" s="79" t="n">
         <v>15</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
           <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
+        </is>
+      </c>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: DECK statistics</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3919,17 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C19" s="77" t="n">
+      <c r="C19" s="79" t="n">
         <v>25</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
           <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: ONON statistics</t>
         </is>
       </c>
     </row>
@@ -3762,12 +3939,17 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C20" s="77" t="n">
+      <c r="C20" s="79" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
           <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: ADS.DE statistics</t>
         </is>
       </c>
     </row>
@@ -3777,12 +3959,17 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C21" s="77" t="n">
+      <c r="C21" s="79" t="n">
         <v>10</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
           <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: VFC statistics</t>
         </is>
       </c>
     </row>
@@ -3799,18 +3986,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="57">
         <f>DCF!C29</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="66" t="inlineStr">
+      <c r="A25" s="68" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C25" s="64">
+      <c r="C25" s="66">
         <f>DCF!C43</f>
         <v/>
       </c>
@@ -3821,48 +4008,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="57">
         <f>C25-C24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="66" t="inlineStr">
+      <c r="A27" s="68" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x) — assumes partial recovery from trough, not full re-rating</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>•  Above comps football-field high (7.5x on FY2025A) — terminal year has higher EBITDA &amp; normalized margins</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>•  ~1 turn above Gordon-implied exit multiple — conservative buffer vs perpetuity math</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>•  Well below historical LULU peak multiples (20–30x) — avoids heroic assumptions</t>
         </is>
@@ -3876,27 +4063,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="74" t="inlineStr">
+      <c r="A35" s="76" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C35" s="75" t="inlineStr">
+      <c r="C35" s="77" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D35" s="75" t="inlineStr">
+      <c r="D35" s="77" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E35" s="75" t="inlineStr">
+      <c r="E35" s="77" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F35" s="75" t="inlineStr">
+      <c r="F35" s="77" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -3908,23 +4095,38 @@
           <t>EV / EBITDA (FY2025A)</t>
         </is>
       </c>
-      <c r="C36" s="77" t="n">
+      <c r="C36" s="79" t="n">
         <v>4.5</v>
       </c>
-      <c r="D36" s="77" t="n">
+      <c r="D36" s="79" t="n">
         <v>7.5</v>
       </c>
-      <c r="E36" s="78">
+      <c r="E36" s="80">
         <f>(C5*C36+C7)/C8</f>
         <v/>
       </c>
-      <c r="F36" s="78">
+      <c r="F36" s="80">
         <f>(C5*D36+C7)/C8</f>
         <v/>
       </c>
-      <c r="G36" s="79" t="inlineStr">
-        <is>
-          <t>Lo: 4.5x EV/EBITDA low case on FY2025A; distressed trough pricing near current market de-rating. Hi: 7.5x EV/EBITDA high case on FY2025A; partial recovery before terminal year, below historical peaks.</t>
+      <c r="G36" s="17" t="inlineStr">
+        <is>
+          <t>4.5x EV/EBITDA low case on FY2025A; distressed trough pricing near current market de-rating.</t>
+        </is>
+      </c>
+      <c r="H36" s="81" t="inlineStr">
+        <is>
+          <t>7.5x EV/EBITDA high case on FY2025A; partial recovery before terminal year, below historical peaks.</t>
+        </is>
+      </c>
+      <c r="I36" s="28" t="inlineStr">
+        <is>
+          <t>LULU current EV/EBITDA (model)</t>
+        </is>
+      </c>
+      <c r="J36" s="81" t="inlineStr">
+        <is>
+          <t>Peer comp set (Comps tab)</t>
         </is>
       </c>
     </row>
@@ -3934,23 +4136,38 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C37" s="77" t="n">
+      <c r="C37" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="77" t="n">
+      <c r="D37" s="79" t="n">
         <v>18</v>
       </c>
-      <c r="E37" s="78">
+      <c r="E37" s="80">
         <f>C6*C37</f>
         <v/>
       </c>
-      <c r="F37" s="78">
+      <c r="F37" s="80">
         <f>C6*D37</f>
         <v/>
       </c>
-      <c r="G37" s="79" t="inlineStr">
-        <is>
-          <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating. Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
+      <c r="G37" s="17" t="inlineStr">
+        <is>
+          <t>10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.</t>
+        </is>
+      </c>
+      <c r="H37" s="81" t="inlineStr">
+        <is>
+          <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
+        </is>
+      </c>
+      <c r="I37" s="28" t="inlineStr">
+        <is>
+          <t>LULU current P/E vs FY26E EPS</t>
+        </is>
+      </c>
+      <c r="J37" s="81" t="inlineStr">
+        <is>
+          <t>Peer P/E ranges (illustrative)</t>
         </is>
       </c>
     </row>
@@ -3960,42 +4177,42 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="80" t="inlineStr">
+      <c r="C38" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="80" t="inlineStr">
+      <c r="D38" s="82" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="78">
+      <c r="E38" s="80">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F38" s="78">
+      <c r="F38" s="80">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="81" t="inlineStr">
+      <c r="A40" s="83" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="82" t="n">
+      <c r="C40" s="84" t="n">
         <v>100</v>
       </c>
-      <c r="D40" s="56" t="inlineStr">
+      <c r="D40" s="58" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="37" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
@@ -4013,8 +4230,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -282,6 +282,19 @@
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="7"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="7"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -349,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -404,7 +417,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -562,13 +575,14 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1489,7 +1503,7 @@
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>WACC tab CAPM build (this model)</t>
+          <t>WACC tab: CAPM build</t>
         </is>
       </c>
     </row>
@@ -2460,6 +2474,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
+    <hyperlink ref="G8" location="'WACC'!C16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
@@ -2476,7 +2491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2490,6 +2505,7 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2552,6 +2568,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="L2" s="41" t="inlineStr">
+        <is>
+          <t>Alt. source</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="42" t="inlineStr">
@@ -2630,6 +2651,21 @@
         <f>H5/G5-1</f>
         <v/>
       </c>
+      <c r="J6" s="17" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical revenue (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
@@ -2661,6 +2697,21 @@
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+        </is>
+      </c>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
@@ -3113,6 +3164,16 @@
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
+      <c r="J26" s="17" t="inlineStr">
+        <is>
+          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+        </is>
+      </c>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>BEA: Real GDP (FRED GDPC1)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="20" t="inlineStr">
@@ -3302,14 +3363,19 @@
       <c r="C43" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="J43" s="17" t="inlineStr">
         <is>
           <t>8.0x FY2030E exit EV/EBITDA; above trough, below premium peers, roughly one turn above Gordon-implied multiple.</t>
         </is>
       </c>
-      <c r="E43" s="28" t="inlineStr">
-        <is>
-          <t>DCF Comps tab: Exit Multiple Build</t>
+      <c r="K43" s="18" t="inlineStr">
+        <is>
+          <t>Macrotrends: LULU EV/EBITDA history</t>
+        </is>
+      </c>
+      <c r="L43" s="28" t="inlineStr">
+        <is>
+          <t>Comps: Exit Multiple Build</t>
         </is>
       </c>
     </row>
@@ -3510,6 +3576,21 @@
       <c r="H59" s="72" t="n">
         <v>0.03</v>
       </c>
+      <c r="I59" s="28" t="inlineStr">
+        <is>
+          <t>Scenarios: terminal g</t>
+        </is>
+      </c>
+      <c r="J59" s="17" t="inlineStr">
+        <is>
+          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
+        </is>
+      </c>
+      <c r="K59" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="72" t="n">
@@ -3535,6 +3616,16 @@
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
+      <c r="I60" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
+      <c r="J60" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="72" t="n">
@@ -3560,6 +3651,11 @@
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
+      <c r="I61" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="72" t="n">
@@ -3585,6 +3681,11 @@
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
+      <c r="I62" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="72" t="n">
@@ -3610,6 +3711,11 @@
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
+      <c r="I63" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="72" t="n">
@@ -3635,6 +3741,11 @@
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
+      <c r="I64" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="J65" s="17" t="inlineStr">
@@ -3644,7 +3755,12 @@
       </c>
       <c r="K65" s="28" t="inlineStr">
         <is>
-          <t>Base WACC/g from Scenarios tab</t>
+          <t>Scenarios: WACC &amp; terminal g</t>
+        </is>
+      </c>
+      <c r="L65" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
     </row>
@@ -3652,18 +3768,35 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId20"/>
+    <hyperlink ref="L43" location="'Comps'!A25"/>
+    <hyperlink ref="I59" location="'Scenarios'!D9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId21"/>
+    <hyperlink ref="I60" location="'WACC'!C16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId22"/>
+    <hyperlink ref="I61" location="'WACC'!C16"/>
+    <hyperlink ref="I62" location="'WACC'!C16"/>
+    <hyperlink ref="I63" location="'WACC'!C16"/>
+    <hyperlink ref="I64" location="'WACC'!C16"/>
+    <hyperlink ref="K65" location="'Scenarios'!D8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3687,6 +3820,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -4119,14 +4253,14 @@
           <t>7.5x EV/EBITDA high case on FY2025A; partial recovery before terminal year, below historical peaks.</t>
         </is>
       </c>
-      <c r="I36" s="28" t="inlineStr">
-        <is>
-          <t>LULU current EV/EBITDA (model)</t>
-        </is>
-      </c>
-      <c r="J36" s="81" t="inlineStr">
-        <is>
-          <t>Peer comp set (Comps tab)</t>
+      <c r="I36" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="J36" s="82" t="inlineStr">
+        <is>
+          <t>Macrotrends: LULU EV/EBITDA history</t>
         </is>
       </c>
     </row>
@@ -4160,14 +4294,14 @@
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="I37" s="28" t="inlineStr">
-        <is>
-          <t>LULU current P/E vs FY26E EPS</t>
-        </is>
-      </c>
-      <c r="J37" s="81" t="inlineStr">
-        <is>
-          <t>Peer P/E ranges (illustrative)</t>
+      <c r="I37" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU P/E (FY26E)</t>
+        </is>
+      </c>
+      <c r="J37" s="82" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE P/E (peer benchmark)</t>
         </is>
       </c>
     </row>
@@ -4177,12 +4311,12 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="82" t="inlineStr">
+      <c r="C38" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="82" t="inlineStr">
+      <c r="D38" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4197,12 +4331,12 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="83" t="inlineStr">
+      <c r="A40" s="84" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="84" t="n">
+      <c r="C40" s="85" t="n">
         <v>100</v>
       </c>
       <c r="D40" s="58" t="inlineStr">
@@ -4236,8 +4370,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -115,6 +115,12 @@
       <name val="Garamond"/>
       <b val="1"/>
       <color rgb="00C8102E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00C8102E"/>
       <sz val="10"/>
     </font>
     <font>
@@ -126,12 +132,6 @@
       <name val="Garamond"/>
       <i val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <i val="1"/>
-      <color rgb="000000CC"/>
       <sz val="8"/>
     </font>
     <font>
@@ -167,9 +167,9 @@
     </font>
     <font>
       <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00C8102E"/>
-      <sz val="9"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -288,13 +288,13 @@
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="7"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="7"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -362,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -379,18 +379,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -414,9 +419,6 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -444,7 +446,7 @@
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -480,6 +482,7 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -517,7 +520,7 @@
     <xf numFmtId="164" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -566,8 +569,11 @@
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -575,7 +581,13 @@
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1086,14 +1098,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1112,74 +1123,81 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Source (click link)</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Risk-free rate (10-yr UST)</t>
         </is>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/DGS10","↳ FRED: 10Y Treasury (DGS10)")</f>
+        <v/>
+      </c>
+      <c r="C3" s="18" t="n">
         <v>0.043</v>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
-        <is>
-          <t>FRED: 10Y Treasury (DGS10)</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17">
+        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html","↳ Damodaran: Historical Implied ERP")</f>
+        <v/>
+      </c>
+      <c r="C4" s="18" t="n">
         <v>0.06</v>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="B5" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU Beta")</f>
+        <v/>
+      </c>
+      <c r="C5" s="20" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="19" t="inlineStr">
         <is>
           <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: LULU Beta</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <f>C3+C5*C4</f>
         <v/>
       </c>
@@ -1192,52 +1210,50 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K (no funded debt)")</f>
+        <v/>
+      </c>
+      <c r="C9" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K (no funded debt)</t>
-        </is>
-      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17">
+        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
+        <v/>
+      </c>
+      <c r="C10" s="18" t="n">
         <v>0.27</v>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>Damodaran: US tax rate dataset</t>
-        </is>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
@@ -1250,66 +1266,55 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
+        <v/>
+      </c>
+      <c r="C14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
+        <v/>
+      </c>
+      <c r="C15" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
         </is>
       </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="24">
         <f>C14*C6+C15*C11</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId7"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1344,17 +1349,17 @@
       <c r="E1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="24" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="D2" s="25" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1366,275 +1371,266 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="F3" s="27" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="G3" s="27" t="inlineStr">
-        <is>
-          <t>Source</t>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Source (click link)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="18" t="n">
         <v>-0.09</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="18" t="n">
         <v>-0.061</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="18" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
+      <c r="G4" s="17">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
+        <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="18" t="n">
         <v>0.028</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="18" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
         </is>
       </c>
-      <c r="G5" s="18" t="inlineStr">
-        <is>
-          <t>LULU historical revenue (10-K)</t>
-        </is>
+      <c r="G5" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical revenue (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>FY2026E EBIT margin</t>
         </is>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="18" t="n">
         <v>0.125</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.139</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="E6" s="18" t="n">
         <v>0.15</v>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
-        </is>
+      <c r="G6" s="17">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="18" t="n">
         <v>0.12</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="18" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="18" t="n">
         <v>0.19</v>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
         </is>
       </c>
-      <c r="G7" s="18" t="inlineStr">
-        <is>
-          <t>LULU historical EBIT margins (10-K)</t>
-        </is>
+      <c r="G7" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical EBIT margins (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="18" t="n">
         <v>0.11</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="18" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="E8" s="18" t="n">
         <v>0.09</v>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
         </is>
       </c>
       <c r="G8" s="28" t="inlineStr">
         <is>
-          <t>WACC tab: CAPM build</t>
+          <t>↳ WACC tab: CAPM build</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="18" t="n">
         <v>0.015</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.0225</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="18" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="19" t="inlineStr">
         <is>
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>BEA: Real GDP (FRED GDPC1)</t>
-        </is>
+      <c r="G9" s="17">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="18" t="n">
         <v>0.3</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="18" t="n">
         <v>0.27</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="18" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>Damodaran: US tax rate dataset</t>
-        </is>
+      <c r="G10" s="17">
+        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="19" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
+      <c r="G11" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="18" t="n">
         <v>0.055</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="18" t="n">
         <v>0.05</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="18" t="n">
         <v>0.045</v>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
+      <c r="G12" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="18" t="n">
         <v>0.08</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="18" t="n">
         <v>0.075</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="18" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="19" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>LULU BS/IS historical (10-K)</t>
-        </is>
+      <c r="G13" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2405,7 +2401,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="20" t="inlineStr">
+      <c r="A57" s="21" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
@@ -2443,7 +2439,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="20" t="inlineStr">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
@@ -2470,16 +2466,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
     <hyperlink ref="G8" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2592,7 +2579,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Net revenue</t>
         </is>
@@ -2626,7 +2613,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
@@ -2651,24 +2638,23 @@
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="19" t="inlineStr">
         <is>
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="K6" s="17">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
+        <v/>
+      </c>
+      <c r="L6" s="49" t="inlineStr">
         <is>
           <t>LULU historical revenue (10-K)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EBIT (operating) margin %</t>
         </is>
@@ -2697,29 +2683,28 @@
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="19" t="inlineStr">
         <is>
           <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
         </is>
       </c>
-      <c r="K7" s="18" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
+      <c r="K7" s="17">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
+        <v/>
+      </c>
+      <c r="L7" s="49" t="inlineStr">
         <is>
           <t>LULU historical EBIT margins (10-K)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="50" t="n">
         <v>2210615</v>
       </c>
       <c r="D8" s="32">
@@ -2742,13 +2727,13 @@
         <f>Scenarios!D30</f>
         <v/>
       </c>
-      <c r="I8" s="50">
+      <c r="I8" s="51">
         <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Less: cash taxes on EBIT</t>
         </is>
@@ -2775,7 +2760,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
@@ -2800,50 +2785,49 @@
         <f>Scenarios!D35</f>
         <v/>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="51">
         <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="18">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="18">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="18">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="18">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="H11" s="16">
+      <c r="H11" s="18">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="19" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
       </c>
-      <c r="K11" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
+      <c r="K11" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Plus: depreciation &amp; amortization</t>
         </is>
@@ -2874,44 +2858,43 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="18">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="18">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="18">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="18">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="H13" s="16">
+      <c r="H13" s="18">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="J13" s="19" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
+      <c r="K13" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Less: capital expenditures</t>
         </is>
@@ -2942,44 +2925,43 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="18">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="18">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="18">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="18">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="18">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="J15" s="19" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>LULU BS/IS historical (10-K)</t>
-        </is>
+      <c r="K15" s="17">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
+        <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>(Increase)/decrease in net working capital</t>
         </is>
@@ -3017,87 +2999,87 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D18" s="51">
+      <c r="D18" s="52">
         <f>Scenarios!D51</f>
         <v/>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="52">
         <f>Scenarios!D52</f>
         <v/>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="52">
         <f>Scenarios!D53</f>
         <v/>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="52">
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="52">
         <f>Scenarios!D55</f>
         <v/>
       </c>
-      <c r="I18" s="50">
+      <c r="I18" s="51">
         <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G19" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="52" t="n">
+      <c r="H19" s="53" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="54">
         <f>1/(1+Scenarios!$D$8)^D19</f>
         <v/>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="54">
         <f>1/(1+Scenarios!$D$8)^E19</f>
         <v/>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="54">
         <f>1/(1+Scenarios!$D$8)^F19</f>
         <v/>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="54">
         <f>1/(1+Scenarios!$D$8)^G19</f>
         <v/>
       </c>
-      <c r="H20" s="53">
+      <c r="H20" s="54">
         <f>1/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
@@ -3124,18 +3106,18 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Scenarios linkage summary (column I should all read OK)</t>
         </is>
       </c>
-      <c r="I23" s="54">
+      <c r="I23" s="55">
         <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3144,18 +3126,18 @@
       <c r="C24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="57">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
@@ -3164,19 +3146,18 @@
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
-      <c r="J26" s="17" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
       </c>
-      <c r="K26" s="18" t="inlineStr">
-        <is>
-          <t>BEA: Real GDP (FRED GDPC1)</t>
-        </is>
+      <c r="K26" s="17">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
@@ -3187,7 +3168,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
@@ -3198,29 +3179,29 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="58">
         <f>C28/C27</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C30" s="56">
+      <c r="C30" s="57">
         <f>C28/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
@@ -3231,7 +3212,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
@@ -3239,14 +3220,14 @@
       <c r="C32" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D32" s="58" t="inlineStr">
+      <c r="D32" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Less: total debt</t>
         </is>
@@ -3254,14 +3235,14 @@
       <c r="C33" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="58" t="inlineStr">
+      <c r="D33" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
@@ -3272,7 +3253,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
@@ -3280,55 +3261,55 @@
       <c r="C35" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D35" s="58" t="inlineStr">
+      <c r="D35" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C36" s="59">
+      <c r="C36" s="60">
         <f>C34/C35</f>
         <v/>
       </c>
-      <c r="I36" s="50">
+      <c r="I36" s="51">
         <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C37" s="60" t="n">
+      <c r="C37" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="D37" s="58" t="inlineStr">
+      <c r="D37" s="59" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C38" s="61">
+      <c r="C38" s="62">
         <f>C36/C37-1</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
@@ -3339,7 +3320,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3348,30 +3329,29 @@
       <c r="C41" s="13" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C43" s="62" t="n">
+      <c r="C43" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="17" t="inlineStr">
-        <is>
-          <t>8.0x FY2030E exit EV/EBITDA; above trough, below premium peers, roughly one turn above Gordon-implied multiple.</t>
-        </is>
-      </c>
-      <c r="K43" s="18" t="inlineStr">
-        <is>
-          <t>Macrotrends: LULU EV/EBITDA history</t>
-        </is>
+      <c r="J43" s="19" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+        </is>
+      </c>
+      <c r="K43" s="17">
+        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
+        <v/>
       </c>
       <c r="L43" s="28" t="inlineStr">
         <is>
@@ -3380,7 +3360,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
@@ -3391,7 +3371,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
@@ -3402,7 +3382,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
@@ -3413,18 +3393,18 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="63">
+      <c r="C47" s="64">
         <f>(C46+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3434,63 +3414,63 @@
       <c r="D49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="64" t="inlineStr"/>
-      <c r="B50" s="65" t="inlineStr">
+      <c r="A50" s="65" t="inlineStr"/>
+      <c r="B50" s="66" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="65" t="inlineStr">
+      <c r="C50" s="66" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="65" t="inlineStr">
+      <c r="D50" s="66" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="20" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="56">
+      <c r="B51" s="57">
         <f>C28</f>
         <v/>
       </c>
-      <c r="C51" s="56">
+      <c r="C51" s="57">
         <f>C44</f>
         <v/>
       </c>
-      <c r="D51" s="56">
+      <c r="D51" s="57">
         <f>B51-C51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="20" t="inlineStr">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B52" s="66">
+      <c r="B52" s="67">
         <f>C29</f>
         <v/>
       </c>
-      <c r="C52" s="66">
+      <c r="C52" s="67">
         <f>C43</f>
         <v/>
       </c>
-      <c r="D52" s="66">
+      <c r="D52" s="67">
         <f>B52-C52</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
@@ -3503,35 +3483,35 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="20" t="inlineStr">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="67">
+      <c r="B54" s="68">
         <f>C36</f>
         <v/>
       </c>
-      <c r="C54" s="67">
+      <c r="C54" s="68">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D54" s="67">
+      <c r="D54" s="68">
         <f>B54-C54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="A55" s="69" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="69">
+      <c r="B55" s="70">
         <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C55" s="70">
+      <c r="C55" s="71">
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
@@ -3542,7 +3522,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -3556,24 +3536,24 @@
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="71" t="inlineStr">
+      <c r="A59" s="72" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="72" t="n">
+      <c r="D59" s="73" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="72" t="n">
+      <c r="E59" s="73" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="72" t="n">
+      <c r="F59" s="73" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="72" t="n">
+      <c r="G59" s="73" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="72" t="n">
+      <c r="H59" s="73" t="n">
         <v>0.03</v>
       </c>
       <c r="I59" s="28" t="inlineStr">
@@ -3581,38 +3561,37 @@
           <t>Scenarios: terminal g</t>
         </is>
       </c>
-      <c r="J59" s="17" t="inlineStr">
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
         </is>
       </c>
-      <c r="K59" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
+      <c r="K59" s="17">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
+        <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="72" t="n">
+      <c r="A60" s="73" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="73">
+      <c r="D60" s="74">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E60" s="73">
+      <c r="E60" s="74">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F60" s="73">
+      <c r="F60" s="74">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G60" s="73">
+      <c r="G60" s="74">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H60" s="73">
+      <c r="H60" s="74">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3621,33 +3600,33 @@
           <t>WACC tab</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr">
+      <c r="J60" s="49" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="72" t="n">
+      <c r="A61" s="73" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="73">
+      <c r="D61" s="74">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E61" s="73">
+      <c r="E61" s="74">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F61" s="73">
+      <c r="F61" s="74">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G61" s="73">
+      <c r="G61" s="74">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H61" s="73">
+      <c r="H61" s="74">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3658,26 +3637,26 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="72" t="n">
+      <c r="A62" s="73" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="73">
+      <c r="D62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E62" s="73">
+      <c r="E62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F62" s="74">
+      <c r="F62" s="75">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G62" s="73">
+      <c r="G62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H62" s="73">
+      <c r="H62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3688,26 +3667,26 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="72" t="n">
+      <c r="A63" s="73" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="73">
+      <c r="D63" s="74">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E63" s="73">
+      <c r="E63" s="74">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F63" s="73">
+      <c r="F63" s="74">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G63" s="73">
+      <c r="G63" s="74">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H63" s="73">
+      <c r="H63" s="74">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3718,26 +3697,26 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="72" t="n">
+      <c r="A64" s="73" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="73">
+      <c r="D64" s="74">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E64" s="73">
+      <c r="E64" s="74">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F64" s="73">
+      <c r="F64" s="74">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G64" s="73">
+      <c r="G64" s="74">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H64" s="73">
+      <c r="H64" s="74">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3748,55 +3727,45 @@
       </c>
     </row>
     <row r="65">
-      <c r="J65" s="17" t="inlineStr">
+      <c r="J65" s="19" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
       <c r="K65" s="28" t="inlineStr">
         <is>
-          <t>Scenarios: WACC &amp; terminal g</t>
-        </is>
-      </c>
-      <c r="L65" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
+          <t>↳ Scenarios: WACC &amp; terminal g</t>
+        </is>
+      </c>
+      <c r="L65" s="49">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId20"/>
-    <hyperlink ref="L43" location="'Comps'!A25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId13"/>
+    <hyperlink ref="L43" location="'Comps'!A26"/>
     <hyperlink ref="I59" location="'Scenarios'!D9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId21"/>
     <hyperlink ref="I60" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId14"/>
     <hyperlink ref="I61" location="'WACC'!C16"/>
     <hyperlink ref="I62" location="'WACC'!C16"/>
     <hyperlink ref="I63" location="'WACC'!C16"/>
     <hyperlink ref="I64" location="'WACC'!C16"/>
     <hyperlink ref="K65" location="'Scenarios'!D8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3808,7 +3777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3843,7 +3812,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2025A revenue</t>
         </is>
@@ -3851,14 +3820,14 @@
       <c r="C4" s="45" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="58" t="inlineStr">
+      <c r="D4" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
@@ -3869,484 +3838,532 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="C6" s="46">
+        <f>DCF!C27</f>
+        <v/>
+      </c>
+      <c r="D6" s="28" t="inlineStr">
+        <is>
+          <t>↳ DCF base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C6" s="60" t="n">
+      <c r="C7" s="61" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C8" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C9" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D8" s="58" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C9" s="60" t="n">
+      <c r="C10" s="61" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="70" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C10" s="75">
-        <f>(C9*C8-C7)/C5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="C11" s="76">
+        <f>(C10*C9-C8)/C5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C11" s="75">
-        <f>C9/C6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="C12" s="76">
+        <f>C10/C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>EXIT MULTIPLE BUILD — FY2030E TERMINAL YEAR</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="70" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="71" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="76" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C15" s="77" t="inlineStr">
+      <c r="C16" s="78" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D15" s="76" t="inlineStr">
+      <c r="D16" s="77" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="E15" s="76" t="inlineStr">
+      <c r="E16" s="77" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C16" s="78">
-        <f>(C9*C8-C7)/C5</f>
-        <v/>
-      </c>
-      <c r="D16" s="37" t="inlineStr">
+      <c r="C17" s="79">
+        <f>(C10*C9-C8)/C5</f>
+        <v/>
+      </c>
+      <c r="D17" s="37" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C17" s="79" t="n">
+      <c r="C18" s="80" t="n">
         <v>18</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: NKE statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="E18" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/NKE/key-statistics/","↳ Yahoo Finance: NKE statistics")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C18" s="79" t="n">
+      <c r="C19" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: DECK statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="E19" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/DECK/key-statistics/","↳ Yahoo Finance: DECK statistics")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C19" s="79" t="n">
+      <c r="C20" s="80" t="n">
         <v>25</v>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
         <is>
           <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: ONON statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="E20" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/ONON/key-statistics/","↳ Yahoo Finance: ONON statistics")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n">
+      <c r="C21" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D21" s="19" t="inlineStr">
         <is>
           <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: ADS.DE statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="E21" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/ADS.DE/key-statistics/","↳ Yahoo Finance: ADS.DE statistics")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C21" s="79" t="n">
+      <c r="C22" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: VFC statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="E22" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/VFC/key-statistics/","↳ Yahoo Finance: VFC statistics")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Terminal multiple selection (DCF exit method)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C24" s="57">
+      <c r="C25" s="58">
         <f>DCF!C29</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="68" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="69" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C25" s="66">
+      <c r="C26" s="67">
         <f>DCF!C43</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C26" s="57">
-        <f>C25-C24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="68" t="inlineStr">
+      <c r="C27" s="58">
+        <f>C26-C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="69" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>•  Above current LULU (~3.5x) — assumes partial recovery from trough, not full re-rating</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="29" t="inlineStr">
         <is>
-          <t>•  Above comps football-field high (7.5x on FY2025A) — terminal year has higher EBITDA &amp; normalized margins</t>
+          <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity</t>
+          <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>•  ~1 turn above Gordon-implied exit multiple — conservative buffer vs perpetuity math</t>
+          <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="29" t="inlineStr">
         <is>
-          <t>•  Well below historical LULU peak multiples (20–30x) — avoids heroic assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>Methodology / multiple ranges (FY2025A — football field)</t>
+          <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="29" t="inlineStr">
+        <is>
+          <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="76" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Methodology / multiple ranges (FY2030E terminal EBITDA — football field)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="77" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C35" s="77" t="inlineStr">
+      <c r="C36" s="78" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D35" s="77" t="inlineStr">
+      <c r="D36" s="78" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E35" s="77" t="inlineStr">
+      <c r="E36" s="78" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F35" s="77" t="inlineStr">
+      <c r="F36" s="78" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>EV / EBITDA (FY2025A)</t>
-        </is>
-      </c>
-      <c r="C36" s="79" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D36" s="79" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E36" s="80">
-        <f>(C5*C36+C7)/C8</f>
-        <v/>
-      </c>
-      <c r="F36" s="80">
-        <f>(C5*D36+C7)/C8</f>
-        <v/>
-      </c>
-      <c r="G36" s="17" t="inlineStr">
-        <is>
-          <t>4.5x EV/EBITDA low case on FY2025A; distressed trough pricing near current market de-rating.</t>
+      <c r="G36" s="81" t="inlineStr">
+        <is>
+          <t>Lo justification</t>
         </is>
       </c>
       <c r="H36" s="81" t="inlineStr">
         <is>
-          <t>7.5x EV/EBITDA high case on FY2025A; partial recovery before terminal year, below historical peaks.</t>
-        </is>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="J36" s="82" t="inlineStr">
-        <is>
-          <t>Macrotrends: LULU EV/EBITDA history</t>
+          <t>Hi justification</t>
+        </is>
+      </c>
+      <c r="I36" s="81" t="inlineStr">
+        <is>
+          <t>Lo source</t>
+        </is>
+      </c>
+      <c r="J36" s="81" t="inlineStr">
+        <is>
+          <t>Hi source</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>EV / EBITDA (FY2030E terminal)</t>
+        </is>
+      </c>
+      <c r="C37" s="80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D37" s="80" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E37" s="82">
+        <f>(C6*C37+C8)/C9</f>
+        <v/>
+      </c>
+      <c r="F37" s="82">
+        <f>(C6*D37+C8)/C9</f>
+        <v/>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.</t>
+        </is>
+      </c>
+      <c r="H37" s="83" t="inlineStr">
+        <is>
+          <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
+        </is>
+      </c>
+      <c r="I37" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU EV/EBITDA")</f>
+        <v/>
+      </c>
+      <c r="J37" s="84">
+        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="69" t="inlineStr">
+        <is>
+          <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
+        </is>
+      </c>
+      <c r="C38" s="85">
+        <f>DCF!C43</f>
+        <v/>
+      </c>
+      <c r="E38" s="86">
+        <f>(C6*C38+C8)/C9</f>
+        <v/>
+      </c>
+      <c r="I38" s="28" t="inlineStr">
+        <is>
+          <t>↳ DCF exit multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C37" s="79" t="n">
+      <c r="C39" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="D37" s="79" t="n">
+      <c r="D39" s="80" t="n">
         <v>18</v>
       </c>
-      <c r="E37" s="80">
-        <f>C6*C37</f>
-        <v/>
-      </c>
-      <c r="F37" s="80">
-        <f>C6*D37</f>
-        <v/>
-      </c>
-      <c r="G37" s="17" t="inlineStr">
+      <c r="E39" s="82">
+        <f>C7*C39</f>
+        <v/>
+      </c>
+      <c r="F39" s="82">
+        <f>C7*D39</f>
+        <v/>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
         <is>
           <t>10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.</t>
         </is>
       </c>
-      <c r="H37" s="81" t="inlineStr">
+      <c r="H39" s="83" t="inlineStr">
         <is>
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="I37" s="18" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: LULU P/E (FY26E)</t>
-        </is>
-      </c>
-      <c r="J37" s="82" t="inlineStr">
+      <c r="I39" s="17">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU P/E (FY26E)")</f>
+        <v/>
+      </c>
+      <c r="J39" s="84" t="inlineStr">
         <is>
           <t>Yahoo Finance: NKE P/E (peer benchmark)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C38" s="83" t="inlineStr">
+      <c r="C40" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="83" t="inlineStr">
+      <c r="D40" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="80">
+      <c r="E40" s="82">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F38" s="80">
+      <c r="F40" s="82">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="84" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="88" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C40" s="85" t="n">
+      <c r="C42" s="89" t="n">
         <v>100</v>
       </c>
-      <c r="D40" s="58" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="37" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
@@ -4356,26 +4373,20 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J36" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D40" r:id="rId22"/>
+    <hyperlink ref="D6" location="'DCF'!C27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
+    <hyperlink ref="I38" location="'DCF'!C43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -386,11 +386,11 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -578,10 +578,10 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1021,7 +1021,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions / inputs (justification + clickable source link)</t>
+          <t>Red font  =  analyst assumptions — source link in col immediately LEFT of justification</t>
         </is>
       </c>
     </row>
@@ -1098,13 +1098,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1113,9 +1113,9 @@
           <t>WEIGHTED AVERAGE COST OF CAPITAL</t>
         </is>
       </c>
-      <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -1123,12 +1123,12 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>Source (click link)</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="E2" s="15" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
@@ -1140,14 +1140,14 @@
           <t>Risk-free rate (10-yr UST)</t>
         </is>
       </c>
-      <c r="B3" s="17">
+      <c r="C3" s="17" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="D3" s="18">
         <f>HYPERLINK("https://fred.stlouisfed.org/series/DGS10","↳ FRED: 10Y Treasury (DGS10)")</f>
         <v/>
       </c>
-      <c r="C3" s="18" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
         </is>
@@ -1159,14 +1159,14 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B4" s="17">
+      <c r="C4" s="17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D4" s="18">
         <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html","↳ Damodaran: Historical Implied ERP")</f>
         <v/>
       </c>
-      <c r="C4" s="18" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
         </is>
@@ -1178,14 +1178,14 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="B5" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU Beta")</f>
-        <v/>
-      </c>
       <c r="C5" s="20" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D5" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU Beta")</f>
+        <v/>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
         </is>
@@ -1215,14 +1215,14 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="C9" s="17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D9" s="18">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K (no funded debt)")</f>
         <v/>
       </c>
-      <c r="C9" s="18" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
         </is>
@@ -1234,14 +1234,14 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="C10" s="17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="D10" s="18">
         <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
         <v/>
       </c>
-      <c r="C10" s="18" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
         </is>
@@ -1271,14 +1271,14 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="C14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
         <v/>
       </c>
-      <c r="C14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
         </is>
@@ -1290,14 +1290,14 @@
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="C15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="18">
         <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
         <v/>
       </c>
-      <c r="C15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="E15" s="19" t="inlineStr">
         <is>
           <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
         </is>
@@ -1328,13 +1328,12 @@
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1373,12 +1372,12 @@
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
+          <t>Source (click link)</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
           <t>Justification (~20 words)</t>
-        </is>
-      </c>
-      <c r="G3" s="15" t="inlineStr">
-        <is>
-          <t>Source (click link)</t>
         </is>
       </c>
     </row>
@@ -1388,23 +1387,23 @@
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n">
+      <c r="C4" s="17" t="n">
         <v>-0.09</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>-0.061</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="17" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F4" s="19" t="inlineStr">
+      <c r="F4" s="18">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
+        <v/>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
         </is>
-      </c>
-      <c r="G4" s="17">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -1413,23 +1412,23 @@
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n">
+      <c r="C5" s="17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>0.028</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="17" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="F5" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical revenue (10-K)")</f>
+        <v/>
+      </c>
+      <c r="G5" s="19" t="inlineStr">
         <is>
           <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
         </is>
-      </c>
-      <c r="G5" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical revenue (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -1438,23 +1437,23 @@
           <t>FY2026E EBIT margin</t>
         </is>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="17" t="n">
         <v>0.125</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>0.139</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="F6" s="19" t="inlineStr">
+      <c r="F6" s="18">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
+        <v/>
+      </c>
+      <c r="G6" s="19" t="inlineStr">
         <is>
           <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
         </is>
-      </c>
-      <c r="G6" s="17">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1463,23 +1462,23 @@
           <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="17" t="n">
         <v>0.12</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="17" t="n">
         <v>0.19</v>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical EBIT margins (10-K)")</f>
+        <v/>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
         <is>
           <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
         </is>
-      </c>
-      <c r="G7" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical EBIT margins (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -1488,23 +1487,23 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="17" t="n">
         <v>0.11</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="17" t="n">
         <v>0.09</v>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
+        <is>
+          <t>↳ WACC tab: CAPM build</t>
+        </is>
+      </c>
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>↳ WACC tab: CAPM build</t>
         </is>
       </c>
     </row>
@@ -1514,23 +1513,23 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n">
+      <c r="C9" s="17" t="n">
         <v>0.015</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>0.0225</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="18">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
+        <v/>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
-      </c>
-      <c r="G9" s="17">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -1539,23 +1538,23 @@
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="C10" s="18" t="n">
+      <c r="C10" s="17" t="n">
         <v>0.3</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>0.27</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="18">
+        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
+        <v/>
+      </c>
+      <c r="G10" s="19" t="inlineStr">
         <is>
           <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
         </is>
-      </c>
-      <c r="G10" s="17">
-        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -1564,23 +1563,23 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n">
+      <c r="C11" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
-      </c>
-      <c r="G11" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1589,23 +1588,23 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n">
+      <c r="C12" s="17" t="n">
         <v>0.055</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
+      </c>
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
-      </c>
-      <c r="G12" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -1614,23 +1613,23 @@
           <t>NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
+      <c r="C13" s="17" t="n">
         <v>0.08</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>0.075</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="17" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
+        <v/>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
-      </c>
-      <c r="G13" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -2466,7 +2465,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G8" location="'WACC'!C16"/>
+    <hyperlink ref="F8" location="'WACC'!C16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2547,12 +2546,12 @@
       </c>
       <c r="J2" s="41" t="inlineStr">
         <is>
+          <t>Source (click link)</t>
+        </is>
+      </c>
+      <c r="K2" s="41" t="inlineStr">
+        <is>
           <t>Justification (~20 words)</t>
-        </is>
-      </c>
-      <c r="K2" s="41" t="inlineStr">
-        <is>
-          <t>Source</t>
         </is>
       </c>
       <c r="L2" s="41" t="inlineStr">
@@ -2638,14 +2637,14 @@
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="J6" s="19" t="inlineStr">
+      <c r="J6" s="18">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
+        <v/>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
         <is>
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
         </is>
-      </c>
-      <c r="K6" s="17">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
-        <v/>
       </c>
       <c r="L6" s="49" t="inlineStr">
         <is>
@@ -2683,14 +2682,14 @@
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="J7" s="19" t="inlineStr">
+      <c r="J7" s="18">
+        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
+        <v/>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
         <is>
           <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
         </is>
-      </c>
-      <c r="K7" s="17">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
-        <v/>
       </c>
       <c r="L7" s="49" t="inlineStr">
         <is>
@@ -2796,34 +2795,34 @@
           <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="J11" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
+      </c>
+      <c r="K11" s="19" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
-      </c>
-      <c r="K11" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -2863,34 +2862,34 @@
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="J13" s="19" t="inlineStr">
+      <c r="J13" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
+        <v/>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
-      </c>
-      <c r="K13" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -2930,34 +2929,34 @@
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="J15" s="19" t="inlineStr">
+      <c r="J15" s="18">
+        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
+        <v/>
+      </c>
+      <c r="K15" s="19" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
-      </c>
-      <c r="K15" s="17">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -3146,14 +3145,14 @@
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J26" s="18">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
+        <v/>
+      </c>
+      <c r="K26" s="19" t="inlineStr">
         <is>
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
-      </c>
-      <c r="K26" s="17">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -3344,14 +3343,14 @@
       <c r="C43" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="19" t="inlineStr">
+      <c r="J43" s="18">
+        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
+        <v/>
+      </c>
+      <c r="K43" s="19" t="inlineStr">
         <is>
           <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
         </is>
-      </c>
-      <c r="K43" s="17">
-        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
-        <v/>
       </c>
       <c r="L43" s="28" t="inlineStr">
         <is>
@@ -3561,14 +3560,14 @@
           <t>Scenarios: terminal g</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="J59" s="18">
+        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
+        <v/>
+      </c>
+      <c r="K59" s="19" t="inlineStr">
         <is>
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
         </is>
-      </c>
-      <c r="K59" s="17">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
-        <v/>
       </c>
     </row>
     <row r="60">
@@ -3727,14 +3726,14 @@
       </c>
     </row>
     <row r="65">
-      <c r="J65" s="19" t="inlineStr">
+      <c r="J65" s="28" t="inlineStr">
+        <is>
+          <t>↳ Scenarios: WACC &amp; terminal g</t>
+        </is>
+      </c>
+      <c r="K65" s="19" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
-        </is>
-      </c>
-      <c r="K65" s="28" t="inlineStr">
-        <is>
-          <t>↳ Scenarios: WACC &amp; terminal g</t>
         </is>
       </c>
       <c r="L65" s="49">
@@ -3765,7 +3764,7 @@
     <hyperlink ref="I62" location="'WACC'!C16"/>
     <hyperlink ref="I63" location="'WACC'!C16"/>
     <hyperlink ref="I64" location="'WACC'!C16"/>
-    <hyperlink ref="K65" location="'Scenarios'!D8"/>
+    <hyperlink ref="J65" location="'Scenarios'!D8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3962,12 +3961,12 @@
       </c>
       <c r="D16" s="77" t="inlineStr">
         <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="E16" s="77" t="inlineStr">
+        <is>
           <t>Justification</t>
-        </is>
-      </c>
-      <c r="E16" s="77" t="inlineStr">
-        <is>
-          <t>Source</t>
         </is>
       </c>
     </row>
@@ -4001,14 +4000,14 @@
       <c r="C18" s="80" t="n">
         <v>18</v>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D18" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/NKE/key-statistics/","↳ Yahoo Finance: NKE statistics")</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
         </is>
-      </c>
-      <c r="E18" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/NKE/key-statistics/","↳ Yahoo Finance: NKE statistics")</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -4020,14 +4019,14 @@
       <c r="C19" s="80" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="19" t="inlineStr">
+      <c r="D19" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/DECK/key-statistics/","↳ Yahoo Finance: DECK statistics")</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
         </is>
-      </c>
-      <c r="E19" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/DECK/key-statistics/","↳ Yahoo Finance: DECK statistics")</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -4039,14 +4038,14 @@
       <c r="C20" s="80" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D20" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/ONON/key-statistics/","↳ Yahoo Finance: ONON statistics")</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
         </is>
-      </c>
-      <c r="E20" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/ONON/key-statistics/","↳ Yahoo Finance: ONON statistics")</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -4058,14 +4057,14 @@
       <c r="C21" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="19" t="inlineStr">
+      <c r="D21" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/ADS.DE/key-statistics/","↳ Yahoo Finance: ADS.DE statistics")</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
         </is>
-      </c>
-      <c r="E21" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/ADS.DE/key-statistics/","↳ Yahoo Finance: ADS.DE statistics")</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -4077,14 +4076,14 @@
       <c r="C22" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="19" t="inlineStr">
+      <c r="D22" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/VFC/key-statistics/","↳ Yahoo Finance: VFC statistics")</f>
+        <v/>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
         </is>
-      </c>
-      <c r="E22" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/VFC/key-statistics/","↳ Yahoo Finance: VFC statistics")</f>
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -4119,7 +4118,7 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Spread (selected − Gordon implied)</t>
+          <t>Spread (selectd (selected − Gordon implied)</t>
         </is>
       </c>
       <c r="C27" s="58">
@@ -4204,22 +4203,22 @@
       </c>
       <c r="G36" s="81" t="inlineStr">
         <is>
+          <t>Lo source</t>
+        </is>
+      </c>
+      <c r="H36" s="81" t="inlineStr">
+        <is>
           <t>Lo justification</t>
         </is>
       </c>
-      <c r="H36" s="81" t="inlineStr">
+      <c r="I36" s="81" t="inlineStr">
+        <is>
+          <t>Hi source</t>
+        </is>
+      </c>
+      <c r="J36" s="81" t="inlineStr">
         <is>
           <t>Hi justification</t>
-        </is>
-      </c>
-      <c r="I36" s="81" t="inlineStr">
-        <is>
-          <t>Lo source</t>
-        </is>
-      </c>
-      <c r="J36" s="81" t="inlineStr">
-        <is>
-          <t>Hi source</t>
         </is>
       </c>
     </row>
@@ -4243,23 +4242,23 @@
         <f>(C6*D37+C8)/C9</f>
         <v/>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G37" s="18">
+        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU EV/EBITDA")</f>
+        <v/>
+      </c>
+      <c r="H37" s="19" t="inlineStr">
         <is>
           <t>6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.</t>
         </is>
       </c>
-      <c r="H37" s="83" t="inlineStr">
+      <c r="I37" s="83">
+        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
+        <v/>
+      </c>
+      <c r="J37" s="84" t="inlineStr">
         <is>
           <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
-      </c>
-      <c r="I37" s="17">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU EV/EBITDA")</f>
-        <v/>
-      </c>
-      <c r="J37" s="84">
-        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -4307,16 +4306,16 @@
           <t>10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.</t>
         </is>
       </c>
-      <c r="H39" s="83" t="inlineStr">
+      <c r="H39" s="84" t="inlineStr">
         <is>
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="18">
         <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU P/E (FY26E)")</f>
         <v/>
       </c>
-      <c r="J39" s="84" t="inlineStr">
+      <c r="J39" s="83" t="inlineStr">
         <is>
           <t>Yahoo Finance: NKE P/E (peer benchmark)</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,7 +138,13 @@
       <name val="Garamond"/>
       <i val="1"/>
       <color rgb="000000CC"/>
-      <sz val="8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="9"/>
       <u val="single"/>
     </font>
     <font>
@@ -167,32 +173,39 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="001F2A44"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Garamond"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="001F2A44"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
+      <i val="1"/>
       <color rgb="000000CC"/>
-      <sz val="10"/>
+      <sz val="8"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -288,13 +301,13 @@
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="7"/>
-      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
       <i val="1"/>
       <color rgb="000000CC"/>
       <sz val="7"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -362,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -389,37 +402,37 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -431,7 +444,7 @@
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -440,10 +453,10 @@
     <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -452,118 +465,121 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="38" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="40" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="42" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,20 +588,20 @@
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -594,7 +610,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1021,7 +1037,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions — source link in col immediately LEFT of justification</t>
+          <t>Red font  =  analyst assumptions — justification then blue Source (click) in next column right</t>
         </is>
       </c>
     </row>
@@ -1103,8 +1119,8 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1125,12 +1141,12 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Source (click link)</t>
+          <t>Justification (~20 words)</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Justification (~20 words)</t>
+          <t>Source (click)</t>
         </is>
       </c>
     </row>
@@ -1143,13 +1159,14 @@
       <c r="C3" s="17" t="n">
         <v>0.043</v>
       </c>
-      <c r="D3" s="18">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/DGS10","↳ FRED: 10Y Treasury (DGS10)")</f>
-        <v/>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
+        </is>
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
+          <t>FRED: 10Y Treasury (DGS10)</t>
         </is>
       </c>
     </row>
@@ -1162,13 +1179,14 @@
       <c r="C4" s="17" t="n">
         <v>0.06</v>
       </c>
-      <c r="D4" s="18">
-        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html","↳ Damodaran: Historical Implied ERP")</f>
-        <v/>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
+        </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
+          <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
     </row>
@@ -1181,13 +1199,14 @@
       <c r="C5" s="20" t="n">
         <v>0.95</v>
       </c>
-      <c r="D5" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU Beta")</f>
-        <v/>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
+        </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
+          <t>Yahoo Finance: LULU Beta</t>
         </is>
       </c>
     </row>
@@ -1218,13 +1237,14 @@
       <c r="C9" s="17" t="n">
         <v>0.05</v>
       </c>
-      <c r="D9" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K (no funded debt)")</f>
-        <v/>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
+        </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
+          <t>LULU FY2025 10-K (no funded debt)</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1257,14 @@
       <c r="C10" s="17" t="n">
         <v>0.27</v>
       </c>
-      <c r="D10" s="18">
-        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
-        <v/>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
+        </is>
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
+          <t>Damodaran: US tax rate dataset</t>
         </is>
       </c>
     </row>
@@ -1274,13 +1295,14 @@
       <c r="C14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
-        <v/>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
+        </is>
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
+          <t>LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
     </row>
@@ -1293,13 +1315,14 @@
       <c r="C15" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU FY2025 10-K balance sheet")</f>
-        <v/>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
+        </is>
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
+          <t>LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
     </row>
@@ -1315,6 +1338,15 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1328,12 +1360,12 @@
   <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1372,12 +1404,12 @@
       </c>
       <c r="F3" s="15" t="inlineStr">
         <is>
-          <t>Source (click link)</t>
+          <t>Justification (~20 words)</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Justification (~20 words)</t>
+          <t>Source (click)</t>
         </is>
       </c>
     </row>
@@ -1396,13 +1428,14 @@
       <c r="E4" s="17" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F4" s="18">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
-        <v/>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+        </is>
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+          <t>LULU Q2 FY2026 earnings release</t>
         </is>
       </c>
     </row>
@@ -1421,13 +1454,14 @@
       <c r="E5" s="17" t="n">
         <v>0.06</v>
       </c>
-      <c r="F5" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical revenue (10-K)")</f>
-        <v/>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+        </is>
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+          <t>LULU historical revenue (10-K)</t>
         </is>
       </c>
     </row>
@@ -1446,13 +1480,14 @@
       <c r="E6" s="17" t="n">
         <v>0.15</v>
       </c>
-      <c r="F6" s="18">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
-        <v/>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+        </is>
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
         </is>
       </c>
     </row>
@@ -1471,13 +1506,14 @@
       <c r="E7" s="17" t="n">
         <v>0.19</v>
       </c>
-      <c r="F7" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU historical EBIT margins (10-K)")</f>
-        <v/>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+        </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+          <t>LULU historical EBIT margins (10-K)</t>
         </is>
       </c>
     </row>
@@ -1496,14 +1532,14 @@
       <c r="E8" s="17" t="n">
         <v>0.09</v>
       </c>
-      <c r="F8" s="28" t="inlineStr">
-        <is>
-          <t>↳ WACC tab: CAPM build</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="inlineStr">
+        <is>
+          <t>WACC tab: CAPM build</t>
         </is>
       </c>
     </row>
@@ -1522,13 +1558,14 @@
       <c r="E9" s="17" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" s="18">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
-        <v/>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+        </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+          <t>BEA: Real GDP (FRED GDPC1)</t>
         </is>
       </c>
     </row>
@@ -1547,13 +1584,14 @@
       <c r="E10" s="17" t="n">
         <v>0.25</v>
       </c>
-      <c r="F10" s="18">
-        <f>HYPERLINK("https://pages.stern.nyu.edu/~adamodar/New_Home_Page/datafile/taxrate.html","↳ Damodaran: US tax rate dataset")</f>
-        <v/>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
+        </is>
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
+          <t>Damodaran: US tax rate dataset</t>
         </is>
       </c>
     </row>
@@ -1572,13 +1610,14 @@
       <c r="E11" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="F11" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -1597,13 +1636,14 @@
       <c r="E12" s="17" t="n">
         <v>0.045</v>
       </c>
-      <c r="F12" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1662,14 @@
       <c r="E13" s="17" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
-        <v/>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+          <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2506,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F8" location="'WACC'!C16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
+    <hyperlink ref="G8" location="'WACC'!C16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2480,7 +2530,7 @@
   <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -2488,10 +2538,11 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2546,12 +2597,12 @@
       </c>
       <c r="J2" s="41" t="inlineStr">
         <is>
-          <t>Source (click link)</t>
+          <t>Justification (~20 words)</t>
         </is>
       </c>
       <c r="K2" s="41" t="inlineStr">
         <is>
-          <t>Justification (~20 words)</t>
+          <t>Source (click)</t>
         </is>
       </c>
       <c r="L2" s="41" t="inlineStr">
@@ -2637,13 +2688,14 @@
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="J6" s="18">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 earnings release")</f>
-        <v/>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+        </is>
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+          <t>LULU Q2 FY2026 earnings release</t>
         </is>
       </c>
       <c r="L6" s="49" t="inlineStr">
@@ -2682,13 +2734,14 @@
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
-      <c r="J7" s="18">
-        <f>HYPERLINK("https://investor.lululemon.com/news-releases","↳ LULU Q2 FY2026 guidance / 10-K margins")</f>
-        <v/>
+      <c r="J7" s="18" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+        </is>
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
         </is>
       </c>
       <c r="L7" s="49" t="inlineStr">
@@ -2815,13 +2868,14 @@
         <f>Scenarios!$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
+      <c r="J11" s="18" t="inlineStr">
+        <is>
+          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -2882,13 +2936,14 @@
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
-      <c r="J13" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU CF statement (10-K)")</f>
-        <v/>
+      <c r="J13" s="18" t="inlineStr">
+        <is>
+          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
     </row>
@@ -2949,13 +3004,14 @@
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
-      <c r="J15" s="18">
-        <f>HYPERLINK("https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm","↳ LULU BS/IS historical (10-K)")</f>
-        <v/>
+      <c r="J15" s="18" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+          <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
     </row>
@@ -3145,13 +3201,14 @@
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
-      <c r="J26" s="18">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ BEA: Real GDP (FRED GDPC1)")</f>
-        <v/>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+        </is>
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+          <t>BEA: Real GDP (FRED GDPC1)</t>
         </is>
       </c>
     </row>
@@ -3343,16 +3400,17 @@
       <c r="C43" s="63" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="18">
-        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
-        <v/>
+      <c r="J43" s="18" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+        </is>
       </c>
       <c r="K43" s="19" t="inlineStr">
         <is>
-          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
-        </is>
-      </c>
-      <c r="L43" s="28" t="inlineStr">
+          <t>Macrotrends: LULU EV/EBITDA history</t>
+        </is>
+      </c>
+      <c r="L43" s="64" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3397,7 +3455,7 @@
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="64">
+      <c r="C47" s="65">
         <f>(C46+C32+C33)/C35</f>
         <v/>
       </c>
@@ -3413,18 +3471,18 @@
       <c r="D49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="65" t="inlineStr"/>
-      <c r="B50" s="66" t="inlineStr">
+      <c r="A50" s="66" t="inlineStr"/>
+      <c r="B50" s="67" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="66" t="inlineStr">
+      <c r="C50" s="67" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="66" t="inlineStr">
+      <c r="D50" s="67" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
@@ -3455,15 +3513,15 @@
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B52" s="67">
+      <c r="B52" s="68">
         <f>C29</f>
         <v/>
       </c>
-      <c r="C52" s="67">
+      <c r="C52" s="68">
         <f>C43</f>
         <v/>
       </c>
-      <c r="D52" s="67">
+      <c r="D52" s="68">
         <f>B52-C52</f>
         <v/>
       </c>
@@ -3487,30 +3545,30 @@
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="68">
+      <c r="B54" s="69">
         <f>C36</f>
         <v/>
       </c>
-      <c r="C54" s="68">
+      <c r="C54" s="69">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D54" s="68">
+      <c r="D54" s="69">
         <f>B54-C54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="69" t="inlineStr">
+      <c r="A55" s="70" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="70">
+      <c r="B55" s="71">
         <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C55" s="71">
+      <c r="C55" s="72">
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
@@ -3535,66 +3593,67 @@
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="72" t="inlineStr">
+      <c r="A59" s="73" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="73" t="n">
+      <c r="D59" s="74" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="73" t="n">
+      <c r="E59" s="74" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="73" t="n">
+      <c r="F59" s="74" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="73" t="n">
+      <c r="G59" s="74" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="73" t="n">
+      <c r="H59" s="74" t="n">
         <v>0.03</v>
       </c>
-      <c r="I59" s="28" t="inlineStr">
+      <c r="I59" s="64" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
       </c>
-      <c r="J59" s="18">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
-        <v/>
+      <c r="J59" s="18" t="inlineStr">
+        <is>
+          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
+        </is>
       </c>
       <c r="K59" s="19" t="inlineStr">
         <is>
-          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
+          <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="73" t="n">
+      <c r="A60" s="74" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="74">
+      <c r="D60" s="75">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E60" s="74">
+      <c r="E60" s="75">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F60" s="74">
+      <c r="F60" s="75">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G60" s="74">
+      <c r="G60" s="75">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H60" s="74">
+      <c r="H60" s="75">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I60" s="28" t="inlineStr">
+      <c r="I60" s="64" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
@@ -3606,165 +3665,175 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="73" t="n">
+      <c r="A61" s="74" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="74">
+      <c r="D61" s="75">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E61" s="74">
+      <c r="E61" s="75">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F61" s="74">
+      <c r="F61" s="75">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G61" s="74">
+      <c r="G61" s="75">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H61" s="74">
+      <c r="H61" s="75">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I61" s="28" t="inlineStr">
+      <c r="I61" s="64" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="73" t="n">
+      <c r="A62" s="74" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="74">
+      <c r="D62" s="75">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E62" s="74">
+      <c r="E62" s="75">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F62" s="75">
+      <c r="F62" s="76">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G62" s="74">
+      <c r="G62" s="75">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H62" s="74">
+      <c r="H62" s="75">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I62" s="28" t="inlineStr">
+      <c r="I62" s="64" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="73" t="n">
+      <c r="A63" s="74" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="74">
+      <c r="D63" s="75">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E63" s="74">
+      <c r="E63" s="75">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F63" s="74">
+      <c r="F63" s="75">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G63" s="74">
+      <c r="G63" s="75">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H63" s="74">
+      <c r="H63" s="75">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I63" s="28" t="inlineStr">
+      <c r="I63" s="64" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="73" t="n">
+      <c r="A64" s="74" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="74">
+      <c r="D64" s="75">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E64" s="74">
+      <c r="E64" s="75">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F64" s="74">
+      <c r="F64" s="75">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G64" s="74">
+      <c r="G64" s="75">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H64" s="74">
+      <c r="H64" s="75">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I64" s="28" t="inlineStr">
+      <c r="I64" s="64" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="J65" s="28" t="inlineStr">
-        <is>
-          <t>↳ Scenarios: WACC &amp; terminal g</t>
-        </is>
-      </c>
-      <c r="K65" s="19" t="inlineStr">
+      <c r="J65" s="18" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="L65" s="49">
-        <f>HYPERLINK("https://fred.stlouisfed.org/series/GDPC1","↳ FRED: Real GDP (GDPC1)")</f>
-        <v/>
+      <c r="K65" s="28" t="inlineStr">
+        <is>
+          <t>Scenarios: WACC &amp; terminal g</t>
+        </is>
+      </c>
+      <c r="L65" s="64" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId20"/>
     <hyperlink ref="L43" location="'Comps'!A26"/>
     <hyperlink ref="I59" location="'Scenarios'!D9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId21"/>
     <hyperlink ref="I60" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId22"/>
     <hyperlink ref="I61" location="'WACC'!C16"/>
     <hyperlink ref="I62" location="'WACC'!C16"/>
     <hyperlink ref="I63" location="'WACC'!C16"/>
     <hyperlink ref="I64" location="'WACC'!C16"/>
-    <hyperlink ref="J65" location="'Scenarios'!D8"/>
+    <hyperlink ref="K65" location="'Scenarios'!D8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3846,7 +3915,7 @@
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D6" s="28" t="inlineStr">
+      <c r="D6" s="64" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
@@ -3913,23 +3982,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="71" t="inlineStr">
+      <c r="A11" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="76">
+      <c r="C11" s="77">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="71" t="inlineStr">
+      <c r="A12" s="72" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C12" s="76">
+      <c r="C12" s="77">
         <f>C10/C7</f>
         <v/>
       </c>
@@ -3942,31 +4011,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="71" t="inlineStr">
+      <c r="A15" s="72" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="77" t="inlineStr">
+      <c r="A16" s="78" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C16" s="78" t="inlineStr">
+      <c r="C16" s="79" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="D16" s="77" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="E16" s="77" t="inlineStr">
+      <c r="E16" s="78" t="inlineStr">
         <is>
           <t>Justification</t>
+        </is>
+      </c>
+      <c r="F16" s="78" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
         </is>
       </c>
     </row>
@@ -3976,16 +4045,16 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C17" s="79">
+      <c r="C17" s="80">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
-      <c r="D17" s="37" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="E17" s="49" t="inlineStr">
+      <c r="F17" s="49" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
@@ -3997,16 +4066,17 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C18" s="80" t="n">
+      <c r="C18" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="D18" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/NKE/key-statistics/","↳ Yahoo Finance: NKE statistics")</f>
-        <v/>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE statistics</t>
         </is>
       </c>
     </row>
@@ -4016,16 +4086,17 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C19" s="80" t="n">
+      <c r="C19" s="81" t="n">
         <v>15</v>
       </c>
-      <c r="D19" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/DECK/key-statistics/","↳ Yahoo Finance: DECK statistics")</f>
-        <v/>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
+      <c r="E19" s="18" t="inlineStr">
         <is>
           <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: DECK statistics</t>
         </is>
       </c>
     </row>
@@ -4035,16 +4106,17 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C20" s="80" t="n">
+      <c r="C20" s="81" t="n">
         <v>25</v>
       </c>
-      <c r="D20" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/ONON/key-statistics/","↳ Yahoo Finance: ONON statistics")</f>
-        <v/>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: ONON statistics</t>
         </is>
       </c>
     </row>
@@ -4054,16 +4126,17 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C21" s="80" t="n">
+      <c r="C21" s="81" t="n">
         <v>12</v>
       </c>
-      <c r="D21" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/ADS.DE/key-statistics/","↳ Yahoo Finance: ADS.DE statistics")</f>
-        <v/>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
+      <c r="E21" s="18" t="inlineStr">
         <is>
           <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: ADS.DE statistics</t>
         </is>
       </c>
     </row>
@@ -4073,16 +4146,17 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C22" s="80" t="n">
+      <c r="C22" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/VFC/key-statistics/","↳ Yahoo Finance: VFC statistics")</f>
-        <v/>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: VFC statistics</t>
         </is>
       </c>
     </row>
@@ -4105,12 +4179,12 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="69" t="inlineStr">
+      <c r="A26" s="70" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C26" s="67">
+      <c r="C26" s="68">
         <f>DCF!C43</f>
         <v/>
       </c>
@@ -4118,7 +4192,7 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Spread (selectd (selected − Gordon implied)</t>
+          <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
       <c r="C27" s="58">
@@ -4127,7 +4201,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="69" t="inlineStr">
+      <c r="A28" s="70" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
@@ -4176,49 +4250,49 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="77" t="inlineStr">
+      <c r="A36" s="78" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C36" s="78" t="inlineStr">
+      <c r="C36" s="79" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D36" s="78" t="inlineStr">
+      <c r="D36" s="79" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E36" s="78" t="inlineStr">
+      <c r="E36" s="79" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F36" s="78" t="inlineStr">
+      <c r="F36" s="79" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
-      <c r="G36" s="81" t="inlineStr">
+      <c r="G36" s="82" t="inlineStr">
+        <is>
+          <t>Lo justification</t>
+        </is>
+      </c>
+      <c r="H36" s="82" t="inlineStr">
         <is>
           <t>Lo source</t>
         </is>
       </c>
-      <c r="H36" s="81" t="inlineStr">
-        <is>
-          <t>Lo justification</t>
-        </is>
-      </c>
-      <c r="I36" s="81" t="inlineStr">
+      <c r="I36" s="82" t="inlineStr">
+        <is>
+          <t>Hi justification</t>
+        </is>
+      </c>
+      <c r="J36" s="82" t="inlineStr">
         <is>
           <t>Hi source</t>
-        </is>
-      </c>
-      <c r="J36" s="81" t="inlineStr">
-        <is>
-          <t>Hi justification</t>
         </is>
       </c>
     </row>
@@ -4228,54 +4302,56 @@
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="C37" s="80" t="n">
+      <c r="C37" s="81" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37" s="80" t="n">
+      <c r="D37" s="81" t="n">
         <v>9.5</v>
       </c>
-      <c r="E37" s="82">
+      <c r="E37" s="83">
         <f>(C6*C37+C8)/C9</f>
         <v/>
       </c>
-      <c r="F37" s="82">
+      <c r="F37" s="83">
         <f>(C6*D37+C8)/C9</f>
         <v/>
       </c>
-      <c r="G37" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU EV/EBITDA")</f>
-        <v/>
+      <c r="G37" s="18" t="inlineStr">
+        <is>
+          <t>6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.</t>
+        </is>
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.</t>
-        </is>
-      </c>
-      <c r="I37" s="83">
-        <f>HYPERLINK("https://www.macrotrends.net/stocks/charts/LULU/lululemon-athletica/enterprise-value-ebitda","↳ Macrotrends: LULU EV/EBITDA history")</f>
-        <v/>
-      </c>
-      <c r="J37" s="84" t="inlineStr">
+          <t>Yahoo Finance: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="I37" s="84" t="inlineStr">
         <is>
           <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
+      <c r="J37" s="85" t="inlineStr">
+        <is>
+          <t>Macrotrends: LULU EV/EBITDA history</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="69" t="inlineStr">
+      <c r="A38" s="70" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="C38" s="85">
+      <c r="C38" s="86">
         <f>DCF!C43</f>
         <v/>
       </c>
-      <c r="E38" s="86">
+      <c r="E38" s="87">
         <f>(C6*C38+C8)/C9</f>
         <v/>
       </c>
-      <c r="I38" s="28" t="inlineStr">
+      <c r="I38" s="64" t="inlineStr">
         <is>
           <t>↳ DCF exit multiple</t>
         </is>
@@ -4287,35 +4363,36 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C39" s="80" t="n">
+      <c r="C39" s="81" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="80" t="n">
+      <c r="D39" s="81" t="n">
         <v>18</v>
       </c>
-      <c r="E39" s="82">
+      <c r="E39" s="83">
         <f>C7*C39</f>
         <v/>
       </c>
-      <c r="F39" s="82">
+      <c r="F39" s="83">
         <f>C7*D39</f>
         <v/>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.</t>
         </is>
       </c>
-      <c r="H39" s="84" t="inlineStr">
+      <c r="H39" s="19" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU P/E (FY26E)</t>
+        </is>
+      </c>
+      <c r="I39" s="84" t="inlineStr">
         <is>
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="I39" s="18">
-        <f>HYPERLINK("https://finance.yahoo.com/quote/LULU/key-statistics/","↳ Yahoo Finance: LULU P/E (FY26E)")</f>
-        <v/>
-      </c>
-      <c r="J39" s="83" t="inlineStr">
+      <c r="J39" s="85" t="inlineStr">
         <is>
           <t>Yahoo Finance: NKE P/E (peer benchmark)</t>
         </is>
@@ -4327,32 +4404,32 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C40" s="87" t="inlineStr">
+      <c r="C40" s="88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="87" t="inlineStr">
+      <c r="D40" s="88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="82">
+      <c r="E40" s="83">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F40" s="82">
+      <c r="F40" s="83">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="88" t="inlineStr">
+      <c r="A42" s="89" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="89" t="n">
+      <c r="C42" s="90" t="n">
         <v>100</v>
       </c>
       <c r="D42" s="59" t="inlineStr">
@@ -4381,11 +4458,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId18"/>
     <hyperlink ref="I38" location="'DCF'!C43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1487,7 +1487,7 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
+          <t>LULU Q2 FY2026 earnings release</t>
         </is>
       </c>
     </row>
@@ -1565,7 +1565,7 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>BEA: Real GDP (FRED GDPC1)</t>
+          <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 guidance / 10-K margins</t>
+          <t>LULU Q2 FY2026 earnings release</t>
         </is>
       </c>
       <c r="L7" s="49" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>BEA: Real GDP (FRED GDPC1)</t>
+          <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="K43" s="19" t="inlineStr">
         <is>
-          <t>Macrotrends: LULU EV/EBITDA history</t>
+          <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
       <c r="L43" s="64" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: ADS.DE statistics</t>
+          <t>Yahoo Finance: adidas (ADDYY)</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU EV/EBITDA</t>
+          <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
       <c r="I37" s="84" t="inlineStr">
@@ -4333,7 +4333,7 @@
       </c>
       <c r="J37" s="85" t="inlineStr">
         <is>
-          <t>Macrotrends: LULU EV/EBITDA history</t>
+          <t>StockAnalysis: LULU valuation</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU P/E (FY26E)</t>
+          <t>Yahoo Finance: LULU P/E</t>
         </is>
       </c>
       <c r="I39" s="84" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="J39" s="85" t="inlineStr">
         <is>
-          <t>Yahoo Finance: NKE P/E (peer benchmark)</t>
+          <t>Yahoo Finance: NKE P/E (peer)</t>
         </is>
       </c>
     </row>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -375,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -388,7 +388,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -406,7 +408,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -432,9 +434,6 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -478,7 +477,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -495,7 +494,6 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -521,9 +519,6 @@
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="166" fontId="38" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -597,7 +592,9 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1037,7 +1034,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions — justification then blue Source (click) in next column right</t>
+          <t>Red font  =  analyst assumptions — justification then blue Source &amp; where to find in next column right</t>
         </is>
       </c>
     </row>
@@ -1062,31 +1059,35 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="42" customHeight="1">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>SEC EDGAR XBRL company facts, CIK 0001397187 (Form 10-K, FY2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>SEC EDGAR filings, CIK 0001397187 (Form 10-K, FY2025)
+Find: Filter by Form 10-K; open FY2025 filing (accession 0001397187-26-000020).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>FY2025 Form 10-K (ended Feb 1, 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>FY2025 Form 10-K (ended Feb 1, 2026)
+Find: Interactive 10-K viewer → table of contents or Ctrl+F for financial statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)
+Find: Search 'outlook', 'guidance', or 'full year 2026' for revenue and diluted EPS ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Current share price (NASDAQ: LULU)</t>
+          <t>Current share price (NASDAQ: LULU)
+Find: Quote header → Last Sale / previous close for NASDAQ: LULU.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1121,7 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1146,11 +1147,11 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Source &amp; where to find</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Risk-free rate (10-yr UST)</t>
@@ -1166,11 +1167,12 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>FRED: 10Y Treasury (DGS10)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>FRED: 10Y Treasury (DGS10)
+Find: Latest DGS10 value in the chart/table (early Sep 2026 ≈ 4.3%); series title is 'Market Yield on U.S. Treasury Securities at 10-Year Constant Maturity'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
@@ -1186,11 +1188,12 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Damodaran: Historical Implied ERP
+Find: Scroll to 'Implied ERP' column; Jan-2026 row ≈ 4.2% — model uses 6.0% as conservative overlay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Levered beta</t>
@@ -1206,7 +1209,8 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU Beta</t>
+          <t>Yahoo Finance: LULU Beta
+Find: Statistics tab → 'Beta (5Y Monthly)'; Yahoo ≈ 0.86; model uses 0.95 with modest uplift.</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1232,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
@@ -1244,11 +1248,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K (no funded debt)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>LULU FY2025 10-K (no funded debt)
+Find: Ctrl+F 'revolving credit' or 'no outstanding borrowings' — confirms no funded term debt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -1264,7 +1269,8 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset</t>
+          <t>Damodaran: US tax rate dataset
+Find: Search 'Effective tax rate' for US firms; Damodaran blended rate supports ~27% normalized assumption.</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1292,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="42" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Equity weight</t>
@@ -1302,11 +1308,12 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
+          <t>LULU FY2025 10-K balance sheet
+Find: Balance Sheet → cash &amp; equity; no funded debt → 100% equity weight at market values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Debt weight</t>
@@ -1322,7 +1329,8 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K balance sheet</t>
+          <t>LULU FY2025 10-K balance sheet
+Find: Balance Sheet → confirm no long-term debt outstanding; debt weight set to 0%.</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1373,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1409,11 +1417,11 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source &amp; where to find</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
@@ -1435,11 +1443,12 @@
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>LULU Q2 FY2026 earnings release
+Find: Search release for 'full year 2026' net revenue outlook (−5% to −7%); model uses −6.1% midpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
@@ -1461,11 +1470,12 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>LULU historical revenue (10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>LULU historical revenue (10-K)
+Find: Income Statement → 'Net revenue' FY2022–FY2025; compute YoY growth vs historical double-digit run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>FY2026E EBIT margin</t>
@@ -1487,11 +1497,12 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>LULU Q2 FY2026 earnings release
+Find: Search release for FY2026 operating margin / EBIT commentary supporting ~13.9% base case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Terminal (FY2030E) EBIT margin</t>
@@ -1513,11 +1524,12 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>LULU historical EBIT margins (10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>LULU historical EBIT margins (10-K)
+Find: Income Statement → operating income ÷ net revenue; compare peak ~20–24% vs 15.5% terminal assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>WACC</t>
@@ -1537,13 +1549,14 @@
           <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
-        <is>
-          <t>WACC tab: CAPM build</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>WACC tab: CAPM build
+Find: Opens WACC tab → green WACC cell (10.0% base); built from CAPM inputs above it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Terminal growth</t>
@@ -1565,11 +1578,12 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+          <t>FRED: Real GDP (GDPC1)
+Find: GDPC1 chart → long-run real GDP growth trend (~2%); terminal g set at 2.25% (GDP + inflation cushion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
@@ -1591,11 +1605,12 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
+          <t>Damodaran: US tax rate dataset
+Find: Same Damodaran effective tax table; cross-check vs LULU ~29% recent effective rate in 10-K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
@@ -1617,11 +1632,12 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
+          <t>LULU CF statement (10-K)
+Find: Cash Flow Statement → 'Depreciation and amortization' ÷ net revenue (FY22–25 avg ≈ 4.5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
@@ -1643,11 +1659,12 @@
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
+          <t>LULU CF statement (10-K)
+Find: Cash Flow Statement → 'Capital expenditures' ÷ net revenue (recent ~5% of sales).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>NWC build % of Δrevenue</t>
@@ -1669,7 +1686,8 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)</t>
+          <t>LULU BS/IS historical (10-K)
+Find: Balance Sheet working capital vs Income Statement revenue changes (AR, inventory, AP, accrued).</t>
         </is>
       </c>
     </row>
@@ -1681,761 +1699,761 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <f>11102600*(1+C4)</f>
         <v/>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <f>11102600*(1+D4)</f>
         <v/>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="29">
         <f>C16*(1+C5)</f>
         <v/>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="29">
         <f>D16*(1+D5)</f>
         <v/>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="29">
         <f>E16*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="29">
         <f>C17*(1+C5)</f>
         <v/>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="29">
         <f>D17*(1+D5)</f>
         <v/>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="29">
         <f>E17*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <f>C18*(1+C5)</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <f>D18*(1+D5)</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <f>E18*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="29">
         <f>C19*(1+C5)</f>
         <v/>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="29">
         <f>D19*(1+D5)</f>
         <v/>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="29">
         <f>E19*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="30">
         <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="30">
         <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="30">
         <f>C6+(C7-C6)*1/4</f>
         <v/>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="30">
         <f>D6+(D7-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C23" s="31">
+      <c r="C23" s="30">
         <f>C6+(C7-C6)*2/4</f>
         <v/>
       </c>
-      <c r="D23" s="31">
+      <c r="D23" s="30">
         <f>D6+(D7-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="30">
         <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="30">
         <f>C6+(C7-C6)*3/4</f>
         <v/>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="30">
         <f>D6+(D7-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="30">
         <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="30">
         <f>C6+(C7-C6)*4/4</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="30">
         <f>D6+(D7-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="29">
         <f>C16*C21</f>
         <v/>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="29">
         <f>D16*D21</f>
         <v/>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="29">
         <f>E16*E21</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="29">
         <f>C17*C22</f>
         <v/>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="29">
         <f>D17*D22</f>
         <v/>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="29">
         <f>E17*E22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="C28" s="30">
+      <c r="C28" s="29">
         <f>C18*C23</f>
         <v/>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="29">
         <f>D18*D23</f>
         <v/>
       </c>
-      <c r="E28" s="30">
+      <c r="E28" s="29">
         <f>E18*E23</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <f>C19*C24</f>
         <v/>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <f>D19*D24</f>
         <v/>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <f>E19*E24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="29">
         <f>C20*C25</f>
         <v/>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="29">
         <f>D20*D25</f>
         <v/>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="29">
         <f>E20*E25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="29">
         <f>C26*(1-C10)</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="29">
         <f>D26*(1-D10)</f>
         <v/>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="29">
         <f>E26*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="29">
         <f>C27*(1-C10)</f>
         <v/>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="29">
         <f>D27*(1-D10)</f>
         <v/>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="29">
         <f>E27*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="29">
         <f>C28*(1-C10)</f>
         <v/>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="29">
         <f>D28*(1-D10)</f>
         <v/>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="29">
         <f>E28*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="29">
         <f>C29*(1-C10)</f>
         <v/>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <f>D29*(1-D10)</f>
         <v/>
       </c>
-      <c r="E34" s="30">
+      <c r="E34" s="29">
         <f>E29*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="29">
         <f>C30*(1-C10)</f>
         <v/>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="29">
         <f>D30*(1-D10)</f>
         <v/>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="29">
         <f>E30*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="29">
         <f>C16*C11</f>
         <v/>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <f>D16*D11</f>
         <v/>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="29">
         <f>E16*E11</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="29">
         <f>C17*C11</f>
         <v/>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <f>D17*D11</f>
         <v/>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="29">
         <f>E17*E11</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="29">
         <f>C18*C11</f>
         <v/>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="29">
         <f>D18*D11</f>
         <v/>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="29">
         <f>E18*E11</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="29">
         <f>C19*C11</f>
         <v/>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="29">
         <f>D19*D11</f>
         <v/>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="29">
         <f>E19*E11</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="C40" s="30">
+      <c r="C40" s="29">
         <f>C20*C11</f>
         <v/>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="29">
         <f>D20*D11</f>
         <v/>
       </c>
-      <c r="E40" s="30">
+      <c r="E40" s="29">
         <f>E20*E11</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="29">
         <f>C16*C12</f>
         <v/>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <f>D16*D12</f>
         <v/>
       </c>
-      <c r="E41" s="30">
+      <c r="E41" s="29">
         <f>E16*E12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="29">
         <f>C17*C12</f>
         <v/>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="29">
         <f>D17*D12</f>
         <v/>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="29">
         <f>E17*E12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="29">
         <f>C18*C12</f>
         <v/>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="29">
         <f>D18*D12</f>
         <v/>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="29">
         <f>E18*E12</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="29">
         <f>C19*C12</f>
         <v/>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="29">
         <f>D19*D12</f>
         <v/>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="29">
         <f>E19*E12</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="C45" s="30">
+      <c r="C45" s="29">
         <f>C20*C12</f>
         <v/>
       </c>
-      <c r="D45" s="30">
+      <c r="D45" s="29">
         <f>D20*D12</f>
         <v/>
       </c>
-      <c r="E45" s="30">
+      <c r="E45" s="29">
         <f>E20*E12</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="C46" s="30">
+      <c r="C46" s="29">
         <f>C13*(C16-11102600)</f>
         <v/>
       </c>
-      <c r="D46" s="30">
+      <c r="D46" s="29">
         <f>D13*(D16-11102600)</f>
         <v/>
       </c>
-      <c r="E46" s="30">
+      <c r="E46" s="29">
         <f>E13*(E16-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="C47" s="30">
+      <c r="C47" s="29">
         <f>C13*(C17-C16)</f>
         <v/>
       </c>
-      <c r="D47" s="30">
+      <c r="D47" s="29">
         <f>D13*(D17-D16)</f>
         <v/>
       </c>
-      <c r="E47" s="30">
+      <c r="E47" s="29">
         <f>E13*(E17-E16)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="C48" s="30">
+      <c r="C48" s="29">
         <f>C13*(C18-C17)</f>
         <v/>
       </c>
-      <c r="D48" s="30">
+      <c r="D48" s="29">
         <f>D13*(D18-D17)</f>
         <v/>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="29">
         <f>E13*(E18-E17)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="C49" s="30">
+      <c r="C49" s="29">
         <f>C13*(C19-C18)</f>
         <v/>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="29">
         <f>D13*(D19-D18)</f>
         <v/>
       </c>
-      <c r="E49" s="30">
+      <c r="E49" s="29">
         <f>E13*(E19-E18)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="C50" s="30">
+      <c r="C50" s="29">
         <f>C13*(C20-C19)</f>
         <v/>
       </c>
-      <c r="D50" s="30">
+      <c r="D50" s="29">
         <f>D13*(D20-D19)</f>
         <v/>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="29">
         <f>E13*(E20-E19)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C51" s="30">
+      <c r="C51" s="29">
         <f>C31+C36-C41-C46</f>
         <v/>
       </c>
-      <c r="D51" s="30">
+      <c r="D51" s="29">
         <f>D31+D36-D41-D46</f>
         <v/>
       </c>
-      <c r="E51" s="30">
+      <c r="E51" s="29">
         <f>E31+E36-E41-E46</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C52" s="30">
+      <c r="C52" s="29">
         <f>C32+C37-C42-C47</f>
         <v/>
       </c>
-      <c r="D52" s="30">
+      <c r="D52" s="29">
         <f>D32+D37-D42-D47</f>
         <v/>
       </c>
-      <c r="E52" s="30">
+      <c r="E52" s="29">
         <f>E32+E37-E42-E47</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C53" s="30">
+      <c r="C53" s="29">
         <f>C33+C38-C43-C48</f>
         <v/>
       </c>
-      <c r="D53" s="30">
+      <c r="D53" s="29">
         <f>D33+D38-D43-D48</f>
         <v/>
       </c>
-      <c r="E53" s="30">
+      <c r="E53" s="29">
         <f>E33+E38-E43-E48</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C54" s="30">
+      <c r="C54" s="29">
         <f>C34+C39-C44-C49</f>
         <v/>
       </c>
-      <c r="D54" s="30">
+      <c r="D54" s="29">
         <f>D34+D39-D44-D49</f>
         <v/>
       </c>
-      <c r="E54" s="30">
+      <c r="E54" s="29">
         <f>E34+E39-E44-E49</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C55" s="30">
+      <c r="C55" s="29">
         <f>C35+C40-C45-C50</f>
         <v/>
       </c>
-      <c r="D55" s="30">
+      <c r="D55" s="29">
         <f>D35+D40-D45-D50</f>
         <v/>
       </c>
-      <c r="E55" s="30">
+      <c r="E55" s="29">
         <f>E35+E40-E45-E50</f>
         <v/>
       </c>
@@ -2446,34 +2464,34 @@
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="31">
         <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
         <v/>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="31">
         <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
         <v/>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="31">
         <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C58" s="34">
+      <c r="C58" s="33">
         <f>(C57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D58" s="35">
+      <c r="D58" s="34">
         <f>(D57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="E58" s="34">
+      <c r="E58" s="33">
         <f>(E57+1807202-0)/111380</f>
         <v/>
       </c>
@@ -2484,21 +2502,21 @@
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="35">
         <f>C58/100.0-1</f>
         <v/>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="35">
         <f>D58/100.0-1</f>
         <v/>
       </c>
-      <c r="E59" s="36">
+      <c r="E59" s="35">
         <f>E58/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2533,15 +2551,15 @@
     <col width="40" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -2560,69 +2578,70 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="38" t="inlineStr">
+      <c r="C2" s="37" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="39" t="inlineStr">
+      <c r="D2" s="38" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="39" t="inlineStr">
+      <c r="E2" s="38" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="39" t="inlineStr">
+      <c r="F2" s="38" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="G2" s="38" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="39" t="inlineStr">
+      <c r="H2" s="38" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="I2" s="40" t="inlineStr">
+      <c r="I2" s="39" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="J2" s="41" t="inlineStr">
+      <c r="J2" s="40" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="K2" s="41" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="K2" s="40" t="inlineStr">
+        <is>
+          <t>Source &amp; where to find</t>
+        </is>
+      </c>
+      <c r="L2" s="40" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="42" t="inlineStr">
+    <row r="3" ht="42" customHeight="1">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
-      <c r="C3" s="43" t="inlineStr">
-        <is>
-          <t>10-K source</t>
-        </is>
-      </c>
-      <c r="I3" s="44" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
+        <is>
+          <t>10-K source
+Find: Interactive 10-K viewer → table of contents or Ctrl+F for financial statements.</t>
+        </is>
+      </c>
+      <c r="I3" s="43" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2634,57 +2653,57 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="C5" s="44" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="45">
         <f>Scenarios!D16</f>
         <v/>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="45">
         <f>Scenarios!D17</f>
         <v/>
       </c>
-      <c r="F5" s="46">
+      <c r="F5" s="45">
         <f>Scenarios!D18</f>
         <v/>
       </c>
-      <c r="G5" s="46">
+      <c r="G5" s="45">
         <f>Scenarios!D19</f>
         <v/>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="45">
         <f>Scenarios!D20</f>
         <v/>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="46">
         <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="47">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="47">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="47">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="47">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="47">
         <f>H5/G5-1</f>
         <v/>
       </c>
@@ -2695,42 +2714,44 @@
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="L6" s="49" t="inlineStr">
-        <is>
-          <t>LULU historical revenue (10-K)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>LULU Q2 FY2026 earnings release
+Find: Search release for 'full year 2026' net revenue outlook (−5% to −7%); model uses −6.1% midpoint.</t>
+        </is>
+      </c>
+      <c r="L6" s="42" t="inlineStr">
+        <is>
+          <t>LULU historical revenue (10-K)
+Find: Income Statement → 'Net revenue' FY2022–FY2025; compute YoY growth vs historical double-digit run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="47">
         <f>Scenarios!D21</f>
         <v/>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="47">
         <f>Scenarios!D22</f>
         <v/>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="47">
         <f>Scenarios!D23</f>
         <v/>
       </c>
-      <c r="G7" s="48">
+      <c r="G7" s="47">
         <f>Scenarios!D24</f>
         <v/>
       </c>
-      <c r="H7" s="48">
+      <c r="H7" s="47">
         <f>Scenarios!D25</f>
         <v/>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="46">
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2741,12 +2762,14 @@
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="L7" s="49" t="inlineStr">
-        <is>
-          <t>LULU historical EBIT margins (10-K)</t>
+          <t>LULU Q2 FY2026 earnings release
+Find: Search release for FY2026 operating margin / EBIT commentary supporting ~13.9% base case.</t>
+        </is>
+      </c>
+      <c r="L7" s="42" t="inlineStr">
+        <is>
+          <t>LULU historical EBIT margins (10-K)
+Find: Income Statement → operating income ÷ net revenue; compare peak ~20–24% vs 15.5% terminal assumption.</t>
         </is>
       </c>
     </row>
@@ -2756,30 +2779,30 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="C8" s="48" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="31">
         <f>Scenarios!D26</f>
         <v/>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="31">
         <f>Scenarios!D27</f>
         <v/>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="31">
         <f>Scenarios!D28</f>
         <v/>
       </c>
-      <c r="G8" s="32">
+      <c r="G8" s="31">
         <f>Scenarios!D29</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="31">
         <f>Scenarios!D30</f>
         <v/>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="49">
         <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2790,23 +2813,23 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="46">
+      <c r="D9" s="45">
         <f>-Scenarios!D26*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="E9" s="46">
+      <c r="E9" s="45">
         <f>-Scenarios!D27*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="F9" s="46">
+      <c r="F9" s="45">
         <f>-Scenarios!D28*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="G9" s="46">
+      <c r="G9" s="45">
         <f>-Scenarios!D29*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="45">
         <f>-Scenarios!D30*Scenarios!$D$10</f>
         <v/>
       </c>
@@ -2817,32 +2840,32 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="31">
         <f>Scenarios!D31</f>
         <v/>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <f>Scenarios!D32</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <f>Scenarios!D33</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="31">
         <f>Scenarios!D34</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="31">
         <f>Scenarios!D35</f>
         <v/>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="49">
         <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="42" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A % of revenue</t>
@@ -2875,7 +2898,8 @@
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)</t>
+          <t>LULU CF statement (10-K)
+Find: Cash Flow Statement → 'Depreciation and amortization' ÷ net revenue (FY22–25 avg ≈ 4.5%).</t>
         </is>
       </c>
     </row>
@@ -2885,32 +2909,32 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="45">
         <f>Scenarios!D36</f>
         <v/>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="45">
         <f>Scenarios!D37</f>
         <v/>
       </c>
-      <c r="F12" s="46">
+      <c r="F12" s="45">
         <f>Scenarios!D38</f>
         <v/>
       </c>
-      <c r="G12" s="46">
+      <c r="G12" s="45">
         <f>Scenarios!D39</f>
         <v/>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="45">
         <f>Scenarios!D40</f>
         <v/>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="46">
         <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
@@ -2943,7 +2967,8 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)</t>
+          <t>LULU CF statement (10-K)
+Find: Cash Flow Statement → 'Capital expenditures' ÷ net revenue (recent ~5% of sales).</t>
         </is>
       </c>
     </row>
@@ -2953,32 +2978,32 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="45">
         <f>-Scenarios!D41</f>
         <v/>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="45">
         <f>-Scenarios!D42</f>
         <v/>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="45">
         <f>-Scenarios!D43</f>
         <v/>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="45">
         <f>-Scenarios!D44</f>
         <v/>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="45">
         <f>-Scenarios!D45</f>
         <v/>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="46">
         <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="42" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
@@ -3011,7 +3036,8 @@
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)</t>
+          <t>LULU BS/IS historical (10-K)
+Find: Balance Sheet working capital vs Income Statement revenue changes (AR, inventory, AP, accrued).</t>
         </is>
       </c>
     </row>
@@ -3021,33 +3047,33 @@
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="45">
         <f>-Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="45">
         <f>-Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="45">
         <f>-Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="45">
         <f>-Scenarios!D49</f>
         <v/>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="45">
         <f>-Scenarios!D50</f>
         <v/>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="46">
         <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
@@ -3059,27 +3085,27 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="50">
         <f>Scenarios!D51</f>
         <v/>
       </c>
-      <c r="E18" s="52">
+      <c r="E18" s="50">
         <f>Scenarios!D52</f>
         <v/>
       </c>
-      <c r="F18" s="52">
+      <c r="F18" s="50">
         <f>Scenarios!D53</f>
         <v/>
       </c>
-      <c r="G18" s="52">
+      <c r="G18" s="50">
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H18" s="52">
+      <c r="H18" s="50">
         <f>Scenarios!D55</f>
         <v/>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="49">
         <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3090,19 +3116,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="D19" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="53" t="n">
+      <c r="E19" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="53" t="n">
+      <c r="F19" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="53" t="n">
+      <c r="G19" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="53" t="n">
+      <c r="H19" s="51" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3112,23 +3138,23 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D20" s="54">
+      <c r="D20" s="52">
         <f>1/(1+Scenarios!$D$8)^D19</f>
         <v/>
       </c>
-      <c r="E20" s="54">
+      <c r="E20" s="52">
         <f>1/(1+Scenarios!$D$8)^E19</f>
         <v/>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="52">
         <f>1/(1+Scenarios!$D$8)^F19</f>
         <v/>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="52">
         <f>1/(1+Scenarios!$D$8)^G19</f>
         <v/>
       </c>
-      <c r="H20" s="54">
+      <c r="H20" s="52">
         <f>1/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
@@ -3139,23 +3165,23 @@
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="31">
         <f>D18*D20</f>
         <v/>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <f>E18*E20</f>
         <v/>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="31">
         <f>F18*F20</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="31">
         <f>G18*G20</f>
         <v/>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="31">
         <f>H18*H20</f>
         <v/>
       </c>
@@ -3166,13 +3192,13 @@
           <t>Scenarios linkage summary (column I should all read OK)</t>
         </is>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="53">
         <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="inlineStr">
+      <c r="A24" s="54" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3186,18 +3212,18 @@
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="55">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="47">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
@@ -3208,7 +3234,8 @@
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)</t>
+          <t>FRED: Real GDP (GDPC1)
+Find: GDPC1 chart → long-run real GDP growth trend (~2%); terminal g set at 2.25% (GDP + inflation cushion).</t>
         </is>
       </c>
     </row>
@@ -3218,7 +3245,7 @@
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="31">
         <f>H8+H12</f>
         <v/>
       </c>
@@ -3229,7 +3256,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="C28" s="46">
+      <c r="C28" s="45">
         <f>H18*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
@@ -3240,7 +3267,7 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C29" s="58">
+      <c r="C29" s="56">
         <f>C28/C27</f>
         <v/>
       </c>
@@ -3251,7 +3278,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C30" s="57">
+      <c r="C30" s="55">
         <f>C28/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
@@ -3262,38 +3289,40 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C31" s="32">
+      <c r="C31" s="31">
         <f>C25+C30</f>
         <v/>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C32" s="45" t="n">
+      <c r="C32" s="44" t="n">
         <v>1807202</v>
       </c>
-      <c r="D32" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
+      <c r="D32" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C33" s="45" t="n">
+      <c r="C33" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
+      <c r="D33" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
         </is>
       </c>
     </row>
@@ -3303,23 +3332,24 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="31">
         <f>C31+C32+C33</f>
         <v/>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="42" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n">
+      <c r="C35" s="44" t="n">
         <v>111380</v>
       </c>
-      <c r="D35" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
+      <c r="D35" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Income Statement/EPS footnote → 'Diluted weighted-average shares outstanding'.</t>
         </is>
       </c>
     </row>
@@ -3329,27 +3359,28 @@
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C36" s="60">
+      <c r="C36" s="57">
         <f>C34/C35</f>
         <v/>
       </c>
-      <c r="I36" s="51">
+      <c r="I36" s="49">
         <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C37" s="61" t="n">
+      <c r="C37" s="58" t="n">
         <v>100</v>
       </c>
-      <c r="D37" s="59" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
+      <c r="D37" s="42" t="inlineStr">
+        <is>
+          <t>NASDAQ
+Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3390,7 @@
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C38" s="62">
+      <c r="C38" s="59">
         <f>C36/C37-1</f>
         <v/>
       </c>
@@ -3370,13 +3401,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="47">
         <f>C30/C31</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="54" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3391,13 +3422,13 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="42" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C43" s="63" t="n">
+      <c r="C43" s="60" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="18" t="inlineStr">
@@ -3407,10 +3438,11 @@
       </c>
       <c r="K43" s="19" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="L43" s="64" t="inlineStr">
+          <t>StockAnalysis: LULU EV/EBITDA
+Find: Valuation section → 'EV/EBITDA' (forward or TTM); 8.0x = football-field midpoint on FY2030E EBITDA.</t>
+        </is>
+      </c>
+      <c r="L43" s="61" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3422,7 +3454,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="C44" s="46">
+      <c r="C44" s="45">
         <f>C27*C43</f>
         <v/>
       </c>
@@ -3433,7 +3465,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C45" s="46">
+      <c r="C45" s="45">
         <f>C44/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
@@ -3444,7 +3476,7 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="31">
         <f>C25+C45</f>
         <v/>
       </c>
@@ -3455,13 +3487,13 @@
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="65">
+      <c r="C47" s="62">
         <f>(C46+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="54" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3471,18 +3503,18 @@
       <c r="D49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="66" t="inlineStr"/>
-      <c r="B50" s="67" t="inlineStr">
+      <c r="A50" s="63" t="inlineStr"/>
+      <c r="B50" s="64" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="67" t="inlineStr">
+      <c r="C50" s="64" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="67" t="inlineStr">
+      <c r="D50" s="64" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
@@ -3494,15 +3526,15 @@
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="57">
+      <c r="B51" s="55">
         <f>C28</f>
         <v/>
       </c>
-      <c r="C51" s="57">
+      <c r="C51" s="55">
         <f>C44</f>
         <v/>
       </c>
-      <c r="D51" s="57">
+      <c r="D51" s="55">
         <f>B51-C51</f>
         <v/>
       </c>
@@ -3513,15 +3545,15 @@
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B52" s="68">
+      <c r="B52" s="65">
         <f>C29</f>
         <v/>
       </c>
-      <c r="C52" s="68">
+      <c r="C52" s="65">
         <f>C43</f>
         <v/>
       </c>
-      <c r="D52" s="68">
+      <c r="D52" s="65">
         <f>B52-C52</f>
         <v/>
       </c>
@@ -3532,9 +3564,9 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B53" s="48" t="inlineStr"/>
-      <c r="C53" s="48" t="inlineStr"/>
-      <c r="D53" s="48">
+      <c r="B53" s="47" t="inlineStr"/>
+      <c r="C53" s="47" t="inlineStr"/>
+      <c r="D53" s="47">
         <f>(B51-C51)/B51</f>
         <v/>
       </c>
@@ -3545,41 +3577,41 @@
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="69">
+      <c r="B54" s="66">
         <f>C36</f>
         <v/>
       </c>
-      <c r="C54" s="69">
+      <c r="C54" s="66">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D54" s="69">
+      <c r="D54" s="66">
         <f>B54-C54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="70" t="inlineStr">
+      <c r="A55" s="67" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="71">
+      <c r="B55" s="68">
         <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C55" s="72">
+      <c r="C55" s="69">
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D55" s="37" t="inlineStr">
+      <c r="D55" s="36" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="56" t="inlineStr">
+      <c r="A58" s="54" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -3592,28 +3624,28 @@
       <c r="G58" s="13" t="n"/>
       <c r="H58" s="13" t="n"/>
     </row>
-    <row r="59">
-      <c r="A59" s="73" t="inlineStr">
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="70" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="74" t="n">
+      <c r="D59" s="71" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="74" t="n">
+      <c r="E59" s="71" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="74" t="n">
+      <c r="F59" s="71" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="74" t="n">
+      <c r="G59" s="71" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="74" t="n">
+      <c r="H59" s="71" t="n">
         <v>0.03</v>
       </c>
-      <c r="I59" s="64" t="inlineStr">
+      <c r="I59" s="61" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
@@ -3625,179 +3657,183 @@
       </c>
       <c r="K59" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="74" t="n">
+          <t>FRED: Real GDP (GDPC1)
+Find: GDPC1 long-run growth bounds terminal-g sensitivity (1.5%–3.0% vs 2.25% base).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="71" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="75">
+      <c r="D60" s="72">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E60" s="75">
+      <c r="E60" s="72">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F60" s="75">
+      <c r="F60" s="72">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G60" s="75">
+      <c r="G60" s="72">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H60" s="75">
+      <c r="H60" s="72">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I60" s="64" t="inlineStr">
+      <c r="I60" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
-      <c r="J60" s="49" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
+      <c r="J60" s="42" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP
+Find: Damodaran implied ERP table anchors discount-rate range; ±100bps around 10.0% WACC base.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="74" t="n">
+      <c r="A61" s="71" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="75">
+      <c r="D61" s="72">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E61" s="75">
+      <c r="E61" s="72">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F61" s="75">
+      <c r="F61" s="72">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G61" s="75">
+      <c r="G61" s="72">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H61" s="75">
+      <c r="H61" s="72">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I61" s="64" t="inlineStr">
+      <c r="I61" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="74" t="n">
+      <c r="A62" s="71" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="75">
+      <c r="D62" s="72">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E62" s="75">
+      <c r="E62" s="72">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F62" s="76">
+      <c r="F62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G62" s="75">
+      <c r="G62" s="72">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H62" s="75">
+      <c r="H62" s="72">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I62" s="64" t="inlineStr">
+      <c r="I62" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="74" t="n">
+      <c r="A63" s="71" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="75">
+      <c r="D63" s="72">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E63" s="75">
+      <c r="E63" s="72">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F63" s="75">
+      <c r="F63" s="72">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G63" s="75">
+      <c r="G63" s="72">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H63" s="75">
+      <c r="H63" s="72">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I63" s="64" t="inlineStr">
+      <c r="I63" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="74" t="n">
+      <c r="A64" s="71" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="75">
+      <c r="D64" s="72">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E64" s="75">
+      <c r="E64" s="72">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F64" s="75">
+      <c r="F64" s="72">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G64" s="75">
+      <c r="G64" s="72">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H64" s="75">
+      <c r="H64" s="72">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I64" s="64" t="inlineStr">
+      <c r="I64" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="42" customHeight="1">
       <c r="J65" s="18" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="K65" s="28" t="inlineStr">
-        <is>
-          <t>Scenarios: WACC &amp; terminal g</t>
-        </is>
-      </c>
-      <c r="L65" s="64" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
+      <c r="K65" s="19" t="inlineStr">
+        <is>
+          <t>Scenarios: WACC &amp; terminal g
+Find: Opens Scenarios tab → WACC row and Terminal g row (base case inputs for sensitivity grid).</t>
+        </is>
+      </c>
+      <c r="L65" s="42" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)
+Find: GDPC1 long-run growth bounds terminal-g sensitivity (1.5%–3.0% vs 2.25% base).</t>
         </is>
       </c>
     </row>
@@ -3851,13 +3887,13 @@
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -3879,18 +3915,19 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="45" t="n">
+      <c r="C4" s="44" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Consolidated Statements of Operations → search 'Net revenue', 'Operating income', etc.</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3937,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="45">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -3911,94 +3948,98 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="46">
+      <c r="C6" s="45">
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D6" s="64" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="61" t="n">
+      <c r="C7" s="58" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D7" s="59" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7" s="42" t="inlineStr">
+        <is>
+          <t>Release
+Find: Search 'diluted earnings per share' and 'net revenue' for Q2/FY2026 guidance ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="44" t="n">
         <v>1807202</v>
       </c>
-      <c r="D8" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="44" t="n">
         <v>111380</v>
       </c>
-      <c r="D9" s="59" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
+      <c r="D9" s="42" t="inlineStr">
+        <is>
+          <t>10-K
+Find: Income Statement/EPS footnote → 'Diluted weighted-average shares outstanding'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="61" t="n">
+      <c r="C10" s="58" t="n">
         <v>100</v>
       </c>
-      <c r="D10" s="59" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>NASDAQ
+Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="72" t="inlineStr">
+      <c r="A11" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="74">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="72" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="74">
         <f>C10/C7</f>
         <v/>
       </c>
@@ -4011,62 +4052,63 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="72" t="inlineStr">
+      <c r="A15" s="69" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="78" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="76" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="E16" s="78" t="inlineStr">
+      <c r="E16" s="75" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="F16" s="78" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
+      <c r="F16" s="75" t="inlineStr">
+        <is>
+          <t>Source &amp; where to find</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C17" s="80">
+      <c r="C17" s="77">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="E17" s="36" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17" s="42" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K
+Find: Ctrl+F the line-item name in FY2025 consolidated financial statements.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C18" s="81" t="n">
+      <c r="C18" s="78" t="n">
         <v>18</v>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -4076,17 +4118,18 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: NKE statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
+          <t>Yahoo Finance: NKE statistics
+Find: Statistics → 'Enterprise Value/EBITDA' or forward EV/EBITDA; illustrative ~18x mature peer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C19" s="81" t="n">
+      <c r="C19" s="78" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
@@ -4096,17 +4139,18 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: DECK statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
+          <t>Yahoo Finance: DECK statistics
+Find: Statistics → EV/EBITDA; Deckers trades ~15x on HOKA/UGG momentum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C20" s="81" t="n">
+      <c r="C20" s="78" t="n">
         <v>25</v>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -4116,17 +4160,18 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: ONON statistics</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>Yahoo Finance: ONON statistics
+Find: Statistics → EV/EBITDA; On ~25x as high-growth premium athletic benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C21" s="81" t="n">
+      <c r="C21" s="78" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -4136,17 +4181,18 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: adidas (ADDYY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
+          <t>Yahoo Finance: adidas (ADDYY)
+Find: Statistics → EV/EBITDA for ADDYY ADR; adidas ~12x restructuring incumbent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="42" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C22" s="81" t="n">
+      <c r="C22" s="78" t="n">
         <v>10</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
@@ -4156,7 +4202,8 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: VFC statistics</t>
+          <t>Yahoo Finance: VFC statistics
+Find: Statistics → EV/EBITDA; VFC ~10x as lower-bound scaled apparel peer.</t>
         </is>
       </c>
     </row>
@@ -4173,18 +4220,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C25" s="58">
+      <c r="C25" s="56">
         <f>DCF!C29</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="70" t="inlineStr">
+      <c r="A26" s="67" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C26" s="68">
+      <c r="C26" s="65">
         <f>DCF!C43</f>
         <v/>
       </c>
@@ -4195,48 +4242,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C27" s="58">
+      <c r="C27" s="56">
         <f>C26-C25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="70" t="inlineStr">
+      <c r="A28" s="67" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="28" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="28" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="28" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="28" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4250,69 +4297,69 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="78" t="inlineStr">
+      <c r="A36" s="75" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="76" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="76" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E36" s="79" t="inlineStr">
+      <c r="E36" s="76" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F36" s="79" t="inlineStr">
+      <c r="F36" s="76" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
-      <c r="G36" s="82" t="inlineStr">
+      <c r="G36" s="79" t="inlineStr">
         <is>
           <t>Lo justification</t>
         </is>
       </c>
-      <c r="H36" s="82" t="inlineStr">
-        <is>
-          <t>Lo source</t>
-        </is>
-      </c>
-      <c r="I36" s="82" t="inlineStr">
+      <c r="H36" s="79" t="inlineStr">
+        <is>
+          <t>Lo source &amp; find</t>
+        </is>
+      </c>
+      <c r="I36" s="79" t="inlineStr">
         <is>
           <t>Hi justification</t>
         </is>
       </c>
-      <c r="J36" s="82" t="inlineStr">
-        <is>
-          <t>Hi source</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
+      <c r="J36" s="79" t="inlineStr">
+        <is>
+          <t>Hi source &amp; find</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="C37" s="81" t="n">
+      <c r="C37" s="78" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37" s="81" t="n">
+      <c r="D37" s="78" t="n">
         <v>9.5</v>
       </c>
-      <c r="E37" s="83">
+      <c r="E37" s="80">
         <f>(C6*C37+C8)/C9</f>
         <v/>
       </c>
-      <c r="F37" s="83">
+      <c r="F37" s="80">
         <f>(C6*D37+C8)/C9</f>
         <v/>
       </c>
@@ -4323,57 +4370,59 @@
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="I37" s="84" t="inlineStr">
+          <t>StockAnalysis: LULU EV/EBITDA
+Find: Same EV/EBITDA field; 6.5x = bear terminal exit below Gordon-implied ~7x.</t>
+        </is>
+      </c>
+      <c r="I37" s="81" t="inlineStr">
         <is>
           <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
-      <c r="J37" s="85" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU valuation</t>
+      <c r="J37" s="82" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU valuation
+Find: Same EV/EBITDA field; 9.5x = bull terminal exit above 8.0x DCF base.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="70" t="inlineStr">
+      <c r="A38" s="67" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="83">
         <f>DCF!C43</f>
         <v/>
       </c>
-      <c r="E38" s="87">
+      <c r="E38" s="84">
         <f>(C6*C38+C8)/C9</f>
         <v/>
       </c>
-      <c r="I38" s="64" t="inlineStr">
+      <c r="I38" s="61" t="inlineStr">
         <is>
           <t>↳ DCF exit multiple</t>
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="42" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C39" s="81" t="n">
+      <c r="C39" s="78" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="81" t="n">
+      <c r="D39" s="78" t="n">
         <v>18</v>
       </c>
-      <c r="E39" s="83">
+      <c r="E39" s="80">
         <f>C7*C39</f>
         <v/>
       </c>
-      <c r="F39" s="83">
+      <c r="F39" s="80">
         <f>C7*D39</f>
         <v/>
       </c>
@@ -4384,17 +4433,19 @@
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU P/E</t>
-        </is>
-      </c>
-      <c r="I39" s="84" t="inlineStr">
+          <t>Yahoo Finance: LULU P/E
+Find: Statistics → 'Trailing P/E' or forward P/E on depressed FY26E EPS (~10x trough).</t>
+        </is>
+      </c>
+      <c r="I39" s="81" t="inlineStr">
         <is>
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="J39" s="85" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: NKE P/E (peer)</t>
+      <c r="J39" s="82" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE P/E (peer)
+Find: NKE forward P/E as mature-peer ceiling; 18x on LULU FY26E recovery case.</t>
         </is>
       </c>
     </row>
@@ -4404,42 +4455,43 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C40" s="88" t="inlineStr">
+      <c r="C40" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="88" t="inlineStr">
+      <c r="D40" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="83">
+      <c r="E40" s="80">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F40" s="83">
+      <c r="F40" s="80">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="89" t="inlineStr">
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="86" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="90" t="n">
+      <c r="C42" s="87" t="n">
         <v>100</v>
       </c>
-      <c r="D42" s="59" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
+      <c r="D42" s="42" t="inlineStr">
+        <is>
+          <t>NASDAQ
+Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1034,7 +1034,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions — justification then blue Source &amp; where to find in next column right</t>
+          <t>Red font  =  analyst assumptions — justification then blue source with Ctrl+F lines in next column</t>
         </is>
       </c>
     </row>
@@ -1059,35 +1059,35 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="B18" s="10" t="inlineStr">
         <is>
           <t>SEC EDGAR filings, CIK 0001397187 (Form 10-K, FY2025)
-Find: Filter by Form 10-K; open FY2025 filing (accession 0001397187-26-000020).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
+Ctrl+F: "10-K" → FY2025 accession 0001397187-26-000020</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="B19" s="10" t="inlineStr">
         <is>
           <t>FY2025 Form 10-K (ended Feb 1, 2026)
-Find: Interactive 10-K viewer → table of contents or Ctrl+F for financial statements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
+Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)
-Find: Search 'outlook', 'guidance', or 'full year 2026' for revenue and diluted EPS ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
+Ctrl+F: "full year 2026" | "net revenue" | "diluted earnings per share"</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Current share price (NASDAQ: LULU)
-Find: Quote header → Last Sale / previous close for NASDAQ: LULU.</t>
+Ctrl+F: "LULU" → Last Sale / Previous Close price</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1147,11 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Source &amp; where to find</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1">
+          <t>Source &amp; Ctrl+F lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Risk-free rate (10-yr UST)</t>
@@ -1168,11 +1168,11 @@
       <c r="E3" s="19" t="inlineStr">
         <is>
           <t>FRED: 10Y Treasury (DGS10)
-Find: Latest DGS10 value in the chart/table (early Sep 2026 ≈ 4.3%); series title is 'Market Yield on U.S. Treasury Securities at 10-Year Constant Maturity'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
+Ctrl+F: "DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
@@ -1189,11 +1189,11 @@
       <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP
-Find: Scroll to 'Implied ERP' column; Jan-2026 row ≈ 4.2% — model uses 6.0% as conservative overlay.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+Ctrl+F: "Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Levered beta</t>
@@ -1210,7 +1210,7 @@
       <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Beta
-Find: Statistics tab → 'Beta (5Y Monthly)'; Yahoo ≈ 0.86; model uses 0.95 with modest uplift.</t>
+Ctrl+F: "Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
@@ -1249,11 +1249,11 @@
       <c r="E9" s="19" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K (no funded debt)
-Find: Ctrl+F 'revolving credit' or 'no outstanding borrowings' — confirms no funded term debt.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+Ctrl+F: "no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -1270,7 +1270,7 @@
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>Damodaran: US tax rate dataset
-Find: Search 'Effective tax rate' for US firms; Damodaran blended rate supports ~27% normalized assumption.</t>
+Ctrl+F: "United States" → Damodaran effective tax rate ~25%; model 27%</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="36" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Equity weight</t>
@@ -1309,11 +1309,11 @@
       <c r="E14" s="19" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K balance sheet
-Find: Balance Sheet → cash &amp; equity; no funded debt → 100% equity weight at market values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
+Ctrl+F: "Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Debt weight</t>
@@ -1330,7 +1330,7 @@
       <c r="E15" s="19" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K balance sheet
-Find: Balance Sheet → confirm no long-term debt outstanding; debt weight set to 0%.</t>
+Ctrl+F: "Long-term debt" → none outstanding; debt weight 0%</t>
         </is>
       </c>
     </row>
@@ -1417,11 +1417,11 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Source &amp; where to find</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="42" customHeight="1">
+          <t>Source &amp; Ctrl+F lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
@@ -1444,11 +1444,11 @@
       <c r="G4" s="19" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
-Find: Search release for 'full year 2026' net revenue outlook (−5% to −7%); model uses −6.1% midpoint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+Ctrl+F: "full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
@@ -1471,11 +1471,11 @@
       <c r="G5" s="19" t="inlineStr">
         <is>
           <t>LULU historical revenue (10-K)
-Find: Income Statement → 'Net revenue' FY2022–FY2025; compute YoY growth vs historical double-digit run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="42" customHeight="1">
+Ctrl+F: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>FY2026E EBIT margin</t>
@@ -1498,11 +1498,11 @@
       <c r="G6" s="19" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
-Find: Search release for FY2026 operating margin / EBIT commentary supporting ~13.9% base case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+Ctrl+F: "full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Terminal (FY2030E) EBIT margin</t>
@@ -1525,11 +1525,11 @@
       <c r="G7" s="19" t="inlineStr">
         <is>
           <t>LULU historical EBIT margins (10-K)
-Find: Income Statement → operating income ÷ net revenue; compare peak ~20–24% vs 15.5% terminal assumption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+Ctrl+F: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>WACC</t>
@@ -1552,11 +1552,11 @@
       <c r="G8" s="19" t="inlineStr">
         <is>
           <t>WACC tab: CAPM build
-Find: Opens WACC tab → green WACC cell (10.0% base); built from CAPM inputs above it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+Ctrl+F: WACC tab → cell C (green) = 10.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Terminal growth</t>
@@ -1579,11 +1579,11 @@
       <c r="G9" s="19" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)
-Find: GDPC1 chart → long-run real GDP growth trend (~2%); terminal g set at 2.25% (GDP + inflation cushion).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+Ctrl+F: "GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
@@ -1606,11 +1606,11 @@
       <c r="G10" s="19" t="inlineStr">
         <is>
           <t>Damodaran: US tax rate dataset
-Find: Same Damodaran effective tax table; cross-check vs LULU ~29% recent effective rate in 10-K.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="42" customHeight="1">
+Ctrl+F: "Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
@@ -1633,11 +1633,11 @@
       <c r="G11" s="19" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)
-Find: Cash Flow Statement → 'Depreciation and amortization' ÷ net revenue (FY22–25 avg ≈ 4.5%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="42" customHeight="1">
+Ctrl+F: "Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
@@ -1660,11 +1660,11 @@
       <c r="G12" s="19" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)
-Find: Cash Flow Statement → 'Capital expenditures' ÷ net revenue (recent ~5% of sales).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
+Ctrl+F: "Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>NWC build % of Δrevenue</t>
@@ -1687,7 +1687,7 @@
       <c r="G13" s="19" t="inlineStr">
         <is>
           <t>LULU BS/IS historical (10-K)
-Find: Balance Sheet working capital vs Income Statement revenue changes (AR, inventory, AP, accrued).</t>
+Ctrl+F: "Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="K2" s="40" t="inlineStr">
         <is>
-          <t>Source &amp; where to find</t>
+          <t>Source &amp; Ctrl+F lines</t>
         </is>
       </c>
       <c r="L2" s="40" t="inlineStr">
@@ -2629,7 +2629,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3" ht="36" customHeight="1">
       <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
@@ -2638,7 +2638,7 @@
       <c r="C3" s="42" t="inlineStr">
         <is>
           <t>10-K source
-Find: Interactive 10-K viewer → table of contents or Ctrl+F for financial statements.</t>
+Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
         </is>
       </c>
       <c r="I3" s="43" t="inlineStr">
@@ -2681,7 +2681,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
@@ -2715,17 +2715,17 @@
       <c r="K6" s="19" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
-Find: Search release for 'full year 2026' net revenue outlook (−5% to −7%); model uses −6.1% midpoint.</t>
+Ctrl+F: "full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
         </is>
       </c>
       <c r="L6" s="42" t="inlineStr">
         <is>
           <t>LULU historical revenue (10-K)
-Find: Income Statement → 'Net revenue' FY2022–FY2025; compute YoY growth vs historical double-digit run.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
+Ctrl+F: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EBIT (operating) margin %</t>
@@ -2763,13 +2763,13 @@
       <c r="K7" s="19" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
-Find: Search release for FY2026 operating margin / EBIT commentary supporting ~13.9% base case.</t>
+Ctrl+F: "full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
         </is>
       </c>
       <c r="L7" s="42" t="inlineStr">
         <is>
           <t>LULU historical EBIT margins (10-K)
-Find: Income Statement → operating income ÷ net revenue; compare peak ~20–24% vs 15.5% terminal assumption.</t>
+Ctrl+F: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A % of revenue</t>
@@ -2899,7 +2899,7 @@
       <c r="K11" s="19" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)
-Find: Cash Flow Statement → 'Depreciation and amortization' ÷ net revenue (FY22–25 avg ≈ 4.5%).</t>
+Ctrl+F: "Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
@@ -2968,7 +2968,7 @@
       <c r="K13" s="19" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)
-Find: Cash Flow Statement → 'Capital expenditures' ÷ net revenue (recent ~5% of sales).</t>
+Ctrl+F: "Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
@@ -3037,7 +3037,7 @@
       <c r="K15" s="19" t="inlineStr">
         <is>
           <t>LULU BS/IS historical (10-K)
-Find: Balance Sheet working capital vs Income Statement revenue changes (AR, inventory, AP, accrued).</t>
+Ctrl+F: "Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3217,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
@@ -3235,7 +3235,7 @@
       <c r="K26" s="19" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)
-Find: GDPC1 chart → long-run real GDP growth trend (~2%); terminal g set at 2.25% (GDP + inflation cushion).</t>
+Ctrl+F: "GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
@@ -3306,11 +3306,11 @@
       <c r="D32" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="42" customHeight="1">
+Ctrl+F: "Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Less: total debt</t>
@@ -3322,7 +3322,7 @@
       <c r="D33" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
+Ctrl+F: "Long-term debt" → $0 (no funded debt)</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3337,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
@@ -3349,7 +3349,7 @@
       <c r="D35" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Income Statement/EPS footnote → 'Diluted weighted-average shares outstanding'.</t>
+Ctrl+F: "Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
@@ -3380,7 +3380,7 @@
       <c r="D37" s="42" t="inlineStr">
         <is>
           <t>NASDAQ
-Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
+Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
+    <row r="43" ht="36" customHeight="1">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
@@ -3439,7 +3439,7 @@
       <c r="K43" s="19" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA
-Find: Valuation section → 'EV/EBITDA' (forward or TTM); 8.0x = football-field midpoint on FY2030E EBITDA.</t>
+Ctrl+F: "Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
         </is>
       </c>
       <c r="L43" s="61" t="inlineStr">
@@ -3624,7 +3624,7 @@
       <c r="G58" s="13" t="n"/>
       <c r="H58" s="13" t="n"/>
     </row>
-    <row r="59" ht="42" customHeight="1">
+    <row r="59" ht="36" customHeight="1">
       <c r="A59" s="70" t="inlineStr">
         <is>
           <t>WACC \ g</t>
@@ -3658,11 +3658,11 @@
       <c r="K59" s="19" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)
-Find: GDPC1 long-run growth bounds terminal-g sensitivity (1.5%–3.0% vs 2.25% base).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="42" customHeight="1">
+Ctrl+F: "GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1">
       <c r="A60" s="71" t="n">
         <v>0.09</v>
       </c>
@@ -3694,7 +3694,7 @@
       <c r="J60" s="42" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP
-Find: Damodaran implied ERP table anchors discount-rate range; ±100bps around 10.0% WACC base.</t>
+Ctrl+F: "Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1">
+    <row r="65" ht="36" customHeight="1">
       <c r="J65" s="18" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
@@ -3827,13 +3827,13 @@
       <c r="K65" s="19" t="inlineStr">
         <is>
           <t>Scenarios: WACC &amp; terminal g
-Find: Opens Scenarios tab → WACC row and Terminal g row (base case inputs for sensitivity grid).</t>
+Ctrl+F: Scenarios tab → "WACC" row &amp; "Terminal growth" row (base inputs)</t>
         </is>
       </c>
       <c r="L65" s="42" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)
-Find: GDPC1 long-run growth bounds terminal-g sensitivity (1.5%–3.0% vs 2.25% base).</t>
+Ctrl+F: "GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
         </is>
       </c>
     </row>
@@ -3915,7 +3915,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2025A revenue</t>
@@ -3927,7 +3927,7 @@
       <c r="D4" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Consolidated Statements of Operations → search 'Net revenue', 'Operating income', etc.</t>
+Ctrl+F: "Net revenue" → FY2025 $11,102,600 ($000)</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FY2026E diluted EPS (guidance midpoint)</t>
@@ -3970,11 +3970,11 @@
       <c r="D7" s="42" t="inlineStr">
         <is>
           <t>Release
-Find: Search 'diluted earnings per share' and 'net revenue' for Q2/FY2026 guidance ranges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="42" customHeight="1">
+Ctrl+F: "diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
@@ -3986,11 +3986,11 @@
       <c r="D8" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Consolidated Balance Sheets → search 'Cash', 'Inventories', 'Total assets', etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="42" customHeight="1">
+Ctrl+F: "Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Diluted shares (000)</t>
@@ -4002,11 +4002,11 @@
       <c r="D9" s="42" t="inlineStr">
         <is>
           <t>10-K
-Find: Income Statement/EPS footnote → 'Diluted weighted-average shares outstanding'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="42" customHeight="1">
+Ctrl+F: "Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
@@ -4018,7 +4018,7 @@
       <c r="D10" s="42" t="inlineStr">
         <is>
           <t>NASDAQ
-Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
+Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>
@@ -4076,11 +4076,11 @@
       </c>
       <c r="F16" s="75" t="inlineStr">
         <is>
-          <t>Source &amp; where to find</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="42" customHeight="1">
+          <t>Source &amp; Ctrl+F lines</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>lululemon (LULU) — current</t>
@@ -4098,11 +4098,11 @@
       <c r="F17" s="42" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K
-Find: Ctrl+F the line-item name in FY2025 consolidated financial statements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="42" customHeight="1">
+Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" → locate line item below</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Nike (NKE)</t>
@@ -4119,11 +4119,11 @@
       <c r="F18" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: NKE statistics
-Find: Statistics → 'Enterprise Value/EBITDA' or forward EV/EBITDA; illustrative ~18x mature peer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="42" customHeight="1">
+Ctrl+F: "Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Deckers (DECK)</t>
@@ -4140,11 +4140,11 @@
       <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: DECK statistics
-Find: Statistics → EV/EBITDA; Deckers trades ~15x on HOKA/UGG momentum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="42" customHeight="1">
+Ctrl+F: "Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>On Holding (ONON)</t>
@@ -4161,11 +4161,11 @@
       <c r="F20" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: ONON statistics
-Find: Statistics → EV/EBITDA; On ~25x as high-growth premium athletic benchmark.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
+Ctrl+F: "Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>adidas (ADS)</t>
@@ -4182,11 +4182,11 @@
       <c r="F21" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: adidas (ADDYY)
-Find: Statistics → EV/EBITDA for ADDYY ADR; adidas ~12x restructuring incumbent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="42" customHeight="1">
+Ctrl+F: "Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>V.F. Corp (VFC)</t>
@@ -4203,7 +4203,7 @@
       <c r="F22" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: VFC statistics
-Find: Statistics → EV/EBITDA; VFC ~10x as lower-bound scaled apparel peer.</t>
+Ctrl+F: "Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
         </is>
       </c>
     </row>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H36" s="79" t="inlineStr">
         <is>
-          <t>Lo source &amp; find</t>
+          <t>Lo source &amp; Ctrl+F</t>
         </is>
       </c>
       <c r="I36" s="79" t="inlineStr">
@@ -4339,11 +4339,11 @@
       </c>
       <c r="J36" s="79" t="inlineStr">
         <is>
-          <t>Hi source &amp; find</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
+          <t>Hi source &amp; Ctrl+F</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
@@ -4371,7 +4371,7 @@
       <c r="H37" s="19" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA
-Find: Same EV/EBITDA field; 6.5x = bear terminal exit below Gordon-implied ~7x.</t>
+Ctrl+F: "Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x</t>
         </is>
       </c>
       <c r="I37" s="81" t="inlineStr">
@@ -4382,7 +4382,7 @@
       <c r="J37" s="82" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU valuation
-Find: Same EV/EBITDA field; 9.5x = bull terminal exit above 8.0x DCF base.</t>
+Ctrl+F: "Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="42" customHeight="1">
+    <row r="39" ht="36" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
@@ -4434,7 +4434,7 @@
       <c r="H39" s="19" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU P/E
-Find: Statistics → 'Trailing P/E' or forward P/E on depressed FY26E EPS (~10x trough).</t>
+Ctrl+F: "Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x</t>
         </is>
       </c>
       <c r="I39" s="81" t="inlineStr">
@@ -4445,7 +4445,7 @@
       <c r="J39" s="82" t="inlineStr">
         <is>
           <t>Yahoo Finance: NKE P/E (peer)
-Find: NKE forward P/E as mature-peer ceiling; 18x on LULU FY26E recovery case.</t>
+Ctrl+F: "Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="A42" s="86" t="inlineStr">
         <is>
           <t>Current price</t>
@@ -4486,7 +4486,7 @@
       <c r="D42" s="42" t="inlineStr">
         <is>
           <t>NASDAQ
-Find: NASDAQ quote page → Last Sale or closing price for LULU.</t>
+Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -375,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -408,6 +408,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -493,6 +496,9 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -531,9 +537,6 @@
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -593,7 +596,7 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1034,7 +1037,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions — justification then blue source with Ctrl+F lines in next column</t>
+          <t>Red font  =  analyst assumptions — Justification | Source (click) | Ctrl+F columns prove the number</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1118,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1133,6 +1137,7 @@
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -1147,7 +1152,12 @@
       </c>
       <c r="E2" s="15" t="inlineStr">
         <is>
-          <t>Source &amp; Ctrl+F lines</t>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
         </is>
       </c>
     </row>
@@ -1167,8 +1177,12 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>FRED: 10Y Treasury (DGS10)
-Ctrl+F: "DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
+          <t>FRED: 10Y Treasury (DGS10)</t>
+        </is>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>"DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
         </is>
       </c>
     </row>
@@ -1188,8 +1202,12 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: Historical Implied ERP
-Ctrl+F: "Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1217,7 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>0.95</v>
       </c>
       <c r="D5" s="18" t="inlineStr">
@@ -1209,18 +1227,22 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU Beta
-Ctrl+F: "Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
+          <t>Yahoo Finance: LULU Beta</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>"Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <f>C3+C5*C4</f>
         <v/>
       </c>
@@ -1248,8 +1270,12 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K (no funded debt)
-Ctrl+F: "no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
+          <t>LULU FY2025 10-K (no funded debt)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>"no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
         </is>
       </c>
     </row>
@@ -1269,8 +1295,12 @@
       </c>
       <c r="E10" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset
-Ctrl+F: "United States" → Damodaran effective tax rate ~25%; model 27%</t>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>"United States" → Damodaran effective tax rate ~25%; model 27%</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1310,7 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="24">
         <f>C9*(1-C10)</f>
         <v/>
       </c>
@@ -1308,8 +1338,12 @@
       </c>
       <c r="E14" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K balance sheet
-Ctrl+F: "Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
         </is>
       </c>
     </row>
@@ -1329,18 +1363,22 @@
       </c>
       <c r="E15" s="19" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K balance sheet
-Ctrl+F: "Long-term debt" → none outstanding; debt weight 0%</t>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>"Long-term debt" → none outstanding; debt weight 0%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <f>C14*C6+C15*C11</f>
         <v/>
       </c>
@@ -1365,15 +1403,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1388,17 +1427,17 @@
       <c r="E1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="25" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E2" s="27" t="inlineStr">
+      <c r="E2" s="28" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1417,7 +1456,12 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>Source &amp; Ctrl+F lines</t>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
         </is>
       </c>
     </row>
@@ -1443,8 +1487,12 @@
       </c>
       <c r="G4" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release
-Ctrl+F: "full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
         </is>
       </c>
     </row>
@@ -1470,8 +1518,12 @@
       </c>
       <c r="G5" s="19" t="inlineStr">
         <is>
-          <t>LULU historical revenue (10-K)
-Ctrl+F: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+          <t>LULU historical revenue (10-K)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
         </is>
       </c>
     </row>
@@ -1497,8 +1549,12 @@
       </c>
       <c r="G6" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release
-Ctrl+F: "full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
         </is>
       </c>
     </row>
@@ -1524,8 +1580,12 @@
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
-          <t>LULU historical EBIT margins (10-K)
-Ctrl+F: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+          <t>LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
         </is>
       </c>
     </row>
@@ -1551,8 +1611,12 @@
       </c>
       <c r="G8" s="19" t="inlineStr">
         <is>
-          <t>WACC tab: CAPM build
-Ctrl+F: WACC tab → cell C (green) = 10.0%</t>
+          <t>WACC tab: CAPM build</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>WACC tab → cell C (green) = 10.0%</t>
         </is>
       </c>
     </row>
@@ -1578,8 +1642,12 @@
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)
-Ctrl+F: "GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
         </is>
       </c>
     </row>
@@ -1605,8 +1673,12 @@
       </c>
       <c r="G10" s="19" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset
-Ctrl+F: "Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>"Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
         </is>
       </c>
     </row>
@@ -1632,8 +1704,12 @@
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)
-Ctrl+F: "Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
         </is>
       </c>
     </row>
@@ -1659,8 +1735,12 @@
       </c>
       <c r="G12" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)
-Ctrl+F: "Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
         </is>
       </c>
     </row>
@@ -1686,8 +1766,12 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)
-Ctrl+F: "Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
         </is>
       </c>
     </row>
@@ -1699,824 +1783,824 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="28" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>11102600*(1+C4)</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>11102600*(1+D4)</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <f>11102600*(1+E4)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="inlineStr">
+      <c r="A17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="30">
         <f>C16*(1+C5)</f>
         <v/>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="30">
         <f>D16*(1+D5)</f>
         <v/>
       </c>
-      <c r="E17" s="29">
+      <c r="E17" s="30">
         <f>E16*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="28" t="inlineStr">
+      <c r="A18" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C18" s="29">
+      <c r="C18" s="30">
         <f>C17*(1+C5)</f>
         <v/>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="30">
         <f>D17*(1+D5)</f>
         <v/>
       </c>
-      <c r="E18" s="29">
+      <c r="E18" s="30">
         <f>E17*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="inlineStr">
+      <c r="A19" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>C18*(1+C5)</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>D18*(1+D5)</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>E18*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="28" t="inlineStr">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C20" s="29">
+      <c r="C20" s="30">
         <f>C19*(1+C5)</f>
         <v/>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="30">
         <f>D19*(1+D5)</f>
         <v/>
       </c>
-      <c r="E20" s="29">
+      <c r="E20" s="30">
         <f>E19*(1+E5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
+      <c r="A21" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>C6+(C7-C6)*0/4</f>
         <v/>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>D6+(D7-D6)*0/4</f>
         <v/>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>E6+(E7-E6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="A22" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <f>C6+(C7-C6)*1/4</f>
         <v/>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <f>D6+(D7-D6)*1/4</f>
         <v/>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <f>E6+(E7-E6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <f>C6+(C7-C6)*2/4</f>
         <v/>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <f>D6+(D7-D6)*2/4</f>
         <v/>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <f>E6+(E7-E6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="A24" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <f>C6+(C7-C6)*3/4</f>
         <v/>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <f>D6+(D7-D6)*3/4</f>
         <v/>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <f>E6+(E7-E6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <f>C6+(C7-C6)*4/4</f>
         <v/>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <f>D6+(D7-D6)*4/4</f>
         <v/>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <f>E6+(E7-E6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="28" t="inlineStr">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="C26" s="29">
+      <c r="C26" s="30">
         <f>C16*C21</f>
         <v/>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="30">
         <f>D16*D21</f>
         <v/>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="30">
         <f>E16*E21</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="C27" s="29">
+      <c r="C27" s="30">
         <f>C17*C22</f>
         <v/>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="30">
         <f>D17*D22</f>
         <v/>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="30">
         <f>E17*E22</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <f>C18*C23</f>
         <v/>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <f>D18*D23</f>
         <v/>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <f>E18*E23</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>C19*C24</f>
         <v/>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <f>D19*D24</f>
         <v/>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <f>E19*E24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="C30" s="29">
+      <c r="C30" s="30">
         <f>C20*C25</f>
         <v/>
       </c>
-      <c r="D30" s="29">
+      <c r="D30" s="30">
         <f>D20*D25</f>
         <v/>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <f>E20*E25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="C31" s="29">
+      <c r="C31" s="30">
         <f>C26*(1-C10)</f>
         <v/>
       </c>
-      <c r="D31" s="29">
+      <c r="D31" s="30">
         <f>D26*(1-D10)</f>
         <v/>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <f>E26*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="C32" s="29">
+      <c r="C32" s="30">
         <f>C27*(1-C10)</f>
         <v/>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="30">
         <f>D27*(1-D10)</f>
         <v/>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f>E27*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="C33" s="29">
+      <c r="C33" s="30">
         <f>C28*(1-C10)</f>
         <v/>
       </c>
-      <c r="D33" s="29">
+      <c r="D33" s="30">
         <f>D28*(1-D10)</f>
         <v/>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <f>E28*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="C34" s="29">
+      <c r="C34" s="30">
         <f>C29*(1-C10)</f>
         <v/>
       </c>
-      <c r="D34" s="29">
+      <c r="D34" s="30">
         <f>D29*(1-D10)</f>
         <v/>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="30">
         <f>E29*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="A35" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="C35" s="29">
+      <c r="C35" s="30">
         <f>C30*(1-C10)</f>
         <v/>
       </c>
-      <c r="D35" s="29">
+      <c r="D35" s="30">
         <f>D30*(1-D10)</f>
         <v/>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="30">
         <f>E30*(1-E10)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="C36" s="29">
+      <c r="C36" s="30">
         <f>C16*C11</f>
         <v/>
       </c>
-      <c r="D36" s="29">
+      <c r="D36" s="30">
         <f>D16*D11</f>
         <v/>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <f>E16*E11</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="C37" s="29">
+      <c r="C37" s="30">
         <f>C17*C11</f>
         <v/>
       </c>
-      <c r="D37" s="29">
+      <c r="D37" s="30">
         <f>D17*D11</f>
         <v/>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <f>E17*E11</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="28" t="inlineStr">
+      <c r="A38" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="C38" s="29">
+      <c r="C38" s="30">
         <f>C18*C11</f>
         <v/>
       </c>
-      <c r="D38" s="29">
+      <c r="D38" s="30">
         <f>D18*D11</f>
         <v/>
       </c>
-      <c r="E38" s="29">
+      <c r="E38" s="30">
         <f>E18*E11</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="inlineStr">
+      <c r="A39" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="C39" s="29">
+      <c r="C39" s="30">
         <f>C19*C11</f>
         <v/>
       </c>
-      <c r="D39" s="29">
+      <c r="D39" s="30">
         <f>D19*D11</f>
         <v/>
       </c>
-      <c r="E39" s="29">
+      <c r="E39" s="30">
         <f>E19*E11</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="28" t="inlineStr">
+      <c r="A40" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="30">
         <f>C20*C11</f>
         <v/>
       </c>
-      <c r="D40" s="29">
+      <c r="D40" s="30">
         <f>D20*D11</f>
         <v/>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="30">
         <f>E20*E11</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="30">
         <f>C16*C12</f>
         <v/>
       </c>
-      <c r="D41" s="29">
+      <c r="D41" s="30">
         <f>D16*D12</f>
         <v/>
       </c>
-      <c r="E41" s="29">
+      <c r="E41" s="30">
         <f>E16*E12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="30">
         <f>C17*C12</f>
         <v/>
       </c>
-      <c r="D42" s="29">
+      <c r="D42" s="30">
         <f>D17*D12</f>
         <v/>
       </c>
-      <c r="E42" s="29">
+      <c r="E42" s="30">
         <f>E17*E12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="A43" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="30">
         <f>C18*C12</f>
         <v/>
       </c>
-      <c r="D43" s="29">
+      <c r="D43" s="30">
         <f>D18*D12</f>
         <v/>
       </c>
-      <c r="E43" s="29">
+      <c r="E43" s="30">
         <f>E18*E12</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="A44" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="30">
         <f>C19*C12</f>
         <v/>
       </c>
-      <c r="D44" s="29">
+      <c r="D44" s="30">
         <f>D19*D12</f>
         <v/>
       </c>
-      <c r="E44" s="29">
+      <c r="E44" s="30">
         <f>E19*E12</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="28" t="inlineStr">
+      <c r="A45" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="30">
         <f>C20*C12</f>
         <v/>
       </c>
-      <c r="D45" s="29">
+      <c r="D45" s="30">
         <f>D20*D12</f>
         <v/>
       </c>
-      <c r="E45" s="29">
+      <c r="E45" s="30">
         <f>E20*E12</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="A46" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="30">
         <f>C13*(C16-11102600)</f>
         <v/>
       </c>
-      <c r="D46" s="29">
+      <c r="D46" s="30">
         <f>D13*(D16-11102600)</f>
         <v/>
       </c>
-      <c r="E46" s="29">
+      <c r="E46" s="30">
         <f>E13*(E16-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="28" t="inlineStr">
+      <c r="A47" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <f>C13*(C17-C16)</f>
         <v/>
       </c>
-      <c r="D47" s="29">
+      <c r="D47" s="30">
         <f>D13*(D17-D16)</f>
         <v/>
       </c>
-      <c r="E47" s="29">
+      <c r="E47" s="30">
         <f>E13*(E17-E16)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="28" t="inlineStr">
+      <c r="A48" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="30">
         <f>C13*(C18-C17)</f>
         <v/>
       </c>
-      <c r="D48" s="29">
+      <c r="D48" s="30">
         <f>D13*(D18-D17)</f>
         <v/>
       </c>
-      <c r="E48" s="29">
+      <c r="E48" s="30">
         <f>E13*(E18-E17)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="28" t="inlineStr">
+      <c r="A49" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="30">
         <f>C13*(C19-C18)</f>
         <v/>
       </c>
-      <c r="D49" s="29">
+      <c r="D49" s="30">
         <f>D13*(D19-D18)</f>
         <v/>
       </c>
-      <c r="E49" s="29">
+      <c r="E49" s="30">
         <f>E13*(E19-E18)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="28" t="inlineStr">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="30">
         <f>C13*(C20-C19)</f>
         <v/>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="30">
         <f>D13*(D20-D19)</f>
         <v/>
       </c>
-      <c r="E50" s="29">
+      <c r="E50" s="30">
         <f>E13*(E20-E19)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="28" t="inlineStr">
+      <c r="A51" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="30">
         <f>C31+C36-C41-C46</f>
         <v/>
       </c>
-      <c r="D51" s="29">
+      <c r="D51" s="30">
         <f>D31+D36-D41-D46</f>
         <v/>
       </c>
-      <c r="E51" s="29">
+      <c r="E51" s="30">
         <f>E31+E36-E41-E46</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="28" t="inlineStr">
+      <c r="A52" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="30">
         <f>C32+C37-C42-C47</f>
         <v/>
       </c>
-      <c r="D52" s="29">
+      <c r="D52" s="30">
         <f>D32+D37-D42-D47</f>
         <v/>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="30">
         <f>E32+E37-E42-E47</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="28" t="inlineStr">
+      <c r="A53" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="30">
         <f>C33+C38-C43-C48</f>
         <v/>
       </c>
-      <c r="D53" s="29">
+      <c r="D53" s="30">
         <f>D33+D38-D43-D48</f>
         <v/>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="30">
         <f>E33+E38-E43-E48</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="28" t="inlineStr">
+      <c r="A54" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="30">
         <f>C34+C39-C44-C49</f>
         <v/>
       </c>
-      <c r="D54" s="29">
+      <c r="D54" s="30">
         <f>D34+D39-D44-D49</f>
         <v/>
       </c>
-      <c r="E54" s="29">
+      <c r="E54" s="30">
         <f>E34+E39-E44-E49</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="28" t="inlineStr">
+      <c r="A55" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="30">
         <f>C35+C40-C45-C50</f>
         <v/>
       </c>
-      <c r="D55" s="29">
+      <c r="D55" s="30">
         <f>D35+D40-D45-D50</f>
         <v/>
       </c>
-      <c r="E55" s="29">
+      <c r="E55" s="30">
         <f>E35+E40-E45-E50</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="21" t="inlineStr">
+      <c r="A57" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
         <v/>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
         <v/>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="inlineStr">
+      <c r="A58" s="33" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C58" s="33">
+      <c r="C58" s="34">
         <f>(C57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D58" s="34">
+      <c r="D58" s="35">
         <f>(D57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="E58" s="33">
+      <c r="E58" s="34">
         <f>(E57+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="21" t="inlineStr">
+      <c r="A59" s="22" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="35">
+      <c r="C59" s="36">
         <f>C58/100.0-1</f>
         <v/>
       </c>
-      <c r="D59" s="35">
+      <c r="D59" s="36">
         <f>D58/100.0-1</f>
         <v/>
       </c>
-      <c r="E59" s="35">
+      <c r="E59" s="36">
         <f>E58/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="A61" s="37" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2545,22 +2629,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="44" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2578,70 +2663,80 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="38" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="38" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="38" t="inlineStr">
+      <c r="E2" s="39" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="38" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="38" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="38" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="I2" s="39" t="inlineStr">
+      <c r="I2" s="40" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="J2" s="40" t="inlineStr">
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="K2" s="40" t="inlineStr">
-        <is>
-          <t>Source &amp; Ctrl+F lines</t>
-        </is>
-      </c>
-      <c r="L2" s="40" t="inlineStr">
+      <c r="K2" s="41" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="L2" s="41" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
+        </is>
+      </c>
+      <c r="M2" s="41" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
+      <c r="N2" s="41" t="inlineStr">
+        <is>
+          <t>Alt. Ctrl+F</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="42" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
         </is>
       </c>
-      <c r="C3" s="42" t="inlineStr">
+      <c r="C3" s="43" t="inlineStr">
         <is>
           <t>10-K source
 Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
         </is>
       </c>
-      <c r="I3" s="43" t="inlineStr">
+      <c r="I3" s="44" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2653,30 +2748,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="44" t="n">
+      <c r="C5" s="45" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="45">
+      <c r="D5" s="46">
         <f>Scenarios!D16</f>
         <v/>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="46">
         <f>Scenarios!D17</f>
         <v/>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="46">
         <f>Scenarios!D18</f>
         <v/>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="46">
         <f>Scenarios!D19</f>
         <v/>
       </c>
-      <c r="H5" s="45">
+      <c r="H5" s="46">
         <f>Scenarios!D20</f>
         <v/>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="47">
         <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2687,23 +2782,23 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="48">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="48">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="48">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="48">
         <f>H5/G5-1</f>
         <v/>
       </c>
@@ -2714,14 +2809,22 @@
       </c>
       <c r="K6" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release
-Ctrl+F: "full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
-        </is>
-      </c>
-      <c r="L6" s="42" t="inlineStr">
-        <is>
-          <t>LULU historical revenue (10-K)
-Ctrl+F: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
+        </is>
+      </c>
+      <c r="M6" s="49" t="inlineStr">
+        <is>
+          <t>LULU historical revenue (10-K)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
         </is>
       </c>
     </row>
@@ -2731,27 +2834,27 @@
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="48">
         <f>Scenarios!D21</f>
         <v/>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="48">
         <f>Scenarios!D22</f>
         <v/>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="48">
         <f>Scenarios!D23</f>
         <v/>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="48">
         <f>Scenarios!D24</f>
         <v/>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="48">
         <f>Scenarios!D25</f>
         <v/>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="47">
         <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2762,47 +2865,55 @@
       </c>
       <c r="K7" s="19" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release
-Ctrl+F: "full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
-        </is>
-      </c>
-      <c r="L7" s="42" t="inlineStr">
-        <is>
-          <t>LULU historical EBIT margins (10-K)
-Ctrl+F: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
+        </is>
+      </c>
+      <c r="M7" s="49" t="inlineStr">
+        <is>
+          <t>LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="50" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>Scenarios!D26</f>
         <v/>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>Scenarios!D27</f>
         <v/>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>Scenarios!D28</f>
         <v/>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="32">
         <f>Scenarios!D29</f>
         <v/>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="32">
         <f>Scenarios!D30</f>
         <v/>
       </c>
-      <c r="I8" s="49">
+      <c r="I8" s="51">
         <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2813,54 +2924,54 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="46">
         <f>-Scenarios!D26*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="46">
         <f>-Scenarios!D27*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="F9" s="45">
+      <c r="F9" s="46">
         <f>-Scenarios!D28*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="G9" s="45">
+      <c r="G9" s="46">
         <f>-Scenarios!D29*Scenarios!$D$10</f>
         <v/>
       </c>
-      <c r="H9" s="45">
+      <c r="H9" s="46">
         <f>-Scenarios!D30*Scenarios!$D$10</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>Scenarios!D31</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>Scenarios!D32</f>
         <v/>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>Scenarios!D33</f>
         <v/>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="32">
         <f>Scenarios!D34</f>
         <v/>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="32">
         <f>Scenarios!D35</f>
         <v/>
       </c>
-      <c r="I10" s="49">
+      <c r="I10" s="51">
         <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2898,8 +3009,12 @@
       </c>
       <c r="K11" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)
-Ctrl+F: "Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
         </is>
       </c>
     </row>
@@ -2909,27 +3024,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="46">
         <f>Scenarios!D36</f>
         <v/>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="46">
         <f>Scenarios!D37</f>
         <v/>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="46">
         <f>Scenarios!D38</f>
         <v/>
       </c>
-      <c r="G12" s="45">
+      <c r="G12" s="46">
         <f>Scenarios!D39</f>
         <v/>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="46">
         <f>Scenarios!D40</f>
         <v/>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="47">
         <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2967,8 +3082,12 @@
       </c>
       <c r="K13" s="19" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)
-Ctrl+F: "Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
         </is>
       </c>
     </row>
@@ -2978,27 +3097,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="46">
         <f>-Scenarios!D41</f>
         <v/>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="46">
         <f>-Scenarios!D42</f>
         <v/>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="46">
         <f>-Scenarios!D43</f>
         <v/>
       </c>
-      <c r="G14" s="45">
+      <c r="G14" s="46">
         <f>-Scenarios!D44</f>
         <v/>
       </c>
-      <c r="H14" s="45">
+      <c r="H14" s="46">
         <f>-Scenarios!D45</f>
         <v/>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="47">
         <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3036,8 +3155,12 @@
       </c>
       <c r="K15" s="19" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)
-Ctrl+F: "Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
         </is>
       </c>
     </row>
@@ -3047,65 +3170,65 @@
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="45">
+      <c r="D16" s="46">
         <f>-Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E16" s="45">
+      <c r="E16" s="46">
         <f>-Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="46">
         <f>-Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G16" s="45">
+      <c r="G16" s="46">
         <f>-Scenarios!D49</f>
         <v/>
       </c>
-      <c r="H16" s="45">
+      <c r="H16" s="46">
         <f>-Scenarios!D50</f>
         <v/>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="47">
         <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="A17" s="37" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="52">
         <f>Scenarios!D51</f>
         <v/>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="52">
         <f>Scenarios!D52</f>
         <v/>
       </c>
-      <c r="F18" s="50">
+      <c r="F18" s="52">
         <f>Scenarios!D53</f>
         <v/>
       </c>
-      <c r="G18" s="50">
+      <c r="G18" s="52">
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H18" s="50">
+      <c r="H18" s="52">
         <f>Scenarios!D55</f>
         <v/>
       </c>
-      <c r="I18" s="49">
+      <c r="I18" s="51">
         <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3116,19 +3239,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="51" t="n">
+      <c r="E19" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="51" t="n">
+      <c r="G19" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="51" t="n">
+      <c r="H19" s="53" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3138,50 +3261,50 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="54">
         <f>1/(1+Scenarios!$D$8)^D19</f>
         <v/>
       </c>
-      <c r="E20" s="52">
+      <c r="E20" s="54">
         <f>1/(1+Scenarios!$D$8)^E19</f>
         <v/>
       </c>
-      <c r="F20" s="52">
+      <c r="F20" s="54">
         <f>1/(1+Scenarios!$D$8)^F19</f>
         <v/>
       </c>
-      <c r="G20" s="52">
+      <c r="G20" s="54">
         <f>1/(1+Scenarios!$D$8)^G19</f>
         <v/>
       </c>
-      <c r="H20" s="52">
+      <c r="H20" s="54">
         <f>1/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>D18*D20</f>
         <v/>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>E18*E20</f>
         <v/>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>F18*F20</f>
         <v/>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>G18*G20</f>
         <v/>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <f>H18*H20</f>
         <v/>
       </c>
@@ -3192,13 +3315,13 @@
           <t>Scenarios linkage summary (column I should all read OK)</t>
         </is>
       </c>
-      <c r="I23" s="53">
+      <c r="I23" s="55">
         <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="54" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3207,12 +3330,12 @@
       <c r="C24" s="13" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="57">
         <f>SUM(D21:H21)</f>
         <v/>
       </c>
@@ -3223,7 +3346,7 @@
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C26" s="47">
+      <c r="C26" s="48">
         <f>Scenarios!$D$9</f>
         <v/>
       </c>
@@ -3234,18 +3357,22 @@
       </c>
       <c r="K26" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)
-Ctrl+F: "GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <f>H8+H12</f>
         <v/>
       </c>
@@ -3256,7 +3383,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="C28" s="45">
+      <c r="C28" s="46">
         <f>H18*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
         <v/>
       </c>
@@ -3267,29 +3394,29 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C29" s="56">
+      <c r="C29" s="58">
         <f>C28/C27</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="57">
         <f>C28/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="32">
         <f>C25+C30</f>
         <v/>
       </c>
@@ -3300,13 +3427,17 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C32" s="44" t="n">
+      <c r="C32" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D32" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+      <c r="D32" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
         </is>
       </c>
     </row>
@@ -3316,23 +3447,27 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C33" s="44" t="n">
+      <c r="C33" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="D33" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Long-term debt" → $0 (no funded debt)</t>
+      <c r="D33" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="inlineStr">
+        <is>
+          <t>"Long-term debt" → $0 (no funded debt)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="21" t="inlineStr">
+      <c r="A34" s="22" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <f>C31+C32+C33</f>
         <v/>
       </c>
@@ -3343,27 +3478,31 @@
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C35" s="44" t="n">
+      <c r="C35" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D35" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+      <c r="D35" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C36" s="57">
+      <c r="C36" s="59">
         <f>C34/C35</f>
         <v/>
       </c>
-      <c r="I36" s="49">
+      <c r="I36" s="51">
         <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3374,23 +3513,27 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C37" s="58" t="n">
+      <c r="C37" s="60" t="n">
         <v>100</v>
       </c>
-      <c r="D37" s="42" t="inlineStr">
-        <is>
-          <t>NASDAQ
-Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
+      <c r="D37" s="49" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="A38" s="22" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C38" s="59">
+      <c r="C38" s="61">
         <f>C36/C37-1</f>
         <v/>
       </c>
@@ -3401,13 +3544,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C39" s="47">
+      <c r="C39" s="48">
         <f>C30/C31</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="54" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3428,7 +3571,7 @@
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C43" s="60" t="n">
+      <c r="C43" s="62" t="n">
         <v>8</v>
       </c>
       <c r="J43" s="18" t="inlineStr">
@@ -3438,11 +3581,10 @@
       </c>
       <c r="K43" s="19" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU EV/EBITDA
-Ctrl+F: "Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
-        </is>
-      </c>
-      <c r="L43" s="61" t="inlineStr">
+          <t>StockAnalysis: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="L43" s="49" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3454,7 +3596,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="C44" s="45">
+      <c r="C44" s="46">
         <f>C27*C43</f>
         <v/>
       </c>
@@ -3465,35 +3607,35 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C45" s="45">
+      <c r="C45" s="46">
         <f>C44/(1+Scenarios!$D$8)^H19</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="32">
         <f>C25+C45</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="22" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="62">
+      <c r="C47" s="63">
         <f>(C46+C32+C33)/C35</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="54" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3503,57 +3645,57 @@
       <c r="D49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="63" t="inlineStr"/>
-      <c r="B50" s="64" t="inlineStr">
+      <c r="A50" s="64" t="inlineStr"/>
+      <c r="B50" s="65" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="64" t="inlineStr">
+      <c r="C50" s="65" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="64" t="inlineStr">
+      <c r="D50" s="65" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="A51" s="22" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="55">
+      <c r="B51" s="57">
         <f>C28</f>
         <v/>
       </c>
-      <c r="C51" s="55">
+      <c r="C51" s="57">
         <f>C44</f>
         <v/>
       </c>
-      <c r="D51" s="55">
+      <c r="D51" s="57">
         <f>B51-C51</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B52" s="65">
+      <c r="B52" s="66">
         <f>C29</f>
         <v/>
       </c>
-      <c r="C52" s="65">
+      <c r="C52" s="66">
         <f>C43</f>
         <v/>
       </c>
-      <c r="D52" s="65">
+      <c r="D52" s="66">
         <f>B52-C52</f>
         <v/>
       </c>
@@ -3564,54 +3706,54 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B53" s="47" t="inlineStr"/>
-      <c r="C53" s="47" t="inlineStr"/>
-      <c r="D53" s="47">
+      <c r="B53" s="48" t="inlineStr"/>
+      <c r="C53" s="48" t="inlineStr"/>
+      <c r="D53" s="48">
         <f>(B51-C51)/B51</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="21" t="inlineStr">
+      <c r="A54" s="22" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="66">
+      <c r="B54" s="67">
         <f>C36</f>
         <v/>
       </c>
-      <c r="C54" s="66">
+      <c r="C54" s="67">
         <f>C47</f>
         <v/>
       </c>
-      <c r="D54" s="66">
+      <c r="D54" s="67">
         <f>B54-C54</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="67" t="inlineStr">
+      <c r="A55" s="68" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="68">
+      <c r="B55" s="69">
         <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C55" s="69">
+      <c r="C55" s="70">
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D55" s="36" t="inlineStr">
+      <c r="D55" s="37" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="54" t="inlineStr">
+      <c r="A58" s="56" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -3625,27 +3767,27 @@
       <c r="H58" s="13" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="70" t="inlineStr">
+      <c r="A59" s="71" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="71" t="n">
+      <c r="D59" s="72" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="71" t="n">
+      <c r="E59" s="72" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="71" t="n">
+      <c r="F59" s="72" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="71" t="n">
+      <c r="G59" s="72" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="71" t="n">
+      <c r="H59" s="72" t="n">
         <v>0.03</v>
       </c>
-      <c r="I59" s="61" t="inlineStr">
+      <c r="I59" s="49" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
@@ -3657,162 +3799,170 @@
       </c>
       <c r="K59" s="19" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)
-Ctrl+F: "GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="L59" s="20" t="inlineStr">
+        <is>
+          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
         </is>
       </c>
     </row>
     <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="71" t="n">
+      <c r="A60" s="72" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="72">
+      <c r="D60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E60" s="72">
+      <c r="E60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F60" s="72">
+      <c r="F60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G60" s="72">
+      <c r="G60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H60" s="72">
+      <c r="H60" s="73">
         <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I60" s="61" t="inlineStr">
+      <c r="I60" s="49" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
-      <c r="J60" s="42" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP
-Ctrl+F: "Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+      <c r="K60" s="49" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="L60" s="20" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="71" t="n">
+      <c r="A61" s="72" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="72">
+      <c r="D61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E61" s="72">
+      <c r="E61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F61" s="72">
+      <c r="F61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G61" s="72">
+      <c r="G61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H61" s="72">
+      <c r="H61" s="73">
         <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I61" s="61" t="inlineStr">
+      <c r="I61" s="49" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="71" t="n">
+      <c r="A62" s="72" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="72">
+      <c r="D62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E62" s="72">
+      <c r="E62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F62" s="73">
+      <c r="F62" s="74">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G62" s="72">
+      <c r="G62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H62" s="72">
+      <c r="H62" s="73">
         <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I62" s="61" t="inlineStr">
+      <c r="I62" s="49" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="71" t="n">
+      <c r="A63" s="72" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="72">
+      <c r="D63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E63" s="72">
+      <c r="E63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F63" s="72">
+      <c r="F63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G63" s="72">
+      <c r="G63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H63" s="72">
+      <c r="H63" s="73">
         <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I63" s="61" t="inlineStr">
+      <c r="I63" s="49" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="71" t="n">
+      <c r="A64" s="72" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="72">
+      <c r="D64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="E64" s="72">
+      <c r="E64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="F64" s="72">
+      <c r="F64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="G64" s="72">
+      <c r="G64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="H64" s="72">
+      <c r="H64" s="73">
         <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
         <v/>
       </c>
-      <c r="I64" s="61" t="inlineStr">
+      <c r="I64" s="49" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
@@ -3826,14 +3976,22 @@
       </c>
       <c r="K65" s="19" t="inlineStr">
         <is>
-          <t>Scenarios: WACC &amp; terminal g
-Ctrl+F: Scenarios tab → "WACC" row &amp; "Terminal growth" row (base inputs)</t>
-        </is>
-      </c>
-      <c r="L65" s="42" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)
-Ctrl+F: "GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+          <t>Scenarios: WACC &amp; terminal g</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>Scenarios tab → "WACC" row &amp; "Terminal growth" row (base inputs)</t>
+        </is>
+      </c>
+      <c r="M65" s="49" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="N65" s="20" t="inlineStr">
+        <is>
+          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
         </is>
       </c>
     </row>
@@ -3842,9 +4000,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
@@ -3863,13 +4021,13 @@
     <hyperlink ref="I59" location="'Scenarios'!D9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId21"/>
     <hyperlink ref="I60" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId22"/>
     <hyperlink ref="I61" location="'WACC'!C16"/>
     <hyperlink ref="I62" location="'WACC'!C16"/>
     <hyperlink ref="I63" location="'WACC'!C16"/>
     <hyperlink ref="I64" location="'WACC'!C16"/>
     <hyperlink ref="K65" location="'Scenarios'!D8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3881,19 +4039,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="2" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -3921,13 +4081,17 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="44" t="n">
+      <c r="C4" s="45" t="n">
         <v>11102600</v>
       </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Net revenue" → FY2025 $11,102,600 ($000)</t>
+      <c r="D4" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>"Net revenue" → FY2025 $11,102,600 ($000)</t>
         </is>
       </c>
     </row>
@@ -3937,7 +4101,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="45">
+      <c r="C5" s="46">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -3948,11 +4112,11 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="45">
+      <c r="C6" s="46">
         <f>DCF!C27</f>
         <v/>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
@@ -3964,13 +4128,17 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="58" t="n">
+      <c r="C7" s="60" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="D7" s="42" t="inlineStr">
-        <is>
-          <t>Release
-Ctrl+F: "diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
+      <c r="D7" s="49" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>"diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
         </is>
       </c>
     </row>
@@ -3980,13 +4148,17 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="45" t="n">
         <v>1807202</v>
       </c>
-      <c r="D8" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
         </is>
       </c>
     </row>
@@ -3996,13 +4168,17 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="45" t="n">
         <v>111380</v>
       </c>
-      <c r="D9" s="42" t="inlineStr">
-        <is>
-          <t>10-K
-Ctrl+F: "Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+      <c r="D9" s="49" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
     </row>
@@ -4012,34 +4188,38 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="58" t="n">
+      <c r="C10" s="60" t="n">
         <v>100</v>
       </c>
-      <c r="D10" s="42" t="inlineStr">
-        <is>
-          <t>NASDAQ
-Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="69" t="inlineStr">
+      <c r="A11" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="74">
+      <c r="C11" s="75">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="69" t="inlineStr">
+      <c r="A12" s="70" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C12" s="74">
+      <c r="C12" s="75">
         <f>C10/C7</f>
         <v/>
       </c>
@@ -4052,31 +4232,36 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="69" t="inlineStr">
+      <c r="A15" s="70" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="75" t="inlineStr">
+      <c r="A16" s="76" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="C16" s="76" t="inlineStr">
+      <c r="C16" s="77" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="E16" s="75" t="inlineStr">
+      <c r="E16" s="76" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="F16" s="75" t="inlineStr">
-        <is>
-          <t>Source &amp; Ctrl+F lines</t>
+      <c r="F16" s="76" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="G16" s="76" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
         </is>
       </c>
     </row>
@@ -4086,19 +4271,23 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="78">
         <f>(C10*C9-C8)/C5</f>
         <v/>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="F17" s="42" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K
-Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" → locate line item below</t>
+      <c r="F17" s="49" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>"Income from operations" $2,210,615 + "Depreciation and amortization" $496,228</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4297,7 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C18" s="78" t="n">
+      <c r="C18" s="79" t="n">
         <v>18</v>
       </c>
       <c r="E18" s="18" t="inlineStr">
@@ -4118,8 +4307,12 @@
       </c>
       <c r="F18" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: NKE statistics
-Ctrl+F: "Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
+          <t>Yahoo Finance: NKE statistics</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
         </is>
       </c>
     </row>
@@ -4129,7 +4322,7 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C19" s="78" t="n">
+      <c r="C19" s="79" t="n">
         <v>15</v>
       </c>
       <c r="E19" s="18" t="inlineStr">
@@ -4139,8 +4332,12 @@
       </c>
       <c r="F19" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: DECK statistics
-Ctrl+F: "Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
+          <t>Yahoo Finance: DECK statistics</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4347,7 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C20" s="78" t="n">
+      <c r="C20" s="79" t="n">
         <v>25</v>
       </c>
       <c r="E20" s="18" t="inlineStr">
@@ -4160,8 +4357,12 @@
       </c>
       <c r="F20" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: ONON statistics
-Ctrl+F: "Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
+          <t>Yahoo Finance: ONON statistics</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4372,7 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C21" s="78" t="n">
+      <c r="C21" s="79" t="n">
         <v>12</v>
       </c>
       <c r="E21" s="18" t="inlineStr">
@@ -4181,8 +4382,12 @@
       </c>
       <c r="F21" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: adidas (ADDYY)
-Ctrl+F: "Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
+          <t>Yahoo Finance: adidas (ADDYY)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4397,7 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C22" s="78" t="n">
+      <c r="C22" s="79" t="n">
         <v>10</v>
       </c>
       <c r="E22" s="18" t="inlineStr">
@@ -4202,8 +4407,12 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: VFC statistics
-Ctrl+F: "Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
+          <t>Yahoo Finance: VFC statistics</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
         </is>
       </c>
     </row>
@@ -4220,18 +4429,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="58">
         <f>DCF!C29</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="68" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C26" s="65">
+      <c r="C26" s="66">
         <f>DCF!C43</f>
         <v/>
       </c>
@@ -4242,48 +4451,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C27" s="56">
+      <c r="C27" s="58">
         <f>C26-C25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="67" t="inlineStr">
+      <c r="A28" s="68" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="29" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="29" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="29" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" s="29" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4297,49 +4506,59 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="A36" s="76" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C36" s="76" t="inlineStr">
+      <c r="C36" s="77" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D36" s="76" t="inlineStr">
+      <c r="D36" s="77" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E36" s="76" t="inlineStr">
+      <c r="E36" s="77" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F36" s="76" t="inlineStr">
+      <c r="F36" s="77" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
-      <c r="G36" s="79" t="inlineStr">
+      <c r="G36" s="80" t="inlineStr">
         <is>
           <t>Lo justification</t>
         </is>
       </c>
-      <c r="H36" s="79" t="inlineStr">
-        <is>
-          <t>Lo source &amp; Ctrl+F</t>
-        </is>
-      </c>
-      <c r="I36" s="79" t="inlineStr">
+      <c r="H36" s="80" t="inlineStr">
+        <is>
+          <t>Lo source</t>
+        </is>
+      </c>
+      <c r="I36" s="80" t="inlineStr">
+        <is>
+          <t>Lo Ctrl+F</t>
+        </is>
+      </c>
+      <c r="J36" s="80" t="inlineStr">
         <is>
           <t>Hi justification</t>
         </is>
       </c>
-      <c r="J36" s="79" t="inlineStr">
-        <is>
-          <t>Hi source &amp; Ctrl+F</t>
+      <c r="K36" s="80" t="inlineStr">
+        <is>
+          <t>Hi source</t>
+        </is>
+      </c>
+      <c r="L36" s="80" t="inlineStr">
+        <is>
+          <t>Hi Ctrl+F</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4568,17 @@
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="C37" s="78" t="n">
+      <c r="C37" s="79" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37" s="78" t="n">
+      <c r="D37" s="79" t="n">
         <v>9.5</v>
       </c>
-      <c r="E37" s="80">
+      <c r="E37" s="81">
         <f>(C6*C37+C8)/C9</f>
         <v/>
       </c>
-      <c r="F37" s="80">
+      <c r="F37" s="81">
         <f>(C6*D37+C8)/C9</f>
         <v/>
       </c>
@@ -4370,37 +4589,45 @@
       </c>
       <c r="H37" s="19" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU EV/EBITDA
-Ctrl+F: "Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x</t>
-        </is>
-      </c>
-      <c r="I37" s="81" t="inlineStr">
+          <t>StockAnalysis: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="I37" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x</t>
+        </is>
+      </c>
+      <c r="J37" s="82" t="inlineStr">
         <is>
           <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
-      <c r="J37" s="82" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU valuation
-Ctrl+F: "Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
+      <c r="K37" s="83" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU valuation</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="67" t="inlineStr">
+      <c r="A38" s="68" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="C38" s="83">
+      <c r="C38" s="84">
         <f>DCF!C43</f>
         <v/>
       </c>
-      <c r="E38" s="84">
+      <c r="E38" s="85">
         <f>(C6*C38+C8)/C9</f>
         <v/>
       </c>
-      <c r="I38" s="61" t="inlineStr">
+      <c r="I38" s="49" t="inlineStr">
         <is>
           <t>↳ DCF exit multiple</t>
         </is>
@@ -4412,17 +4639,17 @@
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C39" s="78" t="n">
+      <c r="C39" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="78" t="n">
+      <c r="D39" s="79" t="n">
         <v>18</v>
       </c>
-      <c r="E39" s="80">
+      <c r="E39" s="81">
         <f>C7*C39</f>
         <v/>
       </c>
-      <c r="F39" s="80">
+      <c r="F39" s="81">
         <f>C7*D39</f>
         <v/>
       </c>
@@ -4433,19 +4660,27 @@
       </c>
       <c r="H39" s="19" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU P/E
-Ctrl+F: "Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x</t>
-        </is>
-      </c>
-      <c r="I39" s="81" t="inlineStr">
+          <t>Yahoo Finance: LULU P/E</t>
+        </is>
+      </c>
+      <c r="I39" s="20" t="inlineStr">
+        <is>
+          <t>"Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x</t>
+        </is>
+      </c>
+      <c r="J39" s="82" t="inlineStr">
         <is>
           <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="J39" s="82" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: NKE P/E (peer)
-Ctrl+F: "Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
+      <c r="K39" s="83" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE P/E (peer)</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>"Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
         </is>
       </c>
     </row>
@@ -4455,43 +4690,47 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C40" s="85" t="inlineStr">
+      <c r="C40" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="85" t="inlineStr">
+      <c r="D40" s="86" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="80">
+      <c r="E40" s="81">
         <f>Scenarios!C58</f>
         <v/>
       </c>
-      <c r="F40" s="80">
+      <c r="F40" s="81">
         <f>Scenarios!E58</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="86" t="inlineStr">
+      <c r="A42" s="87" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="87" t="n">
+      <c r="C42" s="88" t="n">
         <v>100</v>
       </c>
-      <c r="D42" s="42" t="inlineStr">
-        <is>
-          <t>NASDAQ
-Ctrl+F: "Last Sale" or "Previous Close" → LULU share price</t>
+      <c r="D42" s="49" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="37" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
@@ -4517,10 +4756,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J37" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId18"/>
     <hyperlink ref="I38" location="'DCF'!C43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId22"/>
   </hyperlinks>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="45">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -292,25 +292,6 @@
     </font>
     <font>
       <name val="Garamond"/>
-      <i val="1"/>
-      <color rgb="00000000"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <i val="1"/>
-      <color rgb="000000CC"/>
-      <sz val="7"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <i val="1"/>
-      <color rgb="000000CC"/>
-      <sz val="7"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
       <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="11"/>
@@ -375,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -401,18 +382,18 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -455,15 +436,15 @@
     <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -473,14 +454,11 @@
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -494,11 +472,11 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -525,6 +503,9 @@
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="38" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -586,18 +567,12 @@
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -610,7 +585,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="47" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1037,7 +1012,7 @@
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Red font  =  analyst assumptions — Justification | Source (click) | Ctrl+F columns prove the number</t>
+          <t>Red font  =  analyst assumptions — cols B/C/D on every tab: Justification | Source | Ctrl+F</t>
         </is>
       </c>
     </row>
@@ -1118,14 +1093,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1134,10 +1109,10 @@
           <t>WEIGHTED AVERAGE COST OF CAPITAL</t>
         </is>
       </c>
+      <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
@@ -1145,17 +1120,17 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
       <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Justification (~20 words)</t>
-        </is>
-      </c>
-      <c r="E2" s="15" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
@@ -1167,23 +1142,23 @@
           <t>Risk-free rate (10-yr UST)</t>
         </is>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>FRED: 10Y Treasury (DGS10)</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>"DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
         <v>0.043</v>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
-        </is>
-      </c>
-      <c r="E3" s="19" t="inlineStr">
-        <is>
-          <t>FRED: 10Y Treasury (DGS10)</t>
-        </is>
-      </c>
-      <c r="F3" s="20" t="inlineStr">
-        <is>
-          <t>"DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
-        </is>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
@@ -1192,23 +1167,23 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="n">
         <v>0.06</v>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>"Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
-        </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -1217,23 +1192,23 @@
           <t>Levered beta</t>
         </is>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU Beta</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>"Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="n">
         <v>0.95</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: LULU Beta</t>
-        </is>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>"Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -1242,8 +1217,8 @@
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="C6" s="23">
-        <f>C3+C5*C4</f>
+      <c r="E6" s="23">
+        <f>E3+E5*E4</f>
         <v/>
       </c>
     </row>
@@ -1260,23 +1235,23 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K (no funded debt)</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>"no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
         <v>0.05</v>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K (no funded debt)</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>"no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
-        </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -1285,23 +1260,23 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>"United States" → Damodaran effective tax rate ~25%; model 27%</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
         <v>0.27</v>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>Damodaran: US tax rate dataset</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>"United States" → Damodaran effective tax rate ~25%; model 27%</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -1310,8 +1285,8 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="C11" s="24">
-        <f>C9*(1-C10)</f>
+      <c r="E11" s="24">
+        <f>E9*(1-E10)</f>
         <v/>
       </c>
     </row>
@@ -1328,23 +1303,23 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n">
         <v>1</v>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>"Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
-        </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
@@ -1353,23 +1328,23 @@
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>"Long-term debt" → none outstanding; debt weight 0%</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="n">
         <v>0</v>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>"Long-term debt" → none outstanding; debt weight 0%</t>
-        </is>
       </c>
     </row>
     <row r="16">
@@ -1378,20 +1353,20 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C16" s="25">
-        <f>C14*C6+C15*C11</f>
+      <c r="E16" s="25">
+        <f>E14*E6+E15*E11</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1406,13 +1381,13 @@
   <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -1425,19 +1400,22 @@
       <c r="C1" s="13" t="n"/>
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="26" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="D2" s="27" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="E2" s="28" t="inlineStr">
+      <c r="H2" s="28" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1449,17 +1427,17 @@
           <t>Key assumptions (5-yr forecast)</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="G3" s="15" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
@@ -1471,29 +1449,29 @@
           <t>FY2026E revenue growth</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="n">
         <v>-0.09</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="G4" s="20" t="n">
         <v>-0.061</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="H4" s="20" t="n">
         <v>-0.04</v>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
-        </is>
-      </c>
-      <c r="G4" s="19" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
-        </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
@@ -1502,29 +1480,29 @@
           <t>FY2027–FY2030E revenue growth (avg)</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical revenue (10-K)</t>
+        </is>
+      </c>
+      <c r="D5" s="19" t="inlineStr">
+        <is>
+          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="G5" s="20" t="n">
         <v>0.028</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="H5" s="20" t="n">
         <v>0.06</v>
-      </c>
-      <c r="F5" s="18" t="inlineStr">
-        <is>
-          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
-        </is>
-      </c>
-      <c r="G5" s="19" t="inlineStr">
-        <is>
-          <t>LULU historical revenue (10-K)</t>
-        </is>
-      </c>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
-        </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
@@ -1533,29 +1511,29 @@
           <t>FY2026E EBIT margin</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
         <v>0.125</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.139</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="H6" s="20" t="n">
         <v>0.15</v>
-      </c>
-      <c r="F6" s="18" t="inlineStr">
-        <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
-        </is>
-      </c>
-      <c r="G6" s="19" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
-        </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
@@ -1564,29 +1542,29 @@
           <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
         <v>0.12</v>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="G7" s="20" t="n">
         <v>0.155</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="H7" s="20" t="n">
         <v>0.19</v>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>LULU historical EBIT margins (10-K)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
-        </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -1595,29 +1573,29 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>WACC tab: CAPM build</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>WACC tab → cell E (green) = 10.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="n">
         <v>0.11</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="G8" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="H8" s="20" t="n">
         <v>0.09</v>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
-        </is>
-      </c>
-      <c r="G8" s="19" t="inlineStr">
-        <is>
-          <t>WACC tab: CAPM build</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>WACC tab → cell C (green) = 10.0%</t>
-        </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -1626,29 +1604,29 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="n">
         <v>0.015</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="G9" s="20" t="n">
         <v>0.0225</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="H9" s="20" t="n">
         <v>0.03</v>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
-        </is>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
-        </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -1657,29 +1635,29 @@
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Damodaran: US tax rate dataset</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>"Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="G10" s="20" t="n">
         <v>0.27</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="H10" s="20" t="n">
         <v>0.25</v>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
-        </is>
-      </c>
-      <c r="G10" s="19" t="inlineStr">
-        <is>
-          <t>Damodaran: US tax rate dataset</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>"Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
-        </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -1688,29 +1666,29 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n">
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="n">
         <v>0.045</v>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="G11" s="20" t="n">
         <v>0.045</v>
       </c>
-      <c r="E11" s="17" t="n">
+      <c r="H11" s="20" t="n">
         <v>0.045</v>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
-        </is>
-      </c>
-      <c r="G11" s="19" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
-        </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
@@ -1719,29 +1697,29 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="C12" s="17" t="n">
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="n">
         <v>0.055</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="G12" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="H12" s="20" t="n">
         <v>0.045</v>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
-        </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
@@ -1750,29 +1728,29 @@
           <t>NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n">
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="G13" s="20" t="n">
         <v>0.075</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="H13" s="20" t="n">
         <v>0.07000000000000001</v>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
-        </is>
-      </c>
-      <c r="G13" s="19" t="inlineStr">
-        <is>
-          <t>LULU BS/IS historical (10-K)</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
-        </is>
       </c>
     </row>
     <row r="15">
@@ -1788,16 +1766,16 @@
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="C16" s="30">
-        <f>11102600*(1+C4)</f>
-        <v/>
-      </c>
-      <c r="D16" s="30">
-        <f>11102600*(1+D4)</f>
-        <v/>
-      </c>
-      <c r="E16" s="30">
-        <f>11102600*(1+E4)</f>
+      <c r="F16" s="30">
+        <f>11102600*(1+F4)</f>
+        <v/>
+      </c>
+      <c r="G16" s="30">
+        <f>11102600*(1+G4)</f>
+        <v/>
+      </c>
+      <c r="H16" s="30">
+        <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
@@ -1807,16 +1785,16 @@
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="C17" s="30">
-        <f>C16*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D17" s="30">
-        <f>D16*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E17" s="30">
-        <f>E16*(1+E5)</f>
+      <c r="F17" s="30">
+        <f>F16*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G17" s="30">
+        <f>G16*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H17" s="30">
+        <f>H16*(1+H5)</f>
         <v/>
       </c>
     </row>
@@ -1826,16 +1804,16 @@
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="C18" s="30">
-        <f>C17*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D18" s="30">
-        <f>D17*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E18" s="30">
-        <f>E17*(1+E5)</f>
+      <c r="F18" s="30">
+        <f>F17*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G18" s="30">
+        <f>G17*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H18" s="30">
+        <f>H17*(1+H5)</f>
         <v/>
       </c>
     </row>
@@ -1845,16 +1823,16 @@
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="C19" s="30">
-        <f>C18*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D19" s="30">
-        <f>D18*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E19" s="30">
-        <f>E18*(1+E5)</f>
+      <c r="F19" s="30">
+        <f>F18*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G19" s="30">
+        <f>G18*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H19" s="30">
+        <f>H18*(1+H5)</f>
         <v/>
       </c>
     </row>
@@ -1864,16 +1842,16 @@
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="C20" s="30">
-        <f>C19*(1+C5)</f>
-        <v/>
-      </c>
-      <c r="D20" s="30">
-        <f>D19*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E20" s="30">
-        <f>E19*(1+E5)</f>
+      <c r="F20" s="30">
+        <f>F19*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G20" s="30">
+        <f>G19*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H20" s="30">
+        <f>H19*(1+H5)</f>
         <v/>
       </c>
     </row>
@@ -1883,16 +1861,16 @@
           <t xml:space="preserve">  EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="C21" s="31">
-        <f>C6+(C7-C6)*0/4</f>
-        <v/>
-      </c>
-      <c r="D21" s="31">
-        <f>D6+(D7-D6)*0/4</f>
-        <v/>
-      </c>
-      <c r="E21" s="31">
-        <f>E6+(E7-E6)*0/4</f>
+      <c r="F21" s="31">
+        <f>F6+(F7-F6)*0/4</f>
+        <v/>
+      </c>
+      <c r="G21" s="31">
+        <f>G6+(G7-G6)*0/4</f>
+        <v/>
+      </c>
+      <c r="H21" s="31">
+        <f>H6+(H7-H6)*0/4</f>
         <v/>
       </c>
     </row>
@@ -1902,16 +1880,16 @@
           <t xml:space="preserve">  EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="C22" s="31">
-        <f>C6+(C7-C6)*1/4</f>
-        <v/>
-      </c>
-      <c r="D22" s="31">
-        <f>D6+(D7-D6)*1/4</f>
-        <v/>
-      </c>
-      <c r="E22" s="31">
-        <f>E6+(E7-E6)*1/4</f>
+      <c r="F22" s="31">
+        <f>F6+(F7-F6)*1/4</f>
+        <v/>
+      </c>
+      <c r="G22" s="31">
+        <f>G6+(G7-G6)*1/4</f>
+        <v/>
+      </c>
+      <c r="H22" s="31">
+        <f>H6+(H7-H6)*1/4</f>
         <v/>
       </c>
     </row>
@@ -1921,16 +1899,16 @@
           <t xml:space="preserve">  EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="C23" s="31">
-        <f>C6+(C7-C6)*2/4</f>
-        <v/>
-      </c>
-      <c r="D23" s="31">
-        <f>D6+(D7-D6)*2/4</f>
-        <v/>
-      </c>
-      <c r="E23" s="31">
-        <f>E6+(E7-E6)*2/4</f>
+      <c r="F23" s="31">
+        <f>F6+(F7-F6)*2/4</f>
+        <v/>
+      </c>
+      <c r="G23" s="31">
+        <f>G6+(G7-G6)*2/4</f>
+        <v/>
+      </c>
+      <c r="H23" s="31">
+        <f>H6+(H7-H6)*2/4</f>
         <v/>
       </c>
     </row>
@@ -1940,16 +1918,16 @@
           <t xml:space="preserve">  EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="C24" s="31">
-        <f>C6+(C7-C6)*3/4</f>
-        <v/>
-      </c>
-      <c r="D24" s="31">
-        <f>D6+(D7-D6)*3/4</f>
-        <v/>
-      </c>
-      <c r="E24" s="31">
-        <f>E6+(E7-E6)*3/4</f>
+      <c r="F24" s="31">
+        <f>F6+(F7-F6)*3/4</f>
+        <v/>
+      </c>
+      <c r="G24" s="31">
+        <f>G6+(G7-G6)*3/4</f>
+        <v/>
+      </c>
+      <c r="H24" s="31">
+        <f>H6+(H7-H6)*3/4</f>
         <v/>
       </c>
     </row>
@@ -1959,16 +1937,16 @@
           <t xml:space="preserve">  EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="C25" s="31">
-        <f>C6+(C7-C6)*4/4</f>
-        <v/>
-      </c>
-      <c r="D25" s="31">
-        <f>D6+(D7-D6)*4/4</f>
-        <v/>
-      </c>
-      <c r="E25" s="31">
-        <f>E6+(E7-E6)*4/4</f>
+      <c r="F25" s="31">
+        <f>F6+(F7-F6)*4/4</f>
+        <v/>
+      </c>
+      <c r="G25" s="31">
+        <f>G6+(G7-G6)*4/4</f>
+        <v/>
+      </c>
+      <c r="H25" s="31">
+        <f>H6+(H7-H6)*4/4</f>
         <v/>
       </c>
     </row>
@@ -1978,16 +1956,16 @@
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="C26" s="30">
-        <f>C16*C21</f>
-        <v/>
-      </c>
-      <c r="D26" s="30">
-        <f>D16*D21</f>
-        <v/>
-      </c>
-      <c r="E26" s="30">
-        <f>E16*E21</f>
+      <c r="F26" s="30">
+        <f>F16*F21</f>
+        <v/>
+      </c>
+      <c r="G26" s="30">
+        <f>G16*G21</f>
+        <v/>
+      </c>
+      <c r="H26" s="30">
+        <f>H16*H21</f>
         <v/>
       </c>
     </row>
@@ -1997,16 +1975,16 @@
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="C27" s="30">
-        <f>C17*C22</f>
-        <v/>
-      </c>
-      <c r="D27" s="30">
-        <f>D17*D22</f>
-        <v/>
-      </c>
-      <c r="E27" s="30">
-        <f>E17*E22</f>
+      <c r="F27" s="30">
+        <f>F17*F22</f>
+        <v/>
+      </c>
+      <c r="G27" s="30">
+        <f>G17*G22</f>
+        <v/>
+      </c>
+      <c r="H27" s="30">
+        <f>H17*H22</f>
         <v/>
       </c>
     </row>
@@ -2016,16 +1994,16 @@
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="C28" s="30">
-        <f>C18*C23</f>
-        <v/>
-      </c>
-      <c r="D28" s="30">
-        <f>D18*D23</f>
-        <v/>
-      </c>
-      <c r="E28" s="30">
-        <f>E18*E23</f>
+      <c r="F28" s="30">
+        <f>F18*F23</f>
+        <v/>
+      </c>
+      <c r="G28" s="30">
+        <f>G18*G23</f>
+        <v/>
+      </c>
+      <c r="H28" s="30">
+        <f>H18*H23</f>
         <v/>
       </c>
     </row>
@@ -2035,16 +2013,16 @@
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="C29" s="30">
-        <f>C19*C24</f>
-        <v/>
-      </c>
-      <c r="D29" s="30">
-        <f>D19*D24</f>
-        <v/>
-      </c>
-      <c r="E29" s="30">
-        <f>E19*E24</f>
+      <c r="F29" s="30">
+        <f>F19*F24</f>
+        <v/>
+      </c>
+      <c r="G29" s="30">
+        <f>G19*G24</f>
+        <v/>
+      </c>
+      <c r="H29" s="30">
+        <f>H19*H24</f>
         <v/>
       </c>
     </row>
@@ -2054,16 +2032,16 @@
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="C30" s="30">
-        <f>C20*C25</f>
-        <v/>
-      </c>
-      <c r="D30" s="30">
-        <f>D20*D25</f>
-        <v/>
-      </c>
-      <c r="E30" s="30">
-        <f>E20*E25</f>
+      <c r="F30" s="30">
+        <f>F20*F25</f>
+        <v/>
+      </c>
+      <c r="G30" s="30">
+        <f>G20*G25</f>
+        <v/>
+      </c>
+      <c r="H30" s="30">
+        <f>H20*H25</f>
         <v/>
       </c>
     </row>
@@ -2073,16 +2051,16 @@
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="C31" s="30">
-        <f>C26*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="D31" s="30">
-        <f>D26*(1-D10)</f>
-        <v/>
-      </c>
-      <c r="E31" s="30">
-        <f>E26*(1-E10)</f>
+      <c r="F31" s="30">
+        <f>F26*(1-F10)</f>
+        <v/>
+      </c>
+      <c r="G31" s="30">
+        <f>G26*(1-G10)</f>
+        <v/>
+      </c>
+      <c r="H31" s="30">
+        <f>H26*(1-H10)</f>
         <v/>
       </c>
     </row>
@@ -2092,16 +2070,16 @@
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="C32" s="30">
-        <f>C27*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="D32" s="30">
-        <f>D27*(1-D10)</f>
-        <v/>
-      </c>
-      <c r="E32" s="30">
-        <f>E27*(1-E10)</f>
+      <c r="F32" s="30">
+        <f>F27*(1-F10)</f>
+        <v/>
+      </c>
+      <c r="G32" s="30">
+        <f>G27*(1-G10)</f>
+        <v/>
+      </c>
+      <c r="H32" s="30">
+        <f>H27*(1-H10)</f>
         <v/>
       </c>
     </row>
@@ -2111,16 +2089,16 @@
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="C33" s="30">
-        <f>C28*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="D33" s="30">
-        <f>D28*(1-D10)</f>
-        <v/>
-      </c>
-      <c r="E33" s="30">
-        <f>E28*(1-E10)</f>
+      <c r="F33" s="30">
+        <f>F28*(1-F10)</f>
+        <v/>
+      </c>
+      <c r="G33" s="30">
+        <f>G28*(1-G10)</f>
+        <v/>
+      </c>
+      <c r="H33" s="30">
+        <f>H28*(1-H10)</f>
         <v/>
       </c>
     </row>
@@ -2130,16 +2108,16 @@
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="C34" s="30">
-        <f>C29*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="D34" s="30">
-        <f>D29*(1-D10)</f>
-        <v/>
-      </c>
-      <c r="E34" s="30">
-        <f>E29*(1-E10)</f>
+      <c r="F34" s="30">
+        <f>F29*(1-F10)</f>
+        <v/>
+      </c>
+      <c r="G34" s="30">
+        <f>G29*(1-G10)</f>
+        <v/>
+      </c>
+      <c r="H34" s="30">
+        <f>H29*(1-H10)</f>
         <v/>
       </c>
     </row>
@@ -2149,16 +2127,16 @@
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="C35" s="30">
-        <f>C30*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="D35" s="30">
-        <f>D30*(1-D10)</f>
-        <v/>
-      </c>
-      <c r="E35" s="30">
-        <f>E30*(1-E10)</f>
+      <c r="F35" s="30">
+        <f>F30*(1-F10)</f>
+        <v/>
+      </c>
+      <c r="G35" s="30">
+        <f>G30*(1-G10)</f>
+        <v/>
+      </c>
+      <c r="H35" s="30">
+        <f>H30*(1-H10)</f>
         <v/>
       </c>
     </row>
@@ -2168,16 +2146,16 @@
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="C36" s="30">
-        <f>C16*C11</f>
-        <v/>
-      </c>
-      <c r="D36" s="30">
-        <f>D16*D11</f>
-        <v/>
-      </c>
-      <c r="E36" s="30">
-        <f>E16*E11</f>
+      <c r="F36" s="30">
+        <f>F16*F11</f>
+        <v/>
+      </c>
+      <c r="G36" s="30">
+        <f>G16*G11</f>
+        <v/>
+      </c>
+      <c r="H36" s="30">
+        <f>H16*H11</f>
         <v/>
       </c>
     </row>
@@ -2187,16 +2165,16 @@
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="C37" s="30">
-        <f>C17*C11</f>
-        <v/>
-      </c>
-      <c r="D37" s="30">
-        <f>D17*D11</f>
-        <v/>
-      </c>
-      <c r="E37" s="30">
-        <f>E17*E11</f>
+      <c r="F37" s="30">
+        <f>F17*F11</f>
+        <v/>
+      </c>
+      <c r="G37" s="30">
+        <f>G17*G11</f>
+        <v/>
+      </c>
+      <c r="H37" s="30">
+        <f>H17*H11</f>
         <v/>
       </c>
     </row>
@@ -2206,16 +2184,16 @@
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="C38" s="30">
-        <f>C18*C11</f>
-        <v/>
-      </c>
-      <c r="D38" s="30">
-        <f>D18*D11</f>
-        <v/>
-      </c>
-      <c r="E38" s="30">
-        <f>E18*E11</f>
+      <c r="F38" s="30">
+        <f>F18*F11</f>
+        <v/>
+      </c>
+      <c r="G38" s="30">
+        <f>G18*G11</f>
+        <v/>
+      </c>
+      <c r="H38" s="30">
+        <f>H18*H11</f>
         <v/>
       </c>
     </row>
@@ -2225,16 +2203,16 @@
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="C39" s="30">
-        <f>C19*C11</f>
-        <v/>
-      </c>
-      <c r="D39" s="30">
-        <f>D19*D11</f>
-        <v/>
-      </c>
-      <c r="E39" s="30">
-        <f>E19*E11</f>
+      <c r="F39" s="30">
+        <f>F19*F11</f>
+        <v/>
+      </c>
+      <c r="G39" s="30">
+        <f>G19*G11</f>
+        <v/>
+      </c>
+      <c r="H39" s="30">
+        <f>H19*H11</f>
         <v/>
       </c>
     </row>
@@ -2244,16 +2222,16 @@
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="C40" s="30">
-        <f>C20*C11</f>
-        <v/>
-      </c>
-      <c r="D40" s="30">
-        <f>D20*D11</f>
-        <v/>
-      </c>
-      <c r="E40" s="30">
-        <f>E20*E11</f>
+      <c r="F40" s="30">
+        <f>F20*F11</f>
+        <v/>
+      </c>
+      <c r="G40" s="30">
+        <f>G20*G11</f>
+        <v/>
+      </c>
+      <c r="H40" s="30">
+        <f>H20*H11</f>
         <v/>
       </c>
     </row>
@@ -2263,16 +2241,16 @@
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="C41" s="30">
-        <f>C16*C12</f>
-        <v/>
-      </c>
-      <c r="D41" s="30">
-        <f>D16*D12</f>
-        <v/>
-      </c>
-      <c r="E41" s="30">
-        <f>E16*E12</f>
+      <c r="F41" s="30">
+        <f>F16*F12</f>
+        <v/>
+      </c>
+      <c r="G41" s="30">
+        <f>G16*G12</f>
+        <v/>
+      </c>
+      <c r="H41" s="30">
+        <f>H16*H12</f>
         <v/>
       </c>
     </row>
@@ -2282,16 +2260,16 @@
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="C42" s="30">
-        <f>C17*C12</f>
-        <v/>
-      </c>
-      <c r="D42" s="30">
-        <f>D17*D12</f>
-        <v/>
-      </c>
-      <c r="E42" s="30">
-        <f>E17*E12</f>
+      <c r="F42" s="30">
+        <f>F17*F12</f>
+        <v/>
+      </c>
+      <c r="G42" s="30">
+        <f>G17*G12</f>
+        <v/>
+      </c>
+      <c r="H42" s="30">
+        <f>H17*H12</f>
         <v/>
       </c>
     </row>
@@ -2301,16 +2279,16 @@
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="C43" s="30">
-        <f>C18*C12</f>
-        <v/>
-      </c>
-      <c r="D43" s="30">
-        <f>D18*D12</f>
-        <v/>
-      </c>
-      <c r="E43" s="30">
-        <f>E18*E12</f>
+      <c r="F43" s="30">
+        <f>F18*F12</f>
+        <v/>
+      </c>
+      <c r="G43" s="30">
+        <f>G18*G12</f>
+        <v/>
+      </c>
+      <c r="H43" s="30">
+        <f>H18*H12</f>
         <v/>
       </c>
     </row>
@@ -2320,16 +2298,16 @@
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="C44" s="30">
-        <f>C19*C12</f>
-        <v/>
-      </c>
-      <c r="D44" s="30">
-        <f>D19*D12</f>
-        <v/>
-      </c>
-      <c r="E44" s="30">
-        <f>E19*E12</f>
+      <c r="F44" s="30">
+        <f>F19*F12</f>
+        <v/>
+      </c>
+      <c r="G44" s="30">
+        <f>G19*G12</f>
+        <v/>
+      </c>
+      <c r="H44" s="30">
+        <f>H19*H12</f>
         <v/>
       </c>
     </row>
@@ -2339,16 +2317,16 @@
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="C45" s="30">
-        <f>C20*C12</f>
-        <v/>
-      </c>
-      <c r="D45" s="30">
-        <f>D20*D12</f>
-        <v/>
-      </c>
-      <c r="E45" s="30">
-        <f>E20*E12</f>
+      <c r="F45" s="30">
+        <f>F20*F12</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>G20*G12</f>
+        <v/>
+      </c>
+      <c r="H45" s="30">
+        <f>H20*H12</f>
         <v/>
       </c>
     </row>
@@ -2358,16 +2336,16 @@
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="C46" s="30">
-        <f>C13*(C16-11102600)</f>
-        <v/>
-      </c>
-      <c r="D46" s="30">
-        <f>D13*(D16-11102600)</f>
-        <v/>
-      </c>
-      <c r="E46" s="30">
-        <f>E13*(E16-11102600)</f>
+      <c r="F46" s="30">
+        <f>F13*(F16-11102600)</f>
+        <v/>
+      </c>
+      <c r="G46" s="30">
+        <f>G13*(G16-11102600)</f>
+        <v/>
+      </c>
+      <c r="H46" s="30">
+        <f>H13*(H16-11102600)</f>
         <v/>
       </c>
     </row>
@@ -2377,16 +2355,16 @@
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="C47" s="30">
-        <f>C13*(C17-C16)</f>
-        <v/>
-      </c>
-      <c r="D47" s="30">
-        <f>D13*(D17-D16)</f>
-        <v/>
-      </c>
-      <c r="E47" s="30">
-        <f>E13*(E17-E16)</f>
+      <c r="F47" s="30">
+        <f>F13*(F17-F16)</f>
+        <v/>
+      </c>
+      <c r="G47" s="30">
+        <f>G13*(G17-G16)</f>
+        <v/>
+      </c>
+      <c r="H47" s="30">
+        <f>H13*(H17-H16)</f>
         <v/>
       </c>
     </row>
@@ -2396,16 +2374,16 @@
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="C48" s="30">
-        <f>C13*(C18-C17)</f>
-        <v/>
-      </c>
-      <c r="D48" s="30">
-        <f>D13*(D18-D17)</f>
-        <v/>
-      </c>
-      <c r="E48" s="30">
-        <f>E13*(E18-E17)</f>
+      <c r="F48" s="30">
+        <f>F13*(F18-F17)</f>
+        <v/>
+      </c>
+      <c r="G48" s="30">
+        <f>G13*(G18-G17)</f>
+        <v/>
+      </c>
+      <c r="H48" s="30">
+        <f>H13*(H18-H17)</f>
         <v/>
       </c>
     </row>
@@ -2415,16 +2393,16 @@
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="C49" s="30">
-        <f>C13*(C19-C18)</f>
-        <v/>
-      </c>
-      <c r="D49" s="30">
-        <f>D13*(D19-D18)</f>
-        <v/>
-      </c>
-      <c r="E49" s="30">
-        <f>E13*(E19-E18)</f>
+      <c r="F49" s="30">
+        <f>F13*(F19-F18)</f>
+        <v/>
+      </c>
+      <c r="G49" s="30">
+        <f>G13*(G19-G18)</f>
+        <v/>
+      </c>
+      <c r="H49" s="30">
+        <f>H13*(H19-H18)</f>
         <v/>
       </c>
     </row>
@@ -2434,16 +2412,16 @@
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="C50" s="30">
-        <f>C13*(C20-C19)</f>
-        <v/>
-      </c>
-      <c r="D50" s="30">
-        <f>D13*(D20-D19)</f>
-        <v/>
-      </c>
-      <c r="E50" s="30">
-        <f>E13*(E20-E19)</f>
+      <c r="F50" s="30">
+        <f>F13*(F20-F19)</f>
+        <v/>
+      </c>
+      <c r="G50" s="30">
+        <f>G13*(G20-G19)</f>
+        <v/>
+      </c>
+      <c r="H50" s="30">
+        <f>H13*(H20-H19)</f>
         <v/>
       </c>
     </row>
@@ -2453,16 +2431,16 @@
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="C51" s="30">
-        <f>C31+C36-C41-C46</f>
-        <v/>
-      </c>
-      <c r="D51" s="30">
-        <f>D31+D36-D41-D46</f>
-        <v/>
-      </c>
-      <c r="E51" s="30">
-        <f>E31+E36-E41-E46</f>
+      <c r="F51" s="30">
+        <f>F31+F36-F41-F46</f>
+        <v/>
+      </c>
+      <c r="G51" s="30">
+        <f>G31+G36-G41-G46</f>
+        <v/>
+      </c>
+      <c r="H51" s="30">
+        <f>H31+H36-H41-H46</f>
         <v/>
       </c>
     </row>
@@ -2472,16 +2450,16 @@
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="C52" s="30">
-        <f>C32+C37-C42-C47</f>
-        <v/>
-      </c>
-      <c r="D52" s="30">
-        <f>D32+D37-D42-D47</f>
-        <v/>
-      </c>
-      <c r="E52" s="30">
-        <f>E32+E37-E42-E47</f>
+      <c r="F52" s="30">
+        <f>F32+F37-F42-F47</f>
+        <v/>
+      </c>
+      <c r="G52" s="30">
+        <f>G32+G37-G42-G47</f>
+        <v/>
+      </c>
+      <c r="H52" s="30">
+        <f>H32+H37-H42-H47</f>
         <v/>
       </c>
     </row>
@@ -2491,16 +2469,16 @@
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="C53" s="30">
-        <f>C33+C38-C43-C48</f>
-        <v/>
-      </c>
-      <c r="D53" s="30">
-        <f>D33+D38-D43-D48</f>
-        <v/>
-      </c>
-      <c r="E53" s="30">
-        <f>E33+E38-E43-E48</f>
+      <c r="F53" s="30">
+        <f>F33+F38-F43-F48</f>
+        <v/>
+      </c>
+      <c r="G53" s="30">
+        <f>G33+G38-G43-G48</f>
+        <v/>
+      </c>
+      <c r="H53" s="30">
+        <f>H33+H38-H43-H48</f>
         <v/>
       </c>
     </row>
@@ -2510,16 +2488,16 @@
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="C54" s="30">
-        <f>C34+C39-C44-C49</f>
-        <v/>
-      </c>
-      <c r="D54" s="30">
-        <f>D34+D39-D44-D49</f>
-        <v/>
-      </c>
-      <c r="E54" s="30">
-        <f>E34+E39-E44-E49</f>
+      <c r="F54" s="30">
+        <f>F34+F39-F44-F49</f>
+        <v/>
+      </c>
+      <c r="G54" s="30">
+        <f>G34+G39-G44-G49</f>
+        <v/>
+      </c>
+      <c r="H54" s="30">
+        <f>H34+H39-H44-H49</f>
         <v/>
       </c>
     </row>
@@ -2529,16 +2507,16 @@
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="C55" s="30">
-        <f>C35+C40-C45-C50</f>
-        <v/>
-      </c>
-      <c r="D55" s="30">
-        <f>D35+D40-D45-D50</f>
-        <v/>
-      </c>
-      <c r="E55" s="30">
-        <f>E35+E40-E45-E50</f>
+      <c r="F55" s="30">
+        <f>F35+F40-F45-F50</f>
+        <v/>
+      </c>
+      <c r="G55" s="30">
+        <f>G35+G40-G45-G50</f>
+        <v/>
+      </c>
+      <c r="H55" s="30">
+        <f>H35+H40-H45-H50</f>
         <v/>
       </c>
     </row>
@@ -2571,7 +2549,7 @@
         <f>(C57+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="D58" s="35">
+      <c r="D58" s="34">
         <f>(D57+1807202-0)/111380</f>
         <v/>
       </c>
@@ -2586,21 +2564,21 @@
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="36">
+      <c r="C59" s="35">
         <f>C58/100.0-1</f>
         <v/>
       </c>
-      <c r="D59" s="36">
+      <c r="D59" s="35">
         <f>D58/100.0-1</f>
         <v/>
       </c>
-      <c r="E59" s="36">
+      <c r="E59" s="35">
         <f>E58/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="37" t="inlineStr">
+      <c r="A61" s="36" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2608,16 +2586,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId4"/>
-    <hyperlink ref="G8" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink ref="C8" location="'WACC'!E16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2629,23 +2607,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2661,82 +2638,88 @@
       <c r="F1" s="13" t="n"/>
       <c r="G1" s="13" t="n"/>
       <c r="H1" s="13" t="n"/>
+      <c r="I1" s="13" t="n"/>
+      <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="C2" s="38" t="inlineStr">
+      <c r="B2" s="37" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
+      <c r="C2" s="37" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="D2" s="37" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
+        </is>
+      </c>
+      <c r="E2" s="38" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="D2" s="39" t="inlineStr">
+      <c r="F2" s="39" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="E2" s="39" t="inlineStr">
+      <c r="G2" s="39" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="F2" s="39" t="inlineStr">
+      <c r="H2" s="39" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="I2" s="39" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="H2" s="39" t="inlineStr">
+      <c r="J2" s="39" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="I2" s="40" t="inlineStr">
+      <c r="K2" s="40" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="J2" s="41" t="inlineStr">
-        <is>
-          <t>Justification (~20 words)</t>
-        </is>
-      </c>
-      <c r="K2" s="41" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="L2" s="41" t="inlineStr">
-        <is>
-          <t>Ctrl+F (prove number)</t>
-        </is>
-      </c>
-      <c r="M2" s="41" t="inlineStr">
+      <c r="L2" s="37" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="N2" s="41" t="inlineStr">
+      <c r="M2" s="37" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="42" t="inlineStr">
-        <is>
-          <t>Forecast drivers linked to Scenarios tab → Base case (column D)</t>
-        </is>
-      </c>
-      <c r="C3" s="43" t="inlineStr">
-        <is>
-          <t>10-K source
-Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
-        </is>
-      </c>
-      <c r="I3" s="44" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>"CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+        </is>
+      </c>
+      <c r="E3" s="42" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="K3" s="43" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2748,47 +2731,57 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="C5" s="45" t="n">
+      <c r="E5" s="44" t="n">
         <v>11102600</v>
       </c>
-      <c r="D5" s="46">
-        <f>Scenarios!D16</f>
-        <v/>
-      </c>
-      <c r="E5" s="46">
-        <f>Scenarios!D17</f>
-        <v/>
-      </c>
-      <c r="F5" s="46">
-        <f>Scenarios!D18</f>
-        <v/>
-      </c>
-      <c r="G5" s="46">
-        <f>Scenarios!D19</f>
-        <v/>
-      </c>
-      <c r="H5" s="46">
-        <f>Scenarios!D20</f>
-        <v/>
-      </c>
-      <c r="I5" s="47">
-        <f>IF(MAX(ABS(D5-Scenarios!$D$16),ABS(E5-Scenarios!$D$17),ABS(F5-Scenarios!$D$18),ABS(G5-Scenarios!$D$19),ABS(H5-Scenarios!$D$20))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1">
+      <c r="F5" s="45">
+        <f>Scenarios!G16</f>
+        <v/>
+      </c>
+      <c r="G5" s="45">
+        <f>Scenarios!G17</f>
+        <v/>
+      </c>
+      <c r="H5" s="45">
+        <f>Scenarios!G18</f>
+        <v/>
+      </c>
+      <c r="I5" s="45">
+        <f>Scenarios!G19</f>
+        <v/>
+      </c>
+      <c r="J5" s="45">
+        <f>Scenarios!G20</f>
+        <v/>
+      </c>
+      <c r="K5" s="46">
+        <f>IF(MAX(ABS(F5-Scenarios!$G$16),ABS(G5-Scenarios!$G$17),ABS(H5-Scenarios!$G$18),ABS(I5-Scenarios!$G$19),ABS(J5-Scenarios!$G$20))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="D6" s="48">
-        <f>D5/C5-1</f>
-        <v/>
-      </c>
-      <c r="E6" s="48">
-        <f>E5/D5-1</f>
-        <v/>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.
+Also: 2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release
+Also: LULU historical revenue (10-K)</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint
+Also: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+        </is>
       </c>
       <c r="F6" s="48">
         <f>F5/E5-1</f>
@@ -2802,86 +2795,62 @@
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="L6" s="20" t="inlineStr">
-        <is>
-          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
-        </is>
-      </c>
-      <c r="M6" s="49" t="inlineStr">
-        <is>
-          <t>LULU historical revenue (10-K)</t>
-        </is>
-      </c>
-      <c r="N6" s="20" t="inlineStr">
-        <is>
-          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1">
+      <c r="I6" s="48">
+        <f>I5/H5-1</f>
+        <v/>
+      </c>
+      <c r="J6" s="48">
+        <f>J5/I5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>EBIT (operating) margin %</t>
         </is>
       </c>
-      <c r="D7" s="48">
-        <f>Scenarios!D21</f>
-        <v/>
-      </c>
-      <c r="E7" s="48">
-        <f>Scenarios!D22</f>
-        <v/>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.
+Also: 15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release
+Also: LULU historical EBIT margins (10-K)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)
+Also: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+        </is>
       </c>
       <c r="F7" s="48">
-        <f>Scenarios!D23</f>
+        <f>Scenarios!G21</f>
         <v/>
       </c>
       <c r="G7" s="48">
-        <f>Scenarios!D24</f>
+        <f>Scenarios!G22</f>
         <v/>
       </c>
       <c r="H7" s="48">
-        <f>Scenarios!D25</f>
-        <v/>
-      </c>
-      <c r="I7" s="47">
-        <f>IF(MAX(ABS(D7-Scenarios!$D$21),ABS(E7-Scenarios!$D$22),ABS(F7-Scenarios!$D$23),ABS(G7-Scenarios!$D$24),ABS(H7-Scenarios!$D$25))&lt;0.0001,"OK","CHECK")</f>
-        <v/>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
-        </is>
-      </c>
-      <c r="K7" s="19" t="inlineStr">
-        <is>
-          <t>LULU Q2 FY2026 earnings release</t>
-        </is>
-      </c>
-      <c r="L7" s="20" t="inlineStr">
-        <is>
-          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
-        </is>
-      </c>
-      <c r="M7" s="49" t="inlineStr">
-        <is>
-          <t>LULU historical EBIT margins (10-K)</t>
-        </is>
-      </c>
-      <c r="N7" s="20" t="inlineStr">
-        <is>
-          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
-        </is>
+        <f>Scenarios!G23</f>
+        <v/>
+      </c>
+      <c r="I7" s="48">
+        <f>Scenarios!G24</f>
+        <v/>
+      </c>
+      <c r="J7" s="48">
+        <f>Scenarios!G25</f>
+        <v/>
+      </c>
+      <c r="K7" s="46">
+        <f>IF(MAX(ABS(F7-Scenarios!$G$21),ABS(G7-Scenarios!$G$22),ABS(H7-Scenarios!$G$23),ABS(I7-Scenarios!$G$24),ABS(J7-Scenarios!$G$25))&lt;0.0001,"OK","CHECK")</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -2890,31 +2859,31 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C8" s="50" t="n">
+      <c r="E8" s="49" t="n">
         <v>2210615</v>
       </c>
-      <c r="D8" s="32">
-        <f>Scenarios!D26</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>Scenarios!D27</f>
-        <v/>
-      </c>
       <c r="F8" s="32">
-        <f>Scenarios!D28</f>
+        <f>Scenarios!G26</f>
         <v/>
       </c>
       <c r="G8" s="32">
-        <f>Scenarios!D29</f>
+        <f>Scenarios!G27</f>
         <v/>
       </c>
       <c r="H8" s="32">
-        <f>Scenarios!D30</f>
-        <v/>
-      </c>
-      <c r="I8" s="51">
-        <f>IF(MAX(ABS(D8-Scenarios!$D$26),ABS(E8-Scenarios!$D$27),ABS(F8-Scenarios!$D$28),ABS(G8-Scenarios!$D$29),ABS(H8-Scenarios!$D$30))&lt;0.5,"OK","CHECK")</f>
+        <f>Scenarios!G28</f>
+        <v/>
+      </c>
+      <c r="I8" s="32">
+        <f>Scenarios!G29</f>
+        <v/>
+      </c>
+      <c r="J8" s="32">
+        <f>Scenarios!G30</f>
+        <v/>
+      </c>
+      <c r="K8" s="50">
+        <f>IF(MAX(ABS(F8-Scenarios!$G$26),ABS(G8-Scenarios!$G$27),ABS(H8-Scenarios!$G$28),ABS(I8-Scenarios!$G$29),ABS(J8-Scenarios!$G$30))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2924,24 +2893,24 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="D9" s="46">
-        <f>-Scenarios!D26*Scenarios!$D$10</f>
-        <v/>
-      </c>
-      <c r="E9" s="46">
-        <f>-Scenarios!D27*Scenarios!$D$10</f>
-        <v/>
-      </c>
-      <c r="F9" s="46">
-        <f>-Scenarios!D28*Scenarios!$D$10</f>
-        <v/>
-      </c>
-      <c r="G9" s="46">
-        <f>-Scenarios!D29*Scenarios!$D$10</f>
-        <v/>
-      </c>
-      <c r="H9" s="46">
-        <f>-Scenarios!D30*Scenarios!$D$10</f>
+      <c r="F9" s="45">
+        <f>-Scenarios!G26*Scenarios!$G$10</f>
+        <v/>
+      </c>
+      <c r="G9" s="45">
+        <f>-Scenarios!G27*Scenarios!$G$10</f>
+        <v/>
+      </c>
+      <c r="H9" s="45">
+        <f>-Scenarios!G28*Scenarios!$G$10</f>
+        <v/>
+      </c>
+      <c r="I9" s="45">
+        <f>-Scenarios!G29*Scenarios!$G$10</f>
+        <v/>
+      </c>
+      <c r="J9" s="45">
+        <f>-Scenarios!G30*Scenarios!$G$10</f>
         <v/>
       </c>
     </row>
@@ -2951,28 +2920,28 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="D10" s="32">
-        <f>Scenarios!D31</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>Scenarios!D32</f>
-        <v/>
-      </c>
       <c r="F10" s="32">
-        <f>Scenarios!D33</f>
+        <f>Scenarios!G31</f>
         <v/>
       </c>
       <c r="G10" s="32">
-        <f>Scenarios!D34</f>
+        <f>Scenarios!G32</f>
         <v/>
       </c>
       <c r="H10" s="32">
-        <f>Scenarios!D35</f>
-        <v/>
-      </c>
-      <c r="I10" s="51">
-        <f>IF(MAX(ABS(D10-Scenarios!$D$31),ABS(E10-Scenarios!$D$32),ABS(F10-Scenarios!$D$33),ABS(G10-Scenarios!$D$34),ABS(H10-Scenarios!$D$35))&lt;0.5,"OK","CHECK")</f>
+        <f>Scenarios!G33</f>
+        <v/>
+      </c>
+      <c r="I10" s="32">
+        <f>Scenarios!G34</f>
+        <v/>
+      </c>
+      <c r="J10" s="32">
+        <f>Scenarios!G35</f>
+        <v/>
+      </c>
+      <c r="K10" s="50">
+        <f>IF(MAX(ABS(F10-Scenarios!$G$31),ABS(G10-Scenarios!$G$32),ABS(H10-Scenarios!$G$33),ABS(I10-Scenarios!$G$34),ABS(J10-Scenarios!$G$35))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2982,40 +2951,40 @@
           <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="D11" s="17">
-        <f>Scenarios!$D$11</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>Scenarios!$D$11</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
-        <f>Scenarios!$D$11</f>
-        <v/>
-      </c>
-      <c r="G11" s="17">
-        <f>Scenarios!$D$11</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>Scenarios!$D$11</f>
-        <v/>
-      </c>
-      <c r="J11" s="18" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
         </is>
       </c>
-      <c r="K11" s="19" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
       </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
         </is>
+      </c>
+      <c r="F11" s="20">
+        <f>Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="H11" s="20">
+        <f>Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="I11" s="20">
+        <f>Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="J11" s="20">
+        <f>Scenarios!$G$11</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -3024,28 +2993,28 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="D12" s="46">
-        <f>Scenarios!D36</f>
-        <v/>
-      </c>
-      <c r="E12" s="46">
-        <f>Scenarios!D37</f>
-        <v/>
-      </c>
-      <c r="F12" s="46">
-        <f>Scenarios!D38</f>
-        <v/>
-      </c>
-      <c r="G12" s="46">
-        <f>Scenarios!D39</f>
-        <v/>
-      </c>
-      <c r="H12" s="46">
-        <f>Scenarios!D40</f>
-        <v/>
-      </c>
-      <c r="I12" s="47">
-        <f>IF(MAX(ABS(D12-Scenarios!$D$36),ABS(E12-Scenarios!$D$37),ABS(F12-Scenarios!$D$38),ABS(G12-Scenarios!$D$39),ABS(H12-Scenarios!$D$40))&lt;0.5,"OK","CHECK")</f>
+      <c r="F12" s="45">
+        <f>Scenarios!G36</f>
+        <v/>
+      </c>
+      <c r="G12" s="45">
+        <f>Scenarios!G37</f>
+        <v/>
+      </c>
+      <c r="H12" s="45">
+        <f>Scenarios!G38</f>
+        <v/>
+      </c>
+      <c r="I12" s="45">
+        <f>Scenarios!G39</f>
+        <v/>
+      </c>
+      <c r="J12" s="45">
+        <f>Scenarios!G40</f>
+        <v/>
+      </c>
+      <c r="K12" s="46">
+        <f>IF(MAX(ABS(F12-Scenarios!$G$36),ABS(G12-Scenarios!$G$37),ABS(H12-Scenarios!$G$38),ABS(I12-Scenarios!$G$39),ABS(J12-Scenarios!$G$40))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3055,40 +3024,40 @@
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="D13" s="17">
-        <f>Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="E13" s="17">
-        <f>Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
-        <f>Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="G13" s="17">
-        <f>Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="J13" s="18" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
         </is>
       </c>
-      <c r="K13" s="19" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
       </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
         </is>
+      </c>
+      <c r="F13" s="20">
+        <f>Scenarios!$G$12</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>Scenarios!$G$12</f>
+        <v/>
+      </c>
+      <c r="H13" s="20">
+        <f>Scenarios!$G$12</f>
+        <v/>
+      </c>
+      <c r="I13" s="20">
+        <f>Scenarios!$G$12</f>
+        <v/>
+      </c>
+      <c r="J13" s="20">
+        <f>Scenarios!$G$12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -3097,28 +3066,28 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="D14" s="46">
-        <f>-Scenarios!D41</f>
-        <v/>
-      </c>
-      <c r="E14" s="46">
-        <f>-Scenarios!D42</f>
-        <v/>
-      </c>
-      <c r="F14" s="46">
-        <f>-Scenarios!D43</f>
-        <v/>
-      </c>
-      <c r="G14" s="46">
-        <f>-Scenarios!D44</f>
-        <v/>
-      </c>
-      <c r="H14" s="46">
-        <f>-Scenarios!D45</f>
-        <v/>
-      </c>
-      <c r="I14" s="47">
-        <f>IF(MAX(ABS(D14+Scenarios!$D$41),ABS(E14+Scenarios!$D$42),ABS(F14+Scenarios!$D$43),ABS(G14+Scenarios!$D$44),ABS(H14+Scenarios!$D$45))&lt;0.5,"OK","CHECK")</f>
+      <c r="F14" s="45">
+        <f>-Scenarios!G41</f>
+        <v/>
+      </c>
+      <c r="G14" s="45">
+        <f>-Scenarios!G42</f>
+        <v/>
+      </c>
+      <c r="H14" s="45">
+        <f>-Scenarios!G43</f>
+        <v/>
+      </c>
+      <c r="I14" s="45">
+        <f>-Scenarios!G44</f>
+        <v/>
+      </c>
+      <c r="J14" s="45">
+        <f>-Scenarios!G45</f>
+        <v/>
+      </c>
+      <c r="K14" s="46">
+        <f>IF(MAX(ABS(F14+Scenarios!$G$41),ABS(G14+Scenarios!$G$42),ABS(H14+Scenarios!$G$43),ABS(I14+Scenarios!$G$44),ABS(J14+Scenarios!$G$45))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3128,40 +3097,40 @@
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="D15" s="17">
-        <f>Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="E15" s="17">
-        <f>Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="F15" s="17">
-        <f>Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
-        <f>Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
       </c>
-      <c r="K15" s="19" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
         <is>
           <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
         </is>
+      </c>
+      <c r="F15" s="20">
+        <f>Scenarios!$G$13</f>
+        <v/>
+      </c>
+      <c r="G15" s="20">
+        <f>Scenarios!$G$13</f>
+        <v/>
+      </c>
+      <c r="H15" s="20">
+        <f>Scenarios!$G$13</f>
+        <v/>
+      </c>
+      <c r="I15" s="20">
+        <f>Scenarios!$G$13</f>
+        <v/>
+      </c>
+      <c r="J15" s="20">
+        <f>Scenarios!$G$13</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -3170,33 +3139,33 @@
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="D16" s="46">
-        <f>-Scenarios!D46</f>
-        <v/>
-      </c>
-      <c r="E16" s="46">
-        <f>-Scenarios!D47</f>
-        <v/>
-      </c>
-      <c r="F16" s="46">
-        <f>-Scenarios!D48</f>
-        <v/>
-      </c>
-      <c r="G16" s="46">
-        <f>-Scenarios!D49</f>
-        <v/>
-      </c>
-      <c r="H16" s="46">
-        <f>-Scenarios!D50</f>
-        <v/>
-      </c>
-      <c r="I16" s="47">
-        <f>IF(MAX(ABS(D16+Scenarios!$D$46),ABS(E16+Scenarios!$D$47),ABS(F16+Scenarios!$D$48),ABS(G16+Scenarios!$D$49),ABS(H16+Scenarios!$D$50))&lt;0.5,"OK","CHECK")</f>
+      <c r="F16" s="45">
+        <f>-Scenarios!G46</f>
+        <v/>
+      </c>
+      <c r="G16" s="45">
+        <f>-Scenarios!G47</f>
+        <v/>
+      </c>
+      <c r="H16" s="45">
+        <f>-Scenarios!G48</f>
+        <v/>
+      </c>
+      <c r="I16" s="45">
+        <f>-Scenarios!G49</f>
+        <v/>
+      </c>
+      <c r="J16" s="45">
+        <f>-Scenarios!G50</f>
+        <v/>
+      </c>
+      <c r="K16" s="46">
+        <f>IF(MAX(ABS(F16+Scenarios!$G$46),ABS(G16+Scenarios!$G$47),ABS(H16+Scenarios!$G$48),ABS(I16+Scenarios!$G$49),ABS(J16+Scenarios!$G$50))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
@@ -3208,28 +3177,28 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="D18" s="52">
-        <f>Scenarios!D51</f>
-        <v/>
-      </c>
-      <c r="E18" s="52">
-        <f>Scenarios!D52</f>
-        <v/>
-      </c>
-      <c r="F18" s="52">
-        <f>Scenarios!D53</f>
-        <v/>
-      </c>
-      <c r="G18" s="52">
-        <f>Scenarios!D54</f>
-        <v/>
-      </c>
-      <c r="H18" s="52">
-        <f>Scenarios!D55</f>
+      <c r="F18" s="51">
+        <f>Scenarios!G51</f>
+        <v/>
+      </c>
+      <c r="G18" s="51">
+        <f>Scenarios!G52</f>
+        <v/>
+      </c>
+      <c r="H18" s="51">
+        <f>Scenarios!G53</f>
         <v/>
       </c>
       <c r="I18" s="51">
-        <f>IF(MAX(ABS(D18-Scenarios!$D$51),ABS(E18-Scenarios!$D$52),ABS(F18-Scenarios!$D$53),ABS(G18-Scenarios!$D$54),ABS(H18-Scenarios!$D$55))&lt;0.5,"OK","CHECK")</f>
+        <f>Scenarios!G54</f>
+        <v/>
+      </c>
+      <c r="J18" s="51">
+        <f>Scenarios!G55</f>
+        <v/>
+      </c>
+      <c r="K18" s="50">
+        <f>IF(MAX(ABS(F18-Scenarios!$G$51),ABS(G18-Scenarios!$G$52),ABS(H18-Scenarios!$G$53),ABS(I18-Scenarios!$G$54),ABS(J18-Scenarios!$G$55))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3239,19 +3208,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="D19" s="53" t="n">
+      <c r="F19" s="52" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="53" t="n">
+      <c r="G19" s="52" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="53" t="n">
+      <c r="H19" s="52" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="53" t="n">
+      <c r="I19" s="52" t="n">
         <v>4</v>
       </c>
-      <c r="H19" s="53" t="n">
+      <c r="J19" s="52" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3261,24 +3230,24 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="D20" s="54">
-        <f>1/(1+Scenarios!$D$8)^D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="54">
-        <f>1/(1+Scenarios!$D$8)^E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="54">
-        <f>1/(1+Scenarios!$D$8)^F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="54">
-        <f>1/(1+Scenarios!$D$8)^G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="54">
-        <f>1/(1+Scenarios!$D$8)^H19</f>
+      <c r="F20" s="53">
+        <f>1/(1+Scenarios!$G$8)^F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="53">
+        <f>1/(1+Scenarios!$G$8)^G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="53">
+        <f>1/(1+Scenarios!$G$8)^H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="53">
+        <f>1/(1+Scenarios!$G$8)^I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="53">
+        <f>1/(1+Scenarios!$G$8)^J19</f>
         <v/>
       </c>
     </row>
@@ -3288,14 +3257,6 @@
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="D21" s="32">
-        <f>D18*D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="32">
-        <f>E18*E20</f>
-        <v/>
-      </c>
       <c r="F21" s="32">
         <f>F18*F20</f>
         <v/>
@@ -3308,20 +3269,28 @@
         <f>H18*H20</f>
         <v/>
       </c>
+      <c r="I21" s="32">
+        <f>I18*I20</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>J18*J20</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>Scenarios linkage summary (column I should all read OK)</t>
-        </is>
-      </c>
-      <c r="I23" s="55">
-        <f>IF(COUNTIF(I5:I18,"CHECK")=0,"ALL OK","REVIEW")</f>
+          <t>Scenarios linkage summary (column K should all read OK)</t>
+        </is>
+      </c>
+      <c r="K23" s="54">
+        <f>IF(COUNTIF(K5:K18,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="56" t="inlineStr">
+      <c r="A24" s="55" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3335,8 +3304,8 @@
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="C25" s="57">
-        <f>SUM(D21:H21)</f>
+      <c r="E25" s="56">
+        <f>SUM(F21:J21)</f>
         <v/>
       </c>
     </row>
@@ -3346,24 +3315,24 @@
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="C26" s="48">
-        <f>Scenarios!$D$9</f>
-        <v/>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
+      <c r="B26" s="17" t="inlineStr">
         <is>
           <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="L26" s="20" t="inlineStr">
+      <c r="D26" s="19" t="inlineStr">
         <is>
           <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
         </is>
+      </c>
+      <c r="E26" s="48">
+        <f>Scenarios!$G$9</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -3372,8 +3341,8 @@
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C27" s="32">
-        <f>H8+H12</f>
+      <c r="E27" s="32">
+        <f>J8+J12</f>
         <v/>
       </c>
     </row>
@@ -3383,8 +3352,8 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="C28" s="46">
-        <f>H18*(1+Scenarios!$D$9)/(Scenarios!$D$8-Scenarios!$D$9)</f>
+      <c r="E28" s="45">
+        <f>J18*(1+Scenarios!$G$9)/(Scenarios!$G$8-Scenarios!$G$9)</f>
         <v/>
       </c>
     </row>
@@ -3394,8 +3363,8 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="C29" s="58">
-        <f>C28/C27</f>
+      <c r="E29" s="57">
+        <f>E28/E27</f>
         <v/>
       </c>
     </row>
@@ -3405,8 +3374,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C30" s="57">
-        <f>C28/(1+Scenarios!$D$8)^H19</f>
+      <c r="E30" s="56">
+        <f>E28/(1+Scenarios!$G$8)^J19</f>
         <v/>
       </c>
     </row>
@@ -3416,8 +3385,8 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C31" s="32">
-        <f>C25+C30</f>
+      <c r="E31" s="32">
+        <f>E25+E30</f>
         <v/>
       </c>
     </row>
@@ -3427,18 +3396,18 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C32" s="45" t="n">
+      <c r="C32" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+        </is>
+      </c>
+      <c r="E32" s="44" t="n">
         <v>1807202</v>
-      </c>
-      <c r="D32" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="inlineStr">
-        <is>
-          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
-        </is>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
@@ -3447,18 +3416,18 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C33" s="45" t="n">
+      <c r="C33" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>"Long-term debt" → $0 (no funded debt)</t>
+        </is>
+      </c>
+      <c r="E33" s="44" t="n">
         <v>0</v>
-      </c>
-      <c r="D33" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="inlineStr">
-        <is>
-          <t>"Long-term debt" → $0 (no funded debt)</t>
-        </is>
       </c>
     </row>
     <row r="34">
@@ -3467,8 +3436,8 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="C34" s="32">
-        <f>C31+C32+C33</f>
+      <c r="E34" s="32">
+        <f>E31+E32+E33</f>
         <v/>
       </c>
     </row>
@@ -3478,18 +3447,18 @@
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C35" s="45" t="n">
+      <c r="C35" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="n">
         <v>111380</v>
-      </c>
-      <c r="D35" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
-        </is>
       </c>
     </row>
     <row r="36">
@@ -3498,12 +3467,12 @@
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="C36" s="59">
-        <f>C34/C35</f>
-        <v/>
-      </c>
-      <c r="I36" s="51">
-        <f>IF(ABS(C36-Scenarios!$D$58)&lt;0.05,"OK","CHECK")</f>
+      <c r="E36" s="59">
+        <f>E34/E35</f>
+        <v/>
+      </c>
+      <c r="K36" s="50">
+        <f>IF(ABS(E36-Scenarios!$G$58)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3513,18 +3482,18 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C37" s="60" t="n">
+      <c r="C37" s="58" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+        </is>
+      </c>
+      <c r="E37" s="60" t="n">
         <v>100</v>
-      </c>
-      <c r="D37" s="49" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="inlineStr">
-        <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -3533,8 +3502,8 @@
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="C38" s="61">
-        <f>C36/C37-1</f>
+      <c r="E38" s="61">
+        <f>E36/E37-1</f>
         <v/>
       </c>
     </row>
@@ -3544,13 +3513,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="C39" s="48">
-        <f>C30/C31</f>
+      <c r="E39" s="48">
+        <f>E30/E31</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="56" t="inlineStr">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3571,20 +3540,25 @@
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="C43" s="62" t="n">
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
+        </is>
+      </c>
+      <c r="E43" s="62" t="n">
         <v>8</v>
       </c>
-      <c r="J43" s="18" t="inlineStr">
-        <is>
-          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
-        </is>
-      </c>
-      <c r="K43" s="19" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="L43" s="49" t="inlineStr">
+      <c r="M43" s="58" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3596,8 +3570,8 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="C44" s="46">
-        <f>C27*C43</f>
+      <c r="E44" s="45">
+        <f>E27*E43</f>
         <v/>
       </c>
     </row>
@@ -3607,8 +3581,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="C45" s="46">
-        <f>C44/(1+Scenarios!$D$8)^H19</f>
+      <c r="E45" s="45">
+        <f>E44/(1+Scenarios!$G$8)^J19</f>
         <v/>
       </c>
     </row>
@@ -3618,8 +3592,8 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="C46" s="32">
-        <f>C25+C45</f>
+      <c r="E46" s="32">
+        <f>E25+E45</f>
         <v/>
       </c>
     </row>
@@ -3629,13 +3603,13 @@
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="C47" s="63">
-        <f>(C46+C32+C33)/C35</f>
+      <c r="E47" s="63">
+        <f>(E46+E32+E33)/E35</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="56" t="inlineStr">
+      <c r="A49" s="55" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3668,15 +3642,15 @@
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="57">
-        <f>C28</f>
-        <v/>
-      </c>
-      <c r="C51" s="57">
-        <f>C44</f>
-        <v/>
-      </c>
-      <c r="D51" s="57">
+      <c r="B51" s="56">
+        <f>E28</f>
+        <v/>
+      </c>
+      <c r="C51" s="56">
+        <f>E44</f>
+        <v/>
+      </c>
+      <c r="D51" s="56">
         <f>B51-C51</f>
         <v/>
       </c>
@@ -3688,11 +3662,11 @@
         </is>
       </c>
       <c r="B52" s="66">
-        <f>C29</f>
+        <f>E29</f>
         <v/>
       </c>
       <c r="C52" s="66">
-        <f>C43</f>
+        <f>E43</f>
         <v/>
       </c>
       <c r="D52" s="66">
@@ -3720,11 +3694,11 @@
         </is>
       </c>
       <c r="B54" s="67">
-        <f>C36</f>
+        <f>E36</f>
         <v/>
       </c>
       <c r="C54" s="67">
-        <f>C47</f>
+        <f>E47</f>
         <v/>
       </c>
       <c r="D54" s="67">
@@ -3746,14 +3720,14 @@
         <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D55" s="37" t="inlineStr">
+      <c r="D55" s="36" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="56" t="inlineStr">
+      <c r="A58" s="55" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -3772,39 +3746,39 @@
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="D59" s="72" t="n">
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
+        <is>
+          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+        </is>
+      </c>
+      <c r="F59" s="72" t="n">
         <v>0.015</v>
       </c>
-      <c r="E59" s="72" t="n">
+      <c r="G59" s="72" t="n">
         <v>0.02</v>
       </c>
-      <c r="F59" s="72" t="n">
+      <c r="H59" s="72" t="n">
         <v>0.0225</v>
       </c>
-      <c r="G59" s="72" t="n">
+      <c r="I59" s="72" t="n">
         <v>0.025</v>
       </c>
-      <c r="H59" s="72" t="n">
+      <c r="J59" s="72" t="n">
         <v>0.03</v>
       </c>
-      <c r="I59" s="49" t="inlineStr">
+      <c r="L59" s="58" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
-        </is>
-      </c>
-      <c r="J59" s="18" t="inlineStr">
-        <is>
-          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
-        </is>
-      </c>
-      <c r="K59" s="19" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-      <c r="L59" s="20" t="inlineStr">
-        <is>
-          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
         </is>
       </c>
     </row>
@@ -3812,184 +3786,204 @@
       <c r="A60" s="72" t="n">
         <v>0.09</v>
       </c>
-      <c r="D60" s="73">
-        <f>(NPV(0.09,D18:H18)+(H18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="E60" s="73">
-        <f>(NPV(0.09,D18:H18)+(H18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+C32+C33)/C35</f>
-        <v/>
+      <c r="C60" s="58" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+        </is>
       </c>
       <c r="F60" s="73">
-        <f>(NPV(0.09,D18:H18)+(H18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+C32+C33)/C35</f>
+        <f>(NPV(0.09,F18:J18)+(J18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G60" s="73">
-        <f>(NPV(0.09,D18:H18)+(H18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+C32+C33)/C35</f>
+        <f>(NPV(0.09,F18:J18)+(J18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H60" s="73">
-        <f>(NPV(0.09,D18:H18)+(H18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="I60" s="49" t="inlineStr">
+        <f>(NPV(0.09,F18:J18)+(J18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="I60" s="73">
+        <f>(NPV(0.09,F18:J18)+(J18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="J60" s="73">
+        <f>(NPV(0.09,F18:J18)+(J18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="L60" s="58" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
-      <c r="K60" s="49" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
-      </c>
-      <c r="L60" s="20" t="inlineStr">
-        <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+    </row>
+    <row r="61" ht="36" customHeight="1">
       <c r="A61" s="72" t="n">
         <v>0.095</v>
       </c>
-      <c r="D61" s="73">
-        <f>(NPV(0.095,D18:H18)+(H18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="E61" s="73">
-        <f>(NPV(0.095,D18:H18)+(H18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+C32+C33)/C35</f>
-        <v/>
+      <c r="D61" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+        </is>
       </c>
       <c r="F61" s="73">
-        <f>(NPV(0.095,D18:H18)+(H18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+C32+C33)/C35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G61" s="73">
-        <f>(NPV(0.095,D18:H18)+(H18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+C32+C33)/C35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H61" s="73">
-        <f>(NPV(0.095,D18:H18)+(H18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="I61" s="49" t="inlineStr">
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="I61" s="73">
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="J61" s="73">
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="L61" s="58" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="36" customHeight="1">
       <c r="A62" s="72" t="n">
         <v>0.1</v>
       </c>
-      <c r="D62" s="73">
-        <f>(NPV(0.1,D18:H18)+(H18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="E62" s="73">
-        <f>(NPV(0.1,D18:H18)+(H18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="F62" s="74">
-        <f>(NPV(0.1,D18:H18)+(H18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+C32+C33)/C35</f>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+        </is>
+      </c>
+      <c r="F62" s="73">
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G62" s="73">
-        <f>(NPV(0.1,D18:H18)+(H18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="H62" s="73">
-        <f>(NPV(0.1,D18:H18)+(H18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="I62" s="49" t="inlineStr">
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="H62" s="74">
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="I62" s="73">
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="J62" s="73">
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="L62" s="58" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="36" customHeight="1">
       <c r="A63" s="72" t="n">
         <v>0.105</v>
       </c>
-      <c r="D63" s="73">
-        <f>(NPV(0.105,D18:H18)+(H18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="E63" s="73">
-        <f>(NPV(0.105,D18:H18)+(H18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+C32+C33)/C35</f>
-        <v/>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+        </is>
       </c>
       <c r="F63" s="73">
-        <f>(NPV(0.105,D18:H18)+(H18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+C32+C33)/C35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G63" s="73">
-        <f>(NPV(0.105,D18:H18)+(H18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+C32+C33)/C35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H63" s="73">
-        <f>(NPV(0.105,D18:H18)+(H18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="I63" s="49" t="inlineStr">
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="I63" s="73">
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="J63" s="73">
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="L63" s="58" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="36" customHeight="1">
       <c r="A64" s="72" t="n">
         <v>0.11</v>
       </c>
-      <c r="D64" s="73">
-        <f>(NPV(0.11,D18:H18)+(H18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="E64" s="73">
-        <f>(NPV(0.11,D18:H18)+(H18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+C32+C33)/C35</f>
-        <v/>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+        </is>
       </c>
       <c r="F64" s="73">
-        <f>(NPV(0.11,D18:H18)+(H18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+C32+C33)/C35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G64" s="73">
-        <f>(NPV(0.11,D18:H18)+(H18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+C32+C33)/C35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H64" s="73">
-        <f>(NPV(0.11,D18:H18)+(H18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+C32+C33)/C35</f>
-        <v/>
-      </c>
-      <c r="I64" s="49" t="inlineStr">
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="I64" s="73">
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="J64" s="73">
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E32+E33)/E35</f>
+        <v/>
+      </c>
+      <c r="L64" s="58" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="65" ht="36" customHeight="1">
-      <c r="J65" s="18" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="K65" s="19" t="inlineStr">
+      <c r="C65" s="18" t="inlineStr">
         <is>
           <t>Scenarios: WACC &amp; terminal g</t>
         </is>
       </c>
-      <c r="L65" s="20" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Scenarios tab → "WACC" row &amp; "Terminal growth" row (base inputs)</t>
         </is>
       </c>
-      <c r="M65" s="49" t="inlineStr">
+      <c r="L65" s="58" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="N65" s="20" t="inlineStr">
+      <c r="M65" s="19" t="inlineStr">
         <is>
           <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
         </is>
@@ -3997,37 +3991,35 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D32" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D33" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D35" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D37" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId20"/>
-    <hyperlink ref="L43" location="'Comps'!A26"/>
-    <hyperlink ref="I59" location="'Scenarios'!D9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId21"/>
-    <hyperlink ref="I60" location="'WACC'!C16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId22"/>
-    <hyperlink ref="I61" location="'WACC'!C16"/>
-    <hyperlink ref="I62" location="'WACC'!C16"/>
-    <hyperlink ref="I63" location="'WACC'!C16"/>
-    <hyperlink ref="I64" location="'WACC'!C16"/>
-    <hyperlink ref="K65" location="'Scenarios'!D8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId18"/>
+    <hyperlink ref="M43" location="'Comps'!A26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId19"/>
+    <hyperlink ref="L59" location="'Scenarios'!G9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId20"/>
+    <hyperlink ref="L60" location="'WACC'!E16"/>
+    <hyperlink ref="L61" location="'WACC'!E16"/>
+    <hyperlink ref="L62" location="'WACC'!E16"/>
+    <hyperlink ref="L63" location="'WACC'!E16"/>
+    <hyperlink ref="L64" location="'WACC'!E16"/>
+    <hyperlink ref="C65" location="'Scenarios'!G8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4039,21 +4031,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -4067,6 +4055,25 @@
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
       <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="D2" s="15" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -4081,18 +4088,18 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="45" t="n">
+      <c r="C4" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>"Net revenue" → FY2025 $11,102,600 ($000)</t>
+        </is>
+      </c>
+      <c r="E4" s="44" t="n">
         <v>11102600</v>
-      </c>
-      <c r="D4" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>"Net revenue" → FY2025 $11,102,600 ($000)</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -4101,7 +4108,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C5" s="46">
+      <c r="E5" s="45">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -4112,14 +4119,14 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="46">
-        <f>DCF!C27</f>
-        <v/>
-      </c>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="C6" s="58" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
+      </c>
+      <c r="E6" s="45">
+        <f>DCF!E27</f>
+        <v/>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
@@ -4128,18 +4135,18 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="60" t="n">
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>"diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
+        </is>
+      </c>
+      <c r="E7" s="60" t="n">
         <v>9.609999999999999</v>
-      </c>
-      <c r="D7" s="49" t="inlineStr">
-        <is>
-          <t>Release</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>"diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
-        </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
@@ -4148,18 +4155,18 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+        </is>
+      </c>
+      <c r="E8" s="44" t="n">
         <v>1807202</v>
-      </c>
-      <c r="D8" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
-        </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -4168,18 +4175,18 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+        </is>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>111380</v>
-      </c>
-      <c r="D9" s="49" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
-        </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
@@ -4188,18 +4195,18 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="58" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="n">
         <v>100</v>
-      </c>
-      <c r="D10" s="49" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
-        </is>
       </c>
     </row>
     <row r="11">
@@ -4208,8 +4215,8 @@
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="C11" s="75">
-        <f>(C10*C9-C8)/C5</f>
+      <c r="E11" s="75">
+        <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
     </row>
@@ -4219,8 +4226,8 @@
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="C12" s="75">
-        <f>C10/C7</f>
+      <c r="E12" s="75">
+        <f>E10/E7</f>
         <v/>
       </c>
     </row>
@@ -4244,24 +4251,24 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="C16" s="77" t="inlineStr">
+      <c r="B16" s="76" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C16" s="76" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="D16" s="76" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
+        </is>
+      </c>
+      <c r="E16" s="77" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="E16" s="76" t="inlineStr">
-        <is>
-          <t>Justification</t>
-        </is>
-      </c>
-      <c r="F16" s="76" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="G16" s="76" t="inlineStr">
-        <is>
-          <t>Ctrl+F (prove number)</t>
         </is>
       </c>
     </row>
@@ -4271,24 +4278,24 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="C17" s="78">
-        <f>(C10*C9-C8)/C5</f>
-        <v/>
-      </c>
-      <c r="E17" s="37" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="F17" s="49" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
       </c>
-      <c r="G17" s="20" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>"Income from operations" $2,210,615 + "Depreciation and amortization" $496,228</t>
         </is>
+      </c>
+      <c r="E17" s="78">
+        <f>(E10*E9-E8)/E5</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1">
@@ -4297,23 +4304,23 @@
           <t>Nike (NKE)</t>
         </is>
       </c>
-      <c r="C18" s="79" t="n">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: NKE statistics</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
+        </is>
+      </c>
+      <c r="E18" s="79" t="n">
         <v>18</v>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: NKE statistics</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
-        </is>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
@@ -4322,23 +4329,23 @@
           <t>Deckers (DECK)</t>
         </is>
       </c>
-      <c r="C19" s="79" t="n">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: DECK statistics</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
+        </is>
+      </c>
+      <c r="E19" s="79" t="n">
         <v>15</v>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: DECK statistics</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
-        </is>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
@@ -4347,23 +4354,23 @@
           <t>On Holding (ONON)</t>
         </is>
       </c>
-      <c r="C20" s="79" t="n">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: ONON statistics</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
+        </is>
+      </c>
+      <c r="E20" s="79" t="n">
         <v>25</v>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: ONON statistics</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
-        </is>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
@@ -4372,23 +4379,23 @@
           <t>adidas (ADS)</t>
         </is>
       </c>
-      <c r="C21" s="79" t="n">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: adidas (ADDYY)</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
+        </is>
+      </c>
+      <c r="E21" s="79" t="n">
         <v>12</v>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: adidas (ADDYY)</t>
-        </is>
-      </c>
-      <c r="G21" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
-        </is>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -4397,23 +4404,23 @@
           <t>V.F. Corp (VFC)</t>
         </is>
       </c>
-      <c r="C22" s="79" t="n">
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: VFC statistics</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
+        </is>
+      </c>
+      <c r="E22" s="79" t="n">
         <v>10</v>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: VFC statistics</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
-        </is>
       </c>
     </row>
     <row r="24">
@@ -4429,8 +4436,8 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="C25" s="58">
-        <f>DCF!C29</f>
+      <c r="E25" s="57">
+        <f>DCF!E29</f>
         <v/>
       </c>
     </row>
@@ -4440,8 +4447,8 @@
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="C26" s="66">
-        <f>DCF!C43</f>
+      <c r="E26" s="66">
+        <f>DCF!E43</f>
         <v/>
       </c>
     </row>
@@ -4451,8 +4458,8 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="C27" s="58">
-        <f>C26-C25</f>
+      <c r="E27" s="57">
+        <f>E26-E25</f>
         <v/>
       </c>
     </row>
@@ -4511,177 +4518,148 @@
           <t>Method</t>
         </is>
       </c>
-      <c r="C36" s="77" t="inlineStr">
+      <c r="B36" s="76" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C36" s="76" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D36" s="76" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E36" s="77" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="D36" s="77" t="inlineStr">
+      <c r="F36" s="77" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="E36" s="77" t="inlineStr">
+      <c r="G36" s="77" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="F36" s="77" t="inlineStr">
+      <c r="H36" s="77" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
-      <c r="G36" s="80" t="inlineStr">
-        <is>
-          <t>Lo justification</t>
-        </is>
-      </c>
-      <c r="H36" s="80" t="inlineStr">
-        <is>
-          <t>Lo source</t>
-        </is>
-      </c>
-      <c r="I36" s="80" t="inlineStr">
-        <is>
-          <t>Lo Ctrl+F</t>
-        </is>
-      </c>
-      <c r="J36" s="80" t="inlineStr">
-        <is>
-          <t>Hi justification</t>
-        </is>
-      </c>
-      <c r="K36" s="80" t="inlineStr">
-        <is>
-          <t>Hi source</t>
-        </is>
-      </c>
-      <c r="L36" s="80" t="inlineStr">
-        <is>
-          <t>Hi Ctrl+F</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="36" customHeight="1">
+    </row>
+    <row r="37" ht="54" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="C37" s="79" t="n">
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Lo: 6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.
+Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
+        </is>
+      </c>
+      <c r="C37" s="80" t="inlineStr">
+        <is>
+          <t>Lo: StockAnalysis: LULU EV/EBITDA
+Hi: StockAnalysis: LULU valuation</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Lo: "Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x
+Hi: "Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
+        </is>
+      </c>
+      <c r="E37" s="79" t="n">
         <v>6.5</v>
       </c>
-      <c r="D37" s="79" t="n">
+      <c r="F37" s="79" t="n">
         <v>9.5</v>
       </c>
-      <c r="E37" s="81">
-        <f>(C6*C37+C8)/C9</f>
-        <v/>
-      </c>
-      <c r="F37" s="81">
-        <f>(C6*D37+C8)/C9</f>
-        <v/>
-      </c>
-      <c r="G37" s="18" t="inlineStr">
-        <is>
-          <t>6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="G37" s="81">
+        <f>(E6*E37+E8)/E9</f>
+        <v/>
+      </c>
+      <c r="H37" s="81">
+        <f>(E6*F37+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="68" t="inlineStr">
+        <is>
+          <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
-      <c r="I37" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x</t>
-        </is>
-      </c>
-      <c r="J37" s="82" t="inlineStr">
-        <is>
-          <t>9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
-        </is>
-      </c>
-      <c r="K37" s="83" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU valuation</t>
-        </is>
-      </c>
-      <c r="L37" s="20" t="inlineStr">
-        <is>
-          <t>"Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="68" t="inlineStr">
-        <is>
-          <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
-        </is>
-      </c>
-      <c r="C38" s="84">
-        <f>DCF!C43</f>
-        <v/>
-      </c>
-      <c r="E38" s="85">
-        <f>(C6*C38+C8)/C9</f>
-        <v/>
-      </c>
-      <c r="I38" s="49" t="inlineStr">
-        <is>
-          <t>↳ DCF exit multiple</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="36" customHeight="1">
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>"Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
+        </is>
+      </c>
+      <c r="E38" s="82">
+        <f>DCF!E43</f>
+        <v/>
+      </c>
+      <c r="G38" s="83">
+        <f>(E6*E38+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="54" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="C39" s="79" t="n">
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.
+Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
+        </is>
+      </c>
+      <c r="C39" s="80" t="inlineStr">
+        <is>
+          <t>Lo: Yahoo Finance: LULU P/E
+Hi: Yahoo Finance: NKE P/E (peer)</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Lo: "Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x
+Hi: "Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
+        </is>
+      </c>
+      <c r="E39" s="79" t="n">
         <v>10</v>
       </c>
-      <c r="D39" s="79" t="n">
+      <c r="F39" s="79" t="n">
         <v>18</v>
       </c>
-      <c r="E39" s="81">
-        <f>C7*C39</f>
-        <v/>
-      </c>
-      <c r="F39" s="81">
-        <f>C7*D39</f>
-        <v/>
-      </c>
-      <c r="G39" s="18" t="inlineStr">
-        <is>
-          <t>10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: LULU P/E</t>
-        </is>
-      </c>
-      <c r="I39" s="20" t="inlineStr">
-        <is>
-          <t>"Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x</t>
-        </is>
-      </c>
-      <c r="J39" s="82" t="inlineStr">
-        <is>
-          <t>18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
-        </is>
-      </c>
-      <c r="K39" s="83" t="inlineStr">
-        <is>
-          <t>Yahoo Finance: NKE P/E (peer)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>"Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
-        </is>
+      <c r="G39" s="81">
+        <f>E7*E39</f>
+        <v/>
+      </c>
+      <c r="H39" s="81">
+        <f>E7*F39</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -4690,47 +4668,47 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="C40" s="86" t="inlineStr">
+      <c r="E40" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" s="86" t="inlineStr">
+      <c r="F40" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="81">
-        <f>Scenarios!C58</f>
-        <v/>
-      </c>
-      <c r="F40" s="81">
-        <f>Scenarios!E58</f>
+      <c r="G40" s="81">
+        <f>Scenarios!F58</f>
+        <v/>
+      </c>
+      <c r="H40" s="81">
+        <f>Scenarios!H58</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="87" t="inlineStr">
+      <c r="A42" s="85" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="88" t="n">
+      <c r="C42" s="58" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+        </is>
+      </c>
+      <c r="E42" s="86" t="n">
         <v>100</v>
       </c>
-      <c r="D42" s="49" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="E42" s="20" t="inlineStr">
-        <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
-        </is>
-      </c>
     </row>
     <row r="43">
-      <c r="A43" s="37" t="inlineStr">
+      <c r="A43" s="36" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
@@ -4739,29 +4717,27 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId2"/>
-    <hyperlink ref="D6" location="'DCF'!C27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
+    <hyperlink ref="C6" location="'DCF'!E27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId18"/>
-    <hyperlink ref="I38" location="'DCF'!C43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D42" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
+    <hyperlink ref="C38" location="'DCF'!E43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1041,7 +1041,7 @@
       <c r="B18" s="10" t="inlineStr">
         <is>
           <t>SEC EDGAR filings, CIK 0001397187 (Form 10-K, FY2025)
-Ctrl+F: "10-K" → FY2025 accession 0001397187-26-000020</t>
+Ctrl+F: Ctrl+F "10-K" → FY2025 accession 0001397187-26-000020</t>
         </is>
       </c>
     </row>
@@ -1049,7 +1049,7 @@
       <c r="B19" s="10" t="inlineStr">
         <is>
           <t>FY2025 Form 10-K (ended Feb 1, 2026)
-Ctrl+F: "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+Ctrl+F: Ctrl+F "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)
-Ctrl+F: "full year 2026" | "net revenue" | "diluted earnings per share"</t>
+Ctrl+F: Ctrl+F "decline of 5% to 7%" | "$10.350 billion to $10.500 billion" | "$9.48 to $9.73"</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Current share price (NASDAQ: LULU)
-Ctrl+F: "LULU" → Last Sale / Previous Close price</t>
+Ctrl+F: Ctrl+F "LULU" → Last Sale or Previous Close price</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>"DGS10" → read top table row (latest date); Sep 2, 2026 ≈ 4.28% → model 4.3%</t>
+          <t>Ctrl+F "DGS10" → FRED series table; Sep 2026 ≈ 4.28%; model 4.3%</t>
         </is>
       </c>
       <c r="E3" s="20" t="n">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → Jan-2026 row ≈ 4.23%; model uses 6.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → Jan-2026 row shows 4.23%; model uses 6.0%</t>
         </is>
       </c>
       <c r="E4" s="20" t="n">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: LULU Beta</t>
+          <t>StockAnalysis: LULU Beta (5Y)</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>"Beta (5Y Monthly)" → Yahoo shows ≈ 0.86; model 0.95</t>
+          <t>Ctrl+F "Beta (5Y)" → page shows 0.86; model uses 0.95</t>
         </is>
       </c>
       <c r="E5" s="21" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>"no outstanding borrowings" or "revolving credit facility" → no funded term debt</t>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → FY2025 10-K Note 12</t>
         </is>
       </c>
       <c r="E9" s="20" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>"United States" → Damodaran effective tax rate ~25%; model 27%</t>
+          <t>Ctrl+F "Apparel" → Damodaran Tax Rates by Sector (US), Jan-2026; model 27%</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>"Cash and cash equivalents" → $1,807,202 | "Long-term debt" → $0</t>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) | no funded term debt</t>
         </is>
       </c>
       <c r="E14" s="20" t="n">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>"Long-term debt" → none outstanding; debt weight 0%</t>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → debt weight 0%</t>
         </is>
       </c>
       <c r="E15" s="20" t="n">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint</t>
+          <t>Ctrl+F "decline of 5% to 7%" → FY2026 revenue guide; model −6.1% midpoint</t>
         </is>
       </c>
       <c r="F4" s="20" t="n">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>"Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+          <t>Ctrl+F "Net revenue" → FY2025 11,102,600 ($000); FY27–30 growth = model assumption</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)</t>
+          <t>Ctrl+F "operating margin" → "18.8%" Q2 FY2026; FY26 full-year 13.9% EBIT margin = model</t>
         </is>
       </c>
       <c r="F6" s="20" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>"Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+          <t>Ctrl+F "Income from operations" → 2,210,615 ÷ "Net revenue" 11,102,600 = 19.9% FY25</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>WACC tab → cell E (green) = 10.0%</t>
+          <t>WACC tab → Ctrl+F "WACC" → cell E = 10.0%</t>
         </is>
       </c>
       <c r="F8" s="20" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+          <t>Ctrl+F "GDPC1" → FRED Real GDP series; long-run growth ~2%; model terminal g 2.25%</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset</t>
+          <t>LULU effective tax history (10-K)</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>"Provision for income taxes" ÷ "Income before income taxes" → FY25 $659,784 / $2,238,967 = 29.5%</t>
+          <t>Ctrl+F "Income tax expense" → 659,784 ÷ "Income before income tax expense" 2,238,967</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228; ÷ "Net revenue" 11,102,600 = 4.5%</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+          <t>Ctrl+F "680,802" → capex ($000) in investing; ÷ revenue 11,102,600; model 5.0%</t>
         </is>
       </c>
       <c r="F12" s="20" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
+          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>"CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+          <t>Ctrl+F "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
@@ -2779,8 +2779,8 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>"full year 2026" → "net revenue" → "decrease of 5% to 7%" | model −6.1% midpoint
-Also: "Net revenue" → FY22 $8,110,518 | FY23 $9,619,278 | FY24 $10,588,126 | FY25 $11,102,600</t>
+          <t>Ctrl+F "decline of 5% to 7%" → FY2026 revenue guide; model −6.1% midpoint
+Also: Ctrl+F "Net revenue" → FY2025 11,102,600 ($000); FY27–30 growth = model assumption</t>
         </is>
       </c>
       <c r="F6" s="48">
@@ -2824,8 +2824,8 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>"full year 2026" → margin commentary; base EBIT margin 13.9% (model assumption)
-Also: "Income from operations" ÷ "Net revenue" → FY25 $2,210,615 / $11,102,600 = 19.9%</t>
+          <t>Ctrl+F "operating margin" → "18.8%" Q2 FY2026; FY26 full-year 13.9% EBIT margin = model
+Also: Ctrl+F "Income from operations" → 2,210,615 ÷ "Net revenue" 11,102,600 = 19.9% FY25</t>
         </is>
       </c>
       <c r="F7" s="48">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>"Depreciation and amortization" → FY25 $496,228; ÷ "Net revenue" $11,102,600 = 4.5%</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228; ÷ "Net revenue" 11,102,600 = 4.5%</t>
         </is>
       </c>
       <c r="F11" s="20">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>"Capital expenditures" → FY25 $(680,802); ÷ "Net revenue" = 6.1%; model 5.0%</t>
+          <t>Ctrl+F "680,802" → capex ($000) in investing; ÷ revenue 11,102,600; model 5.0%</t>
         </is>
       </c>
       <c r="F13" s="20">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>"Inventories" $1,700,753 | "Accounts payable" $331,421 | "Accrued liabilities" $662,982</t>
+          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
         </is>
       </c>
       <c r="F15" s="20">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>"GDPC1" → FRED Units: Percent Change from Year Ago; long-run ≈ 2%; model 2.25%</t>
+          <t>Ctrl+F "GDPC1" → FRED Real GDP series; long-run growth ~2%; model terminal g 2.25%</t>
         </is>
       </c>
       <c r="E26" s="48">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
       <c r="E32" s="44" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
-          <t>"Long-term debt" → $0 (no funded debt)</t>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
         </is>
       </c>
       <c r="E33" s="44" t="n">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
       <c r="E35" s="44" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
       <c r="E37" s="60" t="n">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="D43" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
+          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
       <c r="E43" s="62" t="n">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="D59" s="19" t="inlineStr">
         <is>
-          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+          <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
       <c r="F59" s="72" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
         </is>
       </c>
       <c r="F60" s="73">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
         </is>
       </c>
       <c r="F61" s="73">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
         </is>
       </c>
       <c r="F62" s="73">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
         </is>
       </c>
       <c r="F63" s="73">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>"Implied ERP (FCFE)" → anchors WACC range 9.0%–11.0%</t>
+          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
         </is>
       </c>
       <c r="F64" s="73">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>Scenarios tab → "WACC" row &amp; "Terminal growth" row (base inputs)</t>
+          <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
       <c r="L65" s="58" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="M65" s="19" t="inlineStr">
         <is>
-          <t>"GDPC1" → bounds terminal-g sensitivity 1.5%–3.0%</t>
+          <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>"Net revenue" → FY2025 $11,102,600 ($000)</t>
+          <t>Ctrl+F "Net revenue" → 11,102,600 ($000) in FY2025 column</t>
         </is>
       </c>
       <c r="E4" s="44" t="n">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>"diluted earnings per share" → "range of $9.48 to $9.73"; model midpoint $9.61</t>
+          <t>Ctrl+F "$9.48 to $9.73" → FY2026 diluted EPS guidance; model midpoint $9.61</t>
         </is>
       </c>
       <c r="E7" s="60" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>"Cash and cash equivalents" → FY2025 $1,807,202 ($000)</t>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
       <c r="E8" s="44" t="n">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>"Diluted weighted-average number of common shares outstanding" → 119,068 (000)</t>
+          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
       <c r="E9" s="44" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
       <c r="E10" s="60" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>"Income from operations" $2,210,615 + "Depreciation and amortization" $496,228</t>
+          <t>Ctrl+F "Income from operations" → 2,210,615 + "Depreciation and amortization" → 496,228</t>
         </is>
       </c>
       <c r="E17" s="78">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: NKE statistics</t>
+          <t>StockAnalysis: NKE EV/EBITDA</t>
         </is>
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" → NKE forward multiple ≈ 18x (illustrative peer)</t>
+          <t>Ctrl+F "EV / EBITDA" → read NKE multiple on page; model peer input 18.0x</t>
         </is>
       </c>
       <c r="E18" s="79" t="n">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: DECK statistics</t>
+          <t>StockAnalysis: DECK EV/EBITDA</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" → DECK forward multiple ≈ 15x</t>
+          <t>Ctrl+F "EV / EBITDA" → read DECK multiple on page; model peer input 15.0x</t>
         </is>
       </c>
       <c r="E19" s="79" t="n">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="C20" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: ONON statistics</t>
+          <t>StockAnalysis: ONON EV/EBITDA</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" → ONON forward multiple ≈ 25x</t>
+          <t>Ctrl+F "EV / EBITDA" → read ONON multiple on page; model peer input 25.0x</t>
         </is>
       </c>
       <c r="E20" s="79" t="n">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: adidas (ADDYY)</t>
+          <t>StockAnalysis: adidas (ADR)</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" → ADDYY forward multiple ≈ 12x</t>
+          <t>Ctrl+F "EV / EBITDA" → read ADDYY multiple on page; model peer input 12.0x</t>
         </is>
       </c>
       <c r="E21" s="79" t="n">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="C22" s="18" t="inlineStr">
         <is>
-          <t>Yahoo Finance: VFC statistics</t>
+          <t>StockAnalysis: VFC EV/EBITDA</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" → VFC forward multiple ≈ 10x</t>
+          <t>Ctrl+F "EV / EBITDA" → read VFC multiple on page; model peer input 10.0x</t>
         </is>
       </c>
       <c r="E22" s="79" t="n">
@@ -4574,8 +4574,8 @@
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>Lo: "Enterprise Value/EBITDA" → LULU current trough; bear terminal 6.5x
-Hi: "Enterprise Value/EBITDA" → bull terminal 9.5x on FY2030E EBITDA</t>
+          <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; bear terminal exit assumption 6.5x
+Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
       <c r="E37" s="79" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>"Enterprise Value/EBITDA" on StockAnalysis; model terminal exit 8.0x FY2030E EBITDA</t>
+          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
       <c r="E38" s="82">
@@ -4637,14 +4637,14 @@
       </c>
       <c r="C39" s="80" t="inlineStr">
         <is>
-          <t>Lo: Yahoo Finance: LULU P/E
-Hi: Yahoo Finance: NKE P/E (peer)</t>
+          <t>Lo: StockAnalysis: LULU Forward P/E
+Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>Lo: "Forward P/E" → LULU on depressed FY26E EPS; low case 10.0x
-Hi: "Forward P/E" → NKE peer benchmark; high case 18.0x on FY26E EPS</t>
+          <t>Lo: Ctrl+F "Forward PE" → LULU ~12.3x; low-case multiple assumption 10.0x
+Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
       <c r="E39" s="79" t="n">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D42" s="19" t="inlineStr">
         <is>
-          <t>"Last Sale" or "Previous Close" → LULU share price</t>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
       <c r="E42" s="86" t="n">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>27% normalized marginal cash tax rate; mid-point between recent effective rates and US federal-plus-state blend.</t>
+          <t>27% DCF cash tax is a model assumption (below FY25 effective 29.5% and FY26 guide ~30%); 3-statement uses 30%.</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.</t>
+          <t>13.9% is a FY2026E model assumption — not the 13% YoY drop in Q2 operating income. Q2 OM was 18.8% (incl. 560bps tariffs); ex-tariff ~13.2%.</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "operating margin" → "18.8%" Q2 FY2026; FY26 full-year 13.9% EBIT margin = model</t>
+          <t>Ctrl+F "decreased 190 basis points to 18.8%" — that is Q2 operating margin. "decreased 13%" is YoY $ decline in income from operations, NOT the margin. Model FY26 EBIT margin 13.9% (assumption; Q2 ex-tariff OM ≈ 18.8% − 560bps = 13.2%)</t>
         </is>
       </c>
       <c r="F6" s="20" t="n">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>27% cash tax rate for scenario FCF; consistent with WACC normalized rate and DCF unlevered cash conversion.</t>
+          <t>27% DCF cash tax is a model assumption; FY25 effective is 29.5% and FY26 guidance is ~30% (used in the 3-statement).</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income tax expense" → 659,784 ÷ "Income before income tax expense" 2,238,967</t>
+          <t>Ctrl+F "Income tax expense" → 659,784 ÷ "Income before income tax expense" 2,238,967 = 29.5% FY25; DCF model uses 27%</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → capex ($000) in investing; ÷ revenue 11,102,600; model 5.0%</t>
+          <t>Ctrl+F "680,802" → FY25 capex ($000) = 6.1% of revenue. Model 5.0% is an assumption (below FY25 and below 2026 guide $725–745M)</t>
         </is>
       </c>
       <c r="F12" s="20" t="n">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>13.9% FY2026 EBIT margin reflects Americas weakness and guided compression; above bear, below historical peak.
+          <t>13.9% is a FY2026E model assumption — not the 13% YoY drop in Q2 operating income. Q2 OM was 18.8% (incl. 560bps tariffs); ex-tariff ~13.2%.
 Also: 15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
         </is>
       </c>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "operating margin" → "18.8%" Q2 FY2026; FY26 full-year 13.9% EBIT margin = model
+          <t>Ctrl+F "decreased 190 basis points to 18.8%" — that is Q2 operating margin. "decreased 13%" is YoY $ decline in income from operations, NOT the margin. Model FY26 EBIT margin 13.9% (assumption; Q2 ex-tariff OM ≈ 18.8% − 560bps = 13.2%)
 Also: Ctrl+F "Income from operations" → 2,210,615 ÷ "Net revenue" 11,102,600 = 19.9% FY25</t>
         </is>
       </c>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → capex ($000) in investing; ÷ revenue 11,102,600; model 5.0%</t>
+          <t>Ctrl+F "680,802" → FY25 capex ($000) = 6.1% of revenue. Model 5.0% is an assumption (below FY25 and below 2026 guide $725–745M)</t>
         </is>
       </c>
       <c r="F13" s="20">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>13.9% is a FY2026E model assumption — not the 13% YoY drop in Q2 operating income. Q2 OM was 18.8% (incl. 560bps tariffs); ex-tariff ~13.2%.</t>
+          <t>FY26 13.9% is derived: Q2 OM 18.8% minus 560bps tariff refunds = 13.2% clean; we set base slightly above that run-rate.</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release</t>
+          <t>Q2 FY2026 release: OM 18.8% less 560bps tariffs</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "decreased 190 basis points to 18.8%" — that is Q2 operating margin. "decreased 13%" is YoY $ decline in income from operations, NOT the margin. Model FY26 EBIT margin 13.9% (assumption; Q2 ex-tariff OM ≈ 18.8% − 560bps = 13.2%)</t>
+          <t>1) Ctrl+F "18.8%" = Q2 operating margin. 2) Ctrl+F "560 basis points" = tariff add. 3) Clean Q2 = 18.8% − 5.6% = 13.2%. Model FY26 base 13.9% sits just above that. Do not use "decreased 13%" — that is the YoY $ decline in income from operations.</t>
         </is>
       </c>
       <c r="F6" s="20" t="n">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+          <t>FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>LULU historical EBIT margins (10-K)</t>
+          <t>FY2025 10-K: Income from operations / revenue</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income from operations" → 2,210,615 ÷ "Net revenue" 11,102,600 = 19.9% FY25</t>
+          <t>Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
         </is>
       </c>
       <c r="F7" s="20" t="n">
@@ -2812,20 +2812,20 @@
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>13.9% is a FY2026E model assumption — not the 13% YoY drop in Q2 operating income. Q2 OM was 18.8% (incl. 560bps tariffs); ex-tariff ~13.2%.
-Also: 15.5% FY2030 EBIT margin assumes partial recovery; still materially below ~20–24% peak operating margins.</t>
+          <t>FY26 13.9% is derived: Q2 OM 18.8% minus 560bps tariff refunds = 13.2% clean; we set base slightly above that run-rate.
+Also: FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
         </is>
       </c>
       <c r="C7" s="47" t="inlineStr">
         <is>
-          <t>LULU Q2 FY2026 earnings release
-Also: LULU historical EBIT margins (10-K)</t>
+          <t>Q2 FY2026 release: OM 18.8% less 560bps tariffs
+Also: FY2025 10-K: Income from operations / revenue</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "decreased 190 basis points to 18.8%" — that is Q2 operating margin. "decreased 13%" is YoY $ decline in income from operations, NOT the margin. Model FY26 EBIT margin 13.9% (assumption; Q2 ex-tariff OM ≈ 18.8% − 560bps = 13.2%)
-Also: Ctrl+F "Income from operations" → 2,210,615 ÷ "Net revenue" 11,102,600 = 19.9% FY25</t>
+          <t>1) Ctrl+F "18.8%" = Q2 operating margin. 2) Ctrl+F "560 basis points" = tariff add. 3) Clean Q2 = 18.8% − 5.6% = 13.2%. Model FY26 base 13.9% sits just above that. Do not use "decreased 13%" — that is the YoY $ decline in income from operations.
+Also: Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
         </is>
       </c>
       <c r="F7" s="48">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1049,7 +1049,7 @@
       <c r="B19" s="10" t="inlineStr">
         <is>
           <t>FY2025 Form 10-K (ended Feb 1, 2026)
-Ctrl+F: Ctrl+F "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+Ctrl+F: Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>4.3% risk-free anchored to FRED 10Y Treasury (DGS10); rounded early-Sep-2026 level for DCF stability.</t>
+          <t>4.8% risk-free = FRED DGS10 on 2026-09-03 (4.77%) rounded; replaces the stale 4.3% input.</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
@@ -1154,11 +1154,11 @@
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "DGS10" → FRED series table; Sep 2026 ≈ 4.28%; model 4.3%</t>
+          <t>Ctrl+F "2026-09-03" → observation 4.77. Model uses 4.8%. Also Ctrl+F "DGS10" for the series title.</t>
         </is>
       </c>
       <c r="E3" s="20" t="n">
-        <v>0.043</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>6.0% additive ERP; conservative vs Damodaran implied ~4.2% (Jan-26); within long-run historical US range.</t>
+          <t>6.0% ERP is a conservative overlay vs Damodaran Jan-2026 implied 4.23%; used to keep CoE above the risk-free 4.8%.</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → Jan-2026 row shows 4.23%; model uses 6.0%</t>
+          <t>Ctrl+F "4.23%" on the 2025 row (last data row). Header is "Implied ERP (FCFE)". Model uses 6.0%.</t>
         </is>
       </c>
       <c r="E4" s="20" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>0.95 levered beta vs ~0.86 market; modest uplift for near-term earnings volatility and post-guidance de-rating.</t>
+          <t>0.95 levered beta vs StockAnalysis Beta (5Y) 0.86; modest uplift for post-guidance volatility.</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Beta (5Y)" → page shows 0.86; model uses 0.95</t>
+          <t>Ctrl+F "Beta (5Y)" → 0.86. Model uses 0.95.</t>
         </is>
       </c>
       <c r="E5" s="21" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>5.0% illustrative pre-tax debt cost; LULU has no funded term debt, only an undrawn revolving credit facility.</t>
+          <t>5.0% illustrative pre-tax debt cost; 10-K: no borrowings outstanding on the revolver.</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "no borrowings were outstanding under this facility" → FY2025 10-K Note 12</t>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" on this 10-K HTML page (search the document, do not use the EDGAR viewer TOC).</t>
         </is>
       </c>
       <c r="E9" s="20" t="n">
@@ -1262,21 +1262,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>27% DCF cash tax is a model assumption (below FY25 effective 29.5% and FY26 guide ~30%); 3-statement uses 30%.</t>
+          <t>30% cash tax matches FY2026 guidance (“approximately 30%”); FY25 effective was 29.5%.</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Damodaran: US tax rate dataset</t>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Apparel" → Damodaran Tax Rates by Sector (US), Jan-2026; model 27%</t>
+          <t>Ctrl+F "a tax rate of approximately 30%" on the FY2026 outlook paragraph.</t>
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10.0% base WACC ties to CAPM build on WACC tab; drives scenario DCFs and base-case valuation.</t>
+          <t>10.5% base WACC = rf 4.8% + 0.95×6.0% ERP on the WACC tab (FRED 4.77% rounded).</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>WACC tab → Ctrl+F "WACC" → cell E = 10.0%</t>
+          <t>WACC tab → cell E (green) = rf 4.8% + β 0.95 × ERP 6.0% = 10.5%</t>
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "GDPC1" → FRED Real GDP series; long-run growth ~2%; model terminal g 2.25%</t>
+          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>27% DCF cash tax is a model assumption; FY25 effective is 29.5% and FY26 guidance is ~30% (used in the 3-statement).</t>
+          <t>30% cash tax from FY2026 outlook; FY25 10-K effective is 29.5% (659,784 / 2,238,967).</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>LULU effective tax history (10-K)</t>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income tax expense" → 659,784 ÷ "Income before income tax expense" 2,238,967 = 29.5% FY25; DCF model uses 27%</t>
+          <t>Ctrl+F "a tax rate of approximately 30%" on the earnings outlook. FY25 10-K: "Income tax expense" 659,784 ÷ "Income before income tax expense" 2,238,967 = 29.5%.</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G10" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="G10" s="20" t="n">
-        <v>0.27</v>
-      </c>
       <c r="H10" s="20" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Depreciation and amortization" → 496,228; ÷ "Net revenue" 11,102,600 = 4.5%</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -1709,14 +1709,14 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex ($000) = 6.1% of revenue. Model 5.0% is an assumption (below FY25 and below 2026 guide $725–745M)</t>
+          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
         </is>
       </c>
       <c r="F12" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G12" s="20" t="n">
         <v>0.055</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0.05</v>
       </c>
       <c r="H12" s="20" t="n">
         <v>0.045</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "CONSOLIDATED STATEMENTS OF OPERATIONS" or "CONSOLIDATED BALANCE SHEETS"</t>
+          <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
       <c r="E3" s="42" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A to revenue near FY22–25 average; reflects store fleet, distribution, and technology amortization load.</t>
+          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Depreciation and amortization" → 496,228; ÷ "Net revenue" 11,102,600 = 4.5%</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
         </is>
       </c>
       <c r="F11" s="20">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>5.0% capex to revenue aligned with recent investment intensity and continued global store expansion plans.</t>
+          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex ($000) = 6.1% of revenue. Model 5.0% is an assumption (below FY25 and below 2026 guide $725–745M)</t>
+          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
         </is>
       </c>
       <c r="F13" s="20">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>2.25% terminal growth approximates long-run GDP plus inflation; conservative perpetuity rate for mature apparel.</t>
+          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "GDPC1" → FRED Real GDP series; long-run growth ~2%; model terminal g 2.25%</t>
+          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
       <c r="E26" s="48">
@@ -3784,7 +3784,7 @@
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="72" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="C60" s="58" t="inlineStr">
         <is>
@@ -3793,27 +3793,27 @@
       </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
       <c r="F60" s="73">
-        <f>(NPV(0.09,F18:J18)+(J18*(1+0.015)/(0.09-0.015))/(1+0.09)^5+E32+E33)/E35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G60" s="73">
-        <f>(NPV(0.09,F18:J18)+(J18*(1+0.02)/(0.09-0.02))/(1+0.09)^5+E32+E33)/E35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H60" s="73">
-        <f>(NPV(0.09,F18:J18)+(J18*(1+0.0225)/(0.09-0.0225))/(1+0.09)^5+E32+E33)/E35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="I60" s="73">
-        <f>(NPV(0.09,F18:J18)+(J18*(1+0.025)/(0.09-0.025))/(1+0.09)^5+E32+E33)/E35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="J60" s="73">
-        <f>(NPV(0.09,F18:J18)+(J18*(1+0.03)/(0.09-0.03))/(1+0.09)^5+E32+E33)/E35</f>
+        <f>(NPV(0.095,F18:J18)+(J18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="L60" s="58" t="inlineStr">
@@ -3824,31 +3824,31 @@
     </row>
     <row r="61" ht="36" customHeight="1">
       <c r="A61" s="72" t="n">
-        <v>0.095</v>
+        <v>0.1</v>
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
       <c r="F61" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E32+E33)/E35</f>
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G61" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E32+E33)/E35</f>
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H61" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E32+E33)/E35</f>
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="I61" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E32+E33)/E35</f>
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="J61" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E32+E33)/E35</f>
+        <f>(NPV(0.1,F18:J18)+(J18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="L61" s="58" t="inlineStr">
@@ -3859,31 +3859,31 @@
     </row>
     <row r="62" ht="36" customHeight="1">
       <c r="A62" s="72" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="D62" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
       <c r="F62" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E32+E33)/E35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G62" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E32+E33)/E35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H62" s="74">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E32+E33)/E35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="I62" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E32+E33)/E35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="J62" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E32+E33)/E35</f>
+        <f>(NPV(0.105,F18:J18)+(J18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="L62" s="58" t="inlineStr">
@@ -3894,31 +3894,31 @@
     </row>
     <row r="63" ht="36" customHeight="1">
       <c r="A63" s="72" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="D63" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
       <c r="F63" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E32+E33)/E35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G63" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E32+E33)/E35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H63" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E32+E33)/E35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="I63" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E32+E33)/E35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="J63" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E32+E33)/E35</f>
+        <f>(NPV(0.11,F18:J18)+(J18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="L63" s="58" t="inlineStr">
@@ -3929,31 +3929,31 @@
     </row>
     <row r="64" ht="36" customHeight="1">
       <c r="A64" s="72" t="n">
-        <v>0.11</v>
+        <v>0.115</v>
       </c>
       <c r="D64" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Implied ERP (FCFE)" → anchors WACC sensitivity range 9.0%–11.0%</t>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
       <c r="F64" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E32+E33)/E35</f>
+        <f>(NPV(0.115,F18:J18)+(J18*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="G64" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E32+E33)/E35</f>
+        <f>(NPV(0.115,F18:J18)+(J18*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="H64" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E32+E33)/E35</f>
+        <f>(NPV(0.115,F18:J18)+(J18*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="I64" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E32+E33)/E35</f>
+        <f>(NPV(0.115,F18:J18)+(J18*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="J64" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E32+E33)/E35</f>
+        <f>(NPV(0.115,F18:J18)+(J18*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E32+E33)/E35</f>
         <v/>
       </c>
       <c r="L64" s="58" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Nike ~18x forward EV/EBITDA illustrative; mature global athletic benchmark with slower growth than LULU peak.</t>
+          <t>Nike EV/EBITDA 12.0x equals StockAnalysis 11.97x, rounded; mature athletic benchmark.</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -4316,11 +4316,11 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → read NKE multiple on page; model peer input 18.0x</t>
+          <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
         </is>
       </c>
       <c r="E18" s="79" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Deckers ~15x reference; premium footwear peer with HOKA/UGG momentum and strong brand heat.</t>
+          <t>Deckers EV/EBITDA 8.0x equals StockAnalysis 7.95x, rounded; closest premium-footwear peer.</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -4341,11 +4341,11 @@
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → read DECK multiple on page; model peer input 15.0x</t>
+          <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
         </is>
       </c>
       <c r="E19" s="79" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>On Holding ~25x; high-growth athletic peer setting upper bound for premium positioning and white space.</t>
+          <t>On Holding EV/EBITDA 14.0x equals StockAnalysis 14.03x, rounded; high-growth athletic peer.</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -4366,11 +4366,11 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → read ONON multiple on page; model peer input 25.0x</t>
+          <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
         </is>
       </c>
       <c r="E20" s="79" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="36" customHeight="1">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>adidas ~12x; global incumbent in restructuring with moderate growth and complex brand portfolio.</t>
+          <t>adidas (ADDYY) EV/EBITDA 9.3x equals StockAnalysis 9.31x; global incumbent.</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -4391,11 +4391,11 @@
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → read ADDYY multiple on page; model peer input 12.0x</t>
+          <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
         </is>
       </c>
       <c r="E21" s="79" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="22" ht="36" customHeight="1">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>VFC ~10x; challenged multi-brand apparel operator representing lower bound for scaled apparel peers.</t>
+          <t>VFC EV/EBITDA 10.7x equals StockAnalysis 10.71x; challenged multi-brand apparel peer.</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -4416,11 +4416,11 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → read VFC multiple on page; model peer input 10.0x</t>
+          <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
         </is>
       </c>
       <c r="E22" s="79" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="24">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1482,24 +1482,24 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+          <t>2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>LULU historical revenue (10-K)</t>
+          <t>StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Net revenue" → FY2025 11,102,600 ($000); FY27–30 growth = model assumption</t>
+          <t>Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
       <c r="F5" s="20" t="n">
         <v>-0.01</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>0.028</v>
+        <v>0.023</v>
       </c>
       <c r="H5" s="20" t="n">
         <v>0.06</v>
@@ -2768,19 +2768,19 @@
       <c r="B6" s="19" t="inlineStr">
         <is>
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint of −5% to −7% after Q2 FY2026 print.
-Also: 2.8% avg FY27–30 growth assumes gradual recovery; well below historical double-digit LULU revenue expansion.</t>
+Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
       <c r="C6" s="47" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
-Also: LULU historical revenue (10-K)</t>
+Also: StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "decline of 5% to 7%" → FY2026 revenue guide; model −6.1% midpoint
-Also: Ctrl+F "Net revenue" → FY2025 11,102,600 ($000); FY27–30 growth = model assumption</t>
+Also: Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
       <c r="F6" s="48">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -356,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -418,6 +418,9 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -436,6 +439,9 @@
     <xf numFmtId="166" fontId="26" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="22" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -483,6 +489,9 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1378,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1508,198 +1517,198 @@
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>FY2026E EBIT margin</t>
+          <t>Run-rate EBIT margin (clean, ex-refunds)</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>FY26 13.9% is derived: Q2 OM 18.8% minus 560bps tariff refunds = 13.2% clean; we set base slightly above that run-rate.</t>
+          <t>13.2% is the real/run-rate OM: Q2 18.8% minus 560bps of tariff refunds. FY26 then adds the $134.5M refund once on top.</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>Q2 FY2026 release: OM 18.8% less 560bps tariffs</t>
+          <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>1) Ctrl+F "18.8%" = Q2 operating margin. 2) Ctrl+F "560 basis points" = tariff add. 3) Clean Q2 = 18.8% − 5.6% = 13.2%. Model FY26 base 13.9% sits just above that. Do not use "decreased 13%" — that is the YoY $ decline in income from operations.</t>
+          <t>Ctrl+F "18.8%" (Q2 OM) and "560 basis points" (tariff boost). Real run-rate = 18.8% − 5.6% = 13.2%. Do not use "decreased 13%".</t>
         </is>
       </c>
       <c r="F6" s="20" t="n">
-        <v>0.125</v>
+        <v>0.12</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>0.139</v>
+        <v>0.132</v>
       </c>
       <c r="H6" s="20" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>Terminal (FY2030E) EBIT margin</t>
+          <t>FY26 IEEPA tariff refunds ($k, already in guide)</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
+          <t>Add back $134.5M in FY26 only — already recognized (reduced COGS). +130bps on FY26 sales, not +560bps (that was Q2-only).</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>FY2025 10-K: Income from operations / revenue</t>
+          <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G7" s="20" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <v>0.19</v>
+          <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>134500</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>134500</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>134500</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>Terminal (FY2030E) EBIT margin</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>10.5% base WACC = rf 4.8% + 0.95×6.0% ERP on the WACC tab (FRED 4.77% rounded).</t>
+          <t>FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>WACC tab: CAPM build</t>
+          <t>FY2025 10-K: Income from operations / revenue</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>WACC tab → cell E (green) = rf 4.8% + β 0.95 × ERP 6.0% = 10.5%</t>
+          <t>Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
         </is>
       </c>
       <c r="F8" s="20" t="n">
-        <v>0.115</v>
+        <v>0.12</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>0.105</v>
+        <v>0.155</v>
       </c>
       <c r="H8" s="20" t="n">
-        <v>0.095</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
+          <t>10.5% base WACC = rf 4.8% + 0.95×6.0% ERP on the WACC tab (FRED 4.77% rounded).</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>FRED: Real GDP (GDPC1)</t>
+          <t>WACC tab: CAPM build</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
+          <t>WACC tab → cell E (green) = rf 4.8% + β 0.95 × ERP 6.0% = 10.5%</t>
         </is>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.015</v>
+        <v>0.115</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.0225</v>
+        <v>0.105</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>0.03</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Cash tax rate</t>
+          <t>Terminal growth</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>30% cash tax from FY2026 outlook; FY25 10-K effective is 29.5% (659,784 / 2,238,967).</t>
+          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
+          <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "a tax rate of approximately 30%" on the earnings outlook. FY25 10-K: "Income tax expense" 659,784 ÷ "Income before income tax expense" 2,238,967 = 29.5%.</t>
+          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
       <c r="F10" s="20" t="n">
-        <v>0.32</v>
+        <v>0.015</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.3</v>
+        <v>0.0225</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>0.28</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t>D&amp;A % of revenue</t>
+          <t>Cash tax rate</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
+          <t>30% cash tax from FY2026 outlook; FY25 10-K effective is 29.5% (659,784 / 2,238,967).</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>LULU CF statement (10-K)</t>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
+          <t>Ctrl+F "a tax rate of approximately 30%" on the earnings outlook. FY25 10-K: "Income tax expense" 659,784 ÷ "Income before income tax expense" 2,238,967 = 29.5%.</t>
         </is>
       </c>
       <c r="F11" s="20" t="n">
-        <v>0.045</v>
+        <v>0.32</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.045</v>
+        <v>0.3</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>0.045</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t>Capex % of revenue</t>
+          <t>D&amp;A % of revenue</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
+          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -1709,14 +1718,14 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
         </is>
       </c>
       <c r="F12" s="20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>0.055</v>
+        <v>0.045</v>
       </c>
       <c r="H12" s="20" t="n">
         <v>0.045</v>
@@ -1725,860 +1734,891 @@
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
           <t>NWC build % of Δrevenue</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
         </is>
       </c>
-      <c r="F13" s="20" t="n">
+      <c r="F14" s="20" t="n">
         <v>0.08</v>
       </c>
-      <c r="G13" s="20" t="n">
+      <c r="G14" s="20" t="n">
         <v>0.075</v>
       </c>
-      <c r="H13" s="20" t="n">
+      <c r="H14" s="20" t="n">
         <v>0.07000000000000001</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>5-year forecast paths (by scenario)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="F16" s="30">
+      <c r="F17" s="31">
         <f>11102600*(1+F4)</f>
         <v/>
       </c>
-      <c r="G16" s="30">
+      <c r="G17" s="31">
         <f>11102600*(1+G4)</f>
         <v/>
       </c>
-      <c r="H16" s="30">
+      <c r="H17" s="31">
         <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="F17" s="30">
-        <f>F16*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G17" s="30">
-        <f>G16*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H17" s="30">
-        <f>H16*(1+H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="F18" s="31">
+        <f>F17*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G18" s="31">
+        <f>G17*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H18" s="31">
+        <f>H17*(1+H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="F18" s="30">
-        <f>F17*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G18" s="30">
-        <f>G17*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H18" s="30">
-        <f>H17*(1+H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="F19" s="31">
+        <f>F18*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G19" s="31">
+        <f>G18*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H19" s="31">
+        <f>H18*(1+H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="F19" s="30">
-        <f>F18*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G19" s="30">
-        <f>G18*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H19" s="30">
-        <f>H18*(1+H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="F20" s="31">
+        <f>F19*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G20" s="31">
+        <f>G19*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H20" s="31">
+        <f>H19*(1+H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="F20" s="30">
-        <f>F19*(1+F5)</f>
-        <v/>
-      </c>
-      <c r="G20" s="30">
-        <f>G19*(1+G5)</f>
-        <v/>
-      </c>
-      <c r="H20" s="30">
-        <f>H19*(1+H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 1</t>
-        </is>
-      </c>
       <c r="F21" s="31">
-        <f>F6+(F7-F6)*0/4</f>
+        <f>F20*(1+F5)</f>
         <v/>
       </c>
       <c r="G21" s="31">
-        <f>G6+(G7-G6)*0/4</f>
+        <f>G20*(1+G5)</f>
         <v/>
       </c>
       <c r="H21" s="31">
-        <f>H6+(H7-H6)*0/4</f>
+        <f>H20*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 2</t>
-        </is>
-      </c>
-      <c r="F22" s="31">
-        <f>F6+(F7-F6)*1/4</f>
-        <v/>
-      </c>
-      <c r="G22" s="31">
-        <f>G6+(G7-G6)*1/4</f>
-        <v/>
-      </c>
-      <c r="H22" s="31">
-        <f>H6+(H7-H6)*1/4</f>
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Clean EBIT margin – year 1</t>
+        </is>
+      </c>
+      <c r="F22" s="32">
+        <f>F6+(F8-F6)*0/4</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>G6+(G8-G6)*0/4</f>
+        <v/>
+      </c>
+      <c r="H22" s="32">
+        <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 3</t>
-        </is>
-      </c>
-      <c r="F23" s="31">
-        <f>F6+(F7-F6)*2/4</f>
-        <v/>
-      </c>
-      <c r="G23" s="31">
-        <f>G6+(G7-G6)*2/4</f>
-        <v/>
-      </c>
-      <c r="H23" s="31">
-        <f>H6+(H7-H6)*2/4</f>
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Clean EBIT margin – year 2</t>
+        </is>
+      </c>
+      <c r="F23" s="32">
+        <f>F6+(F8-F6)*1/4</f>
+        <v/>
+      </c>
+      <c r="G23" s="32">
+        <f>G6+(G8-G6)*1/4</f>
+        <v/>
+      </c>
+      <c r="H23" s="32">
+        <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 4</t>
-        </is>
-      </c>
-      <c r="F24" s="31">
-        <f>F6+(F7-F6)*3/4</f>
-        <v/>
-      </c>
-      <c r="G24" s="31">
-        <f>G6+(G7-G6)*3/4</f>
-        <v/>
-      </c>
-      <c r="H24" s="31">
-        <f>H6+(H7-H6)*3/4</f>
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Clean EBIT margin – year 3</t>
+        </is>
+      </c>
+      <c r="F24" s="32">
+        <f>F6+(F8-F6)*2/4</f>
+        <v/>
+      </c>
+      <c r="G24" s="32">
+        <f>G6+(G8-G6)*2/4</f>
+        <v/>
+      </c>
+      <c r="H24" s="32">
+        <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBIT margin – year 5</t>
-        </is>
-      </c>
-      <c r="F25" s="31">
-        <f>F6+(F7-F6)*4/4</f>
-        <v/>
-      </c>
-      <c r="G25" s="31">
-        <f>G6+(G7-G6)*4/4</f>
-        <v/>
-      </c>
-      <c r="H25" s="31">
-        <f>H6+(H7-H6)*4/4</f>
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Clean EBIT margin – year 4</t>
+        </is>
+      </c>
+      <c r="F25" s="32">
+        <f>F6+(F8-F6)*3/4</f>
+        <v/>
+      </c>
+      <c r="G25" s="32">
+        <f>G6+(G8-G6)*3/4</f>
+        <v/>
+      </c>
+      <c r="H25" s="32">
+        <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Clean EBIT margin – year 5</t>
+        </is>
+      </c>
+      <c r="F26" s="32">
+        <f>F6+(F8-F6)*4/4</f>
+        <v/>
+      </c>
+      <c r="G26" s="32">
+        <f>G6+(G8-G6)*4/4</f>
+        <v/>
+      </c>
+      <c r="H26" s="32">
+        <f>H6+(H8-H6)*4/4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="F26" s="30">
-        <f>F16*F21</f>
-        <v/>
-      </c>
-      <c r="G26" s="30">
-        <f>G16*G21</f>
-        <v/>
-      </c>
-      <c r="H26" s="30">
-        <f>H16*H21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="F27" s="31">
+        <f>F17*F22+F7</f>
+        <v/>
+      </c>
+      <c r="G27" s="31">
+        <f>G17*G22+G7</f>
+        <v/>
+      </c>
+      <c r="H27" s="31">
+        <f>H17*H22+H7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="F27" s="30">
-        <f>F17*F22</f>
-        <v/>
-      </c>
-      <c r="G27" s="30">
-        <f>G17*G22</f>
-        <v/>
-      </c>
-      <c r="H27" s="30">
-        <f>H17*H22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="F28" s="31">
+        <f>F18*F23</f>
+        <v/>
+      </c>
+      <c r="G28" s="31">
+        <f>G18*G23</f>
+        <v/>
+      </c>
+      <c r="H28" s="31">
+        <f>H18*H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="F28" s="30">
-        <f>F18*F23</f>
-        <v/>
-      </c>
-      <c r="G28" s="30">
-        <f>G18*G23</f>
-        <v/>
-      </c>
-      <c r="H28" s="30">
-        <f>H18*H23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="F29" s="31">
+        <f>F19*F24</f>
+        <v/>
+      </c>
+      <c r="G29" s="31">
+        <f>G19*G24</f>
+        <v/>
+      </c>
+      <c r="H29" s="31">
+        <f>H19*H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="F29" s="30">
-        <f>F19*F24</f>
-        <v/>
-      </c>
-      <c r="G29" s="30">
-        <f>G19*G24</f>
-        <v/>
-      </c>
-      <c r="H29" s="30">
-        <f>H19*H24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="F30" s="31">
+        <f>F20*F25</f>
+        <v/>
+      </c>
+      <c r="G30" s="31">
+        <f>G20*G25</f>
+        <v/>
+      </c>
+      <c r="H30" s="31">
+        <f>H20*H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="F30" s="30">
-        <f>F20*F25</f>
-        <v/>
-      </c>
-      <c r="G30" s="30">
-        <f>G20*G25</f>
-        <v/>
-      </c>
-      <c r="H30" s="30">
-        <f>H20*H25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="F31" s="31">
+        <f>F21*F26</f>
+        <v/>
+      </c>
+      <c r="G31" s="31">
+        <f>G21*G26</f>
+        <v/>
+      </c>
+      <c r="H31" s="31">
+        <f>H21*H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="F31" s="30">
-        <f>F26*(1-F10)</f>
-        <v/>
-      </c>
-      <c r="G31" s="30">
-        <f>G26*(1-G10)</f>
-        <v/>
-      </c>
-      <c r="H31" s="30">
-        <f>H26*(1-H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="F32" s="31">
+        <f>F27*(1-F11)</f>
+        <v/>
+      </c>
+      <c r="G32" s="31">
+        <f>G27*(1-G11)</f>
+        <v/>
+      </c>
+      <c r="H32" s="31">
+        <f>H27*(1-H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="F32" s="30">
-        <f>F27*(1-F10)</f>
-        <v/>
-      </c>
-      <c r="G32" s="30">
-        <f>G27*(1-G10)</f>
-        <v/>
-      </c>
-      <c r="H32" s="30">
-        <f>H27*(1-H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="F33" s="31">
+        <f>F28*(1-F11)</f>
+        <v/>
+      </c>
+      <c r="G33" s="31">
+        <f>G28*(1-G11)</f>
+        <v/>
+      </c>
+      <c r="H33" s="31">
+        <f>H28*(1-H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="F33" s="30">
-        <f>F28*(1-F10)</f>
-        <v/>
-      </c>
-      <c r="G33" s="30">
-        <f>G28*(1-G10)</f>
-        <v/>
-      </c>
-      <c r="H33" s="30">
-        <f>H28*(1-H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="F34" s="31">
+        <f>F29*(1-F11)</f>
+        <v/>
+      </c>
+      <c r="G34" s="31">
+        <f>G29*(1-G11)</f>
+        <v/>
+      </c>
+      <c r="H34" s="31">
+        <f>H29*(1-H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="F34" s="30">
-        <f>F29*(1-F10)</f>
-        <v/>
-      </c>
-      <c r="G34" s="30">
-        <f>G29*(1-G10)</f>
-        <v/>
-      </c>
-      <c r="H34" s="30">
-        <f>H29*(1-H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="F35" s="31">
+        <f>F30*(1-F11)</f>
+        <v/>
+      </c>
+      <c r="G35" s="31">
+        <f>G30*(1-G11)</f>
+        <v/>
+      </c>
+      <c r="H35" s="31">
+        <f>H30*(1-H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="F35" s="30">
-        <f>F30*(1-F10)</f>
-        <v/>
-      </c>
-      <c r="G35" s="30">
-        <f>G30*(1-G10)</f>
-        <v/>
-      </c>
-      <c r="H35" s="30">
-        <f>H30*(1-H10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="F36" s="31">
+        <f>F31*(1-F11)</f>
+        <v/>
+      </c>
+      <c r="G36" s="31">
+        <f>G31*(1-G11)</f>
+        <v/>
+      </c>
+      <c r="H36" s="31">
+        <f>H31*(1-H11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="F36" s="30">
-        <f>F16*F11</f>
-        <v/>
-      </c>
-      <c r="G36" s="30">
-        <f>G16*G11</f>
-        <v/>
-      </c>
-      <c r="H36" s="30">
-        <f>H16*H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="F37" s="31">
+        <f>F17*F12</f>
+        <v/>
+      </c>
+      <c r="G37" s="31">
+        <f>G17*G12</f>
+        <v/>
+      </c>
+      <c r="H37" s="31">
+        <f>H17*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="F37" s="30">
-        <f>F17*F11</f>
-        <v/>
-      </c>
-      <c r="G37" s="30">
-        <f>G17*G11</f>
-        <v/>
-      </c>
-      <c r="H37" s="30">
-        <f>H17*H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="F38" s="31">
+        <f>F18*F12</f>
+        <v/>
+      </c>
+      <c r="G38" s="31">
+        <f>G18*G12</f>
+        <v/>
+      </c>
+      <c r="H38" s="31">
+        <f>H18*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="F38" s="30">
-        <f>F18*F11</f>
-        <v/>
-      </c>
-      <c r="G38" s="30">
-        <f>G18*G11</f>
-        <v/>
-      </c>
-      <c r="H38" s="30">
-        <f>H18*H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="F39" s="31">
+        <f>F19*F12</f>
+        <v/>
+      </c>
+      <c r="G39" s="31">
+        <f>G19*G12</f>
+        <v/>
+      </c>
+      <c r="H39" s="31">
+        <f>H19*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="F39" s="30">
-        <f>F19*F11</f>
-        <v/>
-      </c>
-      <c r="G39" s="30">
-        <f>G19*G11</f>
-        <v/>
-      </c>
-      <c r="H39" s="30">
-        <f>H19*H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="F40" s="31">
+        <f>F20*F12</f>
+        <v/>
+      </c>
+      <c r="G40" s="31">
+        <f>G20*G12</f>
+        <v/>
+      </c>
+      <c r="H40" s="31">
+        <f>H20*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="F40" s="30">
-        <f>F20*F11</f>
-        <v/>
-      </c>
-      <c r="G40" s="30">
-        <f>G20*G11</f>
-        <v/>
-      </c>
-      <c r="H40" s="30">
-        <f>H20*H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="F41" s="31">
+        <f>F21*F12</f>
+        <v/>
+      </c>
+      <c r="G41" s="31">
+        <f>G21*G12</f>
+        <v/>
+      </c>
+      <c r="H41" s="31">
+        <f>H21*H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="F41" s="30">
-        <f>F16*F12</f>
-        <v/>
-      </c>
-      <c r="G41" s="30">
-        <f>G16*G12</f>
-        <v/>
-      </c>
-      <c r="H41" s="30">
-        <f>H16*H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="F42" s="31">
+        <f>F17*F13</f>
+        <v/>
+      </c>
+      <c r="G42" s="31">
+        <f>G17*G13</f>
+        <v/>
+      </c>
+      <c r="H42" s="31">
+        <f>H17*H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="F42" s="30">
-        <f>F17*F12</f>
-        <v/>
-      </c>
-      <c r="G42" s="30">
-        <f>G17*G12</f>
-        <v/>
-      </c>
-      <c r="H42" s="30">
-        <f>H17*H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="F43" s="31">
+        <f>F18*F13</f>
+        <v/>
+      </c>
+      <c r="G43" s="31">
+        <f>G18*G13</f>
+        <v/>
+      </c>
+      <c r="H43" s="31">
+        <f>H18*H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="F43" s="30">
-        <f>F18*F12</f>
-        <v/>
-      </c>
-      <c r="G43" s="30">
-        <f>G18*G12</f>
-        <v/>
-      </c>
-      <c r="H43" s="30">
-        <f>H18*H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="F44" s="31">
+        <f>F19*F13</f>
+        <v/>
+      </c>
+      <c r="G44" s="31">
+        <f>G19*G13</f>
+        <v/>
+      </c>
+      <c r="H44" s="31">
+        <f>H19*H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="F44" s="30">
-        <f>F19*F12</f>
-        <v/>
-      </c>
-      <c r="G44" s="30">
-        <f>G19*G12</f>
-        <v/>
-      </c>
-      <c r="H44" s="30">
-        <f>H19*H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="F45" s="31">
+        <f>F20*F13</f>
+        <v/>
+      </c>
+      <c r="G45" s="31">
+        <f>G20*G13</f>
+        <v/>
+      </c>
+      <c r="H45" s="31">
+        <f>H20*H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="F45" s="30">
-        <f>F20*F12</f>
-        <v/>
-      </c>
-      <c r="G45" s="30">
-        <f>G20*G12</f>
-        <v/>
-      </c>
-      <c r="H45" s="30">
-        <f>H20*H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="F46" s="31">
+        <f>F21*F13</f>
+        <v/>
+      </c>
+      <c r="G46" s="31">
+        <f>G21*G13</f>
+        <v/>
+      </c>
+      <c r="H46" s="31">
+        <f>H21*H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="F46" s="30">
-        <f>F13*(F16-11102600)</f>
-        <v/>
-      </c>
-      <c r="G46" s="30">
-        <f>G13*(G16-11102600)</f>
-        <v/>
-      </c>
-      <c r="H46" s="30">
-        <f>H13*(H16-11102600)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="F47" s="31">
+        <f>F14*(F17-11102600)</f>
+        <v/>
+      </c>
+      <c r="G47" s="31">
+        <f>G14*(G17-11102600)</f>
+        <v/>
+      </c>
+      <c r="H47" s="31">
+        <f>H14*(H17-11102600)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="F47" s="30">
-        <f>F13*(F17-F16)</f>
-        <v/>
-      </c>
-      <c r="G47" s="30">
-        <f>G13*(G17-G16)</f>
-        <v/>
-      </c>
-      <c r="H47" s="30">
-        <f>H13*(H17-H16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="F48" s="31">
+        <f>F14*(F18-F17)</f>
+        <v/>
+      </c>
+      <c r="G48" s="31">
+        <f>G14*(G18-G17)</f>
+        <v/>
+      </c>
+      <c r="H48" s="31">
+        <f>H14*(H18-H17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="F48" s="30">
-        <f>F13*(F18-F17)</f>
-        <v/>
-      </c>
-      <c r="G48" s="30">
-        <f>G13*(G18-G17)</f>
-        <v/>
-      </c>
-      <c r="H48" s="30">
-        <f>H13*(H18-H17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="F49" s="31">
+        <f>F14*(F19-F18)</f>
+        <v/>
+      </c>
+      <c r="G49" s="31">
+        <f>G14*(G19-G18)</f>
+        <v/>
+      </c>
+      <c r="H49" s="31">
+        <f>H14*(H19-H18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="F49" s="30">
-        <f>F13*(F19-F18)</f>
-        <v/>
-      </c>
-      <c r="G49" s="30">
-        <f>G13*(G19-G18)</f>
-        <v/>
-      </c>
-      <c r="H49" s="30">
-        <f>H13*(H19-H18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="F50" s="31">
+        <f>F14*(F20-F19)</f>
+        <v/>
+      </c>
+      <c r="G50" s="31">
+        <f>G14*(G20-G19)</f>
+        <v/>
+      </c>
+      <c r="H50" s="31">
+        <f>H14*(H20-H19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="F50" s="30">
-        <f>F13*(F20-F19)</f>
-        <v/>
-      </c>
-      <c r="G50" s="30">
-        <f>G13*(G20-G19)</f>
-        <v/>
-      </c>
-      <c r="H50" s="30">
-        <f>H13*(H20-H19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="F51" s="31">
+        <f>F14*(F21-F20)</f>
+        <v/>
+      </c>
+      <c r="G51" s="31">
+        <f>G14*(G21-G20)</f>
+        <v/>
+      </c>
+      <c r="H51" s="31">
+        <f>H14*(H21-H20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="F51" s="30">
-        <f>F31+F36-F41-F46</f>
-        <v/>
-      </c>
-      <c r="G51" s="30">
-        <f>G31+G36-G41-G46</f>
-        <v/>
-      </c>
-      <c r="H51" s="30">
-        <f>H31+H36-H41-H46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="F52" s="31">
+        <f>F32+F37-F42-F47</f>
+        <v/>
+      </c>
+      <c r="G52" s="31">
+        <f>G32+G37-G42-G47</f>
+        <v/>
+      </c>
+      <c r="H52" s="31">
+        <f>H32+H37-H42-H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="F52" s="30">
-        <f>F32+F37-F42-F47</f>
-        <v/>
-      </c>
-      <c r="G52" s="30">
-        <f>G32+G37-G42-G47</f>
-        <v/>
-      </c>
-      <c r="H52" s="30">
-        <f>H32+H37-H42-H47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="F53" s="31">
+        <f>F33+F38-F43-F48</f>
+        <v/>
+      </c>
+      <c r="G53" s="31">
+        <f>G33+G38-G43-G48</f>
+        <v/>
+      </c>
+      <c r="H53" s="31">
+        <f>H33+H38-H43-H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="F53" s="30">
-        <f>F33+F38-F43-F48</f>
-        <v/>
-      </c>
-      <c r="G53" s="30">
-        <f>G33+G38-G43-G48</f>
-        <v/>
-      </c>
-      <c r="H53" s="30">
-        <f>H33+H38-H43-H48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="F54" s="31">
+        <f>F34+F39-F44-F49</f>
+        <v/>
+      </c>
+      <c r="G54" s="31">
+        <f>G34+G39-G44-G49</f>
+        <v/>
+      </c>
+      <c r="H54" s="31">
+        <f>H34+H39-H44-H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="F54" s="30">
-        <f>F34+F39-F44-F49</f>
-        <v/>
-      </c>
-      <c r="G54" s="30">
-        <f>G34+G39-G44-G49</f>
-        <v/>
-      </c>
-      <c r="H54" s="30">
-        <f>H34+H39-H44-H49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="F55" s="31">
+        <f>F35+F40-F45-F50</f>
+        <v/>
+      </c>
+      <c r="G55" s="31">
+        <f>G35+G40-G45-G50</f>
+        <v/>
+      </c>
+      <c r="H55" s="31">
+        <f>H35+H40-H45-H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F55" s="30">
-        <f>F35+F40-F45-F50</f>
-        <v/>
-      </c>
-      <c r="G55" s="30">
-        <f>G35+G40-G45-G50</f>
-        <v/>
-      </c>
-      <c r="H55" s="30">
-        <f>H35+H40-H45-H50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="22" t="inlineStr">
+      <c r="F56" s="31">
+        <f>F36+F41-F46-F51</f>
+        <v/>
+      </c>
+      <c r="G56" s="31">
+        <f>G36+G41-G46-G51</f>
+        <v/>
+      </c>
+      <c r="H56" s="31">
+        <f>H36+H41-H46-H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="C57" s="32">
-        <f>NPV(C8,C51,C52,C53,C54,C55)+(C55*(1+C9)/(C8-C9))/(1+C8)^5</f>
-        <v/>
-      </c>
-      <c r="D57" s="32">
-        <f>NPV(D8,D51,D52,D53,D54,D55)+(D55*(1+D9)/(D8-D9))/(1+D8)^5</f>
-        <v/>
-      </c>
-      <c r="E57" s="32">
-        <f>NPV(E8,E51,E52,E53,E54,E55)+(E55*(1+E9)/(E8-E9))/(1+E8)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="33" t="inlineStr">
+      <c r="F58" s="33">
+        <f>NPV(F9,F52,F53,F54,F55,F56)+(F56*(1+F10)/(F9-F10))/(1+F9)^5</f>
+        <v/>
+      </c>
+      <c r="G58" s="33">
+        <f>NPV(G9,G52,G53,G54,G55,G56)+(G56*(1+G10)/(G9-G10))/(1+G9)^5</f>
+        <v/>
+      </c>
+      <c r="H58" s="33">
+        <f>NPV(H9,H52,H53,H54,H55,H56)+(H56*(1+H10)/(H9-H10))/(1+H9)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="C58" s="34">
-        <f>(C57+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="D58" s="34">
-        <f>(D57+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="E58" s="34">
-        <f>(E57+1807202-0)/111380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="22" t="inlineStr">
+      <c r="F59" s="35">
+        <f>(F58+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="G59" s="36">
+        <f>(G58+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="H59" s="35">
+        <f>(H58+1807202-0)/111380</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="C59" s="35">
-        <f>C58/100.0-1</f>
-        <v/>
-      </c>
-      <c r="D59" s="35">
-        <f>D58/100.0-1</f>
-        <v/>
-      </c>
-      <c r="E59" s="35">
-        <f>E58/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="36" t="inlineStr">
+      <c r="F60" s="37">
+        <f>F59/100.0-1</f>
+        <v/>
+      </c>
+      <c r="G60" s="37">
+        <f>G59/100.0-1</f>
+        <v/>
+      </c>
+      <c r="H60" s="37">
+        <f>H59/100.0-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="38" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2590,12 +2630,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink ref="C8" location="'WACC'!E16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink ref="C9" location="'WACC'!E16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2607,7 +2648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M65"/>
+  <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2642,69 +2683,69 @@
       <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="37" t="inlineStr">
+      <c r="B2" s="39" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="C2" s="37" t="inlineStr">
+      <c r="C2" s="39" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D2" s="37" t="inlineStr">
+      <c r="D2" s="39" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E2" s="38" t="inlineStr">
+      <c r="E2" s="40" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F2" s="39" t="inlineStr">
+      <c r="F2" s="41" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G2" s="39" t="inlineStr">
+      <c r="G2" s="41" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H2" s="39" t="inlineStr">
+      <c r="H2" s="41" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I2" s="39" t="inlineStr">
+      <c r="I2" s="41" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J2" s="39" t="inlineStr">
+      <c r="J2" s="41" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="K2" s="40" t="inlineStr">
+      <c r="K2" s="42" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="L2" s="37" t="inlineStr">
+      <c r="L2" s="39" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="M2" s="37" t="inlineStr">
+      <c r="M2" s="39" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="43" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
         </is>
@@ -2714,12 +2755,12 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
-      <c r="E3" s="42" t="inlineStr">
+      <c r="E3" s="44" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="K3" s="43" t="inlineStr">
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2731,31 +2772,31 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="E5" s="44" t="n">
+      <c r="E5" s="46" t="n">
         <v>11102600</v>
       </c>
-      <c r="F5" s="45">
-        <f>Scenarios!G16</f>
-        <v/>
-      </c>
-      <c r="G5" s="45">
+      <c r="F5" s="47">
         <f>Scenarios!G17</f>
         <v/>
       </c>
-      <c r="H5" s="45">
+      <c r="G5" s="47">
         <f>Scenarios!G18</f>
         <v/>
       </c>
-      <c r="I5" s="45">
+      <c r="H5" s="47">
         <f>Scenarios!G19</f>
         <v/>
       </c>
-      <c r="J5" s="45">
+      <c r="I5" s="47">
         <f>Scenarios!G20</f>
         <v/>
       </c>
-      <c r="K5" s="46">
-        <f>IF(MAX(ABS(F5-Scenarios!$G$16),ABS(G5-Scenarios!$G$17),ABS(H5-Scenarios!$G$18),ABS(I5-Scenarios!$G$19),ABS(J5-Scenarios!$G$20))&lt;0.5,"OK","CHECK")</f>
+      <c r="J5" s="47">
+        <f>Scenarios!G21</f>
+        <v/>
+      </c>
+      <c r="K5" s="48">
+        <f>IF(MAX(ABS(F5-Scenarios!$G$17),ABS(G5-Scenarios!$G$18),ABS(H5-Scenarios!$G$19),ABS(I5-Scenarios!$G$20),ABS(J5-Scenarios!$G$21))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2771,7 +2812,7 @@
 Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
-      <c r="C6" s="47" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
 Also: StockAnalysis: LULU 3Y revenue forecast</t>
@@ -2783,23 +2824,23 @@
 Also: Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="50">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="50">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="48">
+      <c r="H6" s="50">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="48">
+      <c r="I6" s="50">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="48">
+      <c r="J6" s="50">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -2807,226 +2848,224 @@
     <row r="7" ht="54" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>EBIT (operating) margin %</t>
+          <t>Clean / run-rate EBIT margin %</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
         <is>
-          <t>FY26 13.9% is derived: Q2 OM 18.8% minus 560bps tariff refunds = 13.2% clean; we set base slightly above that run-rate.
+          <t>13.2% is the real/run-rate OM: Q2 18.8% minus 560bps of tariff refunds. FY26 then adds the $134.5M refund once on top.
 Also: FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 release: OM 18.8% less 560bps tariffs
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
 Also: FY2025 10-K: Income from operations / revenue</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>1) Ctrl+F "18.8%" = Q2 operating margin. 2) Ctrl+F "560 basis points" = tariff add. 3) Clean Q2 = 18.8% − 5.6% = 13.2%. Model FY26 base 13.9% sits just above that. Do not use "decreased 13%" — that is the YoY $ decline in income from operations.
+          <t>Ctrl+F "18.8%" (Q2 OM) and "560 basis points" (tariff boost). Real run-rate = 18.8% − 5.6% = 13.2%. Do not use "decreased 13%".
 Also: Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
         </is>
       </c>
-      <c r="F7" s="48">
-        <f>Scenarios!G21</f>
-        <v/>
-      </c>
-      <c r="G7" s="48">
+      <c r="F7" s="50">
         <f>Scenarios!G22</f>
         <v/>
       </c>
-      <c r="H7" s="48">
+      <c r="G7" s="50">
         <f>Scenarios!G23</f>
         <v/>
       </c>
-      <c r="I7" s="48">
+      <c r="H7" s="50">
         <f>Scenarios!G24</f>
         <v/>
       </c>
-      <c r="J7" s="48">
+      <c r="I7" s="50">
         <f>Scenarios!G25</f>
         <v/>
       </c>
-      <c r="K7" s="46">
-        <f>IF(MAX(ABS(F7-Scenarios!$G$21),ABS(G7-Scenarios!$G$22),ABS(H7-Scenarios!$G$23),ABS(I7-Scenarios!$G$24),ABS(J7-Scenarios!$G$25))&lt;0.0001,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="E8" s="49" t="n">
+      <c r="J7" s="50">
+        <f>Scenarios!G26</f>
+        <v/>
+      </c>
+      <c r="K7" s="48">
+        <f>IF(MAX(ABS(F7-Scenarios!$G$22),ABS(G7-Scenarios!$G$23),ABS(H7-Scenarios!$G$24),ABS(I7-Scenarios!$G$25),ABS(J7-Scenarios!$G$26))&lt;0.0001,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Plus: FY26 IEEPA tariff refunds (one-time)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Add back $134.5M in FY26 only — already recognized (reduced COGS). +130bps on FY26 sales, not +560bps (that was Q2-only).</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
+        </is>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="29">
+        <f>Scenarios!$G$7</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>EBIT (incl. FY26 refund)</t>
+        </is>
+      </c>
+      <c r="E9" s="51" t="n">
         <v>2210615</v>
       </c>
-      <c r="F8" s="32">
-        <f>Scenarios!G26</f>
-        <v/>
-      </c>
-      <c r="G8" s="32">
+      <c r="F9" s="33">
         <f>Scenarios!G27</f>
         <v/>
       </c>
-      <c r="H8" s="32">
+      <c r="G9" s="33">
         <f>Scenarios!G28</f>
         <v/>
       </c>
-      <c r="I8" s="32">
+      <c r="H9" s="33">
         <f>Scenarios!G29</f>
         <v/>
       </c>
-      <c r="J8" s="32">
+      <c r="I9" s="33">
         <f>Scenarios!G30</f>
         <v/>
       </c>
-      <c r="K8" s="50">
-        <f>IF(MAX(ABS(F8-Scenarios!$G$26),ABS(G8-Scenarios!$G$27),ABS(H8-Scenarios!$G$28),ABS(I8-Scenarios!$G$29),ABS(J8-Scenarios!$G$30))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="J9" s="33">
+        <f>Scenarios!G31</f>
+        <v/>
+      </c>
+      <c r="K9" s="52">
+        <f>IF(MAX(ABS(F9-Scenarios!$G$27),ABS(G9-Scenarios!$G$28),ABS(H9-Scenarios!$G$29),ABS(I9-Scenarios!$G$30),ABS(J9-Scenarios!$G$31))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Reported EBIT margin % (incl. FY26 refund)</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="n">
+        <v>0.1991078666258354</v>
+      </c>
+      <c r="F10" s="50">
+        <f>F9/F5</f>
+        <v/>
+      </c>
+      <c r="G10" s="50">
+        <f>G9/G5</f>
+        <v/>
+      </c>
+      <c r="H10" s="50">
+        <f>H9/H5</f>
+        <v/>
+      </c>
+      <c r="I10" s="50">
+        <f>I9/I5</f>
+        <v/>
+      </c>
+      <c r="J10" s="50">
+        <f>J9/J5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="F9" s="45">
-        <f>-Scenarios!G26*Scenarios!$G$10</f>
-        <v/>
-      </c>
-      <c r="G9" s="45">
-        <f>-Scenarios!G27*Scenarios!$G$10</f>
-        <v/>
-      </c>
-      <c r="H9" s="45">
-        <f>-Scenarios!G28*Scenarios!$G$10</f>
-        <v/>
-      </c>
-      <c r="I9" s="45">
-        <f>-Scenarios!G29*Scenarios!$G$10</f>
-        <v/>
-      </c>
-      <c r="J9" s="45">
-        <f>-Scenarios!G30*Scenarios!$G$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="F11" s="47">
+        <f>-Scenarios!G27*Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="G11" s="47">
+        <f>-Scenarios!G28*Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="H11" s="47">
+        <f>-Scenarios!G29*Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="I11" s="47">
+        <f>-Scenarios!G30*Scenarios!$G$11</f>
+        <v/>
+      </c>
+      <c r="J11" s="47">
+        <f>-Scenarios!G31*Scenarios!$G$11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F10" s="32">
-        <f>Scenarios!G31</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
+      <c r="F12" s="33">
         <f>Scenarios!G32</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="G12" s="33">
         <f>Scenarios!G33</f>
         <v/>
       </c>
-      <c r="I10" s="32">
+      <c r="H12" s="33">
         <f>Scenarios!G34</f>
         <v/>
       </c>
-      <c r="J10" s="32">
+      <c r="I12" s="33">
         <f>Scenarios!G35</f>
         <v/>
       </c>
-      <c r="K10" s="50">
-        <f>IF(MAX(ABS(F10-Scenarios!$G$31),ABS(G10-Scenarios!$G$32),ABS(H10-Scenarios!$G$33),ABS(I10-Scenarios!$G$34),ABS(J10-Scenarios!$G$35))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
-        </is>
-      </c>
-      <c r="F11" s="20">
-        <f>Scenarios!$G$11</f>
-        <v/>
-      </c>
-      <c r="G11" s="20">
-        <f>Scenarios!$G$11</f>
-        <v/>
-      </c>
-      <c r="H11" s="20">
-        <f>Scenarios!$G$11</f>
-        <v/>
-      </c>
-      <c r="I11" s="20">
-        <f>Scenarios!$G$11</f>
-        <v/>
-      </c>
-      <c r="J11" s="20">
-        <f>Scenarios!$G$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Plus: depreciation &amp; amortization</t>
-        </is>
-      </c>
-      <c r="F12" s="45">
+      <c r="J12" s="33">
         <f>Scenarios!G36</f>
         <v/>
       </c>
-      <c r="G12" s="45">
-        <f>Scenarios!G37</f>
-        <v/>
-      </c>
-      <c r="H12" s="45">
-        <f>Scenarios!G38</f>
-        <v/>
-      </c>
-      <c r="I12" s="45">
-        <f>Scenarios!G39</f>
-        <v/>
-      </c>
-      <c r="J12" s="45">
-        <f>Scenarios!G40</f>
-        <v/>
-      </c>
-      <c r="K12" s="46">
-        <f>IF(MAX(ABS(F12-Scenarios!$G$36),ABS(G12-Scenarios!$G$37),ABS(H12-Scenarios!$G$38),ABS(I12-Scenarios!$G$39),ABS(J12-Scenarios!$G$40))&lt;0.5,"OK","CHECK")</f>
+      <c r="K12" s="52">
+        <f>IF(MAX(ABS(F12-Scenarios!$G$32),ABS(G12-Scenarios!$G$33),ABS(H12-Scenarios!$G$34),ABS(I12-Scenarios!$G$35),ABS(J12-Scenarios!$G$36))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex % of revenue</t>
+          <t xml:space="preserve">  D&amp;A % of revenue</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
+          <t>4.5% D&amp;A / sales = FY25 496,228 / 11,102,600 on the 10-K cash-flow statement.</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -3036,7 +3075,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
+          <t>Ctrl+F "Depreciation and amortization" → 496,228 on this 10-K HTML (not the SEC viewer). ÷ "Net revenue" 11,102,600 = 4.5%.</t>
         </is>
       </c>
       <c r="F13" s="20">
@@ -3063,53 +3102,53 @@
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>Less: capital expenditures</t>
-        </is>
-      </c>
-      <c r="F14" s="45">
-        <f>-Scenarios!G41</f>
-        <v/>
-      </c>
-      <c r="G14" s="45">
-        <f>-Scenarios!G42</f>
-        <v/>
-      </c>
-      <c r="H14" s="45">
-        <f>-Scenarios!G43</f>
-        <v/>
-      </c>
-      <c r="I14" s="45">
-        <f>-Scenarios!G44</f>
-        <v/>
-      </c>
-      <c r="J14" s="45">
-        <f>-Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="K14" s="46">
-        <f>IF(MAX(ABS(F14+Scenarios!$G$41),ABS(G14+Scenarios!$G$42),ABS(H14+Scenarios!$G$43),ABS(I14+Scenarios!$G$44),ABS(J14+Scenarios!$G$45))&lt;0.5,"OK","CHECK")</f>
+          <t>Plus: depreciation &amp; amortization</t>
+        </is>
+      </c>
+      <c r="F14" s="47">
+        <f>Scenarios!G37</f>
+        <v/>
+      </c>
+      <c r="G14" s="47">
+        <f>Scenarios!G38</f>
+        <v/>
+      </c>
+      <c r="H14" s="47">
+        <f>Scenarios!G39</f>
+        <v/>
+      </c>
+      <c r="I14" s="47">
+        <f>Scenarios!G40</f>
+        <v/>
+      </c>
+      <c r="J14" s="47">
+        <f>Scenarios!G41</f>
+        <v/>
+      </c>
+      <c r="K14" s="48">
+        <f>IF(MAX(ABS(F14-Scenarios!$G$37),ABS(G14-Scenarios!$G$38),ABS(H14-Scenarios!$G$39),ABS(I14-Scenarios!$G$40),ABS(J14-Scenarios!$G$41))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NWC build % of Δrevenue</t>
+          <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)</t>
+          <t>LULU CF statement (10-K)</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
+          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
         </is>
       </c>
       <c r="F15" s="20">
@@ -3136,854 +3175,927 @@
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
+          <t>Less: capital expenditures</t>
+        </is>
+      </c>
+      <c r="F16" s="47">
+        <f>-Scenarios!G42</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>-Scenarios!G43</f>
+        <v/>
+      </c>
+      <c r="H16" s="47">
+        <f>-Scenarios!G44</f>
+        <v/>
+      </c>
+      <c r="I16" s="47">
+        <f>-Scenarios!G45</f>
+        <v/>
+      </c>
+      <c r="J16" s="47">
+        <f>-Scenarios!G46</f>
+        <v/>
+      </c>
+      <c r="K16" s="48">
+        <f>IF(MAX(ABS(F16+Scenarios!$G$42),ABS(G16+Scenarios!$G$43),ABS(H16+Scenarios!$G$44),ABS(I16+Scenarios!$G$45),ABS(J16+Scenarios!$G$46))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NWC build % of Δrevenue</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
+        </is>
+      </c>
+      <c r="F17" s="20">
+        <f>Scenarios!$G$14</f>
+        <v/>
+      </c>
+      <c r="G17" s="20">
+        <f>Scenarios!$G$14</f>
+        <v/>
+      </c>
+      <c r="H17" s="20">
+        <f>Scenarios!$G$14</f>
+        <v/>
+      </c>
+      <c r="I17" s="20">
+        <f>Scenarios!$G$14</f>
+        <v/>
+      </c>
+      <c r="J17" s="20">
+        <f>Scenarios!$G$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="F16" s="45">
-        <f>-Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="G16" s="45">
+      <c r="F18" s="47">
         <f>-Scenarios!G47</f>
         <v/>
       </c>
-      <c r="H16" s="45">
+      <c r="G18" s="47">
         <f>-Scenarios!G48</f>
         <v/>
       </c>
-      <c r="I16" s="45">
+      <c r="H18" s="47">
         <f>-Scenarios!G49</f>
         <v/>
       </c>
-      <c r="J16" s="45">
+      <c r="I18" s="47">
         <f>-Scenarios!G50</f>
         <v/>
       </c>
-      <c r="K16" s="46">
-        <f>IF(MAX(ABS(F16+Scenarios!$G$46),ABS(G16+Scenarios!$G$47),ABS(H16+Scenarios!$G$48),ABS(I16+Scenarios!$G$49),ABS(J16+Scenarios!$G$50))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="36" t="inlineStr">
+      <c r="J18" s="47">
+        <f>-Scenarios!G51</f>
+        <v/>
+      </c>
+      <c r="K18" s="48">
+        <f>IF(MAX(ABS(F18+Scenarios!$G$47),ABS(G18+Scenarios!$G$48),ABS(H18+Scenarios!$G$49),ABS(I18+Scenarios!$G$50),ABS(J18+Scenarios!$G$51))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F18" s="51">
-        <f>Scenarios!G51</f>
-        <v/>
-      </c>
-      <c r="G18" s="51">
+      <c r="F20" s="54">
         <f>Scenarios!G52</f>
         <v/>
       </c>
-      <c r="H18" s="51">
+      <c r="G20" s="54">
         <f>Scenarios!G53</f>
         <v/>
       </c>
-      <c r="I18" s="51">
+      <c r="H20" s="54">
         <f>Scenarios!G54</f>
         <v/>
       </c>
-      <c r="J18" s="51">
+      <c r="I20" s="54">
         <f>Scenarios!G55</f>
         <v/>
       </c>
-      <c r="K18" s="50">
-        <f>IF(MAX(ABS(F18-Scenarios!$G$51),ABS(G18-Scenarios!$G$52),ABS(H18-Scenarios!$G$53),ABS(I18-Scenarios!$G$54),ABS(J18-Scenarios!$G$55))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="J20" s="54">
+        <f>Scenarios!G56</f>
+        <v/>
+      </c>
+      <c r="K20" s="52">
+        <f>IF(MAX(ABS(F20-Scenarios!$G$52),ABS(G20-Scenarios!$G$53),ABS(H20-Scenarios!$G$54),ABS(I20-Scenarios!$G$55),ABS(J20-Scenarios!$G$56))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F21" s="55" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="52" t="n">
+      <c r="G21" s="55" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="52" t="n">
+      <c r="H21" s="55" t="n">
         <v>3</v>
       </c>
-      <c r="I19" s="52" t="n">
+      <c r="I21" s="55" t="n">
         <v>4</v>
       </c>
-      <c r="J19" s="52" t="n">
+      <c r="J21" s="55" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="F20" s="53">
-        <f>1/(1+Scenarios!$G$8)^F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="53">
-        <f>1/(1+Scenarios!$G$8)^G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="53">
-        <f>1/(1+Scenarios!$G$8)^H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="53">
-        <f>1/(1+Scenarios!$G$8)^I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="53">
-        <f>1/(1+Scenarios!$G$8)^J19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22" t="inlineStr">
+      <c r="F22" s="56">
+        <f>1/(1+Scenarios!$G$9)^F21</f>
+        <v/>
+      </c>
+      <c r="G22" s="56">
+        <f>1/(1+Scenarios!$G$9)^G21</f>
+        <v/>
+      </c>
+      <c r="H22" s="56">
+        <f>1/(1+Scenarios!$G$9)^H21</f>
+        <v/>
+      </c>
+      <c r="I22" s="56">
+        <f>1/(1+Scenarios!$G$9)^I21</f>
+        <v/>
+      </c>
+      <c r="J22" s="56">
+        <f>1/(1+Scenarios!$G$9)^J21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="F21" s="32">
-        <f>F18*F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="32">
-        <f>G18*G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="32">
-        <f>H18*H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="32">
-        <f>I18*I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="32">
-        <f>J18*J20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="F23" s="33">
+        <f>F20*F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>G20*G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="33">
+        <f>H20*H22</f>
+        <v/>
+      </c>
+      <c r="I23" s="33">
+        <f>I20*I22</f>
+        <v/>
+      </c>
+      <c r="J23" s="33">
+        <f>J20*J22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>Scenarios linkage summary (column K should all read OK)</t>
         </is>
       </c>
-      <c r="K23" s="54">
-        <f>IF(COUNTIF(K5:K18,"CHECK")=0,"ALL OK","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="K25" s="57">
+        <f>IF(COUNTIF(K5:K20,"CHECK")=0,"ALL OK","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
-        <is>
-          <t>Sum of PV of explicit FCF (FY26–FY30)</t>
-        </is>
-      </c>
-      <c r="E25" s="56">
-        <f>SUM(F21:J21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Terminal growth rate (g)</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
-        </is>
-      </c>
-      <c r="E26" s="48">
-        <f>Scenarios!$G$9</f>
-        <v/>
-      </c>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
+          <t>Sum of PV of explicit FCF (FY26–FY30)</t>
+        </is>
+      </c>
+      <c r="E27" s="59">
+        <f>SUM(F23:J23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Terminal growth rate (g)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
+        </is>
+      </c>
+      <c r="E28" s="50">
+        <f>Scenarios!$G$10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E27" s="32">
-        <f>J8+J12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="E29" s="33">
+        <f>J9+J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="E28" s="45">
-        <f>J18*(1+Scenarios!$G$9)/(Scenarios!$G$8-Scenarios!$G$9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="E30" s="47">
+        <f>J20*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="E29" s="57">
-        <f>E28/E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="22" t="inlineStr">
+      <c r="E31" s="60">
+        <f>E30/E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E30" s="56">
-        <f>E28/(1+Scenarios!$G$8)^J19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="E32" s="59">
+        <f>E30/(1+Scenarios!$G$9)^J21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E31" s="32">
-        <f>E25+E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="E33" s="33">
+        <f>E27+E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C32" s="58" t="inlineStr">
+      <c r="C34" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="D32" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E32" s="44" t="n">
+      <c r="E34" s="46" t="n">
         <v>1807202</v>
-      </c>
-    </row>
-    <row r="33" ht="36" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Less: total debt</t>
-        </is>
-      </c>
-      <c r="C33" s="58" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
-        </is>
-      </c>
-      <c r="E33" s="44" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="E34" s="32">
-        <f>E31+E32+E33</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding (000)</t>
-        </is>
-      </c>
-      <c r="C35" s="58" t="inlineStr">
+          <t>Less: total debt</t>
+        </is>
+      </c>
+      <c r="C35" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
-        </is>
-      </c>
-      <c r="E35" s="44" t="n">
-        <v>111380</v>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
+        </is>
+      </c>
+      <c r="E35" s="46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>Implied value per share</t>
-        </is>
-      </c>
-      <c r="E36" s="59">
-        <f>E34/E35</f>
-        <v/>
-      </c>
-      <c r="K36" s="50">
-        <f>IF(ABS(E36-Scenarios!$G$58)&lt;0.05,"OK","CHECK")</f>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="E36" s="33">
+        <f>E33+E34+E35</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Current share price</t>
-        </is>
-      </c>
-      <c r="C37" s="58" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
+          <t>Diluted shares outstanding (000)</t>
+        </is>
+      </c>
+      <c r="C37" s="61" t="inlineStr">
+        <is>
+          <t>10-K</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
-        </is>
-      </c>
-      <c r="E37" s="60" t="n">
-        <v>100</v>
+          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
+        </is>
+      </c>
+      <c r="E37" s="46" t="n">
+        <v>111380</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
+          <t>Implied value per share</t>
+        </is>
+      </c>
+      <c r="E38" s="62">
+        <f>E36/E37</f>
+        <v/>
+      </c>
+      <c r="K38" s="52">
+        <f>IF(ABS(E38-Scenarios!$G$59)&lt;0.05,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="C39" s="61" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
+        </is>
+      </c>
+      <c r="E39" s="63" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="E38" s="61">
-        <f>E36/E37-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="E40" s="64">
+        <f>E38/E39-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="E39" s="48">
-        <f>E30/E31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="E41" s="50">
+        <f>E32/E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="58" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="B43" s="13" t="n"/>
+      <c r="C43" s="13" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="36" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B45" s="17" t="inlineStr">
         <is>
           <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C45" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
-      <c r="D43" s="19" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E43" s="62" t="n">
+      <c r="E45" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="M43" s="58" t="inlineStr">
+      <c r="M45" s="61" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="E44" s="45">
-        <f>E27*E43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="E46" s="47">
+        <f>E29*E45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E45" s="45">
-        <f>E44/(1+Scenarios!$G$8)^J19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="22" t="inlineStr">
+      <c r="E47" s="47">
+        <f>E46/(1+Scenarios!$G$9)^J21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E46" s="32">
-        <f>E25+E45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="22" t="inlineStr">
+      <c r="E48" s="33">
+        <f>E27+E47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="E47" s="63">
-        <f>(E46+E32+E33)/E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="E49" s="66">
+        <f>(E48+E34+E35)/E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="58" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n"/>
-      <c r="C49" s="13" t="n"/>
-      <c r="D49" s="13" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="64" t="inlineStr"/>
-      <c r="B50" s="65" t="inlineStr">
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="67" t="inlineStr"/>
+      <c r="B52" s="68" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C50" s="65" t="inlineStr">
+      <c r="C52" s="68" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D50" s="65" t="inlineStr">
+      <c r="D52" s="68" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B51" s="56">
-        <f>E28</f>
-        <v/>
-      </c>
-      <c r="C51" s="56">
-        <f>E44</f>
-        <v/>
-      </c>
-      <c r="D51" s="56">
-        <f>B51-C51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Exit EV/EBITDA (implied vs selected)</t>
-        </is>
-      </c>
-      <c r="B52" s="66">
-        <f>E29</f>
-        <v/>
-      </c>
-      <c r="C52" s="66">
-        <f>E43</f>
-        <v/>
-      </c>
-      <c r="D52" s="66">
-        <f>B52-C52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value variance (%)</t>
-        </is>
-      </c>
-      <c r="B53" s="48" t="inlineStr"/>
-      <c r="C53" s="48" t="inlineStr"/>
-      <c r="D53" s="48">
-        <f>(B51-C51)/B51</f>
+      <c r="B53" s="59">
+        <f>E30</f>
+        <v/>
+      </c>
+      <c r="C53" s="59">
+        <f>E46</f>
+        <v/>
+      </c>
+      <c r="D53" s="59">
+        <f>B53-C53</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
+          <t>Exit EV/EBITDA (implied vs selected)</t>
+        </is>
+      </c>
+      <c r="B54" s="69">
+        <f>E31</f>
+        <v/>
+      </c>
+      <c r="C54" s="69">
+        <f>E45</f>
+        <v/>
+      </c>
+      <c r="D54" s="69">
+        <f>B54-C54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Terminal value variance (%)</t>
+        </is>
+      </c>
+      <c r="B55" s="50" t="inlineStr"/>
+      <c r="C55" s="50" t="inlineStr"/>
+      <c r="D55" s="50">
+        <f>(B53-C53)/B53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B54" s="67">
-        <f>E36</f>
-        <v/>
-      </c>
-      <c r="C54" s="67">
-        <f>E47</f>
-        <v/>
-      </c>
-      <c r="D54" s="67">
-        <f>B54-C54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="68" t="inlineStr">
+      <c r="B56" s="70">
+        <f>E38</f>
+        <v/>
+      </c>
+      <c r="C56" s="70">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="D56" s="70">
+        <f>B56-C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="71" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B55" s="69">
-        <f>IF(ABS(D52)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C55" s="70">
-        <f>TEXT(D52,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D55" s="36" t="inlineStr">
+      <c r="B57" s="72">
+        <f>IF(ABS(D54)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C57" s="73">
+        <f>TEXT(D54,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D57" s="38" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="55" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="58" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n"/>
-      <c r="C58" s="13" t="n"/>
-      <c r="D58" s="13" t="n"/>
-      <c r="E58" s="13" t="n"/>
-      <c r="F58" s="13" t="n"/>
-      <c r="G58" s="13" t="n"/>
-      <c r="H58" s="13" t="n"/>
-    </row>
-    <row r="59" ht="36" customHeight="1">
-      <c r="A59" s="71" t="inlineStr">
+      <c r="B60" s="13" t="n"/>
+      <c r="C60" s="13" t="n"/>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="13" t="n"/>
+      <c r="G60" s="13" t="n"/>
+      <c r="H60" s="13" t="n"/>
+    </row>
+    <row r="61" ht="36" customHeight="1">
+      <c r="A61" s="74" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C61" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="D59" s="19" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
-      <c r="F59" s="72" t="n">
+      <c r="F61" s="75" t="n">
         <v>0.015</v>
       </c>
-      <c r="G59" s="72" t="n">
+      <c r="G61" s="75" t="n">
         <v>0.02</v>
       </c>
-      <c r="H59" s="72" t="n">
+      <c r="H61" s="75" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I59" s="72" t="n">
+      <c r="I61" s="75" t="n">
         <v>0.025</v>
       </c>
-      <c r="J59" s="72" t="n">
+      <c r="J61" s="75" t="n">
         <v>0.03</v>
       </c>
-      <c r="L59" s="58" t="inlineStr">
+      <c r="L61" s="61" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="36" customHeight="1">
-      <c r="A60" s="72" t="n">
+    <row r="62" ht="36" customHeight="1">
+      <c r="A62" s="75" t="n">
         <v>0.095</v>
       </c>
-      <c r="C60" s="58" t="inlineStr">
+      <c r="C62" s="61" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
-      <c r="D60" s="19" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F60" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="G60" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="H60" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="I60" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="J60" s="73">
-        <f>(NPV(0.095,F18:J18)+(J18*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="L60" s="58" t="inlineStr">
+      <c r="F62" s="76">
+        <f>(NPV(0.095,F20:J20)+(J20*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="G62" s="76">
+        <f>(NPV(0.095,F20:J20)+(J20*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="H62" s="76">
+        <f>(NPV(0.095,F20:J20)+(J20*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="I62" s="76">
+        <f>(NPV(0.095,F20:J20)+(J20*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="J62" s="76">
+        <f>(NPV(0.095,F20:J20)+(J20*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="L62" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="36" customHeight="1">
-      <c r="A61" s="72" t="n">
+    <row r="63" ht="36" customHeight="1">
+      <c r="A63" s="75" t="n">
         <v>0.1</v>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D63" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F61" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="G61" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="H61" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="I61" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="J61" s="73">
-        <f>(NPV(0.1,F18:J18)+(J18*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="L61" s="58" t="inlineStr">
+      <c r="F63" s="76">
+        <f>(NPV(0.1,F20:J20)+(J20*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="G63" s="76">
+        <f>(NPV(0.1,F20:J20)+(J20*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="H63" s="76">
+        <f>(NPV(0.1,F20:J20)+(J20*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="I63" s="76">
+        <f>(NPV(0.1,F20:J20)+(J20*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="J63" s="76">
+        <f>(NPV(0.1,F20:J20)+(J20*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="L63" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="36" customHeight="1">
-      <c r="A62" s="72" t="n">
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="75" t="n">
         <v>0.105</v>
       </c>
-      <c r="D62" s="19" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F62" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="G62" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="H62" s="74">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="I62" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="J62" s="73">
-        <f>(NPV(0.105,F18:J18)+(J18*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="L62" s="58" t="inlineStr">
+      <c r="F64" s="76">
+        <f>(NPV(0.105,F20:J20)+(J20*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="G64" s="76">
+        <f>(NPV(0.105,F20:J20)+(J20*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="H64" s="77">
+        <f>(NPV(0.105,F20:J20)+(J20*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="I64" s="76">
+        <f>(NPV(0.105,F20:J20)+(J20*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="J64" s="76">
+        <f>(NPV(0.105,F20:J20)+(J20*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="L64" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="36" customHeight="1">
-      <c r="A63" s="72" t="n">
+    <row r="65" ht="36" customHeight="1">
+      <c r="A65" s="75" t="n">
         <v>0.11</v>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F63" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="G63" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="H63" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="I63" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="J63" s="73">
-        <f>(NPV(0.11,F18:J18)+(J18*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="L63" s="58" t="inlineStr">
+      <c r="F65" s="76">
+        <f>(NPV(0.11,F20:J20)+(J20*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="G65" s="76">
+        <f>(NPV(0.11,F20:J20)+(J20*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="H65" s="76">
+        <f>(NPV(0.11,F20:J20)+(J20*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="I65" s="76">
+        <f>(NPV(0.11,F20:J20)+(J20*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="J65" s="76">
+        <f>(NPV(0.11,F20:J20)+(J20*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="L65" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="36" customHeight="1">
-      <c r="A64" s="72" t="n">
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="75" t="n">
         <v>0.115</v>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F64" s="73">
-        <f>(NPV(0.115,F18:J18)+(J18*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="G64" s="73">
-        <f>(NPV(0.115,F18:J18)+(J18*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="H64" s="73">
-        <f>(NPV(0.115,F18:J18)+(J18*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="I64" s="73">
-        <f>(NPV(0.115,F18:J18)+(J18*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="J64" s="73">
-        <f>(NPV(0.115,F18:J18)+(J18*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E32+E33)/E35</f>
-        <v/>
-      </c>
-      <c r="L64" s="58" t="inlineStr">
+      <c r="F66" s="76">
+        <f>(NPV(0.115,F20:J20)+(J20*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="G66" s="76">
+        <f>(NPV(0.115,F20:J20)+(J20*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="H66" s="76">
+        <f>(NPV(0.115,F20:J20)+(J20*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="I66" s="76">
+        <f>(NPV(0.115,F20:J20)+(J20*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="J66" s="76">
+        <f>(NPV(0.115,F20:J20)+(J20*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E34+E35)/E37</f>
+        <v/>
+      </c>
+      <c r="L66" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1">
-      <c r="B65" s="17" t="inlineStr">
+    <row r="67" ht="36" customHeight="1">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C67" s="18" t="inlineStr">
         <is>
           <t>Scenarios: WACC &amp; terminal g</t>
         </is>
       </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
-      <c r="L65" s="58" t="inlineStr">
+      <c r="L67" s="61" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="M65" s="19" t="inlineStr">
+      <c r="M67" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
@@ -3995,31 +4107,34 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId18"/>
-    <hyperlink ref="M43" location="'Comps'!A26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId19"/>
-    <hyperlink ref="L59" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C60" r:id="rId20"/>
-    <hyperlink ref="L60" location="'WACC'!E16"/>
-    <hyperlink ref="L61" location="'WACC'!E16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId21"/>
+    <hyperlink ref="M45" location="'Comps'!A26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId22"/>
+    <hyperlink ref="L61" location="'Scenarios'!G10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId23"/>
     <hyperlink ref="L62" location="'WACC'!E16"/>
     <hyperlink ref="L63" location="'WACC'!E16"/>
     <hyperlink ref="L64" location="'WACC'!E16"/>
-    <hyperlink ref="C65" location="'Scenarios'!G8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId21"/>
+    <hyperlink ref="L65" location="'WACC'!E16"/>
+    <hyperlink ref="L66" location="'WACC'!E16"/>
+    <hyperlink ref="C67" location="'Scenarios'!G9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4088,7 +4203,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="58" t="inlineStr">
+      <c r="C4" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4098,7 +4213,7 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 ($000) in FY2025 column</t>
         </is>
       </c>
-      <c r="E4" s="44" t="n">
+      <c r="E4" s="46" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -4108,7 +4223,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E5" s="45">
+      <c r="E5" s="47">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -4119,13 +4234,13 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="58" t="inlineStr">
+      <c r="C6" s="61" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
       </c>
-      <c r="E6" s="45">
-        <f>DCF!E27</f>
+      <c r="E6" s="47">
+        <f>DCF!E29</f>
         <v/>
       </c>
     </row>
@@ -4135,7 +4250,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="58" t="inlineStr">
+      <c r="C7" s="61" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -4145,7 +4260,7 @@
           <t>Ctrl+F "$9.48 to $9.73" → FY2026 diluted EPS guidance; model midpoint $9.61</t>
         </is>
       </c>
-      <c r="E7" s="60" t="n">
+      <c r="E7" s="63" t="n">
         <v>9.609999999999999</v>
       </c>
     </row>
@@ -4155,7 +4270,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="58" t="inlineStr">
+      <c r="C8" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4165,7 +4280,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="46" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -4175,7 +4290,7 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4185,7 +4300,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="46" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -4195,7 +4310,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="58" t="inlineStr">
+      <c r="C10" s="61" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -4205,28 +4320,28 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E10" s="60" t="n">
+      <c r="E10" s="63" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="70" t="inlineStr">
+      <c r="A11" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="78">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="70" t="inlineStr">
+      <c r="A12" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="78">
         <f>E10/E7</f>
         <v/>
       </c>
@@ -4239,34 +4354,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="70" t="inlineStr">
+      <c r="A15" s="73" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="76" t="inlineStr">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="76" t="inlineStr">
+      <c r="B16" s="79" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C16" s="76" t="inlineStr">
+      <c r="C16" s="79" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D16" s="76" t="inlineStr">
+      <c r="D16" s="79" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E16" s="77" t="inlineStr">
+      <c r="E16" s="80" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
@@ -4278,12 +4393,12 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="C17" s="58" t="inlineStr">
+      <c r="C17" s="61" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
@@ -4293,7 +4408,7 @@
           <t>Ctrl+F "Income from operations" → 2,210,615 + "Depreciation and amortization" → 496,228</t>
         </is>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="81">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
@@ -4319,7 +4434,7 @@
           <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
         </is>
       </c>
-      <c r="E18" s="79" t="n">
+      <c r="E18" s="82" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4344,7 +4459,7 @@
           <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
         </is>
       </c>
-      <c r="E19" s="79" t="n">
+      <c r="E19" s="82" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4369,7 +4484,7 @@
           <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
         </is>
       </c>
-      <c r="E20" s="79" t="n">
+      <c r="E20" s="82" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4394,7 +4509,7 @@
           <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
         </is>
       </c>
-      <c r="E21" s="79" t="n">
+      <c r="E21" s="82" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -4419,7 +4534,7 @@
           <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
         </is>
       </c>
-      <c r="E22" s="79" t="n">
+      <c r="E22" s="82" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -4436,19 +4551,19 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="E25" s="57">
-        <f>DCF!E29</f>
+      <c r="E25" s="60">
+        <f>DCF!E31</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="68" t="inlineStr">
+      <c r="A26" s="71" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="E26" s="66">
-        <f>DCF!E43</f>
+      <c r="E26" s="69">
+        <f>DCF!E45</f>
         <v/>
       </c>
     </row>
@@ -4458,48 +4573,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E27" s="57">
+      <c r="E27" s="60">
         <f>E26-E25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="68" t="inlineStr">
+      <c r="A28" s="71" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4513,42 +4628,42 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="76" t="inlineStr">
+      <c r="A36" s="79" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B36" s="76" t="inlineStr">
+      <c r="B36" s="79" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C36" s="76" t="inlineStr">
+      <c r="C36" s="79" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D36" s="76" t="inlineStr">
+      <c r="D36" s="79" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E36" s="77" t="inlineStr">
+      <c r="E36" s="80" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F36" s="77" t="inlineStr">
+      <c r="F36" s="80" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G36" s="77" t="inlineStr">
+      <c r="G36" s="80" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H36" s="77" t="inlineStr">
+      <c r="H36" s="80" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -4566,7 +4681,7 @@
 Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
-      <c r="C37" s="80" t="inlineStr">
+      <c r="C37" s="83" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: LULU valuation</t>
@@ -4578,23 +4693,23 @@
 Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
-      <c r="E37" s="79" t="n">
+      <c r="E37" s="82" t="n">
         <v>6.5</v>
       </c>
-      <c r="F37" s="79" t="n">
+      <c r="F37" s="82" t="n">
         <v>9.5</v>
       </c>
-      <c r="G37" s="81">
+      <c r="G37" s="84">
         <f>(E6*E37+E8)/E9</f>
         <v/>
       </c>
-      <c r="H37" s="81">
+      <c r="H37" s="84">
         <f>(E6*F37+E8)/E9</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
-      <c r="A38" s="68" t="inlineStr">
+      <c r="A38" s="71" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
@@ -4614,11 +4729,11 @@
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E38" s="82">
-        <f>DCF!E43</f>
-        <v/>
-      </c>
-      <c r="G38" s="83">
+      <c r="E38" s="85">
+        <f>DCF!E45</f>
+        <v/>
+      </c>
+      <c r="G38" s="86">
         <f>(E6*E38+E8)/E9</f>
         <v/>
       </c>
@@ -4635,7 +4750,7 @@
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C39" s="80" t="inlineStr">
+      <c r="C39" s="83" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
@@ -4647,17 +4762,17 @@
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E39" s="79" t="n">
+      <c r="E39" s="82" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="79" t="n">
+      <c r="F39" s="82" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="81">
+      <c r="G39" s="84">
         <f>E7*E39</f>
         <v/>
       </c>
-      <c r="H39" s="81">
+      <c r="H39" s="84">
         <f>E7*F39</f>
         <v/>
       </c>
@@ -4668,32 +4783,32 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E40" s="84" t="inlineStr">
+      <c r="E40" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="84" t="inlineStr">
+      <c r="F40" s="87" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="81">
-        <f>Scenarios!F58</f>
-        <v/>
-      </c>
-      <c r="H40" s="81">
-        <f>Scenarios!H58</f>
+      <c r="G40" s="84">
+        <f>Scenarios!F59</f>
+        <v/>
+      </c>
+      <c r="H40" s="84">
+        <f>Scenarios!H59</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="36" customHeight="1">
-      <c r="A42" s="85" t="inlineStr">
+      <c r="A42" s="88" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="58" t="inlineStr">
+      <c r="C42" s="61" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -4703,12 +4818,12 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E42" s="86" t="n">
+      <c r="E42" s="89" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="36" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>
@@ -4718,7 +4833,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink ref="C6" location="'DCF'!E27"/>
+    <hyperlink ref="C6" location="'DCF'!E29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
@@ -4734,7 +4849,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
-    <hyperlink ref="C38" location="'DCF'!E43"/>
+    <hyperlink ref="C38" location="'DCF'!E45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId20"/>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1584,17 +1584,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
+          <t>FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>FY2025 10-K: Income from operations / revenue</t>
+          <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
+          <t>Ctrl+F "19.9%" (one hit) → Operating margin decreased 380 basis points to 19.9%. That is FY25 OM. Do not search the words Income from operations (17 hits). Model FY30 15.5% is a partial-recovery assumption.</t>
         </is>
       </c>
       <c r="F8" s="20" t="n">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
+          <t>5.5% = (7.0+6.0+5.5+5.0+4.0)/5. Year 1 is the $735M guide (7.0% of FY26 sales); then fade toward the 4.5% D&amp;A floor.</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
+          <t>Ctrl+F "$725.0 million and $745.0 million" → 2026 guide (one sentence). Mid $735M ÷ FY26 sales $10,425M = 7.0%. Ctrl+F "680,802" (one hit) → FY25 PP&amp;E spend; 680,802 ÷ 11,102,600 = 6.1%. Ctrl+F "496,228" → D&amp;A 4.5% (maintenance floor). DCF 5.5% is the 5-yr average of the fade 7.0 → 4.0: (7.0+6.0+5.5+5.0+4.0)/5 = 5.5%. We do not run the 7% build-year rate for all five years.</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -2854,19 +2854,19 @@
       <c r="B7" s="19" t="inlineStr">
         <is>
           <t>13.2% is the real/run-rate OM: Q2 18.8% minus 560bps of tariff refunds. FY26 then adds the $134.5M refund once on top.
-Also: FY30 15.5% is a recovery assumption vs FY25 10-K OM 19.9% (2,210,615 / 11,102,600); still well below FY24 peak ~23.7%.</t>
+Also: FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
       <c r="C7" s="49" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
-Also: FY2025 10-K: Income from operations / revenue</t>
+Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "18.8%" (Q2 OM) and "560 basis points" (tariff boost). Real run-rate = 18.8% − 5.6% = 13.2%. Do not use "decreased 13%".
-Also: Ctrl+F "Income from operations" → 2,210,615 and "Net revenue" → 11,102,600. FY25 OM = 19.9%. Model FY30 15.5% is a partial-recovery assumption, not a reported figure.</t>
+Also: Ctrl+F "19.9%" (one hit) → Operating margin decreased 380 basis points to 19.9%. That is FY25 OM. Do not search the words Income from operations (17 hits). Model FY30 15.5% is a partial-recovery assumption.</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>5.5% is a 5-year blend: 2026 10-K guide $725–745M (~7.0% of FY26 sales) fading toward 5.0%.</t>
+          <t>5.5% = (7.0+6.0+5.5+5.0+4.0)/5. Year 1 is the $735M guide (7.0% of FY26 sales); then fade toward the 4.5% D&amp;A floor.</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "725.0 million" → 2026 capex guide $725–745M (~7.0% of FY26 sales). Ctrl+F "680,802" → FY25 capex. Model 5-yr blend 5.5%.</t>
+          <t>Ctrl+F "$725.0 million and $745.0 million" → 2026 guide (one sentence). Mid $735M ÷ FY26 sales $10,425M = 7.0%. Ctrl+F "680,802" (one hit) → FY25 PP&amp;E spend; 680,802 ÷ 11,102,600 = 6.1%. Ctrl+F "496,228" → D&amp;A 4.5% (maintenance floor). DCF 5.5% is the 5-yr average of the fade 7.0 → 4.0: (7.0+6.0+5.5+5.0+4.0)/5 = 5.5%. We do not run the 7% build-year rate for all five years.</t>
         </is>
       </c>
       <c r="F15" s="20">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Income from operations" → 2,210,615 + "Depreciation and amortization" → 496,228</t>
+          <t>Ctrl+F "19.9%" → FY25 OM (EBIT $2,210,615). Ctrl+F "496,228" → Depreciation and amortization. Do not search the words Income from operations (17 hits).</t>
         </is>
       </c>
       <c r="E17" s="81">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>5.5% = (7.0+6.0+5.5+5.0+4.0)/5. Year 1 is the $735M guide (7.0% of FY26 sales); then fade toward the 4.5% D&amp;A floor.</t>
+          <t>FY26 is up vs FY25: $735M / 7.0% vs $681M / 6.1% (sales fall, spend rises). 5.5% = (7.0+6.0+5.5+5.0+4.0)/5 after that spike.</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "$725.0 million and $745.0 million" → 2026 guide (one sentence). Mid $735M ÷ FY26 sales $10,425M = 7.0%. Ctrl+F "680,802" (one hit) → FY25 PP&amp;E spend; 680,802 ÷ 11,102,600 = 6.1%. Ctrl+F "496,228" → D&amp;A 4.5% (maintenance floor). DCF 5.5% is the 5-yr average of the fade 7.0 → 4.0: (7.0+6.0+5.5+5.0+4.0)/5 = 5.5%. We do not run the 7% build-year rate for all five years.</t>
+          <t>Ctrl+F "680,802" (one hit) → FY25 PP&amp;E $680.8M ÷ 11,102,600 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 guide mid $735M ÷ $10,425M sales = 7.0%. FY26 is higher than FY25 in both $ ($735M vs $681M) and % (7.0% vs 6.1%): sales fall 6%, spend rises. FY27 6.0% is the step back to the FY25 6.1% run-rate after that one-year spike. Then 5.5 / 5.0 / 4.0 toward D&amp;A 4.5% (Ctrl+F "496,228"). DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>5.5% = (7.0+6.0+5.5+5.0+4.0)/5. Year 1 is the $735M guide (7.0% of FY26 sales); then fade toward the 4.5% D&amp;A floor.</t>
+          <t>FY26 is up vs FY25: $735M / 7.0% vs $681M / 6.1% (sales fall, spend rises). 5.5% = (7.0+6.0+5.5+5.0+4.0)/5 after that spike.</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "$725.0 million and $745.0 million" → 2026 guide (one sentence). Mid $735M ÷ FY26 sales $10,425M = 7.0%. Ctrl+F "680,802" (one hit) → FY25 PP&amp;E spend; 680,802 ÷ 11,102,600 = 6.1%. Ctrl+F "496,228" → D&amp;A 4.5% (maintenance floor). DCF 5.5% is the 5-yr average of the fade 7.0 → 4.0: (7.0+6.0+5.5+5.0+4.0)/5 = 5.5%. We do not run the 7% build-year rate for all five years.</t>
+          <t>Ctrl+F "680,802" (one hit) → FY25 PP&amp;E $680.8M ÷ 11,102,600 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 guide mid $735M ÷ $10,425M sales = 7.0%. FY26 is higher than FY25 in both $ ($735M vs $681M) and % (7.0% vs 6.1%): sales fall 6%, spend rises. FY27 6.0% is the step back to the FY25 6.1% run-rate after that one-year spike. Then 5.5 / 5.0 / 4.0 toward D&amp;A 4.5% (Ctrl+F "496,228"). DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
         </is>
       </c>
       <c r="F15" s="20">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -421,6 +421,9 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -477,9 +480,6 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1731,25 +1731,28 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="54" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>FY26 is up vs FY25: $735M / 7.0% vs $681M / 6.1% (sales fall, spend rises). 5.5% = (7.0+6.0+5.5+5.0+4.0)/5 after that spike.</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>7.0% = $735M ÷ the $10.4B FY26 sales year, not ÷ FY25 $11.1B (that would be 6.6%). $10B year + higher spend = the % spike.
+Also: FY26 sales are the guided $10.35–$10.50B year (~$10.4B). FY25 was $11.1B. Same capex math must use the $10B denominator.</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>LULU 10-K: 2026 capex guide $725–745M
+Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" (one hit) → FY25 PP&amp;E $680.8M ÷ 11,102,600 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 guide mid $735M ÷ $10,425M sales = 7.0%. FY26 is higher than FY25 in both $ ($735M vs $681M) and % (7.0% vs 6.1%): sales fall 6%, spend rises. FY27 6.0% is the step back to the FY25 6.1% run-rate after that one-year spike. Then 5.5 / 5.0 / 4.0 toward D&amp;A 4.5% (Ctrl+F "496,228"). DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
+          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M. Do not divide $735M by FY25 $11.1B (6.6%). FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
+Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -1801,761 +1804,761 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>11102600*(1+F4)</f>
         <v/>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="32">
         <f>11102600*(1+G4)</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="32">
         <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <f>F17*(1+F5)</f>
         <v/>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <f>G17*(1+G5)</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="32">
         <f>H17*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>F18*(1+F5)</f>
         <v/>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="32">
         <f>G18*(1+G5)</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="32">
         <f>H18*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>F19*(1+F5)</f>
         <v/>
       </c>
-      <c r="G20" s="31">
+      <c r="G20" s="32">
         <f>G19*(1+G5)</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="32">
         <f>H19*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>F20*(1+F5)</f>
         <v/>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <f>G20*(1+G5)</f>
         <v/>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <f>H20*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="A22" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>F6+(F8-F6)*0/4</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <f>G6+(G8-G6)*0/4</f>
         <v/>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="33">
         <f>F6+(F8-F6)*1/4</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="33">
         <f>G6+(G8-G6)*1/4</f>
         <v/>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="33">
         <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <f>F6+(F8-F6)*2/4</f>
         <v/>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <f>G6+(G8-G6)*2/4</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="A25" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <f>F6+(F8-F6)*3/4</f>
         <v/>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <f>G6+(G8-G6)*3/4</f>
         <v/>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="33">
         <f>F6+(F8-F6)*4/4</f>
         <v/>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="33">
         <f>G6+(G8-G6)*4/4</f>
         <v/>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="33">
         <f>H6+(H8-H6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <f>F17*F22+F7</f>
         <v/>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <f>G17*G22+G7</f>
         <v/>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <f>H17*H22+H7</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <f>F18*F23</f>
         <v/>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <f>G18*G23</f>
         <v/>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <f>H18*H23</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="32">
         <f>F19*F24</f>
         <v/>
       </c>
-      <c r="G29" s="31">
+      <c r="G29" s="32">
         <f>G19*G24</f>
         <v/>
       </c>
-      <c r="H29" s="31">
+      <c r="H29" s="32">
         <f>H19*H24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="32">
         <f>F20*F25</f>
         <v/>
       </c>
-      <c r="G30" s="31">
+      <c r="G30" s="32">
         <f>G20*G25</f>
         <v/>
       </c>
-      <c r="H30" s="31">
+      <c r="H30" s="32">
         <f>H20*H25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="32">
         <f>F21*F26</f>
         <v/>
       </c>
-      <c r="G31" s="31">
+      <c r="G31" s="32">
         <f>G21*G26</f>
         <v/>
       </c>
-      <c r="H31" s="31">
+      <c r="H31" s="32">
         <f>H21*H26</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="32">
         <f>F27*(1-F11)</f>
         <v/>
       </c>
-      <c r="G32" s="31">
+      <c r="G32" s="32">
         <f>G27*(1-G11)</f>
         <v/>
       </c>
-      <c r="H32" s="31">
+      <c r="H32" s="32">
         <f>H27*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="32">
         <f>F28*(1-F11)</f>
         <v/>
       </c>
-      <c r="G33" s="31">
+      <c r="G33" s="32">
         <f>G28*(1-G11)</f>
         <v/>
       </c>
-      <c r="H33" s="31">
+      <c r="H33" s="32">
         <f>H28*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="32">
         <f>F29*(1-F11)</f>
         <v/>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <f>G29*(1-G11)</f>
         <v/>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <f>H29*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="A35" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="32">
         <f>F30*(1-F11)</f>
         <v/>
       </c>
-      <c r="G35" s="31">
+      <c r="G35" s="32">
         <f>G30*(1-G11)</f>
         <v/>
       </c>
-      <c r="H35" s="31">
+      <c r="H35" s="32">
         <f>H30*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="A36" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="32">
         <f>F31*(1-F11)</f>
         <v/>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="32">
         <f>G31*(1-G11)</f>
         <v/>
       </c>
-      <c r="H36" s="31">
+      <c r="H36" s="32">
         <f>H31*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="A37" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="32">
         <f>F17*F12</f>
         <v/>
       </c>
-      <c r="G37" s="31">
+      <c r="G37" s="32">
         <f>G17*G12</f>
         <v/>
       </c>
-      <c r="H37" s="31">
+      <c r="H37" s="32">
         <f>H17*H12</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <f>F18*F12</f>
         <v/>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <f>G18*G12</f>
         <v/>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <f>H18*H12</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <f>F19*F12</f>
         <v/>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <f>G19*G12</f>
         <v/>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <f>H19*H12</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="A40" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="F40" s="31">
+      <c r="F40" s="32">
         <f>F20*F12</f>
         <v/>
       </c>
-      <c r="G40" s="31">
+      <c r="G40" s="32">
         <f>G20*G12</f>
         <v/>
       </c>
-      <c r="H40" s="31">
+      <c r="H40" s="32">
         <f>H20*H12</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="A41" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <f>F21*F12</f>
         <v/>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <f>G21*G12</f>
         <v/>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <f>H21*H12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <f>F17*F13</f>
         <v/>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <f>G17*G13</f>
         <v/>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <f>H17*H13</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="32">
         <f>F18*F13</f>
         <v/>
       </c>
-      <c r="G43" s="31">
+      <c r="G43" s="32">
         <f>G18*G13</f>
         <v/>
       </c>
-      <c r="H43" s="31">
+      <c r="H43" s="32">
         <f>H18*H13</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="inlineStr">
+      <c r="A44" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>F19*F13</f>
         <v/>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <f>G19*G13</f>
         <v/>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <f>H19*H13</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="A45" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <f>F20*F13</f>
         <v/>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <f>G20*G13</f>
         <v/>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <f>H20*H13</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="F46" s="31">
+      <c r="F46" s="32">
         <f>F21*F13</f>
         <v/>
       </c>
-      <c r="G46" s="31">
+      <c r="G46" s="32">
         <f>G21*G13</f>
         <v/>
       </c>
-      <c r="H46" s="31">
+      <c r="H46" s="32">
         <f>H21*H13</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+      <c r="A47" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 1</t>
         </is>
       </c>
-      <c r="F47" s="31">
+      <c r="F47" s="32">
         <f>F14*(F17-11102600)</f>
         <v/>
       </c>
-      <c r="G47" s="31">
+      <c r="G47" s="32">
         <f>G14*(G17-11102600)</f>
         <v/>
       </c>
-      <c r="H47" s="31">
+      <c r="H47" s="32">
         <f>H14*(H17-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="A48" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 2</t>
         </is>
       </c>
-      <c r="F48" s="31">
+      <c r="F48" s="32">
         <f>F14*(F18-F17)</f>
         <v/>
       </c>
-      <c r="G48" s="31">
+      <c r="G48" s="32">
         <f>G14*(G18-G17)</f>
         <v/>
       </c>
-      <c r="H48" s="31">
+      <c r="H48" s="32">
         <f>H14*(H18-H17)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 3</t>
         </is>
       </c>
-      <c r="F49" s="31">
+      <c r="F49" s="32">
         <f>F14*(F19-F18)</f>
         <v/>
       </c>
-      <c r="G49" s="31">
+      <c r="G49" s="32">
         <f>G14*(G19-G18)</f>
         <v/>
       </c>
-      <c r="H49" s="31">
+      <c r="H49" s="32">
         <f>H14*(H19-H18)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="A50" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 4</t>
         </is>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <f>F14*(F20-F19)</f>
         <v/>
       </c>
-      <c r="G50" s="31">
+      <c r="G50" s="32">
         <f>G14*(G20-G19)</f>
         <v/>
       </c>
-      <c r="H50" s="31">
+      <c r="H50" s="32">
         <f>H14*(H20-H19)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC – year 5</t>
         </is>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <f>F14*(F21-F20)</f>
         <v/>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <f>G14*(G21-G20)</f>
         <v/>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <f>H14*(H21-H20)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="F52" s="31">
+      <c r="F52" s="32">
         <f>F32+F37-F42-F47</f>
         <v/>
       </c>
-      <c r="G52" s="31">
+      <c r="G52" s="32">
         <f>G32+G37-G42-G47</f>
         <v/>
       </c>
-      <c r="H52" s="31">
+      <c r="H52" s="32">
         <f>H32+H37-H42-H47</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="inlineStr">
+      <c r="A53" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="32">
         <f>F33+F38-F43-F48</f>
         <v/>
       </c>
-      <c r="G53" s="31">
+      <c r="G53" s="32">
         <f>G33+G38-G43-G48</f>
         <v/>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <f>H33+H38-H43-H48</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="inlineStr">
+      <c r="A54" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <f>F34+F39-F44-F49</f>
         <v/>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <f>G34+G39-G44-G49</f>
         <v/>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="32">
         <f>H34+H39-H44-H49</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="F55" s="31">
+      <c r="F55" s="32">
         <f>F35+F40-F45-F50</f>
         <v/>
       </c>
-      <c r="G55" s="31">
+      <c r="G55" s="32">
         <f>G35+G40-G45-G50</f>
         <v/>
       </c>
-      <c r="H55" s="31">
+      <c r="H55" s="32">
         <f>H35+H40-H45-H50</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="inlineStr">
+      <c r="A56" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F56" s="31">
+      <c r="F56" s="32">
         <f>F36+F41-F46-F51</f>
         <v/>
       </c>
-      <c r="G56" s="31">
+      <c r="G56" s="32">
         <f>G36+G41-G46-G51</f>
         <v/>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <f>H36+H41-H46-H51</f>
         <v/>
       </c>
@@ -2566,34 +2569,34 @@
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F58" s="33">
+      <c r="F58" s="34">
         <f>NPV(F9,F52,F53,F54,F55,F56)+(F56*(1+F10)/(F9-F10))/(1+F9)^5</f>
         <v/>
       </c>
-      <c r="G58" s="33">
+      <c r="G58" s="34">
         <f>NPV(G9,G52,G53,G54,G55,G56)+(G56*(1+G10)/(G9-G10))/(1+G9)^5</f>
         <v/>
       </c>
-      <c r="H58" s="33">
+      <c r="H58" s="34">
         <f>NPV(H9,H52,H53,H54,H55,H56)+(H56*(1+H10)/(H9-H10))/(1+H9)^5</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="34" t="inlineStr">
+      <c r="A59" s="35" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F59" s="35">
+      <c r="F59" s="36">
         <f>(F58+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="G59" s="36">
+      <c r="G59" s="37">
         <f>(G58+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="H59" s="35">
+      <c r="H59" s="36">
         <f>(H58+1807202-0)/111380</f>
         <v/>
       </c>
@@ -2604,21 +2607,21 @@
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F60" s="37">
+      <c r="F60" s="38">
         <f>F59/100.0-1</f>
         <v/>
       </c>
-      <c r="G60" s="37">
+      <c r="G60" s="38">
         <f>G59/100.0-1</f>
         <v/>
       </c>
-      <c r="H60" s="37">
+      <c r="H60" s="38">
         <f>H59/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38" t="inlineStr">
+      <c r="A62" s="39" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2683,69 +2686,69 @@
       <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="39" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="C2" s="39" t="inlineStr">
+      <c r="C2" s="40" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D2" s="39" t="inlineStr">
+      <c r="D2" s="40" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E2" s="40" t="inlineStr">
+      <c r="E2" s="41" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F2" s="41" t="inlineStr">
+      <c r="F2" s="42" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G2" s="41" t="inlineStr">
+      <c r="G2" s="42" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H2" s="41" t="inlineStr">
+      <c r="H2" s="42" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I2" s="41" t="inlineStr">
+      <c r="I2" s="42" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J2" s="41" t="inlineStr">
+      <c r="J2" s="42" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="K2" s="42" t="inlineStr">
+      <c r="K2" s="43" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="L2" s="39" t="inlineStr">
+      <c r="L2" s="40" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="M2" s="39" t="inlineStr">
+      <c r="M2" s="40" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="43" t="inlineStr">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
         </is>
@@ -2755,12 +2758,12 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
-      <c r="E3" s="44" t="inlineStr">
+      <c r="E3" s="45" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="K3" s="45" t="inlineStr">
+      <c r="K3" s="46" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2772,30 +2775,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="E5" s="46" t="n">
+      <c r="E5" s="47" t="n">
         <v>11102600</v>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="48">
         <f>Scenarios!G17</f>
         <v/>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="48">
         <f>Scenarios!G18</f>
         <v/>
       </c>
-      <c r="H5" s="47">
+      <c r="H5" s="48">
         <f>Scenarios!G19</f>
         <v/>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="48">
         <f>Scenarios!G20</f>
         <v/>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="48">
         <f>Scenarios!G21</f>
         <v/>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="49">
         <f>IF(MAX(ABS(F5-Scenarios!$G$17),ABS(G5-Scenarios!$G$18),ABS(H5-Scenarios!$G$19),ABS(I5-Scenarios!$G$20),ABS(J5-Scenarios!$G$21))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2812,7 +2815,7 @@
 Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
 Also: StockAnalysis: LULU 3Y revenue forecast</t>
@@ -2857,7 +2860,7 @@
 Also: FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="30" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
 Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
@@ -2889,7 +2892,7 @@
         <f>Scenarios!G26</f>
         <v/>
       </c>
-      <c r="K7" s="48">
+      <c r="K7" s="49">
         <f>IF(MAX(ABS(F7-Scenarios!$G$22),ABS(G7-Scenarios!$G$23),ABS(H7-Scenarios!$G$24),ABS(I7-Scenarios!$G$25),ABS(J7-Scenarios!$G$26))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2915,7 +2918,7 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="47" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="29">
@@ -2944,23 +2947,23 @@
       <c r="E9" s="51" t="n">
         <v>2210615</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <f>Scenarios!G27</f>
         <v/>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="34">
         <f>Scenarios!G28</f>
         <v/>
       </c>
-      <c r="H9" s="33">
+      <c r="H9" s="34">
         <f>Scenarios!G29</f>
         <v/>
       </c>
-      <c r="I9" s="33">
+      <c r="I9" s="34">
         <f>Scenarios!G30</f>
         <v/>
       </c>
-      <c r="J9" s="33">
+      <c r="J9" s="34">
         <f>Scenarios!G31</f>
         <v/>
       </c>
@@ -3005,23 +3008,23 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="48">
         <f>-Scenarios!G27*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="48">
         <f>-Scenarios!G28*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="48">
         <f>-Scenarios!G29*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="48">
         <f>-Scenarios!G30*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="J11" s="47">
+      <c r="J11" s="48">
         <f>-Scenarios!G31*Scenarios!$G$11</f>
         <v/>
       </c>
@@ -3032,23 +3035,23 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>Scenarios!G32</f>
         <v/>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>Scenarios!G33</f>
         <v/>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>Scenarios!G34</f>
         <v/>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>Scenarios!G35</f>
         <v/>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>Scenarios!G36</f>
         <v/>
       </c>
@@ -3105,50 +3108,53 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="48">
         <f>Scenarios!G37</f>
         <v/>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="48">
         <f>Scenarios!G38</f>
         <v/>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="48">
         <f>Scenarios!G39</f>
         <v/>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="48">
         <f>Scenarios!G40</f>
         <v/>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="48">
         <f>Scenarios!G41</f>
         <v/>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="49">
         <f>IF(MAX(ABS(F14-Scenarios!$G$37),ABS(G14-Scenarios!$G$38),ABS(H14-Scenarios!$G$39),ABS(I14-Scenarios!$G$40),ABS(J14-Scenarios!$G$41))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="54" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>FY26 is up vs FY25: $735M / 7.0% vs $681M / 6.1% (sales fall, spend rises). 5.5% = (7.0+6.0+5.5+5.0+4.0)/5 after that spike.</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K)</t>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>7.0% = $735M ÷ the $10.4B FY26 sales year, not ÷ FY25 $11.1B (that would be 6.6%). $10B year + higher spend = the % spike.
+Also: FY26 sales are the guided $10.35–$10.50B year (~$10.4B). FY25 was $11.1B. Same capex math must use the $10B denominator.</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>LULU 10-K: 2026 capex guide $725–745M
+Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" (one hit) → FY25 PP&amp;E $680.8M ÷ 11,102,600 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 guide mid $735M ÷ $10,425M sales = 7.0%. FY26 is higher than FY25 in both $ ($735M vs $681M) and % (7.0% vs 6.1%): sales fall 6%, spend rises. FY27 6.0% is the step back to the FY25 6.1% run-rate after that one-year spike. Then 5.5 / 5.0 / 4.0 toward D&amp;A 4.5% (Ctrl+F "496,228"). DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
+          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M. Do not divide $735M by FY25 $11.1B (6.6%). FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
+Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
         </is>
       </c>
       <c r="F15" s="20">
@@ -3178,27 +3184,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="48">
         <f>-Scenarios!G42</f>
         <v/>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="48">
         <f>-Scenarios!G43</f>
         <v/>
       </c>
-      <c r="H16" s="47">
+      <c r="H16" s="48">
         <f>-Scenarios!G44</f>
         <v/>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="48">
         <f>-Scenarios!G45</f>
         <v/>
       </c>
-      <c r="J16" s="47">
+      <c r="J16" s="48">
         <f>-Scenarios!G46</f>
         <v/>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="49">
         <f>IF(MAX(ABS(F16+Scenarios!$G$42),ABS(G16+Scenarios!$G$43),ABS(H16+Scenarios!$G$44),ABS(I16+Scenarios!$G$45),ABS(J16+Scenarios!$G$46))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3251,33 +3257,33 @@
           <t>(Increase)/decrease in net working capital</t>
         </is>
       </c>
-      <c r="F18" s="47">
+      <c r="F18" s="48">
         <f>-Scenarios!G47</f>
         <v/>
       </c>
-      <c r="G18" s="47">
+      <c r="G18" s="48">
         <f>-Scenarios!G48</f>
         <v/>
       </c>
-      <c r="H18" s="47">
+      <c r="H18" s="48">
         <f>-Scenarios!G49</f>
         <v/>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="48">
         <f>-Scenarios!G50</f>
         <v/>
       </c>
-      <c r="J18" s="47">
+      <c r="J18" s="48">
         <f>-Scenarios!G51</f>
         <v/>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="49">
         <f>IF(MAX(ABS(F18+Scenarios!$G$47),ABS(G18+Scenarios!$G$48),ABS(H18+Scenarios!$G$49),ABS(I18+Scenarios!$G$50),ABS(J18+Scenarios!$G$51))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="38" t="inlineStr">
+      <c r="A19" s="39" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
         </is>
@@ -3369,23 +3375,23 @@
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>F20*F22</f>
         <v/>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="34">
         <f>G20*G22</f>
         <v/>
       </c>
-      <c r="H23" s="33">
+      <c r="H23" s="34">
         <f>H20*H22</f>
         <v/>
       </c>
-      <c r="I23" s="33">
+      <c r="I23" s="34">
         <f>I20*I22</f>
         <v/>
       </c>
-      <c r="J23" s="33">
+      <c r="J23" s="34">
         <f>J20*J22</f>
         <v/>
       </c>
@@ -3453,7 +3459,7 @@
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <f>J9+J14</f>
         <v/>
       </c>
@@ -3464,7 +3470,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="E30" s="47">
+      <c r="E30" s="48">
         <f>J20*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
         <v/>
       </c>
@@ -3497,7 +3503,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E33" s="33">
+      <c r="E33" s="34">
         <f>E27+E32</f>
         <v/>
       </c>
@@ -3518,7 +3524,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E34" s="46" t="n">
+      <c r="E34" s="47" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -3538,7 +3544,7 @@
           <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
         </is>
       </c>
-      <c r="E35" s="46" t="n">
+      <c r="E35" s="47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3548,7 +3554,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="E36" s="33">
+      <c r="E36" s="34">
         <f>E33+E34+E35</f>
         <v/>
       </c>
@@ -3569,7 +3575,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E37" s="46" t="n">
+      <c r="E37" s="47" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -3682,7 +3688,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="E46" s="47">
+      <c r="E46" s="48">
         <f>E29*E45</f>
         <v/>
       </c>
@@ -3693,7 +3699,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E47" s="47">
+      <c r="E47" s="48">
         <f>E46/(1+Scenarios!$G$9)^J21</f>
         <v/>
       </c>
@@ -3704,7 +3710,7 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E48" s="33">
+      <c r="E48" s="34">
         <f>E27+E47</f>
         <v/>
       </c>
@@ -3832,7 +3838,7 @@
         <f>TEXT(D54,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D57" s="38" t="inlineStr">
+      <c r="D57" s="39" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
@@ -4213,7 +4219,7 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 ($000) in FY2025 column</t>
         </is>
       </c>
-      <c r="E4" s="46" t="n">
+      <c r="E4" s="47" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -4223,7 +4229,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="48">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -4239,7 +4245,7 @@
           <t>↳ DCF base case</t>
         </is>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="48">
         <f>DCF!E29</f>
         <v/>
       </c>
@@ -4280,7 +4286,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n">
+      <c r="E8" s="47" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -4300,7 +4306,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E9" s="46" t="n">
+      <c r="E9" s="47" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -4393,7 +4399,7 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
@@ -4586,35 +4592,35 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="31" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="31" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="31" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="31" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="31" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4823,7 +4829,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38" t="inlineStr">
+      <c r="A43" s="39" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1739,8 +1739,8 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>7.0% = $735M ÷ the $10.4B FY26 sales year, not ÷ FY25 $11.1B (that would be 6.6%). $10B year + higher spend = the % spike.
-Also: FY26 sales are the guided $10.35–$10.50B year (~$10.4B). FY25 was $11.1B. Same capex math must use the $10B denominator.</t>
+          <t>FY26 7% is $735M on guided $10.4B sales, not FY25 $11.1B. 5.5% blend = (7+6+5.5+5+4)/5.
+Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
       <c r="C13" s="30" t="inlineStr">
@@ -3141,8 +3141,8 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>7.0% = $735M ÷ the $10.4B FY26 sales year, not ÷ FY25 $11.1B (that would be 6.6%). $10B year + higher spend = the % spike.
-Also: FY26 sales are the guided $10.35–$10.50B year (~$10.4B). FY25 was $11.1B. Same capex math must use the $10B denominator.</t>
+          <t>FY26 7% is $735M on guided $10.4B sales, not FY25 $11.1B. 5.5% blend = (7+6+5.5+5+4)/5.
+Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
       <c r="C15" s="30" t="inlineStr">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1739,7 +1739,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>FY26 7% is $735M on guided $10.4B sales, not FY25 $11.1B. 5.5% blend = (7+6+5.5+5+4)/5.
+          <t>FY26 7.0% is $735M on $10.4B sales, not FY25 $11.1B. Since 7.0% steps toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M. Do not divide $735M by FY25 $11.1B (6.6%). FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
+          <t>Ctrl+F "680,802" → FY25 $680.8M / $11.1B = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 mid $735M / $10.4B sales = 7.0% (not ÷ $11.1B). Since it goes 7.0% toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
 Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
         </is>
       </c>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>FY26 7% is $735M on guided $10.4B sales, not FY25 $11.1B. 5.5% blend = (7+6+5.5+5+4)/5.
+          <t>FY26 7.0% is $735M on $10.4B sales, not FY25 $11.1B. Since 7.0% steps toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M. Do not divide $735M by FY25 $11.1B (6.6%). FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
+          <t>Ctrl+F "680,802" → FY25 $680.8M / $11.1B = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 mid $735M / $10.4B sales = 7.0% (not ÷ $11.1B). Since it goes 7.0% toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
 Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
         </is>
       </c>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1751,8 +1751,8 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 $680.8M / $11.1B = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 mid $735M / $10.4B sales = 7.0% (not ÷ $11.1B). Since it goes 7.0% toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
-Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
+          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M.
+Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator. FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -3153,8 +3153,8 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 $680.8M / $11.1B = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 mid $735M / $10.4B sales = 7.0% (not ÷ $11.1B). Since it goes 7.0% toward FY25 6.1%, we assume a fade: DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.
-Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator.</t>
+          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M.
+Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator. FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
         </is>
       </c>
       <c r="F15" s="20">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1145,7 +1145,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Risk-free rate (10-yr UST)</t>
@@ -1170,7 +1170,7 @@
         <v>0.048</v>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Equity risk premium</t>
@@ -1195,7 +1195,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Levered beta</t>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
@@ -1263,7 +1263,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tax rate</t>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Equity weight</t>
@@ -1331,7 +1331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Debt weight</t>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2026E revenue growth</t>
@@ -1483,7 +1483,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
           <t>FY2027–FY2030E revenue growth (avg)</t>
@@ -1514,7 +1514,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="6" ht="36" customHeight="1">
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Run-rate EBIT margin (clean, ex-refunds)</t>
@@ -1545,7 +1545,7 @@
         <v>0.145</v>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FY26 IEEPA tariff refunds ($k, already in guide)</t>
@@ -1576,7 +1576,7 @@
         <v>134500</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Terminal (FY2030E) EBIT margin</t>
@@ -1607,7 +1607,7 @@
         <v>0.19</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>WACC</t>
@@ -1638,7 +1638,7 @@
         <v>0.095</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Terminal growth</t>
@@ -1669,7 +1669,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
+    <row r="11" ht="28" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
@@ -1700,7 +1700,7 @@
         <v>0.28</v>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>D&amp;A % of revenue</t>
@@ -1731,7 +1731,7 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="13" ht="54" customHeight="1">
+    <row r="13" ht="150" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
@@ -1751,8 +1751,18 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M.
-Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator. FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
+          <t>FY25 actual (10-K)
+  Ctrl+F "680,802"  →  capex $680.8M
+  Ctrl+F "11,102,600"  →  sales $11.1B
+  680.8 / 11,102.6 = 6.1%
+FY26 capex (10-K)
+  Ctrl+F "$725.0 million and $745.0 million"  →  mid $735M
+FY26 sales (earnings)
+  Ctrl+F "$10.350 billion to $10.500 billion"  →  $10.35–$10.50B (mid $10.425B)
+  7.0% = $735M / $10.425B    ($10B year, not FY25 $11.1B)
+DCF blend
+  Fade  7.0 / 6.0 / 5.5 / 5.0 / 4.0
+  5.5% = (7.0+6.0+5.5+5.0+4.0)/5</t>
         </is>
       </c>
       <c r="F13" s="20" t="n">
@@ -1765,7 +1775,7 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
+    <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>NWC build % of Δrevenue</t>
@@ -2747,7 +2757,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="44" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
@@ -2803,7 +2813,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="54" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
@@ -2848,7 +2858,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="54" customHeight="1">
+    <row r="7" ht="42" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Clean / run-rate EBIT margin %</t>
@@ -2897,7 +2907,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Plus: FY26 IEEPA tariff refunds (one-time)</t>
@@ -3060,7 +3070,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A % of revenue</t>
@@ -3133,7 +3143,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" ht="54" customHeight="1">
+    <row r="15" ht="150" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex % of revenue</t>
@@ -3153,8 +3163,18 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "680,802" → FY25 capex $680.8M. Ctrl+F "11,102,600" → FY25 sales $11.1B. 680.8 / 11,102.6 = 6.1%. Ctrl+F "$725.0 million and $745.0 million" → FY26 capex mid $735M.
-Also: Ctrl+F "$10.350 billion to $10.500 billion" → FY26 net revenue guide (one hit). Mid $10.425B. That is the $10B year vs FY25 $11.1B. 7.0% capex uses this $10.4B denominator. FY26 is a $10B sales year: $735M / $10.425B = 7.0%. Then fade 6.0 / 5.5 / 5.0 / 4.0. DCF 5.5% = (7.0+6.0+5.5+5.0+4.0)/5.</t>
+          <t>FY25 actual (10-K)
+  Ctrl+F "680,802"  →  capex $680.8M
+  Ctrl+F "11,102,600"  →  sales $11.1B
+  680.8 / 11,102.6 = 6.1%
+FY26 capex (10-K)
+  Ctrl+F "$725.0 million and $745.0 million"  →  mid $735M
+FY26 sales (earnings)
+  Ctrl+F "$10.350 billion to $10.500 billion"  →  $10.35–$10.50B (mid $10.425B)
+  7.0% = $735M / $10.425B    ($10B year, not FY25 $11.1B)
+DCF blend
+  Fade  7.0 / 6.0 / 5.5 / 5.0 / 4.0
+  5.5% = (7.0+6.0+5.5+5.0+4.0)/5</t>
         </is>
       </c>
       <c r="F15" s="20">
@@ -3209,7 +3229,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC build % of Δrevenue</t>
@@ -3427,7 +3447,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="36" customHeight="1">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
@@ -3508,7 +3528,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="36" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
@@ -3528,7 +3548,7 @@
         <v>1807202</v>
       </c>
     </row>
-    <row r="35" ht="36" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Less: total debt</t>
@@ -3559,7 +3579,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="36" customHeight="1">
+    <row r="37" ht="28" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
@@ -3594,7 +3614,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="28" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
@@ -3652,7 +3672,7 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="36" customHeight="1">
+    <row r="45" ht="28" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
@@ -3858,7 +3878,7 @@
       <c r="G60" s="13" t="n"/>
       <c r="H60" s="13" t="n"/>
     </row>
-    <row r="61" ht="36" customHeight="1">
+    <row r="61" ht="28" customHeight="1">
       <c r="A61" s="74" t="inlineStr">
         <is>
           <t>WACC \ g</t>
@@ -3900,7 +3920,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="36" customHeight="1">
+    <row r="62" ht="28" customHeight="1">
       <c r="A62" s="75" t="n">
         <v>0.095</v>
       </c>
@@ -3940,7 +3960,7 @@
         </is>
       </c>
     </row>
-    <row r="63" ht="36" customHeight="1">
+    <row r="63" ht="28" customHeight="1">
       <c r="A63" s="75" t="n">
         <v>0.1</v>
       </c>
@@ -3975,7 +3995,7 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="36" customHeight="1">
+    <row r="64" ht="28" customHeight="1">
       <c r="A64" s="75" t="n">
         <v>0.105</v>
       </c>
@@ -4010,7 +4030,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="36" customHeight="1">
+    <row r="65" ht="28" customHeight="1">
       <c r="A65" s="75" t="n">
         <v>0.11</v>
       </c>
@@ -4045,7 +4065,7 @@
         </is>
       </c>
     </row>
-    <row r="66" ht="36" customHeight="1">
+    <row r="66" ht="28" customHeight="1">
       <c r="A66" s="75" t="n">
         <v>0.115</v>
       </c>
@@ -4080,7 +4100,7 @@
         </is>
       </c>
     </row>
-    <row r="67" ht="36" customHeight="1">
+    <row r="67" ht="28" customHeight="1">
       <c r="B67" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
@@ -4203,7 +4223,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>FY2025A revenue</t>
@@ -4250,7 +4270,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="36" customHeight="1">
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>FY2026E diluted EPS (guidance midpoint)</t>
@@ -4270,7 +4290,7 @@
         <v>9.609999999999999</v>
       </c>
     </row>
-    <row r="8" ht="36" customHeight="1">
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Cash &amp; equivalents</t>
@@ -4290,7 +4310,7 @@
         <v>1807202</v>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Diluted shares (000)</t>
@@ -4310,7 +4330,7 @@
         <v>111380</v>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
@@ -4393,7 +4413,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>lululemon (LULU) — current</t>
@@ -4419,7 +4439,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Nike (NKE)</t>
@@ -4444,7 +4464,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Deckers (DECK)</t>
@@ -4469,7 +4489,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>On Holding (ONON)</t>
@@ -4494,7 +4514,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>adidas (ADS)</t>
@@ -4519,7 +4539,7 @@
         <v>9.300000000000001</v>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>V.F. Corp (VFC)</t>
@@ -4675,7 +4695,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="54" customHeight="1">
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
@@ -4714,7 +4734,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="28" customHeight="1">
       <c r="A38" s="71" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
@@ -4744,7 +4764,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="54" customHeight="1">
+    <row r="39" ht="42" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
@@ -4808,7 +4828,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="36" customHeight="1">
+    <row r="42" ht="28" customHeight="1">
       <c r="A42" s="88" t="inlineStr">
         <is>
           <t>Current price</t>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1783,7 +1783,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+          <t>7.5% of Δsales is operating NWC: AR + inventory + other CA − AP − accrued. AR is on the 10-K ($190,657); not omitted.</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
+          <t>Ctrl+F "Accounts receivable, net" → 190,657. Ctrl+F "Inventories" → 1,700,753. Ctrl+F "Accounts payable" → 331,421. Ctrl+F "Accrued liabilities and other" → 662,982. NWC = AR + Inv + other CA − AP − accrued; 7.5% of Δsales.</t>
         </is>
       </c>
       <c r="F14" s="20" t="n">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>7.5% of revenue change for ΔNWC; ties working-capital swings to sales trajectory per historical sensitivity.</t>
+          <t>7.5% of Δsales is operating NWC: AR + inventory + other CA − AP − accrued. AR is on the 10-K ($190,657); not omitted.</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982</t>
+          <t>Ctrl+F "Accounts receivable, net" → 190,657. Ctrl+F "Inventories" → 1,700,753. Ctrl+F "Accounts payable" → 331,421. Ctrl+F "Accrued liabilities and other" → 662,982. NWC = AR + Inv + other CA − AP − accrued; 7.5% of Δsales.</t>
         </is>
       </c>
       <c r="F17" s="20">

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1387,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1778,83 +1778,95 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>NWC build % of Δrevenue</t>
+          <t>AR % of revenue (NWC)</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>7.5% of Δsales is operating NWC: AR + inventory + other CA − AP − accrued. AR is on the 10-K ($190,657); not omitted.</t>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G14" s="20" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Other NWC (ex-AR) % of Δrevenue</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>5.8% of Δsales is other NWC (Inv + OCA − AP − accrued). AR is the 1.7% line above, not inside this residual. 1.7+5.8=7.5%.</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
           <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Accounts receivable, net" → 190,657. Ctrl+F "Inventories" → 1,700,753. Ctrl+F "Accounts payable" → 331,421. Ctrl+F "Accrued liabilities and other" → 662,982. NWC = AR + Inv + other CA − AP − accrued; 7.5% of Δsales.</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G14" s="20" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Other NWC ex-AR. Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 5.8% of Δsales; AR is the 1.7% line, not in this residual.</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="G15" s="20" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>5-year forecast paths (by scenario)</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue – year 1</t>
-        </is>
-      </c>
-      <c r="F17" s="32">
-        <f>11102600*(1+F4)</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>11102600*(1+G4)</f>
-        <v/>
-      </c>
-      <c r="H17" s="32">
-        <f>11102600*(1+H4)</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue – year 2</t>
+          <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
       <c r="F18" s="32">
-        <f>F17*(1+F5)</f>
+        <f>11102600*(1+F4)</f>
         <v/>
       </c>
       <c r="G18" s="32">
-        <f>G17*(1+G5)</f>
+        <f>11102600*(1+G4)</f>
         <v/>
       </c>
       <c r="H18" s="32">
-        <f>H17*(1+H5)</f>
+        <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue – year 3</t>
+          <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
       <c r="F19" s="32">
@@ -1873,7 +1885,7 @@
     <row r="20">
       <c r="A20" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue – year 4</t>
+          <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
       <c r="F20" s="32">
@@ -1892,7 +1904,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue – year 5</t>
+          <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
       <c r="F21" s="32">
@@ -1911,140 +1923,140 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clean EBIT margin – year 1</t>
-        </is>
-      </c>
-      <c r="F22" s="33">
-        <f>F6+(F8-F6)*0/4</f>
-        <v/>
-      </c>
-      <c r="G22" s="33">
-        <f>G6+(G8-G6)*0/4</f>
-        <v/>
-      </c>
-      <c r="H22" s="33">
-        <f>H6+(H8-H6)*0/4</f>
+          <t xml:space="preserve">  Revenue – year 5</t>
+        </is>
+      </c>
+      <c r="F22" s="32">
+        <f>F21*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>G21*(1+G5)</f>
+        <v/>
+      </c>
+      <c r="H22" s="32">
+        <f>H21*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clean EBIT margin – year 2</t>
+          <t xml:space="preserve">  Clean EBIT margin – year 1</t>
         </is>
       </c>
       <c r="F23" s="33">
-        <f>F6+(F8-F6)*1/4</f>
+        <f>F6+(F8-F6)*0/4</f>
         <v/>
       </c>
       <c r="G23" s="33">
-        <f>G6+(G8-G6)*1/4</f>
+        <f>G6+(G8-G6)*0/4</f>
         <v/>
       </c>
       <c r="H23" s="33">
-        <f>H6+(H8-H6)*1/4</f>
+        <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clean EBIT margin – year 3</t>
+          <t xml:space="preserve">  Clean EBIT margin – year 2</t>
         </is>
       </c>
       <c r="F24" s="33">
-        <f>F6+(F8-F6)*2/4</f>
+        <f>F6+(F8-F6)*1/4</f>
         <v/>
       </c>
       <c r="G24" s="33">
-        <f>G6+(G8-G6)*2/4</f>
+        <f>G6+(G8-G6)*1/4</f>
         <v/>
       </c>
       <c r="H24" s="33">
-        <f>H6+(H8-H6)*2/4</f>
+        <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clean EBIT margin – year 4</t>
+          <t xml:space="preserve">  Clean EBIT margin – year 3</t>
         </is>
       </c>
       <c r="F25" s="33">
-        <f>F6+(F8-F6)*3/4</f>
+        <f>F6+(F8-F6)*2/4</f>
         <v/>
       </c>
       <c r="G25" s="33">
-        <f>G6+(G8-G6)*3/4</f>
+        <f>G6+(G8-G6)*2/4</f>
         <v/>
       </c>
       <c r="H25" s="33">
-        <f>H6+(H8-H6)*3/4</f>
+        <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Clean EBIT margin – year 5</t>
+          <t xml:space="preserve">  Clean EBIT margin – year 4</t>
         </is>
       </c>
       <c r="F26" s="33">
-        <f>F6+(F8-F6)*4/4</f>
+        <f>F6+(F8-F6)*3/4</f>
         <v/>
       </c>
       <c r="G26" s="33">
-        <f>G6+(G8-G6)*4/4</f>
+        <f>G6+(G8-G6)*3/4</f>
         <v/>
       </c>
       <c r="H26" s="33">
-        <f>H6+(H8-H6)*4/4</f>
+        <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT – year 1</t>
-        </is>
-      </c>
-      <c r="F27" s="32">
-        <f>F17*F22+F7</f>
-        <v/>
-      </c>
-      <c r="G27" s="32">
-        <f>G17*G22+G7</f>
-        <v/>
-      </c>
-      <c r="H27" s="32">
-        <f>H17*H22+H7</f>
+          <t xml:space="preserve">  Clean EBIT margin – year 5</t>
+        </is>
+      </c>
+      <c r="F27" s="33">
+        <f>F6+(F8-F6)*4/4</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>G6+(G8-G6)*4/4</f>
+        <v/>
+      </c>
+      <c r="H27" s="33">
+        <f>H6+(H8-H6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT – year 2</t>
+          <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
       <c r="F28" s="32">
-        <f>F18*F23</f>
+        <f>F18*F23+F7</f>
         <v/>
       </c>
       <c r="G28" s="32">
-        <f>G18*G23</f>
+        <f>G18*G23+G7</f>
         <v/>
       </c>
       <c r="H28" s="32">
-        <f>H18*H23</f>
+        <f>H18*H23+H7</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT – year 3</t>
+          <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
       <c r="F29" s="32">
@@ -2063,7 +2075,7 @@
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT – year 4</t>
+          <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
       <c r="F30" s="32">
@@ -2082,7 +2094,7 @@
     <row r="31">
       <c r="A31" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  EBIT – year 5</t>
+          <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
       <c r="F31" s="32">
@@ -2101,26 +2113,26 @@
     <row r="32">
       <c r="A32" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOPAT – year 1</t>
+          <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
       <c r="F32" s="32">
-        <f>F27*(1-F11)</f>
+        <f>F22*F27</f>
         <v/>
       </c>
       <c r="G32" s="32">
-        <f>G27*(1-G11)</f>
+        <f>G22*G27</f>
         <v/>
       </c>
       <c r="H32" s="32">
-        <f>H27*(1-H11)</f>
+        <f>H22*H27</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOPAT – year 2</t>
+          <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
       <c r="F33" s="32">
@@ -2139,7 +2151,7 @@
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOPAT – year 3</t>
+          <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
       <c r="F34" s="32">
@@ -2158,7 +2170,7 @@
     <row r="35">
       <c r="A35" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOPAT – year 4</t>
+          <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
       <c r="F35" s="32">
@@ -2177,7 +2189,7 @@
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOPAT – year 5</t>
+          <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
       <c r="F36" s="32">
@@ -2196,26 +2208,26 @@
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A – year 1</t>
+          <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
       <c r="F37" s="32">
-        <f>F17*F12</f>
+        <f>F32*(1-F11)</f>
         <v/>
       </c>
       <c r="G37" s="32">
-        <f>G17*G12</f>
+        <f>G32*(1-G11)</f>
         <v/>
       </c>
       <c r="H37" s="32">
-        <f>H17*H12</f>
+        <f>H32*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A – year 2</t>
+          <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
       <c r="F38" s="32">
@@ -2234,7 +2246,7 @@
     <row r="39">
       <c r="A39" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A – year 3</t>
+          <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
       <c r="F39" s="32">
@@ -2253,7 +2265,7 @@
     <row r="40">
       <c r="A40" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A – year 4</t>
+          <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
       <c r="F40" s="32">
@@ -2272,7 +2284,7 @@
     <row r="41">
       <c r="A41" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A – year 5</t>
+          <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
       <c r="F41" s="32">
@@ -2291,26 +2303,26 @@
     <row r="42">
       <c r="A42" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex – year 1</t>
+          <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
       <c r="F42" s="32">
-        <f>F17*F13</f>
+        <f>F22*F12</f>
         <v/>
       </c>
       <c r="G42" s="32">
-        <f>G17*G13</f>
+        <f>G22*G12</f>
         <v/>
       </c>
       <c r="H42" s="32">
-        <f>H17*H13</f>
+        <f>H22*H12</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex – year 2</t>
+          <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
       <c r="F43" s="32">
@@ -2329,7 +2341,7 @@
     <row r="44">
       <c r="A44" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex – year 3</t>
+          <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
       <c r="F44" s="32">
@@ -2348,7 +2360,7 @@
     <row r="45">
       <c r="A45" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex – year 4</t>
+          <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
       <c r="F45" s="32">
@@ -2367,7 +2379,7 @@
     <row r="46">
       <c r="A46" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex – year 5</t>
+          <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
       <c r="F46" s="32">
@@ -2386,252 +2398,556 @@
     <row r="47">
       <c r="A47" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔNWC – year 1</t>
+          <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
       <c r="F47" s="32">
-        <f>F14*(F17-11102600)</f>
+        <f>F22*F13</f>
         <v/>
       </c>
       <c r="G47" s="32">
-        <f>G14*(G17-11102600)</f>
+        <f>G22*G13</f>
         <v/>
       </c>
       <c r="H47" s="32">
-        <f>H14*(H17-11102600)</f>
+        <f>H22*H13</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔNWC – year 2</t>
+          <t xml:space="preserve">  Accounts receivable – year 1</t>
         </is>
       </c>
       <c r="F48" s="32">
-        <f>F14*(F18-F17)</f>
+        <f>F18*F14</f>
         <v/>
       </c>
       <c r="G48" s="32">
-        <f>G14*(G18-G17)</f>
+        <f>G18*G14</f>
         <v/>
       </c>
       <c r="H48" s="32">
-        <f>H14*(H18-H17)</f>
+        <f>H18*H14</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔNWC – year 3</t>
+          <t xml:space="preserve">  Accounts receivable – year 2</t>
         </is>
       </c>
       <c r="F49" s="32">
-        <f>F14*(F19-F18)</f>
+        <f>F19*F14</f>
         <v/>
       </c>
       <c r="G49" s="32">
-        <f>G14*(G19-G18)</f>
+        <f>G19*G14</f>
         <v/>
       </c>
       <c r="H49" s="32">
-        <f>H14*(H19-H18)</f>
+        <f>H19*H14</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔNWC – year 4</t>
+          <t xml:space="preserve">  Accounts receivable – year 3</t>
         </is>
       </c>
       <c r="F50" s="32">
-        <f>F14*(F20-F19)</f>
+        <f>F20*F14</f>
         <v/>
       </c>
       <c r="G50" s="32">
-        <f>G14*(G20-G19)</f>
+        <f>G20*G14</f>
         <v/>
       </c>
       <c r="H50" s="32">
-        <f>H14*(H20-H19)</f>
+        <f>H20*H14</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔNWC – year 5</t>
+          <t xml:space="preserve">  Accounts receivable – year 4</t>
         </is>
       </c>
       <c r="F51" s="32">
-        <f>F14*(F21-F20)</f>
+        <f>F21*F14</f>
         <v/>
       </c>
       <c r="G51" s="32">
-        <f>G14*(G21-G20)</f>
+        <f>G21*G14</f>
         <v/>
       </c>
       <c r="H51" s="32">
-        <f>H14*(H21-H20)</f>
+        <f>H21*H14</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 1</t>
+          <t xml:space="preserve">  Accounts receivable – year 5</t>
         </is>
       </c>
       <c r="F52" s="32">
-        <f>F32+F37-F42-F47</f>
+        <f>F22*F14</f>
         <v/>
       </c>
       <c r="G52" s="32">
-        <f>G32+G37-G42-G47</f>
+        <f>G22*G14</f>
         <v/>
       </c>
       <c r="H52" s="32">
-        <f>H32+H37-H42-H47</f>
+        <f>H22*H14</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 2</t>
+          <t xml:space="preserve">  ΔAR – year 1</t>
         </is>
       </c>
       <c r="F53" s="32">
-        <f>F33+F38-F43-F48</f>
+        <f>F48-190657</f>
         <v/>
       </c>
       <c r="G53" s="32">
-        <f>G33+G38-G43-G48</f>
+        <f>G48-190657</f>
         <v/>
       </c>
       <c r="H53" s="32">
-        <f>H33+H38-H43-H48</f>
+        <f>H48-190657</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 3</t>
+          <t xml:space="preserve">  ΔAR – year 2</t>
         </is>
       </c>
       <c r="F54" s="32">
-        <f>F34+F39-F44-F49</f>
+        <f>F49-F48</f>
         <v/>
       </c>
       <c r="G54" s="32">
-        <f>G34+G39-G44-G49</f>
+        <f>G49-G48</f>
         <v/>
       </c>
       <c r="H54" s="32">
-        <f>H34+H39-H44-H49</f>
+        <f>H49-H48</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Unlevered FCF – year 4</t>
+          <t xml:space="preserve">  ΔAR – year 3</t>
         </is>
       </c>
       <c r="F55" s="32">
-        <f>F35+F40-F45-F50</f>
+        <f>F50-F49</f>
         <v/>
       </c>
       <c r="G55" s="32">
-        <f>G35+G40-G45-G50</f>
+        <f>G50-G49</f>
         <v/>
       </c>
       <c r="H55" s="32">
-        <f>H35+H40-H45-H50</f>
+        <f>H50-H49</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
+          <t xml:space="preserve">  ΔAR – year 4</t>
+        </is>
+      </c>
+      <c r="F56" s="32">
+        <f>F51-F50</f>
+        <v/>
+      </c>
+      <c r="G56" s="32">
+        <f>G51-G50</f>
+        <v/>
+      </c>
+      <c r="H56" s="32">
+        <f>H51-H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔAR – year 5</t>
+        </is>
+      </c>
+      <c r="F57" s="32">
+        <f>F52-F51</f>
+        <v/>
+      </c>
+      <c r="G57" s="32">
+        <f>G52-G51</f>
+        <v/>
+      </c>
+      <c r="H57" s="32">
+        <f>H52-H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 1</t>
+        </is>
+      </c>
+      <c r="F58" s="32">
+        <f>F15*(F18-11102600)</f>
+        <v/>
+      </c>
+      <c r="G58" s="32">
+        <f>G15*(G18-11102600)</f>
+        <v/>
+      </c>
+      <c r="H58" s="32">
+        <f>H15*(H18-11102600)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 2</t>
+        </is>
+      </c>
+      <c r="F59" s="32">
+        <f>F15*(F19-F18)</f>
+        <v/>
+      </c>
+      <c r="G59" s="32">
+        <f>G15*(G19-G18)</f>
+        <v/>
+      </c>
+      <c r="H59" s="32">
+        <f>H15*(H19-H18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 3</t>
+        </is>
+      </c>
+      <c r="F60" s="32">
+        <f>F15*(F20-F19)</f>
+        <v/>
+      </c>
+      <c r="G60" s="32">
+        <f>G15*(G20-G19)</f>
+        <v/>
+      </c>
+      <c r="H60" s="32">
+        <f>H15*(H20-H19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 4</t>
+        </is>
+      </c>
+      <c r="F61" s="32">
+        <f>F15*(F21-F20)</f>
+        <v/>
+      </c>
+      <c r="G61" s="32">
+        <f>G15*(G21-G20)</f>
+        <v/>
+      </c>
+      <c r="H61" s="32">
+        <f>H15*(H21-H20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 5</t>
+        </is>
+      </c>
+      <c r="F62" s="32">
+        <f>F15*(F22-F21)</f>
+        <v/>
+      </c>
+      <c r="G62" s="32">
+        <f>G15*(G22-G21)</f>
+        <v/>
+      </c>
+      <c r="H62" s="32">
+        <f>H15*(H22-H21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 1</t>
+        </is>
+      </c>
+      <c r="F63" s="32">
+        <f>F53+F58</f>
+        <v/>
+      </c>
+      <c r="G63" s="32">
+        <f>G53+G58</f>
+        <v/>
+      </c>
+      <c r="H63" s="32">
+        <f>H53+H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 2</t>
+        </is>
+      </c>
+      <c r="F64" s="32">
+        <f>F54+F59</f>
+        <v/>
+      </c>
+      <c r="G64" s="32">
+        <f>G54+G59</f>
+        <v/>
+      </c>
+      <c r="H64" s="32">
+        <f>H54+H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 3</t>
+        </is>
+      </c>
+      <c r="F65" s="32">
+        <f>F55+F60</f>
+        <v/>
+      </c>
+      <c r="G65" s="32">
+        <f>G55+G60</f>
+        <v/>
+      </c>
+      <c r="H65" s="32">
+        <f>H55+H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 4</t>
+        </is>
+      </c>
+      <c r="F66" s="32">
+        <f>F56+F61</f>
+        <v/>
+      </c>
+      <c r="G66" s="32">
+        <f>G56+G61</f>
+        <v/>
+      </c>
+      <c r="H66" s="32">
+        <f>H56+H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔNWC – year 5</t>
+        </is>
+      </c>
+      <c r="F67" s="32">
+        <f>F57+F62</f>
+        <v/>
+      </c>
+      <c r="G67" s="32">
+        <f>G57+G62</f>
+        <v/>
+      </c>
+      <c r="H67" s="32">
+        <f>H57+H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 1</t>
+        </is>
+      </c>
+      <c r="F68" s="32">
+        <f>F33+F38-F43-F63</f>
+        <v/>
+      </c>
+      <c r="G68" s="32">
+        <f>G33+G38-G43-G63</f>
+        <v/>
+      </c>
+      <c r="H68" s="32">
+        <f>H33+H38-H43-H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 2</t>
+        </is>
+      </c>
+      <c r="F69" s="32">
+        <f>F34+F39-F44-F64</f>
+        <v/>
+      </c>
+      <c r="G69" s="32">
+        <f>G34+G39-G44-G64</f>
+        <v/>
+      </c>
+      <c r="H69" s="32">
+        <f>H34+H39-H44-H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 3</t>
+        </is>
+      </c>
+      <c r="F70" s="32">
+        <f>F35+F40-F45-F65</f>
+        <v/>
+      </c>
+      <c r="G70" s="32">
+        <f>G35+G40-G45-G65</f>
+        <v/>
+      </c>
+      <c r="H70" s="32">
+        <f>H35+H40-H45-H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Unlevered FCF – year 4</t>
+        </is>
+      </c>
+      <c r="F71" s="32">
+        <f>F36+F41-F46-F66</f>
+        <v/>
+      </c>
+      <c r="G71" s="32">
+        <f>G36+G41-G46-G66</f>
+        <v/>
+      </c>
+      <c r="H71" s="32">
+        <f>H36+H41-H46-H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F56" s="32">
-        <f>F36+F41-F46-F51</f>
-        <v/>
-      </c>
-      <c r="G56" s="32">
-        <f>G36+G41-G46-G51</f>
-        <v/>
-      </c>
-      <c r="H56" s="32">
-        <f>H36+H41-H46-H51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="F72" s="32">
+        <f>F37+F42-F47-F67</f>
+        <v/>
+      </c>
+      <c r="G72" s="32">
+        <f>G37+G42-G47-G67</f>
+        <v/>
+      </c>
+      <c r="H72" s="32">
+        <f>H37+H42-H47-H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F58" s="34">
-        <f>NPV(F9,F52,F53,F54,F55,F56)+(F56*(1+F10)/(F9-F10))/(1+F9)^5</f>
-        <v/>
-      </c>
-      <c r="G58" s="34">
-        <f>NPV(G9,G52,G53,G54,G55,G56)+(G56*(1+G10)/(G9-G10))/(1+G9)^5</f>
-        <v/>
-      </c>
-      <c r="H58" s="34">
-        <f>NPV(H9,H52,H53,H54,H55,H56)+(H56*(1+H10)/(H9-H10))/(1+H9)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="35" t="inlineStr">
+      <c r="F74" s="34">
+        <f>NPV(F9,F68,F69,F70,F71,F72)+(F72*(1+F10)/(F9-F10))/(1+F9)^5</f>
+        <v/>
+      </c>
+      <c r="G74" s="34">
+        <f>NPV(G9,G68,G69,G70,G71,G72)+(G72*(1+G10)/(G9-G10))/(1+G9)^5</f>
+        <v/>
+      </c>
+      <c r="H74" s="34">
+        <f>NPV(H9,H68,H69,H70,H71,H72)+(H72*(1+H10)/(H9-H10))/(1+H9)^5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="35" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F59" s="36">
-        <f>(F58+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="G59" s="37">
-        <f>(G58+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="H59" s="36">
-        <f>(H58+1807202-0)/111380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="22" t="inlineStr">
+      <c r="F75" s="36">
+        <f>(F74+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="G75" s="37">
+        <f>(G74+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="H75" s="36">
+        <f>(H74+1807202-0)/111380</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F60" s="38">
-        <f>F59/100.0-1</f>
-        <v/>
-      </c>
-      <c r="G60" s="38">
-        <f>G59/100.0-1</f>
-        <v/>
-      </c>
-      <c r="H60" s="38">
-        <f>H59/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="39" t="inlineStr">
+      <c r="F76" s="38">
+        <f>F75/100.0-1</f>
+        <v/>
+      </c>
+      <c r="G76" s="38">
+        <f>G75/100.0-1</f>
+        <v/>
+      </c>
+      <c r="H76" s="38">
+        <f>H75/100.0-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="39" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2650,6 +2966,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2661,7 +2978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2789,27 +3106,27 @@
         <v>11102600</v>
       </c>
       <c r="F5" s="48">
-        <f>Scenarios!G17</f>
+        <f>Scenarios!G18</f>
         <v/>
       </c>
       <c r="G5" s="48">
-        <f>Scenarios!G18</f>
+        <f>Scenarios!G19</f>
         <v/>
       </c>
       <c r="H5" s="48">
-        <f>Scenarios!G19</f>
+        <f>Scenarios!G20</f>
         <v/>
       </c>
       <c r="I5" s="48">
-        <f>Scenarios!G20</f>
+        <f>Scenarios!G21</f>
         <v/>
       </c>
       <c r="J5" s="48">
-        <f>Scenarios!G21</f>
+        <f>Scenarios!G22</f>
         <v/>
       </c>
       <c r="K5" s="49">
-        <f>IF(MAX(ABS(F5-Scenarios!$G$17),ABS(G5-Scenarios!$G$18),ABS(H5-Scenarios!$G$19),ABS(I5-Scenarios!$G$20),ABS(J5-Scenarios!$G$21))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F5-Scenarios!$G$18),ABS(G5-Scenarios!$G$19),ABS(H5-Scenarios!$G$20),ABS(I5-Scenarios!$G$21),ABS(J5-Scenarios!$G$22))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2883,27 +3200,27 @@
         </is>
       </c>
       <c r="F7" s="50">
-        <f>Scenarios!G22</f>
+        <f>Scenarios!G23</f>
         <v/>
       </c>
       <c r="G7" s="50">
-        <f>Scenarios!G23</f>
+        <f>Scenarios!G24</f>
         <v/>
       </c>
       <c r="H7" s="50">
-        <f>Scenarios!G24</f>
+        <f>Scenarios!G25</f>
         <v/>
       </c>
       <c r="I7" s="50">
-        <f>Scenarios!G25</f>
+        <f>Scenarios!G26</f>
         <v/>
       </c>
       <c r="J7" s="50">
-        <f>Scenarios!G26</f>
+        <f>Scenarios!G27</f>
         <v/>
       </c>
       <c r="K7" s="49">
-        <f>IF(MAX(ABS(F7-Scenarios!$G$22),ABS(G7-Scenarios!$G$23),ABS(H7-Scenarios!$G$24),ABS(I7-Scenarios!$G$25),ABS(J7-Scenarios!$G$26))&lt;0.0001,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F7-Scenarios!$G$23),ABS(G7-Scenarios!$G$24),ABS(H7-Scenarios!$G$25),ABS(I7-Scenarios!$G$26),ABS(J7-Scenarios!$G$27))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -2958,27 +3275,27 @@
         <v>2210615</v>
       </c>
       <c r="F9" s="34">
-        <f>Scenarios!G27</f>
+        <f>Scenarios!G28</f>
         <v/>
       </c>
       <c r="G9" s="34">
-        <f>Scenarios!G28</f>
+        <f>Scenarios!G29</f>
         <v/>
       </c>
       <c r="H9" s="34">
-        <f>Scenarios!G29</f>
+        <f>Scenarios!G30</f>
         <v/>
       </c>
       <c r="I9" s="34">
-        <f>Scenarios!G30</f>
+        <f>Scenarios!G31</f>
         <v/>
       </c>
       <c r="J9" s="34">
-        <f>Scenarios!G31</f>
+        <f>Scenarios!G32</f>
         <v/>
       </c>
       <c r="K9" s="52">
-        <f>IF(MAX(ABS(F9-Scenarios!$G$27),ABS(G9-Scenarios!$G$28),ABS(H9-Scenarios!$G$29),ABS(I9-Scenarios!$G$30),ABS(J9-Scenarios!$G$31))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F9-Scenarios!$G$28),ABS(G9-Scenarios!$G$29),ABS(H9-Scenarios!$G$30),ABS(I9-Scenarios!$G$31),ABS(J9-Scenarios!$G$32))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3019,23 +3336,23 @@
         </is>
       </c>
       <c r="F11" s="48">
-        <f>-Scenarios!G27*Scenarios!$G$11</f>
+        <f>-Scenarios!G28*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="G11" s="48">
-        <f>-Scenarios!G28*Scenarios!$G$11</f>
+        <f>-Scenarios!G29*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="H11" s="48">
-        <f>-Scenarios!G29*Scenarios!$G$11</f>
+        <f>-Scenarios!G30*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="I11" s="48">
-        <f>-Scenarios!G30*Scenarios!$G$11</f>
+        <f>-Scenarios!G31*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="J11" s="48">
-        <f>-Scenarios!G31*Scenarios!$G$11</f>
+        <f>-Scenarios!G32*Scenarios!$G$11</f>
         <v/>
       </c>
     </row>
@@ -3046,27 +3363,27 @@
         </is>
       </c>
       <c r="F12" s="34">
-        <f>Scenarios!G32</f>
+        <f>Scenarios!G33</f>
         <v/>
       </c>
       <c r="G12" s="34">
-        <f>Scenarios!G33</f>
+        <f>Scenarios!G34</f>
         <v/>
       </c>
       <c r="H12" s="34">
-        <f>Scenarios!G34</f>
+        <f>Scenarios!G35</f>
         <v/>
       </c>
       <c r="I12" s="34">
-        <f>Scenarios!G35</f>
+        <f>Scenarios!G36</f>
         <v/>
       </c>
       <c r="J12" s="34">
-        <f>Scenarios!G36</f>
+        <f>Scenarios!G37</f>
         <v/>
       </c>
       <c r="K12" s="52">
-        <f>IF(MAX(ABS(F12-Scenarios!$G$32),ABS(G12-Scenarios!$G$33),ABS(H12-Scenarios!$G$34),ABS(I12-Scenarios!$G$35),ABS(J12-Scenarios!$G$36))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F12-Scenarios!$G$33),ABS(G12-Scenarios!$G$34),ABS(H12-Scenarios!$G$35),ABS(I12-Scenarios!$G$36),ABS(J12-Scenarios!$G$37))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3119,27 +3436,27 @@
         </is>
       </c>
       <c r="F14" s="48">
-        <f>Scenarios!G37</f>
+        <f>Scenarios!G38</f>
         <v/>
       </c>
       <c r="G14" s="48">
-        <f>Scenarios!G38</f>
+        <f>Scenarios!G39</f>
         <v/>
       </c>
       <c r="H14" s="48">
-        <f>Scenarios!G39</f>
+        <f>Scenarios!G40</f>
         <v/>
       </c>
       <c r="I14" s="48">
-        <f>Scenarios!G40</f>
+        <f>Scenarios!G41</f>
         <v/>
       </c>
       <c r="J14" s="48">
-        <f>Scenarios!G41</f>
+        <f>Scenarios!G42</f>
         <v/>
       </c>
       <c r="K14" s="49">
-        <f>IF(MAX(ABS(F14-Scenarios!$G$37),ABS(G14-Scenarios!$G$38),ABS(H14-Scenarios!$G$39),ABS(I14-Scenarios!$G$40),ABS(J14-Scenarios!$G$41))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F14-Scenarios!$G$38),ABS(G14-Scenarios!$G$39),ABS(H14-Scenarios!$G$40),ABS(I14-Scenarios!$G$41),ABS(J14-Scenarios!$G$42))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
@@ -3205,49 +3522,49 @@
         </is>
       </c>
       <c r="F16" s="48">
-        <f>-Scenarios!G42</f>
+        <f>-Scenarios!G43</f>
         <v/>
       </c>
       <c r="G16" s="48">
-        <f>-Scenarios!G43</f>
+        <f>-Scenarios!G44</f>
         <v/>
       </c>
       <c r="H16" s="48">
-        <f>-Scenarios!G44</f>
+        <f>-Scenarios!G45</f>
         <v/>
       </c>
       <c r="I16" s="48">
-        <f>-Scenarios!G45</f>
+        <f>-Scenarios!G46</f>
         <v/>
       </c>
       <c r="J16" s="48">
-        <f>-Scenarios!G46</f>
+        <f>-Scenarios!G47</f>
         <v/>
       </c>
       <c r="K16" s="49">
-        <f>IF(MAX(ABS(F16+Scenarios!$G$42),ABS(G16+Scenarios!$G$43),ABS(H16+Scenarios!$G$44),ABS(I16+Scenarios!$G$45),ABS(J16+Scenarios!$G$46))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F16+Scenarios!$G$43),ABS(G16+Scenarios!$G$44),ABS(H16+Scenarios!$G$45),ABS(I16+Scenarios!$G$46),ABS(J16+Scenarios!$G$47))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NWC build % of Δrevenue</t>
+          <t xml:space="preserve">  AR % of revenue</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>7.5% of Δsales is operating NWC: AR + inventory + other CA − AP − accrued. AR is on the 10-K ($190,657); not omitted.</t>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)</t>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" → 190,657. Ctrl+F "Inventories" → 1,700,753. Ctrl+F "Accounts payable" → 331,421. Ctrl+F "Accrued liabilities and other" → 662,982. NWC = AR + Inv + other CA − AP − accrued; 7.5% of Δsales.</t>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
         </is>
       </c>
       <c r="F17" s="20">
@@ -3271,857 +3588,1010 @@
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>(Increase)/decrease in net working capital</t>
-        </is>
+          <t>Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
+        </is>
+      </c>
+      <c r="E18" s="47" t="n">
+        <v>190657</v>
       </c>
       <c r="F18" s="48">
-        <f>-Scenarios!G47</f>
+        <f>Scenarios!G48</f>
         <v/>
       </c>
       <c r="G18" s="48">
-        <f>-Scenarios!G48</f>
+        <f>Scenarios!G49</f>
         <v/>
       </c>
       <c r="H18" s="48">
-        <f>-Scenarios!G49</f>
+        <f>Scenarios!G50</f>
         <v/>
       </c>
       <c r="I18" s="48">
-        <f>-Scenarios!G50</f>
+        <f>Scenarios!G51</f>
         <v/>
       </c>
       <c r="J18" s="48">
-        <f>-Scenarios!G51</f>
+        <f>Scenarios!G52</f>
         <v/>
       </c>
       <c r="K18" s="49">
-        <f>IF(MAX(ABS(F18+Scenarios!$G$47),ABS(G18+Scenarios!$G$48),ABS(H18+Scenarios!$G$49),ABS(I18+Scenarios!$G$50),ABS(J18+Scenarios!$G$51))&lt;0.5,"OK","CHECK")</f>
+        <f>IF(MAX(ABS(F18-Scenarios!$G$48),ABS(G18-Scenarios!$G$49),ABS(H18-Scenarios!$G$50),ABS(I18-Scenarios!$G$51),ABS(J18-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  memo: FY26 revenue falls −6.1%; negative ΔNWC releases ~$51M cash (adds to FCF, not a use).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow</t>
-        </is>
-      </c>
-      <c r="F20" s="54">
-        <f>Scenarios!G52</f>
-        <v/>
-      </c>
-      <c r="G20" s="54">
-        <f>Scenarios!G53</f>
-        <v/>
-      </c>
-      <c r="H20" s="54">
-        <f>Scenarios!G54</f>
-        <v/>
-      </c>
-      <c r="I20" s="54">
-        <f>Scenarios!G55</f>
-        <v/>
-      </c>
-      <c r="J20" s="54">
-        <f>Scenarios!G56</f>
-        <v/>
-      </c>
-      <c r="K20" s="52">
-        <f>IF(MAX(ABS(F20-Scenarios!$G$52),ABS(G20-Scenarios!$G$53),ABS(H20-Scenarios!$G$54),ABS(I20-Scenarios!$G$55),ABS(J20-Scenarios!$G$56))&lt;0.5,"OK","CHECK")</f>
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ΔAR (increase)/decrease — part of NWC</t>
+        </is>
+      </c>
+      <c r="F19" s="48">
+        <f>-Scenarios!G53</f>
+        <v/>
+      </c>
+      <c r="G19" s="48">
+        <f>-Scenarios!G54</f>
+        <v/>
+      </c>
+      <c r="H19" s="48">
+        <f>-Scenarios!G55</f>
+        <v/>
+      </c>
+      <c r="I19" s="48">
+        <f>-Scenarios!G56</f>
+        <v/>
+      </c>
+      <c r="J19" s="48">
+        <f>-Scenarios!G57</f>
+        <v/>
+      </c>
+      <c r="K19" s="49">
+        <f>IF(MAX(ABS(F19+Scenarios!$G$53),ABS(G19+Scenarios!$G$54),ABS(H19+Scenarios!$G$55),ABS(I19+Scenarios!$G$56),ABS(J19+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Other NWC (ex-AR) % of Δrevenue</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>5.8% of Δsales is other NWC (Inv + OCA − AP − accrued). AR is the 1.7% line above, not inside this residual. 1.7+5.8=7.5%.</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>LULU BS/IS historical (10-K)</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>Other NWC ex-AR. Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 5.8% of Δsales; AR is the 1.7% line, not in this residual.</t>
+        </is>
+      </c>
+      <c r="F20" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="I20" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="J20" s="20">
+        <f>Scenarios!$G$15</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Discount period (years)</t>
-        </is>
-      </c>
-      <c r="F21" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" s="55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" s="55" t="n">
-        <v>5</v>
+          <t xml:space="preserve">  Other ΔNWC (ex-AR) (increase)/decrease</t>
+        </is>
+      </c>
+      <c r="F21" s="48">
+        <f>-Scenarios!G58</f>
+        <v/>
+      </c>
+      <c r="G21" s="48">
+        <f>-Scenarios!G59</f>
+        <v/>
+      </c>
+      <c r="H21" s="48">
+        <f>-Scenarios!G60</f>
+        <v/>
+      </c>
+      <c r="I21" s="48">
+        <f>-Scenarios!G61</f>
+        <v/>
+      </c>
+      <c r="J21" s="48">
+        <f>-Scenarios!G62</f>
+        <v/>
+      </c>
+      <c r="K21" s="49">
+        <f>IF(MAX(ABS(F21+Scenarios!$G$58),ABS(G21+Scenarios!$G$59),ABS(H21+Scenarios!$G$60),ABS(I21+Scenarios!$G$61),ABS(J21+Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
+          <t>Total (increase)/decrease in net working capital</t>
+        </is>
+      </c>
+      <c r="F22" s="48">
+        <f>-Scenarios!G63</f>
+        <v/>
+      </c>
+      <c r="G22" s="48">
+        <f>-Scenarios!G64</f>
+        <v/>
+      </c>
+      <c r="H22" s="48">
+        <f>-Scenarios!G65</f>
+        <v/>
+      </c>
+      <c r="I22" s="48">
+        <f>-Scenarios!G66</f>
+        <v/>
+      </c>
+      <c r="J22" s="48">
+        <f>-Scenarios!G67</f>
+        <v/>
+      </c>
+      <c r="K22" s="49">
+        <f>IF(MAX(ABS(F22+Scenarios!$G$63),ABS(G22+Scenarios!$G$64),ABS(H22+Scenarios!$G$65),ABS(I22+Scenarios!$G$66),ABS(J22+Scenarios!$G$67))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: ΔNWC = ΔAR + other ΔNWC. AR is 1.7% of sales (own line); other is 5.8% of Δsales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="F24" s="54">
+        <f>Scenarios!G68</f>
+        <v/>
+      </c>
+      <c r="G24" s="54">
+        <f>Scenarios!G69</f>
+        <v/>
+      </c>
+      <c r="H24" s="54">
+        <f>Scenarios!G70</f>
+        <v/>
+      </c>
+      <c r="I24" s="54">
+        <f>Scenarios!G71</f>
+        <v/>
+      </c>
+      <c r="J24" s="54">
+        <f>Scenarios!G72</f>
+        <v/>
+      </c>
+      <c r="K24" s="52">
+        <f>IF(MAX(ABS(F24-Scenarios!$G$68),ABS(G24-Scenarios!$G$69),ABS(H24-Scenarios!$G$70),ABS(I24-Scenarios!$G$71),ABS(J24-Scenarios!$G$72))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="F25" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" s="55" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="F22" s="56">
-        <f>1/(1+Scenarios!$G$9)^F21</f>
-        <v/>
-      </c>
-      <c r="G22" s="56">
-        <f>1/(1+Scenarios!$G$9)^G21</f>
-        <v/>
-      </c>
-      <c r="H22" s="56">
-        <f>1/(1+Scenarios!$G$9)^H21</f>
-        <v/>
-      </c>
-      <c r="I22" s="56">
-        <f>1/(1+Scenarios!$G$9)^I21</f>
-        <v/>
-      </c>
-      <c r="J22" s="56">
-        <f>1/(1+Scenarios!$G$9)^J21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>PV of unlevered FCF</t>
-        </is>
-      </c>
-      <c r="F23" s="34">
-        <f>F20*F22</f>
-        <v/>
-      </c>
-      <c r="G23" s="34">
-        <f>G20*G22</f>
-        <v/>
-      </c>
-      <c r="H23" s="34">
-        <f>H20*H22</f>
-        <v/>
-      </c>
-      <c r="I23" s="34">
-        <f>I20*I22</f>
-        <v/>
-      </c>
-      <c r="J23" s="34">
-        <f>J20*J22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Scenarios linkage summary (column K should all read OK)</t>
-        </is>
-      </c>
-      <c r="K25" s="57">
-        <f>IF(COUNTIF(K5:K20,"CHECK")=0,"ALL OK","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="58" t="inlineStr">
-        <is>
-          <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
+      <c r="F26" s="56">
+        <f>1/(1+Scenarios!$G$9)^F25</f>
+        <v/>
+      </c>
+      <c r="G26" s="56">
+        <f>1/(1+Scenarios!$G$9)^G25</f>
+        <v/>
+      </c>
+      <c r="H26" s="56">
+        <f>1/(1+Scenarios!$G$9)^H25</f>
+        <v/>
+      </c>
+      <c r="I26" s="56">
+        <f>1/(1+Scenarios!$G$9)^I25</f>
+        <v/>
+      </c>
+      <c r="J26" s="56">
+        <f>1/(1+Scenarios!$G$9)^J25</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
+          <t>PV of unlevered FCF</t>
+        </is>
+      </c>
+      <c r="F27" s="34">
+        <f>F24*F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>G24*G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>H24*H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="34">
+        <f>I24*I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="34">
+        <f>J24*J26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Scenarios linkage summary (column K should all read OK)</t>
+        </is>
+      </c>
+      <c r="K29" s="57">
+        <f>IF(COUNTIF(K5:K24,"CHECK")=0,"ALL OK","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="58" t="inlineStr">
+        <is>
+          <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n"/>
+      <c r="C30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="E27" s="59">
-        <f>SUM(F23:J23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="E31" s="59">
+        <f>SUM(F27:J27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Terminal growth rate (g)</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C32" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
+      <c r="D32" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
-      <c r="E28" s="50">
+      <c r="E32" s="50">
         <f>Scenarios!$G$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="E29" s="34">
-        <f>J9+J14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="E30" s="48">
-        <f>J20*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
-        </is>
-      </c>
-      <c r="E31" s="60">
-        <f>E30/E29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="22" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="E32" s="59">
-        <f>E30/(1+Scenarios!$G$9)^J21</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
+          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
       <c r="E33" s="34">
-        <f>E27+E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
+        <f>J9+J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C34" s="61" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
-        </is>
-      </c>
-      <c r="E34" s="47" t="n">
-        <v>1807202</v>
-      </c>
-    </row>
-    <row r="35" ht="28" customHeight="1">
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="E34" s="48">
+        <f>J24*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>Less: total debt</t>
-        </is>
-      </c>
-      <c r="C35" s="61" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
-        </is>
-      </c>
-      <c r="E35" s="47" t="n">
-        <v>0</v>
+          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
+        </is>
+      </c>
+      <c r="E35" s="60">
+        <f>E34/E33</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="E36" s="34">
-        <f>E33+E34+E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Diluted shares outstanding (000)</t>
-        </is>
-      </c>
-      <c r="C37" s="61" t="inlineStr">
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="E36" s="59">
+        <f>E34/(1+Scenarios!$G$9)^J25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="E37" s="34">
+        <f>E31+E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C38" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
-        </is>
-      </c>
-      <c r="E37" s="47" t="n">
-        <v>111380</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="22" t="inlineStr">
-        <is>
-          <t>Implied value per share</t>
-        </is>
-      </c>
-      <c r="E38" s="62">
-        <f>E36/E37</f>
-        <v/>
-      </c>
-      <c r="K38" s="52">
-        <f>IF(ABS(E38-Scenarios!$G$59)&lt;0.05,"OK","CHECK")</f>
-        <v/>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
+        </is>
+      </c>
+      <c r="E38" s="47" t="n">
+        <v>1807202</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Current share price</t>
+          <t>Less: total debt</t>
         </is>
       </c>
       <c r="C39" s="61" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>10-K</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
-        </is>
-      </c>
-      <c r="E39" s="63" t="n">
-        <v>100</v>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
+        </is>
+      </c>
+      <c r="E39" s="47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="E40" s="34">
+        <f>E37+E38+E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Diluted shares outstanding (000)</t>
+        </is>
+      </c>
+      <c r="C41" s="61" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
+        </is>
+      </c>
+      <c r="E41" s="47" t="n">
+        <v>111380</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>Implied value per share</t>
+        </is>
+      </c>
+      <c r="E42" s="62">
+        <f>E40/E41</f>
+        <v/>
+      </c>
+      <c r="K42" s="52">
+        <f>IF(ABS(E42-Scenarios!$G$75)&lt;0.05,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="C43" s="61" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
+        </is>
+      </c>
+      <c r="E43" s="63" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="E40" s="64">
-        <f>E38/E39-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="E44" s="64">
+        <f>E42/E43-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="E41" s="50">
-        <f>E32/E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="58" t="inlineStr">
+      <c r="E45" s="50">
+        <f>E36/E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="58" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n"/>
-      <c r="C43" s="13" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="B47" s="13" t="n"/>
+      <c r="C47" s="13" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>Exit multiple selection (see Comps tab for peer build)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C49" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D49" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E45" s="65" t="n">
+      <c r="E49" s="65" t="n">
         <v>8</v>
       </c>
-      <c r="M45" s="61" t="inlineStr">
+      <c r="M49" s="61" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="E46" s="48">
-        <f>E29*E45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="E50" s="48">
+        <f>E33*E49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E47" s="48">
-        <f>E46/(1+Scenarios!$G$9)^J21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="22" t="inlineStr">
+      <c r="E51" s="48">
+        <f>E50/(1+Scenarios!$G$9)^J25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E48" s="34">
-        <f>E27+E47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="22" t="inlineStr">
-        <is>
-          <t>Implied value per share (exit method)</t>
-        </is>
-      </c>
-      <c r="E49" s="66">
-        <f>(E48+E34+E35)/E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="58" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="67" t="inlineStr"/>
-      <c r="B52" s="68" t="inlineStr">
-        <is>
-          <t>Gordon Growth</t>
-        </is>
-      </c>
-      <c r="C52" s="68" t="inlineStr">
-        <is>
-          <t>Exit Multiple</t>
-        </is>
-      </c>
-      <c r="D52" s="68" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
+      <c r="E52" s="34">
+        <f>E31+E51</f>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
+          <t>Implied value per share (exit method)</t>
+        </is>
+      </c>
+      <c r="E53" s="66">
+        <f>(E52+E38+E39)/E41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="58" t="inlineStr">
+        <is>
+          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="n"/>
+      <c r="C55" s="13" t="n"/>
+      <c r="D55" s="13" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="67" t="inlineStr"/>
+      <c r="B56" s="68" t="inlineStr">
+        <is>
+          <t>Gordon Growth</t>
+        </is>
+      </c>
+      <c r="C56" s="68" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D56" s="68" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B53" s="59">
-        <f>E30</f>
-        <v/>
-      </c>
-      <c r="C53" s="59">
-        <f>E46</f>
-        <v/>
-      </c>
-      <c r="D53" s="59">
-        <f>B53-C53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="22" t="inlineStr">
+      <c r="B57" s="59">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="C57" s="59">
+        <f>E50</f>
+        <v/>
+      </c>
+      <c r="D57" s="59">
+        <f>B57-C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B54" s="69">
-        <f>E31</f>
-        <v/>
-      </c>
-      <c r="C54" s="69">
-        <f>E45</f>
-        <v/>
-      </c>
-      <c r="D54" s="69">
-        <f>B54-C54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="B58" s="69">
+        <f>E35</f>
+        <v/>
+      </c>
+      <c r="C58" s="69">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="D58" s="69">
+        <f>B58-C58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B55" s="50" t="inlineStr"/>
-      <c r="C55" s="50" t="inlineStr"/>
-      <c r="D55" s="50">
-        <f>(B53-C53)/B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="B59" s="50" t="inlineStr"/>
+      <c r="C59" s="50" t="inlineStr"/>
+      <c r="D59" s="50">
+        <f>(B57-C57)/B57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B56" s="70">
-        <f>E38</f>
-        <v/>
-      </c>
-      <c r="C56" s="70">
-        <f>E49</f>
-        <v/>
-      </c>
-      <c r="D56" s="70">
-        <f>B56-C56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="71" t="inlineStr">
+      <c r="B60" s="70">
+        <f>E42</f>
+        <v/>
+      </c>
+      <c r="C60" s="70">
+        <f>E53</f>
+        <v/>
+      </c>
+      <c r="D60" s="70">
+        <f>B60-C60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="71" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B57" s="72">
-        <f>IF(ABS(D54)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C57" s="73">
-        <f>TEXT(D54,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D57" s="39" t="inlineStr">
+      <c r="B61" s="72">
+        <f>IF(ABS(D58)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C61" s="73">
+        <f>TEXT(D58,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D61" s="39" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="58" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="58" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n"/>
-      <c r="C60" s="13" t="n"/>
-      <c r="D60" s="13" t="n"/>
-      <c r="E60" s="13" t="n"/>
-      <c r="F60" s="13" t="n"/>
-      <c r="G60" s="13" t="n"/>
-      <c r="H60" s="13" t="n"/>
-    </row>
-    <row r="61" ht="28" customHeight="1">
-      <c r="A61" s="74" t="inlineStr">
+      <c r="B64" s="13" t="n"/>
+      <c r="C64" s="13" t="n"/>
+      <c r="D64" s="13" t="n"/>
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="13" t="n"/>
+      <c r="G64" s="13" t="n"/>
+      <c r="H64" s="13" t="n"/>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="74" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C65" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
-      <c r="F61" s="75" t="n">
+      <c r="F65" s="75" t="n">
         <v>0.015</v>
       </c>
-      <c r="G61" s="75" t="n">
+      <c r="G65" s="75" t="n">
         <v>0.02</v>
       </c>
-      <c r="H61" s="75" t="n">
+      <c r="H65" s="75" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I61" s="75" t="n">
+      <c r="I65" s="75" t="n">
         <v>0.025</v>
       </c>
-      <c r="J61" s="75" t="n">
+      <c r="J65" s="75" t="n">
         <v>0.03</v>
       </c>
-      <c r="L61" s="61" t="inlineStr">
+      <c r="L65" s="61" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="75" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C62" s="61" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
-      </c>
-      <c r="D62" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F62" s="76">
-        <f>(NPV(0.095,F20:J20)+(J20*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="G62" s="76">
-        <f>(NPV(0.095,F20:J20)+(J20*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="H62" s="76">
-        <f>(NPV(0.095,F20:J20)+(J20*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="I62" s="76">
-        <f>(NPV(0.095,F20:J20)+(J20*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="J62" s="76">
-        <f>(NPV(0.095,F20:J20)+(J20*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="L62" s="61" t="inlineStr">
-        <is>
-          <t>WACC tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F63" s="76">
-        <f>(NPV(0.1,F20:J20)+(J20*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="G63" s="76">
-        <f>(NPV(0.1,F20:J20)+(J20*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="H63" s="76">
-        <f>(NPV(0.1,F20:J20)+(J20*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="I63" s="76">
-        <f>(NPV(0.1,F20:J20)+(J20*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="J63" s="76">
-        <f>(NPV(0.1,F20:J20)+(J20*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="L63" s="61" t="inlineStr">
-        <is>
-          <t>WACC tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="75" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F64" s="76">
-        <f>(NPV(0.105,F20:J20)+(J20*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="G64" s="76">
-        <f>(NPV(0.105,F20:J20)+(J20*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="H64" s="77">
-        <f>(NPV(0.105,F20:J20)+(J20*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="I64" s="76">
-        <f>(NPV(0.105,F20:J20)+(J20*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="J64" s="76">
-        <f>(NPV(0.105,F20:J20)+(J20*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="L64" s="61" t="inlineStr">
-        <is>
-          <t>WACC tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="75" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F65" s="76">
-        <f>(NPV(0.11,F20:J20)+(J20*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="G65" s="76">
-        <f>(NPV(0.11,F20:J20)+(J20*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="H65" s="76">
-        <f>(NPV(0.11,F20:J20)+(J20*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="I65" s="76">
-        <f>(NPV(0.11,F20:J20)+(J20*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="J65" s="76">
-        <f>(NPV(0.11,F20:J20)+(J20*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="L65" s="61" t="inlineStr">
-        <is>
-          <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="75" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C66" s="61" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F66" s="76">
+        <f>(NPV(0.095,F24:J24)+(J24*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="G66" s="76">
+        <f>(NPV(0.095,F24:J24)+(J24*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="H66" s="76">
+        <f>(NPV(0.095,F24:J24)+(J24*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="I66" s="76">
+        <f>(NPV(0.095,F24:J24)+(J24*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="J66" s="76">
+        <f>(NPV(0.095,F24:J24)+(J24*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="L66" s="61" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F67" s="76">
+        <f>(NPV(0.1,F24:J24)+(J24*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="G67" s="76">
+        <f>(NPV(0.1,F24:J24)+(J24*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="H67" s="76">
+        <f>(NPV(0.1,F24:J24)+(J24*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="I67" s="76">
+        <f>(NPV(0.1,F24:J24)+(J24*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="J67" s="76">
+        <f>(NPV(0.1,F24:J24)+(J24*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="L67" s="61" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="75" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F68" s="76">
+        <f>(NPV(0.105,F24:J24)+(J24*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="G68" s="76">
+        <f>(NPV(0.105,F24:J24)+(J24*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="H68" s="77">
+        <f>(NPV(0.105,F24:J24)+(J24*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="I68" s="76">
+        <f>(NPV(0.105,F24:J24)+(J24*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="J68" s="76">
+        <f>(NPV(0.105,F24:J24)+(J24*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="L68" s="61" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="75" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F69" s="76">
+        <f>(NPV(0.11,F24:J24)+(J24*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="G69" s="76">
+        <f>(NPV(0.11,F24:J24)+(J24*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="H69" s="76">
+        <f>(NPV(0.11,F24:J24)+(J24*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="I69" s="76">
+        <f>(NPV(0.11,F24:J24)+(J24*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="J69" s="76">
+        <f>(NPV(0.11,F24:J24)+(J24*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="L69" s="61" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="28" customHeight="1">
+      <c r="A70" s="75" t="n">
         <v>0.115</v>
       </c>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F66" s="76">
-        <f>(NPV(0.115,F20:J20)+(J20*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="G66" s="76">
-        <f>(NPV(0.115,F20:J20)+(J20*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="H66" s="76">
-        <f>(NPV(0.115,F20:J20)+(J20*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="I66" s="76">
-        <f>(NPV(0.115,F20:J20)+(J20*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="J66" s="76">
-        <f>(NPV(0.115,F20:J20)+(J20*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E34+E35)/E37</f>
-        <v/>
-      </c>
-      <c r="L66" s="61" t="inlineStr">
+      <c r="F70" s="76">
+        <f>(NPV(0.115,F24:J24)+(J24*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="G70" s="76">
+        <f>(NPV(0.115,F24:J24)+(J24*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="H70" s="76">
+        <f>(NPV(0.115,F24:J24)+(J24*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="I70" s="76">
+        <f>(NPV(0.115,F24:J24)+(J24*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="J70" s="76">
+        <f>(NPV(0.115,F24:J24)+(J24*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E38+E39)/E41</f>
+        <v/>
+      </c>
+      <c r="L70" s="61" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="17" t="inlineStr">
+    <row r="71" ht="28" customHeight="1">
+      <c r="B71" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C71" s="18" t="inlineStr">
         <is>
           <t>Scenarios: WACC &amp; terminal g</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D71" s="19" t="inlineStr">
         <is>
           <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
-      <c r="L67" s="61" t="inlineStr">
+      <c r="L71" s="61" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="M67" s="19" t="inlineStr">
+      <c r="M71" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
@@ -4140,27 +4610,30 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId21"/>
-    <hyperlink ref="M45" location="'Comps'!A26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C61" r:id="rId22"/>
-    <hyperlink ref="L61" location="'Scenarios'!G10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId23"/>
-    <hyperlink ref="L62" location="'WACC'!E16"/>
-    <hyperlink ref="L63" location="'WACC'!E16"/>
-    <hyperlink ref="L64" location="'WACC'!E16"/>
-    <hyperlink ref="L65" location="'WACC'!E16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId24"/>
+    <hyperlink ref="M49" location="'Comps'!A26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId25"/>
+    <hyperlink ref="L65" location="'Scenarios'!G10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId26"/>
     <hyperlink ref="L66" location="'WACC'!E16"/>
-    <hyperlink ref="C67" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId24"/>
+    <hyperlink ref="L67" location="'WACC'!E16"/>
+    <hyperlink ref="L68" location="'WACC'!E16"/>
+    <hyperlink ref="L69" location="'WACC'!E16"/>
+    <hyperlink ref="L70" location="'WACC'!E16"/>
+    <hyperlink ref="C71" location="'Scenarios'!G9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4266,7 +4739,7 @@
         </is>
       </c>
       <c r="E6" s="48">
-        <f>DCF!E29</f>
+        <f>DCF!E33</f>
         <v/>
       </c>
     </row>
@@ -4578,7 +5051,7 @@
         </is>
       </c>
       <c r="E25" s="60">
-        <f>DCF!E31</f>
+        <f>DCF!E35</f>
         <v/>
       </c>
     </row>
@@ -4589,7 +5062,7 @@
         </is>
       </c>
       <c r="E26" s="69">
-        <f>DCF!E45</f>
+        <f>DCF!E49</f>
         <v/>
       </c>
     </row>
@@ -4756,7 +5229,7 @@
         </is>
       </c>
       <c r="E38" s="85">
-        <f>DCF!E45</f>
+        <f>DCF!E49</f>
         <v/>
       </c>
       <c r="G38" s="86">
@@ -4820,11 +5293,11 @@
         </is>
       </c>
       <c r="G40" s="84">
-        <f>Scenarios!F59</f>
+        <f>Scenarios!F75</f>
         <v/>
       </c>
       <c r="H40" s="84">
-        <f>Scenarios!H59</f>
+        <f>Scenarios!H75</f>
         <v/>
       </c>
     </row>
@@ -4859,7 +5332,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink ref="C6" location="'DCF'!E29"/>
+    <hyperlink ref="C6" location="'DCF'!E33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
@@ -4875,7 +5348,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
-    <hyperlink ref="C38" location="'DCF'!E45"/>
+    <hyperlink ref="C38" location="'DCF'!E49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId20"/>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1390,7 +1390,7 @@
   <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
@@ -2981,7 +2981,7 @@
   <dimension ref="A1:M71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1778,12 +1778,12 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>AR % of revenue (NWC)</t>
+          <t>AR % of revenue (inside NWC)</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
         </is>
       </c>
       <c r="F14" s="20" t="n">
@@ -1809,12 +1809,12 @@
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>Other NWC (ex-AR) % of Δrevenue</t>
+          <t>NWC % of Δrevenue (includes AR)</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>5.8% of Δsales is other NWC (Inv + OCA − AP − accrued). AR is the 1.7% line above, not inside this residual. 1.7+5.8=7.5%.</t>
+          <t>7.5% of Δsales is total NWC and includes AR (1.7% of sales) plus inv, OCA, AP, accrued. AR is inside this 7.5%.</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -1824,17 +1824,17 @@
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Other NWC ex-AR. Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 5.8% of Δsales; AR is the 1.7% line, not in this residual.</t>
+          <t>Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 7.5% of Δsales includes AR.</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.065</v>
+        <v>0.08</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.058</v>
+        <v>0.075</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2607,95 +2607,95 @@
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 1</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 1</t>
         </is>
       </c>
       <c r="F58" s="32">
-        <f>F15*(F18-11102600)</f>
+        <f>F15*(F18-11102600)-F53</f>
         <v/>
       </c>
       <c r="G58" s="32">
-        <f>G15*(G18-11102600)</f>
+        <f>G15*(G18-11102600)-G53</f>
         <v/>
       </c>
       <c r="H58" s="32">
-        <f>H15*(H18-11102600)</f>
+        <f>H15*(H18-11102600)-H53</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 2</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 2</t>
         </is>
       </c>
       <c r="F59" s="32">
-        <f>F15*(F19-F18)</f>
+        <f>F15*(F19-F18)-F54</f>
         <v/>
       </c>
       <c r="G59" s="32">
-        <f>G15*(G19-G18)</f>
+        <f>G15*(G19-G18)-G54</f>
         <v/>
       </c>
       <c r="H59" s="32">
-        <f>H15*(H19-H18)</f>
+        <f>H15*(H19-H18)-H54</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 3</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 3</t>
         </is>
       </c>
       <c r="F60" s="32">
-        <f>F15*(F20-F19)</f>
+        <f>F15*(F20-F19)-F55</f>
         <v/>
       </c>
       <c r="G60" s="32">
-        <f>G15*(G20-G19)</f>
+        <f>G15*(G20-G19)-G55</f>
         <v/>
       </c>
       <c r="H60" s="32">
-        <f>H15*(H20-H19)</f>
+        <f>H15*(H20-H19)-H55</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 4</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 4</t>
         </is>
       </c>
       <c r="F61" s="32">
-        <f>F15*(F21-F20)</f>
+        <f>F15*(F21-F20)-F56</f>
         <v/>
       </c>
       <c r="G61" s="32">
-        <f>G15*(G21-G20)</f>
+        <f>G15*(G21-G20)-G56</f>
         <v/>
       </c>
       <c r="H61" s="32">
-        <f>H15*(H21-H20)</f>
+        <f>H15*(H21-H20)-H56</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) – year 5</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 5</t>
         </is>
       </c>
       <c r="F62" s="32">
-        <f>F15*(F22-F21)</f>
+        <f>F15*(F22-F21)-F57</f>
         <v/>
       </c>
       <c r="G62" s="32">
-        <f>G15*(G22-G21)</f>
+        <f>G15*(G22-G21)-G57</f>
         <v/>
       </c>
       <c r="H62" s="32">
-        <f>H15*(H22-H21)</f>
+        <f>H15*(H22-H21)-H57</f>
         <v/>
       </c>
     </row>
@@ -3549,12 +3549,12 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AR % of revenue</t>
+          <t xml:space="preserve">  AR % of revenue (included in NWC)</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
         </is>
       </c>
       <c r="F17" s="20">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Own DCF NWC line; wholesale / marketplace mix.</t>
+          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This is the DCF AR / NWC line.</t>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
         </is>
       </c>
       <c r="E18" s="47" t="n">
@@ -3640,7 +3640,7 @@
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR (increase)/decrease — part of NWC</t>
+          <t xml:space="preserve">  ΔAR (increase)/decrease — included in NWC</t>
         </is>
       </c>
       <c r="F19" s="48">
@@ -3671,12 +3671,12 @@
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other NWC (ex-AR) % of Δrevenue</t>
+          <t xml:space="preserve">  NWC % of Δrevenue (includes AR)</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>5.8% of Δsales is other NWC (Inv + OCA − AP − accrued). AR is the 1.7% line above, not inside this residual. 1.7+5.8=7.5%.</t>
+          <t>7.5% of Δsales is total NWC and includes AR (1.7% of sales) plus inv, OCA, AP, accrued. AR is inside this 7.5%.</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>Other NWC ex-AR. Ctrl+F "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 5.8% of Δsales; AR is the 1.7% line, not in this residual.</t>
+          <t>Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 7.5% of Δsales includes AR.</t>
         </is>
       </c>
       <c r="F20" s="20">
@@ -3713,7 +3713,7 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (ex-AR) (increase)/decrease</t>
+          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR)</t>
         </is>
       </c>
       <c r="F21" s="48">
@@ -3775,7 +3775,7 @@
     <row r="23">
       <c r="A23" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  memo: ΔNWC = ΔAR + other ΔNWC. AR is 1.7% of sales (own line); other is 5.8% of Δsales.</t>
+          <t xml:space="preserve">  memo: 7.5% ΔNWC includes AR. ΔAR is shown above and is inside the 7.5%, not added on top.</t>
         </is>
       </c>
     </row>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1387,7 +1387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1778,63 +1778,63 @@
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>AR % of revenue (inside NWC)</t>
+          <t>NWC % of Δrevenue (AR + inv + OCA − AP − accrued)</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
+          <t>One NWC line: 7.5% of Δsales = AR + inv + OCA − AP − accrued. AR is not a separate FCF item.</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+          <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
       <c r="D14" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
+          <t>One NWC. Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982.</t>
         </is>
       </c>
       <c r="F14" s="20" t="n">
-        <v>0.015</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>0.017</v>
+        <v>0.075</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
-          <t>NWC % of Δrevenue (includes AR)</t>
+          <t xml:space="preserve">  of which: AR % of revenue</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>7.5% of Δsales is total NWC and includes AR (1.7% of sales) plus inv, OCA, AP, accrued. AR is inside this 7.5%.</t>
+          <t>AR sits inside NWC: 190,657 / 11,102,600 = 1.7% of sales. Same NWC block as inv, OCA, AP, accrued.</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>LULU BS/IS historical (10-K)</t>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
       </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 7.5% of Δsales includes AR.</t>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
         </is>
       </c>
       <c r="F15" s="20" t="n">
-        <v>0.08</v>
+        <v>0.015</v>
       </c>
       <c r="G15" s="20" t="n">
-        <v>0.075</v>
+        <v>0.017</v>
       </c>
       <c r="H15" s="20" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="17">
@@ -2417,537 +2417,347 @@
     <row r="48">
       <c r="A48" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable – year 1</t>
+          <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 1</t>
         </is>
       </c>
       <c r="F48" s="32">
-        <f>F18*F14</f>
+        <f>F18*F15</f>
         <v/>
       </c>
       <c r="G48" s="32">
-        <f>G18*G14</f>
+        <f>G18*G15</f>
         <v/>
       </c>
       <c r="H48" s="32">
-        <f>H18*H14</f>
+        <f>H18*H15</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable – year 2</t>
+          <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 2</t>
         </is>
       </c>
       <c r="F49" s="32">
-        <f>F19*F14</f>
+        <f>F19*F15</f>
         <v/>
       </c>
       <c r="G49" s="32">
-        <f>G19*G14</f>
+        <f>G19*G15</f>
         <v/>
       </c>
       <c r="H49" s="32">
-        <f>H19*H14</f>
+        <f>H19*H15</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable – year 3</t>
+          <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 3</t>
         </is>
       </c>
       <c r="F50" s="32">
-        <f>F20*F14</f>
+        <f>F20*F15</f>
         <v/>
       </c>
       <c r="G50" s="32">
-        <f>G20*G14</f>
+        <f>G20*G15</f>
         <v/>
       </c>
       <c r="H50" s="32">
-        <f>H20*H14</f>
+        <f>H20*H15</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable – year 4</t>
+          <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 4</t>
         </is>
       </c>
       <c r="F51" s="32">
-        <f>F21*F14</f>
+        <f>F21*F15</f>
         <v/>
       </c>
       <c r="G51" s="32">
-        <f>G21*G14</f>
+        <f>G21*G15</f>
         <v/>
       </c>
       <c r="H51" s="32">
-        <f>H21*H14</f>
+        <f>H21*H15</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable – year 5</t>
+          <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 5</t>
         </is>
       </c>
       <c r="F52" s="32">
-        <f>F22*F14</f>
+        <f>F22*F15</f>
         <v/>
       </c>
       <c r="G52" s="32">
-        <f>G22*G14</f>
+        <f>G22*G15</f>
         <v/>
       </c>
       <c r="H52" s="32">
-        <f>H22*H14</f>
+        <f>H22*H15</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR – year 1</t>
+          <t xml:space="preserve">  ΔNWC (includes AR) – year 1</t>
         </is>
       </c>
       <c r="F53" s="32">
-        <f>F48-190657</f>
+        <f>F14*(F18-11102600)</f>
         <v/>
       </c>
       <c r="G53" s="32">
-        <f>G48-190657</f>
+        <f>G14*(G18-11102600)</f>
         <v/>
       </c>
       <c r="H53" s="32">
-        <f>H48-190657</f>
+        <f>H14*(H18-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR – year 2</t>
+          <t xml:space="preserve">  ΔNWC (includes AR) – year 2</t>
         </is>
       </c>
       <c r="F54" s="32">
-        <f>F49-F48</f>
+        <f>F14*(F19-F18)</f>
         <v/>
       </c>
       <c r="G54" s="32">
-        <f>G49-G48</f>
+        <f>G14*(G19-G18)</f>
         <v/>
       </c>
       <c r="H54" s="32">
-        <f>H49-H48</f>
+        <f>H14*(H19-H18)</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR – year 3</t>
+          <t xml:space="preserve">  ΔNWC (includes AR) – year 3</t>
         </is>
       </c>
       <c r="F55" s="32">
-        <f>F50-F49</f>
+        <f>F14*(F20-F19)</f>
         <v/>
       </c>
       <c r="G55" s="32">
-        <f>G50-G49</f>
+        <f>G14*(G20-G19)</f>
         <v/>
       </c>
       <c r="H55" s="32">
-        <f>H50-H49</f>
+        <f>H14*(H20-H19)</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR – year 4</t>
+          <t xml:space="preserve">  ΔNWC (includes AR) – year 4</t>
         </is>
       </c>
       <c r="F56" s="32">
-        <f>F51-F50</f>
+        <f>F14*(F21-F20)</f>
         <v/>
       </c>
       <c r="G56" s="32">
-        <f>G51-G50</f>
+        <f>G14*(G21-G20)</f>
         <v/>
       </c>
       <c r="H56" s="32">
-        <f>H51-H50</f>
+        <f>H14*(H21-H20)</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ΔAR – year 5</t>
+          <t xml:space="preserve">  ΔNWC (includes AR) – year 5</t>
         </is>
       </c>
       <c r="F57" s="32">
-        <f>F52-F51</f>
+        <f>F14*(F22-F21)</f>
         <v/>
       </c>
       <c r="G57" s="32">
-        <f>G52-G51</f>
+        <f>G14*(G22-G21)</f>
         <v/>
       </c>
       <c r="H57" s="32">
-        <f>H52-H51</f>
+        <f>H14*(H22-H21)</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 1</t>
+          <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
       <c r="F58" s="32">
-        <f>F15*(F18-11102600)-F53</f>
+        <f>F33+F38-F43-F53</f>
         <v/>
       </c>
       <c r="G58" s="32">
-        <f>G15*(G18-11102600)-G53</f>
+        <f>G33+G38-G43-G53</f>
         <v/>
       </c>
       <c r="H58" s="32">
-        <f>H15*(H18-11102600)-H53</f>
+        <f>H33+H38-H43-H53</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 2</t>
+          <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
       <c r="F59" s="32">
-        <f>F15*(F19-F18)-F54</f>
+        <f>F34+F39-F44-F54</f>
         <v/>
       </c>
       <c r="G59" s="32">
-        <f>G15*(G19-G18)-G54</f>
+        <f>G34+G39-G44-G54</f>
         <v/>
       </c>
       <c r="H59" s="32">
-        <f>H15*(H19-H18)-H54</f>
+        <f>H34+H39-H44-H54</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 3</t>
+          <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
       <c r="F60" s="32">
-        <f>F15*(F20-F19)-F55</f>
+        <f>F35+F40-F45-F55</f>
         <v/>
       </c>
       <c r="G60" s="32">
-        <f>G15*(G20-G19)-G55</f>
+        <f>G35+G40-G45-G55</f>
         <v/>
       </c>
       <c r="H60" s="32">
-        <f>H15*(H20-H19)-H55</f>
+        <f>H35+H40-H45-H55</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 4</t>
+          <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
       <c r="F61" s="32">
-        <f>F15*(F21-F20)-F56</f>
+        <f>F36+F41-F46-F56</f>
         <v/>
       </c>
       <c r="G61" s="32">
-        <f>G15*(G21-G20)-G56</f>
+        <f>G36+G41-G46-G56</f>
         <v/>
       </c>
       <c r="H61" s="32">
-        <f>H15*(H21-H20)-H56</f>
+        <f>H36+H41-H46-H56</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR) – year 5</t>
+          <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
       <c r="F62" s="32">
-        <f>F15*(F22-F21)-F57</f>
+        <f>F37+F42-F47-F57</f>
         <v/>
       </c>
       <c r="G62" s="32">
-        <f>G15*(G22-G21)-G57</f>
+        <f>G37+G42-G47-G57</f>
         <v/>
       </c>
       <c r="H62" s="32">
-        <f>H15*(H22-H21)-H57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔNWC – year 1</t>
-        </is>
-      </c>
-      <c r="F63" s="32">
-        <f>F53+F58</f>
-        <v/>
-      </c>
-      <c r="G63" s="32">
-        <f>G53+G58</f>
-        <v/>
-      </c>
-      <c r="H63" s="32">
-        <f>H53+H58</f>
+        <f>H37+H42-H47-H57</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔNWC – year 2</t>
-        </is>
-      </c>
-      <c r="F64" s="32">
-        <f>F54+F59</f>
-        <v/>
-      </c>
-      <c r="G64" s="32">
-        <f>G54+G59</f>
-        <v/>
-      </c>
-      <c r="H64" s="32">
-        <f>H54+H59</f>
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Enterprise value (DCF)</t>
+        </is>
+      </c>
+      <c r="F64" s="34">
+        <f>NPV(F9,F58,F59,F60,F61,F62)+(F62*(1+F10)/(F9-F10))/(1+F9)^5</f>
+        <v/>
+      </c>
+      <c r="G64" s="34">
+        <f>NPV(G9,G58,G59,G60,G61,G62)+(G62*(1+G10)/(G9-G10))/(1+G9)^5</f>
+        <v/>
+      </c>
+      <c r="H64" s="34">
+        <f>NPV(H9,H58,H59,H60,H61,H62)+(H62*(1+H10)/(H9-H10))/(1+H9)^5</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔNWC – year 3</t>
-        </is>
-      </c>
-      <c r="F65" s="32">
-        <f>F55+F60</f>
-        <v/>
-      </c>
-      <c r="G65" s="32">
-        <f>G55+G60</f>
-        <v/>
-      </c>
-      <c r="H65" s="32">
-        <f>H55+H60</f>
+      <c r="A65" s="35" t="inlineStr">
+        <is>
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="F65" s="36">
+        <f>(F64+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="G65" s="37">
+        <f>(G64+1807202-0)/111380</f>
+        <v/>
+      </c>
+      <c r="H65" s="36">
+        <f>(H64+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔNWC – year 4</t>
-        </is>
-      </c>
-      <c r="F66" s="32">
-        <f>F56+F61</f>
-        <v/>
-      </c>
-      <c r="G66" s="32">
-        <f>G56+G61</f>
-        <v/>
-      </c>
-      <c r="H66" s="32">
-        <f>H56+H61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔNWC – year 5</t>
-        </is>
-      </c>
-      <c r="F67" s="32">
-        <f>F57+F62</f>
-        <v/>
-      </c>
-      <c r="G67" s="32">
-        <f>G57+G62</f>
-        <v/>
-      </c>
-      <c r="H67" s="32">
-        <f>H57+H62</f>
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Upside / (downside) vs current</t>
+        </is>
+      </c>
+      <c r="F66" s="38">
+        <f>F65/100.0-1</f>
+        <v/>
+      </c>
+      <c r="G66" s="38">
+        <f>G65/100.0-1</f>
+        <v/>
+      </c>
+      <c r="H66" s="38">
+        <f>H65/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 1</t>
-        </is>
-      </c>
-      <c r="F68" s="32">
-        <f>F33+F38-F43-F63</f>
-        <v/>
-      </c>
-      <c r="G68" s="32">
-        <f>G33+G38-G43-G63</f>
-        <v/>
-      </c>
-      <c r="H68" s="32">
-        <f>H33+H38-H43-H63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 2</t>
-        </is>
-      </c>
-      <c r="F69" s="32">
-        <f>F34+F39-F44-F64</f>
-        <v/>
-      </c>
-      <c r="G69" s="32">
-        <f>G34+G39-G44-G64</f>
-        <v/>
-      </c>
-      <c r="H69" s="32">
-        <f>H34+H39-H44-H64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 3</t>
-        </is>
-      </c>
-      <c r="F70" s="32">
-        <f>F35+F40-F45-F65</f>
-        <v/>
-      </c>
-      <c r="G70" s="32">
-        <f>G35+G40-G45-G65</f>
-        <v/>
-      </c>
-      <c r="H70" s="32">
-        <f>H35+H40-H45-H65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 4</t>
-        </is>
-      </c>
-      <c r="F71" s="32">
-        <f>F36+F41-F46-F66</f>
-        <v/>
-      </c>
-      <c r="G71" s="32">
-        <f>G36+G41-G46-G66</f>
-        <v/>
-      </c>
-      <c r="H71" s="32">
-        <f>H36+H41-H46-H66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Unlevered FCF – year 5</t>
-        </is>
-      </c>
-      <c r="F72" s="32">
-        <f>F37+F42-F47-F67</f>
-        <v/>
-      </c>
-      <c r="G72" s="32">
-        <f>G37+G42-G47-G67</f>
-        <v/>
-      </c>
-      <c r="H72" s="32">
-        <f>H37+H42-H47-H67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="22" t="inlineStr">
-        <is>
-          <t>Enterprise value (DCF)</t>
-        </is>
-      </c>
-      <c r="F74" s="34">
-        <f>NPV(F9,F68,F69,F70,F71,F72)+(F72*(1+F10)/(F9-F10))/(1+F9)^5</f>
-        <v/>
-      </c>
-      <c r="G74" s="34">
-        <f>NPV(G9,G68,G69,G70,G71,G72)+(G72*(1+G10)/(G9-G10))/(1+G9)^5</f>
-        <v/>
-      </c>
-      <c r="H74" s="34">
-        <f>NPV(H9,H68,H69,H70,H71,H72)+(H72*(1+H10)/(H9-H10))/(1+H9)^5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="35" t="inlineStr">
-        <is>
-          <t>Implied share price</t>
-        </is>
-      </c>
-      <c r="F75" s="36">
-        <f>(F74+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="G75" s="37">
-        <f>(G74+1807202-0)/111380</f>
-        <v/>
-      </c>
-      <c r="H75" s="36">
-        <f>(H74+1807202-0)/111380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="22" t="inlineStr">
-        <is>
-          <t>Upside / (downside) vs current</t>
-        </is>
-      </c>
-      <c r="F76" s="38">
-        <f>F75/100.0-1</f>
-        <v/>
-      </c>
-      <c r="G76" s="38">
-        <f>G75/100.0-1</f>
-        <v/>
-      </c>
-      <c r="H76" s="38">
-        <f>H75/100.0-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="39" t="inlineStr">
+      <c r="A68" s="39" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2978,7 +2788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3549,22 +3359,22 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  AR % of revenue (included in NWC)</t>
+          <t>NWC % of Δrevenue (AR + inv + OCA − AP − accrued)</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
+          <t>One NWC line: 7.5% of Δsales = AR + inv + OCA − AP − accrued. AR is not a separate FCF item.</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+          <t>LULU BS/IS historical (10-K)</t>
         </is>
       </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
+          <t>One NWC. Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982.</t>
         </is>
       </c>
       <c r="F17" s="20">
@@ -3591,12 +3401,12 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Accounts receivable, net</t>
+          <t xml:space="preserve">  of which: AR % of revenue</t>
         </is>
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>AR 1.7% of sales = FY25 Accounts receivable, net 190,657 / 11,102,600. Included in the 7.5% NWC, not added on top.</t>
+          <t>AR sits inside NWC: 190,657 / 11,102,600 = 1.7% of sales. Same NWC block as inv, OCA, AP, accrued.</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -3606,422 +3416,391 @@
       </c>
       <c r="D18" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. This AR is inside the 7.5% NWC, not extra.</t>
-        </is>
-      </c>
-      <c r="E18" s="47" t="n">
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
+        </is>
+      </c>
+      <c r="F18" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="G18" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="H18" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="I18" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+      <c r="J18" s="20">
+        <f>Scenarios!$G$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  of which: Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>AR sits inside NWC: 190,657 / 11,102,600 = 1.7% of sales. Same NWC block as inv, OCA, AP, accrued.</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
+        </is>
+      </c>
+      <c r="E19" s="47" t="n">
         <v>190657</v>
       </c>
-      <c r="F18" s="48">
+      <c r="F19" s="48">
         <f>Scenarios!G48</f>
         <v/>
       </c>
-      <c r="G18" s="48">
+      <c r="G19" s="48">
         <f>Scenarios!G49</f>
         <v/>
       </c>
-      <c r="H18" s="48">
+      <c r="H19" s="48">
         <f>Scenarios!G50</f>
         <v/>
       </c>
-      <c r="I18" s="48">
+      <c r="I19" s="48">
         <f>Scenarios!G51</f>
         <v/>
       </c>
-      <c r="J18" s="48">
+      <c r="J19" s="48">
         <f>Scenarios!G52</f>
         <v/>
       </c>
-      <c r="K18" s="49">
-        <f>IF(MAX(ABS(F18-Scenarios!$G$48),ABS(G18-Scenarios!$G$49),ABS(H18-Scenarios!$G$50),ABS(I18-Scenarios!$G$51),ABS(J18-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ΔAR (increase)/decrease — included in NWC</t>
-        </is>
-      </c>
-      <c r="F19" s="48">
+      <c r="K19" s="49">
+        <f>IF(MAX(ABS(F19-Scenarios!$G$48),ABS(G19-Scenarios!$G$49),ABS(H19-Scenarios!$G$50),ABS(I19-Scenarios!$G$51),ABS(J19-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>(Increase)/decrease in NWC (includes AR)</t>
+        </is>
+      </c>
+      <c r="F20" s="48">
         <f>-Scenarios!G53</f>
         <v/>
       </c>
-      <c r="G19" s="48">
+      <c r="G20" s="48">
         <f>-Scenarios!G54</f>
         <v/>
       </c>
-      <c r="H19" s="48">
+      <c r="H20" s="48">
         <f>-Scenarios!G55</f>
         <v/>
       </c>
-      <c r="I19" s="48">
+      <c r="I20" s="48">
         <f>-Scenarios!G56</f>
         <v/>
       </c>
-      <c r="J19" s="48">
+      <c r="J20" s="48">
         <f>-Scenarios!G57</f>
         <v/>
       </c>
-      <c r="K19" s="49">
-        <f>IF(MAX(ABS(F19+Scenarios!$G$53),ABS(G19+Scenarios!$G$54),ABS(H19+Scenarios!$G$55),ABS(I19+Scenarios!$G$56),ABS(J19+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NWC % of Δrevenue (includes AR)</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>7.5% of Δsales is total NWC and includes AR (1.7% of sales) plus inv, OCA, AP, accrued. AR is inside this 7.5%.</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>LULU BS/IS historical (10-K)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Accounts receivable, net" → 190,657 | "Inventories" → 1,700,753 | "Accounts payable" → 331,421 | "Accrued liabilities and other" → 662,982. 7.5% of Δsales includes AR.</t>
-        </is>
-      </c>
-      <c r="F20" s="20">
-        <f>Scenarios!$G$15</f>
-        <v/>
-      </c>
-      <c r="G20" s="20">
-        <f>Scenarios!$G$15</f>
-        <v/>
-      </c>
-      <c r="H20" s="20">
-        <f>Scenarios!$G$15</f>
-        <v/>
-      </c>
-      <c r="I20" s="20">
-        <f>Scenarios!$G$15</f>
-        <v/>
-      </c>
-      <c r="J20" s="20">
-        <f>Scenarios!$G$15</f>
+      <c r="K20" s="49">
+        <f>IF(MAX(ABS(F20+Scenarios!$G$53),ABS(G20+Scenarios!$G$54),ABS(H20+Scenarios!$G$55),ABS(I20+Scenarios!$G$56),ABS(J20+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Other ΔNWC (NWC − ΔAR)</t>
-        </is>
-      </c>
-      <c r="F21" s="48">
-        <f>-Scenarios!G58</f>
-        <v/>
-      </c>
-      <c r="G21" s="48">
-        <f>-Scenarios!G59</f>
-        <v/>
-      </c>
-      <c r="H21" s="48">
-        <f>-Scenarios!G60</f>
-        <v/>
-      </c>
-      <c r="I21" s="48">
-        <f>-Scenarios!G61</f>
-        <v/>
-      </c>
-      <c r="J21" s="48">
-        <f>-Scenarios!G62</f>
-        <v/>
-      </c>
-      <c r="K21" s="49">
-        <f>IF(MAX(ABS(F21+Scenarios!$G$58),ABS(G21+Scenarios!$G$59),ABS(H21+Scenarios!$G$60),ABS(I21+Scenarios!$G$61),ABS(J21+Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
-        <v/>
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: NWC and AR are one line. 7.5% of Δsales already includes AR; UFCF does not take ΔAR separately.</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Total (increase)/decrease in net working capital</t>
-        </is>
-      </c>
-      <c r="F22" s="48">
-        <f>-Scenarios!G63</f>
-        <v/>
-      </c>
-      <c r="G22" s="48">
-        <f>-Scenarios!G64</f>
-        <v/>
-      </c>
-      <c r="H22" s="48">
-        <f>-Scenarios!G65</f>
-        <v/>
-      </c>
-      <c r="I22" s="48">
-        <f>-Scenarios!G66</f>
-        <v/>
-      </c>
-      <c r="J22" s="48">
-        <f>-Scenarios!G67</f>
-        <v/>
-      </c>
-      <c r="K22" s="49">
-        <f>IF(MAX(ABS(F22+Scenarios!$G$63),ABS(G22+Scenarios!$G$64),ABS(H22+Scenarios!$G$65),ABS(I22+Scenarios!$G$66),ABS(J22+Scenarios!$G$67))&lt;0.5,"OK","CHECK")</f>
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Unlevered free cash flow</t>
+        </is>
+      </c>
+      <c r="F22" s="54">
+        <f>Scenarios!G58</f>
+        <v/>
+      </c>
+      <c r="G22" s="54">
+        <f>Scenarios!G59</f>
+        <v/>
+      </c>
+      <c r="H22" s="54">
+        <f>Scenarios!G60</f>
+        <v/>
+      </c>
+      <c r="I22" s="54">
+        <f>Scenarios!G61</f>
+        <v/>
+      </c>
+      <c r="J22" s="54">
+        <f>Scenarios!G62</f>
+        <v/>
+      </c>
+      <c r="K22" s="52">
+        <f>IF(MAX(ABS(F22-Scenarios!$G$58),ABS(G22-Scenarios!$G$59),ABS(H22-Scenarios!$G$60),ABS(I22-Scenarios!$G$61),ABS(J22-Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  memo: 7.5% ΔNWC includes AR. ΔAR is shown above and is inside the 7.5%, not added on top.</t>
-        </is>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="F23" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="I23" s="55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" s="55" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow</t>
-        </is>
-      </c>
-      <c r="F24" s="54">
-        <f>Scenarios!G68</f>
-        <v/>
-      </c>
-      <c r="G24" s="54">
-        <f>Scenarios!G69</f>
-        <v/>
-      </c>
-      <c r="H24" s="54">
-        <f>Scenarios!G70</f>
-        <v/>
-      </c>
-      <c r="I24" s="54">
-        <f>Scenarios!G71</f>
-        <v/>
-      </c>
-      <c r="J24" s="54">
-        <f>Scenarios!G72</f>
-        <v/>
-      </c>
-      <c r="K24" s="52">
-        <f>IF(MAX(ABS(F24-Scenarios!$G$68),ABS(G24-Scenarios!$G$69),ABS(H24-Scenarios!$G$70),ABS(I24-Scenarios!$G$71),ABS(J24-Scenarios!$G$72))&lt;0.5,"OK","CHECK")</f>
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Discount factor @ WACC</t>
+        </is>
+      </c>
+      <c r="F24" s="56">
+        <f>1/(1+Scenarios!$G$9)^F23</f>
+        <v/>
+      </c>
+      <c r="G24" s="56">
+        <f>1/(1+Scenarios!$G$9)^G23</f>
+        <v/>
+      </c>
+      <c r="H24" s="56">
+        <f>1/(1+Scenarios!$G$9)^H23</f>
+        <v/>
+      </c>
+      <c r="I24" s="56">
+        <f>1/(1+Scenarios!$G$9)^I23</f>
+        <v/>
+      </c>
+      <c r="J24" s="56">
+        <f>1/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Discount period (years)</t>
-        </is>
-      </c>
-      <c r="F25" s="55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="55" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="I25" s="55" t="n">
-        <v>4</v>
-      </c>
-      <c r="J25" s="55" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>Discount factor @ WACC</t>
-        </is>
-      </c>
-      <c r="F26" s="56">
-        <f>1/(1+Scenarios!$G$9)^F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="56">
-        <f>1/(1+Scenarios!$G$9)^G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="56">
-        <f>1/(1+Scenarios!$G$9)^H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="56">
-        <f>1/(1+Scenarios!$G$9)^I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="56">
-        <f>1/(1+Scenarios!$G$9)^J25</f>
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>PV of unlevered FCF</t>
+        </is>
+      </c>
+      <c r="F25" s="34">
+        <f>F22*F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>G22*G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>H22*H24</f>
+        <v/>
+      </c>
+      <c r="I25" s="34">
+        <f>I22*I24</f>
+        <v/>
+      </c>
+      <c r="J25" s="34">
+        <f>J22*J24</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="22" t="inlineStr">
-        <is>
-          <t>PV of unlevered FCF</t>
-        </is>
-      </c>
-      <c r="F27" s="34">
-        <f>F24*F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="34">
-        <f>G24*G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="34">
-        <f>H24*H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="34">
-        <f>I24*I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="34">
-        <f>J24*J26</f>
-        <v/>
-      </c>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Scenarios linkage summary (column K should all read OK)</t>
+        </is>
+      </c>
+      <c r="K27" s="57">
+        <f>IF(COUNTIF(K5:K22,"CHECK")=0,"ALL OK","REVIEW")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Scenarios linkage summary (column K should all read OK)</t>
-        </is>
-      </c>
-      <c r="K29" s="57">
-        <f>IF(COUNTIF(K5:K24,"CHECK")=0,"ALL OK","REVIEW")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="58" t="inlineStr">
-        <is>
-          <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Sum of PV of explicit FCF (FY26–FY30)</t>
+        </is>
+      </c>
+      <c r="E29" s="59">
+        <f>SUM(F25:J25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Terminal growth rate (g)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
+        </is>
+      </c>
+      <c r="E30" s="50">
+        <f>Scenarios!$G$10</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>Sum of PV of explicit FCF (FY26–FY30)</t>
-        </is>
-      </c>
-      <c r="E31" s="59">
-        <f>SUM(F27:J27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
+          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="E31" s="34">
+        <f>J9+J14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Terminal growth rate (g)</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>2.25% terminal g sits next to FRED GDPC1 Q2/Q2 real GDP ≈ 2.1% (24,269.613 / 23,770.976 − 1).</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
-        </is>
-      </c>
-      <c r="E32" s="50">
-        <f>Scenarios!$G$10</f>
+          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
+        </is>
+      </c>
+      <c r="E32" s="48">
+        <f>J22*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="E33" s="34">
-        <f>J9+J14</f>
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
+        </is>
+      </c>
+      <c r="E33" s="60">
+        <f>E32/E31</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
-        </is>
-      </c>
-      <c r="E34" s="48">
-        <f>J24*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="E34" s="59">
+        <f>E32/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
-        </is>
-      </c>
-      <c r="E35" s="60">
-        <f>E34/E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="22" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="E36" s="59">
-        <f>E34/(1+Scenarios!$G$9)^J25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="22" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E37" s="34">
-        <f>E31+E36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="E35" s="34">
+        <f>E29+E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C38" s="61" t="inlineStr">
+      <c r="C36" s="61" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E38" s="47" t="n">
+      <c r="E36" s="47" t="n">
         <v>1807202</v>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Less: total debt</t>
+        </is>
+      </c>
+      <c r="C37" s="61" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
+        </is>
+      </c>
+      <c r="E37" s="47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="E38" s="34">
+        <f>E35+E36+E37</f>
+        <v/>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>Less: total debt</t>
+          <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
       <c r="C39" s="61" t="inlineStr">
@@ -4031,373 +3810,412 @@
       </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
+          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
       <c r="E39" s="47" t="n">
-        <v>0</v>
+        <v>111380</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="E40" s="34">
-        <f>E37+E38+E39</f>
+          <t>Implied value per share</t>
+        </is>
+      </c>
+      <c r="E40" s="62">
+        <f>E38/E39</f>
+        <v/>
+      </c>
+      <c r="K40" s="52">
+        <f>IF(ABS(E40-Scenarios!$G$65)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>Diluted shares outstanding (000)</t>
+          <t>Current share price</t>
         </is>
       </c>
       <c r="C41" s="61" t="inlineStr">
         <is>
-          <t>10-K</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
-        </is>
-      </c>
-      <c r="E41" s="47" t="n">
-        <v>111380</v>
+          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
+        </is>
+      </c>
+      <c r="E41" s="63" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>Implied value per share</t>
-        </is>
-      </c>
-      <c r="E42" s="62">
-        <f>E40/E41</f>
-        <v/>
-      </c>
-      <c r="K42" s="52">
-        <f>IF(ABS(E42-Scenarios!$G$75)&lt;0.05,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="28" customHeight="1">
+          <t>Implied upside / (downside)</t>
+        </is>
+      </c>
+      <c r="E42" s="64">
+        <f>E40/E41-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>Current share price</t>
-        </is>
-      </c>
-      <c r="C43" s="61" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="D43" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
-        </is>
-      </c>
-      <c r="E43" s="63" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="22" t="inlineStr">
-        <is>
-          <t>Implied upside / (downside)</t>
-        </is>
-      </c>
-      <c r="E44" s="64">
-        <f>E42/E43-1</f>
+          <t xml:space="preserve">  memo: % of EV from terminal value</t>
+        </is>
+      </c>
+      <c r="E43" s="50">
+        <f>E34/E35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  memo: % of EV from terminal value</t>
-        </is>
-      </c>
-      <c r="E45" s="50">
-        <f>E36/E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="58" t="inlineStr">
+      <c r="A45" s="58" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n"/>
-      <c r="C47" s="13" t="n"/>
+      <c r="B45" s="13" t="n"/>
+      <c r="C45" s="13" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>Exit multiple selection (see Comps tab for peer build)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
+        </is>
+      </c>
+      <c r="E47" s="65" t="n">
+        <v>8</v>
+      </c>
+      <c r="M47" s="61" t="inlineStr">
+        <is>
+          <t>Comps: Exit Multiple Build</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Exit multiple selection (see Comps tab for peer build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Terminal value = Terminal EBITDA × exit multiple</t>
+        </is>
+      </c>
+      <c r="E48" s="48">
+        <f>E31*E47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
-        </is>
-      </c>
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
-        </is>
-      </c>
-      <c r="E49" s="65" t="n">
-        <v>8</v>
-      </c>
-      <c r="M49" s="61" t="inlineStr">
-        <is>
-          <t>Comps: Exit Multiple Build</t>
-        </is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="E49" s="48">
+        <f>E48/(1+Scenarios!$G$9)^J23</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value = Terminal EBITDA × exit multiple</t>
-        </is>
-      </c>
-      <c r="E50" s="48">
-        <f>E33*E49</f>
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="E50" s="34">
+        <f>E29+E49</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="E51" s="48">
-        <f>E50/(1+Scenarios!$G$9)^J25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="E52" s="34">
-        <f>E31+E51</f>
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>Implied value per share (exit method)</t>
+        </is>
+      </c>
+      <c r="E51" s="66">
+        <f>(E50+E36+E37)/E39</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="22" t="inlineStr">
-        <is>
-          <t>Implied value per share (exit method)</t>
-        </is>
-      </c>
-      <c r="E53" s="66">
-        <f>(E52+E38+E39)/E41</f>
-        <v/>
+      <c r="A53" s="58" t="inlineStr">
+        <is>
+          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="n"/>
+      <c r="C53" s="13" t="n"/>
+      <c r="D53" s="13" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="67" t="inlineStr"/>
+      <c r="B54" s="68" t="inlineStr">
+        <is>
+          <t>Gordon Growth</t>
+        </is>
+      </c>
+      <c r="C54" s="68" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D54" s="68" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="58" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>Terminal value ($)</t>
+        </is>
+      </c>
+      <c r="B55" s="59">
+        <f>E32</f>
+        <v/>
+      </c>
+      <c r="C55" s="59">
+        <f>E48</f>
+        <v/>
+      </c>
+      <c r="D55" s="59">
+        <f>B55-C55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="67" t="inlineStr"/>
-      <c r="B56" s="68" t="inlineStr">
-        <is>
-          <t>Gordon Growth</t>
-        </is>
-      </c>
-      <c r="C56" s="68" t="inlineStr">
-        <is>
-          <t>Exit Multiple</t>
-        </is>
-      </c>
-      <c r="D56" s="68" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA (implied vs selected)</t>
+        </is>
+      </c>
+      <c r="B56" s="69">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="C56" s="69">
+        <f>E47</f>
+        <v/>
+      </c>
+      <c r="D56" s="69">
+        <f>B56-C56</f>
+        <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="22" t="inlineStr">
-        <is>
-          <t>Terminal value ($)</t>
-        </is>
-      </c>
-      <c r="B57" s="59">
-        <f>E34</f>
-        <v/>
-      </c>
-      <c r="C57" s="59">
-        <f>E50</f>
-        <v/>
-      </c>
-      <c r="D57" s="59">
-        <f>B57-C57</f>
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>Terminal value variance (%)</t>
+        </is>
+      </c>
+      <c r="B57" s="50" t="inlineStr"/>
+      <c r="C57" s="50" t="inlineStr"/>
+      <c r="D57" s="50">
+        <f>(B55-C55)/B55</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>Exit EV/EBITDA (implied vs selected)</t>
-        </is>
-      </c>
-      <c r="B58" s="69">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="C58" s="69">
-        <f>E49</f>
-        <v/>
-      </c>
-      <c r="D58" s="69">
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="B58" s="70">
+        <f>E40</f>
+        <v/>
+      </c>
+      <c r="C58" s="70">
+        <f>E51</f>
+        <v/>
+      </c>
+      <c r="D58" s="70">
         <f>B58-C58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value variance (%)</t>
-        </is>
-      </c>
-      <c r="B59" s="50" t="inlineStr"/>
-      <c r="C59" s="50" t="inlineStr"/>
-      <c r="D59" s="50">
-        <f>(B57-C57)/B57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="22" t="inlineStr">
-        <is>
-          <t>Implied share price</t>
-        </is>
-      </c>
-      <c r="B60" s="70">
-        <f>E42</f>
-        <v/>
-      </c>
-      <c r="C60" s="70">
-        <f>E53</f>
-        <v/>
-      </c>
-      <c r="D60" s="70">
-        <f>B60-C60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="71" t="inlineStr">
+      <c r="A59" s="71" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B61" s="72">
-        <f>IF(ABS(D58)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C61" s="73">
-        <f>TEXT(D58,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D61" s="39" t="inlineStr">
+      <c r="B59" s="72">
+        <f>IF(ABS(D56)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C59" s="73">
+        <f>TEXT(D56,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
+        <v/>
+      </c>
+      <c r="D59" s="39" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="58" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="58" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B64" s="13" t="n"/>
-      <c r="C64" s="13" t="n"/>
-      <c r="D64" s="13" t="n"/>
-      <c r="E64" s="13" t="n"/>
-      <c r="F64" s="13" t="n"/>
-      <c r="G64" s="13" t="n"/>
-      <c r="H64" s="13" t="n"/>
+      <c r="B62" s="13" t="n"/>
+      <c r="C62" s="13" t="n"/>
+      <c r="D62" s="13" t="n"/>
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="13" t="n"/>
+      <c r="G62" s="13" t="n"/>
+      <c r="H62" s="13" t="n"/>
+    </row>
+    <row r="63" ht="28" customHeight="1">
+      <c r="A63" s="74" t="inlineStr">
+        <is>
+          <t>WACC \ g</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
+        </is>
+      </c>
+      <c r="F63" s="75" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G63" s="75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H63" s="75" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="I63" s="75" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="J63" s="75" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L63" s="61" t="inlineStr">
+        <is>
+          <t>Scenarios: terminal g</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="75" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="C64" s="61" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F64" s="76">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="G64" s="76">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="H64" s="76">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="I64" s="76">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="J64" s="76">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="L64" s="61" t="inlineStr">
+        <is>
+          <t>WACC tab</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="74" t="inlineStr">
-        <is>
-          <t>WACC \ g</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>FRED: Real GDP (GDPC1)</t>
-        </is>
+      <c r="A65" s="75" t="n">
+        <v>0.1</v>
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
-        </is>
-      </c>
-      <c r="F65" s="75" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="G65" s="75" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="H65" s="75" t="n">
-        <v>0.0225</v>
-      </c>
-      <c r="I65" s="75" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="J65" s="75" t="n">
-        <v>0.03</v>
+          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
+        </is>
+      </c>
+      <c r="F65" s="76">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="G65" s="76">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="H65" s="76">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="I65" s="76">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="J65" s="76">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E36+E37)/E39</f>
+        <v/>
       </c>
       <c r="L65" s="61" t="inlineStr">
         <is>
-          <t>Scenarios: terminal g</t>
+          <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
       <c r="A66" s="75" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="C66" s="61" t="inlineStr">
-        <is>
-          <t>Damodaran: Historical Implied ERP</t>
-        </is>
+        <v>0.105</v>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
@@ -4405,23 +4223,23 @@
         </is>
       </c>
       <c r="F66" s="76">
-        <f>(NPV(0.095,F24:J24)+(J24*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E38+E39)/E41</f>
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="G66" s="76">
-        <f>(NPV(0.095,F24:J24)+(J24*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="H66" s="76">
-        <f>(NPV(0.095,F24:J24)+(J24*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E38+E39)/E41</f>
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="H66" s="77">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="I66" s="76">
-        <f>(NPV(0.095,F24:J24)+(J24*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E38+E39)/E41</f>
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="J66" s="76">
-        <f>(NPV(0.095,F24:J24)+(J24*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E38+E39)/E41</f>
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="L66" s="61" t="inlineStr">
@@ -4432,7 +4250,7 @@
     </row>
     <row r="67" ht="28" customHeight="1">
       <c r="A67" s="75" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
@@ -4440,23 +4258,23 @@
         </is>
       </c>
       <c r="F67" s="76">
-        <f>(NPV(0.1,F24:J24)+(J24*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E38+E39)/E41</f>
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="G67" s="76">
-        <f>(NPV(0.1,F24:J24)+(J24*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E38+E39)/E41</f>
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="H67" s="76">
-        <f>(NPV(0.1,F24:J24)+(J24*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E38+E39)/E41</f>
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="I67" s="76">
-        <f>(NPV(0.1,F24:J24)+(J24*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E38+E39)/E41</f>
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="J67" s="76">
-        <f>(NPV(0.1,F24:J24)+(J24*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E38+E39)/E41</f>
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="L67" s="61" t="inlineStr">
@@ -4467,7 +4285,7 @@
     </row>
     <row r="68" ht="28" customHeight="1">
       <c r="A68" s="75" t="n">
-        <v>0.105</v>
+        <v>0.115</v>
       </c>
       <c r="D68" s="19" t="inlineStr">
         <is>
@@ -4475,23 +4293,23 @@
         </is>
       </c>
       <c r="F68" s="76">
-        <f>(NPV(0.105,F24:J24)+(J24*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E38+E39)/E41</f>
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="G68" s="76">
-        <f>(NPV(0.105,F24:J24)+(J24*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="H68" s="77">
-        <f>(NPV(0.105,F24:J24)+(J24*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E38+E39)/E41</f>
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E36+E37)/E39</f>
+        <v/>
+      </c>
+      <c r="H68" s="76">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="I68" s="76">
-        <f>(NPV(0.105,F24:J24)+(J24*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E38+E39)/E41</f>
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="J68" s="76">
-        <f>(NPV(0.105,F24:J24)+(J24*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E38+E39)/E41</f>
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
       <c r="L68" s="61" t="inlineStr">
@@ -4501,97 +4319,27 @@
       </c>
     </row>
     <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="75" t="n">
-        <v>0.11</v>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>Scenarios: WACC &amp; terminal g</t>
+        </is>
       </c>
       <c r="D69" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F69" s="76">
-        <f>(NPV(0.11,F24:J24)+(J24*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="G69" s="76">
-        <f>(NPV(0.11,F24:J24)+(J24*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="H69" s="76">
-        <f>(NPV(0.11,F24:J24)+(J24*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="I69" s="76">
-        <f>(NPV(0.11,F24:J24)+(J24*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="J69" s="76">
-        <f>(NPV(0.11,F24:J24)+(J24*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E38+E39)/E41</f>
-        <v/>
+          <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
+        </is>
       </c>
       <c r="L69" s="61" t="inlineStr">
         <is>
-          <t>WACC tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="28" customHeight="1">
-      <c r="A70" s="75" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="D70" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
-        </is>
-      </c>
-      <c r="F70" s="76">
-        <f>(NPV(0.115,F24:J24)+(J24*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="G70" s="76">
-        <f>(NPV(0.115,F24:J24)+(J24*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="H70" s="76">
-        <f>(NPV(0.115,F24:J24)+(J24*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="I70" s="76">
-        <f>(NPV(0.115,F24:J24)+(J24*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="J70" s="76">
-        <f>(NPV(0.115,F24:J24)+(J24*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E38+E39)/E41</f>
-        <v/>
-      </c>
-      <c r="L70" s="61" t="inlineStr">
-        <is>
-          <t>WACC tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>Scenarios: WACC &amp; terminal g</t>
-        </is>
-      </c>
-      <c r="D71" s="19" t="inlineStr">
-        <is>
-          <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
-        </is>
-      </c>
-      <c r="L71" s="61" t="inlineStr">
-        <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="M71" s="19" t="inlineStr">
+      <c r="M69" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
@@ -4611,29 +4359,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId24"/>
-    <hyperlink ref="M49" location="'Comps'!A26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId25"/>
-    <hyperlink ref="L65" location="'Scenarios'!G10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C66" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId24"/>
+    <hyperlink ref="M47" location="'Comps'!A26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
+    <hyperlink ref="L63" location="'Scenarios'!G10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
+    <hyperlink ref="L64" location="'WACC'!E16"/>
+    <hyperlink ref="L65" location="'WACC'!E16"/>
     <hyperlink ref="L66" location="'WACC'!E16"/>
     <hyperlink ref="L67" location="'WACC'!E16"/>
     <hyperlink ref="L68" location="'WACC'!E16"/>
-    <hyperlink ref="L69" location="'WACC'!E16"/>
-    <hyperlink ref="L70" location="'WACC'!E16"/>
-    <hyperlink ref="C71" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId27"/>
+    <hyperlink ref="C69" location="'Scenarios'!G9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4739,7 +4487,7 @@
         </is>
       </c>
       <c r="E6" s="48">
-        <f>DCF!E33</f>
+        <f>DCF!E31</f>
         <v/>
       </c>
     </row>
@@ -5051,7 +4799,7 @@
         </is>
       </c>
       <c r="E25" s="60">
-        <f>DCF!E35</f>
+        <f>DCF!E33</f>
         <v/>
       </c>
     </row>
@@ -5062,7 +4810,7 @@
         </is>
       </c>
       <c r="E26" s="69">
-        <f>DCF!E49</f>
+        <f>DCF!E47</f>
         <v/>
       </c>
     </row>
@@ -5229,7 +4977,7 @@
         </is>
       </c>
       <c r="E38" s="85">
-        <f>DCF!E49</f>
+        <f>DCF!E47</f>
         <v/>
       </c>
       <c r="G38" s="86">
@@ -5293,11 +5041,11 @@
         </is>
       </c>
       <c r="G40" s="84">
-        <f>Scenarios!F75</f>
+        <f>Scenarios!F65</f>
         <v/>
       </c>
       <c r="H40" s="84">
-        <f>Scenarios!H75</f>
+        <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
@@ -5332,7 +5080,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId2"/>
-    <hyperlink ref="C6" location="'DCF'!E33"/>
+    <hyperlink ref="C6" location="'DCF'!E31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
@@ -5348,7 +5096,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
-    <hyperlink ref="C38" location="'DCF'!E49"/>
+    <hyperlink ref="C38" location="'DCF'!E47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId20"/>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -356,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -394,11 +394,14 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -1102,10 +1105,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -1198,12 +1201,12 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Levered beta</t>
+          <t>Observed Beta (5Y)</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>0.95 levered beta vs StockAnalysis Beta (5Y) 0.86; modest uplift for post-guidance volatility.</t>
+          <t>StockAnalysis Beta (5Y) is 0.86. Raw 5-year equity beta; no funded debt so levered ≈ unlevered.</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -1213,157 +1216,216 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Beta (5Y)" → 0.86. Model uses 0.95.</t>
+          <t>Ctrl+F "Beta (5Y)" → 0.86. This is the raw 5-year beta, not the 0.95 the model uses.</t>
         </is>
       </c>
       <c r="E5" s="21" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Post-guide vol uplift</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>10% because that 5Y beta is too calm after the Sep-4 −17% print and FY26 guide cut.</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU Sep-4 print</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "-17.38%" → Sep 4 close after Sep 3 earnings. Also Ctrl+F "52-Week Price Change" → -49.32%. +10% is the analyst overlay.</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Levered beta = ROUND(5Y × (1+uplift), 2)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>0.95 = ROUND(0.86 × 1.10, 2). 0.86 × 1.10 = 0.946, which rounds to 0.95. Formula, not a free 0.95.</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU Beta (5Y)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Observed 5Y beta (StockAnalysis)
+  Ctrl+F "Beta (5Y)"  →  0.86
+Why not use 0.86 as-is
+  Ctrl+F "-17.38%"  →  Sep 4 close after Sep 3 earnings
+  Ctrl+F "52-Week Price Change"  →  -49.32%
+  5Y beta is too calm for a name that just printed a guide cut
+Model levered beta
+  0.86 × 1.10 = 0.946
+  0.95 = ROUND(0.86 × 1.10, 2)</t>
+        </is>
+      </c>
+      <c r="E7" s="23">
+        <f>ROUND(E5*(1+E6),2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="E6" s="23">
-        <f>E3+E5*E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="E8" s="24">
+        <f>E3+E7*E4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Cost of debt</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>5.0% illustrative pre-tax debt cost; 10-K: no borrowings outstanding on the revolver.</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K (no funded debt)</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "no borrowings were outstanding under this facility" on this 10-K HTML page (search the document, do not use the EDGAR viewer TOC).</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E11" s="20" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>30% cash tax matches FY2026 guidance (“approximately 30%”); FY25 effective was 29.5%.</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "a tax rate of approximately 30%" on the FY2026 outlook paragraph.</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
+      <c r="E12" s="20" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="E11" s="24">
-        <f>E9*(1-E10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="E13" s="25">
+        <f>E11*(1-E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Capital structure (market values)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) | no funded term debt</t>
         </is>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E16" s="20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "no borrowings were outstanding under this facility" → debt weight 0%</t>
         </is>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E17" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="E16" s="25">
-        <f>E14*E6+E15*E11</f>
+      <c r="E18" s="26">
+        <f>E16*E8+E17*E13</f>
         <v/>
       </c>
     </row>
@@ -1372,10 +1434,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1414,17 +1478,17 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="G2" s="27" t="inlineStr">
+      <c r="G2" s="28" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="H2" s="28" t="inlineStr">
+      <c r="H2" s="29" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1566,13 +1630,13 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="30" t="n">
         <v>134500</v>
       </c>
-      <c r="G7" s="29" t="n">
+      <c r="G7" s="30" t="n">
         <v>134500</v>
       </c>
-      <c r="H7" s="29" t="n">
+      <c r="H7" s="30" t="n">
         <v>134500</v>
       </c>
     </row>
@@ -1743,7 +1807,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -1845,856 +1909,856 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="31" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <f>11102600*(1+F4)</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="33">
         <f>11102600*(1+G4)</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="33">
         <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>F18*(1+F5)</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="33">
         <f>G18*(1+G5)</f>
         <v/>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="33">
         <f>H18*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="31" t="inlineStr">
+      <c r="A20" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="33">
         <f>F19*(1+F5)</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="33">
         <f>G19*(1+G5)</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="33">
         <f>H19*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <f>F20*(1+F5)</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <f>G20*(1+G5)</f>
         <v/>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <f>H20*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>F21*(1+F5)</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <f>G21*(1+G5)</f>
         <v/>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <f>H21*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="34">
         <f>F6+(F8-F6)*0/4</f>
         <v/>
       </c>
-      <c r="G23" s="33">
+      <c r="G23" s="34">
         <f>G6+(G8-G6)*0/4</f>
         <v/>
       </c>
-      <c r="H23" s="33">
+      <c r="H23" s="34">
         <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="31" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="34">
         <f>F6+(F8-F6)*1/4</f>
         <v/>
       </c>
-      <c r="G24" s="33">
+      <c r="G24" s="34">
         <f>G6+(G8-G6)*1/4</f>
         <v/>
       </c>
-      <c r="H24" s="33">
+      <c r="H24" s="34">
         <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="34">
         <f>F6+(F8-F6)*2/4</f>
         <v/>
       </c>
-      <c r="G25" s="33">
+      <c r="G25" s="34">
         <f>G6+(G8-G6)*2/4</f>
         <v/>
       </c>
-      <c r="H25" s="33">
+      <c r="H25" s="34">
         <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="31" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="34">
         <f>F6+(F8-F6)*3/4</f>
         <v/>
       </c>
-      <c r="G26" s="33">
+      <c r="G26" s="34">
         <f>G6+(G8-G6)*3/4</f>
         <v/>
       </c>
-      <c r="H26" s="33">
+      <c r="H26" s="34">
         <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="inlineStr">
+      <c r="A27" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <f>F6+(F8-F6)*4/4</f>
         <v/>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <f>G6+(G8-G6)*4/4</f>
         <v/>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <f>H6+(H8-H6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <f>F18*F23+F7</f>
         <v/>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <f>G18*G23+G7</f>
         <v/>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <f>H18*H23+H7</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="33">
         <f>F19*F24</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="33">
         <f>G19*G24</f>
         <v/>
       </c>
-      <c r="H29" s="32">
+      <c r="H29" s="33">
         <f>H19*H24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <f>F20*F25</f>
         <v/>
       </c>
-      <c r="G30" s="32">
+      <c r="G30" s="33">
         <f>G20*G25</f>
         <v/>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="33">
         <f>H20*H25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="33">
         <f>F21*F26</f>
         <v/>
       </c>
-      <c r="G31" s="32">
+      <c r="G31" s="33">
         <f>G21*G26</f>
         <v/>
       </c>
-      <c r="H31" s="32">
+      <c r="H31" s="33">
         <f>H21*H26</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="33">
         <f>F22*F27</f>
         <v/>
       </c>
-      <c r="G32" s="32">
+      <c r="G32" s="33">
         <f>G22*G27</f>
         <v/>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="33">
         <f>H22*H27</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <f>F28*(1-F11)</f>
         <v/>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <f>G28*(1-G11)</f>
         <v/>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <f>H28*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="31" t="inlineStr">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <f>F29*(1-F11)</f>
         <v/>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <f>G29*(1-G11)</f>
         <v/>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="33">
         <f>H29*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="inlineStr">
+      <c r="A35" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="33">
         <f>F30*(1-F11)</f>
         <v/>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <f>G30*(1-G11)</f>
         <v/>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <f>H30*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="31" t="inlineStr">
+      <c r="A36" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <f>F31*(1-F11)</f>
         <v/>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <f>G31*(1-G11)</f>
         <v/>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="33">
         <f>H31*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="inlineStr">
+      <c r="A37" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="33">
         <f>F32*(1-F11)</f>
         <v/>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="33">
         <f>G32*(1-G11)</f>
         <v/>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="33">
         <f>H32*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <f>F18*F12</f>
         <v/>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <f>G18*G12</f>
         <v/>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <f>H18*H12</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="inlineStr">
+      <c r="A39" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <f>F19*F12</f>
         <v/>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <f>G19*G12</f>
         <v/>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <f>H19*H12</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="31" t="inlineStr">
+      <c r="A40" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="33">
         <f>F20*F12</f>
         <v/>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="33">
         <f>G20*G12</f>
         <v/>
       </c>
-      <c r="H40" s="32">
+      <c r="H40" s="33">
         <f>H20*H12</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <f>F21*F12</f>
         <v/>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <f>G21*G12</f>
         <v/>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <f>H21*H12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="31" t="inlineStr">
+      <c r="A42" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <f>F22*F12</f>
         <v/>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <f>G22*G12</f>
         <v/>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <f>H22*H12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="inlineStr">
+      <c r="A43" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="F43" s="32">
+      <c r="F43" s="33">
         <f>F18*F13</f>
         <v/>
       </c>
-      <c r="G43" s="32">
+      <c r="G43" s="33">
         <f>G18*G13</f>
         <v/>
       </c>
-      <c r="H43" s="32">
+      <c r="H43" s="33">
         <f>H18*H13</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="31" t="inlineStr">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <f>F19*F13</f>
         <v/>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <f>G19*G13</f>
         <v/>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <f>H19*H13</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="31" t="inlineStr">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <f>F20*F13</f>
         <v/>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <f>G20*G13</f>
         <v/>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <f>H20*H13</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="31" t="inlineStr">
+      <c r="A46" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="F46" s="32">
+      <c r="F46" s="33">
         <f>F21*F13</f>
         <v/>
       </c>
-      <c r="G46" s="32">
+      <c r="G46" s="33">
         <f>G21*G13</f>
         <v/>
       </c>
-      <c r="H46" s="32">
+      <c r="H46" s="33">
         <f>H21*H13</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="31" t="inlineStr">
+      <c r="A47" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="33">
         <f>F22*F13</f>
         <v/>
       </c>
-      <c r="G47" s="32">
+      <c r="G47" s="33">
         <f>G22*G13</f>
         <v/>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="33">
         <f>H22*H13</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="31" t="inlineStr">
+      <c r="A48" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 1</t>
         </is>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="33">
         <f>F18*F15</f>
         <v/>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <f>G18*G15</f>
         <v/>
       </c>
-      <c r="H48" s="32">
+      <c r="H48" s="33">
         <f>H18*H15</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 2</t>
         </is>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="33">
         <f>F19*F15</f>
         <v/>
       </c>
-      <c r="G49" s="32">
+      <c r="G49" s="33">
         <f>G19*G15</f>
         <v/>
       </c>
-      <c r="H49" s="32">
+      <c r="H49" s="33">
         <f>H19*H15</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="31" t="inlineStr">
+      <c r="A50" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 3</t>
         </is>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="33">
         <f>F20*F15</f>
         <v/>
       </c>
-      <c r="G50" s="32">
+      <c r="G50" s="33">
         <f>G20*G15</f>
         <v/>
       </c>
-      <c r="H50" s="32">
+      <c r="H50" s="33">
         <f>H20*H15</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="31" t="inlineStr">
+      <c r="A51" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 4</t>
         </is>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="33">
         <f>F21*F15</f>
         <v/>
       </c>
-      <c r="G51" s="32">
+      <c r="G51" s="33">
         <f>G21*G15</f>
         <v/>
       </c>
-      <c r="H51" s="32">
+      <c r="H51" s="33">
         <f>H21*H15</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="31" t="inlineStr">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 5</t>
         </is>
       </c>
-      <c r="F52" s="32">
+      <c r="F52" s="33">
         <f>F22*F15</f>
         <v/>
       </c>
-      <c r="G52" s="32">
+      <c r="G52" s="33">
         <f>G22*G15</f>
         <v/>
       </c>
-      <c r="H52" s="32">
+      <c r="H52" s="33">
         <f>H22*H15</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="31" t="inlineStr">
+      <c r="A53" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 1</t>
         </is>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="33">
         <f>F14*(F18-11102600)</f>
         <v/>
       </c>
-      <c r="G53" s="32">
+      <c r="G53" s="33">
         <f>G14*(G18-11102600)</f>
         <v/>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <f>H14*(H18-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="31" t="inlineStr">
+      <c r="A54" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 2</t>
         </is>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <f>F14*(F19-F18)</f>
         <v/>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <f>G14*(G19-G18)</f>
         <v/>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <f>H14*(H19-H18)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="31" t="inlineStr">
+      <c r="A55" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 3</t>
         </is>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="33">
         <f>F14*(F20-F19)</f>
         <v/>
       </c>
-      <c r="G55" s="32">
+      <c r="G55" s="33">
         <f>G14*(G20-G19)</f>
         <v/>
       </c>
-      <c r="H55" s="32">
+      <c r="H55" s="33">
         <f>H14*(H20-H19)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="31" t="inlineStr">
+      <c r="A56" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 4</t>
         </is>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="33">
         <f>F14*(F21-F20)</f>
         <v/>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="33">
         <f>G14*(G21-G20)</f>
         <v/>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <f>H14*(H21-H20)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 5</t>
         </is>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <f>F14*(F22-F21)</f>
         <v/>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <f>G14*(G22-G21)</f>
         <v/>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <f>H14*(H22-H21)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="33">
         <f>F33+F38-F43-F53</f>
         <v/>
       </c>
-      <c r="G58" s="32">
+      <c r="G58" s="33">
         <f>G33+G38-G43-G53</f>
         <v/>
       </c>
-      <c r="H58" s="32">
+      <c r="H58" s="33">
         <f>H33+H38-H43-H53</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="31" t="inlineStr">
+      <c r="A59" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="33">
         <f>F34+F39-F44-F54</f>
         <v/>
       </c>
-      <c r="G59" s="32">
+      <c r="G59" s="33">
         <f>G34+G39-G44-G54</f>
         <v/>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <f>H34+H39-H44-H54</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="31" t="inlineStr">
+      <c r="A60" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="33">
         <f>F35+F40-F45-F55</f>
         <v/>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="33">
         <f>G35+G40-G45-G55</f>
         <v/>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="33">
         <f>H35+H40-H45-H55</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="33">
         <f>F36+F41-F46-F56</f>
         <v/>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="33">
         <f>G36+G41-G46-G56</f>
         <v/>
       </c>
-      <c r="H61" s="32">
+      <c r="H61" s="33">
         <f>H36+H41-H46-H56</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="31" t="inlineStr">
+      <c r="A62" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <f>F37+F42-F47-F57</f>
         <v/>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <f>G37+G42-G47-G57</f>
         <v/>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <f>H37+H42-H47-H57</f>
         <v/>
       </c>
@@ -2705,34 +2769,34 @@
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F64" s="34">
+      <c r="F64" s="35">
         <f>NPV(F9,F58,F59,F60,F61,F62)+(F62*(1+F10)/(F9-F10))/(1+F9)^5</f>
         <v/>
       </c>
-      <c r="G64" s="34">
+      <c r="G64" s="35">
         <f>NPV(G9,G58,G59,G60,G61,G62)+(G62*(1+G10)/(G9-G10))/(1+G9)^5</f>
         <v/>
       </c>
-      <c r="H64" s="34">
+      <c r="H64" s="35">
         <f>NPV(H9,H58,H59,H60,H61,H62)+(H62*(1+H10)/(H9-H10))/(1+H9)^5</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="35" t="inlineStr">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F65" s="36">
+      <c r="F65" s="37">
         <f>(F64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="G65" s="37">
+      <c r="G65" s="38">
         <f>(G64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="H65" s="36">
+      <c r="H65" s="37">
         <f>(H64+1807202-0)/111380</f>
         <v/>
       </c>
@@ -2743,21 +2807,21 @@
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F66" s="38">
+      <c r="F66" s="39">
         <f>F65/100.0-1</f>
         <v/>
       </c>
-      <c r="G66" s="38">
+      <c r="G66" s="39">
         <f>G65/100.0-1</f>
         <v/>
       </c>
-      <c r="H66" s="38">
+      <c r="H66" s="39">
         <f>H65/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="39" t="inlineStr">
+      <c r="A68" s="40" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2770,7 +2834,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink ref="C9" location="'WACC'!E16"/>
+    <hyperlink ref="C9" location="'WACC'!E18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
@@ -2823,69 +2887,69 @@
       <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="C2" s="40" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D2" s="40" t="inlineStr">
+      <c r="D2" s="41" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E2" s="41" t="inlineStr">
+      <c r="E2" s="42" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F2" s="42" t="inlineStr">
+      <c r="F2" s="43" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G2" s="42" t="inlineStr">
+      <c r="G2" s="43" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H2" s="42" t="inlineStr">
+      <c r="H2" s="43" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I2" s="42" t="inlineStr">
+      <c r="I2" s="43" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J2" s="42" t="inlineStr">
+      <c r="J2" s="43" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="K2" s="43" t="inlineStr">
+      <c r="K2" s="44" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="L2" s="40" t="inlineStr">
+      <c r="L2" s="41" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="M2" s="40" t="inlineStr">
+      <c r="M2" s="41" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="44" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
         </is>
@@ -2895,12 +2959,12 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
-      <c r="E3" s="45" t="inlineStr">
+      <c r="E3" s="46" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="K3" s="46" t="inlineStr">
+      <c r="K3" s="47" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2912,30 +2976,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="E5" s="47" t="n">
+      <c r="E5" s="48" t="n">
         <v>11102600</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="49">
         <f>Scenarios!G18</f>
         <v/>
       </c>
-      <c r="G5" s="48">
+      <c r="G5" s="49">
         <f>Scenarios!G19</f>
         <v/>
       </c>
-      <c r="H5" s="48">
+      <c r="H5" s="49">
         <f>Scenarios!G20</f>
         <v/>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="49">
         <f>Scenarios!G21</f>
         <v/>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="49">
         <f>Scenarios!G22</f>
         <v/>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="50">
         <f>IF(MAX(ABS(F5-Scenarios!$G$18),ABS(G5-Scenarios!$G$19),ABS(H5-Scenarios!$G$20),ABS(I5-Scenarios!$G$21),ABS(J5-Scenarios!$G$22))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -2952,7 +3016,7 @@
 Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
 Also: StockAnalysis: LULU 3Y revenue forecast</t>
@@ -2964,23 +3028,23 @@
 Also: Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="51">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="51">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="51">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="50">
+      <c r="I6" s="51">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="50">
+      <c r="J6" s="51">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -2997,7 +3061,7 @@
 Also: FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
 Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
@@ -3009,27 +3073,27 @@
 Also: Ctrl+F "19.9%" (one hit) → Operating margin decreased 380 basis points to 19.9%. That is FY25 OM. Do not search the words Income from operations (17 hits). Model FY30 15.5% is a partial-recovery assumption.</t>
         </is>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="51">
         <f>Scenarios!G23</f>
         <v/>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="51">
         <f>Scenarios!G24</f>
         <v/>
       </c>
-      <c r="H7" s="50">
+      <c r="H7" s="51">
         <f>Scenarios!G25</f>
         <v/>
       </c>
-      <c r="I7" s="50">
+      <c r="I7" s="51">
         <f>Scenarios!G26</f>
         <v/>
       </c>
-      <c r="J7" s="50">
+      <c r="J7" s="51">
         <f>Scenarios!G27</f>
         <v/>
       </c>
-      <c r="K7" s="49">
+      <c r="K7" s="50">
         <f>IF(MAX(ABS(F7-Scenarios!$G$23),ABS(G7-Scenarios!$G$24),ABS(H7-Scenarios!$G$25),ABS(I7-Scenarios!$G$26),ABS(J7-Scenarios!$G$27))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3055,23 +3119,23 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="48" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <f>Scenarios!$G$7</f>
         <v/>
       </c>
-      <c r="G8" s="29" t="n">
+      <c r="G8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="29" t="n">
+      <c r="H8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="29" t="n">
+      <c r="I8" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="29" t="n">
+      <c r="J8" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3081,30 +3145,30 @@
           <t>EBIT (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E9" s="51" t="n">
+      <c r="E9" s="52" t="n">
         <v>2210615</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>Scenarios!G28</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="35">
         <f>Scenarios!G29</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="35">
         <f>Scenarios!G30</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="35">
         <f>Scenarios!G31</f>
         <v/>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="35">
         <f>Scenarios!G32</f>
         <v/>
       </c>
-      <c r="K9" s="52">
+      <c r="K9" s="53">
         <f>IF(MAX(ABS(F9-Scenarios!$G$28),ABS(G9-Scenarios!$G$29),ABS(H9-Scenarios!$G$30),ABS(I9-Scenarios!$G$31),ABS(J9-Scenarios!$G$32))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3115,26 +3179,26 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E10" s="53" t="n">
+      <c r="E10" s="54" t="n">
         <v>0.1991078666258354</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="51">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G10" s="50">
+      <c r="G10" s="51">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H10" s="50">
+      <c r="H10" s="51">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I10" s="50">
+      <c r="I10" s="51">
         <f>I9/I5</f>
         <v/>
       </c>
-      <c r="J10" s="50">
+      <c r="J10" s="51">
         <f>J9/J5</f>
         <v/>
       </c>
@@ -3145,23 +3209,23 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="49">
         <f>-Scenarios!G28*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="49">
         <f>-Scenarios!G29*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="H11" s="48">
+      <c r="H11" s="49">
         <f>-Scenarios!G30*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="I11" s="48">
+      <c r="I11" s="49">
         <f>-Scenarios!G31*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="J11" s="48">
+      <c r="J11" s="49">
         <f>-Scenarios!G32*Scenarios!$G$11</f>
         <v/>
       </c>
@@ -3172,27 +3236,27 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F12" s="34">
+      <c r="F12" s="35">
         <f>Scenarios!G33</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="35">
         <f>Scenarios!G34</f>
         <v/>
       </c>
-      <c r="H12" s="34">
+      <c r="H12" s="35">
         <f>Scenarios!G35</f>
         <v/>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="35">
         <f>Scenarios!G36</f>
         <v/>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="35">
         <f>Scenarios!G37</f>
         <v/>
       </c>
-      <c r="K12" s="52">
+      <c r="K12" s="53">
         <f>IF(MAX(ABS(F12-Scenarios!$G$33),ABS(G12-Scenarios!$G$34),ABS(H12-Scenarios!$G$35),ABS(I12-Scenarios!$G$36),ABS(J12-Scenarios!$G$37))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3245,27 +3309,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="49">
         <f>Scenarios!G38</f>
         <v/>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="49">
         <f>Scenarios!G39</f>
         <v/>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="49">
         <f>Scenarios!G40</f>
         <v/>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="49">
         <f>Scenarios!G41</f>
         <v/>
       </c>
-      <c r="J14" s="48">
+      <c r="J14" s="49">
         <f>Scenarios!G42</f>
         <v/>
       </c>
-      <c r="K14" s="49">
+      <c r="K14" s="50">
         <f>IF(MAX(ABS(F14-Scenarios!$G$38),ABS(G14-Scenarios!$G$39),ABS(H14-Scenarios!$G$40),ABS(I14-Scenarios!$G$41),ABS(J14-Scenarios!$G$42))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3282,7 +3346,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -3331,27 +3395,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="49">
         <f>-Scenarios!G43</f>
         <v/>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="49">
         <f>-Scenarios!G44</f>
         <v/>
       </c>
-      <c r="H16" s="48">
+      <c r="H16" s="49">
         <f>-Scenarios!G45</f>
         <v/>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="49">
         <f>-Scenarios!G46</f>
         <v/>
       </c>
-      <c r="J16" s="48">
+      <c r="J16" s="49">
         <f>-Scenarios!G47</f>
         <v/>
       </c>
-      <c r="K16" s="49">
+      <c r="K16" s="50">
         <f>IF(MAX(ABS(F16+Scenarios!$G$43),ABS(G16+Scenarios!$G$44),ABS(H16+Scenarios!$G$45),ABS(I16+Scenarios!$G$46),ABS(J16+Scenarios!$G$47))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3461,30 +3525,30 @@
           <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
         </is>
       </c>
-      <c r="E19" s="47" t="n">
+      <c r="E19" s="48" t="n">
         <v>190657</v>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="49">
         <f>Scenarios!G48</f>
         <v/>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="49">
         <f>Scenarios!G49</f>
         <v/>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="49">
         <f>Scenarios!G50</f>
         <v/>
       </c>
-      <c r="I19" s="48">
+      <c r="I19" s="49">
         <f>Scenarios!G51</f>
         <v/>
       </c>
-      <c r="J19" s="48">
+      <c r="J19" s="49">
         <f>Scenarios!G52</f>
         <v/>
       </c>
-      <c r="K19" s="49">
+      <c r="K19" s="50">
         <f>IF(MAX(ABS(F19-Scenarios!$G$48),ABS(G19-Scenarios!$G$49),ABS(H19-Scenarios!$G$50),ABS(I19-Scenarios!$G$51),ABS(J19-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3495,33 +3559,33 @@
           <t>(Increase)/decrease in NWC (includes AR)</t>
         </is>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="49">
         <f>-Scenarios!G53</f>
         <v/>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="49">
         <f>-Scenarios!G54</f>
         <v/>
       </c>
-      <c r="H20" s="48">
+      <c r="H20" s="49">
         <f>-Scenarios!G55</f>
         <v/>
       </c>
-      <c r="I20" s="48">
+      <c r="I20" s="49">
         <f>-Scenarios!G56</f>
         <v/>
       </c>
-      <c r="J20" s="48">
+      <c r="J20" s="49">
         <f>-Scenarios!G57</f>
         <v/>
       </c>
-      <c r="K20" s="49">
+      <c r="K20" s="50">
         <f>IF(MAX(ABS(F20+Scenarios!$G$53),ABS(G20+Scenarios!$G$54),ABS(H20+Scenarios!$G$55),ABS(I20+Scenarios!$G$56),ABS(J20+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: NWC and AR are one line. 7.5% of Δsales already includes AR; UFCF does not take ΔAR separately.</t>
         </is>
@@ -3533,27 +3597,27 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="55">
         <f>Scenarios!G58</f>
         <v/>
       </c>
-      <c r="G22" s="54">
+      <c r="G22" s="55">
         <f>Scenarios!G59</f>
         <v/>
       </c>
-      <c r="H22" s="54">
+      <c r="H22" s="55">
         <f>Scenarios!G60</f>
         <v/>
       </c>
-      <c r="I22" s="54">
+      <c r="I22" s="55">
         <f>Scenarios!G61</f>
         <v/>
       </c>
-      <c r="J22" s="54">
+      <c r="J22" s="55">
         <f>Scenarios!G62</f>
         <v/>
       </c>
-      <c r="K22" s="52">
+      <c r="K22" s="53">
         <f>IF(MAX(ABS(F22-Scenarios!$G$58),ABS(G22-Scenarios!$G$59),ABS(H22-Scenarios!$G$60),ABS(I22-Scenarios!$G$61),ABS(J22-Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3564,19 +3628,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="F23" s="55" t="n">
+      <c r="F23" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="55" t="n">
+      <c r="G23" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="55" t="n">
+      <c r="H23" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="55" t="n">
+      <c r="I23" s="56" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="55" t="n">
+      <c r="J23" s="56" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3586,23 +3650,23 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="F24" s="56">
+      <c r="F24" s="57">
         <f>1/(1+Scenarios!$G$9)^F23</f>
         <v/>
       </c>
-      <c r="G24" s="56">
+      <c r="G24" s="57">
         <f>1/(1+Scenarios!$G$9)^G23</f>
         <v/>
       </c>
-      <c r="H24" s="56">
+      <c r="H24" s="57">
         <f>1/(1+Scenarios!$G$9)^H23</f>
         <v/>
       </c>
-      <c r="I24" s="56">
+      <c r="I24" s="57">
         <f>1/(1+Scenarios!$G$9)^I23</f>
         <v/>
       </c>
-      <c r="J24" s="56">
+      <c r="J24" s="57">
         <f>1/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
@@ -3613,23 +3677,23 @@
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="35">
         <f>F22*F24</f>
         <v/>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="35">
         <f>G22*G24</f>
         <v/>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="35">
         <f>H22*H24</f>
         <v/>
       </c>
-      <c r="I25" s="34">
+      <c r="I25" s="35">
         <f>I22*I24</f>
         <v/>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="35">
         <f>J22*J24</f>
         <v/>
       </c>
@@ -3640,13 +3704,13 @@
           <t>Scenarios linkage summary (column K should all read OK)</t>
         </is>
       </c>
-      <c r="K27" s="57">
+      <c r="K27" s="58">
         <f>IF(COUNTIF(K5:K22,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="58" t="inlineStr">
+      <c r="A28" s="59" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3660,7 +3724,7 @@
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="E29" s="59">
+      <c r="E29" s="60">
         <f>SUM(F25:J25)</f>
         <v/>
       </c>
@@ -3686,7 +3750,7 @@
           <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="51">
         <f>Scenarios!$G$10</f>
         <v/>
       </c>
@@ -3697,7 +3761,7 @@
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="35">
         <f>J9+J14</f>
         <v/>
       </c>
@@ -3708,7 +3772,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="E32" s="48">
+      <c r="E32" s="49">
         <f>J22*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
         <v/>
       </c>
@@ -3719,7 +3783,7 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="E33" s="60">
+      <c r="E33" s="61">
         <f>E32/E31</f>
         <v/>
       </c>
@@ -3730,7 +3794,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E34" s="59">
+      <c r="E34" s="60">
         <f>E32/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
@@ -3741,7 +3805,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <f>E29+E34</f>
         <v/>
       </c>
@@ -3752,7 +3816,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C36" s="61" t="inlineStr">
+      <c r="C36" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3762,7 +3826,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E36" s="47" t="n">
+      <c r="E36" s="48" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -3772,7 +3836,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C37" s="61" t="inlineStr">
+      <c r="C37" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3782,7 +3846,7 @@
           <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
         </is>
       </c>
-      <c r="E37" s="47" t="n">
+      <c r="E37" s="48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3792,7 +3856,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="35">
         <f>E35+E36+E37</f>
         <v/>
       </c>
@@ -3803,7 +3867,7 @@
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C39" s="61" t="inlineStr">
+      <c r="C39" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3813,7 +3877,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E39" s="47" t="n">
+      <c r="E39" s="48" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -3823,11 +3887,11 @@
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="E40" s="62">
+      <c r="E40" s="63">
         <f>E38/E39</f>
         <v/>
       </c>
-      <c r="K40" s="52">
+      <c r="K40" s="53">
         <f>IF(ABS(E40-Scenarios!$G$65)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3838,7 +3902,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C41" s="61" t="inlineStr">
+      <c r="C41" s="62" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -3848,7 +3912,7 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E41" s="63" t="n">
+      <c r="E41" s="64" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3858,7 +3922,7 @@
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="E42" s="64">
+      <c r="E42" s="65">
         <f>E40/E41-1</f>
         <v/>
       </c>
@@ -3869,13 +3933,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="E43" s="50">
+      <c r="E43" s="51">
         <f>E34/E35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="58" t="inlineStr">
+      <c r="A45" s="59" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3911,10 +3975,10 @@
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E47" s="65" t="n">
+      <c r="E47" s="66" t="n">
         <v>8</v>
       </c>
-      <c r="M47" s="61" t="inlineStr">
+      <c r="M47" s="62" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3926,7 +3990,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="E48" s="48">
+      <c r="E48" s="49">
         <f>E31*E47</f>
         <v/>
       </c>
@@ -3937,7 +4001,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>E48/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
@@ -3948,7 +4012,7 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="35">
         <f>E29+E49</f>
         <v/>
       </c>
@@ -3959,13 +4023,13 @@
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="E51" s="66">
+      <c r="E51" s="67">
         <f>(E50+E36+E37)/E39</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="58" t="inlineStr">
+      <c r="A53" s="59" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -3975,18 +4039,18 @@
       <c r="D53" s="13" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="67" t="inlineStr"/>
-      <c r="B54" s="68" t="inlineStr">
+      <c r="A54" s="68" t="inlineStr"/>
+      <c r="B54" s="69" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C54" s="68" t="inlineStr">
+      <c r="C54" s="69" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D54" s="68" t="inlineStr">
+      <c r="D54" s="69" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
@@ -3998,15 +4062,15 @@
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B55" s="59">
+      <c r="B55" s="60">
         <f>E32</f>
         <v/>
       </c>
-      <c r="C55" s="59">
+      <c r="C55" s="60">
         <f>E48</f>
         <v/>
       </c>
-      <c r="D55" s="59">
+      <c r="D55" s="60">
         <f>B55-C55</f>
         <v/>
       </c>
@@ -4017,15 +4081,15 @@
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B56" s="69">
+      <c r="B56" s="70">
         <f>E33</f>
         <v/>
       </c>
-      <c r="C56" s="69">
+      <c r="C56" s="70">
         <f>E47</f>
         <v/>
       </c>
-      <c r="D56" s="69">
+      <c r="D56" s="70">
         <f>B56-C56</f>
         <v/>
       </c>
@@ -4036,9 +4100,9 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B57" s="50" t="inlineStr"/>
-      <c r="C57" s="50" t="inlineStr"/>
-      <c r="D57" s="50">
+      <c r="B57" s="51" t="inlineStr"/>
+      <c r="C57" s="51" t="inlineStr"/>
+      <c r="D57" s="51">
         <f>(B55-C55)/B55</f>
         <v/>
       </c>
@@ -4049,41 +4113,41 @@
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B58" s="70">
+      <c r="B58" s="71">
         <f>E40</f>
         <v/>
       </c>
-      <c r="C58" s="70">
+      <c r="C58" s="71">
         <f>E51</f>
         <v/>
       </c>
-      <c r="D58" s="70">
+      <c r="D58" s="71">
         <f>B58-C58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="71" t="inlineStr">
+      <c r="A59" s="72" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B59" s="72">
+      <c r="B59" s="73">
         <f>IF(ABS(D56)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C59" s="73">
+      <c r="C59" s="74">
         <f>TEXT(D56,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D59" s="39" t="inlineStr">
+      <c r="D59" s="40" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="58" t="inlineStr">
+      <c r="A62" s="59" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -4097,7 +4161,7 @@
       <c r="H62" s="13" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="74" t="inlineStr">
+      <c r="A63" s="75" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
@@ -4117,32 +4181,32 @@
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
-      <c r="F63" s="75" t="n">
+      <c r="F63" s="76" t="n">
         <v>0.015</v>
       </c>
-      <c r="G63" s="75" t="n">
+      <c r="G63" s="76" t="n">
         <v>0.02</v>
       </c>
-      <c r="H63" s="75" t="n">
+      <c r="H63" s="76" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I63" s="75" t="n">
+      <c r="I63" s="76" t="n">
         <v>0.025</v>
       </c>
-      <c r="J63" s="75" t="n">
+      <c r="J63" s="76" t="n">
         <v>0.03</v>
       </c>
-      <c r="L63" s="61" t="inlineStr">
+      <c r="L63" s="62" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="75" t="n">
+      <c r="A64" s="76" t="n">
         <v>0.095</v>
       </c>
-      <c r="C64" s="61" t="inlineStr">
+      <c r="C64" s="62" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -4152,34 +4216,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F64" s="76">
+      <c r="F64" s="77">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G64" s="76">
+      <c r="G64" s="77">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H64" s="76">
+      <c r="H64" s="77">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I64" s="76">
+      <c r="I64" s="77">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J64" s="76">
+      <c r="J64" s="77">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L64" s="61" t="inlineStr">
+      <c r="L64" s="62" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="75" t="n">
+      <c r="A65" s="76" t="n">
         <v>0.1</v>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -4187,34 +4251,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F65" s="76">
+      <c r="F65" s="77">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G65" s="76">
+      <c r="G65" s="77">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H65" s="76">
+      <c r="H65" s="77">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I65" s="76">
+      <c r="I65" s="77">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J65" s="76">
+      <c r="J65" s="77">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L65" s="61" t="inlineStr">
+      <c r="L65" s="62" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="75" t="n">
+      <c r="A66" s="76" t="n">
         <v>0.105</v>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -4222,34 +4286,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F66" s="76">
+      <c r="F66" s="77">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G66" s="76">
+      <c r="G66" s="77">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H66" s="77">
+      <c r="H66" s="78">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I66" s="76">
+      <c r="I66" s="77">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J66" s="76">
+      <c r="J66" s="77">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L66" s="61" t="inlineStr">
+      <c r="L66" s="62" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="75" t="n">
+      <c r="A67" s="76" t="n">
         <v>0.11</v>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -4257,34 +4321,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F67" s="76">
+      <c r="F67" s="77">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G67" s="76">
+      <c r="G67" s="77">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H67" s="76">
+      <c r="H67" s="77">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I67" s="76">
+      <c r="I67" s="77">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J67" s="76">
+      <c r="J67" s="77">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L67" s="61" t="inlineStr">
+      <c r="L67" s="62" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="75" t="n">
+      <c r="A68" s="76" t="n">
         <v>0.115</v>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -4292,27 +4356,27 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F68" s="76">
+      <c r="F68" s="77">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G68" s="76">
+      <c r="G68" s="77">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H68" s="76">
+      <c r="H68" s="77">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I68" s="76">
+      <c r="I68" s="77">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J68" s="76">
+      <c r="J68" s="77">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L68" s="61" t="inlineStr">
+      <c r="L68" s="62" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
@@ -4334,7 +4398,7 @@
           <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
-      <c r="L69" s="61" t="inlineStr">
+      <c r="L69" s="62" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -4375,11 +4439,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
     <hyperlink ref="L63" location="'Scenarios'!G10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
-    <hyperlink ref="L64" location="'WACC'!E16"/>
-    <hyperlink ref="L65" location="'WACC'!E16"/>
-    <hyperlink ref="L66" location="'WACC'!E16"/>
-    <hyperlink ref="L67" location="'WACC'!E16"/>
-    <hyperlink ref="L68" location="'WACC'!E16"/>
+    <hyperlink ref="L64" location="'WACC'!E18"/>
+    <hyperlink ref="L65" location="'WACC'!E18"/>
+    <hyperlink ref="L66" location="'WACC'!E18"/>
+    <hyperlink ref="L67" location="'WACC'!E18"/>
+    <hyperlink ref="L68" location="'WACC'!E18"/>
     <hyperlink ref="C69" location="'Scenarios'!G9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId27"/>
   </hyperlinks>
@@ -4450,7 +4514,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="61" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4460,7 +4524,7 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 ($000) in FY2025 column</t>
         </is>
       </c>
-      <c r="E4" s="47" t="n">
+      <c r="E4" s="48" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -4470,7 +4534,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="49">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -4481,12 +4545,12 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="61" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="49">
         <f>DCF!E31</f>
         <v/>
       </c>
@@ -4497,7 +4561,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="61" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -4507,7 +4571,7 @@
           <t>Ctrl+F "$9.48 to $9.73" → FY2026 diluted EPS guidance; model midpoint $9.61</t>
         </is>
       </c>
-      <c r="E7" s="63" t="n">
+      <c r="E7" s="64" t="n">
         <v>9.609999999999999</v>
       </c>
     </row>
@@ -4517,7 +4581,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="61" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4527,7 +4591,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E8" s="47" t="n">
+      <c r="E8" s="48" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -4537,7 +4601,7 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="61" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4547,7 +4611,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E9" s="47" t="n">
+      <c r="E9" s="48" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -4557,7 +4621,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="61" t="inlineStr">
+      <c r="C10" s="62" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -4567,28 +4631,28 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E10" s="63" t="n">
+      <c r="E10" s="64" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="73" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="E11" s="78">
+      <c r="E11" s="79">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="73" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="79">
         <f>E10/E7</f>
         <v/>
       </c>
@@ -4601,34 +4665,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="73" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="79" t="inlineStr">
+      <c r="A16" s="80" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="79" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C16" s="79" t="inlineStr">
+      <c r="C16" s="80" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D16" s="79" t="inlineStr">
+      <c r="D16" s="80" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E16" s="80" t="inlineStr">
+      <c r="E16" s="81" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
@@ -4640,12 +4704,12 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="40" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="C17" s="61" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
@@ -4655,7 +4719,7 @@
           <t>Ctrl+F "19.9%" → FY25 OM (EBIT $2,210,615). Ctrl+F "496,228" → Depreciation and amortization. Do not search the words Income from operations (17 hits).</t>
         </is>
       </c>
-      <c r="E17" s="81">
+      <c r="E17" s="82">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
@@ -4681,7 +4745,7 @@
           <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
         </is>
       </c>
-      <c r="E18" s="82" t="n">
+      <c r="E18" s="83" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4706,7 +4770,7 @@
           <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
         </is>
       </c>
-      <c r="E19" s="82" t="n">
+      <c r="E19" s="83" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4731,7 +4795,7 @@
           <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
         </is>
       </c>
-      <c r="E20" s="82" t="n">
+      <c r="E20" s="83" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4756,7 +4820,7 @@
           <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
         </is>
       </c>
-      <c r="E21" s="82" t="n">
+      <c r="E21" s="83" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -4781,7 +4845,7 @@
           <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
         </is>
       </c>
-      <c r="E22" s="82" t="n">
+      <c r="E22" s="83" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -4798,18 +4862,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="E25" s="60">
+      <c r="E25" s="61">
         <f>DCF!E33</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="71" t="inlineStr">
+      <c r="A26" s="72" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="70">
         <f>DCF!E47</f>
         <v/>
       </c>
@@ -4820,48 +4884,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E27" s="60">
+      <c r="E27" s="61">
         <f>E26-E25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="71" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="32" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="31" t="inlineStr">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="inlineStr">
+      <c r="A31" s="32" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="inlineStr">
+      <c r="A33" s="32" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4875,42 +4939,42 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="79" t="inlineStr">
+      <c r="A36" s="80" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="80" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D36" s="79" t="inlineStr">
+      <c r="D36" s="80" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E36" s="80" t="inlineStr">
+      <c r="E36" s="81" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F36" s="80" t="inlineStr">
+      <c r="F36" s="81" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G36" s="80" t="inlineStr">
+      <c r="G36" s="81" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H36" s="80" t="inlineStr">
+      <c r="H36" s="81" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -4928,7 +4992,7 @@
 Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
-      <c r="C37" s="83" t="inlineStr">
+      <c r="C37" s="84" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: LULU valuation</t>
@@ -4940,23 +5004,23 @@
 Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
-      <c r="E37" s="82" t="n">
+      <c r="E37" s="83" t="n">
         <v>6.5</v>
       </c>
-      <c r="F37" s="82" t="n">
+      <c r="F37" s="83" t="n">
         <v>9.5</v>
       </c>
-      <c r="G37" s="84">
+      <c r="G37" s="85">
         <f>(E6*E37+E8)/E9</f>
         <v/>
       </c>
-      <c r="H37" s="84">
+      <c r="H37" s="85">
         <f>(E6*F37+E8)/E9</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="71" t="inlineStr">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
@@ -4976,11 +5040,11 @@
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E38" s="85">
+      <c r="E38" s="86">
         <f>DCF!E47</f>
         <v/>
       </c>
-      <c r="G38" s="86">
+      <c r="G38" s="87">
         <f>(E6*E38+E8)/E9</f>
         <v/>
       </c>
@@ -4997,7 +5061,7 @@
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C39" s="83" t="inlineStr">
+      <c r="C39" s="84" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
@@ -5009,17 +5073,17 @@
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E39" s="82" t="n">
+      <c r="E39" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="82" t="n">
+      <c r="F39" s="83" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="84">
+      <c r="G39" s="85">
         <f>E7*E39</f>
         <v/>
       </c>
-      <c r="H39" s="84">
+      <c r="H39" s="85">
         <f>E7*F39</f>
         <v/>
       </c>
@@ -5030,32 +5094,32 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E40" s="87" t="inlineStr">
+      <c r="E40" s="88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="87" t="inlineStr">
+      <c r="F40" s="88" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="84">
+      <c r="G40" s="85">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H40" s="84">
+      <c r="H40" s="85">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="88" t="inlineStr">
+      <c r="A42" s="89" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="61" t="inlineStr">
+      <c r="C42" s="62" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -5065,12 +5129,12 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E42" s="89" t="n">
+      <c r="E42" s="90" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -356,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -395,6 +395,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1201,12 +1204,12 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>Observed Beta (5Y)</t>
+          <t>Observed Beta (5Y) — not used in WACC</t>
         </is>
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>StockAnalysis Beta (5Y) is 0.86. Raw 5-year equity beta; no funded debt so levered ≈ unlevered.</t>
+          <t>StockAnalysis Beta (5Y) is 0.86. Company 5Y print; too calm after the guide cut, so not the WACC input.</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
@@ -1216,7 +1219,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Beta (5Y)" → 0.86. This is the raw 5-year beta, not the 0.95 the model uses.</t>
+          <t>Ctrl+F "Beta (5Y)" → 0.86. Company 5Y beta. Not the WACC input.</t>
         </is>
       </c>
       <c r="E5" s="21" t="n">
@@ -1226,69 +1229,66 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Post-guide vol uplift</t>
+          <t>Damodaran Retail (Special Lines) βu</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>10% because that 5Y beta is too calm after the Sep-4 −17% print and FY26 guide cut.</t>
+          <t>Damodaran Jan-2026 Retail (Special Lines) unlevered beta is 0.95. No funded debt, so that is our levered beta.</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU Sep-4 print</t>
+          <t>Damodaran: US betas by sector (Jan 2026)</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "-17.38%" → Sep 4 close after Sep 3 earnings. Also Ctrl+F "52-Week Price Change" → -49.32%. +10% is the analyst overlay.</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>Levered beta = ROUND(5Y × (1+uplift), 2)</t>
+          <t>Ctrl+F "Retail (Special Lines)" → Unlevered beta 0.95 (column after Effective Tax rate). Do not take the levered Beta column (1.09). Date of Analysis is January 2026.</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" ht="112" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Levered beta (industry βu; no funded debt)</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>0.95 = ROUND(0.86 × 1.10, 2). 0.86 × 1.10 = 0.946, which rounds to 0.95. Formula, not a free 0.95.</t>
+          <t>0.95 is Damodaran’s industry unlevered beta, not 0.86 times a 10% overlay. Links to the industry row above.</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU Beta (5Y)</t>
+          <t>Damodaran: Retail (Special Lines) βu</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Observed 5Y beta (StockAnalysis)
+          <t>Company 5Y (StockAnalysis) — not the WACC input
   Ctrl+F "Beta (5Y)"  →  0.86
-Why not use 0.86 as-is
-  Ctrl+F "-17.38%"  →  Sep 4 close after Sep 3 earnings
-  Ctrl+F "52-Week Price Change"  →  -49.32%
-  5Y beta is too calm for a name that just printed a guide cut
-Model levered beta
-  0.86 × 1.10 = 0.946
-  0.95 = ROUND(0.86 × 1.10, 2)</t>
-        </is>
-      </c>
-      <c r="E7" s="23">
-        <f>ROUND(E5*(1+E6),2)</f>
+Industry bottom-up (Damodaran, Jan 2026) — this is the 0.95
+  Ctrl+F "Retail (Special Lines)"  →  Unlevered beta 0.95
+  Do not take the levered Beta column (1.09)
+  LULU has no funded debt, so unlevered = levered</t>
+        </is>
+      </c>
+      <c r="E7" s="24">
+        <f>E6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>E3+E7*E4</f>
         <v/>
       </c>
@@ -1356,7 +1356,7 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>E11*(1-E12)</f>
         <v/>
       </c>
@@ -1419,12 +1419,12 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="23" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f>E16*E8+E17*E13</f>
         <v/>
       </c>
@@ -1478,17 +1478,17 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="F2" s="27" t="inlineStr">
+      <c r="F2" s="28" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="G2" s="28" t="inlineStr">
+      <c r="G2" s="29" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="H2" s="29" t="inlineStr">
+      <c r="H2" s="30" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1630,13 +1630,13 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="31" t="n">
         <v>134500</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="31" t="n">
         <v>134500</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="31" t="n">
         <v>134500</v>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -1909,919 +1909,919 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+      <c r="A18" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="34">
         <f>11102600*(1+F4)</f>
         <v/>
       </c>
-      <c r="G18" s="33">
+      <c r="G18" s="34">
         <f>11102600*(1+G4)</f>
         <v/>
       </c>
-      <c r="H18" s="33">
+      <c r="H18" s="34">
         <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="34">
         <f>F18*(1+F5)</f>
         <v/>
       </c>
-      <c r="G19" s="33">
+      <c r="G19" s="34">
         <f>G18*(1+G5)</f>
         <v/>
       </c>
-      <c r="H19" s="33">
+      <c r="H19" s="34">
         <f>H18*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="34">
         <f>F19*(1+F5)</f>
         <v/>
       </c>
-      <c r="G20" s="33">
+      <c r="G20" s="34">
         <f>G19*(1+G5)</f>
         <v/>
       </c>
-      <c r="H20" s="33">
+      <c r="H20" s="34">
         <f>H19*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="34">
         <f>F20*(1+F5)</f>
         <v/>
       </c>
-      <c r="G21" s="33">
+      <c r="G21" s="34">
         <f>G20*(1+G5)</f>
         <v/>
       </c>
-      <c r="H21" s="33">
+      <c r="H21" s="34">
         <f>H20*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="A22" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="34">
         <f>F21*(1+F5)</f>
         <v/>
       </c>
-      <c r="G22" s="33">
+      <c r="G22" s="34">
         <f>G21*(1+G5)</f>
         <v/>
       </c>
-      <c r="H22" s="33">
+      <c r="H22" s="34">
         <f>H21*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="F23" s="34">
+      <c r="F23" s="35">
         <f>F6+(F8-F6)*0/4</f>
         <v/>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="35">
         <f>G6+(G8-G6)*0/4</f>
         <v/>
       </c>
-      <c r="H23" s="34">
+      <c r="H23" s="35">
         <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="35">
         <f>F6+(F8-F6)*1/4</f>
         <v/>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="35">
         <f>G6+(G8-G6)*1/4</f>
         <v/>
       </c>
-      <c r="H24" s="34">
+      <c r="H24" s="35">
         <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="inlineStr">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="35">
         <f>F6+(F8-F6)*2/4</f>
         <v/>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="35">
         <f>G6+(G8-G6)*2/4</f>
         <v/>
       </c>
-      <c r="H25" s="34">
+      <c r="H25" s="35">
         <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="inlineStr">
+      <c r="A26" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="F26" s="34">
+      <c r="F26" s="35">
         <f>F6+(F8-F6)*3/4</f>
         <v/>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="35">
         <f>G6+(G8-G6)*3/4</f>
         <v/>
       </c>
-      <c r="H26" s="34">
+      <c r="H26" s="35">
         <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="32" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="F27" s="34">
+      <c r="F27" s="35">
         <f>F6+(F8-F6)*4/4</f>
         <v/>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="35">
         <f>G6+(G8-G6)*4/4</f>
         <v/>
       </c>
-      <c r="H27" s="34">
+      <c r="H27" s="35">
         <f>H6+(H8-H6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <f>F18*F23+F7</f>
         <v/>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <f>G18*G23+G7</f>
         <v/>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <f>H18*H23+H7</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <f>F19*F24</f>
         <v/>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <f>G19*G24</f>
         <v/>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="34">
         <f>H19*H24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="34">
         <f>F20*F25</f>
         <v/>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <f>G20*G25</f>
         <v/>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <f>H20*H25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <f>F21*F26</f>
         <v/>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <f>G21*G26</f>
         <v/>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <f>H21*H26</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="34">
         <f>F22*F27</f>
         <v/>
       </c>
-      <c r="G32" s="33">
+      <c r="G32" s="34">
         <f>G22*G27</f>
         <v/>
       </c>
-      <c r="H32" s="33">
+      <c r="H32" s="34">
         <f>H22*H27</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="34">
         <f>F28*(1-F11)</f>
         <v/>
       </c>
-      <c r="G33" s="33">
+      <c r="G33" s="34">
         <f>G28*(1-G11)</f>
         <v/>
       </c>
-      <c r="H33" s="33">
+      <c r="H33" s="34">
         <f>H28*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="32" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="34">
         <f>F29*(1-F11)</f>
         <v/>
       </c>
-      <c r="G34" s="33">
+      <c r="G34" s="34">
         <f>G29*(1-G11)</f>
         <v/>
       </c>
-      <c r="H34" s="33">
+      <c r="H34" s="34">
         <f>H29*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="32" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="34">
         <f>F30*(1-F11)</f>
         <v/>
       </c>
-      <c r="G35" s="33">
+      <c r="G35" s="34">
         <f>G30*(1-G11)</f>
         <v/>
       </c>
-      <c r="H35" s="33">
+      <c r="H35" s="34">
         <f>H30*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="32" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="34">
         <f>F31*(1-F11)</f>
         <v/>
       </c>
-      <c r="G36" s="33">
+      <c r="G36" s="34">
         <f>G31*(1-G11)</f>
         <v/>
       </c>
-      <c r="H36" s="33">
+      <c r="H36" s="34">
         <f>H31*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="32" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="F37" s="33">
+      <c r="F37" s="34">
         <f>F32*(1-F11)</f>
         <v/>
       </c>
-      <c r="G37" s="33">
+      <c r="G37" s="34">
         <f>G32*(1-G11)</f>
         <v/>
       </c>
-      <c r="H37" s="33">
+      <c r="H37" s="34">
         <f>H32*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <f>F18*F12</f>
         <v/>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <f>G18*G12</f>
         <v/>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <f>H18*H12</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="32" t="inlineStr">
+      <c r="A39" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <f>F19*F12</f>
         <v/>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <f>G19*G12</f>
         <v/>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <f>H19*H12</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="32" t="inlineStr">
+      <c r="A40" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="F40" s="33">
+      <c r="F40" s="34">
         <f>F20*F12</f>
         <v/>
       </c>
-      <c r="G40" s="33">
+      <c r="G40" s="34">
         <f>G20*G12</f>
         <v/>
       </c>
-      <c r="H40" s="33">
+      <c r="H40" s="34">
         <f>H20*H12</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <f>F21*F12</f>
         <v/>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <f>G21*G12</f>
         <v/>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <f>H21*H12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="32" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <f>F22*F12</f>
         <v/>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <f>G22*G12</f>
         <v/>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <f>H22*H12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="32" t="inlineStr">
+      <c r="A43" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="F43" s="33">
+      <c r="F43" s="34">
         <f>F18*F13</f>
         <v/>
       </c>
-      <c r="G43" s="33">
+      <c r="G43" s="34">
         <f>G18*G13</f>
         <v/>
       </c>
-      <c r="H43" s="33">
+      <c r="H43" s="34">
         <f>H18*H13</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+      <c r="A44" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <f>F19*F13</f>
         <v/>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <f>G19*G13</f>
         <v/>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <f>H19*H13</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+      <c r="A45" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <f>F20*F13</f>
         <v/>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <f>G20*G13</f>
         <v/>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <f>H20*H13</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="32" t="inlineStr">
+      <c r="A46" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="F46" s="33">
+      <c r="F46" s="34">
         <f>F21*F13</f>
         <v/>
       </c>
-      <c r="G46" s="33">
+      <c r="G46" s="34">
         <f>G21*G13</f>
         <v/>
       </c>
-      <c r="H46" s="33">
+      <c r="H46" s="34">
         <f>H21*H13</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="32" t="inlineStr">
+      <c r="A47" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="34">
         <f>F22*F13</f>
         <v/>
       </c>
-      <c r="G47" s="33">
+      <c r="G47" s="34">
         <f>G22*G13</f>
         <v/>
       </c>
-      <c r="H47" s="33">
+      <c r="H47" s="34">
         <f>H22*H13</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="32" t="inlineStr">
+      <c r="A48" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 1</t>
         </is>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="34">
         <f>F18*F15</f>
         <v/>
       </c>
-      <c r="G48" s="33">
+      <c r="G48" s="34">
         <f>G18*G15</f>
         <v/>
       </c>
-      <c r="H48" s="33">
+      <c r="H48" s="34">
         <f>H18*H15</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 2</t>
         </is>
       </c>
-      <c r="F49" s="33">
+      <c r="F49" s="34">
         <f>F19*F15</f>
         <v/>
       </c>
-      <c r="G49" s="33">
+      <c r="G49" s="34">
         <f>G19*G15</f>
         <v/>
       </c>
-      <c r="H49" s="33">
+      <c r="H49" s="34">
         <f>H19*H15</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="32" t="inlineStr">
+      <c r="A50" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 3</t>
         </is>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="34">
         <f>F20*F15</f>
         <v/>
       </c>
-      <c r="G50" s="33">
+      <c r="G50" s="34">
         <f>G20*G15</f>
         <v/>
       </c>
-      <c r="H50" s="33">
+      <c r="H50" s="34">
         <f>H20*H15</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="32" t="inlineStr">
+      <c r="A51" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 4</t>
         </is>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="34">
         <f>F21*F15</f>
         <v/>
       </c>
-      <c r="G51" s="33">
+      <c r="G51" s="34">
         <f>G21*G15</f>
         <v/>
       </c>
-      <c r="H51" s="33">
+      <c r="H51" s="34">
         <f>H21*H15</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="32" t="inlineStr">
+      <c r="A52" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 5</t>
         </is>
       </c>
-      <c r="F52" s="33">
+      <c r="F52" s="34">
         <f>F22*F15</f>
         <v/>
       </c>
-      <c r="G52" s="33">
+      <c r="G52" s="34">
         <f>G22*G15</f>
         <v/>
       </c>
-      <c r="H52" s="33">
+      <c r="H52" s="34">
         <f>H22*H15</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="32" t="inlineStr">
+      <c r="A53" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 1</t>
         </is>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="34">
         <f>F14*(F18-11102600)</f>
         <v/>
       </c>
-      <c r="G53" s="33">
+      <c r="G53" s="34">
         <f>G14*(G18-11102600)</f>
         <v/>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <f>H14*(H18-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="32" t="inlineStr">
+      <c r="A54" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 2</t>
         </is>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <f>F14*(F19-F18)</f>
         <v/>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <f>G14*(G19-G18)</f>
         <v/>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <f>H14*(H19-H18)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="32" t="inlineStr">
+      <c r="A55" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 3</t>
         </is>
       </c>
-      <c r="F55" s="33">
+      <c r="F55" s="34">
         <f>F14*(F20-F19)</f>
         <v/>
       </c>
-      <c r="G55" s="33">
+      <c r="G55" s="34">
         <f>G14*(G20-G19)</f>
         <v/>
       </c>
-      <c r="H55" s="33">
+      <c r="H55" s="34">
         <f>H14*(H20-H19)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="32" t="inlineStr">
+      <c r="A56" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 4</t>
         </is>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="34">
         <f>F14*(F21-F20)</f>
         <v/>
       </c>
-      <c r="G56" s="33">
+      <c r="G56" s="34">
         <f>G14*(G21-G20)</f>
         <v/>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <f>H14*(H21-H20)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="32" t="inlineStr">
+      <c r="A57" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 5</t>
         </is>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <f>F14*(F22-F21)</f>
         <v/>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <f>G14*(G22-G21)</f>
         <v/>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <f>H14*(H22-H21)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="32" t="inlineStr">
+      <c r="A58" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="F58" s="33">
+      <c r="F58" s="34">
         <f>F33+F38-F43-F53</f>
         <v/>
       </c>
-      <c r="G58" s="33">
+      <c r="G58" s="34">
         <f>G33+G38-G43-G53</f>
         <v/>
       </c>
-      <c r="H58" s="33">
+      <c r="H58" s="34">
         <f>H33+H38-H43-H53</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="32" t="inlineStr">
+      <c r="A59" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="34">
         <f>F34+F39-F44-F54</f>
         <v/>
       </c>
-      <c r="G59" s="33">
+      <c r="G59" s="34">
         <f>G34+G39-G44-G54</f>
         <v/>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <f>H34+H39-H44-H54</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="32" t="inlineStr">
+      <c r="A60" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="34">
         <f>F35+F40-F45-F55</f>
         <v/>
       </c>
-      <c r="G60" s="33">
+      <c r="G60" s="34">
         <f>G35+G40-G45-G55</f>
         <v/>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <f>H35+H40-H45-H55</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="A61" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="F61" s="33">
+      <c r="F61" s="34">
         <f>F36+F41-F46-F56</f>
         <v/>
       </c>
-      <c r="G61" s="33">
+      <c r="G61" s="34">
         <f>G36+G41-G46-G56</f>
         <v/>
       </c>
-      <c r="H61" s="33">
+      <c r="H61" s="34">
         <f>H36+H41-H46-H56</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="32" t="inlineStr">
+      <c r="A62" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <f>F37+F42-F47-F57</f>
         <v/>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <f>G37+G42-G47-G57</f>
         <v/>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <f>H37+H42-H47-H57</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="22" t="inlineStr">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F64" s="35">
+      <c r="F64" s="36">
         <f>NPV(F9,F58,F59,F60,F61,F62)+(F62*(1+F10)/(F9-F10))/(1+F9)^5</f>
         <v/>
       </c>
-      <c r="G64" s="35">
+      <c r="G64" s="36">
         <f>NPV(G9,G58,G59,G60,G61,G62)+(G62*(1+G10)/(G9-G10))/(1+G9)^5</f>
         <v/>
       </c>
-      <c r="H64" s="35">
+      <c r="H64" s="36">
         <f>NPV(H9,H58,H59,H60,H61,H62)+(H62*(1+H10)/(H9-H10))/(1+H9)^5</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="36" t="inlineStr">
+      <c r="A65" s="37" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F65" s="37">
+      <c r="F65" s="38">
         <f>(F64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="G65" s="38">
+      <c r="G65" s="39">
         <f>(G64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="H65" s="37">
+      <c r="H65" s="38">
         <f>(H64+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="22" t="inlineStr">
+      <c r="A66" s="23" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F66" s="39">
+      <c r="F66" s="40">
         <f>F65/100.0-1</f>
         <v/>
       </c>
-      <c r="G66" s="39">
+      <c r="G66" s="40">
         <f>G65/100.0-1</f>
         <v/>
       </c>
-      <c r="H66" s="39">
+      <c r="H66" s="40">
         <f>H65/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="40" t="inlineStr">
+      <c r="A68" s="41" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2887,69 +2887,69 @@
       <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="42" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="C2" s="41" t="inlineStr">
+      <c r="C2" s="42" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D2" s="41" t="inlineStr">
+      <c r="D2" s="42" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E2" s="42" t="inlineStr">
+      <c r="E2" s="43" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F2" s="43" t="inlineStr">
+      <c r="F2" s="44" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G2" s="43" t="inlineStr">
+      <c r="G2" s="44" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H2" s="43" t="inlineStr">
+      <c r="H2" s="44" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I2" s="43" t="inlineStr">
+      <c r="I2" s="44" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J2" s="43" t="inlineStr">
+      <c r="J2" s="44" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="K2" s="44" t="inlineStr">
+      <c r="K2" s="45" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="L2" s="41" t="inlineStr">
+      <c r="L2" s="42" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="M2" s="41" t="inlineStr">
+      <c r="M2" s="42" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="45" t="inlineStr">
+      <c r="A3" s="46" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
         </is>
@@ -2959,12 +2959,12 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
-      <c r="E3" s="46" t="inlineStr">
+      <c r="E3" s="47" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="K3" s="47" t="inlineStr">
+      <c r="K3" s="48" t="inlineStr">
         <is>
           <t>(should be 0)</t>
         </is>
@@ -2976,30 +2976,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="E5" s="48" t="n">
+      <c r="E5" s="49" t="n">
         <v>11102600</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="50">
         <f>Scenarios!G18</f>
         <v/>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="50">
         <f>Scenarios!G19</f>
         <v/>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="50">
         <f>Scenarios!G20</f>
         <v/>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="50">
         <f>Scenarios!G21</f>
         <v/>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="50">
         <f>Scenarios!G22</f>
         <v/>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="51">
         <f>IF(MAX(ABS(F5-Scenarios!$G$18),ABS(G5-Scenarios!$G$19),ABS(H5-Scenarios!$G$20),ABS(I5-Scenarios!$G$21),ABS(J5-Scenarios!$G$22))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3016,7 +3016,7 @@
 Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
-      <c r="C6" s="31" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
 Also: StockAnalysis: LULU 3Y revenue forecast</t>
@@ -3028,23 +3028,23 @@
 Also: Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
-      <c r="F6" s="51">
+      <c r="F6" s="52">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="52">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="52">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="51">
+      <c r="I6" s="52">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="51">
+      <c r="J6" s="52">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -3061,7 +3061,7 @@
 Also: FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="32" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
 Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
@@ -3073,27 +3073,27 @@
 Also: Ctrl+F "19.9%" (one hit) → Operating margin decreased 380 basis points to 19.9%. That is FY25 OM. Do not search the words Income from operations (17 hits). Model FY30 15.5% is a partial-recovery assumption.</t>
         </is>
       </c>
-      <c r="F7" s="51">
+      <c r="F7" s="52">
         <f>Scenarios!G23</f>
         <v/>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="52">
         <f>Scenarios!G24</f>
         <v/>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="52">
         <f>Scenarios!G25</f>
         <v/>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="52">
         <f>Scenarios!G26</f>
         <v/>
       </c>
-      <c r="J7" s="51">
+      <c r="J7" s="52">
         <f>Scenarios!G27</f>
         <v/>
       </c>
-      <c r="K7" s="50">
+      <c r="K7" s="51">
         <f>IF(MAX(ABS(F7-Scenarios!$G$23),ABS(G7-Scenarios!$G$24),ABS(H7-Scenarios!$G$25),ABS(I7-Scenarios!$G$26),ABS(J7-Scenarios!$G$27))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3119,56 +3119,56 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>Scenarios!$G$7</f>
         <v/>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>EBIT (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="53" t="n">
         <v>2210615</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>Scenarios!G28</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="36">
         <f>Scenarios!G29</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="36">
         <f>Scenarios!G30</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="36">
         <f>Scenarios!G31</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="36">
         <f>Scenarios!G32</f>
         <v/>
       </c>
-      <c r="K9" s="53">
+      <c r="K9" s="54">
         <f>IF(MAX(ABS(F9-Scenarios!$G$28),ABS(G9-Scenarios!$G$29),ABS(H9-Scenarios!$G$30),ABS(I9-Scenarios!$G$31),ABS(J9-Scenarios!$G$32))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3179,26 +3179,26 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E10" s="54" t="n">
+      <c r="E10" s="55" t="n">
         <v>0.1991078666258354</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="52">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="52">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H10" s="51">
+      <c r="H10" s="52">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="52">
         <f>I9/I5</f>
         <v/>
       </c>
-      <c r="J10" s="51">
+      <c r="J10" s="52">
         <f>J9/J5</f>
         <v/>
       </c>
@@ -3209,54 +3209,54 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="F11" s="49">
+      <c r="F11" s="50">
         <f>-Scenarios!G28*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="50">
         <f>-Scenarios!G29*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="50">
         <f>-Scenarios!G30*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="I11" s="49">
+      <c r="I11" s="50">
         <f>-Scenarios!G31*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="J11" s="49">
+      <c r="J11" s="50">
         <f>-Scenarios!G32*Scenarios!$G$11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="22" t="inlineStr">
+      <c r="A12" s="23" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>Scenarios!G33</f>
         <v/>
       </c>
-      <c r="G12" s="35">
+      <c r="G12" s="36">
         <f>Scenarios!G34</f>
         <v/>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="36">
         <f>Scenarios!G35</f>
         <v/>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="36">
         <f>Scenarios!G36</f>
         <v/>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="36">
         <f>Scenarios!G37</f>
         <v/>
       </c>
-      <c r="K12" s="53">
+      <c r="K12" s="54">
         <f>IF(MAX(ABS(F12-Scenarios!$G$33),ABS(G12-Scenarios!$G$34),ABS(H12-Scenarios!$G$35),ABS(I12-Scenarios!$G$36),ABS(J12-Scenarios!$G$37))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3309,27 +3309,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="F14" s="49">
+      <c r="F14" s="50">
         <f>Scenarios!G38</f>
         <v/>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="50">
         <f>Scenarios!G39</f>
         <v/>
       </c>
-      <c r="H14" s="49">
+      <c r="H14" s="50">
         <f>Scenarios!G40</f>
         <v/>
       </c>
-      <c r="I14" s="49">
+      <c r="I14" s="50">
         <f>Scenarios!G41</f>
         <v/>
       </c>
-      <c r="J14" s="49">
+      <c r="J14" s="50">
         <f>Scenarios!G42</f>
         <v/>
       </c>
-      <c r="K14" s="50">
+      <c r="K14" s="51">
         <f>IF(MAX(ABS(F14-Scenarios!$G$38),ABS(G14-Scenarios!$G$39),ABS(H14-Scenarios!$G$40),ABS(I14-Scenarios!$G$41),ABS(J14-Scenarios!$G$42))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3346,7 +3346,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C15" s="31" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -3395,27 +3395,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="F16" s="49">
+      <c r="F16" s="50">
         <f>-Scenarios!G43</f>
         <v/>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="50">
         <f>-Scenarios!G44</f>
         <v/>
       </c>
-      <c r="H16" s="49">
+      <c r="H16" s="50">
         <f>-Scenarios!G45</f>
         <v/>
       </c>
-      <c r="I16" s="49">
+      <c r="I16" s="50">
         <f>-Scenarios!G46</f>
         <v/>
       </c>
-      <c r="J16" s="49">
+      <c r="J16" s="50">
         <f>-Scenarios!G47</f>
         <v/>
       </c>
-      <c r="K16" s="50">
+      <c r="K16" s="51">
         <f>IF(MAX(ABS(F16+Scenarios!$G$43),ABS(G16+Scenarios!$G$44),ABS(H16+Scenarios!$G$45),ABS(I16+Scenarios!$G$46),ABS(J16+Scenarios!$G$47))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3525,30 +3525,30 @@
           <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
         </is>
       </c>
-      <c r="E19" s="48" t="n">
+      <c r="E19" s="49" t="n">
         <v>190657</v>
       </c>
-      <c r="F19" s="49">
+      <c r="F19" s="50">
         <f>Scenarios!G48</f>
         <v/>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="50">
         <f>Scenarios!G49</f>
         <v/>
       </c>
-      <c r="H19" s="49">
+      <c r="H19" s="50">
         <f>Scenarios!G50</f>
         <v/>
       </c>
-      <c r="I19" s="49">
+      <c r="I19" s="50">
         <f>Scenarios!G51</f>
         <v/>
       </c>
-      <c r="J19" s="49">
+      <c r="J19" s="50">
         <f>Scenarios!G52</f>
         <v/>
       </c>
-      <c r="K19" s="50">
+      <c r="K19" s="51">
         <f>IF(MAX(ABS(F19-Scenarios!$G$48),ABS(G19-Scenarios!$G$49),ABS(H19-Scenarios!$G$50),ABS(I19-Scenarios!$G$51),ABS(J19-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3559,65 +3559,65 @@
           <t>(Increase)/decrease in NWC (includes AR)</t>
         </is>
       </c>
-      <c r="F20" s="49">
+      <c r="F20" s="50">
         <f>-Scenarios!G53</f>
         <v/>
       </c>
-      <c r="G20" s="49">
+      <c r="G20" s="50">
         <f>-Scenarios!G54</f>
         <v/>
       </c>
-      <c r="H20" s="49">
+      <c r="H20" s="50">
         <f>-Scenarios!G55</f>
         <v/>
       </c>
-      <c r="I20" s="49">
+      <c r="I20" s="50">
         <f>-Scenarios!G56</f>
         <v/>
       </c>
-      <c r="J20" s="49">
+      <c r="J20" s="50">
         <f>-Scenarios!G57</f>
         <v/>
       </c>
-      <c r="K20" s="50">
+      <c r="K20" s="51">
         <f>IF(MAX(ABS(F20+Scenarios!$G$53),ABS(G20+Scenarios!$G$54),ABS(H20+Scenarios!$G$55),ABS(I20+Scenarios!$G$56),ABS(J20+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="40" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: NWC and AR are one line. 7.5% of Δsales already includes AR; UFCF does not take ΔAR separately.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F22" s="55">
+      <c r="F22" s="56">
         <f>Scenarios!G58</f>
         <v/>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="56">
         <f>Scenarios!G59</f>
         <v/>
       </c>
-      <c r="H22" s="55">
+      <c r="H22" s="56">
         <f>Scenarios!G60</f>
         <v/>
       </c>
-      <c r="I22" s="55">
+      <c r="I22" s="56">
         <f>Scenarios!G61</f>
         <v/>
       </c>
-      <c r="J22" s="55">
+      <c r="J22" s="56">
         <f>Scenarios!G62</f>
         <v/>
       </c>
-      <c r="K22" s="53">
+      <c r="K22" s="54">
         <f>IF(MAX(ABS(F22-Scenarios!$G$58),ABS(G22-Scenarios!$G$59),ABS(H22-Scenarios!$G$60),ABS(I22-Scenarios!$G$61),ABS(J22-Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3628,19 +3628,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="F23" s="56" t="n">
+      <c r="F23" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="56" t="n">
+      <c r="G23" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="56" t="n">
+      <c r="H23" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="56" t="n">
+      <c r="I23" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="56" t="n">
+      <c r="J23" s="57" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3650,50 +3650,50 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="F24" s="57">
+      <c r="F24" s="58">
         <f>1/(1+Scenarios!$G$9)^F23</f>
         <v/>
       </c>
-      <c r="G24" s="57">
+      <c r="G24" s="58">
         <f>1/(1+Scenarios!$G$9)^G23</f>
         <v/>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="58">
         <f>1/(1+Scenarios!$G$9)^H23</f>
         <v/>
       </c>
-      <c r="I24" s="57">
+      <c r="I24" s="58">
         <f>1/(1+Scenarios!$G$9)^I23</f>
         <v/>
       </c>
-      <c r="J24" s="57">
+      <c r="J24" s="58">
         <f>1/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="36">
         <f>F22*F24</f>
         <v/>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <f>G22*G24</f>
         <v/>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="36">
         <f>H22*H24</f>
         <v/>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="36">
         <f>I22*I24</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="36">
         <f>J22*J24</f>
         <v/>
       </c>
@@ -3704,13 +3704,13 @@
           <t>Scenarios linkage summary (column K should all read OK)</t>
         </is>
       </c>
-      <c r="K27" s="58">
+      <c r="K27" s="59">
         <f>IF(COUNTIF(K5:K22,"CHECK")=0,"ALL OK","REVIEW")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="59" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>VALUATION — GORDON GROWTH (PERPETUITY) METHOD</t>
         </is>
@@ -3719,12 +3719,12 @@
       <c r="C28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="22" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
       </c>
-      <c r="E29" s="60">
+      <c r="E29" s="61">
         <f>SUM(F25:J25)</f>
         <v/>
       </c>
@@ -3750,18 +3750,18 @@
           <t>Ctrl+F "Q2 2026" → 24,269.613 and "Q2 2025" → 23,770.976. YoY = 2.1%. Model terminal g 2.25%.</t>
         </is>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="52">
         <f>Scenarios!$G$10</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="22" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <f>J9+J14</f>
         <v/>
       </c>
@@ -3772,7 +3772,7 @@
           <t>Terminal value = FCF₅×(1+g)/(WACC−g)</t>
         </is>
       </c>
-      <c r="E32" s="49">
+      <c r="E32" s="50">
         <f>J22*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
         <v/>
       </c>
@@ -3783,29 +3783,29 @@
           <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
         </is>
       </c>
-      <c r="E33" s="61">
+      <c r="E33" s="62">
         <f>E32/E31</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E34" s="60">
+      <c r="E34" s="61">
         <f>E32/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <f>E29+E34</f>
         <v/>
       </c>
@@ -3816,7 +3816,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C36" s="62" t="inlineStr">
+      <c r="C36" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3826,7 +3826,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E36" s="48" t="n">
+      <c r="E36" s="49" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C37" s="62" t="inlineStr">
+      <c r="C37" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3846,17 +3846,17 @@
           <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
         </is>
       </c>
-      <c r="E37" s="48" t="n">
+      <c r="E37" s="49" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="36">
         <f>E35+E36+E37</f>
         <v/>
       </c>
@@ -3867,7 +3867,7 @@
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C39" s="62" t="inlineStr">
+      <c r="C39" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -3877,21 +3877,21 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E39" s="48" t="n">
+      <c r="E39" s="49" t="n">
         <v>111380</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="22" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="E40" s="63">
+      <c r="E40" s="64">
         <f>E38/E39</f>
         <v/>
       </c>
-      <c r="K40" s="53">
+      <c r="K40" s="54">
         <f>IF(ABS(E40-Scenarios!$G$65)&lt;0.05,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3902,7 +3902,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C41" s="62" t="inlineStr">
+      <c r="C41" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -3912,17 +3912,17 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E41" s="64" t="n">
+      <c r="E41" s="65" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="22" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="E42" s="65">
+      <c r="E42" s="66">
         <f>E40/E41-1</f>
         <v/>
       </c>
@@ -3933,13 +3933,13 @@
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="E43" s="51">
+      <c r="E43" s="52">
         <f>E34/E35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="59" t="inlineStr">
+      <c r="A45" s="60" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
@@ -3975,10 +3975,10 @@
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E47" s="66" t="n">
+      <c r="E47" s="67" t="n">
         <v>8</v>
       </c>
-      <c r="M47" s="62" t="inlineStr">
+      <c r="M47" s="63" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
@@ -3990,7 +3990,7 @@
           <t>Terminal value = Terminal EBITDA × exit multiple</t>
         </is>
       </c>
-      <c r="E48" s="49">
+      <c r="E48" s="50">
         <f>E31*E47</f>
         <v/>
       </c>
@@ -4001,35 +4001,35 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E49" s="49">
+      <c r="E49" s="50">
         <f>E48/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="22" t="inlineStr">
+      <c r="A50" s="23" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="36">
         <f>E29+E49</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="22" t="inlineStr">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="E51" s="67">
+      <c r="E51" s="68">
         <f>(E50+E36+E37)/E39</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="59" t="inlineStr">
+      <c r="A53" s="60" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
@@ -4039,57 +4039,57 @@
       <c r="D53" s="13" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="inlineStr"/>
-      <c r="B54" s="69" t="inlineStr">
+      <c r="A54" s="69" t="inlineStr"/>
+      <c r="B54" s="70" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C54" s="69" t="inlineStr">
+      <c r="C54" s="70" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D54" s="69" t="inlineStr">
+      <c r="D54" s="70" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="22" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B55" s="60">
+      <c r="B55" s="61">
         <f>E32</f>
         <v/>
       </c>
-      <c r="C55" s="60">
+      <c r="C55" s="61">
         <f>E48</f>
         <v/>
       </c>
-      <c r="D55" s="60">
+      <c r="D55" s="61">
         <f>B55-C55</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="22" t="inlineStr">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B56" s="70">
+      <c r="B56" s="71">
         <f>E33</f>
         <v/>
       </c>
-      <c r="C56" s="70">
+      <c r="C56" s="71">
         <f>E47</f>
         <v/>
       </c>
-      <c r="D56" s="70">
+      <c r="D56" s="71">
         <f>B56-C56</f>
         <v/>
       </c>
@@ -4100,54 +4100,54 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B57" s="51" t="inlineStr"/>
-      <c r="C57" s="51" t="inlineStr"/>
-      <c r="D57" s="51">
+      <c r="B57" s="52" t="inlineStr"/>
+      <c r="C57" s="52" t="inlineStr"/>
+      <c r="D57" s="52">
         <f>(B55-C55)/B55</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="22" t="inlineStr">
+      <c r="A58" s="23" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B58" s="71">
+      <c r="B58" s="72">
         <f>E40</f>
         <v/>
       </c>
-      <c r="C58" s="71">
+      <c r="C58" s="72">
         <f>E51</f>
         <v/>
       </c>
-      <c r="D58" s="71">
+      <c r="D58" s="72">
         <f>B58-C58</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="72" t="inlineStr">
+      <c r="A59" s="73" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B59" s="73">
+      <c r="B59" s="74">
         <f>IF(ABS(D56)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C59" s="74">
+      <c r="C59" s="75">
         <f>TEXT(D56,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D59" s="40" t="inlineStr">
+      <c r="D59" s="41" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="59" t="inlineStr">
+      <c r="A62" s="60" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
@@ -4161,7 +4161,7 @@
       <c r="H62" s="13" t="n"/>
     </row>
     <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="75" t="inlineStr">
+      <c r="A63" s="76" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
@@ -4181,32 +4181,32 @@
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
-      <c r="F63" s="76" t="n">
+      <c r="F63" s="77" t="n">
         <v>0.015</v>
       </c>
-      <c r="G63" s="76" t="n">
+      <c r="G63" s="77" t="n">
         <v>0.02</v>
       </c>
-      <c r="H63" s="76" t="n">
+      <c r="H63" s="77" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I63" s="76" t="n">
+      <c r="I63" s="77" t="n">
         <v>0.025</v>
       </c>
-      <c r="J63" s="76" t="n">
+      <c r="J63" s="77" t="n">
         <v>0.03</v>
       </c>
-      <c r="L63" s="62" t="inlineStr">
+      <c r="L63" s="63" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
       </c>
     </row>
     <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="76" t="n">
+      <c r="A64" s="77" t="n">
         <v>0.095</v>
       </c>
-      <c r="C64" s="62" t="inlineStr">
+      <c r="C64" s="63" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -4216,34 +4216,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F64" s="77">
+      <c r="F64" s="78">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G64" s="77">
+      <c r="G64" s="78">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H64" s="77">
+      <c r="H64" s="78">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I64" s="77">
+      <c r="I64" s="78">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J64" s="77">
+      <c r="J64" s="78">
         <f>(NPV(0.095,F22:J22)+(J22*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L64" s="62" t="inlineStr">
+      <c r="L64" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="76" t="n">
+      <c r="A65" s="77" t="n">
         <v>0.1</v>
       </c>
       <c r="D65" s="19" t="inlineStr">
@@ -4251,34 +4251,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F65" s="77">
+      <c r="F65" s="78">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G65" s="77">
+      <c r="G65" s="78">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H65" s="77">
+      <c r="H65" s="78">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I65" s="77">
+      <c r="I65" s="78">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J65" s="77">
+      <c r="J65" s="78">
         <f>(NPV(0.1,F22:J22)+(J22*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L65" s="62" t="inlineStr">
+      <c r="L65" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="76" t="n">
+      <c r="A66" s="77" t="n">
         <v>0.105</v>
       </c>
       <c r="D66" s="19" t="inlineStr">
@@ -4286,34 +4286,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F66" s="77">
+      <c r="F66" s="78">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G66" s="77">
+      <c r="G66" s="78">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H66" s="78">
+      <c r="H66" s="79">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I66" s="77">
+      <c r="I66" s="78">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J66" s="77">
+      <c r="J66" s="78">
         <f>(NPV(0.105,F22:J22)+(J22*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L66" s="62" t="inlineStr">
+      <c r="L66" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="76" t="n">
+      <c r="A67" s="77" t="n">
         <v>0.11</v>
       </c>
       <c r="D67" s="19" t="inlineStr">
@@ -4321,34 +4321,34 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F67" s="77">
+      <c r="F67" s="78">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G67" s="77">
+      <c r="G67" s="78">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H67" s="77">
+      <c r="H67" s="78">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I67" s="77">
+      <c r="I67" s="78">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J67" s="77">
+      <c r="J67" s="78">
         <f>(NPV(0.11,F22:J22)+(J22*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L67" s="62" t="inlineStr">
+      <c r="L67" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
     <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="76" t="n">
+      <c r="A68" s="77" t="n">
         <v>0.115</v>
       </c>
       <c r="D68" s="19" t="inlineStr">
@@ -4356,27 +4356,27 @@
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F68" s="77">
+      <c r="F68" s="78">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="G68" s="77">
+      <c r="G68" s="78">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="H68" s="77">
+      <c r="H68" s="78">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="I68" s="77">
+      <c r="I68" s="78">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="J68" s="77">
+      <c r="J68" s="78">
         <f>(NPV(0.115,F22:J22)+(J22*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E36+E37)/E39</f>
         <v/>
       </c>
-      <c r="L68" s="62" t="inlineStr">
+      <c r="L68" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
@@ -4398,7 +4398,7 @@
           <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
-      <c r="L69" s="62" t="inlineStr">
+      <c r="L69" s="63" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -4514,7 +4514,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4524,7 +4524,7 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 ($000) in FY2025 column</t>
         </is>
       </c>
-      <c r="E4" s="48" t="n">
+      <c r="E4" s="49" t="n">
         <v>11102600</v>
       </c>
     </row>
@@ -4534,7 +4534,7 @@
           <t>FY2025A EBITDA (EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E5" s="49">
+      <c r="E5" s="50">
         <f>2210615+496228</f>
         <v/>
       </c>
@@ -4545,12 +4545,12 @@
           <t>FY2030E terminal EBITDA (DCF EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="63" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="50">
         <f>DCF!E31</f>
         <v/>
       </c>
@@ -4561,7 +4561,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="63" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -4571,7 +4571,7 @@
           <t>Ctrl+F "$9.48 to $9.73" → FY2026 diluted EPS guidance; model midpoint $9.61</t>
         </is>
       </c>
-      <c r="E7" s="64" t="n">
+      <c r="E7" s="65" t="n">
         <v>9.609999999999999</v>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4591,7 +4591,7 @@
           <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
         </is>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="49" t="n">
         <v>1807202</v>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
           <t>Diluted shares (000)</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -4611,7 +4611,7 @@
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E9" s="48" t="n">
+      <c r="E9" s="49" t="n">
         <v>111380</v>
       </c>
     </row>
@@ -4621,7 +4621,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="62" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -4631,28 +4631,28 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E10" s="64" t="n">
+      <c r="E10" s="65" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="E11" s="79">
+      <c r="E11" s="80">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="74" t="inlineStr">
+      <c r="A12" s="75" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="E12" s="79">
+      <c r="E12" s="80">
         <f>E10/E7</f>
         <v/>
       </c>
@@ -4665,34 +4665,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="74" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="80" t="inlineStr">
+      <c r="A16" s="81" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B16" s="81" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C16" s="80" t="inlineStr">
+      <c r="C16" s="81" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D16" s="80" t="inlineStr">
+      <c r="D16" s="81" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E16" s="81" t="inlineStr">
+      <c r="E16" s="82" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
@@ -4704,12 +4704,12 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="B17" s="40" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="63" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K</t>
         </is>
@@ -4719,7 +4719,7 @@
           <t>Ctrl+F "19.9%" → FY25 OM (EBIT $2,210,615). Ctrl+F "496,228" → Depreciation and amortization. Do not search the words Income from operations (17 hits).</t>
         </is>
       </c>
-      <c r="E17" s="82">
+      <c r="E17" s="83">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
@@ -4745,7 +4745,7 @@
           <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
         </is>
       </c>
-      <c r="E18" s="83" t="n">
+      <c r="E18" s="84" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
           <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
         </is>
       </c>
-      <c r="E19" s="83" t="n">
+      <c r="E19" s="84" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
           <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
         </is>
       </c>
-      <c r="E20" s="83" t="n">
+      <c r="E20" s="84" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
           <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
         </is>
       </c>
-      <c r="E21" s="83" t="n">
+      <c r="E21" s="84" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
           <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
         </is>
       </c>
-      <c r="E22" s="83" t="n">
+      <c r="E22" s="84" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -4862,18 +4862,18 @@
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="62">
         <f>DCF!E33</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="72" t="inlineStr">
+      <c r="A26" s="73" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="E26" s="70">
+      <c r="E26" s="71">
         <f>DCF!E47</f>
         <v/>
       </c>
@@ -4884,48 +4884,48 @@
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E27" s="61">
+      <c r="E27" s="62">
         <f>E26-E25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72" t="inlineStr">
+      <c r="A28" s="73" t="inlineStr">
         <is>
           <t>Rationale for 8.0x</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="32" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="32" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="32" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -4939,42 +4939,42 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="80" t="inlineStr">
+      <c r="A36" s="81" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B36" s="80" t="inlineStr">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C36" s="80" t="inlineStr">
+      <c r="C36" s="81" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D36" s="80" t="inlineStr">
+      <c r="D36" s="81" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E36" s="81" t="inlineStr">
+      <c r="E36" s="82" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F36" s="81" t="inlineStr">
+      <c r="F36" s="82" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G36" s="81" t="inlineStr">
+      <c r="G36" s="82" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H36" s="81" t="inlineStr">
+      <c r="H36" s="82" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -4992,7 +4992,7 @@
 Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
         </is>
       </c>
-      <c r="C37" s="84" t="inlineStr">
+      <c r="C37" s="85" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: LULU valuation</t>
@@ -5004,23 +5004,23 @@
 Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
-      <c r="E37" s="83" t="n">
+      <c r="E37" s="84" t="n">
         <v>6.5</v>
       </c>
-      <c r="F37" s="83" t="n">
+      <c r="F37" s="84" t="n">
         <v>9.5</v>
       </c>
-      <c r="G37" s="85">
+      <c r="G37" s="86">
         <f>(E6*E37+E8)/E9</f>
         <v/>
       </c>
-      <c r="H37" s="85">
+      <c r="H37" s="86">
         <f>(E6*F37+E8)/E9</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="72" t="inlineStr">
+      <c r="A38" s="73" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
@@ -5040,11 +5040,11 @@
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
         </is>
       </c>
-      <c r="E38" s="86">
+      <c r="E38" s="87">
         <f>DCF!E47</f>
         <v/>
       </c>
-      <c r="G38" s="87">
+      <c r="G38" s="88">
         <f>(E6*E38+E8)/E9</f>
         <v/>
       </c>
@@ -5061,7 +5061,7 @@
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C39" s="84" t="inlineStr">
+      <c r="C39" s="85" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
@@ -5073,17 +5073,17 @@
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E39" s="83" t="n">
+      <c r="E39" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="83" t="n">
+      <c r="F39" s="84" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="85">
+      <c r="G39" s="86">
         <f>E7*E39</f>
         <v/>
       </c>
-      <c r="H39" s="85">
+      <c r="H39" s="86">
         <f>E7*F39</f>
         <v/>
       </c>
@@ -5094,32 +5094,32 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E40" s="88" t="inlineStr">
+      <c r="E40" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="88" t="inlineStr">
+      <c r="F40" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="85">
+      <c r="G40" s="86">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H40" s="85">
+      <c r="H40" s="86">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="89" t="inlineStr">
+      <c r="A42" s="90" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="62" t="inlineStr">
+      <c r="C42" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -5129,12 +5129,12 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E42" s="90" t="n">
+      <c r="E42" s="91" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40" t="inlineStr">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -397,6 +397,9 @@
     <xf numFmtId="2" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -406,6 +409,9 @@
     <xf numFmtId="2" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -427,9 +433,6 @@
     <xf numFmtId="165" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -453,9 +456,6 @@
     </xf>
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1108,7 +1108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1226,40 +1226,43 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="42" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Damodaran Retail (Special Lines) βu</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>Damodaran Jan-2026 Retail (Special Lines) unlevered beta is 0.95. No funded debt, so that is our levered beta.</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>Damodaran: US betas by sector (Jan 2026)</t>
+          <t>Unlevered retail beta (Damodaran Special Lines)</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>We use Damodaran’s unlevered Retail (Special Lines) beta of 0.95 because LULU has no debt.
+No debt: 0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Damodaran: US betas by sector (Jan 2026)
+No debt: LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "Retail (Special Lines)" → Unlevered beta 0.95 (column after Effective Tax rate). Do not take the levered Beta column (1.09). Date of Analysis is January 2026.</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="n">
+          <t>Ctrl+F "Retail (Special Lines)" → Unlevered beta 0.95 (not the levered Beta 1.09). We take unlevered because LULU has no debt.
+No debt: Ctrl+F "no borrowings were outstanding under this facility" → debt weight 0%</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="n">
         <v>0.95</v>
       </c>
     </row>
-    <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>Levered beta (industry βu; no funded debt)</t>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Beta used = unlevered retail β — LULU has no debt</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>0.95 is Damodaran’s industry unlevered beta, not 0.86 times a 10% overlay. Links to the industry row above.</t>
+          <t>Beta used is that unlevered retail β. No funded debt → βu = βe. Do not use the levered industry 1.09.</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
@@ -1269,163 +1272,172 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Company 5Y (StockAnalysis) — not the WACC input
-  Ctrl+F "Beta (5Y)"  →  0.86
-Industry bottom-up (Damodaran, Jan 2026) — this is the 0.95
+          <t>We use the unlevered retail beta because LULU has no debt (βu = βe).
+Damodaran Jan 2026 — this is the 0.95
   Ctrl+F "Retail (Special Lines)"  →  Unlevered beta 0.95
   Do not take the levered Beta column (1.09)
-  LULU has no funded debt, so unlevered = levered</t>
-        </is>
-      </c>
-      <c r="E7" s="24">
+Why unlevered, not levered 1.09
+  Ctrl+F "no borrowings were outstanding under this facility" on the FY25 10-K
+Company 5Y (StockAnalysis) — shown, not used
+  Ctrl+F "Beta (5Y)"  →  0.86</t>
+        </is>
+      </c>
+      <c r="E7" s="25">
         <f>E6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: we use the unlevered retail beta because LULU has no debt (βu = βe). Not the levered industry 1.09.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Cost of equity = rf + β × ERP</t>
         </is>
       </c>
-      <c r="E8" s="25">
+      <c r="E9" s="27">
         <f>E3+E7*E4</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Cost of debt</t>
         </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Pre-tax cost of debt</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>5.0% illustrative pre-tax debt cost; 10-K: no borrowings outstanding on the revolver.</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K (no funded debt)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "no borrowings were outstanding under this facility" on this 10-K HTML page (search the document, do not use the EDGAR viewer TOC).</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.05</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
+          <t>Pre-tax cost of debt</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>5.0% illustrative pre-tax debt cost; 10-K: no borrowings outstanding on the revolver.</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K (no funded debt)</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "no borrowings were outstanding under this facility" on this 10-K HTML page (search the document, do not use the EDGAR viewer TOC).</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>30% cash tax matches FY2026 guidance (“approximately 30%”); FY25 effective was 29.5%.</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "a tax rate of approximately 30%" on the FY2026 outlook paragraph.</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E13" s="20" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="E13" s="26">
-        <f>E11*(1-E12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="E14" s="28">
+        <f>E12*(1-E13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Capital structure (market values)</t>
         </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Equity weight</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K balance sheet</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) | no funded term debt</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
+          <t>Equity weight</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>100% equity weight; net-cash balance sheet with no material funded debt at market values per FY2025 10-K.</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K balance sheet</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) | no funded term debt</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>0% debt weight; no outstanding term loans or bonds, so WACC effectively equals levered cost of equity here.</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K balance sheet</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "no borrowings were outstanding under this facility" → debt weight 0%</t>
         </is>
       </c>
-      <c r="E17" s="20" t="n">
+      <c r="E18" s="20" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="E18" s="27">
-        <f>E16*E8+E17*E13</f>
+      <c r="E19" s="29">
+        <f>E17*E9+E18*E14</f>
         <v/>
       </c>
     </row>
@@ -1436,10 +1448,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1478,17 +1490,17 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="F2" s="28" t="inlineStr">
+      <c r="F2" s="30" t="inlineStr">
         <is>
           <t>Bear</t>
         </is>
       </c>
-      <c r="G2" s="29" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="H2" s="30" t="inlineStr">
+      <c r="H2" s="32" t="inlineStr">
         <is>
           <t>Bull</t>
         </is>
@@ -1630,13 +1642,13 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <v>134500</v>
       </c>
-      <c r="G7" s="31" t="n">
+      <c r="G7" s="33" t="n">
         <v>134500</v>
       </c>
-      <c r="H7" s="31" t="n">
+      <c r="H7" s="33" t="n">
         <v>134500</v>
       </c>
     </row>
@@ -1807,7 +1819,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -1909,919 +1921,919 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="33" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 1</t>
         </is>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="35">
         <f>11102600*(1+F4)</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="35">
         <f>11102600*(1+G4)</f>
         <v/>
       </c>
-      <c r="H18" s="34">
+      <c r="H18" s="35">
         <f>11102600*(1+H4)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 2</t>
         </is>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="35">
         <f>F18*(1+F5)</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="35">
         <f>G18*(1+G5)</f>
         <v/>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="35">
         <f>H18*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="33" t="inlineStr">
+      <c r="A20" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 3</t>
         </is>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="35">
         <f>F19*(1+F5)</f>
         <v/>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="35">
         <f>G19*(1+G5)</f>
         <v/>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="35">
         <f>H19*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="33" t="inlineStr">
+      <c r="A21" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 4</t>
         </is>
       </c>
-      <c r="F21" s="34">
+      <c r="F21" s="35">
         <f>F20*(1+F5)</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="35">
         <f>G20*(1+G5)</f>
         <v/>
       </c>
-      <c r="H21" s="34">
+      <c r="H21" s="35">
         <f>H20*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Revenue – year 5</t>
         </is>
       </c>
-      <c r="F22" s="34">
+      <c r="F22" s="35">
         <f>F21*(1+F5)</f>
         <v/>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="35">
         <f>G21*(1+G5)</f>
         <v/>
       </c>
-      <c r="H22" s="34">
+      <c r="H22" s="35">
         <f>H21*(1+H5)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 1</t>
         </is>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="36">
         <f>F6+(F8-F6)*0/4</f>
         <v/>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="36">
         <f>G6+(G8-G6)*0/4</f>
         <v/>
       </c>
-      <c r="H23" s="35">
+      <c r="H23" s="36">
         <f>H6+(H8-H6)*0/4</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 2</t>
         </is>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="36">
         <f>F6+(F8-F6)*1/4</f>
         <v/>
       </c>
-      <c r="G24" s="35">
+      <c r="G24" s="36">
         <f>G6+(G8-G6)*1/4</f>
         <v/>
       </c>
-      <c r="H24" s="35">
+      <c r="H24" s="36">
         <f>H6+(H8-H6)*1/4</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 3</t>
         </is>
       </c>
-      <c r="F25" s="35">
+      <c r="F25" s="36">
         <f>F6+(F8-F6)*2/4</f>
         <v/>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <f>G6+(G8-G6)*2/4</f>
         <v/>
       </c>
-      <c r="H25" s="35">
+      <c r="H25" s="36">
         <f>H6+(H8-H6)*2/4</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="33" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 4</t>
         </is>
       </c>
-      <c r="F26" s="35">
+      <c r="F26" s="36">
         <f>F6+(F8-F6)*3/4</f>
         <v/>
       </c>
-      <c r="G26" s="35">
+      <c r="G26" s="36">
         <f>G6+(G8-G6)*3/4</f>
         <v/>
       </c>
-      <c r="H26" s="35">
+      <c r="H26" s="36">
         <f>H6+(H8-H6)*3/4</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Clean EBIT margin – year 5</t>
         </is>
       </c>
-      <c r="F27" s="35">
+      <c r="F27" s="36">
         <f>F6+(F8-F6)*4/4</f>
         <v/>
       </c>
-      <c r="G27" s="35">
+      <c r="G27" s="36">
         <f>G6+(G8-G6)*4/4</f>
         <v/>
       </c>
-      <c r="H27" s="35">
+      <c r="H27" s="36">
         <f>H6+(H8-H6)*4/4</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="33" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 1</t>
         </is>
       </c>
-      <c r="F28" s="34">
+      <c r="F28" s="35">
         <f>F18*F23+F7</f>
         <v/>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="35">
         <f>G18*G23+G7</f>
         <v/>
       </c>
-      <c r="H28" s="34">
+      <c r="H28" s="35">
         <f>H18*H23+H7</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 2</t>
         </is>
       </c>
-      <c r="F29" s="34">
+      <c r="F29" s="35">
         <f>F19*F24</f>
         <v/>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="35">
         <f>G19*G24</f>
         <v/>
       </c>
-      <c r="H29" s="34">
+      <c r="H29" s="35">
         <f>H19*H24</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 3</t>
         </is>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="35">
         <f>F20*F25</f>
         <v/>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="35">
         <f>G20*G25</f>
         <v/>
       </c>
-      <c r="H30" s="34">
+      <c r="H30" s="35">
         <f>H20*H25</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 4</t>
         </is>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="35">
         <f>F21*F26</f>
         <v/>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="35">
         <f>G21*G26</f>
         <v/>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="35">
         <f>H21*H26</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  EBIT – year 5</t>
         </is>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="35">
         <f>F22*F27</f>
         <v/>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="35">
         <f>G22*G27</f>
         <v/>
       </c>
-      <c r="H32" s="34">
+      <c r="H32" s="35">
         <f>H22*H27</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 1</t>
         </is>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <f>F28*(1-F11)</f>
         <v/>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <f>G28*(1-G11)</f>
         <v/>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <f>H28*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="33" t="inlineStr">
+      <c r="A34" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 2</t>
         </is>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <f>F29*(1-F11)</f>
         <v/>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <f>G29*(1-G11)</f>
         <v/>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <f>H29*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 3</t>
         </is>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <f>F30*(1-F11)</f>
         <v/>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <f>G30*(1-G11)</f>
         <v/>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <f>H30*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="33" t="inlineStr">
+      <c r="A36" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 4</t>
         </is>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <f>F31*(1-F11)</f>
         <v/>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <f>G31*(1-G11)</f>
         <v/>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <f>H31*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="33" t="inlineStr">
+      <c r="A37" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NOPAT – year 5</t>
         </is>
       </c>
-      <c r="F37" s="34">
+      <c r="F37" s="35">
         <f>F32*(1-F11)</f>
         <v/>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="35">
         <f>G32*(1-G11)</f>
         <v/>
       </c>
-      <c r="H37" s="34">
+      <c r="H37" s="35">
         <f>H32*(1-H11)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="33" t="inlineStr">
+      <c r="A38" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 1</t>
         </is>
       </c>
-      <c r="F38" s="34">
+      <c r="F38" s="35">
         <f>F18*F12</f>
         <v/>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="35">
         <f>G18*G12</f>
         <v/>
       </c>
-      <c r="H38" s="34">
+      <c r="H38" s="35">
         <f>H18*H12</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 2</t>
         </is>
       </c>
-      <c r="F39" s="34">
+      <c r="F39" s="35">
         <f>F19*F12</f>
         <v/>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="35">
         <f>G19*G12</f>
         <v/>
       </c>
-      <c r="H39" s="34">
+      <c r="H39" s="35">
         <f>H19*H12</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="33" t="inlineStr">
+      <c r="A40" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 3</t>
         </is>
       </c>
-      <c r="F40" s="34">
+      <c r="F40" s="35">
         <f>F20*F12</f>
         <v/>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="35">
         <f>G20*G12</f>
         <v/>
       </c>
-      <c r="H40" s="34">
+      <c r="H40" s="35">
         <f>H20*H12</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="inlineStr">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 4</t>
         </is>
       </c>
-      <c r="F41" s="34">
+      <c r="F41" s="35">
         <f>F21*F12</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="35">
         <f>G21*G12</f>
         <v/>
       </c>
-      <c r="H41" s="34">
+      <c r="H41" s="35">
         <f>H21*H12</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="inlineStr">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  D&amp;A – year 5</t>
         </is>
       </c>
-      <c r="F42" s="34">
+      <c r="F42" s="35">
         <f>F22*F12</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="35">
         <f>G22*G12</f>
         <v/>
       </c>
-      <c r="H42" s="34">
+      <c r="H42" s="35">
         <f>H22*H12</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="inlineStr">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 1</t>
         </is>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="35">
         <f>F18*F13</f>
         <v/>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="35">
         <f>G18*G13</f>
         <v/>
       </c>
-      <c r="H43" s="34">
+      <c r="H43" s="35">
         <f>H18*H13</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="inlineStr">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 2</t>
         </is>
       </c>
-      <c r="F44" s="34">
+      <c r="F44" s="35">
         <f>F19*F13</f>
         <v/>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="35">
         <f>G19*G13</f>
         <v/>
       </c>
-      <c r="H44" s="34">
+      <c r="H44" s="35">
         <f>H19*H13</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="inlineStr">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 3</t>
         </is>
       </c>
-      <c r="F45" s="34">
+      <c r="F45" s="35">
         <f>F20*F13</f>
         <v/>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="35">
         <f>G20*G13</f>
         <v/>
       </c>
-      <c r="H45" s="34">
+      <c r="H45" s="35">
         <f>H20*H13</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="inlineStr">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 4</t>
         </is>
       </c>
-      <c r="F46" s="34">
+      <c r="F46" s="35">
         <f>F21*F13</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="35">
         <f>G21*G13</f>
         <v/>
       </c>
-      <c r="H46" s="34">
+      <c r="H46" s="35">
         <f>H21*H13</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="inlineStr">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Capex – year 5</t>
         </is>
       </c>
-      <c r="F47" s="34">
+      <c r="F47" s="35">
         <f>F22*F13</f>
         <v/>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="35">
         <f>G22*G13</f>
         <v/>
       </c>
-      <c r="H47" s="34">
+      <c r="H47" s="35">
         <f>H22*H13</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="33" t="inlineStr">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 1</t>
         </is>
       </c>
-      <c r="F48" s="34">
+      <c r="F48" s="35">
         <f>F18*F15</f>
         <v/>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="35">
         <f>G18*G15</f>
         <v/>
       </c>
-      <c r="H48" s="34">
+      <c r="H48" s="35">
         <f>H18*H15</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="inlineStr">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 2</t>
         </is>
       </c>
-      <c r="F49" s="34">
+      <c r="F49" s="35">
         <f>F19*F15</f>
         <v/>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="35">
         <f>G19*G15</f>
         <v/>
       </c>
-      <c r="H49" s="34">
+      <c r="H49" s="35">
         <f>H19*H15</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="inlineStr">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 3</t>
         </is>
       </c>
-      <c r="F50" s="34">
+      <c r="F50" s="35">
         <f>F20*F15</f>
         <v/>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="35">
         <f>G20*G15</f>
         <v/>
       </c>
-      <c r="H50" s="34">
+      <c r="H50" s="35">
         <f>H20*H15</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="inlineStr">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 4</t>
         </is>
       </c>
-      <c r="F51" s="34">
+      <c r="F51" s="35">
         <f>F21*F15</f>
         <v/>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="35">
         <f>G21*G15</f>
         <v/>
       </c>
-      <c r="H51" s="34">
+      <c r="H51" s="35">
         <f>H21*H15</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="inlineStr">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  NWC – AR balance (inside NWC) – year 5</t>
         </is>
       </c>
-      <c r="F52" s="34">
+      <c r="F52" s="35">
         <f>F22*F15</f>
         <v/>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="35">
         <f>G22*G15</f>
         <v/>
       </c>
-      <c r="H52" s="34">
+      <c r="H52" s="35">
         <f>H22*H15</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="inlineStr">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 1</t>
         </is>
       </c>
-      <c r="F53" s="34">
+      <c r="F53" s="35">
         <f>F14*(F18-11102600)</f>
         <v/>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="35">
         <f>G14*(G18-11102600)</f>
         <v/>
       </c>
-      <c r="H53" s="34">
+      <c r="H53" s="35">
         <f>H14*(H18-11102600)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="inlineStr">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 2</t>
         </is>
       </c>
-      <c r="F54" s="34">
+      <c r="F54" s="35">
         <f>F14*(F19-F18)</f>
         <v/>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="35">
         <f>G14*(G19-G18)</f>
         <v/>
       </c>
-      <c r="H54" s="34">
+      <c r="H54" s="35">
         <f>H14*(H19-H18)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="inlineStr">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 3</t>
         </is>
       </c>
-      <c r="F55" s="34">
+      <c r="F55" s="35">
         <f>F14*(F20-F19)</f>
         <v/>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="35">
         <f>G14*(G20-G19)</f>
         <v/>
       </c>
-      <c r="H55" s="34">
+      <c r="H55" s="35">
         <f>H14*(H20-H19)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="inlineStr">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 4</t>
         </is>
       </c>
-      <c r="F56" s="34">
+      <c r="F56" s="35">
         <f>F14*(F21-F20)</f>
         <v/>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="35">
         <f>G14*(G21-G20)</f>
         <v/>
       </c>
-      <c r="H56" s="34">
+      <c r="H56" s="35">
         <f>H14*(H21-H20)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="inlineStr">
+      <c r="A57" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  ΔNWC (includes AR) – year 5</t>
         </is>
       </c>
-      <c r="F57" s="34">
+      <c r="F57" s="35">
         <f>F14*(F22-F21)</f>
         <v/>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="35">
         <f>G14*(G22-G21)</f>
         <v/>
       </c>
-      <c r="H57" s="34">
+      <c r="H57" s="35">
         <f>H14*(H22-H21)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="33" t="inlineStr">
+      <c r="A58" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 1</t>
         </is>
       </c>
-      <c r="F58" s="34">
+      <c r="F58" s="35">
         <f>F33+F38-F43-F53</f>
         <v/>
       </c>
-      <c r="G58" s="34">
+      <c r="G58" s="35">
         <f>G33+G38-G43-G53</f>
         <v/>
       </c>
-      <c r="H58" s="34">
+      <c r="H58" s="35">
         <f>H33+H38-H43-H53</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="33" t="inlineStr">
+      <c r="A59" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 2</t>
         </is>
       </c>
-      <c r="F59" s="34">
+      <c r="F59" s="35">
         <f>F34+F39-F44-F54</f>
         <v/>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="35">
         <f>G34+G39-G44-G54</f>
         <v/>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <f>H34+H39-H44-H54</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="33" t="inlineStr">
+      <c r="A60" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 3</t>
         </is>
       </c>
-      <c r="F60" s="34">
+      <c r="F60" s="35">
         <f>F35+F40-F45-F55</f>
         <v/>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="35">
         <f>G35+G40-G45-G55</f>
         <v/>
       </c>
-      <c r="H60" s="34">
+      <c r="H60" s="35">
         <f>H35+H40-H45-H55</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="inlineStr">
+      <c r="A61" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 4</t>
         </is>
       </c>
-      <c r="F61" s="34">
+      <c r="F61" s="35">
         <f>F36+F41-F46-F56</f>
         <v/>
       </c>
-      <c r="G61" s="34">
+      <c r="G61" s="35">
         <f>G36+G41-G46-G56</f>
         <v/>
       </c>
-      <c r="H61" s="34">
+      <c r="H61" s="35">
         <f>H36+H41-H46-H56</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="33" t="inlineStr">
+      <c r="A62" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Unlevered FCF – year 5</t>
         </is>
       </c>
-      <c r="F62" s="34">
+      <c r="F62" s="35">
         <f>F37+F42-F47-F57</f>
         <v/>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="35">
         <f>G37+G42-G47-G57</f>
         <v/>
       </c>
-      <c r="H62" s="34">
+      <c r="H62" s="35">
         <f>H37+H42-H47-H57</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="23" t="inlineStr">
+      <c r="A64" s="24" t="inlineStr">
         <is>
           <t>Enterprise value (DCF)</t>
         </is>
       </c>
-      <c r="F64" s="36">
+      <c r="F64" s="37">
         <f>NPV(F9,F58,F59,F60,F61,F62)+(F62*(1+F10)/(F9-F10))/(1+F9)^5</f>
         <v/>
       </c>
-      <c r="G64" s="36">
+      <c r="G64" s="37">
         <f>NPV(G9,G58,G59,G60,G61,G62)+(G62*(1+G10)/(G9-G10))/(1+G9)^5</f>
         <v/>
       </c>
-      <c r="H64" s="36">
+      <c r="H64" s="37">
         <f>NPV(H9,H58,H59,H60,H61,H62)+(H62*(1+H10)/(H9-H10))/(1+H9)^5</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="37" t="inlineStr">
+      <c r="A65" s="38" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="F65" s="38">
+      <c r="F65" s="39">
         <f>(F64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="G65" s="39">
+      <c r="G65" s="40">
         <f>(G64+1807202-0)/111380</f>
         <v/>
       </c>
-      <c r="H65" s="38">
+      <c r="H65" s="39">
         <f>(H64+1807202-0)/111380</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="23" t="inlineStr">
+      <c r="A66" s="24" t="inlineStr">
         <is>
           <t>Upside / (downside) vs current</t>
         </is>
       </c>
-      <c r="F66" s="40">
+      <c r="F66" s="41">
         <f>F65/100.0-1</f>
         <v/>
       </c>
-      <c r="G66" s="40">
+      <c r="G66" s="41">
         <f>G65/100.0-1</f>
         <v/>
       </c>
-      <c r="H66" s="40">
+      <c r="H66" s="41">
         <f>H65/100.0-1</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="41" t="inlineStr">
+      <c r="A68" s="26" t="inlineStr">
         <is>
           <t>Current price $100.00; cash $1,807,202 k; net debt $0 (net-cash balance sheet).</t>
         </is>
@@ -2834,7 +2846,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId5"/>
-    <hyperlink ref="C9" location="'WACC'!E18"/>
+    <hyperlink ref="C9" location="'WACC'!E19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId8"/>
@@ -3016,7 +3028,7 @@
 Also: 2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast (3Y) of 2.26%; next-year consensus is +2.64%.</t>
         </is>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release
 Also: StockAnalysis: LULU 3Y revenue forecast</t>
@@ -3061,7 +3073,7 @@
 Also: FY30 15.5% is a partial recovery vs the FY25 10-K OM of 19.9% (unique Ctrl+F). Still well below the FY24 23.7% peak.</t>
         </is>
       </c>
-      <c r="C7" s="32" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs
 Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
@@ -3122,25 +3134,25 @@
       <c r="E8" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="33">
         <f>Scenarios!$G$7</f>
         <v/>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>EBIT (incl. FY26 refund)</t>
         </is>
@@ -3148,23 +3160,23 @@
       <c r="E9" s="53" t="n">
         <v>2210615</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="37">
         <f>Scenarios!G28</f>
         <v/>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="37">
         <f>Scenarios!G29</f>
         <v/>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="37">
         <f>Scenarios!G30</f>
         <v/>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="37">
         <f>Scenarios!G31</f>
         <v/>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="37">
         <f>Scenarios!G32</f>
         <v/>
       </c>
@@ -3231,28 +3243,28 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="37">
         <f>Scenarios!G33</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="37">
         <f>Scenarios!G34</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="37">
         <f>Scenarios!G35</f>
         <v/>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="37">
         <f>Scenarios!G36</f>
         <v/>
       </c>
-      <c r="J12" s="36">
+      <c r="J12" s="37">
         <f>Scenarios!G37</f>
         <v/>
       </c>
@@ -3346,7 +3358,7 @@
 Also: FY26 sales are $10.35–$10.50B (earnings). Use that $10.4B year as the 7% denominator, not FY25 $11.1B.</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M
 Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
@@ -3585,14 +3597,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: NWC and AR are one line. 7.5% of Δsales already includes AR; UFCF does not take ΔAR separately.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="24" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
@@ -3672,28 +3684,28 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="37">
         <f>F22*F24</f>
         <v/>
       </c>
-      <c r="G25" s="36">
+      <c r="G25" s="37">
         <f>G22*G24</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="37">
         <f>H22*H24</f>
         <v/>
       </c>
-      <c r="I25" s="36">
+      <c r="I25" s="37">
         <f>I22*I24</f>
         <v/>
       </c>
-      <c r="J25" s="36">
+      <c r="J25" s="37">
         <f>J22*J24</f>
         <v/>
       </c>
@@ -3719,7 +3731,7 @@
       <c r="C28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>Sum of PV of explicit FCF (FY26–FY30)</t>
         </is>
@@ -3756,12 +3768,12 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
         </is>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <f>J9+J14</f>
         <v/>
       </c>
@@ -3789,7 +3801,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>PV of terminal value</t>
         </is>
@@ -3800,12 +3812,12 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <f>E29+E34</f>
         <v/>
       </c>
@@ -3851,12 +3863,12 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="37">
         <f>E35+E36+E37</f>
         <v/>
       </c>
@@ -3882,7 +3894,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
@@ -3917,7 +3929,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
@@ -4007,18 +4019,18 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="A50" s="24" t="inlineStr">
         <is>
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="E50" s="36">
+      <c r="E50" s="37">
         <f>E29+E49</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="inlineStr">
+      <c r="A51" s="24" t="inlineStr">
         <is>
           <t>Implied value per share (exit method)</t>
         </is>
@@ -4057,7 +4069,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+      <c r="A55" s="24" t="inlineStr">
         <is>
           <t>Terminal value ($)</t>
         </is>
@@ -4076,7 +4088,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="23" t="inlineStr">
+      <c r="A56" s="24" t="inlineStr">
         <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
@@ -4108,7 +4120,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="A58" s="24" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
@@ -4140,7 +4152,7 @@
         <f>TEXT(D56,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
         <v/>
       </c>
-      <c r="D59" s="41" t="inlineStr">
+      <c r="D59" s="26" t="inlineStr">
         <is>
           <t>Gordon implied should bracket exit assumption</t>
         </is>
@@ -4439,11 +4451,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
     <hyperlink ref="L63" location="'Scenarios'!G10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
-    <hyperlink ref="L64" location="'WACC'!E18"/>
-    <hyperlink ref="L65" location="'WACC'!E18"/>
-    <hyperlink ref="L66" location="'WACC'!E18"/>
-    <hyperlink ref="L67" location="'WACC'!E18"/>
-    <hyperlink ref="L68" location="'WACC'!E18"/>
+    <hyperlink ref="L64" location="'WACC'!E19"/>
+    <hyperlink ref="L65" location="'WACC'!E19"/>
+    <hyperlink ref="L66" location="'WACC'!E19"/>
+    <hyperlink ref="L67" location="'WACC'!E19"/>
+    <hyperlink ref="L68" location="'WACC'!E19"/>
     <hyperlink ref="C69" location="'Scenarios'!G9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId27"/>
   </hyperlinks>
@@ -4704,7 +4716,7 @@
           <t>lululemon (LULU) — current</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Distressed trough multiple on FY2025A EBITDA</t>
         </is>
@@ -4897,35 +4909,35 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="33" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="34" t="inlineStr">
         <is>
           <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="33" t="inlineStr">
+      <c r="A32" s="34" t="inlineStr">
         <is>
           <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="33" t="inlineStr">
+      <c r="A33" s="34" t="inlineStr">
         <is>
           <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
         </is>
@@ -5134,7 +5146,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
         </is>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -1111,7 +1111,7 @@
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
+          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark 23.5x are growth prints, not FY30 exit.</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D47" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
+          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x equals Deckers, not the public mean</t>
         </is>
       </c>
       <c r="E47" s="67" t="n">
@@ -4447,7 +4447,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId24"/>
-    <hyperlink ref="M47" location="'Comps'!A26"/>
+    <hyperlink ref="M47" location="'Comps'!A33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
     <hyperlink ref="L63" location="'Scenarios'!G10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
@@ -4469,13 +4469,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -4861,294 +4861,429 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Terminal multiple selection (DCF exit method)</t>
-        </is>
+    <row r="23" ht="150" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Gymshark (private)</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>23.5x = 1,250 / 53.3. 2020 GA EV on FY25 EBITDA; private growth print, not an FY30 exit.
+Also: FY25 EBITDA £53.3m (SGB). 62.3% is gross margin, not EBITDA. Margin ≈ 53.3 / 646 = 8.3%.</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>Guardian: Gymshark 2020 GA £1.25bn
+Also: SGB: Gymshark FY25 EBITDA £53.3m</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>Private print — do not use as FY30 exit
+  23.5x = 1,250 / 53.3
+2020 GA EV (Guardian)
+  Ctrl+F "£1.25bn valuation"
+  Ctrl+F "sold a 21% stake"
+FY25 EBITDA (SGB)
+  Ctrl+F "our EBITDA, which reached £53.3 million"
+  Do not take "62.3 percent" — that is gross margin
+  EBITDA margin ≈ 53.3 / 646 = 8.3%</t>
+        </is>
+      </c>
+      <c r="E23" s="84">
+        <f>1250/53.3</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>Gordon Growth implied exit EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="E25" s="62">
-        <f>DCF!E33</f>
-        <v/>
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Averages (live Excel AVERAGE — shown so TV is not a blended print)</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="73" t="inlineStr">
-        <is>
-          <t>Selected exit multiple (base case)</t>
-        </is>
-      </c>
-      <c r="E26" s="71">
-        <f>DCF!E47</f>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Public 5-name mean (NKE / DECK / ONON / ADS / VFC)</t>
+        </is>
+      </c>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>10.8x simple mean. Too high for a 2.25% g / 15.5% OM terminal year — not the TV.</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of the five public prints</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
+        </is>
+      </c>
+      <c r="E26" s="83">
+        <f>AVERAGE(E18,E19,E20,E21,E22)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
+          <t>Mature public mean (DECK / ADS / VFC)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>~9.3x closest mature set. Still haircut ~1 turn to 8.0x for 2.25% terminal g.</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Haircut to selected 8.0x.</t>
+        </is>
+      </c>
+      <c r="E27" s="83">
+        <f>AVERAGE(E19,E21,E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Mean incl. Gymshark (do not use for TV)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>~12.9x. Gymshark 23.5x is a 2020 growth print; averaging it overstates FY30 exit.</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of five publics + Gymshark</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Math: (12.0+8.0+14.0+9.3+10.7+1,250/53.3)/6 ≈ 12.9x. Not the TV.</t>
+        </is>
+      </c>
+      <c r="E28" s="83">
+        <f>AVERAGE(E18,E19,E20,E21,E22,E23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="75" t="inlineStr">
+        <is>
+          <t>We do not average EV/EBITDA for terminal value. A 2.25% g year is not a growth-comp tape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Terminal multiple selection (DCF exit method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Gordon Growth implied exit EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="E32" s="62">
+        <f>DCF!E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="73" t="inlineStr">
+        <is>
+          <t>Selected exit multiple (base case)</t>
+        </is>
+      </c>
+      <c r="E33" s="71">
+        <f>DCF!E47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E27" s="62">
-        <f>E26-E25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="73" t="inlineStr">
-        <is>
-          <t>Rationale for 8.0x</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>•  Mid-point of terminal football field (6.5–9.5x on FY2030E EBITDA) — 8.0x sits between bear and bull exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>•  Above Gordon-implied exit (~7x) — ~1 turn buffer vs perpetuity math on terminal FCF</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>•  Below premium-growth peers (ONON ~25x, DECK ~15x) — reflects Americas maturity at terminal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>•  Above current LULU (~3.5x on FY2025A) — assumes partial recovery, not full re-rating to historical peaks</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="34" t="inlineStr">
-        <is>
-          <t>•  Peer simple avg ~16x not used — terminal multiple discounted for lower terminal growth vs ONON/NKE</t>
-        </is>
+      <c r="E34" s="62">
+        <f>E33-E32</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="73" t="inlineStr">
+        <is>
+          <t>Rationale for 8.0x (not the average)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t>•  8.0x equals Deckers (7.95x rounded) — closest mature premium analog on the tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="34" t="inlineStr">
+        <is>
+          <t>•  ~1 turn above Gordon-implied ~7x — buffer vs perpetuity math on 2.25% terminal g</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>•  Mid-point of the 6.5–9.5x football field — not the 10.8x public 5-name mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>•  Mature public mean (DECK / ADS / VFC) is ~9.3x; we haircut ~1 turn for 2.25% terminal g</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>•  Gymshark 23.5x = 1,250 / 53.3 is a 2020 private growth print; averaging it (~12.9x) is not an FY30 exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="34" t="inlineStr">
+        <is>
+          <t>•  Current LULU ~3.5x on FY2025A is a trough — 8.0x assumes partial recovery, not a re-rate to ONON 14x</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Methodology / multiple ranges (FY2030E terminal EBITDA — football field)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="81" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="81" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B36" s="81" t="inlineStr">
+      <c r="B44" s="81" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C36" s="81" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D36" s="81" t="inlineStr">
+      <c r="D44" s="81" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E36" s="82" t="inlineStr">
+      <c r="E44" s="82" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F36" s="82" t="inlineStr">
+      <c r="F44" s="82" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G36" s="82" t="inlineStr">
+      <c r="G44" s="82" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H36" s="82" t="inlineStr">
+      <c r="H44" s="82" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="B37" s="19" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>Lo: 6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.
-Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below peer median ~15x.</t>
-        </is>
-      </c>
-      <c r="C37" s="85" t="inlineStr">
+Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below public mean ~10.8x.</t>
+        </is>
+      </c>
+      <c r="C45" s="85" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: LULU valuation</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D45" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; bear terminal exit assumption 6.5x
 Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
-      <c r="E37" s="84" t="n">
+      <c r="E45" s="84" t="n">
         <v>6.5</v>
       </c>
-      <c r="F37" s="84" t="n">
+      <c r="F45" s="84" t="n">
         <v>9.5</v>
       </c>
-      <c r="G37" s="86">
-        <f>(E6*E37+E8)/E9</f>
-        <v/>
-      </c>
-      <c r="H37" s="86">
-        <f>(E6*F37+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="73" t="inlineStr">
+      <c r="G45" s="86">
+        <f>(E6*E45+E8)/E9</f>
+        <v/>
+      </c>
+      <c r="H45" s="86">
+        <f>(E6*F45+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="73" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>8.0x FY2030E exit EV/EBITDA; mid-point of terminal football field (6.5–9.5x); ~1 turn above Gordon-implied ~7x.</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark 23.5x are growth prints, not FY30 exit.</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
-      <c r="D38" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x (assumption)</t>
-        </is>
-      </c>
-      <c r="E38" s="87">
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x equals Deckers, not the public mean</t>
+        </is>
+      </c>
+      <c r="E46" s="87">
         <f>DCF!E47</f>
         <v/>
       </c>
-      <c r="G38" s="88">
-        <f>(E6*E38+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="G46" s="88">
+        <f>(E6*E46+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="42" customHeight="1">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="B39" s="19" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C39" s="85" t="inlineStr">
+      <c r="C47" s="85" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "Forward PE" → LULU ~12.3x; low-case multiple assumption 10.0x
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E39" s="84" t="n">
+      <c r="E47" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="F39" s="84" t="n">
+      <c r="F47" s="84" t="n">
         <v>18</v>
       </c>
-      <c r="G39" s="86">
-        <f>E7*E39</f>
-        <v/>
-      </c>
-      <c r="H39" s="86">
-        <f>E7*F39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="G47" s="86">
+        <f>E7*E47</f>
+        <v/>
+      </c>
+      <c r="H47" s="86">
+        <f>E7*F47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E40" s="89" t="inlineStr">
+      <c r="E48" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F40" s="89" t="inlineStr">
+      <c r="F48" s="89" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G40" s="86">
+      <c r="G48" s="86">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H40" s="86">
+      <c r="H48" s="86">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="90" t="inlineStr">
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="90" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C42" s="63" t="inlineStr">
+      <c r="C50" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="D42" s="19" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E42" s="91" t="n">
+      <c r="E50" s="91" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="26" t="inlineStr">
-        <is>
-          <t>Note: peer set includes NKE, DECK, ONON, adidas, VFC; multiples are analyst ranges (red).</t>
+    <row r="51">
+      <c r="A51" s="26" t="inlineStr">
+        <is>
+          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Gymshark is a private reference (23.5x = 1,250/53.3). Selected TV is 8.0x, not the average.</t>
         </is>
       </c>
     </row>
@@ -5171,11 +5306,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId17"/>
-    <hyperlink ref="C38" location="'DCF'!E47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId18"/>
+    <hyperlink ref="C46" location="'DCF'!E47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -20,12 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0x"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="45">
     <font>
@@ -356,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -582,13 +583,19 @@
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3974,7 +3981,7 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark 23.5x are growth prints, not FY30 exit.</t>
+          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark implied 23.5x are not FY30 exit.</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
@@ -4447,7 +4454,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId24"/>
-    <hyperlink ref="M47" location="'Comps'!A33"/>
+    <hyperlink ref="M47" location="'Comps'!A38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
     <hyperlink ref="L63" location="'Scenarios'!G10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
@@ -4469,7 +4476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4861,429 +4868,483 @@
         <v>10.7</v>
       </c>
     </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>Gymshark (private)</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>23.5x = 1,250 / 53.3. 2020 GA EV on FY25 EBITDA; private growth print, not an FY30 exit.
-Also: FY25 EBITDA £53.3m (SGB). 62.3% is gross margin, not EBITDA. Margin ≈ 53.3 / 646 = 8.3%.</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>Guardian: Gymshark 2020 GA £1.25bn
-Also: SGB: Gymshark FY25 EBITDA £53.3m</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>Private print — do not use as FY30 exit
-  23.5x = 1,250 / 53.3
-2020 GA EV (Guardian)
-  Ctrl+F "£1.25bn valuation"
-  Ctrl+F "sold a 21% stake"
-FY25 EBITDA (SGB)
-  Ctrl+F "our EBITDA, which reached £53.3 million"
-  Do not take "62.3 percent" — that is gross margin
-  EBITDA margin ≈ 53.3 / 646 = 8.3%</t>
-        </is>
-      </c>
-      <c r="E23" s="84">
-        <f>1250/53.3</f>
-        <v/>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>GYMSHARK BUILD — implied multiple (no source prints EV/EBITDA)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>Column E on the next two rows is £m, not a multiple. Implied EV/EBITDA is the black formula below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Gymshark 2020 GA valuation (£m)</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>£1.25bn = 1,250 in £m. 2020 GA headline valuation (Guardian). Not a published EV or EV/EBITDA.</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Guardian: Gymshark 2020 GA £1.25bn</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "£1.25bn valuation" and "sold a 21% stake". That proves the 2020 valuation (£m = 1,250), not EV/EBITDA.</t>
+        </is>
+      </c>
+      <c r="E26" s="85" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Gymshark FY25 EBITDA (£m)</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>FY25 EBITDA is £53.3m (SGB). 62.3% is gross margin. This cell is EBITDA £m, not a multiple.</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>SGB: Gymshark FY25 EBITDA £53.3m</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "our EBITDA, which reached £53.3 million". That proves FY25 EBITDA £m. Do not take "62.3 percent" (gross margin).</t>
+        </is>
+      </c>
+      <c r="E27" s="86" t="n">
+        <v>53.3</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="73" t="inlineStr">
+        <is>
+          <t>Gymshark implied EV/EBITDA (model math)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>No page prints Gymshark EV/EBITDA. Black formula = 2020 valuation / FY25 EBITDA. Cross-year; not the TV.</t>
+        </is>
+      </c>
+      <c r="C28" s="63" t="inlineStr">
+        <is>
+          <t>Comps: Gymshark valuation / EBITDA</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>No Ctrl+F. Neither Guardian nor SGB prints EV/EBITDA. This cell is E26 / E27 (2020 valuation ÷ FY25 EBITDA).</t>
+        </is>
+      </c>
+      <c r="E28" s="87">
+        <f>E26/E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Averages (live Excel AVERAGE — shown so TV is not a blended print)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Public 5-name mean (NKE / DECK / ONON / ADS / VFC)</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>10.8x simple mean. Too high for a 2.25% g / 15.5% OM terminal year — not the TV.</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Derived: Excel AVERAGE of the five public prints</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
         </is>
       </c>
-      <c r="E26" s="83">
+      <c r="E31" s="83">
         <f>AVERAGE(E18,E19,E20,E21,E22)</f>
         <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>Mature public mean (DECK / ADS / VFC)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="inlineStr">
-        <is>
-          <t>~9.3x closest mature set. Still haircut ~1 turn to 8.0x for 2.25% terminal g.</t>
-        </is>
-      </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
-        </is>
-      </c>
-      <c r="D27" s="26" t="inlineStr">
-        <is>
-          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Haircut to selected 8.0x.</t>
-        </is>
-      </c>
-      <c r="E27" s="83">
-        <f>AVERAGE(E19,E21,E22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Mean incl. Gymshark (do not use for TV)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>~12.9x. Gymshark 23.5x is a 2020 growth print; averaging it overstates FY30 exit.</t>
-        </is>
-      </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>Derived: Excel AVERAGE of five publics + Gymshark</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>Math: (12.0+8.0+14.0+9.3+10.7+1,250/53.3)/6 ≈ 12.9x. Not the TV.</t>
-        </is>
-      </c>
-      <c r="E28" s="83">
-        <f>AVERAGE(E18,E19,E20,E21,E22,E23)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="75" t="inlineStr">
-        <is>
-          <t>We do not average EV/EBITDA for terminal value. A 2.25% g year is not a growth-comp tape.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Terminal multiple selection (DCF exit method)</t>
-        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
+          <t>Mature public mean (DECK / ADS / VFC)</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>~9.3x closest mature set. Still haircut ~1 turn to 8.0x for 2.25% terminal g.</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Haircut to selected 8.0x.</t>
+        </is>
+      </c>
+      <c r="E32" s="83">
+        <f>AVERAGE(E19,E21,E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Mean incl. Gymshark (do not use for TV)</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>~12.9x. Gymshark implied 23.5x is model math (2020 val / FY25 EBITDA); averaging it overstates FY30 exit.</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of five publics + Gymshark</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Math: (12.0+8.0+14.0+9.3+10.7+1,250/53.3)/6 ≈ 12.9x. Not the TV.</t>
+        </is>
+      </c>
+      <c r="E33" s="83">
+        <f>AVERAGE(E18,E19,E20,E21,E22,E28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="75" t="inlineStr">
+        <is>
+          <t>We do not average EV/EBITDA for terminal value. A 2.25% g year is not a growth-comp tape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Terminal multiple selection (DCF exit method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
           <t>Gordon Growth implied exit EV/EBITDA</t>
         </is>
       </c>
-      <c r="E32" s="62">
+      <c r="E37" s="62">
         <f>DCF!E33</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="73" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="73" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="E33" s="71">
+      <c r="E38" s="71">
         <f>DCF!E47</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E34" s="62">
-        <f>E33-E32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="73" t="inlineStr">
+      <c r="E39" s="62">
+        <f>E38-E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="73" t="inlineStr">
         <is>
           <t>Rationale for 8.0x (not the average)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="34" t="inlineStr">
-        <is>
-          <t>•  8.0x equals Deckers (7.95x rounded) — closest mature premium analog on the tape</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="34" t="inlineStr">
-        <is>
-          <t>•  ~1 turn above Gordon-implied ~7x — buffer vs perpetuity math on 2.25% terminal g</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="inlineStr">
-        <is>
-          <t>•  Mid-point of the 6.5–9.5x football field — not the 10.8x public 5-name mean</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>•  Mature public mean (DECK / ADS / VFC) is ~9.3x; we haircut ~1 turn for 2.25% terminal g</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>•  Gymshark 23.5x = 1,250 / 53.3 is a 2020 private growth print; averaging it (~12.9x) is not an FY30 exit</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
         <is>
+          <t>•  8.0x equals Deckers (7.95x rounded) — closest mature premium analog on the tape</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="34" t="inlineStr">
+        <is>
+          <t>•  ~1 turn above Gordon-implied ~7x — buffer vs perpetuity math on 2.25% terminal g</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="34" t="inlineStr">
+        <is>
+          <t>•  Mid-point of the 6.5–9.5x football field — not the 10.8x public 5-name mean</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="34" t="inlineStr">
+        <is>
+          <t>•  Mature public mean (DECK / ADS / VFC) is ~9.3x; we haircut ~1 turn for 2.25% terminal g</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>•  Gymshark implied 23.5x is 2020 valuation / FY25 EBITDA — no page prints that multiple; averaging it (~12.9x) is not an FY30 exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
           <t>•  Current LULU ~3.5x on FY2025A is a trough — 8.0x assumes partial recovery, not a re-rate to ONON 14x</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Methodology / multiple ranges (FY2030E terminal EBITDA — football field)</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="81" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="81" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B44" s="81" t="inlineStr">
+      <c r="B49" s="81" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C44" s="81" t="inlineStr">
+      <c r="C49" s="81" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D44" s="81" t="inlineStr">
+      <c r="D49" s="81" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E44" s="82" t="inlineStr">
+      <c r="E49" s="82" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F44" s="82" t="inlineStr">
+      <c r="F49" s="82" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G44" s="82" t="inlineStr">
+      <c r="G49" s="82" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H44" s="82" t="inlineStr">
+      <c r="H49" s="82" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="16" t="inlineStr">
+    <row r="50" ht="42" customHeight="1">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="B45" s="19" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Lo: 6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.
 Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below public mean ~10.8x.</t>
         </is>
       </c>
-      <c r="C45" s="85" t="inlineStr">
+      <c r="C50" s="88" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: LULU valuation</t>
         </is>
       </c>
-      <c r="D45" s="19" t="inlineStr">
+      <c r="D50" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; bear terminal exit assumption 6.5x
 Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
         </is>
       </c>
-      <c r="E45" s="84" t="n">
+      <c r="E50" s="84" t="n">
         <v>6.5</v>
       </c>
-      <c r="F45" s="84" t="n">
+      <c r="F50" s="84" t="n">
         <v>9.5</v>
       </c>
-      <c r="G45" s="86">
-        <f>(E6*E45+E8)/E9</f>
-        <v/>
-      </c>
-      <c r="H45" s="86">
-        <f>(E6*F45+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="73" t="inlineStr">
+      <c r="G50" s="89">
+        <f>(E6*E50+E8)/E9</f>
+        <v/>
+      </c>
+      <c r="H50" s="89">
+        <f>(E6*F50+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="73" t="inlineStr">
         <is>
           <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark 23.5x are growth prints, not FY30 exit.</t>
-        </is>
-      </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark implied 23.5x are not FY30 exit.</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU EV/EBITDA</t>
         </is>
       </c>
-      <c r="D46" s="19" t="inlineStr">
+      <c r="D51" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x equals Deckers, not the public mean</t>
         </is>
       </c>
-      <c r="E46" s="87">
+      <c r="E51" s="87">
         <f>DCF!E47</f>
         <v/>
       </c>
-      <c r="G46" s="88">
-        <f>(E6*E46+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="42" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="G51" s="90">
+        <f>(E6*E51+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="42" customHeight="1">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="B47" s="19" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C47" s="85" t="inlineStr">
+      <c r="C52" s="88" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
       </c>
-      <c r="D47" s="19" t="inlineStr">
+      <c r="D52" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "Forward PE" → LULU ~12.3x; low-case multiple assumption 10.0x
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E47" s="84" t="n">
+      <c r="E52" s="84" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="84" t="n">
+      <c r="F52" s="84" t="n">
         <v>18</v>
       </c>
-      <c r="G47" s="86">
-        <f>E7*E47</f>
-        <v/>
-      </c>
-      <c r="H47" s="86">
-        <f>E7*F47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="G52" s="89">
+        <f>E7*E52</f>
+        <v/>
+      </c>
+      <c r="H52" s="89">
+        <f>E7*F52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E48" s="89" t="inlineStr">
+      <c r="E53" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F48" s="89" t="inlineStr">
+      <c r="F53" s="91" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G48" s="86">
+      <c r="G53" s="89">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H48" s="86">
+      <c r="H53" s="89">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="90" t="inlineStr">
+    <row r="55" ht="28" customHeight="1">
+      <c r="A55" s="92" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C50" s="63" t="inlineStr">
+      <c r="C55" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D55" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E50" s="91" t="n">
+      <c r="E55" s="93" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Gymshark is a private reference (23.5x = 1,250/53.3). Selected TV is 8.0x, not the average.</t>
+    <row r="56">
+      <c r="A56" s="26" t="inlineStr">
+        <is>
+          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Gymshark 23.5x is implied (2020 £1.25bn / FY25 £53.3m) — no source prints EV/EBITDA. Selected TV is 8.0x, not the average.</t>
         </is>
       </c>
     </row>
@@ -5306,12 +5367,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId18"/>
-    <hyperlink ref="C46" location="'DCF'!E47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId20"/>
+    <hyperlink ref="C28" location="'Comps'!E26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId21"/>
+    <hyperlink ref="C51" location="'DCF'!E47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -357,7 +357,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -529,9 +529,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2871,7 +2868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3799,7 +3796,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Implied exit EV/EBITDA (Gordon Growth)</t>
+          <t xml:space="preserve">  Implied exit EV/EBITDA = Gordon TV / FY30 EBITDA</t>
         </is>
       </c>
       <c r="E33" s="62">
@@ -3808,621 +3805,633 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="E34" s="61">
-        <f>E32/(1+Scenarios!$G$9)^J23</f>
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: (UFCF₃₀ / EBITDA₃₀) × (1+g) / (WACC−g)</t>
+        </is>
+      </c>
+      <c r="E34" s="62">
+        <f>J22/E31*(1+Scenarios!$G$10)/(Scenarios!$G$9-Scenarios!$G$10)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="24" t="inlineStr">
         <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="E35" s="61">
+        <f>E32/(1+Scenarios!$G$9)^J23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="E35" s="37">
-        <f>E29+E34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="C36" s="63" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
-        </is>
-      </c>
-      <c r="E36" s="49" t="n">
-        <v>1807202</v>
+      <c r="E36" s="37">
+        <f>E29+E35</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="16" t="inlineStr">
         <is>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
+        </is>
+      </c>
+      <c r="C37" s="63" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Cash and cash equivalents" → 1,807,202 ($000) FY2025</t>
+        </is>
+      </c>
+      <c r="E37" s="49" t="n">
+        <v>1807202</v>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="C37" s="63" t="inlineStr">
+      <c r="C38" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="D37" s="19" t="inlineStr">
+      <c r="D38" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "no borrowings were outstanding under this facility" → no funded term debt</t>
         </is>
       </c>
-      <c r="E37" s="49" t="n">
+      <c r="E38" s="49" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="E38" s="37">
-        <f>E35+E36+E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="E39" s="37">
+        <f>E36+E37+E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Diluted shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C39" s="63" t="inlineStr">
+      <c r="C40" s="63" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="D39" s="19" t="inlineStr">
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "Diluted weighted-average number of shares outstanding" → 119,068 (000)</t>
         </is>
       </c>
-      <c r="E39" s="49" t="n">
+      <c r="E40" s="49" t="n">
         <v>111380</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>Implied value per share</t>
         </is>
       </c>
-      <c r="E40" s="64">
-        <f>E38/E39</f>
-        <v/>
-      </c>
-      <c r="K40" s="54">
-        <f>IF(ABS(E40-Scenarios!$G$65)&lt;0.05,"OK","CHECK")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="E41" s="64">
+        <f>E39/E40</f>
+        <v/>
+      </c>
+      <c r="K41" s="54">
+        <f>IF(ABS(E41-Scenarios!$G$65)&lt;0.05,"OK","CHECK")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C41" s="63" t="inlineStr">
+      <c r="C42" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="D41" s="19" t="inlineStr">
+      <c r="D42" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E41" s="65" t="n">
+      <c r="E42" s="65" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>Implied upside / (downside)</t>
         </is>
       </c>
-      <c r="E42" s="66">
-        <f>E40/E41-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="E43" s="66">
+        <f>E41/E42-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: % of EV from terminal value</t>
         </is>
       </c>
-      <c r="E43" s="52">
-        <f>E34/E35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="60" t="inlineStr">
+      <c r="E44" s="52">
+        <f>E35/E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="60" t="inlineStr">
         <is>
           <t>CROSS-CHECK — EXIT MULTIPLE METHOD</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n"/>
-      <c r="C45" s="13" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Exit multiple selection (see Comps tab for peer build)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="16" t="inlineStr">
-        <is>
-          <t>Selected exit EV/EBITDA multiple (FY2030E)</t>
-        </is>
-      </c>
-      <c r="B47" s="17" t="inlineStr">
-        <is>
-          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark implied 23.5x are not FY30 exit.</t>
-        </is>
-      </c>
-      <c r="C47" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x equals Deckers, not the public mean</t>
-        </is>
-      </c>
-      <c r="E47" s="67" t="n">
-        <v>8</v>
-      </c>
-      <c r="M47" s="63" t="inlineStr">
+      <c r="B46" s="13" t="n"/>
+      <c r="C46" s="13" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>Exit multiple is the Gordon identity — not a peer pick or an average</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Selected exit EV/EBITDA (Gordon implied)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Selected exit is Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)×(1+g)/(WACC−g). Not Deckers and not a peer average.</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>No peer Ctrl+F. This cell = Gordon TV / FY30 EBITDA = (UFCF/EBITDA)×(1+g)/(WACC−g). WACC and g are sourced on those rows.</t>
+        </is>
+      </c>
+      <c r="E48" s="62">
+        <f>E33</f>
+        <v/>
+      </c>
+      <c r="M48" s="63" t="inlineStr">
         <is>
           <t>Comps: Exit Multiple Build</t>
         </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value = Terminal EBITDA × exit multiple</t>
-        </is>
-      </c>
-      <c r="E48" s="50">
-        <f>E31*E47</f>
-        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
+          <t>Terminal value = Terminal EBITDA × exit multiple</t>
+        </is>
+      </c>
+      <c r="E49" s="50">
+        <f>E31*E48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="E49" s="50">
-        <f>E48/(1+Scenarios!$G$9)^J23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="24" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="E50" s="37">
-        <f>E29+E49</f>
+      <c r="E50" s="50">
+        <f>E49/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="24" t="inlineStr">
         <is>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="E51" s="37">
+        <f>E29+E50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
           <t>Implied value per share (exit method)</t>
         </is>
       </c>
-      <c r="E51" s="68">
-        <f>(E50+E36+E37)/E39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="60" t="inlineStr">
+      <c r="E52" s="67">
+        <f>(E51+E37+E38)/E40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="60" t="inlineStr">
         <is>
           <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
         </is>
       </c>
-      <c r="B53" s="13" t="n"/>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="69" t="inlineStr"/>
-      <c r="B54" s="70" t="inlineStr">
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="68" t="inlineStr"/>
+      <c r="B55" s="69" t="inlineStr">
         <is>
           <t>Gordon Growth</t>
         </is>
       </c>
-      <c r="C54" s="70" t="inlineStr">
+      <c r="C55" s="69" t="inlineStr">
         <is>
           <t>Exit Multiple</t>
         </is>
       </c>
-      <c r="D54" s="70" t="inlineStr">
+      <c r="D55" s="69" t="inlineStr">
         <is>
           <t>Variance</t>
         </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="24" t="inlineStr">
-        <is>
-          <t>Terminal value ($)</t>
-        </is>
-      </c>
-      <c r="B55" s="61">
-        <f>E32</f>
-        <v/>
-      </c>
-      <c r="C55" s="61">
-        <f>E48</f>
-        <v/>
-      </c>
-      <c r="D55" s="61">
-        <f>B55-C55</f>
-        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="24" t="inlineStr">
         <is>
+          <t>Terminal value ($)</t>
+        </is>
+      </c>
+      <c r="B56" s="61">
+        <f>E32</f>
+        <v/>
+      </c>
+      <c r="C56" s="61">
+        <f>E49</f>
+        <v/>
+      </c>
+      <c r="D56" s="61">
+        <f>B56-C56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B56" s="71">
+      <c r="B57" s="70">
         <f>E33</f>
         <v/>
       </c>
-      <c r="C56" s="71">
-        <f>E47</f>
-        <v/>
-      </c>
-      <c r="D56" s="71">
-        <f>B56-C56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
+      <c r="C57" s="70">
+        <f>E48</f>
+        <v/>
+      </c>
+      <c r="D57" s="70">
+        <f>B57-C57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
         <is>
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B57" s="52" t="inlineStr"/>
-      <c r="C57" s="52" t="inlineStr"/>
-      <c r="D57" s="52">
-        <f>(B55-C55)/B55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="B58" s="52" t="inlineStr"/>
+      <c r="C58" s="52" t="inlineStr"/>
+      <c r="D58" s="52">
+        <f>(B56-C56)/B56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
         <is>
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B58" s="72">
-        <f>E40</f>
-        <v/>
-      </c>
-      <c r="C58" s="72">
-        <f>E51</f>
-        <v/>
-      </c>
-      <c r="D58" s="72">
-        <f>B58-C58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="73" t="inlineStr">
+      <c r="B59" s="71">
+        <f>E41</f>
+        <v/>
+      </c>
+      <c r="C59" s="71">
+        <f>E52</f>
+        <v/>
+      </c>
+      <c r="D59" s="71">
+        <f>B59-C59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="72" t="inlineStr">
         <is>
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B59" s="74">
-        <f>IF(ABS(D56)&lt;=1.5,"PASS","REVIEW")</f>
-        <v/>
-      </c>
-      <c r="C59" s="75">
-        <f>TEXT(D56,"0.0")&amp;"x spread vs 8.0x exit multiple"</f>
-        <v/>
-      </c>
-      <c r="D59" s="26" t="inlineStr">
-        <is>
-          <t>Gordon implied should bracket exit assumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="60" t="inlineStr">
+      <c r="B60" s="73">
+        <f>IF(ABS(D57)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C60" s="74">
+        <f>TEXT(D57,"0.0")&amp;"x spread vs Gordon-implied exit"</f>
+        <v/>
+      </c>
+      <c r="D60" s="26" t="inlineStr">
+        <is>
+          <t>Selected exit is the Gordon identity, so spread should be 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="60" t="inlineStr">
         <is>
           <t>SENSITIVITY — IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="n"/>
-      <c r="C62" s="13" t="n"/>
-      <c r="D62" s="13" t="n"/>
-      <c r="E62" s="13" t="n"/>
-      <c r="F62" s="13" t="n"/>
-      <c r="G62" s="13" t="n"/>
-      <c r="H62" s="13" t="n"/>
-    </row>
-    <row r="63" ht="28" customHeight="1">
-      <c r="A63" s="76" t="inlineStr">
+      <c r="B63" s="13" t="n"/>
+      <c r="C63" s="13" t="n"/>
+      <c r="D63" s="13" t="n"/>
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="13" t="n"/>
+      <c r="G63" s="13" t="n"/>
+      <c r="H63" s="13" t="n"/>
+    </row>
+    <row r="64" ht="28" customHeight="1">
+      <c r="A64" s="75" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by long-run real GDP and inflation benchmarks.</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C64" s="18" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
       </c>
-      <c r="F63" s="77" t="n">
+      <c r="F64" s="76" t="n">
         <v>0.015</v>
       </c>
-      <c r="G63" s="77" t="n">
+      <c r="G64" s="76" t="n">
         <v>0.02</v>
       </c>
-      <c r="H63" s="77" t="n">
+      <c r="H64" s="76" t="n">
         <v>0.0225</v>
       </c>
-      <c r="I63" s="77" t="n">
+      <c r="I64" s="76" t="n">
         <v>0.025</v>
       </c>
-      <c r="J63" s="77" t="n">
+      <c r="J64" s="76" t="n">
         <v>0.03</v>
       </c>
-      <c r="L63" s="63" t="inlineStr">
+      <c r="L64" s="63" t="inlineStr">
         <is>
           <t>Scenarios: terminal g</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="A64" s="77" t="n">
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="76" t="n">
         <v>0.095</v>
       </c>
-      <c r="C64" s="63" t="inlineStr">
+      <c r="C65" s="63" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F64" s="78">
-        <f>(NPV(0.095,F22:J22)+(J22*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="G64" s="78">
-        <f>(NPV(0.095,F22:J22)+(J22*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="H64" s="78">
-        <f>(NPV(0.095,F22:J22)+(J22*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="I64" s="78">
-        <f>(NPV(0.095,F22:J22)+(J22*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="J64" s="78">
-        <f>(NPV(0.095,F22:J22)+(J22*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="L64" s="63" t="inlineStr">
+      <c r="F65" s="77">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.015)/(0.095-0.015))/(1+0.095)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="G65" s="77">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.02)/(0.095-0.02))/(1+0.095)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="H65" s="77">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="I65" s="77">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.025)/(0.095-0.025))/(1+0.095)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="J65" s="77">
+        <f>(NPV(0.095,F22:J22)+(J22*(1+0.03)/(0.095-0.03))/(1+0.095)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="L65" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="77" t="n">
+    <row r="66" ht="28" customHeight="1">
+      <c r="A66" s="76" t="n">
         <v>0.1</v>
       </c>
-      <c r="D65" s="19" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F65" s="78">
-        <f>(NPV(0.1,F22:J22)+(J22*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="G65" s="78">
-        <f>(NPV(0.1,F22:J22)+(J22*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="H65" s="78">
-        <f>(NPV(0.1,F22:J22)+(J22*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="I65" s="78">
-        <f>(NPV(0.1,F22:J22)+(J22*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="J65" s="78">
-        <f>(NPV(0.1,F22:J22)+(J22*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="L65" s="63" t="inlineStr">
+      <c r="F66" s="77">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.015)/(0.1-0.015))/(1+0.1)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="G66" s="77">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.02)/(0.1-0.02))/(1+0.1)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="H66" s="77">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="I66" s="77">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.025)/(0.1-0.025))/(1+0.1)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="J66" s="77">
+        <f>(NPV(0.1,F22:J22)+(J22*(1+0.03)/(0.1-0.03))/(1+0.1)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="L66" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="A66" s="77" t="n">
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="76" t="n">
         <v>0.105</v>
       </c>
-      <c r="D66" s="19" t="inlineStr">
+      <c r="D67" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F66" s="78">
-        <f>(NPV(0.105,F22:J22)+(J22*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="G66" s="78">
-        <f>(NPV(0.105,F22:J22)+(J22*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="H66" s="79">
-        <f>(NPV(0.105,F22:J22)+(J22*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="I66" s="78">
-        <f>(NPV(0.105,F22:J22)+(J22*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="J66" s="78">
-        <f>(NPV(0.105,F22:J22)+(J22*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="L66" s="63" t="inlineStr">
+      <c r="F67" s="77">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.015)/(0.105-0.015))/(1+0.105)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="G67" s="77">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.02)/(0.105-0.02))/(1+0.105)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="H67" s="78">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="I67" s="77">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.025)/(0.105-0.025))/(1+0.105)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="J67" s="77">
+        <f>(NPV(0.105,F22:J22)+(J22*(1+0.03)/(0.105-0.03))/(1+0.105)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="L67" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="77" t="n">
+    <row r="68" ht="28" customHeight="1">
+      <c r="A68" s="76" t="n">
         <v>0.11</v>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F67" s="78">
-        <f>(NPV(0.11,F22:J22)+(J22*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="G67" s="78">
-        <f>(NPV(0.11,F22:J22)+(J22*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="H67" s="78">
-        <f>(NPV(0.11,F22:J22)+(J22*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="I67" s="78">
-        <f>(NPV(0.11,F22:J22)+(J22*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="J67" s="78">
-        <f>(NPV(0.11,F22:J22)+(J22*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="L67" s="63" t="inlineStr">
+      <c r="F68" s="77">
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.015)/(0.11-0.015))/(1+0.11)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="G68" s="77">
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.02)/(0.11-0.02))/(1+0.11)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="H68" s="77">
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="I68" s="77">
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.025)/(0.11-0.025))/(1+0.11)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="J68" s="77">
+        <f>(NPV(0.11,F22:J22)+(J22*(1+0.03)/(0.11-0.03))/(1+0.11)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="L68" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="A68" s="77" t="n">
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="76" t="n">
         <v>0.115</v>
       </c>
-      <c r="D68" s="19" t="inlineStr">
+      <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "4.23%" (2025 implied ERP). Sensitivity WACC axis brackets the 10.5% base.</t>
         </is>
       </c>
-      <c r="F68" s="78">
-        <f>(NPV(0.115,F22:J22)+(J22*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="G68" s="78">
-        <f>(NPV(0.115,F22:J22)+(J22*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="H68" s="78">
-        <f>(NPV(0.115,F22:J22)+(J22*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="I68" s="78">
-        <f>(NPV(0.115,F22:J22)+(J22*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="J68" s="78">
-        <f>(NPV(0.115,F22:J22)+(J22*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E36+E37)/E39</f>
-        <v/>
-      </c>
-      <c r="L68" s="63" t="inlineStr">
+      <c r="F69" s="77">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.015)/(0.115-0.015))/(1+0.115)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="G69" s="77">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.02)/(0.115-0.02))/(1+0.115)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="H69" s="77">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="I69" s="77">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.025)/(0.115-0.025))/(1+0.115)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="J69" s="77">
+        <f>(NPV(0.115,F22:J22)+(J22*(1+0.03)/(0.115-0.03))/(1+0.115)^5+E37+E38)/E40</f>
+        <v/>
+      </c>
+      <c r="L69" s="63" t="inlineStr">
         <is>
           <t>WACC tab</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="B69" s="17" t="inlineStr">
+    <row r="70" ht="28" customHeight="1">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>Red WACC and g grid values bracket base case ±100bps discount rate and ±75bps terminal growth for sensitivity.</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C70" s="18" t="inlineStr">
         <is>
           <t>Scenarios: WACC &amp; terminal g</t>
         </is>
       </c>
-      <c r="D69" s="19" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Scenarios tab → Ctrl+F "WACC" and "Terminal growth" rows (base-case inputs)</t>
         </is>
       </c>
-      <c r="L69" s="63" t="inlineStr">
+      <c r="L70" s="63" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
       </c>
-      <c r="M69" s="19" t="inlineStr">
+      <c r="M70" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "GDPC1" → bounds terminal-g sensitivity grid 1.5%–3.0%</t>
         </is>
@@ -4445,26 +4454,26 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId24"/>
-    <hyperlink ref="M47" location="'Comps'!A38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C63" r:id="rId25"/>
-    <hyperlink ref="L63" location="'Scenarios'!G10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId26"/>
-    <hyperlink ref="L64" location="'WACC'!E19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId23"/>
+    <hyperlink ref="C48" location="'DCF'!E33"/>
+    <hyperlink ref="M48" location="'Comps'!A38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId24"/>
+    <hyperlink ref="L64" location="'Scenarios'!G10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId25"/>
     <hyperlink ref="L65" location="'WACC'!E19"/>
     <hyperlink ref="L66" location="'WACC'!E19"/>
     <hyperlink ref="L67" location="'WACC'!E19"/>
     <hyperlink ref="L68" location="'WACC'!E19"/>
-    <hyperlink ref="C69" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId27"/>
+    <hyperlink ref="L69" location="'WACC'!E19"/>
+    <hyperlink ref="C70" location="'Scenarios'!G9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4655,23 +4664,23 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current EV / EBITDA</t>
         </is>
       </c>
-      <c r="E11" s="80">
+      <c r="E11" s="79">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="inlineStr">
+      <c r="A12" s="74" t="inlineStr">
         <is>
           <t xml:space="preserve">  memo: current P / E (FY2026E)</t>
         </is>
       </c>
-      <c r="E12" s="80">
+      <c r="E12" s="79">
         <f>E10/E7</f>
         <v/>
       </c>
@@ -4684,34 +4693,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>Peer / reference EV/EBITDA (forward / illustrative)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="81" t="inlineStr">
+      <c r="A16" s="80" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="81" t="inlineStr">
+      <c r="B16" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C16" s="81" t="inlineStr">
+      <c r="C16" s="80" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D16" s="81" t="inlineStr">
+      <c r="D16" s="80" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E16" s="82" t="inlineStr">
+      <c r="E16" s="81" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
@@ -4738,7 +4747,7 @@
           <t>Ctrl+F "19.9%" → FY25 OM (EBIT $2,210,615). Ctrl+F "496,228" → Depreciation and amortization. Do not search the words Income from operations (17 hits).</t>
         </is>
       </c>
-      <c r="E17" s="83">
+      <c r="E17" s="82">
         <f>(E10*E9-E8)/E5</f>
         <v/>
       </c>
@@ -4764,7 +4773,7 @@
           <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
         </is>
       </c>
-      <c r="E18" s="84" t="n">
+      <c r="E18" s="83" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4789,7 +4798,7 @@
           <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
         </is>
       </c>
-      <c r="E19" s="84" t="n">
+      <c r="E19" s="83" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4814,7 +4823,7 @@
           <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
         </is>
       </c>
-      <c r="E20" s="84" t="n">
+      <c r="E20" s="83" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4839,7 +4848,7 @@
           <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
         </is>
       </c>
-      <c r="E21" s="84" t="n">
+      <c r="E21" s="83" t="n">
         <v>9.300000000000001</v>
       </c>
     </row>
@@ -4864,7 +4873,7 @@
           <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
         </is>
       </c>
-      <c r="E22" s="84" t="n">
+      <c r="E22" s="83" t="n">
         <v>10.7</v>
       </c>
     </row>
@@ -4903,7 +4912,7 @@
           <t>Ctrl+F "£1.25bn valuation" and "sold a 21% stake". That proves the 2020 valuation (£m = 1,250), not EV/EBITDA.</t>
         </is>
       </c>
-      <c r="E26" s="85" t="n">
+      <c r="E26" s="84" t="n">
         <v>1250</v>
       </c>
     </row>
@@ -4928,12 +4937,12 @@
           <t>Ctrl+F "our EBITDA, which reached £53.3 million". That proves FY25 EBITDA £m. Do not take "62.3 percent" (gross margin).</t>
         </is>
       </c>
-      <c r="E27" s="86" t="n">
+      <c r="E27" s="85" t="n">
         <v>53.3</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="73" t="inlineStr">
+      <c r="A28" s="72" t="inlineStr">
         <is>
           <t>Gymshark implied EV/EBITDA (model math)</t>
         </is>
@@ -4953,7 +4962,7 @@
           <t>No Ctrl+F. Neither Guardian nor SGB prints EV/EBITDA. This cell is E26 / E27 (2020 valuation ÷ FY25 EBITDA).</t>
         </is>
       </c>
-      <c r="E28" s="87">
+      <c r="E28" s="86">
         <f>E26/E27</f>
         <v/>
       </c>
@@ -4986,7 +4995,7 @@
           <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
         </is>
       </c>
-      <c r="E31" s="83">
+      <c r="E31" s="82">
         <f>AVERAGE(E18,E19,E20,E21,E22)</f>
         <v/>
       </c>
@@ -4999,7 +5008,7 @@
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>~9.3x closest mature set. Still haircut ~1 turn to 8.0x for 2.25% terminal g.</t>
+          <t>~9.3x closest mature set. Comps check only — selected exit is Gordon implied, below this tape.</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
@@ -5009,10 +5018,10 @@
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Haircut to selected 8.0x.</t>
-        </is>
-      </c>
-      <c r="E32" s="83">
+          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Not the selected FY30 exit.</t>
+        </is>
+      </c>
+      <c r="E32" s="82">
         <f>AVERAGE(E19,E21,E22)</f>
         <v/>
       </c>
@@ -5038,13 +5047,13 @@
           <t>Math: (12.0+8.0+14.0+9.3+10.7+1,250/53.3)/6 ≈ 12.9x. Not the TV.</t>
         </is>
       </c>
-      <c r="E33" s="83">
+      <c r="E33" s="82">
         <f>AVERAGE(E18,E19,E20,E21,E22,E28)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="74" t="inlineStr">
         <is>
           <t>We do not average EV/EBITDA for terminal value. A 2.25% g year is not a growth-comp tape.</t>
         </is>
@@ -5069,13 +5078,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="73" t="inlineStr">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>Selected exit multiple (base case)</t>
         </is>
       </c>
-      <c r="E38" s="71">
-        <f>DCF!E47</f>
+      <c r="E38" s="70">
+        <f>DCF!E48</f>
         <v/>
       </c>
     </row>
@@ -5091,51 +5100,51 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="73" t="inlineStr">
-        <is>
-          <t>Rationale for 8.0x (not the average)</t>
+      <c r="A40" s="72" t="inlineStr">
+        <is>
+          <t>Rationale for selected exit (Gordon identity, not a peer pick)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="34" t="inlineStr">
         <is>
-          <t>•  8.0x equals Deckers (7.95x rounded) — closest mature premium analog on the tape</t>
+          <t>•  Selected exit = Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)×(1+g)/(WACC−g). Live formula, not a typed 8.0x</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="34" t="inlineStr">
         <is>
-          <t>•  ~1 turn above Gordon-implied ~7x — buffer vs perpetuity math on 2.25% terminal g</t>
+          <t>•  At base WACC 10.5% and g 2.25% that identity is ~6.0x — the stale “Gordon ~7x / pick Deckers 8.0x” overlay is gone</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="34" t="inlineStr">
         <is>
-          <t>•  Mid-point of the 6.5–9.5x football field — not the 10.8x public 5-name mean</t>
+          <t>•  Deckers 8.0x is a public print, not a derivation of our exit. It is only the football-field cap</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>•  Mature public mean (DECK / ADS / VFC) is ~9.3x; we haircut ~1 turn for 2.25% terminal g</t>
+          <t>•  Public 5-name mean 10.8x and mature mean 9.3x are current trading tapes, not a 2.25% g terminal year</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>•  Gymshark implied 23.5x is 2020 valuation / FY25 EBITDA — no page prints that multiple; averaging it (~12.9x) is not an FY30 exit</t>
+          <t>•  Gymshark implied 23.5x is 2020 valuation / FY25 EBITDA — no page prints that multiple; averaging it is not an FY30 exit</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>•  Current LULU ~3.5x on FY2025A is a trough — 8.0x assumes partial recovery, not a re-rate to ONON 14x</t>
+          <t>•  Current LULU ~3.5–5x is a trough. Gordon 6.0x is a partial recovery, not a re-rate to ONON 14x</t>
         </is>
       </c>
     </row>
@@ -5147,42 +5156,42 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="81" t="inlineStr">
+      <c r="A49" s="80" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B49" s="81" t="inlineStr">
+      <c r="B49" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C49" s="81" t="inlineStr">
+      <c r="C49" s="80" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D49" s="81" t="inlineStr">
+      <c r="D49" s="80" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E49" s="82" t="inlineStr">
+      <c r="E49" s="81" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F49" s="82" t="inlineStr">
+      <c r="F49" s="81" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G49" s="82" t="inlineStr">
+      <c r="G49" s="81" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H49" s="82" t="inlineStr">
+      <c r="H49" s="81" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
@@ -5196,63 +5205,63 @@
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>Lo: 6.5x on FY2030E terminal EBITDA; bear exit below Gordon-implied ~7x; brackets DCF downside.
-Hi: 9.5x on FY2030E terminal EBITDA; bull exit above 8.0x DCF base; still below public mean ~10.8x.</t>
-        </is>
-      </c>
-      <c r="C50" s="88" t="inlineStr">
+          <t>Lo: 5.0x on FY2030E EBITDA ≈ LULU current trough print. Floor of the range, not the selected exit.
+Hi: 8.0x = Deckers print as the high end of the range only. Selected exit is Gordon implied, not this cap.</t>
+        </is>
+      </c>
+      <c r="C50" s="87" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
-Hi: StockAnalysis: LULU valuation</t>
+Hi: StockAnalysis: DECK EV/EBITDA</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
         <is>
-          <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; bear terminal exit assumption 6.5x
-Hi: Ctrl+F "EV / EBITDA" → bull terminal exit assumption 9.5x on FY2030E EBITDA</t>
-        </is>
-      </c>
-      <c r="E50" s="84" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F50" s="84" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G50" s="89">
+          <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; football-field floor 5.0x
+Hi: Ctrl+F "EV / EBITDA" → 7.95. Football-field cap 8.0x (Deckers). Not the selected exit.</t>
+        </is>
+      </c>
+      <c r="E50" s="83" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="83" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" s="88">
         <f>(E6*E50+E8)/E9</f>
         <v/>
       </c>
-      <c r="H50" s="89">
+      <c r="H50" s="88">
         <f>(E6*F50+E8)/E9</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="73" t="inlineStr">
-        <is>
-          <t>DCF exit method (8.0x on FY2030E EBITDA)</t>
+      <c r="A51" s="72" t="inlineStr">
+        <is>
+          <t>DCF exit method (Gordon-implied on FY2030E EBITDA)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>8.0x equals Deckers; ~1 turn above Gordon ~7x. Public mean 10.8x and Gymshark implied 23.5x are not FY30 exit.</t>
+          <t>Selected exit is Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)×(1+g)/(WACC−g). Not Deckers and not a peer average.</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>StockAnalysis: LULU EV/EBITDA</t>
+          <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
       </c>
       <c r="D51" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → LULU ~4.99x on page; model terminal exit 8.0x equals Deckers, not the public mean</t>
-        </is>
-      </c>
-      <c r="E51" s="87">
-        <f>DCF!E47</f>
-        <v/>
-      </c>
-      <c r="G51" s="90">
+          <t>No peer Ctrl+F. This cell = Gordon TV / FY30 EBITDA = (UFCF/EBITDA)×(1+g)/(WACC−g). WACC and g are sourced on those rows.</t>
+        </is>
+      </c>
+      <c r="E51" s="86">
+        <f>DCF!E48</f>
+        <v/>
+      </c>
+      <c r="G51" s="89">
         <f>(E6*E51+E8)/E9</f>
         <v/>
       </c>
@@ -5269,7 +5278,7 @@
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C52" s="88" t="inlineStr">
+      <c r="C52" s="87" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
@@ -5281,17 +5290,17 @@
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E52" s="84" t="n">
+      <c r="E52" s="83" t="n">
         <v>10</v>
       </c>
-      <c r="F52" s="84" t="n">
+      <c r="F52" s="83" t="n">
         <v>18</v>
       </c>
-      <c r="G52" s="89">
+      <c r="G52" s="88">
         <f>E7*E52</f>
         <v/>
       </c>
-      <c r="H52" s="89">
+      <c r="H52" s="88">
         <f>E7*F52</f>
         <v/>
       </c>
@@ -5302,27 +5311,27 @@
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E53" s="91" t="inlineStr">
+      <c r="E53" s="90" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="91" t="inlineStr">
+      <c r="F53" s="90" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="89">
+      <c r="G53" s="88">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H53" s="89">
+      <c r="H53" s="88">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="92" t="inlineStr">
+      <c r="A55" s="91" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
@@ -5337,14 +5346,14 @@
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E55" s="93" t="n">
+      <c r="E55" s="92" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="26" t="inlineStr">
         <is>
-          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Gymshark 23.5x is implied (2020 £1.25bn / FY25 £53.3m) — no source prints EV/EBITDA. Selected TV is 8.0x, not the average.</t>
+          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Selected TV is Gordon implied (TV/EBITDA), not Deckers and not an average. Gymshark 23.5x is implied only.</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5382,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId20"/>
     <hyperlink ref="C28" location="'Comps'!E26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId21"/>
-    <hyperlink ref="C51" location="'DCF'!E47"/>
+    <hyperlink ref="C51" location="'DCF'!E48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId24"/>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="168" formatCode="0.0x"/>
     <numFmt numFmtId="169" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -293,6 +293,12 @@
     </font>
     <font>
       <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
       <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="11"/>
@@ -580,15 +586,15 @@
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -604,7 +610,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4880,182 +4886,186 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>GYMSHARK BUILD — implied multiple (no source prints EV/EBITDA)</t>
+          <t>ALO YOGA BUILD — no source prints EV/EBITDA (Firecrawl: Reuters + Forbes)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="26" t="inlineStr">
         <is>
-          <t>Column E on the next two rows is £m, not a multiple. Implied EV/EBITDA is the black formula below.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1">
+          <t>Column E on the next two rows is $bn, not EV/EBITDA. The black formula is implied EV/Sales on an unclosed ask.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Gymshark 2020 GA valuation (£m)</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>£1.25bn = 1,250 in £m. 2020 GA headline valuation (Guardian). Not a published EV or EV/EBITDA.</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>Guardian: Gymshark 2020 GA £1.25bn</t>
+          <t>Alo / Color Image 2023 Moelis ask ($bn)</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Reuters: about $10 billion Moelis ask for Color Image. 2026 follow-up: no deal announced. Ask, not a print.
+Also: Reuters June 2026: no deal was announced on the 2023 process. The $10bn is still an ask.</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Reuters: Alo parent $10bn Moelis ask
+Also: Reuters: Alo 2023 process — no deal</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "£1.25bn valuation" and "sold a 21% stake". That proves the 2020 valuation (£m = 1,250), not EV/EBITDA.</t>
+          <t>Ctrl+F "at about $10 billion" and "hired investment bank Moelis". That is the 2023 ask, not a closed EV.
+Also: Ctrl+F "roughly $10 billion" and "No deal was announced". Still an ask.</t>
         </is>
       </c>
       <c r="E26" s="84" t="n">
-        <v>1250</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Gymshark FY25 EBITDA (£m)</t>
+          <t>Color Image parent sales, Forbes est. ($bn)</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>FY25 EBITDA is £53.3m (SGB). 62.3% is gross margin. This cell is EBITDA £m, not a multiple.</t>
+          <t>Forbes estimates Color Image parent sales nearly $2 billion. Mixed Alo + Bella+Canvas. Not Alo-only, not audited.</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>SGB: Gymshark FY25 EBITDA £53.3m</t>
+          <t>Forbes: Color Image nearly $2bn sales</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "our EBITDA, which reached £53.3 million". That proves FY25 EBITDA £m. Do not take "62.3 percent" (gross margin).</t>
-        </is>
-      </c>
-      <c r="E27" s="85" t="n">
-        <v>53.3</v>
+          <t>Ctrl+F "nearly $2 billion". Forbes estimate for Color Image parent (Alo + Bella+Canvas), not Alo-only EBITDA.</t>
+        </is>
+      </c>
+      <c r="E27" s="84" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="72" t="inlineStr">
         <is>
-          <t>Gymshark implied EV/EBITDA (model math)</t>
+          <t>Alo implied EV/Sales (ask / parent sales)</t>
         </is>
       </c>
       <c r="B28" s="26" t="inlineStr">
         <is>
-          <t>No page prints Gymshark EV/EBITDA. Black formula = 2020 valuation / FY25 EBITDA. Cross-year; not the TV.</t>
+          <t>5.0x = 10 / 2. Implied EV/Sales on an unclosed ask and parent sales. Not EV/EBITDA. Not the TV.</t>
         </is>
       </c>
       <c r="C28" s="63" t="inlineStr">
         <is>
-          <t>Comps: Gymshark valuation / EBITDA</t>
+          <t>Comps: Alo ask / parent sales</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>No Ctrl+F. Neither Guardian nor SGB prints EV/EBITDA. This cell is E26 / E27 (2020 valuation ÷ FY25 EBITDA).</t>
-        </is>
-      </c>
-      <c r="E28" s="86">
+          <t>No Ctrl+F for EV/EBITDA — Firecrawl found none on Reuters or Forbes. This cell is E26 / E27 (ask ÷ parent sales). Not the TV.</t>
+        </is>
+      </c>
+      <c r="E28" s="85">
         <f>E26/E27</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Alo EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>No page prints Alo or Color Image EBITDA. PitchBook Alo column is blank. Cannot imply EV/EBITDA.</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>None — no EBITDA source</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>No Ctrl+F. Reuters, Forbes, and PitchBook do not print Alo EV/EBITDA.</t>
+        </is>
+      </c>
+      <c r="E29" s="86" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Averages (live Excel AVERAGE — shown so TV is not a blended print)</t>
         </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Public 5-name mean (NKE / DECK / ONON / ADS / VFC)</t>
-        </is>
-      </c>
-      <c r="B31" s="26" t="inlineStr">
-        <is>
-          <t>10.8x simple mean. Too high for a 2.25% g / 15.5% OM terminal year — not the TV.</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Derived: Excel AVERAGE of the five public prints</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
-        <is>
-          <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
-        </is>
-      </c>
-      <c r="E31" s="82">
-        <f>AVERAGE(E18,E19,E20,E21,E22)</f>
-        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>Mature public mean (DECK / ADS / VFC)</t>
+          <t>Public 5-name mean (NKE / DECK / ONON / ADS / VFC)</t>
         </is>
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>~9.3x closest mature set. Comps check only — selected exit is Gordon implied, below this tape.</t>
+          <t>10.8x simple mean. Too high for a 2.25% g / 15.5% OM terminal year — not the TV.</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
+          <t>Derived: Excel AVERAGE of the five public prints</t>
         </is>
       </c>
       <c r="D32" s="26" t="inlineStr">
         <is>
-          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Not the selected FY30 exit.</t>
+          <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
         </is>
       </c>
       <c r="E32" s="82">
-        <f>AVERAGE(E19,E21,E22)</f>
+        <f>AVERAGE(E18,E19,E20,E21,E22)</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>Mean incl. Gymshark (do not use for TV)</t>
+          <t>Mature public mean (DECK / ADS / VFC)</t>
         </is>
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>~12.9x. Gymshark implied 23.5x is model math (2020 val / FY25 EBITDA); averaging it overstates FY30 exit.</t>
+          <t>~9.3x closest mature set. Comps check only — selected exit is Gordon implied, below this tape.</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Derived: Excel AVERAGE of five publics + Gymshark</t>
+          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
         </is>
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t>Math: (12.0+8.0+14.0+9.3+10.7+1,250/53.3)/6 ≈ 12.9x. Not the TV.</t>
+          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Not the selected FY30 exit.</t>
         </is>
       </c>
       <c r="E33" s="82">
-        <f>AVERAGE(E18,E19,E20,E21,E22,E28)</f>
+        <f>AVERAGE(E19,E21,E22)</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="74" t="inlineStr">
         <is>
-          <t>We do not average EV/EBITDA for terminal value. A 2.25% g year is not a growth-comp tape.</t>
+          <t>We do not average peers for terminal value, and we do not use Alo 5.0x EV/Sales as EV/EBITDA.</t>
         </is>
       </c>
     </row>
@@ -5137,7 +5147,7 @@
     <row r="45">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>•  Gymshark implied 23.5x is 2020 valuation / FY25 EBITDA — no page prints that multiple; averaging it is not an FY30 exit</t>
+          <t>•  Alo has no EV/EBITDA print. Implied 5.0x is EV/Sales (unclosed $10bn ask / ~$2bn parent sales) — not the FY30 exit</t>
         </is>
       </c>
     </row>
@@ -5257,7 +5267,7 @@
           <t>No peer Ctrl+F. This cell = Gordon TV / FY30 EBITDA = (UFCF/EBITDA)×(1+g)/(WACC−g). WACC and g are sourced on those rows.</t>
         </is>
       </c>
-      <c r="E51" s="86">
+      <c r="E51" s="85">
         <f>DCF!E48</f>
         <v/>
       </c>
@@ -5353,7 +5363,7 @@
     <row r="56">
       <c r="A56" s="26" t="inlineStr">
         <is>
-          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Selected TV is Gordon implied (TV/EBITDA), not Deckers and not an average. Gymshark 23.5x is implied only.</t>
+          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Alo is a private reference (implied 5.0x EV/Sales; EV/EBITDA n.a.). Selected TV is Gordon implied, not Alo.</t>
         </is>
       </c>
     </row>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -363,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -580,23 +580,29 @@
     <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4469,7 +4475,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId23"/>
     <hyperlink ref="C48" location="'DCF'!E33"/>
-    <hyperlink ref="M48" location="'Comps'!A38"/>
+    <hyperlink ref="M48" location="'Comps'!A45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C64" r:id="rId24"/>
     <hyperlink ref="L64" location="'Scenarios'!G10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C65" r:id="rId25"/>
@@ -4491,7 +4497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -4502,6 +4508,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -4706,131 +4714,118 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="80" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>PITCHBOOK PUBCOMPS — daily EV / TTM EBITDA as of 04-Sep-2026 ($000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>EV/EBITDA is a black formula (I/J). UAA is shown but excluded from averages (negative TTM EBITDA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="80" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="B16" s="80" t="inlineStr">
+      <c r="B18" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C16" s="80" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="D16" s="80" t="inlineStr">
-        <is>
-          <t>Ctrl+F (prove number)</t>
-        </is>
-      </c>
-      <c r="E16" s="81" t="inlineStr">
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D18" s="80" t="inlineStr">
+        <is>
+          <t>Ctrl+F / proof</t>
+        </is>
+      </c>
+      <c r="E18" s="81" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>lululemon (LULU) — current</t>
-        </is>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>Distressed trough multiple on FY2025A EBITDA</t>
-        </is>
-      </c>
-      <c r="C17" s="63" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "19.9%" → FY25 OM (EBIT $2,210,615). Ctrl+F "496,228" → Depreciation and amortization. Do not search the words Income from operations (17 hits).</t>
-        </is>
-      </c>
-      <c r="E17" s="82">
-        <f>(E10*E9-E8)/E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>Nike (NKE)</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Nike EV/EBITDA 12.0x equals StockAnalysis 11.97x, rounded; mature athletic benchmark.</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: NKE EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>Ctrl+F "EV / EBITDA" → 11.97. Model uses 12.0x.</t>
-        </is>
-      </c>
-      <c r="E18" s="83" t="n">
-        <v>12</v>
+      <c r="I18" s="81" t="inlineStr">
+        <is>
+          <t>EV ($000)</t>
+        </is>
+      </c>
+      <c r="J18" s="81" t="inlineStr">
+        <is>
+          <t>EBITDA ($000)</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>Deckers (DECK)</t>
+          <t>lululemon (LULU)</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Deckers EV/EBITDA 8.0x equals StockAnalysis 7.95x, rounded; closest premium-footwear peer.</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: DECK EV/EBITDA</t>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C19" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
       </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → 7.95. Model uses 8.0x.</t>
-        </is>
-      </c>
-      <c r="E19" s="83" t="n">
-        <v>8</v>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E19" s="83">
+        <f>IF(J19&lt;=0,"n.m.",I19/J19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="84" t="n">
+        <v>11890440</v>
+      </c>
+      <c r="J19" s="84" t="n">
+        <v>2548084</v>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>On Holding (ONON)</t>
+          <t>Under Armour (UAA)</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>On Holding EV/EBITDA 14.0x equals StockAnalysis 14.03x, rounded; high-growth athletic peer.</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: ONON EV/EBITDA</t>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C20" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
       </c>
       <c r="D20" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → 14.03. Model uses 14.0x.</t>
-        </is>
-      </c>
-      <c r="E20" s="83" t="n">
-        <v>14</v>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E20" s="83">
+        <f>IF(J20&lt;=0,"n.m.",I20/J20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="84" t="n">
+        <v>3208397</v>
+      </c>
+      <c r="J20" s="84" t="n">
+        <v>-23230</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -4841,529 +4836,767 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>adidas (ADDYY) EV/EBITDA 9.3x equals StockAnalysis 9.31x; global incumbent.</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: adidas (ADR)</t>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C21" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → 9.31. Model uses 9.3x.</t>
-        </is>
-      </c>
-      <c r="E21" s="83" t="n">
-        <v>9.300000000000001</v>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E21" s="83">
+        <f>IF(J21&lt;=0,"n.m.",I21/J21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="84" t="n">
+        <v>35661944</v>
+      </c>
+      <c r="J21" s="84" t="n">
+        <v>3857684</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>V.F. Corp (VFC)</t>
+          <t>Nike (NKE)</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>VFC EV/EBITDA 10.7x equals StockAnalysis 10.71x; challenged multi-brand apparel peer.</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>StockAnalysis: VFC EV/EBITDA</t>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C22" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>Ctrl+F "EV / EBITDA" → 10.71. Model uses 10.7x.</t>
-        </is>
-      </c>
-      <c r="E22" s="83" t="n">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E22" s="83">
+        <f>IF(J22&lt;=0,"n.m.",I22/J22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="84" t="n">
+        <v>58972350</v>
+      </c>
+      <c r="J22" s="84" t="n">
+        <v>4647000</v>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Deckers (DECK)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C23" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E23" s="83">
+        <f>IF(J23&lt;=0,"n.m.",I23/J23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="84" t="n">
+        <v>10555510</v>
+      </c>
+      <c r="J23" s="84" t="n">
+        <v>1329439</v>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Williams-Sonoma (WSM)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C24" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E24" s="83">
+        <f>IF(J24&lt;=0,"n.m.",I24/J24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="84" t="n">
+        <v>27284350</v>
+      </c>
+      <c r="J24" s="84" t="n">
+        <v>1768400</v>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Crocs (CROX)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C25" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E25" s="83">
+        <f>IF(J25&lt;=0,"n.m.",I25/J25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="84" t="n">
+        <v>7153911</v>
+      </c>
+      <c r="J25" s="84" t="n">
+        <v>922278</v>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Movado (MOV)</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C26" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E26" s="83">
+        <f>IF(J26&lt;=0,"n.m.",I26/J26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="84" t="n">
+        <v>616045</v>
+      </c>
+      <c r="J26" s="84" t="n">
+        <v>62010</v>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Levi Strauss (LEVI)</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C27" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E27" s="83">
+        <f>IF(J27&lt;=0,"n.m.",I27/J27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="84" t="n">
+        <v>9422753</v>
+      </c>
+      <c r="J27" s="84" t="n">
+        <v>976700</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>La-Z-Boy (LZB)</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C28" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D28" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E28" s="83">
+        <f>IF(J28&lt;=0,"n.m.",I28/J28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="84" t="n">
+        <v>1598873</v>
+      </c>
+      <c r="J28" s="84" t="n">
+        <v>235723</v>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Kontoor (KTB)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV / TTM EBITDA. UAA excluded from the mean (negative EBITDA).</t>
+        </is>
+      </c>
+      <c r="C29" s="82" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>No public HTML. PitchBook Comps Set 04-Sep-2026. Prove daily EV and TTM EBITDA on that screen; E = I/J.</t>
+        </is>
+      </c>
+      <c r="E29" s="83">
+        <f>IF(J29&lt;=0,"n.m.",I29/J29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="84" t="n">
+        <v>5236269</v>
+      </c>
+      <c r="J29" s="84" t="n">
+        <v>407521</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>ALO YOGA BUILD — no source prints EV/EBITDA (Firecrawl: Reuters + Forbes)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Column E on the next two rows is $bn, not EV/EBITDA. The black formula is implied EV/Sales on an unclosed ask.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Alo / Color Image 2023 Moelis ask ($bn)</t>
         </is>
       </c>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>Reuters: about $10 billion Moelis ask for Color Image. 2026 follow-up: no deal announced. Ask, not a print.
 Also: Reuters June 2026: no deal was announced on the 2023 process. The $10bn is still an ask.</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>Reuters: Alo parent $10bn Moelis ask
 Also: Reuters: Alo 2023 process — no deal</t>
         </is>
       </c>
-      <c r="D26" s="19" t="inlineStr">
+      <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "at about $10 billion" and "hired investment bank Moelis". That is the 2023 ask, not a closed EV.
 Also: Ctrl+F "roughly $10 billion" and "No deal was announced". Still an ask.</t>
         </is>
       </c>
-      <c r="E26" s="84" t="n">
+      <c r="E33" s="85" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Color Image parent sales, Forbes est. ($bn)</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Forbes estimates Color Image parent sales nearly $2 billion. Mixed Alo + Bella+Canvas. Not Alo-only, not audited.</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C34" s="18" t="inlineStr">
         <is>
           <t>Forbes: Color Image nearly $2bn sales</t>
         </is>
       </c>
-      <c r="D27" s="19" t="inlineStr">
+      <c r="D34" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "nearly $2 billion". Forbes estimate for Color Image parent (Alo + Bella+Canvas), not Alo-only EBITDA.</t>
         </is>
       </c>
-      <c r="E27" s="84" t="n">
+      <c r="E34" s="85" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="72" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="72" t="inlineStr">
         <is>
           <t>Alo implied EV/Sales (ask / parent sales)</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>5.0x = 10 / 2. Implied EV/Sales on an unclosed ask and parent sales. Not EV/EBITDA. Not the TV.</t>
         </is>
       </c>
-      <c r="C28" s="63" t="inlineStr">
+      <c r="C35" s="63" t="inlineStr">
         <is>
           <t>Comps: Alo ask / parent sales</t>
         </is>
       </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>No Ctrl+F for EV/EBITDA — Firecrawl found none on Reuters or Forbes. This cell is E26 / E27 (ask ÷ parent sales). Not the TV.</t>
-        </is>
-      </c>
-      <c r="E28" s="85">
-        <f>E26/E27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>No Ctrl+F for EV/EBITDA — Firecrawl found none on Reuters or Forbes. This cell is E33 / E34 (ask ÷ parent sales). Not the TV.</t>
+        </is>
+      </c>
+      <c r="E35" s="86">
+        <f>E33/E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Alo EV/EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>No page prints Alo or Color Image EBITDA. PitchBook Alo column is blank. Cannot imply EV/EBITDA.</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>None — no EBITDA source</t>
         </is>
       </c>
-      <c r="D29" s="19" t="inlineStr">
+      <c r="D36" s="19" t="inlineStr">
         <is>
           <t>No Ctrl+F. Reuters, Forbes, and PitchBook do not print Alo EV/EBITDA.</t>
         </is>
       </c>
-      <c r="E29" s="86" t="inlineStr">
+      <c r="E36" s="87" t="inlineStr">
         <is>
           <t>n.a.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Averages (live Excel AVERAGE — shown so TV is not a blended print)</t>
         </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>Public 5-name mean (NKE / DECK / ONON / ADS / VFC)</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>10.8x simple mean. Too high for a 2.25% g / 15.5% OM terminal year — not the TV.</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Derived: Excel AVERAGE of the five public prints</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>Math: (12.0+8.0+14.0+9.3+10.7)/5 = 10.8x. Do not use as FY30 exit.</t>
-        </is>
-      </c>
-      <c r="E32" s="82">
-        <f>AVERAGE(E18,E19,E20,E21,E22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Mature public mean (DECK / ADS / VFC)</t>
-        </is>
-      </c>
-      <c r="B33" s="26" t="inlineStr">
-        <is>
-          <t>~9.3x closest mature set. Comps check only — selected exit is Gordon implied, below this tape.</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>Derived: Excel AVERAGE of Deckers, adidas, VFC</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="inlineStr">
-        <is>
-          <t>Math: (8.0+9.3+10.7)/3 = 9.3x. Not the selected FY30 exit.</t>
-        </is>
-      </c>
-      <c r="E33" s="82">
-        <f>AVERAGE(E19,E21,E22)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="74" t="inlineStr">
-        <is>
-          <t>We do not average peers for terminal value, and we do not use Alo 5.0x EV/Sales as EV/EBITDA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>Terminal multiple selection (DCF exit method)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Gordon Growth implied exit EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="E37" s="62">
-        <f>DCF!E33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="72" t="inlineStr">
-        <is>
-          <t>Selected exit multiple (base case)</t>
-        </is>
-      </c>
-      <c r="E38" s="70">
-        <f>DCF!E48</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
+          <t>Core athletic / apparel mean (LULU / NKE / ADS / DECK / CROX / LEVI / KTB)</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>PitchBook core set, UAA out. Current tape — not a 2.25% g FY30 exit.</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of the seven core prints</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Each E cell is I/J from the PitchBook extract. Do not use as FY30 exit.</t>
+        </is>
+      </c>
+      <c r="E39" s="83">
+        <f>AVERAGE(E19,E22,E21,E23,E25,E27,E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>All positive-EBITDA mean (ex-UAA; includes WSM / MOV / LZB)</t>
+        </is>
+      </c>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>Wider PitchBook tape. WSM/MOV/LZB are adjacent retail, not athletic. Not the TV.</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Derived: Excel AVERAGE of every positive-EBITDA row</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>UAA omitted because TTM EBITDA is negative. Not the selected FY30 exit.</t>
+        </is>
+      </c>
+      <c r="E40" s="83">
+        <f>AVERAGE(E19,E21,E22,E23,E24,E25,E26,E27,E28,E29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="74" t="inlineStr">
+        <is>
+          <t>We do not average peers for terminal value, and we do not use Alo 5.0x EV/Sales as EV/EBITDA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Terminal multiple selection (DCF exit method)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Gordon Growth implied exit EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="E44" s="62">
+        <f>DCF!E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="72" t="inlineStr">
+        <is>
+          <t>Selected exit multiple (base case)</t>
+        </is>
+      </c>
+      <c r="E45" s="70">
+        <f>DCF!E48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
           <t>Spread (selected − Gordon implied)</t>
         </is>
       </c>
-      <c r="E39" s="62">
-        <f>E38-E37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="72" t="inlineStr">
+      <c r="E46" s="62">
+        <f>E45-E44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="72" t="inlineStr">
         <is>
           <t>Rationale for selected exit (Gordon identity, not a peer pick)</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="34" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>•  Selected exit = Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)×(1+g)/(WACC−g). Live formula, not a typed 8.0x</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="34" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>•  At base WACC 10.5% and g 2.25% that identity is ~6.0x — the stale “Gordon ~7x / pick Deckers 8.0x” overlay is gone</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>•  Deckers 8.0x is a public print, not a derivation of our exit. It is only the football-field cap</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>•  Public 5-name mean 10.8x and mature mean 9.3x are current trading tapes, not a 2.25% g terminal year</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>•  PitchBook pubcomps (04-Sep-2026) are the current tape: each multiple is daily EV / TTM EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>•  That tape is a check, not the exit. A 2.25% g / 15.5% OM year is not today’s NKE/WSM multiple</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>•  Alo has no EV/EBITDA print. Implied 5.0x is EV/Sales (unclosed $10bn ask / ~$2bn parent sales) — not the FY30 exit</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="34" t="inlineStr">
-        <is>
-          <t>•  Current LULU ~3.5–5x is a trough. Gordon 6.0x is a partial recovery, not a re-rate to ONON 14x</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
+          <t>•  PitchBook LULU is ~4.7x TTM. Gordon 6.0x is a partial recovery, not a re-rate to WSM ~15x</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>Methodology / multiple ranges (FY2030E terminal EBITDA — football field)</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="80" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="80" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B49" s="80" t="inlineStr">
+      <c r="B56" s="80" t="inlineStr">
         <is>
           <t>Justification</t>
         </is>
       </c>
-      <c r="C49" s="80" t="inlineStr">
+      <c r="C56" s="80" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="D49" s="80" t="inlineStr">
+      <c r="D56" s="80" t="inlineStr">
         <is>
           <t>Ctrl+F</t>
         </is>
       </c>
-      <c r="E49" s="81" t="inlineStr">
+      <c r="E56" s="81" t="inlineStr">
         <is>
           <t>Low mult.</t>
         </is>
       </c>
-      <c r="F49" s="81" t="inlineStr">
+      <c r="F56" s="81" t="inlineStr">
         <is>
           <t>High mult.</t>
         </is>
       </c>
-      <c r="G49" s="81" t="inlineStr">
+      <c r="G56" s="81" t="inlineStr">
         <is>
           <t>Implied px (low)</t>
         </is>
       </c>
-      <c r="H49" s="81" t="inlineStr">
+      <c r="H56" s="81" t="inlineStr">
         <is>
           <t>Implied px (high)</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="B50" s="19" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Lo: 5.0x on FY2030E EBITDA ≈ LULU current trough print. Floor of the range, not the selected exit.
 Hi: 8.0x = Deckers print as the high end of the range only. Selected exit is Gordon implied, not this cap.</t>
         </is>
       </c>
-      <c r="C50" s="87" t="inlineStr">
+      <c r="C57" s="88" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA
 Hi: StockAnalysis: DECK EV/EBITDA</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "EV / EBITDA" → LULU trough ~5x; football-field floor 5.0x
 Hi: Ctrl+F "EV / EBITDA" → 7.95. Football-field cap 8.0x (Deckers). Not the selected exit.</t>
         </is>
       </c>
-      <c r="E50" s="83" t="n">
+      <c r="E57" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="F50" s="83" t="n">
+      <c r="F57" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="G50" s="88">
-        <f>(E6*E50+E8)/E9</f>
-        <v/>
-      </c>
-      <c r="H50" s="88">
-        <f>(E6*F50+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="72" t="inlineStr">
+      <c r="G57" s="90">
+        <f>(E6*E57+E8)/E9</f>
+        <v/>
+      </c>
+      <c r="H57" s="90">
+        <f>(E6*F57+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="72" t="inlineStr">
         <is>
           <t>DCF exit method (Gordon-implied on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Selected exit is Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)×(1+g)/(WACC−g). Not Deckers and not a peer average.</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C58" s="18" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
       </c>
-      <c r="D51" s="19" t="inlineStr">
+      <c r="D58" s="19" t="inlineStr">
         <is>
           <t>No peer Ctrl+F. This cell = Gordon TV / FY30 EBITDA = (UFCF/EBITDA)×(1+g)/(WACC−g). WACC and g are sourced on those rows.</t>
         </is>
       </c>
-      <c r="E51" s="85">
+      <c r="E58" s="86">
         <f>DCF!E48</f>
         <v/>
       </c>
-      <c r="G51" s="89">
-        <f>(E6*E51+E8)/E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="42" customHeight="1">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="G58" s="91">
+        <f>(E6*E58+E8)/E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="42" customHeight="1">
+      <c r="A59" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
         </is>
       </c>
-      <c r="B52" s="19" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>Lo: 10x P/E low on FY2026E EPS; trough earnings multiple after guidance reset and sentiment de-rating.
 Hi: 18x P/E high on FY2026E EPS; modest recovery case still below historical premium LULU multiples.</t>
         </is>
       </c>
-      <c r="C52" s="87" t="inlineStr">
+      <c r="C59" s="88" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E
 Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
       </c>
-      <c r="D52" s="19" t="inlineStr">
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Lo: Ctrl+F "Forward PE" → LULU ~12.3x; low-case multiple assumption 10.0x
 Hi: Ctrl+F "Forward PE" → NKE peer benchmark; high-case assumption 18.0x</t>
         </is>
       </c>
-      <c r="E52" s="83" t="n">
+      <c r="E59" s="89" t="n">
         <v>10</v>
       </c>
-      <c r="F52" s="83" t="n">
+      <c r="F59" s="89" t="n">
         <v>18</v>
       </c>
-      <c r="G52" s="88">
-        <f>E7*E52</f>
-        <v/>
-      </c>
-      <c r="H52" s="88">
-        <f>E7*F52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="G59" s="90">
+        <f>E7*E59</f>
+        <v/>
+      </c>
+      <c r="H59" s="90">
+        <f>E7*F59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
         <is>
           <t>DCF (bear – bull)</t>
         </is>
       </c>
-      <c r="E53" s="90" t="inlineStr">
+      <c r="E60" s="92" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="90" t="inlineStr">
+      <c r="F60" s="92" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G53" s="88">
+      <c r="G60" s="90">
         <f>Scenarios!F65</f>
         <v/>
       </c>
-      <c r="H53" s="88">
+      <c r="H60" s="90">
         <f>Scenarios!H65</f>
         <v/>
       </c>
     </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="91" t="inlineStr">
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="93" t="inlineStr">
         <is>
           <t>Current price</t>
         </is>
       </c>
-      <c r="C55" s="63" t="inlineStr">
+      <c r="C62" s="63" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="D55" s="19" t="inlineStr">
+      <c r="D62" s="19" t="inlineStr">
         <is>
           <t>Ctrl+F "LULU" → Last Sale or Previous Close on NASDAQ quote page</t>
         </is>
       </c>
-      <c r="E55" s="92" t="n">
+      <c r="E62" s="94" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="26" t="inlineStr">
-        <is>
-          <t>Note: public set is NKE, DECK, ONON, adidas, VFC (red). Alo is a private reference (implied 5.0x EV/Sales; EV/EBITDA n.a.). Selected TV is Gordon implied, not Alo.</t>
+    <row r="63">
+      <c r="A63" s="26" t="inlineStr">
+        <is>
+          <t>Note: pubcomps are PitchBook 04-Sep-2026 (EV/EBITDA = daily EV / TTM EBITDA). UAA excluded from the mean. Selected TV is Gordon implied, not the PitchBook average. Alo EV/EBITDA is n.a.</t>
         </is>
       </c>
     </row>
@@ -5380,22 +5613,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId20"/>
-    <hyperlink ref="C28" location="'Comps'!E26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId21"/>
-    <hyperlink ref="C51" location="'DCF'!E48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C52" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId14"/>
+    <hyperlink ref="C35" location="'Comps'!E33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId15"/>
+    <hyperlink ref="C58" location="'DCF'!E48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C59" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C62" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/LULU/LULU_DCF_Valuation_Model.xlsx
+++ b/LULU/LULU_DCF_Valuation_Model.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,11 +25,11 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0x"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -192,8 +193,56 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="000000CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="000000CC"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
       <color rgb="000000CC"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <color rgb="000000CC"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -240,13 +289,6 @@
     <font>
       <name val="Garamond"/>
       <b val="1"/>
-      <color rgb="000000CC"/>
-      <sz val="10"/>
-      <u val="single"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
@@ -267,12 +309,6 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Garamond"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Garamond"/>
@@ -363,7 +399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -464,26 +500,88 @@
     <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -491,7 +589,7 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -500,7 +598,7 @@
     <xf numFmtId="165" fontId="35" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -512,96 +610,81 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="45" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="48" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +699,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="45" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="51" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -984,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B23"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1057,51 +1140,66 @@
     <row r="15">
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>WACC  •  DCF (base case + sensitivity)  •  Scenarios  •  Comps / Football Field</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
+          <t>WACC  •  Revenue Drivers  •  Scenarios  •  DCF  •  Comps / Football Field</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>ASSUMPTIONS MEMO (1-page PDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>LULU_Assumptions_Memo.pdf — justifications, Ctrl+F anchors, and strategic context
+Ctrl+F: Open the linked PDF for a single-page summary of all red assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>SOURCES</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="36" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>SEC EDGAR filings, CIK 0001397187 (Form 10-K, FY2025)
 Ctrl+F: Ctrl+F "10-K" → FY2025 accession 0001397187-26-000020</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+    <row r="21" ht="36" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>FY2025 Form 10-K (ended Feb 1, 2026)
 Ctrl+F: Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+    <row r="22" ht="36" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)
 Ctrl+F: Ctrl+F "decline of 5% to 7%" | "$10.350 billion to $10.500 billion" | "$9.48 to $9.73"</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+    <row r="23" ht="36" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Current share price (NASDAQ: LULU)
 Ctrl+F: Ctrl+F "LULU" → Last Sale or Previous Close price</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="11" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>Built from scratch for the GIS IR selection assignment.</t>
         </is>
@@ -1109,10 +1207,11 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2880,6 +2979,2057 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="42" t="inlineStr">
+        <is>
+          <t>BOTTOM-UP REVENUE DRIVER SCHEDULE (FY2026E–FY2030E)</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+      <c r="H1" s="13" t="n"/>
+      <c r="I1" s="13" t="n"/>
+      <c r="J1" s="13" t="n"/>
+      <c r="K1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>FY2025A = Firecrawl-ingested 10-K anchors (blue). FY26–30 = red operational assumptions. Consolidated revenue cross-checks to Scenarios base case.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>Justification (~20 words)</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>Source (click)</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="inlineStr">
+        <is>
+          <t>Ctrl+F (prove number)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="44" t="inlineStr">
+        <is>
+          <t>I. STORE FLEET &amp; SQUARE FOOTAGE (company-operated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="45" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D5" s="46" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E5" s="47" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="G5" s="47" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="H5" s="47" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="I5" s="47" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="J5" s="47" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K5" s="47" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas — beginning stores</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="n">
+        <v>462</v>
+      </c>
+      <c r="F6" s="35">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="G6" s="35">
+        <f>F9</f>
+        <v/>
+      </c>
+      <c r="H6" s="35">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="I6" s="35">
+        <f>H9</f>
+        <v/>
+      </c>
+      <c r="J6" s="35">
+        <f>I9</f>
+        <v/>
+      </c>
+      <c r="K6" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas — openings</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>Store openings skew to China (+20 FY26) vs mature Americas (+8). Anchored to FY25 +44 net stores and 11% sq-ft growth.</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Total company-operated stores" → 811 (FY25). FY25 added 44 net stores; model skews openings to China.</t>
+        </is>
+      </c>
+      <c r="F7" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G7" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I7" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas — closures</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Closures assume 2–3 per mature region annually as leases roll; immaterial vs openings in expansion markets.</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "lease" / store fleet — immaterial closures vs expansion; 2–3 per mature region.</t>
+        </is>
+      </c>
+      <c r="F8" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas — ending stores</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Americas" → FY2025 ending stores 476.</t>
+        </is>
+      </c>
+      <c r="E9" s="49" t="n">
+        <v>476</v>
+      </c>
+      <c r="F9" s="53">
+        <f>F6+F7-F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="53">
+        <f>G6+G7-G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="53">
+        <f>H6+H7-H8</f>
+        <v/>
+      </c>
+      <c r="I9" s="53">
+        <f>I6+I7-I8</f>
+        <v/>
+      </c>
+      <c r="J9" s="53">
+        <f>J6+J7-J8</f>
+        <v/>
+      </c>
+      <c r="K9" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland — beginning stores</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="n">
+        <v>151</v>
+      </c>
+      <c r="F10" s="35">
+        <f>E13</f>
+        <v/>
+      </c>
+      <c r="G10" s="35">
+        <f>F13</f>
+        <v/>
+      </c>
+      <c r="H10" s="35">
+        <f>G13</f>
+        <v/>
+      </c>
+      <c r="I10" s="35">
+        <f>H13</f>
+        <v/>
+      </c>
+      <c r="J10" s="35">
+        <f>I13</f>
+        <v/>
+      </c>
+      <c r="K10" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland — openings</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>Store openings skew to China (+20 FY26) vs mature Americas (+8). Anchored to FY25 +44 net stores and 11% sq-ft growth.</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Total company-operated stores" → 811 (FY25). FY25 added 44 net stores; model skews openings to China.</t>
+        </is>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="H11" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="I11" s="51" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="51" t="n">
+        <v>12</v>
+      </c>
+      <c r="K11" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland — closures</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Closures assume 2–3 per mature region annually as leases roll; immaterial vs openings in expansion markets.</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "lease" / store fleet — immaterial closures vs expansion; 2–3 per mature region.</t>
+        </is>
+      </c>
+      <c r="F12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland — ending stores</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "China Mainland" → FY2025 ending stores 172.</t>
+        </is>
+      </c>
+      <c r="E13" s="49" t="n">
+        <v>172</v>
+      </c>
+      <c r="F13" s="53">
+        <f>F10+F11-F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="53">
+        <f>G10+G11-G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="53">
+        <f>H10+H11-H12</f>
+        <v/>
+      </c>
+      <c r="I13" s="53">
+        <f>I10+I11-I12</f>
+        <v/>
+      </c>
+      <c r="J13" s="53">
+        <f>J10+J11-J12</f>
+        <v/>
+      </c>
+      <c r="K13" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World — beginning stores</t>
+        </is>
+      </c>
+      <c r="E14" s="49" t="n">
+        <v>154</v>
+      </c>
+      <c r="F14" s="35">
+        <f>E17</f>
+        <v/>
+      </c>
+      <c r="G14" s="35">
+        <f>F17</f>
+        <v/>
+      </c>
+      <c r="H14" s="35">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="I14" s="35">
+        <f>H17</f>
+        <v/>
+      </c>
+      <c r="J14" s="35">
+        <f>I17</f>
+        <v/>
+      </c>
+      <c r="K14" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World — openings</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>Store openings skew to China (+20 FY26) vs mature Americas (+8). Anchored to FY25 +44 net stores and 11% sq-ft growth.</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Total company-operated stores" → 811 (FY25). FY25 added 44 net stores; model skews openings to China.</t>
+        </is>
+      </c>
+      <c r="F15" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H15" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World — closures</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Closures assume 2–3 per mature region annually as leases roll; immaterial vs openings in expansion markets.</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "lease" / store fleet — immaterial closures vs expansion; 2–3 per mature region.</t>
+        </is>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World — ending stores</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Rest of World" → FY2025 ending stores 163.</t>
+        </is>
+      </c>
+      <c r="E17" s="49" t="n">
+        <v>163</v>
+      </c>
+      <c r="F17" s="53">
+        <f>F14+F15-F16</f>
+        <v/>
+      </c>
+      <c r="G17" s="53">
+        <f>G14+G15-G16</f>
+        <v/>
+      </c>
+      <c r="H17" s="53">
+        <f>H14+H15-H16</f>
+        <v/>
+      </c>
+      <c r="I17" s="53">
+        <f>I14+I15-I16</f>
+        <v/>
+      </c>
+      <c r="J17" s="53">
+        <f>J14+J15-J16</f>
+        <v/>
+      </c>
+      <c r="K17" s="50" t="inlineStr">
+        <is>
+          <t>stores</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>Total ending stores</t>
+        </is>
+      </c>
+      <c r="E18" s="54" t="n">
+        <v>811</v>
+      </c>
+      <c r="F18" s="53">
+        <f>F9+F13+F17</f>
+        <v/>
+      </c>
+      <c r="G18" s="53">
+        <f>G9+G13+G17</f>
+        <v/>
+      </c>
+      <c r="H18" s="53">
+        <f>H9+H13+H17</f>
+        <v/>
+      </c>
+      <c r="I18" s="53">
+        <f>I9+I13+I17</f>
+        <v/>
+      </c>
+      <c r="J18" s="53">
+        <f>J9+J13+J17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="34" t="inlineStr">
+        <is>
+          <t>Avg square feet per store</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>4,367 avg sq ft/store = implied FY25 total sq ft / 811 stores. Modest expansion to 4,500 by FY30.</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: sales per square foot</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "sales per square foot were $1,426" → implied 3.54M sq ft / 811 stores ≈ 4,367 sq ft.</t>
+        </is>
+      </c>
+      <c r="E19" s="51" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G19" s="51" t="n">
+        <v>4425</v>
+      </c>
+      <c r="H19" s="51" t="n">
+        <v>4450</v>
+      </c>
+      <c r="I19" s="51" t="n">
+        <v>4475</v>
+      </c>
+      <c r="J19" s="51" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K19" s="50" t="inlineStr">
+        <is>
+          <t>sq ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="34" t="inlineStr">
+        <is>
+          <t>Total square footage (end stores × avg sq ft)</t>
+        </is>
+      </c>
+      <c r="E20" s="35">
+        <f>E18*E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="35">
+        <f>F18*F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="35">
+        <f>G18*G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="35">
+        <f>H18*H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="35">
+        <f>I18*I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="35">
+        <f>J18*J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="50" t="inlineStr">
+        <is>
+          <t>sq ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>II. STORE PRODUCTIVITY (brick &amp; mortar channel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B23" s="46" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C23" s="46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D23" s="46" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E23" s="47" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="F23" s="48" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="G23" s="47" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="H23" s="47" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="I23" s="47" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="J23" s="47" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K23" s="47" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="34" t="inlineStr">
+        <is>
+          <t>Sales per square foot ($)</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>FY26 SPSF $1,380 reflects Americas traffic/conversion pressure; recovers toward $1,440 by FY30.</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: comparable sales &amp; SPSF</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "sales per square foot were $1,426" → FY25 reported $1,426; FY26 model $1,380 on traffic pressure.</t>
+        </is>
+      </c>
+      <c r="E24" s="51" t="n">
+        <v>1426</v>
+      </c>
+      <c r="F24" s="51" t="n">
+        <v>1360</v>
+      </c>
+      <c r="G24" s="51" t="n">
+        <v>1380</v>
+      </c>
+      <c r="H24" s="51" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I24" s="51" t="n">
+        <v>1420</v>
+      </c>
+      <c r="J24" s="51" t="n">
+        <v>1440</v>
+      </c>
+      <c r="K24" s="50" t="inlineStr">
+        <is>
+          <t>$/sq ft</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas — comparable sales growth</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>FY26 Americas comp −4% vs FY25 −3% (10-K). China +14% vs +20% reported; RoW moderates from +9%.</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segment comp sales</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Americas comparable sales decreased 3%" / "China Mainland comparable sales increased 20%"</t>
+        </is>
+      </c>
+      <c r="E25" s="55" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F25" s="55" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="G25" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I25" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="J25" s="55" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K25" s="50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland — comparable sales growth</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>FY26 Americas comp −4% vs FY25 −3% (10-K). China +14% vs +20% reported; RoW moderates from +9%.</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segment comp sales</t>
+        </is>
+      </c>
+      <c r="D26" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Americas comparable sales decreased 3%" / "China Mainland comparable sales increased 20%"</t>
+        </is>
+      </c>
+      <c r="E26" s="55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F26" s="55" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G26" s="55" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H26" s="55" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="55" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J26" s="55" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K26" s="50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World — comparable sales growth</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>FY26 Americas comp −4% vs FY25 −3% (10-K). China +14% vs +20% reported; RoW moderates from +9%.</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segment comp sales</t>
+        </is>
+      </c>
+      <c r="D27" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Americas comparable sales decreased 3%" / "China Mainland comparable sales increased 20%"</t>
+        </is>
+      </c>
+      <c r="E27" s="55" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F27" s="55" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G27" s="55" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H27" s="55" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I27" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="J27" s="55" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K27" s="50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>Prior-year store channel revenue ($000)</t>
+        </is>
+      </c>
+      <c r="E28" s="56" t="n">
+        <v>5049744</v>
+      </c>
+      <c r="K28" s="50" t="inlineStr">
+        <is>
+          <t>$000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>Comparable store revenue ($000)</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="n">
+        <v>5049744</v>
+      </c>
+      <c r="F29" s="35" t="inlineStr">
+        <is>
+          <t>(E28*0.71*(1+F25)+E28*0.16*(1+F26)+E28*0.13*(1+F27))</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="inlineStr">
+        <is>
+          <t>(F28*0.71*(1+G25)+F28*0.16*(1+G26)+F28*0.13*(1+G27))</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="inlineStr">
+        <is>
+          <t>(G28*0.71*(1+H25)+G28*0.16*(1+H26)+G28*0.13*(1+H27))</t>
+        </is>
+      </c>
+      <c r="I29" s="35" t="inlineStr">
+        <is>
+          <t>(H28*0.71*(1+I25)+H28*0.16*(1+I26)+H28*0.13*(1+I27))</t>
+        </is>
+      </c>
+      <c r="J29" s="35" t="inlineStr">
+        <is>
+          <t>(I28*0.71*(1+J25)+I28*0.16*(1+J26)+I28*0.13*(1+J27))</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>Net new store revenue contribution ($000)</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>New-store contribution = net openings × sq ft × SPSF × 55% first-year ramp (standard retail maturity).</t>
+        </is>
+      </c>
+      <c r="C30" s="57" t="inlineStr">
+        <is>
+          <t>Revenue Drivers tab: formula</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>Formula: net openings × sq ft × SPSF / 1000 × 55% ramp. Not a sourced print.</t>
+        </is>
+      </c>
+      <c r="E30" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="35">
+        <f>(F7-F8+F11-F12+F15-F16)*F19*F24/1000*0.55</f>
+        <v/>
+      </c>
+      <c r="G30" s="35">
+        <f>(G7-G8+G11-G12+G15-G16)*G19*G24/1000*0.55</f>
+        <v/>
+      </c>
+      <c r="H30" s="35">
+        <f>(H7-H8+H11-H12+H15-H16)*H19*H24/1000*0.55</f>
+        <v/>
+      </c>
+      <c r="I30" s="35">
+        <f>(I7-I8+I11-I12+I15-I16)*I19*I24/1000*0.55</f>
+        <v/>
+      </c>
+      <c r="J30" s="35">
+        <f>(J7-J8+J11-J12+J15-J16)*J19*J24/1000*0.55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="inlineStr">
+        <is>
+          <t>Store channel revenue ($000)</t>
+        </is>
+      </c>
+      <c r="E31" s="54" t="n">
+        <v>5049744</v>
+      </c>
+      <c r="F31" s="53">
+        <f>F29+F30</f>
+        <v/>
+      </c>
+      <c r="G31" s="53">
+        <f>G29+G30</f>
+        <v/>
+      </c>
+      <c r="H31" s="53">
+        <f>H29+H30</f>
+        <v/>
+      </c>
+      <c r="I31" s="53">
+        <f>I29+I30</f>
+        <v/>
+      </c>
+      <c r="J31" s="53">
+        <f>J29+J30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: fleet traffic (millions of visits)</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Fleet traffic memo line — not a separate FCF item. Calibrated to FY25 store productivity commentary.</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store traffic commentary</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "store traffic" → lower traffic in Americas; memo line only.</t>
+        </is>
+      </c>
+      <c r="E32" s="58" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F32" s="58" t="n">
+        <v>40</v>
+      </c>
+      <c r="G32" s="58" t="n">
+        <v>41</v>
+      </c>
+      <c r="H32" s="58" t="n">
+        <v>42</v>
+      </c>
+      <c r="I32" s="58" t="n">
+        <v>43</v>
+      </c>
+      <c r="J32" s="58" t="n">
+        <v>44</v>
+      </c>
+      <c r="K32" s="50" t="inlineStr">
+        <is>
+          <t>M visits</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: in-store conversion rate</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>In-store conversion memo — 10-K cites lower conversion in Americas; FY26 27% improving to 29%.</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: conversion rate commentary</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "conversion rates" → lower in Americas; in-store memo 27%→29%.</t>
+        </is>
+      </c>
+      <c r="E33" s="55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F33" s="55" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G33" s="55" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="H33" s="55" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I33" s="55" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="J33" s="55" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  memo: in-store average transaction ($)</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>In-store average transaction $115–$122; supports SPSF and comp-sales bridge on the driver tab.</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: average order value commentary</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "average order value" → lower AOV in Americas; memo $115–$122.</t>
+        </is>
+      </c>
+      <c r="E34" s="59" t="n">
+        <v>118</v>
+      </c>
+      <c r="F34" s="59" t="n">
+        <v>115</v>
+      </c>
+      <c r="G34" s="59" t="n">
+        <v>116</v>
+      </c>
+      <c r="H34" s="59" t="n">
+        <v>118</v>
+      </c>
+      <c r="I34" s="59" t="n">
+        <v>120</v>
+      </c>
+      <c r="J34" s="59" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>III. DIRECT-TO-CONSUMER (e-commerce / digital)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="45" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B37" s="46" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C37" s="46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D37" s="46" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E37" s="47" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="F37" s="48" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="G37" s="47" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="H37" s="47" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="I37" s="47" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="J37" s="47" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K37" s="47" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="34" t="inlineStr">
+        <is>
+          <t>Unique digital sessions (millions)</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>485M FY25 sessions implied from reported e-comm revenue / conv / AOV. FY26 −3% on Americas softness.</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: e-commerce revenue</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "E-commerce" → 4,918,697 ($000). Sessions implied from revenue / conv / AOV.</t>
+        </is>
+      </c>
+      <c r="E38" s="51" t="n">
+        <v>485</v>
+      </c>
+      <c r="F38" s="51" t="n">
+        <v>485</v>
+      </c>
+      <c r="G38" s="51" t="n">
+        <v>505</v>
+      </c>
+      <c r="H38" s="51" t="n">
+        <v>525</v>
+      </c>
+      <c r="I38" s="51" t="n">
+        <v>545</v>
+      </c>
+      <c r="J38" s="51" t="n">
+        <v>560</v>
+      </c>
+      <c r="K38" s="50" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>Digital conversion rate</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>3.3% FY26 digital conversion vs 3.5% pressure cited in 10-K Americas; gradual recovery to 3.6%.</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: digital / traffic commentary</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "lower conversion rates" (Americas MD&amp;A). FY26 model 3.3% digital conversion.</t>
+        </is>
+      </c>
+      <c r="E39" s="55" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="F39" s="55" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="G39" s="55" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="H39" s="55" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="I39" s="55" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J39" s="55" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>Digital average order value ($)</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>AOV $305 FY26 on promo intensity; steps to $315 by FY30 as mix normalizes.</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: e-commerce revenue</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "average order value" (Americas MD&amp;A). FY26 model $305 AOV.</t>
+        </is>
+      </c>
+      <c r="E40" s="59" t="n">
+        <v>307</v>
+      </c>
+      <c r="F40" s="59" t="n">
+        <v>305</v>
+      </c>
+      <c r="G40" s="59" t="n">
+        <v>308</v>
+      </c>
+      <c r="H40" s="59" t="n">
+        <v>310</v>
+      </c>
+      <c r="I40" s="59" t="n">
+        <v>312</v>
+      </c>
+      <c r="J40" s="59" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="52" t="inlineStr">
+        <is>
+          <t>E-commerce revenue ($000)</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "E-commerce" → 4,918,697 ($000 FY2025). Forward = sessions × conversion × AOV.</t>
+        </is>
+      </c>
+      <c r="E41" s="54" t="n">
+        <v>4918697</v>
+      </c>
+      <c r="F41" s="53">
+        <f>F38*1000000*F39*F40/1000</f>
+        <v/>
+      </c>
+      <c r="G41" s="53">
+        <f>G38*1000000*G39*G40/1000</f>
+        <v/>
+      </c>
+      <c r="H41" s="53">
+        <f>H38*1000000*H39*H40/1000</f>
+        <v/>
+      </c>
+      <c r="I41" s="53">
+        <f>I38*1000000*I39*I40/1000</f>
+        <v/>
+      </c>
+      <c r="J41" s="53">
+        <f>J38*1000000*J39*J40/1000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>IV. OTHER CHANNELS, GEOGRAPHY &amp; PRODUCT MIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="45" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B44" s="46" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C44" s="46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D44" s="46" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E44" s="47" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="F44" s="48" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="G44" s="47" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="H44" s="47" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="I44" s="47" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="J44" s="47" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K44" s="47" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>Other channels (wholesale / license / outlets) ($000)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Other channels (wholesale/license/outlets) held at FY25 $1.13B base; low-single-digit growth thereafter.</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: channel revenue table</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Company-operated stores" and "E-commerce" → residual other channels ≈ $1.13B.</t>
+        </is>
+      </c>
+      <c r="E45" s="56" t="n">
+        <v>1134159</v>
+      </c>
+      <c r="F45" s="35">
+        <f>E45*(1+-0.02)</f>
+        <v/>
+      </c>
+      <c r="G45" s="35">
+        <f>F45*(1+0.0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="35">
+        <f>G45*(1+0.02)</f>
+        <v/>
+      </c>
+      <c r="I45" s="35">
+        <f>H45*(1+0.02)</f>
+        <v/>
+      </c>
+      <c r="J45" s="35">
+        <f>I45*(1+0.02)</f>
+        <v/>
+      </c>
+      <c r="K45" s="50" t="inlineStr">
+        <is>
+          <t>$000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Americas net revenue ($000)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>Geographic split scales with consolidated growth; FY25 Americas 70.7% of revenue per 10-K segment table.</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Americas" segment table → $7,847,044 net revenue (70.7%).</t>
+        </is>
+      </c>
+      <c r="E46" s="56" t="n">
+        <v>7847044</v>
+      </c>
+      <c r="F46" s="35">
+        <f>E46*(F31+F41+F45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="G46" s="35">
+        <f>E46*(G31+G41+G45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="H46" s="35">
+        <f>E46*(H31+H41+H45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="I46" s="35">
+        <f>E46*(I31+I41+I45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="J46" s="35">
+        <f>E46*(J31+J41+J45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="K46" s="50" t="inlineStr">
+        <is>
+          <t>$000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  China Mainland net revenue ($000)</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>China 15.8% of FY25 revenue; fastest comp and store growth — expansion market in the driver schedule.</t>
+        </is>
+      </c>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "China Mainland" segment → $1,754,799 net revenue (15.8%).</t>
+        </is>
+      </c>
+      <c r="E47" s="56" t="n">
+        <v>1754799</v>
+      </c>
+      <c r="F47" s="35">
+        <f>E47*(F31+F41+F45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="G47" s="35">
+        <f>E47*(G31+G41+G45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="H47" s="35">
+        <f>E47*(H31+H41+H45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="I47" s="35">
+        <f>E47*(I31+I41+I45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="J47" s="35">
+        <f>E47*(J31+J41+J45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="K47" s="50" t="inlineStr">
+        <is>
+          <t>$000</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Rest of World net revenue ($000)</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>Rest of World 13.5% of FY25 revenue; mid-single-digit comps and steady openings.</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "Rest of World" segment → $1,500,757 net revenue (13.5%).</t>
+        </is>
+      </c>
+      <c r="E48" s="56" t="n">
+        <v>1500757</v>
+      </c>
+      <c r="F48" s="35">
+        <f>E48*(F31+F41+F45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="G48" s="35">
+        <f>E48*(G31+G41+G45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="H48" s="35">
+        <f>E48*(H31+H41+H45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="I48" s="35">
+        <f>E48*(I31+I41+I45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="J48" s="35">
+        <f>E48*(J31+J41+J45)/(E31+E41+E45)</f>
+        <v/>
+      </c>
+      <c r="K48" s="50" t="inlineStr">
+        <is>
+          <t>$000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
+          <t>Women's % of revenue</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>Women's mix fades 62.5%→60% as men's penetrates; FY25 reported 63% women's per 10-K category disclosure.</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "women's, men's, and accessories" → 63% / 24% / 13% of net revenue.</t>
+        </is>
+      </c>
+      <c r="E49" s="55" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="F49" s="55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G49" s="55" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="H49" s="55" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="I49" s="55" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="J49" s="55" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="50" ht="28" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t>Men's % of revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>Men's mix rises 24.5%→27%; FY25 men's grew 4% vs women's 5% per 10-K category commentary.</t>
+        </is>
+      </c>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
+      <c r="D50" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "men's" category growth 4% in MD&amp;A; mix rises to 27% by FY30.</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="F50" s="55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G50" s="55" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="H50" s="55" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I50" s="55" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="J50" s="55" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
+        <is>
+          <t>Accessories &amp; other % of revenue</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>Accessories steady at 13% of revenue; FY25 accessories +8% per 10-K category disclosure.</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Ctrl+F "accessories" +8% category growth; hold 13% mix.</t>
+        </is>
+      </c>
+      <c r="E51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="G51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="J51" s="55" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>V. CONSOLIDATED REVENUE &amp; RECONCILIATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>Driver</t>
+        </is>
+      </c>
+      <c r="B54" s="46" t="inlineStr">
+        <is>
+          <t>Justification</t>
+        </is>
+      </c>
+      <c r="C54" s="46" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D54" s="46" t="inlineStr">
+        <is>
+          <t>Ctrl+F</t>
+        </is>
+      </c>
+      <c r="E54" s="47" t="inlineStr">
+        <is>
+          <t>FY2025A</t>
+        </is>
+      </c>
+      <c r="F54" s="48" t="inlineStr">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="G54" s="47" t="inlineStr">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="H54" s="47" t="inlineStr">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="I54" s="47" t="inlineStr">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="J54" s="47" t="inlineStr">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="K54" s="47" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="60" t="inlineStr">
+        <is>
+          <t>Bottom-up total revenue ($000)</t>
+        </is>
+      </c>
+      <c r="E55" s="61" t="n">
+        <v>11102600</v>
+      </c>
+      <c r="F55" s="62">
+        <f>F31+F41+F45</f>
+        <v/>
+      </c>
+      <c r="G55" s="62">
+        <f>G31+G41+G45</f>
+        <v/>
+      </c>
+      <c r="H55" s="62">
+        <f>H31+H41+H45</f>
+        <v/>
+      </c>
+      <c r="I55" s="62">
+        <f>I31+I41+I45</f>
+        <v/>
+      </c>
+      <c r="J55" s="62">
+        <f>J31+J41+J45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="34" t="inlineStr">
+        <is>
+          <t>Scenarios base-case revenue ($000)</t>
+        </is>
+      </c>
+      <c r="E56" s="56" t="n">
+        <v>11102600</v>
+      </c>
+      <c r="F56" s="35">
+        <f>Scenarios!G18</f>
+        <v/>
+      </c>
+      <c r="G56" s="35">
+        <f>Scenarios!G19</f>
+        <v/>
+      </c>
+      <c r="H56" s="35">
+        <f>Scenarios!G20</f>
+        <v/>
+      </c>
+      <c r="I56" s="35">
+        <f>Scenarios!G21</f>
+        <v/>
+      </c>
+      <c r="J56" s="35">
+        <f>Scenarios!G22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>Variance (bottom-up − scenarios) ($000)</t>
+        </is>
+      </c>
+      <c r="E57" s="35">
+        <f>E55-E56</f>
+        <v/>
+      </c>
+      <c r="F57" s="35">
+        <f>F55-F56</f>
+        <v/>
+      </c>
+      <c r="G57" s="35">
+        <f>G55-G56</f>
+        <v/>
+      </c>
+      <c r="H57" s="35">
+        <f>H55-H56</f>
+        <v/>
+      </c>
+      <c r="I57" s="35">
+        <f>I55-I56</f>
+        <v/>
+      </c>
+      <c r="J57" s="35">
+        <f>J55-J56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>Variance (%)</t>
+        </is>
+      </c>
+      <c r="E58" s="36">
+        <f>IF(E56=0,"",E57/E56)</f>
+        <v/>
+      </c>
+      <c r="F58" s="36">
+        <f>IF(F56=0,"",F57/F56)</f>
+        <v/>
+      </c>
+      <c r="G58" s="36">
+        <f>IF(G56=0,"",G57/G56)</f>
+        <v/>
+      </c>
+      <c r="H58" s="36">
+        <f>IF(H56=0,"",H57/H56)</f>
+        <v/>
+      </c>
+      <c r="I58" s="36">
+        <f>IF(I56=0,"",I57/I56)</f>
+        <v/>
+      </c>
+      <c r="J58" s="36">
+        <f>IF(J56=0,"",J57/J56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26" t="inlineStr">
+        <is>
+          <t>Note: DCF / Scenarios consolidated revenue is the valuation anchor. Drivers explain the path; minor variances are acceptable if documented.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C49" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId34"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2915,69 +5065,69 @@
       <c r="J1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="63" t="inlineStr">
         <is>
           <t>Justification (~20 words)</t>
         </is>
       </c>
-      <c r="C2" s="42" t="inlineStr">
+      <c r="C2" s="63" t="inlineStr">
         <is>
           <t>Source (click)</t>
         </is>
       </c>
-      <c r="D2" s="42" t="inlineStr">
+      <c r="D2" s="63" t="inlineStr">
         <is>
           <t>Ctrl+F (prove number)</t>
         </is>
       </c>
-      <c r="E2" s="43" t="inlineStr">
+      <c r="E2" s="64" t="inlineStr">
         <is>
           <t>FY2025A</t>
         </is>
       </c>
-      <c r="F2" s="44" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>FY2026E</t>
         </is>
       </c>
-      <c r="G2" s="44" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>FY2027E</t>
         </is>
       </c>
-      <c r="H2" s="44" t="inlineStr">
+      <c r="H2" s="65" t="inlineStr">
         <is>
           <t>FY2028E</t>
         </is>
       </c>
-      <c r="I2" s="44" t="inlineStr">
+      <c r="I2" s="65" t="inlineStr">
         <is>
           <t>FY2029E</t>
         </is>
       </c>
-      <c r="J2" s="44" t="inlineStr">
+      <c r="J2" s="65" t="inlineStr">
         <is>
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="K2" s="45" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Δ vs Scenarios</t>
         </is>
       </c>
-      <c r="L2" s="42" t="inlineStr">
+      <c r="L2" s="63" t="inlineStr">
         <is>
           <t>Alt. source</t>
         </is>
       </c>
-      <c r="M2" s="42" t="inlineStr">
+      <c r="M2" s="63" t="inlineStr">
         <is>
           <t>Alt. Ctrl+F</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="46" t="inlineStr">
+      <c r="A3" s="67" t="inlineStr">
         <is>
           <t>Forecast drivers linked to Scenarios tab → Base case (column G)</t>
         </is>
@@ -2987,14 +5137,28 @@
           <t>Ctrl+F "Net revenue" → 11,102,600 or "Depreciation and amortization" → 496,228 on this 10-K HTML file</t>
         </is>
       </c>
-      <c r="E3" s="47" t="inlineStr">
+      <c r="E3" s="68" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
       </c>
-      <c r="K3" s="48" t="inlineStr">
+      <c r="K3" s="69" t="inlineStr">
         <is>
           <t>(should be 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Assumptions Memo (PDF)
+Ctrl+F: 1-page summary: justifications, Ctrl+F anchors, WACC, terminal multiple.</t>
+        </is>
+      </c>
+      <c r="C4" s="70" t="inlineStr">
+        <is>
+          <t>Revenue Drivers tab
+Ctrl+F: Bottom-up store / DTC / category schedule (FY26–30).</t>
         </is>
       </c>
     </row>
@@ -3004,30 +5168,30 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="71" t="n">
         <v>11102600</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="72">
         <f>Scenarios!G18</f>
         <v/>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="72">
         <f>Scenarios!G19</f>
         <v/>
       </c>
-      <c r="H5" s="50">
+      <c r="H5" s="72">
         <f>Scenarios!G20</f>
         <v/>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="72">
         <f>Scenarios!G21</f>
         <v/>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="72">
         <f>Scenarios!G22</f>
         <v/>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="73">
         <f>IF(MAX(ABS(F5-Scenarios!$G$18),ABS(G5-Scenarios!$G$19),ABS(H5-Scenarios!$G$20),ABS(I5-Scenarios!$G$21),ABS(J5-Scenarios!$G$22))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3056,23 +5220,23 @@
 Also: Ctrl+F "Revenue Growth Forecast (3Y)" → 2.26%. That is the unique line (do not search "Net revenue"). Model FY27–30 uses 2.3%.</t>
         </is>
       </c>
-      <c r="F6" s="52">
+      <c r="F6" s="74">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="52">
+      <c r="G6" s="74">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="52">
+      <c r="H6" s="74">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="52">
+      <c r="I6" s="74">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="52">
+      <c r="J6" s="74">
         <f>J5/I5-1</f>
         <v/>
       </c>
@@ -3101,27 +5265,27 @@
 Also: Ctrl+F "19.9%" (one hit) → Operating margin decreased 380 basis points to 19.9%. That is FY25 OM. Do not search the words Income from operations (17 hits). Model FY30 15.5% is a partial-recovery assumption.</t>
         </is>
       </c>
-      <c r="F7" s="52">
+      <c r="F7" s="74">
         <f>Scenarios!G23</f>
         <v/>
       </c>
-      <c r="G7" s="52">
+      <c r="G7" s="74">
         <f>Scenarios!G24</f>
         <v/>
       </c>
-      <c r="H7" s="52">
+      <c r="H7" s="74">
         <f>Scenarios!G25</f>
         <v/>
       </c>
-      <c r="I7" s="52">
+      <c r="I7" s="74">
         <f>Scenarios!G26</f>
         <v/>
       </c>
-      <c r="J7" s="52">
+      <c r="J7" s="74">
         <f>Scenarios!G27</f>
         <v/>
       </c>
-      <c r="K7" s="51">
+      <c r="K7" s="73">
         <f>IF(MAX(ABS(F7-Scenarios!$G$23),ABS(G7-Scenarios!$G$24),ABS(H7-Scenarios!$G$25),ABS(I7-Scenarios!$G$26),ABS(J7-Scenarios!$G$27))&lt;0.0001,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3147,7 +5311,7 @@
           <t>Ctrl+F "134.5 million" → IEEPA tariff refunds reduced COGS. Add this dollar amount to FY26 EBIT only. Full-year boost = 134.5 / FY26 sales ≈ 1.3ppt, not 5.6ppt.</t>
         </is>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="71" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="33">
@@ -3173,7 +5337,7 @@
           <t>EBIT (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E9" s="53" t="n">
+      <c r="E9" s="75" t="n">
         <v>2210615</v>
       </c>
       <c r="F9" s="37">
@@ -3196,7 +5360,7 @@
         <f>Scenarios!G32</f>
         <v/>
       </c>
-      <c r="K9" s="54">
+      <c r="K9" s="76">
         <f>IF(MAX(ABS(F9-Scenarios!$G$28),ABS(G9-Scenarios!$G$29),ABS(H9-Scenarios!$G$30),ABS(I9-Scenarios!$G$31),ABS(J9-Scenarios!$G$32))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3207,26 +5371,26 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E10" s="55" t="n">
+      <c r="E10" s="77" t="n">
         <v>0.1991078666258354</v>
       </c>
-      <c r="F10" s="52">
+      <c r="F10" s="74">
         <f>F9/F5</f>
         <v/>
       </c>
-      <c r="G10" s="52">
+      <c r="G10" s="74">
         <f>G9/G5</f>
         <v/>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="74">
         <f>H9/H5</f>
         <v/>
       </c>
-      <c r="I10" s="52">
+      <c r="I10" s="74">
         <f>I9/I5</f>
         <v/>
       </c>
-      <c r="J10" s="52">
+      <c r="J10" s="74">
         <f>J9/J5</f>
         <v/>
       </c>
@@ -3237,23 +5401,23 @@
           <t>Less: cash taxes on EBIT</t>
         </is>
       </c>
-      <c r="F11" s="50">
+      <c r="F11" s="72">
         <f>-Scenarios!G28*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="G11" s="50">
+      <c r="G11" s="72">
         <f>-Scenarios!G29*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="H11" s="50">
+      <c r="H11" s="72">
         <f>-Scenarios!G30*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="I11" s="50">
+      <c r="I11" s="72">
         <f>-Scenarios!G31*Scenarios!$G$11</f>
         <v/>
       </c>
-      <c r="J11" s="50">
+      <c r="J11" s="72">
         <f>-Scenarios!G32*Scenarios!$G$11</f>
         <v/>
       </c>
@@ -3284,7 +5448,7 @@
         <f>Scenarios!G37</f>
         <v/>
       </c>
-      <c r="K12" s="54">
+      <c r="K12" s="76">
         <f>IF(MAX(ABS(F12-Scenarios!$G$33),ABS(G12-Scenarios!$G$34),ABS(H12-Scenarios!$G$35),ABS(I12-Scenarios!$G$36),ABS(J12-Scenarios!$G$37))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3337,27 +5501,27 @@
           <t>Plus: depreciation &amp; amortization</t>
         </is>
       </c>
-      <c r="F14" s="50">
+      <c r="F14" s="72">
         <f>Scenarios!G38</f>
         <v/>
       </c>
-      <c r="G14" s="50">
+      <c r="G14" s="72">
         <f>Scenarios!G39</f>
         <v/>
       </c>
-      <c r="H14" s="50">
+      <c r="H14" s="72">
         <f>Scenarios!G40</f>
         <v/>
       </c>
-      <c r="I14" s="50">
+      <c r="I14" s="72">
         <f>Scenarios!G41</f>
         <v/>
       </c>
-      <c r="J14" s="50">
+      <c r="J14" s="72">
         <f>Scenarios!G42</f>
         <v/>
       </c>
-      <c r="K14" s="51">
+      <c r="K14" s="73">
         <f>IF(MAX(ABS(F14-Scenarios!$G$38),ABS(G14-Scenarios!$G$39),ABS(H14-Scenarios!$G$40),ABS(I14-Scenarios!$G$41),ABS(J14-Scenarios!$G$42))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3423,27 +5587,27 @@
           <t>Less: capital expenditures</t>
         </is>
       </c>
-      <c r="F16" s="50">
+      <c r="F16" s="72">
         <f>-Scenarios!G43</f>
         <v/>
       </c>
-      <c r="G16" s="50">
+      <c r="G16" s="72">
         <f>-Scenarios!G44</f>
         <v/>
       </c>
-      <c r="H16" s="50">
+      <c r="H16" s="72">
         <f>-Scenarios!G45</f>
         <v/>
       </c>
-      <c r="I16" s="50">
+      <c r="I16" s="72">
         <f>-Scenarios!G46</f>
         <v/>
       </c>
-      <c r="J16" s="50">
+      <c r="J16" s="72">
         <f>-Scenarios!G47</f>
         <v/>
       </c>
-      <c r="K16" s="51">
+      <c r="K16" s="73">
         <f>IF(MAX(ABS(F16+Scenarios!$G$43),ABS(G16+Scenarios!$G$44),ABS(H16+Scenarios!$G$45),ABS(I16+Scenarios!$G$46),ABS(J16+Scenarios!$G$47))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3553,30 +5717,30 @@
           <t>Ctrl+F "Accounts receivable, net" (one hit on the BS) → 190,657. 190,657 / 11,102,600 = 1.7% of sales. Lives inside the NWC line below.</t>
         </is>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="71" t="n">
         <v>190657</v>
       </c>
-      <c r="F19" s="50">
+      <c r="F19" s="72">
         <f>Scenarios!G48</f>
         <v/>
       </c>
-      <c r="G19" s="50">
+      <c r="G19" s="72">
         <f>Scenarios!G49</f>
         <v/>
       </c>
-      <c r="H19" s="50">
+      <c r="H19" s="72">
         <f>Scenarios!G50</f>
         <v/>
       </c>
-      <c r="I19" s="50">
+      <c r="I19" s="72">
         <f>Scenarios!G51</f>
         <v/>
       </c>
-      <c r="J19" s="50">
+      <c r="J19" s="72">
         <f>Scenarios!G52</f>
         <v/>
       </c>
-      <c r="K19" s="51">
+      <c r="K19" s="73">
         <f>IF(MAX(ABS(F19-Scenarios!$G$48),ABS(G19-Scenarios!$G$49),ABS(H19-Scenarios!$G$50),ABS(I19-Scenarios!$G$51),ABS(J19-Scenarios!$G$52))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3587,27 +5751,27 @@
           <t>(Increase)/decrease in NWC (includes AR)</t>
         </is>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="72">
         <f>-Scenarios!G53</f>
         <v/>
       </c>
-      <c r="G20" s="50">
+      <c r="G20" s="72">
         <f>-Scenarios!G54</f>
         <v/>
       </c>
-      <c r="H20" s="50">
+      <c r="H20" s="72">
         <f>-Scenarios!G55</f>
         <v/>
       </c>
-      <c r="I20" s="50">
+      <c r="I20" s="72">
         <f>-Scenarios!G56</f>
         <v/>
       </c>
-      <c r="J20" s="50">
+      <c r="J20" s="72">
         <f>-Scenarios!G57</f>
         <v/>
       </c>
-      <c r="K20" s="51">
+      <c r="K20" s="73">
         <f>IF(MAX(ABS(F20+Scenarios!$G$53),ABS(G20+Scenarios!$G$54),ABS(H20+Scenarios!$G$55),ABS(I20+Scenarios!$G$56),ABS(J20+Scenarios!$G$57))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3625,27 +5789,27 @@
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="78">
         <f>Scenarios!G58</f>
         <v/>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="78">
         <f>Scenarios!G59</f>
         <v/>
       </c>
-      <c r="H22" s="56">
+      <c r="H22" s="78">
         <f>Scenarios!G60</f>
         <v/>
       </c>
-      <c r="I22" s="56">
+      <c r="I22" s="78">
         <f>Scenarios!G61</f>
         <v/>
       </c>
-      <c r="J22" s="56">
+      <c r="J22" s="78">
         <f>Scenarios!G62</f>
         <v/>
       </c>
-      <c r="K22" s="54">
+      <c r="K22" s="76">
         <f>IF(MAX(ABS(F22-Scenarios!$G$58),ABS(G22-Scenarios!$G$59),ABS(H22-Scenarios!$G$60),ABS(I22-Scenarios!$G$61),ABS(J22-Scenarios!$G$62))&lt;0.5,"OK","CHECK")</f>
         <v/>
       </c>
@@ -3656,19 +5820,19 @@
           <t>Discount period (years)</t>
         </is>
       </c>
-      <c r="F23" s="57" t="n">
+      <c r="F23" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="57" t="n">
+      <c r="G23" s="79" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="57" t="n">
+      <c r="H23" s="79" t="n">
         <v>3</v>
       </c>
-      <c r="I23" s="57" t="n">
+      <c r="I23" s="79" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="57" t="n">
+      <c r="J23" s="79" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3678,23 +5842,23 @@
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="F24" s="58">
+      <c r="F24" s="80">
         <f>1/(1+Scenarios!$G$9)^F23</f>
         <v/>
       </c>
-      <c r="G24" s="58">
+      <c r="G24" s="80">
         <f>1/(1+Scenarios!$G$9)^G23</f>
         <v/>
       </c>
-      <c r="H24" s="58">
+      <c r="H24" s="80">
         <f>1/(1+Scenarios!$G$9)^H23</f>
         <v/>
       </c>
-      <c r="I24" s="58">
+      <c r="I24" s="80">
         <f>1/(1+Scenarios!$G$9)^I23</f>
         <v/>
       </c>
-      <c r="J24" s="58">
+      <c r="J24" s="80">
         <f>1/(1+Scenarios!$G$9)^J23</f>
         <v/>
       </c>
@@ -3